--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,21 @@
     <t>['2', '43']</t>
   </si>
   <si>
+    <t>['47', '90+4']</t>
+  </si>
+  <si>
+    <t>['43', '48', '72']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['48', '56', '60', '69']</t>
+  </si>
+  <si>
+    <t>['51', '77']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -949,9 +964,6 @@
     <t>['12', '73']</t>
   </si>
   <si>
-    <t>['14']</t>
-  </si>
-  <si>
     <t>['43']</t>
   </si>
   <si>
@@ -1100,6 +1112,9 @@
   </si>
   <si>
     <t>['12', '63']</t>
+  </si>
+  <si>
+    <t>['20', '72']</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1923,7 +1938,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2001,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
         <v>1.58</v>
@@ -2129,7 +2144,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2335,7 +2350,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2541,7 +2556,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2747,7 +2762,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2828,7 +2843,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2953,7 +2968,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3031,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ8">
         <v>1.45</v>
@@ -3159,7 +3174,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3240,7 +3255,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ9">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3571,7 +3586,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3983,7 +3998,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4064,7 +4079,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ13">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4601,7 +4616,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4682,7 +4697,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4885,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17">
         <v>1.17</v>
@@ -5091,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5297,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19">
         <v>1.45</v>
@@ -5425,7 +5440,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6121,7 +6136,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ23">
         <v>1.45</v>
@@ -6327,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ24">
         <v>0.58</v>
@@ -6455,7 +6470,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6661,7 +6676,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6739,10 +6754,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR26">
         <v>1.18</v>
@@ -6867,7 +6882,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7279,7 +7294,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7691,7 +7706,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7772,7 +7787,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ31">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -7978,7 +7993,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ32">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8309,7 +8324,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8390,7 +8405,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ34">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR34">
         <v>1.12</v>
@@ -8515,7 +8530,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9005,7 +9020,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ37">
         <v>2.08</v>
@@ -9133,7 +9148,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9211,7 +9226,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ38">
         <v>1.42</v>
@@ -9339,7 +9354,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9751,7 +9766,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10038,7 +10053,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ42">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -10369,7 +10384,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10447,7 +10462,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ44">
         <v>0.75</v>
@@ -10575,7 +10590,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10781,7 +10796,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10862,7 +10877,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.3</v>
@@ -10987,7 +11002,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11193,7 +11208,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11274,7 +11289,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ48">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -11605,7 +11620,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11811,7 +11826,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11892,7 +11907,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -12017,7 +12032,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12095,7 +12110,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -12301,7 +12316,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ53">
         <v>1</v>
@@ -12507,7 +12522,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
         <v>1.33</v>
@@ -12841,7 +12856,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -12919,7 +12934,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56">
         <v>0.82</v>
@@ -13253,7 +13268,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13459,7 +13474,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13871,7 +13886,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14077,7 +14092,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14158,7 +14173,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ62">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.68</v>
@@ -14283,7 +14298,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14364,7 +14379,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ63">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14567,7 +14582,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ64">
         <v>1.9</v>
@@ -14773,10 +14788,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14901,7 +14916,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14979,7 +14994,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ66">
         <v>1.42</v>
@@ -15313,7 +15328,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15519,7 +15534,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15600,7 +15615,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15725,7 +15740,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15931,7 +15946,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16137,7 +16152,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16343,7 +16358,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16549,7 +16564,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16755,7 +16770,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16833,7 +16848,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ75">
         <v>0.45</v>
@@ -17373,7 +17388,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17579,7 +17594,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17657,7 +17672,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ79">
         <v>1.9</v>
@@ -17991,7 +18006,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18403,7 +18418,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18484,7 +18499,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ83">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18609,7 +18624,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19102,7 +19117,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19227,7 +19242,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19308,7 +19323,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ87">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -19511,7 +19526,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ88">
         <v>0.58</v>
@@ -19717,10 +19732,10 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ89">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.66</v>
@@ -19845,7 +19860,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -19923,7 +19938,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20257,7 +20272,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20669,7 +20684,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20875,7 +20890,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21081,7 +21096,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21162,7 +21177,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ96">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21287,7 +21302,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21365,10 +21380,10 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -21699,7 +21714,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21983,7 +21998,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ100">
         <v>0.82</v>
@@ -22111,7 +22126,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22317,7 +22332,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22398,7 +22413,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ102">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR102">
         <v>1.75</v>
@@ -22601,7 +22616,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ103">
         <v>1.33</v>
@@ -22729,7 +22744,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23141,7 +23156,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23425,10 +23440,10 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ107">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -23631,7 +23646,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
         <v>0.45</v>
@@ -23965,7 +23980,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24043,7 +24058,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ110">
         <v>0.82</v>
@@ -24171,7 +24186,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24377,7 +24392,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24455,7 +24470,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24661,7 +24676,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ113">
         <v>0.45</v>
@@ -24789,7 +24804,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="Q114">
         <v>2.25</v>
@@ -24870,7 +24885,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ114">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -24995,7 +25010,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25201,7 +25216,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25407,7 +25422,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25488,7 +25503,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ117">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25613,7 +25628,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25819,7 +25834,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26025,7 +26040,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26103,10 +26118,10 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26231,7 +26246,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26437,7 +26452,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26643,7 +26658,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26849,7 +26864,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27055,7 +27070,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27467,7 +27482,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27545,7 +27560,7 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ127">
         <v>1.33</v>
@@ -27673,7 +27688,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27754,7 +27769,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ128">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -28085,7 +28100,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28291,7 +28306,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28703,7 +28718,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29193,10 +29208,10 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ135">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR135">
         <v>1.75</v>
@@ -29321,7 +29336,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29399,7 +29414,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ136">
         <v>0.75</v>
@@ -29608,7 +29623,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ137">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -29811,7 +29826,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ138">
         <v>0.82</v>
@@ -30226,7 +30241,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ140">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -30429,7 +30444,7 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ141">
         <v>1.45</v>
@@ -30763,7 +30778,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30969,7 +30984,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31175,7 +31190,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31256,7 +31271,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ145">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR145">
         <v>1.6</v>
@@ -31381,7 +31396,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31587,7 +31602,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31793,7 +31808,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32080,7 +32095,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32205,7 +32220,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32286,7 +32301,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ150">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32411,7 +32426,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32489,7 +32504,7 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ151">
         <v>1.42</v>
@@ -32823,7 +32838,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33029,7 +33044,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33235,7 +33250,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33313,7 +33328,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ155">
         <v>0.45</v>
@@ -33519,7 +33534,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -34265,7 +34280,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34343,7 +34358,7 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ160">
         <v>1.55</v>
@@ -34677,7 +34692,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34755,7 +34770,7 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ162">
         <v>1.9</v>
@@ -35170,7 +35185,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ164">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35295,7 +35310,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35376,7 +35391,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ165">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR165">
         <v>1.91</v>
@@ -35501,7 +35516,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35707,7 +35722,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36119,7 +36134,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36325,7 +36340,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36403,7 +36418,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ170">
         <v>1.58</v>
@@ -36531,7 +36546,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36943,7 +36958,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37149,7 +37164,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37227,10 +37242,10 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ174">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -37767,7 +37782,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37845,7 +37860,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ177">
         <v>1</v>
@@ -37973,7 +37988,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38051,7 +38066,7 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ178">
         <v>1.42</v>
@@ -38385,7 +38400,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38466,7 +38481,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ180">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -38591,7 +38606,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39209,7 +39224,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39415,7 +39430,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39621,7 +39636,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39908,7 +39923,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ187">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR187">
         <v>1.79</v>
@@ -40111,7 +40126,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ188">
         <v>0.58</v>
@@ -40239,7 +40254,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40523,10 +40538,10 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR190">
         <v>1.73</v>
@@ -40857,7 +40872,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41063,7 +41078,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41269,7 +41284,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41347,7 +41362,7 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ194">
         <v>1.17</v>
@@ -41475,7 +41490,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41553,10 +41568,10 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ195">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -41681,7 +41696,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41759,7 +41774,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ196">
         <v>1.55</v>
@@ -42093,7 +42108,7 @@
         <v>224</v>
       </c>
       <c r="P198" t="s">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="Q198">
         <v>2.5</v>
@@ -42299,7 +42314,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42380,7 +42395,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ199">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42583,7 +42598,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ200">
         <v>0.45</v>
@@ -42711,7 +42726,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43329,7 +43344,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43410,7 +43425,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ204">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR204">
         <v>1.4</v>
@@ -43616,7 +43631,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ205">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR205">
         <v>1.65</v>
@@ -43741,7 +43756,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43947,7 +43962,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44153,7 +44168,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44231,7 +44246,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ208">
         <v>1.17</v>
@@ -44359,7 +44374,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44437,7 +44452,7 @@
         <v>1.6</v>
       </c>
       <c r="AP209">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ209">
         <v>1.45</v>
@@ -44565,7 +44580,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44852,7 +44867,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ211">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR211">
         <v>1.58</v>
@@ -45261,7 +45276,7 @@
         <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ213">
         <v>1.42</v>
@@ -45595,7 +45610,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45673,10 +45688,10 @@
         <v>1.55</v>
       </c>
       <c r="AP215">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ215">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -45882,7 +45897,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ216">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR216">
         <v>1.61</v>
@@ -46007,7 +46022,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46497,7 +46512,7 @@
         <v>0.5</v>
       </c>
       <c r="AP219">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ219">
         <v>0.45</v>
@@ -46831,7 +46846,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47449,7 +47464,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -48067,7 +48082,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48273,7 +48288,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48557,7 +48572,7 @@
         <v>0.5</v>
       </c>
       <c r="AP229">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ229">
         <v>0.45</v>
@@ -48636,6 +48651,1036 @@
       </c>
       <c r="BP229">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7465645</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F230">
+        <v>24</v>
+      </c>
+      <c r="G230" t="s">
+        <v>76</v>
+      </c>
+      <c r="H230" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+      <c r="L230">
+        <v>2</v>
+      </c>
+      <c r="M230">
+        <v>1</v>
+      </c>
+      <c r="N230">
+        <v>3</v>
+      </c>
+      <c r="O230" t="s">
+        <v>247</v>
+      </c>
+      <c r="P230" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q230">
+        <v>1.95</v>
+      </c>
+      <c r="R230">
+        <v>2.5</v>
+      </c>
+      <c r="S230">
+        <v>4.75</v>
+      </c>
+      <c r="T230">
+        <v>1.25</v>
+      </c>
+      <c r="U230">
+        <v>3.55</v>
+      </c>
+      <c r="V230">
+        <v>2.2</v>
+      </c>
+      <c r="W230">
+        <v>1.6</v>
+      </c>
+      <c r="X230">
+        <v>5.5</v>
+      </c>
+      <c r="Y230">
+        <v>1.13</v>
+      </c>
+      <c r="Z230">
+        <v>1.53</v>
+      </c>
+      <c r="AA230">
+        <v>4.5</v>
+      </c>
+      <c r="AB230">
+        <v>5.25</v>
+      </c>
+      <c r="AC230">
+        <v>1.03</v>
+      </c>
+      <c r="AD230">
+        <v>11</v>
+      </c>
+      <c r="AE230">
+        <v>1.18</v>
+      </c>
+      <c r="AF230">
+        <v>4.75</v>
+      </c>
+      <c r="AG230">
+        <v>1.57</v>
+      </c>
+      <c r="AH230">
+        <v>2.38</v>
+      </c>
+      <c r="AI230">
+        <v>1.62</v>
+      </c>
+      <c r="AJ230">
+        <v>2.1</v>
+      </c>
+      <c r="AK230">
+        <v>1.15</v>
+      </c>
+      <c r="AL230">
+        <v>1.15</v>
+      </c>
+      <c r="AM230">
+        <v>2.4</v>
+      </c>
+      <c r="AN230">
+        <v>2</v>
+      </c>
+      <c r="AO230">
+        <v>1.67</v>
+      </c>
+      <c r="AP230">
+        <v>2.08</v>
+      </c>
+      <c r="AQ230">
+        <v>1.54</v>
+      </c>
+      <c r="AR230">
+        <v>1.81</v>
+      </c>
+      <c r="AS230">
+        <v>1.27</v>
+      </c>
+      <c r="AT230">
+        <v>3.08</v>
+      </c>
+      <c r="AU230">
+        <v>6</v>
+      </c>
+      <c r="AV230">
+        <v>5</v>
+      </c>
+      <c r="AW230">
+        <v>13</v>
+      </c>
+      <c r="AX230">
+        <v>2</v>
+      </c>
+      <c r="AY230">
+        <v>19</v>
+      </c>
+      <c r="AZ230">
+        <v>7</v>
+      </c>
+      <c r="BA230">
+        <v>11</v>
+      </c>
+      <c r="BB230">
+        <v>2</v>
+      </c>
+      <c r="BC230">
+        <v>13</v>
+      </c>
+      <c r="BD230">
+        <v>1.53</v>
+      </c>
+      <c r="BE230">
+        <v>6.75</v>
+      </c>
+      <c r="BF230">
+        <v>2.75</v>
+      </c>
+      <c r="BG230">
+        <v>1.28</v>
+      </c>
+      <c r="BH230">
+        <v>3.3</v>
+      </c>
+      <c r="BI230">
+        <v>1.49</v>
+      </c>
+      <c r="BJ230">
+        <v>2.43</v>
+      </c>
+      <c r="BK230">
+        <v>1.79</v>
+      </c>
+      <c r="BL230">
+        <v>1.9</v>
+      </c>
+      <c r="BM230">
+        <v>2.23</v>
+      </c>
+      <c r="BN230">
+        <v>1.57</v>
+      </c>
+      <c r="BO230">
+        <v>2.8</v>
+      </c>
+      <c r="BP230">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7465646</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F231">
+        <v>24</v>
+      </c>
+      <c r="G231" t="s">
+        <v>85</v>
+      </c>
+      <c r="H231" t="s">
+        <v>88</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="L231">
+        <v>3</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>3</v>
+      </c>
+      <c r="O231" t="s">
+        <v>248</v>
+      </c>
+      <c r="P231" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q231">
+        <v>3.75</v>
+      </c>
+      <c r="R231">
+        <v>2.5</v>
+      </c>
+      <c r="S231">
+        <v>2.4</v>
+      </c>
+      <c r="T231">
+        <v>1.25</v>
+      </c>
+      <c r="U231">
+        <v>3.75</v>
+      </c>
+      <c r="V231">
+        <v>2.1</v>
+      </c>
+      <c r="W231">
+        <v>1.67</v>
+      </c>
+      <c r="X231">
+        <v>5</v>
+      </c>
+      <c r="Y231">
+        <v>1.17</v>
+      </c>
+      <c r="Z231">
+        <v>3.6</v>
+      </c>
+      <c r="AA231">
+        <v>4</v>
+      </c>
+      <c r="AB231">
+        <v>1.91</v>
+      </c>
+      <c r="AC231">
+        <v>1.01</v>
+      </c>
+      <c r="AD231">
+        <v>17</v>
+      </c>
+      <c r="AE231">
+        <v>1.15</v>
+      </c>
+      <c r="AF231">
+        <v>5.5</v>
+      </c>
+      <c r="AG231">
+        <v>1.44</v>
+      </c>
+      <c r="AH231">
+        <v>2.7</v>
+      </c>
+      <c r="AI231">
+        <v>1.44</v>
+      </c>
+      <c r="AJ231">
+        <v>2.63</v>
+      </c>
+      <c r="AK231">
+        <v>1.9</v>
+      </c>
+      <c r="AL231">
+        <v>1.25</v>
+      </c>
+      <c r="AM231">
+        <v>1.25</v>
+      </c>
+      <c r="AN231">
+        <v>1.83</v>
+      </c>
+      <c r="AO231">
+        <v>1.73</v>
+      </c>
+      <c r="AP231">
+        <v>1.92</v>
+      </c>
+      <c r="AQ231">
+        <v>1.58</v>
+      </c>
+      <c r="AR231">
+        <v>1.77</v>
+      </c>
+      <c r="AS231">
+        <v>1.5</v>
+      </c>
+      <c r="AT231">
+        <v>3.27</v>
+      </c>
+      <c r="AU231">
+        <v>6</v>
+      </c>
+      <c r="AV231">
+        <v>2</v>
+      </c>
+      <c r="AW231">
+        <v>11</v>
+      </c>
+      <c r="AX231">
+        <v>7</v>
+      </c>
+      <c r="AY231">
+        <v>17</v>
+      </c>
+      <c r="AZ231">
+        <v>9</v>
+      </c>
+      <c r="BA231">
+        <v>5</v>
+      </c>
+      <c r="BB231">
+        <v>4</v>
+      </c>
+      <c r="BC231">
+        <v>9</v>
+      </c>
+      <c r="BD231">
+        <v>2.6</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>1.58</v>
+      </c>
+      <c r="BG231">
+        <v>1.25</v>
+      </c>
+      <c r="BH231">
+        <v>3.45</v>
+      </c>
+      <c r="BI231">
+        <v>1.45</v>
+      </c>
+      <c r="BJ231">
+        <v>2.55</v>
+      </c>
+      <c r="BK231">
+        <v>1.73</v>
+      </c>
+      <c r="BL231">
+        <v>1.98</v>
+      </c>
+      <c r="BM231">
+        <v>2.12</v>
+      </c>
+      <c r="BN231">
+        <v>1.63</v>
+      </c>
+      <c r="BO231">
+        <v>2.7</v>
+      </c>
+      <c r="BP231">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7465647</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F232">
+        <v>24</v>
+      </c>
+      <c r="G232" t="s">
+        <v>86</v>
+      </c>
+      <c r="H232" t="s">
+        <v>77</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>2</v>
+      </c>
+      <c r="L232">
+        <v>1</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>2</v>
+      </c>
+      <c r="O232" t="s">
+        <v>249</v>
+      </c>
+      <c r="P232" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q232">
+        <v>2.95</v>
+      </c>
+      <c r="R232">
+        <v>2.57</v>
+      </c>
+      <c r="S232">
+        <v>3.01</v>
+      </c>
+      <c r="T232">
+        <v>1.22</v>
+      </c>
+      <c r="U232">
+        <v>3.8</v>
+      </c>
+      <c r="V232">
+        <v>2.12</v>
+      </c>
+      <c r="W232">
+        <v>1.68</v>
+      </c>
+      <c r="X232">
+        <v>4.65</v>
+      </c>
+      <c r="Y232">
+        <v>1.17</v>
+      </c>
+      <c r="Z232">
+        <v>2.45</v>
+      </c>
+      <c r="AA232">
+        <v>3.85</v>
+      </c>
+      <c r="AB232">
+        <v>2.5</v>
+      </c>
+      <c r="AC232">
+        <v>1.01</v>
+      </c>
+      <c r="AD232">
+        <v>17</v>
+      </c>
+      <c r="AE232">
+        <v>1.12</v>
+      </c>
+      <c r="AF232">
+        <v>5.75</v>
+      </c>
+      <c r="AG232">
+        <v>1.44</v>
+      </c>
+      <c r="AH232">
+        <v>2.75</v>
+      </c>
+      <c r="AI232">
+        <v>1.36</v>
+      </c>
+      <c r="AJ232">
+        <v>2.8</v>
+      </c>
+      <c r="AK232">
+        <v>1.5</v>
+      </c>
+      <c r="AL232">
+        <v>1.2</v>
+      </c>
+      <c r="AM232">
+        <v>1.53</v>
+      </c>
+      <c r="AN232">
+        <v>1.91</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
+        <v>1.83</v>
+      </c>
+      <c r="AQ232">
+        <v>1</v>
+      </c>
+      <c r="AR232">
+        <v>1.8</v>
+      </c>
+      <c r="AS232">
+        <v>1.75</v>
+      </c>
+      <c r="AT232">
+        <v>3.55</v>
+      </c>
+      <c r="AU232">
+        <v>2</v>
+      </c>
+      <c r="AV232">
+        <v>7</v>
+      </c>
+      <c r="AW232">
+        <v>9</v>
+      </c>
+      <c r="AX232">
+        <v>15</v>
+      </c>
+      <c r="AY232">
+        <v>11</v>
+      </c>
+      <c r="AZ232">
+        <v>22</v>
+      </c>
+      <c r="BA232">
+        <v>1</v>
+      </c>
+      <c r="BB232">
+        <v>4</v>
+      </c>
+      <c r="BC232">
+        <v>5</v>
+      </c>
+      <c r="BD232">
+        <v>1.96</v>
+      </c>
+      <c r="BE232">
+        <v>6.5</v>
+      </c>
+      <c r="BF232">
+        <v>2.02</v>
+      </c>
+      <c r="BG232">
+        <v>1.25</v>
+      </c>
+      <c r="BH232">
+        <v>3.45</v>
+      </c>
+      <c r="BI232">
+        <v>1.44</v>
+      </c>
+      <c r="BJ232">
+        <v>2.55</v>
+      </c>
+      <c r="BK232">
+        <v>1.72</v>
+      </c>
+      <c r="BL232">
+        <v>1.98</v>
+      </c>
+      <c r="BM232">
+        <v>2.1</v>
+      </c>
+      <c r="BN232">
+        <v>1.64</v>
+      </c>
+      <c r="BO232">
+        <v>2.65</v>
+      </c>
+      <c r="BP232">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7465648</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F233">
+        <v>24</v>
+      </c>
+      <c r="G233" t="s">
+        <v>71</v>
+      </c>
+      <c r="H233" t="s">
+        <v>79</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>4</v>
+      </c>
+      <c r="M233">
+        <v>2</v>
+      </c>
+      <c r="N233">
+        <v>6</v>
+      </c>
+      <c r="O233" t="s">
+        <v>250</v>
+      </c>
+      <c r="P233" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q233">
+        <v>1.91</v>
+      </c>
+      <c r="R233">
+        <v>2.63</v>
+      </c>
+      <c r="S233">
+        <v>6</v>
+      </c>
+      <c r="T233">
+        <v>1.25</v>
+      </c>
+      <c r="U233">
+        <v>3.75</v>
+      </c>
+      <c r="V233">
+        <v>2.2</v>
+      </c>
+      <c r="W233">
+        <v>1.62</v>
+      </c>
+      <c r="X233">
+        <v>5</v>
+      </c>
+      <c r="Y233">
+        <v>1.17</v>
+      </c>
+      <c r="Z233">
+        <v>1.4</v>
+      </c>
+      <c r="AA233">
+        <v>5.5</v>
+      </c>
+      <c r="AB233">
+        <v>6</v>
+      </c>
+      <c r="AC233">
+        <v>1.01</v>
+      </c>
+      <c r="AD233">
+        <v>17</v>
+      </c>
+      <c r="AE233">
+        <v>1.1</v>
+      </c>
+      <c r="AF233">
+        <v>7</v>
+      </c>
+      <c r="AG233">
+        <v>1.44</v>
+      </c>
+      <c r="AH233">
+        <v>2.7</v>
+      </c>
+      <c r="AI233">
+        <v>1.67</v>
+      </c>
+      <c r="AJ233">
+        <v>2.1</v>
+      </c>
+      <c r="AK233">
+        <v>1.14</v>
+      </c>
+      <c r="AL233">
+        <v>1.15</v>
+      </c>
+      <c r="AM233">
+        <v>2.75</v>
+      </c>
+      <c r="AN233">
+        <v>1.08</v>
+      </c>
+      <c r="AO233">
+        <v>1.08</v>
+      </c>
+      <c r="AP233">
+        <v>1.23</v>
+      </c>
+      <c r="AQ233">
+        <v>1</v>
+      </c>
+      <c r="AR233">
+        <v>1.63</v>
+      </c>
+      <c r="AS233">
+        <v>1.25</v>
+      </c>
+      <c r="AT233">
+        <v>2.88</v>
+      </c>
+      <c r="AU233">
+        <v>9</v>
+      </c>
+      <c r="AV233">
+        <v>7</v>
+      </c>
+      <c r="AW233">
+        <v>13</v>
+      </c>
+      <c r="AX233">
+        <v>5</v>
+      </c>
+      <c r="AY233">
+        <v>22</v>
+      </c>
+      <c r="AZ233">
+        <v>12</v>
+      </c>
+      <c r="BA233">
+        <v>4</v>
+      </c>
+      <c r="BB233">
+        <v>6</v>
+      </c>
+      <c r="BC233">
+        <v>10</v>
+      </c>
+      <c r="BD233">
+        <v>1.38</v>
+      </c>
+      <c r="BE233">
+        <v>7</v>
+      </c>
+      <c r="BF233">
+        <v>3.3</v>
+      </c>
+      <c r="BG233">
+        <v>1.27</v>
+      </c>
+      <c r="BH233">
+        <v>3.3</v>
+      </c>
+      <c r="BI233">
+        <v>1.49</v>
+      </c>
+      <c r="BJ233">
+        <v>2.43</v>
+      </c>
+      <c r="BK233">
+        <v>1.77</v>
+      </c>
+      <c r="BL233">
+        <v>1.93</v>
+      </c>
+      <c r="BM233">
+        <v>2.18</v>
+      </c>
+      <c r="BN233">
+        <v>1.58</v>
+      </c>
+      <c r="BO233">
+        <v>2.8</v>
+      </c>
+      <c r="BP233">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7465650</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45688.66666666666</v>
+      </c>
+      <c r="F234">
+        <v>24</v>
+      </c>
+      <c r="G234" t="s">
+        <v>87</v>
+      </c>
+      <c r="H234" t="s">
+        <v>81</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>1</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>3</v>
+      </c>
+      <c r="O234" t="s">
+        <v>251</v>
+      </c>
+      <c r="P234" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q234">
+        <v>2.3</v>
+      </c>
+      <c r="R234">
+        <v>2.3</v>
+      </c>
+      <c r="S234">
+        <v>4</v>
+      </c>
+      <c r="T234">
+        <v>1.3</v>
+      </c>
+      <c r="U234">
+        <v>3.2</v>
+      </c>
+      <c r="V234">
+        <v>2.38</v>
+      </c>
+      <c r="W234">
+        <v>1.53</v>
+      </c>
+      <c r="X234">
+        <v>6</v>
+      </c>
+      <c r="Y234">
+        <v>1.11</v>
+      </c>
+      <c r="Z234">
+        <v>1.8</v>
+      </c>
+      <c r="AA234">
+        <v>3.85</v>
+      </c>
+      <c r="AB234">
+        <v>3.95</v>
+      </c>
+      <c r="AC234">
+        <v>1.04</v>
+      </c>
+      <c r="AD234">
+        <v>10</v>
+      </c>
+      <c r="AE234">
+        <v>1.2</v>
+      </c>
+      <c r="AF234">
+        <v>4.33</v>
+      </c>
+      <c r="AG234">
+        <v>1.67</v>
+      </c>
+      <c r="AH234">
+        <v>2.15</v>
+      </c>
+      <c r="AI234">
+        <v>1.6</v>
+      </c>
+      <c r="AJ234">
+        <v>2.15</v>
+      </c>
+      <c r="AK234">
+        <v>1.22</v>
+      </c>
+      <c r="AL234">
+        <v>1.2</v>
+      </c>
+      <c r="AM234">
+        <v>1.95</v>
+      </c>
+      <c r="AN234">
+        <v>1.18</v>
+      </c>
+      <c r="AO234">
+        <v>1</v>
+      </c>
+      <c r="AP234">
+        <v>1.33</v>
+      </c>
+      <c r="AQ234">
+        <v>0.92</v>
+      </c>
+      <c r="AR234">
+        <v>1.75</v>
+      </c>
+      <c r="AS234">
+        <v>1.53</v>
+      </c>
+      <c r="AT234">
+        <v>3.28</v>
+      </c>
+      <c r="AU234">
+        <v>4</v>
+      </c>
+      <c r="AV234">
+        <v>5</v>
+      </c>
+      <c r="AW234">
+        <v>7</v>
+      </c>
+      <c r="AX234">
+        <v>8</v>
+      </c>
+      <c r="AY234">
+        <v>11</v>
+      </c>
+      <c r="AZ234">
+        <v>13</v>
+      </c>
+      <c r="BA234">
+        <v>5</v>
+      </c>
+      <c r="BB234">
+        <v>3</v>
+      </c>
+      <c r="BC234">
+        <v>8</v>
+      </c>
+      <c r="BD234">
+        <v>1.52</v>
+      </c>
+      <c r="BE234">
+        <v>7</v>
+      </c>
+      <c r="BF234">
+        <v>2.8</v>
+      </c>
+      <c r="BG234">
+        <v>1.26</v>
+      </c>
+      <c r="BH234">
+        <v>3.4</v>
+      </c>
+      <c r="BI234">
+        <v>1.47</v>
+      </c>
+      <c r="BJ234">
+        <v>2.48</v>
+      </c>
+      <c r="BK234">
+        <v>1.74</v>
+      </c>
+      <c r="BL234">
+        <v>1.96</v>
+      </c>
+      <c r="BM234">
+        <v>2.17</v>
+      </c>
+      <c r="BN234">
+        <v>1.6</v>
+      </c>
+      <c r="BO234">
+        <v>2.8</v>
+      </c>
+      <c r="BP234">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="370">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,9 @@
     <t>['51', '77']</t>
   </si>
   <si>
+    <t>['23', '47', '58']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1115,6 +1118,12 @@
   </si>
   <si>
     <t>['20', '72']</t>
+  </si>
+  <si>
+    <t>['13', '16', '72']</t>
+  </si>
+  <si>
+    <t>['42', '85']</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1938,7 +1947,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2144,7 +2153,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2350,7 +2359,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2428,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ5">
         <v>2.08</v>
@@ -2556,7 +2565,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2762,7 +2771,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2968,7 +2977,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3174,7 +3183,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3461,7 +3470,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3586,7 +3595,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3873,7 +3882,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ12">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3998,7 +4007,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4488,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4616,7 +4625,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5440,7 +5449,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6470,7 +6479,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6676,7 +6685,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6882,7 +6891,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7294,7 +7303,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7375,7 +7384,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7706,7 +7715,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8324,7 +8333,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8402,7 +8411,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8530,7 +8539,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9148,7 +9157,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9354,7 +9363,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9766,7 +9775,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10384,7 +10393,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10590,7 +10599,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10796,7 +10805,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11002,7 +11011,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11083,7 +11092,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ47">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11208,7 +11217,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11286,7 +11295,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ48">
         <v>1.58</v>
@@ -11620,7 +11629,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11826,7 +11835,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11904,7 +11913,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ51">
         <v>0.92</v>
@@ -12032,7 +12041,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12113,7 +12122,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12525,7 +12534,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -12728,7 +12737,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ55">
         <v>1.45</v>
@@ -12856,7 +12865,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -12937,7 +12946,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ56">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13268,7 +13277,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13474,7 +13483,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13886,7 +13895,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14092,7 +14101,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14298,7 +14307,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14916,7 +14925,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15328,7 +15337,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15534,7 +15543,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15740,7 +15749,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15946,7 +15955,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16152,7 +16161,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16358,7 +16367,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16436,7 +16445,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ73">
         <v>0.45</v>
@@ -16564,7 +16573,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16642,7 +16651,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ74">
         <v>1.17</v>
@@ -16770,7 +16779,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17057,7 +17066,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17388,7 +17397,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17469,7 +17478,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ78">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17594,7 +17603,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18006,7 +18015,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18418,7 +18427,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18624,7 +18633,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19242,7 +19251,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19860,7 +19869,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20272,7 +20281,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20556,7 +20565,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ93">
         <v>1.45</v>
@@ -20684,7 +20693,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20890,7 +20899,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21096,7 +21105,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21302,7 +21311,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21714,7 +21723,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22001,7 +22010,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ100">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22126,7 +22135,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22204,7 +22213,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ101">
         <v>0.58</v>
@@ -22332,7 +22341,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22619,7 +22628,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22744,7 +22753,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23156,7 +23165,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23237,7 +23246,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ106">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23980,7 +23989,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24061,7 +24070,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ110">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24186,7 +24195,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24392,7 +24401,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25010,7 +25019,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25216,7 +25225,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25422,7 +25431,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25628,7 +25637,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25834,7 +25843,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25912,7 +25921,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ119">
         <v>2.08</v>
@@ -26040,7 +26049,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26246,7 +26255,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26324,7 +26333,7 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ121">
         <v>1.45</v>
@@ -26452,7 +26461,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26658,7 +26667,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26864,7 +26873,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27070,7 +27079,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27482,7 +27491,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27563,7 +27572,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ127">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27688,7 +27697,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28100,7 +28109,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28306,7 +28315,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28590,7 +28599,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28718,7 +28727,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29336,7 +29345,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29620,7 +29629,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ137">
         <v>1.54</v>
@@ -29829,7 +29838,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ138">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -30778,7 +30787,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30984,7 +30993,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31062,7 +31071,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ144">
         <v>1.58</v>
@@ -31190,7 +31199,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31396,7 +31405,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31602,7 +31611,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31808,7 +31817,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31889,7 +31898,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32220,7 +32229,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32426,7 +32435,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32838,7 +32847,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33044,7 +33053,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33250,7 +33259,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34155,7 +34164,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ159">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34280,7 +34289,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34692,7 +34701,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34976,7 +34985,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ163">
         <v>0.75</v>
@@ -35310,7 +35319,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35516,7 +35525,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35722,7 +35731,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36134,7 +36143,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36340,7 +36349,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36546,7 +36555,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36958,7 +36967,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37036,10 +37045,10 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ173">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37164,7 +37173,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37782,7 +37791,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37988,7 +37997,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38400,7 +38409,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38606,7 +38615,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38687,7 +38696,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ181">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -39224,7 +39233,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39430,7 +39439,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39636,7 +39645,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39920,7 +39929,7 @@
         <v>1.67</v>
       </c>
       <c r="AP187">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ187">
         <v>1.58</v>
@@ -40254,7 +40263,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40872,7 +40881,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41078,7 +41087,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41159,7 +41168,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ193">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41284,7 +41293,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41490,7 +41499,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41696,7 +41705,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42314,7 +42323,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42392,7 +42401,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ199">
         <v>0.92</v>
@@ -42726,7 +42735,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42807,7 +42816,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ201">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -43010,7 +43019,7 @@
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ202">
         <v>1.58</v>
@@ -43344,7 +43353,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43756,7 +43765,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43962,7 +43971,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44168,7 +44177,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44374,7 +44383,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44580,7 +44589,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44661,7 +44670,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ210">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR210">
         <v>1.37</v>
@@ -45073,7 +45082,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ212">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.95</v>
@@ -45482,7 +45491,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ214">
         <v>1.55</v>
@@ -45610,7 +45619,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46022,7 +46031,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46846,7 +46855,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47464,7 +47473,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47954,7 +47963,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AQ226">
         <v>1</v>
@@ -48082,7 +48091,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48288,7 +48297,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -49318,7 +49327,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49681,6 +49690,418 @@
       </c>
       <c r="BP234">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7465651</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45689.52083333334</v>
+      </c>
+      <c r="F235">
+        <v>24</v>
+      </c>
+      <c r="G235" t="s">
+        <v>83</v>
+      </c>
+      <c r="H235" t="s">
+        <v>75</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>2</v>
+      </c>
+      <c r="K235">
+        <v>2</v>
+      </c>
+      <c r="L235">
+        <v>1</v>
+      </c>
+      <c r="M235">
+        <v>3</v>
+      </c>
+      <c r="N235">
+        <v>4</v>
+      </c>
+      <c r="O235" t="s">
+        <v>237</v>
+      </c>
+      <c r="P235" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q235">
+        <v>1.73</v>
+      </c>
+      <c r="R235">
+        <v>2.7</v>
+      </c>
+      <c r="S235">
+        <v>5.75</v>
+      </c>
+      <c r="T235">
+        <v>1.2</v>
+      </c>
+      <c r="U235">
+        <v>3.95</v>
+      </c>
+      <c r="V235">
+        <v>2</v>
+      </c>
+      <c r="W235">
+        <v>1.73</v>
+      </c>
+      <c r="X235">
+        <v>4.7</v>
+      </c>
+      <c r="Y235">
+        <v>1.17</v>
+      </c>
+      <c r="Z235">
+        <v>1.35</v>
+      </c>
+      <c r="AA235">
+        <v>5.25</v>
+      </c>
+      <c r="AB235">
+        <v>7</v>
+      </c>
+      <c r="AC235">
+        <v>1.01</v>
+      </c>
+      <c r="AD235">
+        <v>17</v>
+      </c>
+      <c r="AE235">
+        <v>1.12</v>
+      </c>
+      <c r="AF235">
+        <v>5.75</v>
+      </c>
+      <c r="AG235">
+        <v>1.44</v>
+      </c>
+      <c r="AH235">
+        <v>2.75</v>
+      </c>
+      <c r="AI235">
+        <v>1.65</v>
+      </c>
+      <c r="AJ235">
+        <v>2.05</v>
+      </c>
+      <c r="AK235">
+        <v>1.09</v>
+      </c>
+      <c r="AL235">
+        <v>1.11</v>
+      </c>
+      <c r="AM235">
+        <v>3</v>
+      </c>
+      <c r="AN235">
+        <v>2.55</v>
+      </c>
+      <c r="AO235">
+        <v>0.82</v>
+      </c>
+      <c r="AP235">
+        <v>2.33</v>
+      </c>
+      <c r="AQ235">
+        <v>1</v>
+      </c>
+      <c r="AR235">
+        <v>1.73</v>
+      </c>
+      <c r="AS235">
+        <v>1.43</v>
+      </c>
+      <c r="AT235">
+        <v>3.16</v>
+      </c>
+      <c r="AU235">
+        <v>11</v>
+      </c>
+      <c r="AV235">
+        <v>7</v>
+      </c>
+      <c r="AW235">
+        <v>16</v>
+      </c>
+      <c r="AX235">
+        <v>4</v>
+      </c>
+      <c r="AY235">
+        <v>27</v>
+      </c>
+      <c r="AZ235">
+        <v>11</v>
+      </c>
+      <c r="BA235">
+        <v>13</v>
+      </c>
+      <c r="BB235">
+        <v>1</v>
+      </c>
+      <c r="BC235">
+        <v>14</v>
+      </c>
+      <c r="BD235">
+        <v>1.33</v>
+      </c>
+      <c r="BE235">
+        <v>7.5</v>
+      </c>
+      <c r="BF235">
+        <v>3.65</v>
+      </c>
+      <c r="BG235">
+        <v>1.18</v>
+      </c>
+      <c r="BH235">
+        <v>4.1</v>
+      </c>
+      <c r="BI235">
+        <v>1.32</v>
+      </c>
+      <c r="BJ235">
+        <v>3.05</v>
+      </c>
+      <c r="BK235">
+        <v>1.53</v>
+      </c>
+      <c r="BL235">
+        <v>2.3</v>
+      </c>
+      <c r="BM235">
+        <v>1.84</v>
+      </c>
+      <c r="BN235">
+        <v>1.84</v>
+      </c>
+      <c r="BO235">
+        <v>2.25</v>
+      </c>
+      <c r="BP235">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7465652</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45689.61458333334</v>
+      </c>
+      <c r="F236">
+        <v>24</v>
+      </c>
+      <c r="G236" t="s">
+        <v>73</v>
+      </c>
+      <c r="H236" t="s">
+        <v>82</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+      <c r="L236">
+        <v>3</v>
+      </c>
+      <c r="M236">
+        <v>2</v>
+      </c>
+      <c r="N236">
+        <v>5</v>
+      </c>
+      <c r="O236" t="s">
+        <v>252</v>
+      </c>
+      <c r="P236" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q236">
+        <v>3.2</v>
+      </c>
+      <c r="R236">
+        <v>2.25</v>
+      </c>
+      <c r="S236">
+        <v>2.75</v>
+      </c>
+      <c r="T236">
+        <v>1.28</v>
+      </c>
+      <c r="U236">
+        <v>3.3</v>
+      </c>
+      <c r="V236">
+        <v>2.3</v>
+      </c>
+      <c r="W236">
+        <v>1.55</v>
+      </c>
+      <c r="X236">
+        <v>5.4</v>
+      </c>
+      <c r="Y236">
+        <v>1.13</v>
+      </c>
+      <c r="Z236">
+        <v>2.85</v>
+      </c>
+      <c r="AA236">
+        <v>3.6</v>
+      </c>
+      <c r="AB236">
+        <v>2.25</v>
+      </c>
+      <c r="AC236">
+        <v>1.04</v>
+      </c>
+      <c r="AD236">
+        <v>10</v>
+      </c>
+      <c r="AE236">
+        <v>1.2</v>
+      </c>
+      <c r="AF236">
+        <v>4.33</v>
+      </c>
+      <c r="AG236">
+        <v>1.62</v>
+      </c>
+      <c r="AH236">
+        <v>2.25</v>
+      </c>
+      <c r="AI236">
+        <v>1.48</v>
+      </c>
+      <c r="AJ236">
+        <v>2.4</v>
+      </c>
+      <c r="AK236">
+        <v>1.62</v>
+      </c>
+      <c r="AL236">
+        <v>1.22</v>
+      </c>
+      <c r="AM236">
+        <v>1.4</v>
+      </c>
+      <c r="AN236">
+        <v>1.73</v>
+      </c>
+      <c r="AO236">
+        <v>1.33</v>
+      </c>
+      <c r="AP236">
+        <v>1.83</v>
+      </c>
+      <c r="AQ236">
+        <v>1.23</v>
+      </c>
+      <c r="AR236">
+        <v>1.7</v>
+      </c>
+      <c r="AS236">
+        <v>1.75</v>
+      </c>
+      <c r="AT236">
+        <v>3.45</v>
+      </c>
+      <c r="AU236">
+        <v>7</v>
+      </c>
+      <c r="AV236">
+        <v>6</v>
+      </c>
+      <c r="AW236">
+        <v>13</v>
+      </c>
+      <c r="AX236">
+        <v>10</v>
+      </c>
+      <c r="AY236">
+        <v>20</v>
+      </c>
+      <c r="AZ236">
+        <v>17</v>
+      </c>
+      <c r="BA236">
+        <v>6</v>
+      </c>
+      <c r="BB236">
+        <v>8</v>
+      </c>
+      <c r="BC236">
+        <v>14</v>
+      </c>
+      <c r="BD236">
+        <v>2.23</v>
+      </c>
+      <c r="BE236">
+        <v>6.4</v>
+      </c>
+      <c r="BF236">
+        <v>1.79</v>
+      </c>
+      <c r="BG236">
+        <v>1.33</v>
+      </c>
+      <c r="BH236">
+        <v>2.95</v>
+      </c>
+      <c r="BI236">
+        <v>1.56</v>
+      </c>
+      <c r="BJ236">
+        <v>2.23</v>
+      </c>
+      <c r="BK236">
+        <v>1.93</v>
+      </c>
+      <c r="BL236">
+        <v>1.77</v>
+      </c>
+      <c r="BM236">
+        <v>2.43</v>
+      </c>
+      <c r="BN236">
+        <v>1.49</v>
+      </c>
+      <c r="BO236">
+        <v>3.15</v>
+      </c>
+      <c r="BP236">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="373">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,12 @@
     <t>['23', '47', '58']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['15', '73', '77']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1124,6 +1130,9 @@
   </si>
   <si>
     <t>['42', '85']</t>
+  </si>
+  <si>
+    <t>['16', '19']</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP236"/>
+  <dimension ref="A1:BP239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1947,7 +1956,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2153,7 +2162,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2359,7 +2368,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2565,7 +2574,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2643,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ6">
         <v>1.42</v>
@@ -2771,7 +2780,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2977,7 +2986,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3058,7 +3067,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ8">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3183,7 +3192,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3261,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9">
         <v>1.58</v>
@@ -3467,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>1.23</v>
@@ -3595,7 +3604,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4007,7 +4016,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4625,7 +4634,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5118,7 +5127,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5324,7 +5333,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ19">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5449,7 +5458,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5939,7 +5948,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ22">
         <v>2.08</v>
@@ -6148,7 +6157,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ23">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6479,7 +6488,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6557,7 +6566,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ25">
         <v>0.45</v>
@@ -6685,7 +6694,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6891,7 +6900,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7303,7 +7312,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7587,7 +7596,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
         <v>1.58</v>
@@ -7715,7 +7724,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8333,7 +8342,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8539,7 +8548,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8826,7 +8835,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ36">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -9157,7 +9166,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9363,7 +9372,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9775,7 +9784,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10059,7 +10068,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42">
         <v>1.54</v>
@@ -10393,7 +10402,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10599,7 +10608,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10805,7 +10814,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10883,7 +10892,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11011,7 +11020,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11089,7 +11098,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11217,7 +11226,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11629,7 +11638,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11707,10 +11716,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ50">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -11835,7 +11844,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12041,7 +12050,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12328,7 +12337,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ53">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -12740,7 +12749,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -12865,7 +12874,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13277,7 +13286,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13483,7 +13492,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13564,7 +13573,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -13895,7 +13904,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14101,7 +14110,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14307,7 +14316,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14925,7 +14934,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15337,7 +15346,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15543,7 +15552,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15621,7 +15630,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ69">
         <v>1.54</v>
@@ -15749,7 +15758,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15827,7 +15836,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15955,7 +15964,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16161,7 +16170,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16242,7 +16251,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ72">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16367,7 +16376,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16573,7 +16582,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16779,7 +16788,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17397,7 +17406,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17475,7 +17484,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17603,7 +17612,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18015,7 +18024,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18096,7 +18105,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ81">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18427,7 +18436,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18633,7 +18642,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18711,10 +18720,10 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -19251,7 +19260,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19329,7 +19338,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ87">
         <v>1.54</v>
@@ -19869,7 +19878,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20281,7 +20290,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20568,7 +20577,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -20693,7 +20702,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20771,10 +20780,10 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ94">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -20899,7 +20908,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21105,7 +21114,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21183,7 +21192,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ96">
         <v>0.92</v>
@@ -21311,7 +21320,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21723,7 +21732,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22135,7 +22144,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22341,7 +22350,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22419,7 +22428,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22753,7 +22762,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23040,7 +23049,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -23165,7 +23174,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23989,7 +23998,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24195,7 +24204,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24401,7 +24410,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25019,7 +25028,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25225,7 +25234,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25303,7 +25312,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ116">
         <v>1.17</v>
@@ -25431,7 +25440,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25637,7 +25646,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25843,7 +25852,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26049,7 +26058,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26255,7 +26264,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26336,7 +26345,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ121">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26461,7 +26470,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26539,7 +26548,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122">
         <v>2.08</v>
@@ -26667,7 +26676,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26748,7 +26757,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ123">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -26873,7 +26882,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -26951,7 +26960,7 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ124">
         <v>1.58</v>
@@ -27079,7 +27088,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27160,7 +27169,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27491,7 +27500,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27697,7 +27706,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28109,7 +28118,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28315,7 +28324,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28727,7 +28736,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29011,7 +29020,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ134">
         <v>1.55</v>
@@ -29345,7 +29354,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30456,7 +30465,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ141">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -30662,7 +30671,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ142">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -30787,7 +30796,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30993,7 +31002,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31199,7 +31208,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31405,7 +31414,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31611,7 +31620,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31817,7 +31826,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32229,7 +32238,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32435,7 +32444,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32719,7 +32728,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ152">
         <v>0.45</v>
@@ -32847,7 +32856,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32925,10 +32934,10 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33053,7 +33062,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33259,7 +33268,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33958,7 +33967,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34289,7 +34298,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34701,7 +34710,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35319,7 +35328,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35525,7 +35534,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35731,7 +35740,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35812,7 +35821,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ167">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -36015,7 +36024,7 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ168">
         <v>0.45</v>
@@ -36143,7 +36152,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36221,10 +36230,10 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ169">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -36349,7 +36358,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36555,7 +36564,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36633,7 +36642,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ171">
         <v>0.58</v>
@@ -36967,7 +36976,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37173,7 +37182,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37791,7 +37800,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37872,7 +37881,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -37997,7 +38006,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38409,7 +38418,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38615,7 +38624,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38902,7 +38911,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ182">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39233,7 +39242,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39311,7 +39320,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ184">
         <v>1.9</v>
@@ -39439,7 +39448,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39520,7 +39529,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ185">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39645,7 +39654,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39723,7 +39732,7 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ186">
         <v>2.08</v>
@@ -40263,7 +40272,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40341,7 +40350,7 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ189">
         <v>0.75</v>
@@ -40881,7 +40890,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -40962,7 +40971,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ192">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41087,7 +41096,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41293,7 +41302,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41499,7 +41508,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41705,7 +41714,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42323,7 +42332,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42735,7 +42744,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43225,7 +43234,7 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ203">
         <v>0.58</v>
@@ -43353,7 +43362,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43765,7 +43774,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43846,7 +43855,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ206">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -43971,7 +43980,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44049,7 +44058,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ207">
         <v>0.75</v>
@@ -44177,7 +44186,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44383,7 +44392,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44464,7 +44473,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ209">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR209">
         <v>1.86</v>
@@ -44589,7 +44598,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44667,7 +44676,7 @@
         <v>1.18</v>
       </c>
       <c r="AP210">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AQ210">
         <v>1.23</v>
@@ -45619,7 +45628,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46031,7 +46040,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46727,7 +46736,7 @@
         <v>2.11</v>
       </c>
       <c r="AP220">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ220">
         <v>1.9</v>
@@ -46855,7 +46864,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47473,7 +47482,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47966,7 +47975,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ226">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48091,7 +48100,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48297,7 +48306,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48378,7 +48387,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ228">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR228">
         <v>1.56</v>
@@ -49026,13 +49035,13 @@
         <v>9</v>
       </c>
       <c r="BA231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB231">
         <v>4</v>
       </c>
       <c r="BC231">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD231">
         <v>2.6</v>
@@ -49327,7 +49336,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49739,7 +49748,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49945,7 +49954,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50102,6 +50111,624 @@
       </c>
       <c r="BP236">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7465653</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45690.53125</v>
+      </c>
+      <c r="F237">
+        <v>24</v>
+      </c>
+      <c r="G237" t="s">
+        <v>74</v>
+      </c>
+      <c r="H237" t="s">
+        <v>72</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>253</v>
+      </c>
+      <c r="P237" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q237">
+        <v>3</v>
+      </c>
+      <c r="R237">
+        <v>2.2</v>
+      </c>
+      <c r="S237">
+        <v>3.4</v>
+      </c>
+      <c r="T237">
+        <v>1.36</v>
+      </c>
+      <c r="U237">
+        <v>3</v>
+      </c>
+      <c r="V237">
+        <v>2.75</v>
+      </c>
+      <c r="W237">
+        <v>1.4</v>
+      </c>
+      <c r="X237">
+        <v>7</v>
+      </c>
+      <c r="Y237">
+        <v>1.1</v>
+      </c>
+      <c r="Z237">
+        <v>2.45</v>
+      </c>
+      <c r="AA237">
+        <v>3.37</v>
+      </c>
+      <c r="AB237">
+        <v>2.87</v>
+      </c>
+      <c r="AC237">
+        <v>1.04</v>
+      </c>
+      <c r="AD237">
+        <v>12</v>
+      </c>
+      <c r="AE237">
+        <v>1.25</v>
+      </c>
+      <c r="AF237">
+        <v>3.75</v>
+      </c>
+      <c r="AG237">
+        <v>1.82</v>
+      </c>
+      <c r="AH237">
+        <v>2.01</v>
+      </c>
+      <c r="AI237">
+        <v>1.67</v>
+      </c>
+      <c r="AJ237">
+        <v>2.1</v>
+      </c>
+      <c r="AK237">
+        <v>1.42</v>
+      </c>
+      <c r="AL237">
+        <v>1.25</v>
+      </c>
+      <c r="AM237">
+        <v>1.57</v>
+      </c>
+      <c r="AN237">
+        <v>1.67</v>
+      </c>
+      <c r="AO237">
+        <v>1.45</v>
+      </c>
+      <c r="AP237">
+        <v>1.62</v>
+      </c>
+      <c r="AQ237">
+        <v>1.42</v>
+      </c>
+      <c r="AR237">
+        <v>1.48</v>
+      </c>
+      <c r="AS237">
+        <v>1.35</v>
+      </c>
+      <c r="AT237">
+        <v>2.83</v>
+      </c>
+      <c r="AU237">
+        <v>5</v>
+      </c>
+      <c r="AV237">
+        <v>5</v>
+      </c>
+      <c r="AW237">
+        <v>4</v>
+      </c>
+      <c r="AX237">
+        <v>3</v>
+      </c>
+      <c r="AY237">
+        <v>9</v>
+      </c>
+      <c r="AZ237">
+        <v>8</v>
+      </c>
+      <c r="BA237">
+        <v>2</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>6</v>
+      </c>
+      <c r="BD237">
+        <v>1.88</v>
+      </c>
+      <c r="BE237">
+        <v>6.4</v>
+      </c>
+      <c r="BF237">
+        <v>2.12</v>
+      </c>
+      <c r="BG237">
+        <v>1.27</v>
+      </c>
+      <c r="BH237">
+        <v>3.3</v>
+      </c>
+      <c r="BI237">
+        <v>1.47</v>
+      </c>
+      <c r="BJ237">
+        <v>2.48</v>
+      </c>
+      <c r="BK237">
+        <v>1.76</v>
+      </c>
+      <c r="BL237">
+        <v>1.94</v>
+      </c>
+      <c r="BM237">
+        <v>2.18</v>
+      </c>
+      <c r="BN237">
+        <v>1.58</v>
+      </c>
+      <c r="BO237">
+        <v>2.8</v>
+      </c>
+      <c r="BP237">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7465654</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45691.66666666666</v>
+      </c>
+      <c r="F238">
+        <v>24</v>
+      </c>
+      <c r="G238" t="s">
+        <v>78</v>
+      </c>
+      <c r="H238" t="s">
+        <v>80</v>
+      </c>
+      <c r="I238">
+        <v>1</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="L238">
+        <v>3</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>3</v>
+      </c>
+      <c r="O238" t="s">
+        <v>254</v>
+      </c>
+      <c r="P238" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q238">
+        <v>2.5</v>
+      </c>
+      <c r="R238">
+        <v>2.4</v>
+      </c>
+      <c r="S238">
+        <v>3.75</v>
+      </c>
+      <c r="T238">
+        <v>1.29</v>
+      </c>
+      <c r="U238">
+        <v>3.5</v>
+      </c>
+      <c r="V238">
+        <v>2.38</v>
+      </c>
+      <c r="W238">
+        <v>1.53</v>
+      </c>
+      <c r="X238">
+        <v>5.5</v>
+      </c>
+      <c r="Y238">
+        <v>1.14</v>
+      </c>
+      <c r="Z238">
+        <v>1.91</v>
+      </c>
+      <c r="AA238">
+        <v>3.8</v>
+      </c>
+      <c r="AB238">
+        <v>3.6</v>
+      </c>
+      <c r="AC238">
+        <v>1.02</v>
+      </c>
+      <c r="AD238">
+        <v>17</v>
+      </c>
+      <c r="AE238">
+        <v>1.17</v>
+      </c>
+      <c r="AF238">
+        <v>5</v>
+      </c>
+      <c r="AG238">
+        <v>1.57</v>
+      </c>
+      <c r="AH238">
+        <v>2.35</v>
+      </c>
+      <c r="AI238">
+        <v>1.5</v>
+      </c>
+      <c r="AJ238">
+        <v>2.5</v>
+      </c>
+      <c r="AK238">
+        <v>1.33</v>
+      </c>
+      <c r="AL238">
+        <v>1.2</v>
+      </c>
+      <c r="AM238">
+        <v>1.85</v>
+      </c>
+      <c r="AN238">
+        <v>1.09</v>
+      </c>
+      <c r="AO238">
+        <v>1.45</v>
+      </c>
+      <c r="AP238">
+        <v>1.25</v>
+      </c>
+      <c r="AQ238">
+        <v>1.33</v>
+      </c>
+      <c r="AR238">
+        <v>1.78</v>
+      </c>
+      <c r="AS238">
+        <v>1.37</v>
+      </c>
+      <c r="AT238">
+        <v>3.15</v>
+      </c>
+      <c r="AU238">
+        <v>7</v>
+      </c>
+      <c r="AV238">
+        <v>9</v>
+      </c>
+      <c r="AW238">
+        <v>6</v>
+      </c>
+      <c r="AX238">
+        <v>9</v>
+      </c>
+      <c r="AY238">
+        <v>13</v>
+      </c>
+      <c r="AZ238">
+        <v>18</v>
+      </c>
+      <c r="BA238">
+        <v>6</v>
+      </c>
+      <c r="BB238">
+        <v>7</v>
+      </c>
+      <c r="BC238">
+        <v>13</v>
+      </c>
+      <c r="BD238">
+        <v>1.71</v>
+      </c>
+      <c r="BE238">
+        <v>6.75</v>
+      </c>
+      <c r="BF238">
+        <v>2.38</v>
+      </c>
+      <c r="BG238">
+        <v>1.33</v>
+      </c>
+      <c r="BH238">
+        <v>2.95</v>
+      </c>
+      <c r="BI238">
+        <v>1.56</v>
+      </c>
+      <c r="BJ238">
+        <v>2.23</v>
+      </c>
+      <c r="BK238">
+        <v>1.92</v>
+      </c>
+      <c r="BL238">
+        <v>1.77</v>
+      </c>
+      <c r="BM238">
+        <v>2.4</v>
+      </c>
+      <c r="BN238">
+        <v>1.49</v>
+      </c>
+      <c r="BO238">
+        <v>3.15</v>
+      </c>
+      <c r="BP238">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7465612</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45691.66666666666</v>
+      </c>
+      <c r="F239">
+        <v>21</v>
+      </c>
+      <c r="G239" t="s">
+        <v>77</v>
+      </c>
+      <c r="H239" t="s">
+        <v>76</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239">
+        <v>3</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>104</v>
+      </c>
+      <c r="P239" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q239">
+        <v>2.88</v>
+      </c>
+      <c r="R239">
+        <v>2.38</v>
+      </c>
+      <c r="S239">
+        <v>3.2</v>
+      </c>
+      <c r="T239">
+        <v>1.29</v>
+      </c>
+      <c r="U239">
+        <v>3.5</v>
+      </c>
+      <c r="V239">
+        <v>2.38</v>
+      </c>
+      <c r="W239">
+        <v>1.53</v>
+      </c>
+      <c r="X239">
+        <v>5.5</v>
+      </c>
+      <c r="Y239">
+        <v>1.14</v>
+      </c>
+      <c r="Z239">
+        <v>2.3</v>
+      </c>
+      <c r="AA239">
+        <v>3.9</v>
+      </c>
+      <c r="AB239">
+        <v>2.7</v>
+      </c>
+      <c r="AC239">
+        <v>1.01</v>
+      </c>
+      <c r="AD239">
+        <v>19</v>
+      </c>
+      <c r="AE239">
+        <v>1.17</v>
+      </c>
+      <c r="AF239">
+        <v>5</v>
+      </c>
+      <c r="AG239">
+        <v>1.57</v>
+      </c>
+      <c r="AH239">
+        <v>2.35</v>
+      </c>
+      <c r="AI239">
+        <v>1.5</v>
+      </c>
+      <c r="AJ239">
+        <v>2.5</v>
+      </c>
+      <c r="AK239">
+        <v>1.44</v>
+      </c>
+      <c r="AL239">
+        <v>1.2</v>
+      </c>
+      <c r="AM239">
+        <v>1.65</v>
+      </c>
+      <c r="AN239">
+        <v>2.27</v>
+      </c>
+      <c r="AO239">
+        <v>1</v>
+      </c>
+      <c r="AP239">
+        <v>2.08</v>
+      </c>
+      <c r="AQ239">
+        <v>1.18</v>
+      </c>
+      <c r="AR239">
+        <v>1.84</v>
+      </c>
+      <c r="AS239">
+        <v>1.51</v>
+      </c>
+      <c r="AT239">
+        <v>3.35</v>
+      </c>
+      <c r="AU239">
+        <v>6</v>
+      </c>
+      <c r="AV239">
+        <v>6</v>
+      </c>
+      <c r="AW239">
+        <v>10</v>
+      </c>
+      <c r="AX239">
+        <v>4</v>
+      </c>
+      <c r="AY239">
+        <v>16</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
+        <v>0</v>
+      </c>
+      <c r="BC239">
+        <v>6</v>
+      </c>
+      <c r="BD239">
+        <v>1.9</v>
+      </c>
+      <c r="BE239">
+        <v>6.4</v>
+      </c>
+      <c r="BF239">
+        <v>2.08</v>
+      </c>
+      <c r="BG239">
+        <v>1.3</v>
+      </c>
+      <c r="BH239">
+        <v>3.05</v>
+      </c>
+      <c r="BI239">
+        <v>1.53</v>
+      </c>
+      <c r="BJ239">
+        <v>2.3</v>
+      </c>
+      <c r="BK239">
+        <v>1.86</v>
+      </c>
+      <c r="BL239">
+        <v>1.82</v>
+      </c>
+      <c r="BM239">
+        <v>2.35</v>
+      </c>
+      <c r="BN239">
+        <v>1.5</v>
+      </c>
+      <c r="BO239">
+        <v>3.05</v>
+      </c>
+      <c r="BP239">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -50462,19 +50462,19 @@
         <v>7</v>
       </c>
       <c r="AV238">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW238">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX238">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY238">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ238">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA238">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -50324,7 +50324,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>7465654</v>
+        <v>7465612</v>
       </c>
       <c r="C238" t="s">
         <v>68</v>
@@ -50336,46 +50336,46 @@
         <v>45691.66666666666</v>
       </c>
       <c r="F238">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G238" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H238" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I238">
         <v>1</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K238">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N238">
         <v>3</v>
       </c>
       <c r="O238" t="s">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>93</v>
+        <v>372</v>
       </c>
       <c r="Q238">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R238">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S238">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="T238">
         <v>1.29</v>
@@ -50396,19 +50396,19 @@
         <v>1.14</v>
       </c>
       <c r="Z238">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AA238">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB238">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC238">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD238">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AE238">
         <v>1.17</v>
@@ -50429,100 +50429,100 @@
         <v>2.5</v>
       </c>
       <c r="AK238">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL238">
         <v>1.2</v>
       </c>
       <c r="AM238">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AN238">
-        <v>1.09</v>
+        <v>2.27</v>
       </c>
       <c r="AO238">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="AP238">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ238">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AR238">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AS238">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AT238">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AU238">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV238">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW238">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AX238">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY238">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ238">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BA238">
         <v>6</v>
       </c>
       <c r="BB238">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BC238">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BD238">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="BE238">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF238">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="BG238">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BH238">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BI238">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BJ238">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="BK238">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BL238">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BM238">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BN238">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BO238">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BP238">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="239" spans="1:68">
@@ -50530,7 +50530,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>7465612</v>
+        <v>7465654</v>
       </c>
       <c r="C239" t="s">
         <v>68</v>
@@ -50539,49 +50539,49 @@
         <v>69</v>
       </c>
       <c r="E239" s="2">
-        <v>45691.66666666666</v>
+        <v>45691.67708333334</v>
       </c>
       <c r="F239">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G239" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H239" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I239">
         <v>1</v>
       </c>
       <c r="J239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
         <v>3</v>
       </c>
-      <c r="L239">
-        <v>1</v>
-      </c>
       <c r="M239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N239">
         <v>3</v>
       </c>
       <c r="O239" t="s">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="P239" t="s">
-        <v>372</v>
+        <v>93</v>
       </c>
       <c r="Q239">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R239">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S239">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T239">
         <v>1.29</v>
@@ -50602,19 +50602,19 @@
         <v>1.14</v>
       </c>
       <c r="Z239">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AA239">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB239">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AC239">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD239">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE239">
         <v>1.17</v>
@@ -50635,100 +50635,100 @@
         <v>2.5</v>
       </c>
       <c r="AK239">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL239">
         <v>1.2</v>
       </c>
       <c r="AM239">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AN239">
-        <v>2.27</v>
+        <v>1.09</v>
       </c>
       <c r="AO239">
-        <v>1</v>
+        <v>1.45</v>
       </c>
       <c r="AP239">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AQ239">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR239">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AS239">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT239">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AU239">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV239">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW239">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX239">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY239">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ239">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BA239">
         <v>6</v>
       </c>
       <c r="BB239">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC239">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD239">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="BE239">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF239">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="BG239">
+        <v>1.33</v>
+      </c>
+      <c r="BH239">
+        <v>2.95</v>
+      </c>
+      <c r="BI239">
+        <v>1.56</v>
+      </c>
+      <c r="BJ239">
+        <v>2.23</v>
+      </c>
+      <c r="BK239">
+        <v>1.92</v>
+      </c>
+      <c r="BL239">
+        <v>1.77</v>
+      </c>
+      <c r="BM239">
+        <v>2.4</v>
+      </c>
+      <c r="BN239">
+        <v>1.49</v>
+      </c>
+      <c r="BO239">
+        <v>3.15</v>
+      </c>
+      <c r="BP239">
         <v>1.3</v>
-      </c>
-      <c r="BH239">
-        <v>3.05</v>
-      </c>
-      <c r="BI239">
-        <v>1.53</v>
-      </c>
-      <c r="BJ239">
-        <v>2.3</v>
-      </c>
-      <c r="BK239">
-        <v>1.86</v>
-      </c>
-      <c r="BL239">
-        <v>1.82</v>
-      </c>
-      <c r="BM239">
-        <v>2.35</v>
-      </c>
-      <c r="BN239">
-        <v>1.5</v>
-      </c>
-      <c r="BO239">
-        <v>3.05</v>
-      </c>
-      <c r="BP239">
-        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="379">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,18 @@
     <t>['15', '73', '77']</t>
   </si>
   <si>
+    <t>['1', '45+1', '79']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['5', '8', '82']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1133,6 +1145,12 @@
   </si>
   <si>
     <t>['16', '19']</t>
+  </si>
+  <si>
+    <t>['20', '50', '86']</t>
+  </si>
+  <si>
+    <t>['47', '56']</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP239"/>
+  <dimension ref="A1:BP243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1828,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1956,7 +1974,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2162,7 +2180,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2368,7 +2386,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2574,7 +2592,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2780,7 +2798,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2986,7 +3004,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3192,7 +3210,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3270,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ9">
         <v>1.58</v>
@@ -3604,7 +3622,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4016,7 +4034,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4300,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4634,7 +4652,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4921,7 +4939,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5127,7 +5145,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5458,7 +5476,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5536,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ20">
         <v>1.9</v>
@@ -6488,7 +6506,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6566,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ25">
         <v>0.45</v>
@@ -6694,7 +6712,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6900,7 +6918,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -6978,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27">
         <v>0.75</v>
@@ -7312,7 +7330,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7724,7 +7742,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8217,7 +8235,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8342,7 +8360,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8548,7 +8566,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9166,7 +9184,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9372,7 +9390,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9453,7 +9471,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9656,10 +9674,10 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ40">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -9784,7 +9802,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9862,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10068,7 +10086,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ42">
         <v>1.54</v>
@@ -10402,7 +10420,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10608,7 +10626,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10814,7 +10832,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11020,7 +11038,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11226,7 +11244,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11510,7 +11528,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ49">
         <v>1.58</v>
@@ -11638,7 +11656,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11716,7 +11734,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ50">
         <v>1.42</v>
@@ -11844,7 +11862,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12050,7 +12068,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12337,7 +12355,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ53">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -12874,7 +12892,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13161,7 +13179,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13286,7 +13304,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13367,7 +13385,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ58">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13492,7 +13510,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13573,7 +13591,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ59">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -13776,7 +13794,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ60">
         <v>1.58</v>
@@ -13904,7 +13922,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -13985,7 +14003,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14110,7 +14128,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14316,7 +14334,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14934,7 +14952,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15218,7 +15236,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ67">
         <v>0.58</v>
@@ -15346,7 +15364,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15552,7 +15570,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15758,7 +15776,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15964,7 +15982,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16170,7 +16188,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16248,7 +16266,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ72">
         <v>1.33</v>
@@ -16376,7 +16394,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16457,7 +16475,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ73">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16582,7 +16600,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16663,7 +16681,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ74">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -16788,7 +16806,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17072,7 +17090,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ76">
         <v>1.23</v>
@@ -17281,7 +17299,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ77">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17406,7 +17424,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17484,7 +17502,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17612,7 +17630,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18024,7 +18042,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18436,7 +18454,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18642,7 +18660,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18723,7 +18741,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ84">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -18926,7 +18944,7 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ85">
         <v>1.42</v>
@@ -19260,7 +19278,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19878,7 +19896,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20290,7 +20308,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20702,7 +20720,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20908,7 +20926,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21114,7 +21132,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21320,7 +21338,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21732,7 +21750,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21810,7 +21828,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ99">
         <v>1.9</v>
@@ -22144,7 +22162,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22350,7 +22368,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22428,7 +22446,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22762,7 +22780,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23049,7 +23067,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -23174,7 +23192,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23667,7 +23685,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -23873,7 +23891,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ109">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -23998,7 +24016,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24204,7 +24222,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24282,10 +24300,10 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ111">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24410,7 +24428,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24900,7 +24918,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ114">
         <v>1.54</v>
@@ -25028,7 +25046,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25106,7 +25124,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -25234,7 +25252,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25315,7 +25333,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ116">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25440,7 +25458,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25646,7 +25664,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25727,7 +25745,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ118">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25852,7 +25870,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26058,7 +26076,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26264,7 +26282,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26470,7 +26488,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26676,7 +26694,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26882,7 +26900,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -26960,7 +26978,7 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ124">
         <v>1.58</v>
@@ -27088,7 +27106,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27166,10 +27184,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27375,7 +27393,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ126">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -27500,7 +27518,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27706,7 +27724,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28118,7 +28136,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28324,7 +28342,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28736,7 +28754,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28817,7 +28835,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ133">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -29023,7 +29041,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ134">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29354,7 +29372,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30050,7 +30068,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ139">
         <v>0.45</v>
@@ -30256,7 +30274,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ140">
         <v>0.92</v>
@@ -30796,7 +30814,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30874,7 +30892,7 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ143">
         <v>0.58</v>
@@ -31002,7 +31020,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31208,7 +31226,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31414,7 +31432,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31620,7 +31638,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31826,7 +31844,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32238,7 +32256,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32444,7 +32462,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32728,10 +32746,10 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ152">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -32856,7 +32874,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -32937,7 +32955,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33062,7 +33080,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33143,7 +33161,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ154">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33268,7 +33286,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33349,7 +33367,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ155">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33758,7 +33776,7 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ157">
         <v>0.75</v>
@@ -33967,7 +33985,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ158">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34170,7 +34188,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -34298,7 +34316,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34379,7 +34397,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ160">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34710,7 +34728,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35200,7 +35218,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35328,7 +35346,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35406,7 +35424,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165">
         <v>1.58</v>
@@ -35534,7 +35552,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35740,7 +35758,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36152,7 +36170,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36230,7 +36248,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ169">
         <v>1.33</v>
@@ -36358,7 +36376,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36564,7 +36582,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36851,7 +36869,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ172">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -36976,7 +36994,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37182,7 +37200,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37466,10 +37484,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ175">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -37675,7 +37693,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ176">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -37800,7 +37818,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37881,7 +37899,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ177">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -38006,7 +38024,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38418,7 +38436,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38624,7 +38642,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39114,7 +39132,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ183">
         <v>1.58</v>
@@ -39242,7 +39260,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39448,7 +39466,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39526,7 +39544,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -39654,7 +39672,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39732,7 +39750,7 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ186">
         <v>2.08</v>
@@ -40272,7 +40290,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40890,7 +40908,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41096,7 +41114,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41302,7 +41320,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41383,7 +41401,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ194">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41508,7 +41526,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41714,7 +41732,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41795,7 +41813,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ196">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -42204,7 +42222,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ198">
         <v>1</v>
@@ -42332,7 +42350,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42619,7 +42637,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ200">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42744,7 +42762,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43362,7 +43380,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43440,7 +43458,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ204">
         <v>1.58</v>
@@ -43774,7 +43792,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43980,7 +43998,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44186,7 +44204,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44267,7 +44285,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ208">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR208">
         <v>1.87</v>
@@ -44392,7 +44410,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44598,7 +44616,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -45088,7 +45106,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45503,7 +45521,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ214">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AR214">
         <v>1.73</v>
@@ -45628,7 +45646,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46040,7 +46058,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46324,7 +46342,7 @@
         <v>2.2</v>
       </c>
       <c r="AP218">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ218">
         <v>2.08</v>
@@ -46533,7 +46551,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ219">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR219">
         <v>1.74</v>
@@ -46736,7 +46754,7 @@
         <v>2.11</v>
       </c>
       <c r="AP220">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ220">
         <v>1.9</v>
@@ -46864,7 +46882,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -46942,7 +46960,7 @@
         <v>2.27</v>
       </c>
       <c r="AP221">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ221">
         <v>2.08</v>
@@ -47148,7 +47166,7 @@
         <v>0.64</v>
       </c>
       <c r="AP222">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ222">
         <v>0.58</v>
@@ -47354,7 +47372,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP223">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ223">
         <v>0.45</v>
@@ -47482,7 +47500,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47975,7 +47993,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ226">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48100,7 +48118,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48181,7 +48199,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ227">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR227">
         <v>1.46</v>
@@ -48306,7 +48324,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -49336,7 +49354,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49748,7 +49766,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49954,7 +49972,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50366,7 +50384,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50444,10 +50462,10 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ238">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR238">
         <v>1.84</v>
@@ -50729,6 +50747,830 @@
       </c>
       <c r="BP239">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7465661</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F240">
+        <v>25</v>
+      </c>
+      <c r="G240" t="s">
+        <v>82</v>
+      </c>
+      <c r="H240" t="s">
+        <v>78</v>
+      </c>
+      <c r="I240">
+        <v>2</v>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240">
+        <v>3</v>
+      </c>
+      <c r="L240">
+        <v>3</v>
+      </c>
+      <c r="M240">
+        <v>3</v>
+      </c>
+      <c r="N240">
+        <v>6</v>
+      </c>
+      <c r="O240" t="s">
+        <v>255</v>
+      </c>
+      <c r="P240" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q240">
+        <v>2.2</v>
+      </c>
+      <c r="R240">
+        <v>2.5</v>
+      </c>
+      <c r="S240">
+        <v>4.33</v>
+      </c>
+      <c r="T240">
+        <v>1.25</v>
+      </c>
+      <c r="U240">
+        <v>3.75</v>
+      </c>
+      <c r="V240">
+        <v>2.2</v>
+      </c>
+      <c r="W240">
+        <v>1.62</v>
+      </c>
+      <c r="X240">
+        <v>5</v>
+      </c>
+      <c r="Y240">
+        <v>1.17</v>
+      </c>
+      <c r="Z240">
+        <v>1.66</v>
+      </c>
+      <c r="AA240">
+        <v>4.19</v>
+      </c>
+      <c r="AB240">
+        <v>4.4</v>
+      </c>
+      <c r="AC240">
+        <v>1.01</v>
+      </c>
+      <c r="AD240">
+        <v>17</v>
+      </c>
+      <c r="AE240">
+        <v>1.16</v>
+      </c>
+      <c r="AF240">
+        <v>5</v>
+      </c>
+      <c r="AG240">
+        <v>1.5</v>
+      </c>
+      <c r="AH240">
+        <v>2.5</v>
+      </c>
+      <c r="AI240">
+        <v>1.5</v>
+      </c>
+      <c r="AJ240">
+        <v>2.5</v>
+      </c>
+      <c r="AK240">
+        <v>1.2</v>
+      </c>
+      <c r="AL240">
+        <v>1.23</v>
+      </c>
+      <c r="AM240">
+        <v>2.1</v>
+      </c>
+      <c r="AN240">
+        <v>1.82</v>
+      </c>
+      <c r="AO240">
+        <v>1.17</v>
+      </c>
+      <c r="AP240">
+        <v>1.75</v>
+      </c>
+      <c r="AQ240">
+        <v>1.15</v>
+      </c>
+      <c r="AR240">
+        <v>1.93</v>
+      </c>
+      <c r="AS240">
+        <v>1.32</v>
+      </c>
+      <c r="AT240">
+        <v>3.25</v>
+      </c>
+      <c r="AU240">
+        <v>9</v>
+      </c>
+      <c r="AV240">
+        <v>5</v>
+      </c>
+      <c r="AW240">
+        <v>12</v>
+      </c>
+      <c r="AX240">
+        <v>4</v>
+      </c>
+      <c r="AY240">
+        <v>28</v>
+      </c>
+      <c r="AZ240">
+        <v>10</v>
+      </c>
+      <c r="BA240">
+        <v>10</v>
+      </c>
+      <c r="BB240">
+        <v>2</v>
+      </c>
+      <c r="BC240">
+        <v>12</v>
+      </c>
+      <c r="BD240">
+        <v>1.47</v>
+      </c>
+      <c r="BE240">
+        <v>7</v>
+      </c>
+      <c r="BF240">
+        <v>2.95</v>
+      </c>
+      <c r="BG240">
+        <v>1.24</v>
+      </c>
+      <c r="BH240">
+        <v>3.65</v>
+      </c>
+      <c r="BI240">
+        <v>1.43</v>
+      </c>
+      <c r="BJ240">
+        <v>2.6</v>
+      </c>
+      <c r="BK240">
+        <v>1.7</v>
+      </c>
+      <c r="BL240">
+        <v>2.02</v>
+      </c>
+      <c r="BM240">
+        <v>2.07</v>
+      </c>
+      <c r="BN240">
+        <v>1.67</v>
+      </c>
+      <c r="BO240">
+        <v>2.55</v>
+      </c>
+      <c r="BP240">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7465657</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F241">
+        <v>25</v>
+      </c>
+      <c r="G241" t="s">
+        <v>77</v>
+      </c>
+      <c r="H241" t="s">
+        <v>85</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
+        <v>256</v>
+      </c>
+      <c r="P241" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q241">
+        <v>2.38</v>
+      </c>
+      <c r="R241">
+        <v>2.5</v>
+      </c>
+      <c r="S241">
+        <v>3.75</v>
+      </c>
+      <c r="T241">
+        <v>1.25</v>
+      </c>
+      <c r="U241">
+        <v>3.75</v>
+      </c>
+      <c r="V241">
+        <v>2.1</v>
+      </c>
+      <c r="W241">
+        <v>1.67</v>
+      </c>
+      <c r="X241">
+        <v>5</v>
+      </c>
+      <c r="Y241">
+        <v>1.17</v>
+      </c>
+      <c r="Z241">
+        <v>1.83</v>
+      </c>
+      <c r="AA241">
+        <v>4</v>
+      </c>
+      <c r="AB241">
+        <v>3.75</v>
+      </c>
+      <c r="AC241">
+        <v>1.01</v>
+      </c>
+      <c r="AD241">
+        <v>15</v>
+      </c>
+      <c r="AE241">
+        <v>1.14</v>
+      </c>
+      <c r="AF241">
+        <v>5.5</v>
+      </c>
+      <c r="AG241">
+        <v>1.44</v>
+      </c>
+      <c r="AH241">
+        <v>2.7</v>
+      </c>
+      <c r="AI241">
+        <v>1.44</v>
+      </c>
+      <c r="AJ241">
+        <v>2.63</v>
+      </c>
+      <c r="AK241">
+        <v>1.28</v>
+      </c>
+      <c r="AL241">
+        <v>1.23</v>
+      </c>
+      <c r="AM241">
+        <v>1.9</v>
+      </c>
+      <c r="AN241">
+        <v>2.08</v>
+      </c>
+      <c r="AO241">
+        <v>1.55</v>
+      </c>
+      <c r="AP241">
+        <v>2.15</v>
+      </c>
+      <c r="AQ241">
+        <v>1.42</v>
+      </c>
+      <c r="AR241">
+        <v>1.82</v>
+      </c>
+      <c r="AS241">
+        <v>1.26</v>
+      </c>
+      <c r="AT241">
+        <v>3.08</v>
+      </c>
+      <c r="AU241">
+        <v>5</v>
+      </c>
+      <c r="AV241">
+        <v>0</v>
+      </c>
+      <c r="AW241">
+        <v>9</v>
+      </c>
+      <c r="AX241">
+        <v>6</v>
+      </c>
+      <c r="AY241">
+        <v>14</v>
+      </c>
+      <c r="AZ241">
+        <v>6</v>
+      </c>
+      <c r="BA241">
+        <v>8</v>
+      </c>
+      <c r="BB241">
+        <v>4</v>
+      </c>
+      <c r="BC241">
+        <v>12</v>
+      </c>
+      <c r="BD241">
+        <v>1.58</v>
+      </c>
+      <c r="BE241">
+        <v>6.75</v>
+      </c>
+      <c r="BF241">
+        <v>2.55</v>
+      </c>
+      <c r="BG241">
+        <v>1.24</v>
+      </c>
+      <c r="BH241">
+        <v>3.55</v>
+      </c>
+      <c r="BI241">
+        <v>1.43</v>
+      </c>
+      <c r="BJ241">
+        <v>2.55</v>
+      </c>
+      <c r="BK241">
+        <v>1.7</v>
+      </c>
+      <c r="BL241">
+        <v>2.02</v>
+      </c>
+      <c r="BM241">
+        <v>2.07</v>
+      </c>
+      <c r="BN241">
+        <v>1.66</v>
+      </c>
+      <c r="BO241">
+        <v>2.65</v>
+      </c>
+      <c r="BP241">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7465658</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F242">
+        <v>25</v>
+      </c>
+      <c r="G242" t="s">
+        <v>70</v>
+      </c>
+      <c r="H242" t="s">
+        <v>74</v>
+      </c>
+      <c r="I242">
+        <v>2</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>2</v>
+      </c>
+      <c r="L242">
+        <v>3</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>3</v>
+      </c>
+      <c r="O242" t="s">
+        <v>257</v>
+      </c>
+      <c r="P242" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q242">
+        <v>2.38</v>
+      </c>
+      <c r="R242">
+        <v>2.3</v>
+      </c>
+      <c r="S242">
+        <v>4.5</v>
+      </c>
+      <c r="T242">
+        <v>1.33</v>
+      </c>
+      <c r="U242">
+        <v>3.25</v>
+      </c>
+      <c r="V242">
+        <v>2.63</v>
+      </c>
+      <c r="W242">
+        <v>1.44</v>
+      </c>
+      <c r="X242">
+        <v>6.5</v>
+      </c>
+      <c r="Y242">
+        <v>1.11</v>
+      </c>
+      <c r="Z242">
+        <v>1.72</v>
+      </c>
+      <c r="AA242">
+        <v>3.89</v>
+      </c>
+      <c r="AB242">
+        <v>4.54</v>
+      </c>
+      <c r="AC242">
+        <v>1.03</v>
+      </c>
+      <c r="AD242">
+        <v>13</v>
+      </c>
+      <c r="AE242">
+        <v>1.22</v>
+      </c>
+      <c r="AF242">
+        <v>4.2</v>
+      </c>
+      <c r="AG242">
+        <v>1.68</v>
+      </c>
+      <c r="AH242">
+        <v>2.1</v>
+      </c>
+      <c r="AI242">
+        <v>1.67</v>
+      </c>
+      <c r="AJ242">
+        <v>2.1</v>
+      </c>
+      <c r="AK242">
+        <v>1.21</v>
+      </c>
+      <c r="AL242">
+        <v>1.25</v>
+      </c>
+      <c r="AM242">
+        <v>2</v>
+      </c>
+      <c r="AN242">
+        <v>1.09</v>
+      </c>
+      <c r="AO242">
+        <v>0.45</v>
+      </c>
+      <c r="AP242">
+        <v>1.25</v>
+      </c>
+      <c r="AQ242">
+        <v>0.42</v>
+      </c>
+      <c r="AR242">
+        <v>1.34</v>
+      </c>
+      <c r="AS242">
+        <v>1.11</v>
+      </c>
+      <c r="AT242">
+        <v>2.45</v>
+      </c>
+      <c r="AU242">
+        <v>7</v>
+      </c>
+      <c r="AV242">
+        <v>2</v>
+      </c>
+      <c r="AW242">
+        <v>3</v>
+      </c>
+      <c r="AX242">
+        <v>3</v>
+      </c>
+      <c r="AY242">
+        <v>10</v>
+      </c>
+      <c r="AZ242">
+        <v>5</v>
+      </c>
+      <c r="BA242">
+        <v>3</v>
+      </c>
+      <c r="BB242">
+        <v>2</v>
+      </c>
+      <c r="BC242">
+        <v>5</v>
+      </c>
+      <c r="BD242">
+        <v>1.54</v>
+      </c>
+      <c r="BE242">
+        <v>6.75</v>
+      </c>
+      <c r="BF242">
+        <v>2.7</v>
+      </c>
+      <c r="BG242">
+        <v>1.24</v>
+      </c>
+      <c r="BH242">
+        <v>3.55</v>
+      </c>
+      <c r="BI242">
+        <v>1.44</v>
+      </c>
+      <c r="BJ242">
+        <v>2.55</v>
+      </c>
+      <c r="BK242">
+        <v>1.71</v>
+      </c>
+      <c r="BL242">
+        <v>2</v>
+      </c>
+      <c r="BM242">
+        <v>2.08</v>
+      </c>
+      <c r="BN242">
+        <v>1.65</v>
+      </c>
+      <c r="BO242">
+        <v>2.65</v>
+      </c>
+      <c r="BP242">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7465660</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45695.66666666666</v>
+      </c>
+      <c r="F243">
+        <v>25</v>
+      </c>
+      <c r="G243" t="s">
+        <v>88</v>
+      </c>
+      <c r="H243" t="s">
+        <v>76</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>1</v>
+      </c>
+      <c r="M243">
+        <v>2</v>
+      </c>
+      <c r="N243">
+        <v>3</v>
+      </c>
+      <c r="O243" t="s">
+        <v>258</v>
+      </c>
+      <c r="P243" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q243">
+        <v>2.5</v>
+      </c>
+      <c r="R243">
+        <v>2.5</v>
+      </c>
+      <c r="S243">
+        <v>3.75</v>
+      </c>
+      <c r="T243">
+        <v>1.25</v>
+      </c>
+      <c r="U243">
+        <v>3.75</v>
+      </c>
+      <c r="V243">
+        <v>2.2</v>
+      </c>
+      <c r="W243">
+        <v>1.62</v>
+      </c>
+      <c r="X243">
+        <v>5</v>
+      </c>
+      <c r="Y243">
+        <v>1.17</v>
+      </c>
+      <c r="Z243">
+        <v>1.95</v>
+      </c>
+      <c r="AA243">
+        <v>3.7</v>
+      </c>
+      <c r="AB243">
+        <v>3.6</v>
+      </c>
+      <c r="AC243">
+        <v>1.01</v>
+      </c>
+      <c r="AD243">
+        <v>15</v>
+      </c>
+      <c r="AE243">
+        <v>1.16</v>
+      </c>
+      <c r="AF243">
+        <v>5</v>
+      </c>
+      <c r="AG243">
+        <v>1.5</v>
+      </c>
+      <c r="AH243">
+        <v>2.5</v>
+      </c>
+      <c r="AI243">
+        <v>1.44</v>
+      </c>
+      <c r="AJ243">
+        <v>2.63</v>
+      </c>
+      <c r="AK243">
+        <v>1.31</v>
+      </c>
+      <c r="AL243">
+        <v>1.25</v>
+      </c>
+      <c r="AM243">
+        <v>1.78</v>
+      </c>
+      <c r="AN243">
+        <v>2.5</v>
+      </c>
+      <c r="AO243">
+        <v>1.18</v>
+      </c>
+      <c r="AP243">
+        <v>2.31</v>
+      </c>
+      <c r="AQ243">
+        <v>1.33</v>
+      </c>
+      <c r="AR243">
+        <v>1.91</v>
+      </c>
+      <c r="AS243">
+        <v>1.5</v>
+      </c>
+      <c r="AT243">
+        <v>3.41</v>
+      </c>
+      <c r="AU243">
+        <v>4</v>
+      </c>
+      <c r="AV243">
+        <v>4</v>
+      </c>
+      <c r="AW243">
+        <v>9</v>
+      </c>
+      <c r="AX243">
+        <v>12</v>
+      </c>
+      <c r="AY243">
+        <v>13</v>
+      </c>
+      <c r="AZ243">
+        <v>17</v>
+      </c>
+      <c r="BA243">
+        <v>4</v>
+      </c>
+      <c r="BB243">
+        <v>7</v>
+      </c>
+      <c r="BC243">
+        <v>11</v>
+      </c>
+      <c r="BD243">
+        <v>1.63</v>
+      </c>
+      <c r="BE243">
+        <v>6.4</v>
+      </c>
+      <c r="BF243">
+        <v>2.55</v>
+      </c>
+      <c r="BG243">
+        <v>1.36</v>
+      </c>
+      <c r="BH243">
+        <v>2.85</v>
+      </c>
+      <c r="BI243">
+        <v>1.6</v>
+      </c>
+      <c r="BJ243">
+        <v>2.17</v>
+      </c>
+      <c r="BK243">
+        <v>1.98</v>
+      </c>
+      <c r="BL243">
+        <v>1.74</v>
+      </c>
+      <c r="BM243">
+        <v>2.5</v>
+      </c>
+      <c r="BN243">
+        <v>1.46</v>
+      </c>
+      <c r="BO243">
+        <v>3.3</v>
+      </c>
+      <c r="BP243">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1152,6 +1152,9 @@
   <si>
     <t>['47', '56']</t>
   </si>
+  <si>
+    <t>['2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1512,7 +1515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP243"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2055,7 +2058,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2258,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>0.45</v>
@@ -7617,7 +7620,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -8850,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -11531,7 +11534,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ49">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -13176,7 +13179,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.42</v>
@@ -13797,7 +13800,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ60">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -14412,7 +14415,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.58</v>
@@ -17917,7 +17920,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ80">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -20180,7 +20183,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>0.75</v>
@@ -21007,7 +21010,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ95">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -23270,7 +23273,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
         <v>1.23</v>
@@ -26981,7 +26984,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ124">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -28008,7 +28011,7 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129">
         <v>1.42</v>
@@ -31101,7 +31104,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ144">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -32334,7 +32337,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
         <v>1.54</v>
@@ -33982,7 +33985,7 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>1.33</v>
@@ -36457,7 +36460,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ170">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -37690,7 +37693,7 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1.42</v>
@@ -39135,7 +39138,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ183">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -43049,7 +43052,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ202">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -47581,7 +47584,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ224">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR224">
         <v>1.73</v>
@@ -48196,7 +48199,7 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ227">
         <v>1.15</v>
@@ -51381,7 +51384,7 @@
         <v>69</v>
       </c>
       <c r="E243" s="2">
-        <v>45695.66666666666</v>
+        <v>45695.67361111111</v>
       </c>
       <c r="F243">
         <v>25</v>
@@ -51571,6 +51574,212 @@
       </c>
       <c r="BP243">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7465662</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45696.52083333334</v>
+      </c>
+      <c r="F244">
+        <v>25</v>
+      </c>
+      <c r="G244" t="s">
+        <v>72</v>
+      </c>
+      <c r="H244" t="s">
+        <v>86</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>1</v>
+      </c>
+      <c r="L244">
+        <v>0</v>
+      </c>
+      <c r="M244">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>1</v>
+      </c>
+      <c r="O244" t="s">
+        <v>93</v>
+      </c>
+      <c r="P244" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q244">
+        <v>3.1</v>
+      </c>
+      <c r="R244">
+        <v>2.3</v>
+      </c>
+      <c r="S244">
+        <v>3.1</v>
+      </c>
+      <c r="T244">
+        <v>1.3</v>
+      </c>
+      <c r="U244">
+        <v>3.4</v>
+      </c>
+      <c r="V244">
+        <v>2.5</v>
+      </c>
+      <c r="W244">
+        <v>1.5</v>
+      </c>
+      <c r="X244">
+        <v>6</v>
+      </c>
+      <c r="Y244">
+        <v>1.13</v>
+      </c>
+      <c r="Z244">
+        <v>2.54</v>
+      </c>
+      <c r="AA244">
+        <v>3.59</v>
+      </c>
+      <c r="AB244">
+        <v>2.6</v>
+      </c>
+      <c r="AC244">
+        <v>1.02</v>
+      </c>
+      <c r="AD244">
+        <v>15</v>
+      </c>
+      <c r="AE244">
+        <v>1.2</v>
+      </c>
+      <c r="AF244">
+        <v>4.5</v>
+      </c>
+      <c r="AG244">
+        <v>1.62</v>
+      </c>
+      <c r="AH244">
+        <v>2.25</v>
+      </c>
+      <c r="AI244">
+        <v>1.5</v>
+      </c>
+      <c r="AJ244">
+        <v>2.5</v>
+      </c>
+      <c r="AK244">
+        <v>1.52</v>
+      </c>
+      <c r="AL244">
+        <v>1.25</v>
+      </c>
+      <c r="AM244">
+        <v>1.53</v>
+      </c>
+      <c r="AN244">
+        <v>1.64</v>
+      </c>
+      <c r="AO244">
+        <v>1.58</v>
+      </c>
+      <c r="AP244">
+        <v>1.5</v>
+      </c>
+      <c r="AQ244">
+        <v>1.69</v>
+      </c>
+      <c r="AR244">
+        <v>1.44</v>
+      </c>
+      <c r="AS244">
+        <v>1.25</v>
+      </c>
+      <c r="AT244">
+        <v>2.69</v>
+      </c>
+      <c r="AU244">
+        <v>8</v>
+      </c>
+      <c r="AV244">
+        <v>5</v>
+      </c>
+      <c r="AW244">
+        <v>10</v>
+      </c>
+      <c r="AX244">
+        <v>7</v>
+      </c>
+      <c r="AY244">
+        <v>18</v>
+      </c>
+      <c r="AZ244">
+        <v>12</v>
+      </c>
+      <c r="BA244">
+        <v>8</v>
+      </c>
+      <c r="BB244">
+        <v>2</v>
+      </c>
+      <c r="BC244">
+        <v>10</v>
+      </c>
+      <c r="BD244">
+        <v>2</v>
+      </c>
+      <c r="BE244">
+        <v>6.4</v>
+      </c>
+      <c r="BF244">
+        <v>1.98</v>
+      </c>
+      <c r="BG244">
+        <v>1.29</v>
+      </c>
+      <c r="BH244">
+        <v>3.15</v>
+      </c>
+      <c r="BI244">
+        <v>1.5</v>
+      </c>
+      <c r="BJ244">
+        <v>2.35</v>
+      </c>
+      <c r="BK244">
+        <v>1.82</v>
+      </c>
+      <c r="BL244">
+        <v>1.86</v>
+      </c>
+      <c r="BM244">
+        <v>2.3</v>
+      </c>
+      <c r="BN244">
+        <v>1.54</v>
+      </c>
+      <c r="BO244">
+        <v>2.95</v>
+      </c>
+      <c r="BP244">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="381">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -793,6 +793,9 @@
     <t>['64']</t>
   </si>
   <si>
+    <t>['4', '21', '71', '79', '88', '90+3']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1515,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1977,7 +1980,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2183,7 +2186,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2264,7 +2267,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2389,7 +2392,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2595,7 +2598,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2801,7 +2804,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3007,7 +3010,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3213,7 +3216,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3625,7 +3628,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3909,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -4037,7 +4040,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4115,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ13">
         <v>1.54</v>
@@ -4655,7 +4658,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5479,7 +5482,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5766,7 +5769,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6384,7 +6387,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR24">
         <v>2.49</v>
@@ -6509,7 +6512,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6590,7 +6593,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ25">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6715,7 +6718,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6921,7 +6924,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7333,7 +7336,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7411,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ29">
         <v>1.23</v>
@@ -7745,7 +7748,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8235,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ33">
         <v>1.15</v>
@@ -8363,7 +8366,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8569,7 +8572,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9187,7 +9190,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9393,7 +9396,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9805,7 +9808,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10295,10 +10298,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ43">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR43">
         <v>1.9</v>
@@ -10423,7 +10426,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10629,7 +10632,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10707,10 +10710,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ45">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -10835,7 +10838,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11041,7 +11044,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11247,7 +11250,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11659,7 +11662,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11865,7 +11868,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12071,7 +12074,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12895,7 +12898,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13307,7 +13310,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13513,7 +13516,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13925,7 +13928,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14131,7 +14134,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14209,7 +14212,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14337,7 +14340,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14955,7 +14958,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15242,7 +15245,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ67">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR67">
         <v>1.6</v>
@@ -15367,7 +15370,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15573,7 +15576,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15779,7 +15782,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15985,7 +15988,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16191,7 +16194,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16397,7 +16400,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16603,7 +16606,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16809,7 +16812,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16890,7 +16893,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ75">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17299,7 +17302,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ77">
         <v>1.42</v>
@@ -17427,7 +17430,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17633,7 +17636,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18045,7 +18048,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18329,7 +18332,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ82">
         <v>2.08</v>
@@ -18457,7 +18460,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18663,7 +18666,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19281,7 +19284,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19568,7 +19571,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ88">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR88">
         <v>1.89</v>
@@ -19899,7 +19902,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20311,7 +20314,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20389,7 +20392,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20723,7 +20726,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20929,7 +20932,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21007,7 +21010,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ95">
         <v>1.69</v>
@@ -21135,7 +21138,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21341,7 +21344,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21628,7 +21631,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ98">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21753,7 +21756,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22165,7 +22168,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22246,7 +22249,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ101">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR101">
         <v>1.83</v>
@@ -22371,7 +22374,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22783,7 +22786,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23195,7 +23198,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24019,7 +24022,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24225,7 +24228,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24431,7 +24434,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24718,7 +24721,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ113">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -25049,7 +25052,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25255,7 +25258,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25461,7 +25464,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25667,7 +25670,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25745,7 +25748,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ118">
         <v>1.42</v>
@@ -25873,7 +25876,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26079,7 +26082,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26285,7 +26288,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26491,7 +26494,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26697,7 +26700,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26903,7 +26906,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27109,7 +27112,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27521,7 +27524,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27727,7 +27730,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27805,7 +27808,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ128">
         <v>1.58</v>
@@ -28139,7 +28142,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28220,7 +28223,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ130">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28345,7 +28348,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28757,7 +28760,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28835,7 +28838,7 @@
         <v>1.17</v>
       </c>
       <c r="AP133">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ133">
         <v>1.15</v>
@@ -29375,7 +29378,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30074,7 +30077,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ139">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30689,7 +30692,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142">
         <v>1.33</v>
@@ -30817,7 +30820,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -30898,7 +30901,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ143">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR143">
         <v>1.29</v>
@@ -31023,7 +31026,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31229,7 +31232,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31435,7 +31438,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31513,7 +31516,7 @@
         <v>2.5</v>
       </c>
       <c r="AP146">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ146">
         <v>1.9</v>
@@ -31641,7 +31644,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31847,7 +31850,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32259,7 +32262,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32465,7 +32468,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32877,7 +32880,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33083,7 +33086,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33289,7 +33292,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34319,7 +34322,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34731,7 +34734,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35349,7 +35352,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35555,7 +35558,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35633,7 +35636,7 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ166">
         <v>2.08</v>
@@ -35761,7 +35764,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36048,7 +36051,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ168">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -36173,7 +36176,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36379,7 +36382,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36585,7 +36588,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36666,7 +36669,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ171">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -36869,7 +36872,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ172">
         <v>0.42</v>
@@ -36997,7 +37000,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37203,7 +37206,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37821,7 +37824,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38027,7 +38030,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38439,7 +38442,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38645,7 +38648,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38929,7 +38932,7 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ182">
         <v>1.42</v>
@@ -39263,7 +39266,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39469,7 +39472,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39675,7 +39678,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40168,7 +40171,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ188">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40293,7 +40296,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40786,7 +40789,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ191">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -40911,7 +40914,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41117,7 +41120,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41323,7 +41326,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41529,7 +41532,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41735,7 +41738,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42019,7 +42022,7 @@
         <v>1.6</v>
       </c>
       <c r="AP197">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ197">
         <v>1.42</v>
@@ -42353,7 +42356,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42765,7 +42768,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43258,7 +43261,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ203">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -43383,7 +43386,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43667,7 +43670,7 @@
         <v>1.3</v>
       </c>
       <c r="AP205">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43795,7 +43798,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44001,7 +44004,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44207,7 +44210,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44413,7 +44416,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44619,7 +44622,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44903,7 +44906,7 @@
         <v>1.09</v>
       </c>
       <c r="AP211">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ211">
         <v>0.92</v>
@@ -45649,7 +45652,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46061,7 +46064,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46885,7 +46888,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47172,7 +47175,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ222">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR222">
         <v>1.91</v>
@@ -47378,7 +47381,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ223">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR223">
         <v>1.93</v>
@@ -47503,7 +47506,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47787,7 +47790,7 @@
         <v>0.82</v>
       </c>
       <c r="AP225">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ225">
         <v>0.75</v>
@@ -48121,7 +48124,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48327,7 +48330,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48614,7 +48617,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ229">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR229">
         <v>1.74</v>
@@ -49357,7 +49360,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49769,7 +49772,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49975,7 +49978,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50387,7 +50390,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50799,7 +50802,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51417,7 +51420,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51623,7 +51626,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51780,6 +51783,418 @@
       </c>
       <c r="BP244">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7465663</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45697.34375</v>
+      </c>
+      <c r="F245">
+        <v>25</v>
+      </c>
+      <c r="G245" t="s">
+        <v>80</v>
+      </c>
+      <c r="H245" t="s">
+        <v>73</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>0</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245" t="s">
+        <v>93</v>
+      </c>
+      <c r="P245" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q245">
+        <v>2.88</v>
+      </c>
+      <c r="R245">
+        <v>2.38</v>
+      </c>
+      <c r="S245">
+        <v>3.25</v>
+      </c>
+      <c r="T245">
+        <v>1.3</v>
+      </c>
+      <c r="U245">
+        <v>3.4</v>
+      </c>
+      <c r="V245">
+        <v>2.38</v>
+      </c>
+      <c r="W245">
+        <v>1.53</v>
+      </c>
+      <c r="X245">
+        <v>6</v>
+      </c>
+      <c r="Y245">
+        <v>1.13</v>
+      </c>
+      <c r="Z245">
+        <v>2.35</v>
+      </c>
+      <c r="AA245">
+        <v>3.6</v>
+      </c>
+      <c r="AB245">
+        <v>2.7</v>
+      </c>
+      <c r="AC245">
+        <v>1.02</v>
+      </c>
+      <c r="AD245">
+        <v>17</v>
+      </c>
+      <c r="AE245">
+        <v>1.18</v>
+      </c>
+      <c r="AF245">
+        <v>4.75</v>
+      </c>
+      <c r="AG245">
+        <v>1.53</v>
+      </c>
+      <c r="AH245">
+        <v>2.4</v>
+      </c>
+      <c r="AI245">
+        <v>1.5</v>
+      </c>
+      <c r="AJ245">
+        <v>2.5</v>
+      </c>
+      <c r="AK245">
+        <v>1.45</v>
+      </c>
+      <c r="AL245">
+        <v>1.25</v>
+      </c>
+      <c r="AM245">
+        <v>1.57</v>
+      </c>
+      <c r="AN245">
+        <v>0.75</v>
+      </c>
+      <c r="AO245">
+        <v>0.58</v>
+      </c>
+      <c r="AP245">
+        <v>0.77</v>
+      </c>
+      <c r="AQ245">
+        <v>0.62</v>
+      </c>
+      <c r="AR245">
+        <v>1.55</v>
+      </c>
+      <c r="AS245">
+        <v>1.3</v>
+      </c>
+      <c r="AT245">
+        <v>2.85</v>
+      </c>
+      <c r="AU245">
+        <v>5</v>
+      </c>
+      <c r="AV245">
+        <v>4</v>
+      </c>
+      <c r="AW245">
+        <v>21</v>
+      </c>
+      <c r="AX245">
+        <v>6</v>
+      </c>
+      <c r="AY245">
+        <v>26</v>
+      </c>
+      <c r="AZ245">
+        <v>10</v>
+      </c>
+      <c r="BA245">
+        <v>10</v>
+      </c>
+      <c r="BB245">
+        <v>3</v>
+      </c>
+      <c r="BC245">
+        <v>13</v>
+      </c>
+      <c r="BD245">
+        <v>1.88</v>
+      </c>
+      <c r="BE245">
+        <v>6.4</v>
+      </c>
+      <c r="BF245">
+        <v>2.12</v>
+      </c>
+      <c r="BG245">
+        <v>1.32</v>
+      </c>
+      <c r="BH245">
+        <v>3.05</v>
+      </c>
+      <c r="BI245">
+        <v>1.54</v>
+      </c>
+      <c r="BJ245">
+        <v>2.28</v>
+      </c>
+      <c r="BK245">
+        <v>1.89</v>
+      </c>
+      <c r="BL245">
+        <v>1.8</v>
+      </c>
+      <c r="BM245">
+        <v>2.4</v>
+      </c>
+      <c r="BN245">
+        <v>1.5</v>
+      </c>
+      <c r="BO245">
+        <v>3.1</v>
+      </c>
+      <c r="BP245">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7465665</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45697.53125</v>
+      </c>
+      <c r="F246">
+        <v>25</v>
+      </c>
+      <c r="G246" t="s">
+        <v>81</v>
+      </c>
+      <c r="H246" t="s">
+        <v>84</v>
+      </c>
+      <c r="I246">
+        <v>2</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>2</v>
+      </c>
+      <c r="L246">
+        <v>6</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>6</v>
+      </c>
+      <c r="O246" t="s">
+        <v>259</v>
+      </c>
+      <c r="P246" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q246">
+        <v>1.83</v>
+      </c>
+      <c r="R246">
+        <v>2.6</v>
+      </c>
+      <c r="S246">
+        <v>6.5</v>
+      </c>
+      <c r="T246">
+        <v>1.29</v>
+      </c>
+      <c r="U246">
+        <v>3.5</v>
+      </c>
+      <c r="V246">
+        <v>2.25</v>
+      </c>
+      <c r="W246">
+        <v>1.57</v>
+      </c>
+      <c r="X246">
+        <v>5.5</v>
+      </c>
+      <c r="Y246">
+        <v>1.14</v>
+      </c>
+      <c r="Z246">
+        <v>1.4</v>
+      </c>
+      <c r="AA246">
+        <v>4.75</v>
+      </c>
+      <c r="AB246">
+        <v>7</v>
+      </c>
+      <c r="AC246">
+        <v>1.01</v>
+      </c>
+      <c r="AD246">
+        <v>17</v>
+      </c>
+      <c r="AE246">
+        <v>1.16</v>
+      </c>
+      <c r="AF246">
+        <v>5</v>
+      </c>
+      <c r="AG246">
+        <v>1.53</v>
+      </c>
+      <c r="AH246">
+        <v>2.4</v>
+      </c>
+      <c r="AI246">
+        <v>1.73</v>
+      </c>
+      <c r="AJ246">
+        <v>2</v>
+      </c>
+      <c r="AK246">
+        <v>1.07</v>
+      </c>
+      <c r="AL246">
+        <v>1.12</v>
+      </c>
+      <c r="AM246">
+        <v>3.1</v>
+      </c>
+      <c r="AN246">
+        <v>1.82</v>
+      </c>
+      <c r="AO246">
+        <v>0.45</v>
+      </c>
+      <c r="AP246">
+        <v>1.92</v>
+      </c>
+      <c r="AQ246">
+        <v>0.42</v>
+      </c>
+      <c r="AR246">
+        <v>1.7</v>
+      </c>
+      <c r="AS246">
+        <v>1.21</v>
+      </c>
+      <c r="AT246">
+        <v>2.91</v>
+      </c>
+      <c r="AU246">
+        <v>10</v>
+      </c>
+      <c r="AV246">
+        <v>3</v>
+      </c>
+      <c r="AW246">
+        <v>10</v>
+      </c>
+      <c r="AX246">
+        <v>3</v>
+      </c>
+      <c r="AY246">
+        <v>20</v>
+      </c>
+      <c r="AZ246">
+        <v>6</v>
+      </c>
+      <c r="BA246">
+        <v>13</v>
+      </c>
+      <c r="BB246">
+        <v>2</v>
+      </c>
+      <c r="BC246">
+        <v>15</v>
+      </c>
+      <c r="BD246">
+        <v>1.33</v>
+      </c>
+      <c r="BE246">
+        <v>7.5</v>
+      </c>
+      <c r="BF246">
+        <v>3.55</v>
+      </c>
+      <c r="BG246">
+        <v>1.29</v>
+      </c>
+      <c r="BH246">
+        <v>3.2</v>
+      </c>
+      <c r="BI246">
+        <v>1.5</v>
+      </c>
+      <c r="BJ246">
+        <v>2.35</v>
+      </c>
+      <c r="BK246">
+        <v>1.84</v>
+      </c>
+      <c r="BL246">
+        <v>1.84</v>
+      </c>
+      <c r="BM246">
+        <v>2.3</v>
+      </c>
+      <c r="BN246">
+        <v>1.54</v>
+      </c>
+      <c r="BO246">
+        <v>2.9</v>
+      </c>
+      <c r="BP246">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="385">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,15 @@
     <t>['4', '21', '71', '79', '88', '90+3']</t>
   </si>
   <si>
+    <t>['53', '57', '81']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['36', '59']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -857,9 +866,6 @@
   </si>
   <si>
     <t>['18', '68', '83', '90+2']</t>
-  </si>
-  <si>
-    <t>['51']</t>
   </si>
   <si>
     <t>['40', '49']</t>
@@ -1157,6 +1163,12 @@
   </si>
   <si>
     <t>['2']</t>
+  </si>
+  <si>
+    <t>['22', '60']</t>
+  </si>
+  <si>
+    <t>['13', '18', '76', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1518,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP246"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1980,7 +1992,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2186,7 +2198,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2392,7 +2404,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2473,7 +2485,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ5">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2598,7 +2610,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2679,7 +2691,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ6">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2804,7 +2816,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2882,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>0.92</v>
@@ -3010,7 +3022,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3216,7 +3228,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3628,7 +3640,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3706,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ11">
         <v>0.75</v>
@@ -4040,7 +4052,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4658,7 +4670,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5482,7 +5494,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5563,7 +5575,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ20">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5766,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
         <v>0.62</v>
@@ -5975,7 +5987,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ22">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6512,7 +6524,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6718,7 +6730,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6924,7 +6936,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7208,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7336,7 +7348,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7748,7 +7760,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7826,7 +7838,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ31">
         <v>0.92</v>
@@ -8032,7 +8044,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
         <v>1.54</v>
@@ -8366,7 +8378,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8572,7 +8584,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8653,7 +8665,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -9065,7 +9077,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ37">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9190,7 +9202,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9271,7 +9283,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ38">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9396,7 +9408,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9474,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1.42</v>
@@ -9808,7 +9820,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10426,7 +10438,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -10632,7 +10644,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10838,7 +10850,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11044,7 +11056,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11250,7 +11262,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11662,7 +11674,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11868,7 +11880,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12074,7 +12086,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12898,7 +12910,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13310,7 +13322,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13516,7 +13528,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13594,7 +13606,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ59">
         <v>1.33</v>
@@ -13928,7 +13940,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14006,7 +14018,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
         <v>1.15</v>
@@ -14134,7 +14146,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14340,7 +14352,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14627,7 +14639,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ64">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -14958,7 +14970,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15039,7 +15051,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ66">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15370,7 +15382,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15448,7 +15460,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ68">
         <v>0.75</v>
@@ -15576,7 +15588,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15782,7 +15794,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15988,7 +16000,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16069,7 +16081,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16194,7 +16206,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16400,7 +16412,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16606,7 +16618,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16812,7 +16824,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17430,7 +17442,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17636,7 +17648,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17717,7 +17729,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ79">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -17920,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>1.69</v>
@@ -18048,7 +18060,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18126,7 +18138,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ81">
         <v>1.42</v>
@@ -18335,7 +18347,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ82">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18460,7 +18472,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18538,7 +18550,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.58</v>
@@ -18666,7 +18678,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18953,7 +18965,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ85">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19284,7 +19296,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19902,7 +19914,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20314,7 +20326,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20726,7 +20738,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20932,7 +20944,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21138,7 +21150,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21344,7 +21356,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21628,7 +21640,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
         <v>0.42</v>
@@ -21756,7 +21768,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21837,7 +21849,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ99">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22168,7 +22180,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22374,7 +22386,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22786,7 +22798,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22864,10 +22876,10 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ104">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23070,7 +23082,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23198,7 +23210,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24022,7 +24034,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24228,7 +24240,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24434,7 +24446,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25052,7 +25064,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25258,7 +25270,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25464,7 +25476,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25542,7 +25554,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25670,7 +25682,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25876,7 +25888,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25957,7 +25969,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ119">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -26082,7 +26094,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26288,7 +26300,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26494,7 +26506,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26575,7 +26587,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ122">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26700,7 +26712,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26778,7 +26790,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -26906,7 +26918,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27112,7 +27124,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27396,7 +27408,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ126">
         <v>0.42</v>
@@ -27524,7 +27536,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27730,7 +27742,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28017,7 +28029,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28142,7 +28154,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28348,7 +28360,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28426,10 +28438,10 @@
         <v>2.4</v>
       </c>
       <c r="AP131">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ131">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28760,7 +28772,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29378,7 +29390,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30820,7 +30832,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -31026,7 +31038,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31232,7 +31244,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31310,7 +31322,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ145">
         <v>1.58</v>
@@ -31438,7 +31450,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31519,7 +31531,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ146">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31644,7 +31656,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31722,10 +31734,10 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ147">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -31850,7 +31862,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32134,7 +32146,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ149">
         <v>0.92</v>
@@ -32262,7 +32274,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32468,7 +32480,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32549,7 +32561,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ151">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -32880,7 +32892,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33086,7 +33098,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33164,7 +33176,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ154">
         <v>1.15</v>
@@ -33292,7 +33304,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34322,7 +34334,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34609,7 +34621,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ161">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34734,7 +34746,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34815,7 +34827,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ162">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35352,7 +35364,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35558,7 +35570,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35639,7 +35651,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ166">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -35764,7 +35776,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35842,7 +35854,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ167">
         <v>1.42</v>
@@ -36176,7 +36188,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36382,7 +36394,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36588,7 +36600,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37000,7 +37012,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37206,7 +37218,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37824,7 +37836,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38030,7 +38042,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38111,7 +38123,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38314,7 +38326,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38442,7 +38454,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38648,7 +38660,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38726,7 +38738,7 @@
         <v>1.11</v>
       </c>
       <c r="AP181">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ181">
         <v>1.23</v>
@@ -39266,7 +39278,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39347,7 +39359,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ184">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39472,7 +39484,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39678,7 +39690,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39759,7 +39771,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ186">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40296,7 +40308,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40786,7 +40798,7 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ191">
         <v>0.42</v>
@@ -40914,7 +40926,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41120,7 +41132,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41198,7 +41210,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41326,7 +41338,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41532,7 +41544,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41738,7 +41750,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42025,7 +42037,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ197">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42356,7 +42368,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42768,7 +42780,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42846,7 +42858,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ201">
         <v>1.23</v>
@@ -43386,7 +43398,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43798,7 +43810,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43876,7 +43888,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ206">
         <v>1.33</v>
@@ -44004,7 +44016,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44210,7 +44222,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44416,7 +44428,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44622,7 +44634,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -45321,7 +45333,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ213">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR213">
         <v>1.76</v>
@@ -45652,7 +45664,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45936,7 +45948,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ216">
         <v>1</v>
@@ -46064,7 +46076,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46351,7 +46363,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ218">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR218">
         <v>1.9</v>
@@ -46763,7 +46775,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ220">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR220">
         <v>1.66</v>
@@ -46888,7 +46900,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -46969,7 +46981,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ221">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AR221">
         <v>1.34</v>
@@ -47506,7 +47518,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47584,7 +47596,7 @@
         <v>1.45</v>
       </c>
       <c r="AP224">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ224">
         <v>1.69</v>
@@ -48124,7 +48136,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48330,7 +48342,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48408,7 +48420,7 @@
         <v>1.3</v>
       </c>
       <c r="AP228">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AQ228">
         <v>1.33</v>
@@ -49360,7 +49372,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49772,7 +49784,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49978,7 +49990,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50390,7 +50402,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50802,7 +50814,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51420,7 +51432,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51626,7 +51638,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52195,6 +52207,624 @@
       </c>
       <c r="BP246">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7465666</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45698.66666666666</v>
+      </c>
+      <c r="F247">
+        <v>25</v>
+      </c>
+      <c r="G247" t="s">
+        <v>89</v>
+      </c>
+      <c r="H247" t="s">
+        <v>83</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+      <c r="J247">
+        <v>1</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>3</v>
+      </c>
+      <c r="M247">
+        <v>2</v>
+      </c>
+      <c r="N247">
+        <v>5</v>
+      </c>
+      <c r="O247" t="s">
+        <v>260</v>
+      </c>
+      <c r="P247" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q247">
+        <v>4.5</v>
+      </c>
+      <c r="R247">
+        <v>2.5</v>
+      </c>
+      <c r="S247">
+        <v>2.2</v>
+      </c>
+      <c r="T247">
+        <v>1.25</v>
+      </c>
+      <c r="U247">
+        <v>3.75</v>
+      </c>
+      <c r="V247">
+        <v>2.2</v>
+      </c>
+      <c r="W247">
+        <v>1.62</v>
+      </c>
+      <c r="X247">
+        <v>5</v>
+      </c>
+      <c r="Y247">
+        <v>1.17</v>
+      </c>
+      <c r="Z247">
+        <v>4.33</v>
+      </c>
+      <c r="AA247">
+        <v>4.33</v>
+      </c>
+      <c r="AB247">
+        <v>1.67</v>
+      </c>
+      <c r="AC247">
+        <v>1.01</v>
+      </c>
+      <c r="AD247">
+        <v>17</v>
+      </c>
+      <c r="AE247">
+        <v>1.14</v>
+      </c>
+      <c r="AF247">
+        <v>5.5</v>
+      </c>
+      <c r="AG247">
+        <v>1.48</v>
+      </c>
+      <c r="AH247">
+        <v>2.6</v>
+      </c>
+      <c r="AI247">
+        <v>1.5</v>
+      </c>
+      <c r="AJ247">
+        <v>2.5</v>
+      </c>
+      <c r="AK247">
+        <v>2.35</v>
+      </c>
+      <c r="AL247">
+        <v>1.16</v>
+      </c>
+      <c r="AM247">
+        <v>1.2</v>
+      </c>
+      <c r="AN247">
+        <v>1.36</v>
+      </c>
+      <c r="AO247">
+        <v>1.42</v>
+      </c>
+      <c r="AP247">
+        <v>1.5</v>
+      </c>
+      <c r="AQ247">
+        <v>1.31</v>
+      </c>
+      <c r="AR247">
+        <v>1.71</v>
+      </c>
+      <c r="AS247">
+        <v>1.73</v>
+      </c>
+      <c r="AT247">
+        <v>3.44</v>
+      </c>
+      <c r="AU247">
+        <v>9</v>
+      </c>
+      <c r="AV247">
+        <v>4</v>
+      </c>
+      <c r="AW247">
+        <v>6</v>
+      </c>
+      <c r="AX247">
+        <v>8</v>
+      </c>
+      <c r="AY247">
+        <v>15</v>
+      </c>
+      <c r="AZ247">
+        <v>12</v>
+      </c>
+      <c r="BA247">
+        <v>9</v>
+      </c>
+      <c r="BB247">
+        <v>7</v>
+      </c>
+      <c r="BC247">
+        <v>16</v>
+      </c>
+      <c r="BD247">
+        <v>2.9</v>
+      </c>
+      <c r="BE247">
+        <v>7</v>
+      </c>
+      <c r="BF247">
+        <v>1.5</v>
+      </c>
+      <c r="BG247">
+        <v>1.22</v>
+      </c>
+      <c r="BH247">
+        <v>3.8</v>
+      </c>
+      <c r="BI247">
+        <v>1.38</v>
+      </c>
+      <c r="BJ247">
+        <v>2.75</v>
+      </c>
+      <c r="BK247">
+        <v>1.63</v>
+      </c>
+      <c r="BL247">
+        <v>2.12</v>
+      </c>
+      <c r="BM247">
+        <v>1.98</v>
+      </c>
+      <c r="BN247">
+        <v>1.73</v>
+      </c>
+      <c r="BO247">
+        <v>2.48</v>
+      </c>
+      <c r="BP247">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7465667</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45698.66666666666</v>
+      </c>
+      <c r="F248">
+        <v>25</v>
+      </c>
+      <c r="G248" t="s">
+        <v>79</v>
+      </c>
+      <c r="H248" t="s">
+        <v>87</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>2</v>
+      </c>
+      <c r="K248">
+        <v>2</v>
+      </c>
+      <c r="L248">
+        <v>1</v>
+      </c>
+      <c r="M248">
+        <v>4</v>
+      </c>
+      <c r="N248">
+        <v>5</v>
+      </c>
+      <c r="O248" t="s">
+        <v>261</v>
+      </c>
+      <c r="P248" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q248">
+        <v>4.5</v>
+      </c>
+      <c r="R248">
+        <v>2.6</v>
+      </c>
+      <c r="S248">
+        <v>2.2</v>
+      </c>
+      <c r="T248">
+        <v>1.25</v>
+      </c>
+      <c r="U248">
+        <v>3.75</v>
+      </c>
+      <c r="V248">
+        <v>2.1</v>
+      </c>
+      <c r="W248">
+        <v>1.67</v>
+      </c>
+      <c r="X248">
+        <v>4.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.18</v>
+      </c>
+      <c r="Z248">
+        <v>4.33</v>
+      </c>
+      <c r="AA248">
+        <v>4.33</v>
+      </c>
+      <c r="AB248">
+        <v>1.67</v>
+      </c>
+      <c r="AC248">
+        <v>1.01</v>
+      </c>
+      <c r="AD248">
+        <v>17</v>
+      </c>
+      <c r="AE248">
+        <v>1.14</v>
+      </c>
+      <c r="AF248">
+        <v>5.5</v>
+      </c>
+      <c r="AG248">
+        <v>1.44</v>
+      </c>
+      <c r="AH248">
+        <v>2.7</v>
+      </c>
+      <c r="AI248">
+        <v>1.5</v>
+      </c>
+      <c r="AJ248">
+        <v>2.5</v>
+      </c>
+      <c r="AK248">
+        <v>2.4</v>
+      </c>
+      <c r="AL248">
+        <v>1.2</v>
+      </c>
+      <c r="AM248">
+        <v>1.14</v>
+      </c>
+      <c r="AN248">
+        <v>0.73</v>
+      </c>
+      <c r="AO248">
+        <v>2.08</v>
+      </c>
+      <c r="AP248">
+        <v>0.67</v>
+      </c>
+      <c r="AQ248">
+        <v>2.15</v>
+      </c>
+      <c r="AR248">
+        <v>1.53</v>
+      </c>
+      <c r="AS248">
+        <v>1.86</v>
+      </c>
+      <c r="AT248">
+        <v>3.39</v>
+      </c>
+      <c r="AU248">
+        <v>6</v>
+      </c>
+      <c r="AV248">
+        <v>10</v>
+      </c>
+      <c r="AW248">
+        <v>6</v>
+      </c>
+      <c r="AX248">
+        <v>14</v>
+      </c>
+      <c r="AY248">
+        <v>14</v>
+      </c>
+      <c r="AZ248">
+        <v>32</v>
+      </c>
+      <c r="BA248">
+        <v>3</v>
+      </c>
+      <c r="BB248">
+        <v>6</v>
+      </c>
+      <c r="BC248">
+        <v>9</v>
+      </c>
+      <c r="BD248">
+        <v>3.4</v>
+      </c>
+      <c r="BE248">
+        <v>7</v>
+      </c>
+      <c r="BF248">
+        <v>1.38</v>
+      </c>
+      <c r="BG248">
+        <v>1.25</v>
+      </c>
+      <c r="BH248">
+        <v>3.45</v>
+      </c>
+      <c r="BI248">
+        <v>1.44</v>
+      </c>
+      <c r="BJ248">
+        <v>2.55</v>
+      </c>
+      <c r="BK248">
+        <v>1.7</v>
+      </c>
+      <c r="BL248">
+        <v>2.02</v>
+      </c>
+      <c r="BM248">
+        <v>2.08</v>
+      </c>
+      <c r="BN248">
+        <v>1.65</v>
+      </c>
+      <c r="BO248">
+        <v>2.65</v>
+      </c>
+      <c r="BP248">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7465668</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45698.66666666666</v>
+      </c>
+      <c r="F249">
+        <v>25</v>
+      </c>
+      <c r="G249" t="s">
+        <v>75</v>
+      </c>
+      <c r="H249" t="s">
+        <v>71</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>2</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>2</v>
+      </c>
+      <c r="O249" t="s">
+        <v>262</v>
+      </c>
+      <c r="P249" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q249">
+        <v>3.4</v>
+      </c>
+      <c r="R249">
+        <v>2.38</v>
+      </c>
+      <c r="S249">
+        <v>2.75</v>
+      </c>
+      <c r="T249">
+        <v>1.29</v>
+      </c>
+      <c r="U249">
+        <v>3.5</v>
+      </c>
+      <c r="V249">
+        <v>2.38</v>
+      </c>
+      <c r="W249">
+        <v>1.53</v>
+      </c>
+      <c r="X249">
+        <v>5.5</v>
+      </c>
+      <c r="Y249">
+        <v>1.14</v>
+      </c>
+      <c r="Z249">
+        <v>3</v>
+      </c>
+      <c r="AA249">
+        <v>3.6</v>
+      </c>
+      <c r="AB249">
+        <v>2.2</v>
+      </c>
+      <c r="AC249">
+        <v>1.01</v>
+      </c>
+      <c r="AD249">
+        <v>13</v>
+      </c>
+      <c r="AE249">
+        <v>1.18</v>
+      </c>
+      <c r="AF249">
+        <v>4.75</v>
+      </c>
+      <c r="AG249">
+        <v>1.57</v>
+      </c>
+      <c r="AH249">
+        <v>2.35</v>
+      </c>
+      <c r="AI249">
+        <v>1.5</v>
+      </c>
+      <c r="AJ249">
+        <v>2.5</v>
+      </c>
+      <c r="AK249">
+        <v>1.72</v>
+      </c>
+      <c r="AL249">
+        <v>1.22</v>
+      </c>
+      <c r="AM249">
+        <v>1.38</v>
+      </c>
+      <c r="AN249">
+        <v>0.83</v>
+      </c>
+      <c r="AO249">
+        <v>1.9</v>
+      </c>
+      <c r="AP249">
+        <v>1</v>
+      </c>
+      <c r="AQ249">
+        <v>1.73</v>
+      </c>
+      <c r="AR249">
+        <v>1.74</v>
+      </c>
+      <c r="AS249">
+        <v>1.61</v>
+      </c>
+      <c r="AT249">
+        <v>3.35</v>
+      </c>
+      <c r="AU249">
+        <v>6</v>
+      </c>
+      <c r="AV249">
+        <v>5</v>
+      </c>
+      <c r="AW249">
+        <v>15</v>
+      </c>
+      <c r="AX249">
+        <v>5</v>
+      </c>
+      <c r="AY249">
+        <v>21</v>
+      </c>
+      <c r="AZ249">
+        <v>10</v>
+      </c>
+      <c r="BA249">
+        <v>3</v>
+      </c>
+      <c r="BB249">
+        <v>5</v>
+      </c>
+      <c r="BC249">
+        <v>8</v>
+      </c>
+      <c r="BD249">
+        <v>2.17</v>
+      </c>
+      <c r="BE249">
+        <v>6.75</v>
+      </c>
+      <c r="BF249">
+        <v>1.81</v>
+      </c>
+      <c r="BG249">
+        <v>1.19</v>
+      </c>
+      <c r="BH249">
+        <v>4.1</v>
+      </c>
+      <c r="BI249">
+        <v>1.33</v>
+      </c>
+      <c r="BJ249">
+        <v>2.95</v>
+      </c>
+      <c r="BK249">
+        <v>1.55</v>
+      </c>
+      <c r="BL249">
+        <v>2.28</v>
+      </c>
+      <c r="BM249">
+        <v>1.88</v>
+      </c>
+      <c r="BN249">
+        <v>1.81</v>
+      </c>
+      <c r="BO249">
+        <v>2.3</v>
+      </c>
+      <c r="BP249">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="387">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -805,6 +805,12 @@
     <t>['36', '59']</t>
   </si>
   <si>
+    <t>['9', '71']</t>
+  </si>
+  <si>
+    <t>['41', '45+2']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1530,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1992,7 +1998,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2198,7 +2204,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2404,7 +2410,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2482,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ5">
         <v>2.15</v>
@@ -2610,7 +2616,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2816,7 +2822,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2897,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3022,7 +3028,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3100,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -3228,7 +3234,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3515,7 +3521,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ10">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3640,7 +3646,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3721,7 +3727,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ11">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4052,7 +4058,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4133,7 +4139,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ13">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4339,7 +4345,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4670,7 +4676,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4954,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ17">
         <v>1.15</v>
@@ -5160,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ18">
         <v>1.33</v>
@@ -5366,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ19">
         <v>1.42</v>
@@ -5494,7 +5500,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6396,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ24">
         <v>0.62</v>
@@ -6524,7 +6530,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6730,7 +6736,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6808,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26">
         <v>1.58</v>
@@ -6936,7 +6942,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7017,7 +7023,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7348,7 +7354,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7429,7 +7435,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7760,7 +7766,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7841,7 +7847,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ31">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -8047,7 +8053,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8378,7 +8384,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8456,7 +8462,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8584,7 +8590,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9074,7 +9080,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ37">
         <v>2.15</v>
@@ -9202,7 +9208,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9280,7 +9286,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ38">
         <v>1.31</v>
@@ -9408,7 +9414,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9695,7 +9701,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ40">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -9820,7 +9826,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10107,7 +10113,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ42">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -10516,10 +10522,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10644,7 +10650,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10850,7 +10856,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11056,7 +11062,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11262,7 +11268,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11340,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48">
         <v>1.58</v>
@@ -11674,7 +11680,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11880,7 +11886,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11961,7 +11967,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ51">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -12086,7 +12092,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12167,7 +12173,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12370,7 +12376,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12576,10 +12582,10 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ54">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -12910,7 +12916,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13197,7 +13203,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13322,7 +13328,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13528,7 +13534,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13940,7 +13946,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14146,7 +14152,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14352,7 +14358,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14636,7 +14642,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ64">
         <v>1.73</v>
@@ -14842,10 +14848,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ65">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -14970,7 +14976,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15048,7 +15054,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66">
         <v>1.31</v>
@@ -15382,7 +15388,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15463,7 +15469,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15588,7 +15594,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15669,7 +15675,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ69">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15794,7 +15800,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16000,7 +16006,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16206,7 +16212,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16412,7 +16418,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16490,10 +16496,10 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ73">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16618,7 +16624,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16824,7 +16830,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16902,7 +16908,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ75">
         <v>0.42</v>
@@ -17111,7 +17117,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ76">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17442,7 +17448,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17648,7 +17654,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17726,7 +17732,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ79">
         <v>1.73</v>
@@ -18060,7 +18066,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18472,7 +18478,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18678,7 +18684,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19171,7 +19177,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ86">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19296,7 +19302,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19377,7 +19383,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ87">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -19786,7 +19792,7 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19914,7 +19920,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -19992,7 +19998,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -20201,7 +20207,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20326,7 +20332,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20610,7 +20616,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20738,7 +20744,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20944,7 +20950,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21150,7 +21156,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21231,7 +21237,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ96">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21356,7 +21362,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21434,7 +21440,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ97">
         <v>1.58</v>
@@ -21768,7 +21774,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22052,7 +22058,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -22180,7 +22186,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22386,7 +22392,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22670,10 +22676,10 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ103">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22798,7 +22804,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23210,7 +23216,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23291,7 +23297,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23494,10 +23500,10 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ107">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -23703,7 +23709,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -24034,7 +24040,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24112,7 +24118,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24240,7 +24246,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24446,7 +24452,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24524,7 +24530,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112">
         <v>1</v>
@@ -24730,7 +24736,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ113">
         <v>0.42</v>
@@ -24939,7 +24945,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ114">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -25064,7 +25070,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25145,7 +25151,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25270,7 +25276,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25476,7 +25482,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25682,7 +25688,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25888,7 +25894,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26094,7 +26100,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26175,7 +26181,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ120">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26300,7 +26306,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26378,7 +26384,7 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121">
         <v>1.42</v>
@@ -26506,7 +26512,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26712,7 +26718,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26918,7 +26924,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27124,7 +27130,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27411,7 +27417,7 @@
         <v>1</v>
       </c>
       <c r="AQ126">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -27536,7 +27542,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27614,10 +27620,10 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ127">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27742,7 +27748,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28154,7 +28160,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28360,7 +28366,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28644,7 +28650,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ132">
         <v>1</v>
@@ -28772,7 +28778,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29262,7 +29268,7 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29390,7 +29396,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29471,7 +29477,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -29677,7 +29683,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ137">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -29880,7 +29886,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -30295,7 +30301,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -30498,7 +30504,7 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ141">
         <v>1.42</v>
@@ -30832,7 +30838,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -31038,7 +31044,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31116,7 +31122,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ144">
         <v>1.69</v>
@@ -31244,7 +31250,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31450,7 +31456,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31656,7 +31662,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31862,7 +31868,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31943,7 +31949,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32149,7 +32155,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ149">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32274,7 +32280,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32355,7 +32361,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32480,7 +32486,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32558,7 +32564,7 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ151">
         <v>1.31</v>
@@ -32767,7 +32773,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ152">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -32892,7 +32898,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33098,7 +33104,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33304,7 +33310,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33382,10 +33388,10 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -33797,7 +33803,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ157">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34334,7 +34340,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34412,7 +34418,7 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160">
         <v>1.42</v>
@@ -34746,7 +34752,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34824,7 +34830,7 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ162">
         <v>1.73</v>
@@ -35033,7 +35039,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ163">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35364,7 +35370,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35570,7 +35576,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35776,7 +35782,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36188,7 +36194,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36394,7 +36400,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36472,7 +36478,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ170">
         <v>1.69</v>
@@ -36600,7 +36606,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36887,7 +36893,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ172">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -37012,7 +37018,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37090,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37218,7 +37224,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -37296,10 +37302,10 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ174">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -37836,7 +37842,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37914,7 +37920,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ177">
         <v>1.33</v>
@@ -38042,7 +38048,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38454,7 +38460,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38535,7 +38541,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ180">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -38660,7 +38666,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38741,7 +38747,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ181">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -39278,7 +39284,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39484,7 +39490,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39690,7 +39696,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40180,7 +40186,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ188">
         <v>0.62</v>
@@ -40308,7 +40314,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40389,7 +40395,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ189">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40592,7 +40598,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ190">
         <v>1</v>
@@ -40926,7 +40932,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41132,7 +41138,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41338,7 +41344,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41416,7 +41422,7 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ194">
         <v>1.15</v>
@@ -41544,7 +41550,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41622,10 +41628,10 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ195">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -41750,7 +41756,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42368,7 +42374,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42446,10 +42452,10 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ199">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42652,10 +42658,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ200">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42780,7 +42786,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42861,7 +42867,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ201">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -43398,7 +43404,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43810,7 +43816,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44016,7 +44022,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44097,7 +44103,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ207">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44222,7 +44228,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44300,7 +44306,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ208">
         <v>1.15</v>
@@ -44428,7 +44434,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44506,7 +44512,7 @@
         <v>1.6</v>
       </c>
       <c r="AP209">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ209">
         <v>1.42</v>
@@ -44634,7 +44640,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44715,7 +44721,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ210">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR210">
         <v>1.37</v>
@@ -44921,7 +44927,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ211">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR211">
         <v>1.58</v>
@@ -45330,7 +45336,7 @@
         <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ213">
         <v>1.31</v>
@@ -45536,7 +45542,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ214">
         <v>1.42</v>
@@ -45664,7 +45670,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45745,7 +45751,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ215">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -46076,7 +46082,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46566,10 +46572,10 @@
         <v>0.5</v>
       </c>
       <c r="AP219">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ219">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR219">
         <v>1.74</v>
@@ -46900,7 +46906,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47518,7 +47524,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47805,7 +47811,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ225">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR225">
         <v>1.68</v>
@@ -48136,7 +48142,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48342,7 +48348,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48626,7 +48632,7 @@
         <v>0.5</v>
       </c>
       <c r="AP229">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ229">
         <v>0.42</v>
@@ -48832,10 +48838,10 @@
         <v>1.67</v>
       </c>
       <c r="AP230">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ230">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR230">
         <v>1.81</v>
@@ -49038,7 +49044,7 @@
         <v>1.73</v>
       </c>
       <c r="AP231">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ231">
         <v>1.58</v>
@@ -49244,7 +49250,7 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ232">
         <v>1</v>
@@ -49372,7 +49378,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49656,10 +49662,10 @@
         <v>1</v>
       </c>
       <c r="AP234">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ234">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR234">
         <v>1.75</v>
@@ -49784,7 +49790,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49990,7 +49996,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50068,10 +50074,10 @@
         <v>1.33</v>
       </c>
       <c r="AP236">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ236">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR236">
         <v>1.7</v>
@@ -50402,7 +50408,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50814,7 +50820,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51307,7 +51313,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ242">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AR242">
         <v>1.34</v>
@@ -51432,7 +51438,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51638,7 +51644,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52256,7 +52262,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52462,7 +52468,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52825,6 +52831,1036 @@
       </c>
       <c r="BP249">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7465677</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F250">
+        <v>26</v>
+      </c>
+      <c r="G250" t="s">
+        <v>86</v>
+      </c>
+      <c r="H250" t="s">
+        <v>82</v>
+      </c>
+      <c r="I250">
+        <v>1</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>3</v>
+      </c>
+      <c r="O250" t="s">
+        <v>263</v>
+      </c>
+      <c r="P250" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q250">
+        <v>2.75</v>
+      </c>
+      <c r="R250">
+        <v>2.3</v>
+      </c>
+      <c r="S250">
+        <v>3.1</v>
+      </c>
+      <c r="T250">
+        <v>1.25</v>
+      </c>
+      <c r="U250">
+        <v>3.55</v>
+      </c>
+      <c r="V250">
+        <v>2.1</v>
+      </c>
+      <c r="W250">
+        <v>1.65</v>
+      </c>
+      <c r="X250">
+        <v>4.8</v>
+      </c>
+      <c r="Y250">
+        <v>1.16</v>
+      </c>
+      <c r="Z250">
+        <v>2.35</v>
+      </c>
+      <c r="AA250">
+        <v>3.7</v>
+      </c>
+      <c r="AB250">
+        <v>2.7</v>
+      </c>
+      <c r="AC250">
+        <v>1.01</v>
+      </c>
+      <c r="AD250">
+        <v>13</v>
+      </c>
+      <c r="AE250">
+        <v>1.17</v>
+      </c>
+      <c r="AF250">
+        <v>5</v>
+      </c>
+      <c r="AG250">
+        <v>1.5</v>
+      </c>
+      <c r="AH250">
+        <v>2.55</v>
+      </c>
+      <c r="AI250">
+        <v>1.4</v>
+      </c>
+      <c r="AJ250">
+        <v>2.65</v>
+      </c>
+      <c r="AK250">
+        <v>1.45</v>
+      </c>
+      <c r="AL250">
+        <v>1.22</v>
+      </c>
+      <c r="AM250">
+        <v>1.57</v>
+      </c>
+      <c r="AN250">
+        <v>1.83</v>
+      </c>
+      <c r="AO250">
+        <v>1.23</v>
+      </c>
+      <c r="AP250">
+        <v>1.92</v>
+      </c>
+      <c r="AQ250">
+        <v>1.14</v>
+      </c>
+      <c r="AR250">
+        <v>1.74</v>
+      </c>
+      <c r="AS250">
+        <v>1.76</v>
+      </c>
+      <c r="AT250">
+        <v>3.5</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>8</v>
+      </c>
+      <c r="AW250">
+        <v>5</v>
+      </c>
+      <c r="AX250">
+        <v>13</v>
+      </c>
+      <c r="AY250">
+        <v>9</v>
+      </c>
+      <c r="AZ250">
+        <v>21</v>
+      </c>
+      <c r="BA250">
+        <v>0</v>
+      </c>
+      <c r="BB250">
+        <v>8</v>
+      </c>
+      <c r="BC250">
+        <v>8</v>
+      </c>
+      <c r="BD250">
+        <v>2</v>
+      </c>
+      <c r="BE250">
+        <v>6.4</v>
+      </c>
+      <c r="BF250">
+        <v>1.98</v>
+      </c>
+      <c r="BG250">
+        <v>1.27</v>
+      </c>
+      <c r="BH250">
+        <v>3.3</v>
+      </c>
+      <c r="BI250">
+        <v>1.47</v>
+      </c>
+      <c r="BJ250">
+        <v>2.48</v>
+      </c>
+      <c r="BK250">
+        <v>1.76</v>
+      </c>
+      <c r="BL250">
+        <v>1.93</v>
+      </c>
+      <c r="BM250">
+        <v>2.18</v>
+      </c>
+      <c r="BN250">
+        <v>1.58</v>
+      </c>
+      <c r="BO250">
+        <v>2.8</v>
+      </c>
+      <c r="BP250">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7465674</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F251">
+        <v>26</v>
+      </c>
+      <c r="G251" t="s">
+        <v>87</v>
+      </c>
+      <c r="H251" t="s">
+        <v>74</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>2</v>
+      </c>
+      <c r="O251" t="s">
+        <v>127</v>
+      </c>
+      <c r="P251" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q251">
+        <v>1.91</v>
+      </c>
+      <c r="R251">
+        <v>2.5</v>
+      </c>
+      <c r="S251">
+        <v>6</v>
+      </c>
+      <c r="T251">
+        <v>1.29</v>
+      </c>
+      <c r="U251">
+        <v>3.5</v>
+      </c>
+      <c r="V251">
+        <v>2.38</v>
+      </c>
+      <c r="W251">
+        <v>1.53</v>
+      </c>
+      <c r="X251">
+        <v>5.5</v>
+      </c>
+      <c r="Y251">
+        <v>1.14</v>
+      </c>
+      <c r="Z251">
+        <v>1.42</v>
+      </c>
+      <c r="AA251">
+        <v>4.5</v>
+      </c>
+      <c r="AB251">
+        <v>6</v>
+      </c>
+      <c r="AC251">
+        <v>1.02</v>
+      </c>
+      <c r="AD251">
+        <v>17</v>
+      </c>
+      <c r="AE251">
+        <v>1.18</v>
+      </c>
+      <c r="AF251">
+        <v>4.75</v>
+      </c>
+      <c r="AG251">
+        <v>1.6</v>
+      </c>
+      <c r="AH251">
+        <v>2.3</v>
+      </c>
+      <c r="AI251">
+        <v>1.8</v>
+      </c>
+      <c r="AJ251">
+        <v>1.91</v>
+      </c>
+      <c r="AK251">
+        <v>1.1</v>
+      </c>
+      <c r="AL251">
+        <v>1.18</v>
+      </c>
+      <c r="AM251">
+        <v>2.85</v>
+      </c>
+      <c r="AN251">
+        <v>1.33</v>
+      </c>
+      <c r="AO251">
+        <v>0.42</v>
+      </c>
+      <c r="AP251">
+        <v>1.31</v>
+      </c>
+      <c r="AQ251">
+        <v>0.46</v>
+      </c>
+      <c r="AR251">
+        <v>1.71</v>
+      </c>
+      <c r="AS251">
+        <v>1.1</v>
+      </c>
+      <c r="AT251">
+        <v>2.81</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>2</v>
+      </c>
+      <c r="AW251">
+        <v>16</v>
+      </c>
+      <c r="AX251">
+        <v>0</v>
+      </c>
+      <c r="AY251">
+        <v>23</v>
+      </c>
+      <c r="AZ251">
+        <v>2</v>
+      </c>
+      <c r="BA251">
+        <v>5</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>10</v>
+      </c>
+      <c r="BD251">
+        <v>1.3</v>
+      </c>
+      <c r="BE251">
+        <v>8</v>
+      </c>
+      <c r="BF251">
+        <v>3.9</v>
+      </c>
+      <c r="BG251">
+        <v>1.25</v>
+      </c>
+      <c r="BH251">
+        <v>3.4</v>
+      </c>
+      <c r="BI251">
+        <v>1.44</v>
+      </c>
+      <c r="BJ251">
+        <v>2.55</v>
+      </c>
+      <c r="BK251">
+        <v>1.74</v>
+      </c>
+      <c r="BL251">
+        <v>1.98</v>
+      </c>
+      <c r="BM251">
+        <v>2.12</v>
+      </c>
+      <c r="BN251">
+        <v>1.63</v>
+      </c>
+      <c r="BO251">
+        <v>2.65</v>
+      </c>
+      <c r="BP251">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7465673</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F252">
+        <v>26</v>
+      </c>
+      <c r="G252" t="s">
+        <v>73</v>
+      </c>
+      <c r="H252" t="s">
+        <v>70</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>2</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>2</v>
+      </c>
+      <c r="O252" t="s">
+        <v>264</v>
+      </c>
+      <c r="P252" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q252">
+        <v>2.8</v>
+      </c>
+      <c r="R252">
+        <v>2.3</v>
+      </c>
+      <c r="S252">
+        <v>3.5</v>
+      </c>
+      <c r="T252">
+        <v>1.28</v>
+      </c>
+      <c r="U252">
+        <v>3.4</v>
+      </c>
+      <c r="V252">
+        <v>2.34</v>
+      </c>
+      <c r="W252">
+        <v>1.54</v>
+      </c>
+      <c r="X252">
+        <v>5.4</v>
+      </c>
+      <c r="Y252">
+        <v>1.12</v>
+      </c>
+      <c r="Z252">
+        <v>2.25</v>
+      </c>
+      <c r="AA252">
+        <v>3.6</v>
+      </c>
+      <c r="AB252">
+        <v>2.95</v>
+      </c>
+      <c r="AC252">
+        <v>1.02</v>
+      </c>
+      <c r="AD252">
+        <v>17</v>
+      </c>
+      <c r="AE252">
+        <v>1.18</v>
+      </c>
+      <c r="AF252">
+        <v>4.75</v>
+      </c>
+      <c r="AG252">
+        <v>1.6</v>
+      </c>
+      <c r="AH252">
+        <v>2.3</v>
+      </c>
+      <c r="AI252">
+        <v>1.52</v>
+      </c>
+      <c r="AJ252">
+        <v>2.5</v>
+      </c>
+      <c r="AK252">
+        <v>1.4</v>
+      </c>
+      <c r="AL252">
+        <v>1.22</v>
+      </c>
+      <c r="AM252">
+        <v>1.66</v>
+      </c>
+      <c r="AN252">
+        <v>1.83</v>
+      </c>
+      <c r="AO252">
+        <v>1.54</v>
+      </c>
+      <c r="AP252">
+        <v>1.92</v>
+      </c>
+      <c r="AQ252">
+        <v>1.43</v>
+      </c>
+      <c r="AR252">
+        <v>1.74</v>
+      </c>
+      <c r="AS252">
+        <v>1.24</v>
+      </c>
+      <c r="AT252">
+        <v>2.98</v>
+      </c>
+      <c r="AU252">
+        <v>7</v>
+      </c>
+      <c r="AV252">
+        <v>3</v>
+      </c>
+      <c r="AW252">
+        <v>2</v>
+      </c>
+      <c r="AX252">
+        <v>9</v>
+      </c>
+      <c r="AY252">
+        <v>9</v>
+      </c>
+      <c r="AZ252">
+        <v>12</v>
+      </c>
+      <c r="BA252">
+        <v>2</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>6</v>
+      </c>
+      <c r="BD252">
+        <v>1.81</v>
+      </c>
+      <c r="BE252">
+        <v>6.5</v>
+      </c>
+      <c r="BF252">
+        <v>2.18</v>
+      </c>
+      <c r="BG252">
+        <v>1.3</v>
+      </c>
+      <c r="BH252">
+        <v>3.15</v>
+      </c>
+      <c r="BI252">
+        <v>1.5</v>
+      </c>
+      <c r="BJ252">
+        <v>2.33</v>
+      </c>
+      <c r="BK252">
+        <v>1.84</v>
+      </c>
+      <c r="BL252">
+        <v>1.84</v>
+      </c>
+      <c r="BM252">
+        <v>2.32</v>
+      </c>
+      <c r="BN252">
+        <v>1.52</v>
+      </c>
+      <c r="BO252">
+        <v>2.95</v>
+      </c>
+      <c r="BP252">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7465671</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F253">
+        <v>26</v>
+      </c>
+      <c r="G253" t="s">
+        <v>85</v>
+      </c>
+      <c r="H253" t="s">
+        <v>81</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>1</v>
+      </c>
+      <c r="O253" t="s">
+        <v>93</v>
+      </c>
+      <c r="P253" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q253">
+        <v>3.1</v>
+      </c>
+      <c r="R253">
+        <v>2.15</v>
+      </c>
+      <c r="S253">
+        <v>3</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3</v>
+      </c>
+      <c r="V253">
+        <v>2.55</v>
+      </c>
+      <c r="W253">
+        <v>1.45</v>
+      </c>
+      <c r="X253">
+        <v>6.95</v>
+      </c>
+      <c r="Y253">
+        <v>1.08</v>
+      </c>
+      <c r="Z253">
+        <v>2.6</v>
+      </c>
+      <c r="AA253">
+        <v>3.45</v>
+      </c>
+      <c r="AB253">
+        <v>2.5</v>
+      </c>
+      <c r="AC253">
+        <v>1.05</v>
+      </c>
+      <c r="AD253">
+        <v>9.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.25</v>
+      </c>
+      <c r="AF253">
+        <v>3.85</v>
+      </c>
+      <c r="AG253">
+        <v>1.77</v>
+      </c>
+      <c r="AH253">
+        <v>2</v>
+      </c>
+      <c r="AI253">
+        <v>1.6</v>
+      </c>
+      <c r="AJ253">
+        <v>2.15</v>
+      </c>
+      <c r="AK253">
+        <v>1.5</v>
+      </c>
+      <c r="AL253">
+        <v>1.25</v>
+      </c>
+      <c r="AM253">
+        <v>1.48</v>
+      </c>
+      <c r="AN253">
+        <v>1.92</v>
+      </c>
+      <c r="AO253">
+        <v>0.92</v>
+      </c>
+      <c r="AP253">
+        <v>1.79</v>
+      </c>
+      <c r="AQ253">
+        <v>1.07</v>
+      </c>
+      <c r="AR253">
+        <v>1.77</v>
+      </c>
+      <c r="AS253">
+        <v>1.52</v>
+      </c>
+      <c r="AT253">
+        <v>3.29</v>
+      </c>
+      <c r="AU253">
+        <v>5</v>
+      </c>
+      <c r="AV253">
+        <v>7</v>
+      </c>
+      <c r="AW253">
+        <v>9</v>
+      </c>
+      <c r="AX253">
+        <v>8</v>
+      </c>
+      <c r="AY253">
+        <v>14</v>
+      </c>
+      <c r="AZ253">
+        <v>15</v>
+      </c>
+      <c r="BA253">
+        <v>9</v>
+      </c>
+      <c r="BB253">
+        <v>2</v>
+      </c>
+      <c r="BC253">
+        <v>11</v>
+      </c>
+      <c r="BD253">
+        <v>2.08</v>
+      </c>
+      <c r="BE253">
+        <v>6.75</v>
+      </c>
+      <c r="BF253">
+        <v>1.91</v>
+      </c>
+      <c r="BG253">
+        <v>1.26</v>
+      </c>
+      <c r="BH253">
+        <v>3.4</v>
+      </c>
+      <c r="BI253">
+        <v>1.46</v>
+      </c>
+      <c r="BJ253">
+        <v>2.48</v>
+      </c>
+      <c r="BK253">
+        <v>1.74</v>
+      </c>
+      <c r="BL253">
+        <v>1.97</v>
+      </c>
+      <c r="BM253">
+        <v>2.17</v>
+      </c>
+      <c r="BN253">
+        <v>1.6</v>
+      </c>
+      <c r="BO253">
+        <v>2.75</v>
+      </c>
+      <c r="BP253">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7465669</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45702.66666666666</v>
+      </c>
+      <c r="F254">
+        <v>26</v>
+      </c>
+      <c r="G254" t="s">
+        <v>76</v>
+      </c>
+      <c r="H254" t="s">
+        <v>89</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+      <c r="L254">
+        <v>1</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>1</v>
+      </c>
+      <c r="O254" t="s">
+        <v>145</v>
+      </c>
+      <c r="P254" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q254">
+        <v>1.83</v>
+      </c>
+      <c r="R254">
+        <v>2.6</v>
+      </c>
+      <c r="S254">
+        <v>6.5</v>
+      </c>
+      <c r="T254">
+        <v>1.29</v>
+      </c>
+      <c r="U254">
+        <v>3.5</v>
+      </c>
+      <c r="V254">
+        <v>2.25</v>
+      </c>
+      <c r="W254">
+        <v>1.57</v>
+      </c>
+      <c r="X254">
+        <v>5.5</v>
+      </c>
+      <c r="Y254">
+        <v>1.14</v>
+      </c>
+      <c r="Z254">
+        <v>1.36</v>
+      </c>
+      <c r="AA254">
+        <v>4.5</v>
+      </c>
+      <c r="AB254">
+        <v>7</v>
+      </c>
+      <c r="AC254">
+        <v>1.01</v>
+      </c>
+      <c r="AD254">
+        <v>17</v>
+      </c>
+      <c r="AE254">
+        <v>1.14</v>
+      </c>
+      <c r="AF254">
+        <v>5.5</v>
+      </c>
+      <c r="AG254">
+        <v>1.53</v>
+      </c>
+      <c r="AH254">
+        <v>2.4</v>
+      </c>
+      <c r="AI254">
+        <v>1.8</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>1.12</v>
+      </c>
+      <c r="AL254">
+        <v>1.17</v>
+      </c>
+      <c r="AM254">
+        <v>2.75</v>
+      </c>
+      <c r="AN254">
+        <v>2.08</v>
+      </c>
+      <c r="AO254">
+        <v>0.75</v>
+      </c>
+      <c r="AP254">
+        <v>2.14</v>
+      </c>
+      <c r="AQ254">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR254">
+        <v>1.85</v>
+      </c>
+      <c r="AS254">
+        <v>1.59</v>
+      </c>
+      <c r="AT254">
+        <v>3.44</v>
+      </c>
+      <c r="AU254">
+        <v>8</v>
+      </c>
+      <c r="AV254">
+        <v>4</v>
+      </c>
+      <c r="AW254">
+        <v>9</v>
+      </c>
+      <c r="AX254">
+        <v>3</v>
+      </c>
+      <c r="AY254">
+        <v>17</v>
+      </c>
+      <c r="AZ254">
+        <v>7</v>
+      </c>
+      <c r="BA254">
+        <v>6</v>
+      </c>
+      <c r="BB254">
+        <v>5</v>
+      </c>
+      <c r="BC254">
+        <v>11</v>
+      </c>
+      <c r="BD254">
+        <v>1.38</v>
+      </c>
+      <c r="BE254">
+        <v>7</v>
+      </c>
+      <c r="BF254">
+        <v>3.4</v>
+      </c>
+      <c r="BG254">
+        <v>1.27</v>
+      </c>
+      <c r="BH254">
+        <v>3.4</v>
+      </c>
+      <c r="BI254">
+        <v>1.46</v>
+      </c>
+      <c r="BJ254">
+        <v>2.5</v>
+      </c>
+      <c r="BK254">
+        <v>1.74</v>
+      </c>
+      <c r="BL254">
+        <v>1.97</v>
+      </c>
+      <c r="BM254">
+        <v>2.17</v>
+      </c>
+      <c r="BN254">
+        <v>1.6</v>
+      </c>
+      <c r="BO254">
+        <v>2.7</v>
+      </c>
+      <c r="BP254">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="388">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -811,6 +811,9 @@
     <t>['41', '45+2']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -878,9 +881,6 @@
   </si>
   <si>
     <t>['2', '6', '78']</t>
-  </si>
-  <si>
-    <t>['56']</t>
   </si>
   <si>
     <t>['42', '62']</t>
@@ -1175,6 +1175,9 @@
   </si>
   <si>
     <t>['13', '18', '76', '90+4']</t>
+  </si>
+  <si>
+    <t>['8', '13']</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP254"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1998,7 +2001,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2076,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3">
         <v>1.69</v>
@@ -2204,7 +2207,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2410,7 +2413,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2616,7 +2619,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2822,7 +2825,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3028,7 +3031,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3234,7 +3237,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3315,7 +3318,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ9">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3646,7 +3649,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4058,7 +4061,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4676,7 +4679,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5500,7 +5503,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6196,7 +6199,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23">
         <v>1.42</v>
@@ -6530,7 +6533,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6736,7 +6739,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6817,7 +6820,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR26">
         <v>1.18</v>
@@ -6942,7 +6945,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7354,7 +7357,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7766,7 +7769,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8384,7 +8387,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8590,7 +8593,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9208,7 +9211,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9414,7 +9417,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9826,7 +9829,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10650,7 +10653,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10856,7 +10859,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11062,7 +11065,7 @@
         <v>93</v>
       </c>
       <c r="P47" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>2.88</v>
@@ -11349,7 +11352,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -12170,7 +12173,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ52">
         <v>1.14</v>
@@ -12994,7 +12997,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -14439,7 +14442,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -18559,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="AQ83">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -19586,7 +19589,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ88">
         <v>0.62</v>
@@ -21443,7 +21446,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ97">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -23706,7 +23709,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
         <v>0.46</v>
@@ -26178,7 +26181,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ120">
         <v>1.07</v>
@@ -27542,7 +27545,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27829,7 +27832,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ128">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -29474,7 +29477,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ136">
         <v>0.6899999999999999</v>
@@ -30838,7 +30841,7 @@
         <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="Q143">
         <v>2.8</v>
@@ -31331,7 +31334,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ145">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR145">
         <v>1.6</v>
@@ -33594,7 +33597,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -34752,7 +34755,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35451,7 +35454,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR165">
         <v>1.91</v>
@@ -35782,7 +35785,7 @@
         <v>204</v>
       </c>
       <c r="P167" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -38126,7 +38129,7 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ178">
         <v>1.31</v>
@@ -39983,7 +39986,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ187">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR187">
         <v>1.79</v>
@@ -40314,7 +40317,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41834,7 +41837,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ196">
         <v>1.42</v>
@@ -42786,7 +42789,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43485,7 +43488,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ204">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR204">
         <v>1.4</v>
@@ -45748,7 +45751,7 @@
         <v>1.55</v>
       </c>
       <c r="AP215">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ215">
         <v>1.43</v>
@@ -49047,7 +49050,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ231">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AR231">
         <v>1.77</v>
@@ -49456,7 +49459,7 @@
         <v>1.08</v>
       </c>
       <c r="AP233">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ233">
         <v>1</v>
@@ -52880,7 +52883,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53861,6 +53864,212 @@
       </c>
       <c r="BP254">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7465675</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45703.52083333334</v>
+      </c>
+      <c r="F255">
+        <v>26</v>
+      </c>
+      <c r="G255" t="s">
+        <v>71</v>
+      </c>
+      <c r="H255" t="s">
+        <v>88</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>2</v>
+      </c>
+      <c r="K255">
+        <v>2</v>
+      </c>
+      <c r="L255">
+        <v>1</v>
+      </c>
+      <c r="M255">
+        <v>2</v>
+      </c>
+      <c r="N255">
+        <v>3</v>
+      </c>
+      <c r="O255" t="s">
+        <v>265</v>
+      </c>
+      <c r="P255" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q255">
+        <v>3.25</v>
+      </c>
+      <c r="R255">
+        <v>2.4</v>
+      </c>
+      <c r="S255">
+        <v>2.88</v>
+      </c>
+      <c r="T255">
+        <v>1.29</v>
+      </c>
+      <c r="U255">
+        <v>3.5</v>
+      </c>
+      <c r="V255">
+        <v>2.25</v>
+      </c>
+      <c r="W255">
+        <v>1.57</v>
+      </c>
+      <c r="X255">
+        <v>5.5</v>
+      </c>
+      <c r="Y255">
+        <v>1.14</v>
+      </c>
+      <c r="Z255">
+        <v>2.75</v>
+      </c>
+      <c r="AA255">
+        <v>3.75</v>
+      </c>
+      <c r="AB255">
+        <v>2.25</v>
+      </c>
+      <c r="AC255">
+        <v>1.03</v>
+      </c>
+      <c r="AD255">
+        <v>11</v>
+      </c>
+      <c r="AE255">
+        <v>1.16</v>
+      </c>
+      <c r="AF255">
+        <v>5</v>
+      </c>
+      <c r="AG255">
+        <v>1.53</v>
+      </c>
+      <c r="AH255">
+        <v>2.4</v>
+      </c>
+      <c r="AI255">
+        <v>1.5</v>
+      </c>
+      <c r="AJ255">
+        <v>2.5</v>
+      </c>
+      <c r="AK255">
+        <v>1.55</v>
+      </c>
+      <c r="AL255">
+        <v>1.2</v>
+      </c>
+      <c r="AM255">
+        <v>1.53</v>
+      </c>
+      <c r="AN255">
+        <v>1.23</v>
+      </c>
+      <c r="AO255">
+        <v>1.58</v>
+      </c>
+      <c r="AP255">
+        <v>1.14</v>
+      </c>
+      <c r="AQ255">
+        <v>1.69</v>
+      </c>
+      <c r="AR255">
+        <v>1.7</v>
+      </c>
+      <c r="AS255">
+        <v>1.46</v>
+      </c>
+      <c r="AT255">
+        <v>3.16</v>
+      </c>
+      <c r="AU255">
+        <v>6</v>
+      </c>
+      <c r="AV255">
+        <v>5</v>
+      </c>
+      <c r="AW255">
+        <v>9</v>
+      </c>
+      <c r="AX255">
+        <v>3</v>
+      </c>
+      <c r="AY255">
+        <v>15</v>
+      </c>
+      <c r="AZ255">
+        <v>8</v>
+      </c>
+      <c r="BA255">
+        <v>9</v>
+      </c>
+      <c r="BB255">
+        <v>0</v>
+      </c>
+      <c r="BC255">
+        <v>9</v>
+      </c>
+      <c r="BD255">
+        <v>1.98</v>
+      </c>
+      <c r="BE255">
+        <v>6.4</v>
+      </c>
+      <c r="BF255">
+        <v>1.98</v>
+      </c>
+      <c r="BG255">
+        <v>1.34</v>
+      </c>
+      <c r="BH255">
+        <v>2.9</v>
+      </c>
+      <c r="BI255">
+        <v>1.58</v>
+      </c>
+      <c r="BJ255">
+        <v>2.2</v>
+      </c>
+      <c r="BK255">
+        <v>1.94</v>
+      </c>
+      <c r="BL255">
+        <v>1.76</v>
+      </c>
+      <c r="BM255">
+        <v>2.43</v>
+      </c>
+      <c r="BN255">
+        <v>1.48</v>
+      </c>
+      <c r="BO255">
+        <v>3.15</v>
+      </c>
+      <c r="BP255">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="389">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -814,6 +814,9 @@
     <t>['56']</t>
   </si>
   <si>
+    <t>['45', '90+3']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1084,9 +1087,6 @@
     <t>['31', '88']</t>
   </si>
   <si>
-    <t>['45', '90+3']</t>
-  </si>
-  <si>
     <t>['73']</t>
   </si>
   <si>
@@ -1178,6 +1178,9 @@
   </si>
   <si>
     <t>['8', '13']</t>
+  </si>
+  <si>
+    <t>['59']</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2001,7 +2004,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2207,7 +2210,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2413,7 +2416,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2619,7 +2622,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2825,7 +2828,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2903,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
         <v>1.07</v>
@@ -3031,7 +3034,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3237,7 +3240,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3649,7 +3652,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4061,7 +4064,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4551,10 +4554,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4679,7 +4682,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5378,7 +5381,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ19">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5503,7 +5506,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6202,7 +6205,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ23">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6533,7 +6536,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6739,7 +6742,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6945,7 +6948,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7229,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28">
         <v>1.31</v>
@@ -7357,7 +7360,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7769,7 +7772,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8053,7 +8056,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ32">
         <v>1.43</v>
@@ -8387,7 +8390,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8593,7 +8596,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9211,7 +9214,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9417,7 +9420,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9829,7 +9832,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9910,7 +9913,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
         <v>1.77</v>
@@ -10653,7 +10656,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10859,7 +10862,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11271,7 +11274,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11683,7 +11686,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11764,7 +11767,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ50">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -11889,7 +11892,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -11967,7 +11970,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ51">
         <v>1.07</v>
@@ -12095,7 +12098,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12791,7 +12794,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12919,7 +12922,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13331,7 +13334,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13537,7 +13540,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13949,7 +13952,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14155,7 +14158,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14361,7 +14364,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14979,7 +14982,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15391,7 +15394,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15469,7 +15472,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ68">
         <v>0.6899999999999999</v>
@@ -15597,7 +15600,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15803,7 +15806,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15884,7 +15887,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -16009,7 +16012,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16215,7 +16218,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16421,7 +16424,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16627,7 +16630,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16705,7 +16708,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ74">
         <v>1.15</v>
@@ -16833,7 +16836,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17451,7 +17454,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17657,7 +17660,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18069,7 +18072,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18150,7 +18153,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ81">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18481,7 +18484,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18559,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ83">
         <v>1.69</v>
@@ -18687,7 +18690,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19305,7 +19308,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19923,7 +19926,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20004,7 +20007,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR90">
         <v>1.95</v>
@@ -20335,7 +20338,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20416,7 +20419,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR92">
         <v>1.75</v>
@@ -20747,7 +20750,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20828,7 +20831,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ94">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -20953,7 +20956,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21159,7 +21162,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21365,7 +21368,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21777,7 +21780,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22189,7 +22192,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22267,7 +22270,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ101">
         <v>0.62</v>
@@ -22395,7 +22398,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22807,7 +22810,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23219,7 +23222,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24043,7 +24046,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24249,7 +24252,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24455,7 +24458,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24536,7 +24539,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR112">
         <v>1.74</v>
@@ -25073,7 +25076,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25279,7 +25282,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25485,7 +25488,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25563,7 +25566,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25691,7 +25694,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25897,7 +25900,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -25975,7 +25978,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ119">
         <v>2.15</v>
@@ -26103,7 +26106,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26309,7 +26312,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26390,7 +26393,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ121">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26515,7 +26518,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26721,7 +26724,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26927,7 +26930,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27133,7 +27136,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27417,7 +27420,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ126">
         <v>0.46</v>
@@ -27545,7 +27548,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27751,7 +27754,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28163,7 +28166,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28369,7 +28372,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28656,7 +28659,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ132">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR132">
         <v>1.8</v>
@@ -28781,7 +28784,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29399,7 +29402,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29683,7 +29686,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ137">
         <v>1.43</v>
@@ -30510,7 +30513,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -31047,7 +31050,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31253,7 +31256,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31459,7 +31462,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31665,7 +31668,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31743,7 +31746,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ147">
         <v>2.15</v>
@@ -31871,7 +31874,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32283,7 +32286,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32489,7 +32492,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32901,7 +32904,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33107,7 +33110,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33313,7 +33316,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33600,7 +33603,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR156">
         <v>1.76</v>
@@ -34343,7 +34346,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34755,7 +34758,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35039,7 +35042,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ163">
         <v>0.6899999999999999</v>
@@ -35373,7 +35376,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35579,7 +35582,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35863,10 +35866,10 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ167">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -36197,7 +36200,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36403,7 +36406,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36609,7 +36612,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37021,7 +37024,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37227,7 +37230,7 @@
         <v>209</v>
       </c>
       <c r="P174" t="s">
-        <v>356</v>
+        <v>266</v>
       </c>
       <c r="Q174">
         <v>2.55</v>
@@ -38051,7 +38054,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38338,7 +38341,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ179">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR179">
         <v>1.58</v>
@@ -38956,7 +38959,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ182">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39983,7 +39986,7 @@
         <v>1.67</v>
       </c>
       <c r="AP187">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ187">
         <v>1.69</v>
@@ -40317,7 +40320,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40807,7 +40810,7 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ191">
         <v>0.42</v>
@@ -41016,7 +41019,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ192">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -42252,7 +42255,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ198">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR198">
         <v>1.99</v>
@@ -42377,7 +42380,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42789,7 +42792,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43073,7 +43076,7 @@
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ202">
         <v>1.69</v>
@@ -43897,7 +43900,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ206">
         <v>1.33</v>
@@ -44025,7 +44028,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44437,7 +44440,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44518,7 +44521,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ209">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR209">
         <v>1.86</v>
@@ -46166,7 +46169,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR217">
         <v>1.39</v>
@@ -47605,7 +47608,7 @@
         <v>1.45</v>
       </c>
       <c r="AP224">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ224">
         <v>1.69</v>
@@ -48017,7 +48020,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ226">
         <v>1.33</v>
@@ -49256,7 +49259,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ232">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR232">
         <v>1.8</v>
@@ -49871,7 +49874,7 @@
         <v>0.82</v>
       </c>
       <c r="AP235">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ235">
         <v>1</v>
@@ -50286,7 +50289,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ237">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR237">
         <v>1.48</v>
@@ -52755,7 +52758,7 @@
         <v>1.9</v>
       </c>
       <c r="AP249">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ249">
         <v>1.73</v>
@@ -52883,7 +52886,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -54070,6 +54073,418 @@
       </c>
       <c r="BP255">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7465676</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45704.34375</v>
+      </c>
+      <c r="F256">
+        <v>26</v>
+      </c>
+      <c r="G256" t="s">
+        <v>75</v>
+      </c>
+      <c r="H256" t="s">
+        <v>77</v>
+      </c>
+      <c r="I256">
+        <v>1</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <v>2</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
+      </c>
+      <c r="N256">
+        <v>2</v>
+      </c>
+      <c r="O256" t="s">
+        <v>266</v>
+      </c>
+      <c r="P256" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q256">
+        <v>3.5</v>
+      </c>
+      <c r="R256">
+        <v>2.4</v>
+      </c>
+      <c r="S256">
+        <v>2.63</v>
+      </c>
+      <c r="T256">
+        <v>1.29</v>
+      </c>
+      <c r="U256">
+        <v>3.5</v>
+      </c>
+      <c r="V256">
+        <v>2.25</v>
+      </c>
+      <c r="W256">
+        <v>1.57</v>
+      </c>
+      <c r="X256">
+        <v>5.5</v>
+      </c>
+      <c r="Y256">
+        <v>1.14</v>
+      </c>
+      <c r="Z256">
+        <v>2.9</v>
+      </c>
+      <c r="AA256">
+        <v>4.1</v>
+      </c>
+      <c r="AB256">
+        <v>2.05</v>
+      </c>
+      <c r="AC256">
+        <v>1.01</v>
+      </c>
+      <c r="AD256">
+        <v>13</v>
+      </c>
+      <c r="AE256">
+        <v>1.16</v>
+      </c>
+      <c r="AF256">
+        <v>5</v>
+      </c>
+      <c r="AG256">
+        <v>1.5</v>
+      </c>
+      <c r="AH256">
+        <v>2.5</v>
+      </c>
+      <c r="AI256">
+        <v>1.5</v>
+      </c>
+      <c r="AJ256">
+        <v>2.5</v>
+      </c>
+      <c r="AK256">
+        <v>1.8</v>
+      </c>
+      <c r="AL256">
+        <v>1.2</v>
+      </c>
+      <c r="AM256">
+        <v>1.35</v>
+      </c>
+      <c r="AN256">
+        <v>1</v>
+      </c>
+      <c r="AO256">
+        <v>1</v>
+      </c>
+      <c r="AP256">
+        <v>1.14</v>
+      </c>
+      <c r="AQ256">
+        <v>0.92</v>
+      </c>
+      <c r="AR256">
+        <v>1.77</v>
+      </c>
+      <c r="AS256">
+        <v>1.79</v>
+      </c>
+      <c r="AT256">
+        <v>3.56</v>
+      </c>
+      <c r="AU256">
+        <v>4</v>
+      </c>
+      <c r="AV256">
+        <v>3</v>
+      </c>
+      <c r="AW256">
+        <v>8</v>
+      </c>
+      <c r="AX256">
+        <v>12</v>
+      </c>
+      <c r="AY256">
+        <v>12</v>
+      </c>
+      <c r="AZ256">
+        <v>15</v>
+      </c>
+      <c r="BA256">
+        <v>3</v>
+      </c>
+      <c r="BB256">
+        <v>4</v>
+      </c>
+      <c r="BC256">
+        <v>7</v>
+      </c>
+      <c r="BD256">
+        <v>2.3</v>
+      </c>
+      <c r="BE256">
+        <v>6.75</v>
+      </c>
+      <c r="BF256">
+        <v>1.74</v>
+      </c>
+      <c r="BG256">
+        <v>1.19</v>
+      </c>
+      <c r="BH256">
+        <v>4.1</v>
+      </c>
+      <c r="BI256">
+        <v>1.34</v>
+      </c>
+      <c r="BJ256">
+        <v>2.9</v>
+      </c>
+      <c r="BK256">
+        <v>1.56</v>
+      </c>
+      <c r="BL256">
+        <v>2.23</v>
+      </c>
+      <c r="BM256">
+        <v>1.89</v>
+      </c>
+      <c r="BN256">
+        <v>1.8</v>
+      </c>
+      <c r="BO256">
+        <v>2.33</v>
+      </c>
+      <c r="BP256">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7465670</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45704.53125</v>
+      </c>
+      <c r="F257">
+        <v>26</v>
+      </c>
+      <c r="G257" t="s">
+        <v>83</v>
+      </c>
+      <c r="H257" t="s">
+        <v>72</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>1</v>
+      </c>
+      <c r="N257">
+        <v>2</v>
+      </c>
+      <c r="O257" t="s">
+        <v>173</v>
+      </c>
+      <c r="P257" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q257">
+        <v>1.8</v>
+      </c>
+      <c r="R257">
+        <v>2.6</v>
+      </c>
+      <c r="S257">
+        <v>7</v>
+      </c>
+      <c r="T257">
+        <v>1.29</v>
+      </c>
+      <c r="U257">
+        <v>3.5</v>
+      </c>
+      <c r="V257">
+        <v>2.38</v>
+      </c>
+      <c r="W257">
+        <v>1.53</v>
+      </c>
+      <c r="X257">
+        <v>5.5</v>
+      </c>
+      <c r="Y257">
+        <v>1.14</v>
+      </c>
+      <c r="Z257">
+        <v>1.33</v>
+      </c>
+      <c r="AA257">
+        <v>5</v>
+      </c>
+      <c r="AB257">
+        <v>8</v>
+      </c>
+      <c r="AC257">
+        <v>1.01</v>
+      </c>
+      <c r="AD257">
+        <v>19</v>
+      </c>
+      <c r="AE257">
+        <v>1.18</v>
+      </c>
+      <c r="AF257">
+        <v>5</v>
+      </c>
+      <c r="AG257">
+        <v>1.57</v>
+      </c>
+      <c r="AH257">
+        <v>2.35</v>
+      </c>
+      <c r="AI257">
+        <v>1.83</v>
+      </c>
+      <c r="AJ257">
+        <v>1.83</v>
+      </c>
+      <c r="AK257">
+        <v>1.06</v>
+      </c>
+      <c r="AL257">
+        <v>1.11</v>
+      </c>
+      <c r="AM257">
+        <v>3.3</v>
+      </c>
+      <c r="AN257">
+        <v>2.33</v>
+      </c>
+      <c r="AO257">
+        <v>1.42</v>
+      </c>
+      <c r="AP257">
+        <v>2.23</v>
+      </c>
+      <c r="AQ257">
+        <v>1.38</v>
+      </c>
+      <c r="AR257">
+        <v>1.84</v>
+      </c>
+      <c r="AS257">
+        <v>1.37</v>
+      </c>
+      <c r="AT257">
+        <v>3.21</v>
+      </c>
+      <c r="AU257">
+        <v>7</v>
+      </c>
+      <c r="AV257">
+        <v>6</v>
+      </c>
+      <c r="AW257">
+        <v>15</v>
+      </c>
+      <c r="AX257">
+        <v>6</v>
+      </c>
+      <c r="AY257">
+        <v>22</v>
+      </c>
+      <c r="AZ257">
+        <v>12</v>
+      </c>
+      <c r="BA257">
+        <v>12</v>
+      </c>
+      <c r="BB257">
+        <v>3</v>
+      </c>
+      <c r="BC257">
+        <v>15</v>
+      </c>
+      <c r="BD257">
+        <v>1.3</v>
+      </c>
+      <c r="BE257">
+        <v>7.5</v>
+      </c>
+      <c r="BF257">
+        <v>3.7</v>
+      </c>
+      <c r="BG257">
+        <v>1.32</v>
+      </c>
+      <c r="BH257">
+        <v>3.05</v>
+      </c>
+      <c r="BI257">
+        <v>1.55</v>
+      </c>
+      <c r="BJ257">
+        <v>2.28</v>
+      </c>
+      <c r="BK257">
+        <v>1.9</v>
+      </c>
+      <c r="BL257">
+        <v>1.79</v>
+      </c>
+      <c r="BM257">
+        <v>2.38</v>
+      </c>
+      <c r="BN257">
+        <v>1.5</v>
+      </c>
+      <c r="BO257">
+        <v>3.05</v>
+      </c>
+      <c r="BP257">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -53185,13 +53185,13 @@
         <v>2.81</v>
       </c>
       <c r="AU251">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW251">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AX251">
         <v>0</v>
@@ -53200,7 +53200,7 @@
         <v>23</v>
       </c>
       <c r="AZ251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA251">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="393">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -817,6 +817,15 @@
     <t>['45', '90+3']</t>
   </si>
   <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['3', '21', '31', '65', '90+2']</t>
+  </si>
+  <si>
+    <t>['8', '33', '62']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1144,9 +1153,6 @@
     <t>['30', '52', '90+5']</t>
   </si>
   <si>
-    <t>['72']</t>
-  </si>
-  <si>
     <t>['12', '63']</t>
   </si>
   <si>
@@ -1181,6 +1187,12 @@
   </si>
   <si>
     <t>['59']</t>
+  </si>
+  <si>
+    <t>['24', '54', '62']</t>
+  </si>
+  <si>
+    <t>['26', '34', '38', '61']</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP257"/>
+  <dimension ref="A1:BP262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1879,7 +1891,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2004,7 +2016,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2210,7 +2222,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2288,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ4">
         <v>0.42</v>
@@ -2416,7 +2428,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2622,7 +2634,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2700,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2828,7 +2840,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3034,7 +3046,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3240,7 +3252,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3318,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ9">
         <v>1.69</v>
@@ -3652,7 +3664,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3939,7 +3951,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4064,7 +4076,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4142,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ13">
         <v>1.43</v>
@@ -4348,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ14">
         <v>0.46</v>
@@ -4682,7 +4694,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4969,7 +4981,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ17">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5506,7 +5518,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5587,7 +5599,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ20">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5996,7 +6008,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>2.15</v>
@@ -6536,7 +6548,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6614,7 +6626,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ25">
         <v>0.42</v>
@@ -6742,7 +6754,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6948,7 +6960,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7235,7 +7247,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ28">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7360,7 +7372,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7772,7 +7784,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8262,10 +8274,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ33">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8390,7 +8402,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8596,7 +8608,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8677,7 +8689,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -8880,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -9214,7 +9226,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9295,7 +9307,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ38">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9420,7 +9432,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9501,7 +9513,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9832,7 +9844,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9910,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ41">
         <v>0.92</v>
@@ -10116,7 +10128,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ42">
         <v>1.43</v>
@@ -10322,7 +10334,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ43">
         <v>0.62</v>
@@ -10656,7 +10668,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10862,7 +10874,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -10940,7 +10952,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ46">
         <v>1</v>
@@ -11149,7 +11161,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11274,7 +11286,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11686,7 +11698,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11764,7 +11776,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ50">
         <v>1.38</v>
@@ -11892,7 +11904,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12098,7 +12110,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12922,7 +12934,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13003,7 +13015,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13206,7 +13218,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ57">
         <v>0.46</v>
@@ -13334,7 +13346,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13415,7 +13427,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ58">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13540,7 +13552,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13952,7 +13964,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14033,7 +14045,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14158,7 +14170,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14364,7 +14376,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14442,7 +14454,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ63">
         <v>1.69</v>
@@ -14651,7 +14663,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ64">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -14982,7 +14994,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15063,7 +15075,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15266,7 +15278,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ67">
         <v>0.62</v>
@@ -15394,7 +15406,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15600,7 +15612,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15678,7 +15690,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>1.43</v>
@@ -15806,7 +15818,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16012,7 +16024,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16218,7 +16230,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16424,7 +16436,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16630,7 +16642,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16711,7 +16723,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ74">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -16836,7 +16848,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17326,10 +17338,10 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ77">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17454,7 +17466,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17532,10 +17544,10 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17660,7 +17672,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17741,7 +17753,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ79">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18072,7 +18084,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18484,7 +18496,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18690,7 +18702,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18768,7 +18780,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18974,10 +18986,10 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ85">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19308,7 +19320,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19926,7 +19938,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20210,7 +20222,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ91">
         <v>0.6899999999999999</v>
@@ -20338,7 +20350,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20416,7 +20428,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ92">
         <v>0.92</v>
@@ -20750,7 +20762,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20956,7 +20968,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21162,7 +21174,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21240,7 +21252,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96">
         <v>1.07</v>
@@ -21368,7 +21380,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21780,7 +21792,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21861,7 +21873,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ99">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22067,7 +22079,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ100">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22192,7 +22204,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22398,7 +22410,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22476,7 +22488,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22810,7 +22822,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22891,7 +22903,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ104">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23222,7 +23234,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23300,7 +23312,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ106">
         <v>1.14</v>
@@ -23921,7 +23933,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ109">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -24046,7 +24058,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24127,7 +24139,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24252,7 +24264,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24333,7 +24345,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ111">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24458,7 +24470,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25076,7 +25088,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25154,7 +25166,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ115">
         <v>0.6899999999999999</v>
@@ -25282,7 +25294,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25360,10 +25372,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25488,7 +25500,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25694,7 +25706,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25775,7 +25787,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ118">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25900,7 +25912,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26106,7 +26118,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26312,7 +26324,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26518,7 +26530,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26724,7 +26736,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26930,7 +26942,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27008,7 +27020,7 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ124">
         <v>1.69</v>
@@ -27136,7 +27148,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27548,7 +27560,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27754,7 +27766,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27832,7 +27844,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128">
         <v>1.69</v>
@@ -28038,10 +28050,10 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ129">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28166,7 +28178,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28372,7 +28384,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28453,7 +28465,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ131">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28784,7 +28796,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28865,7 +28877,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ133">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -29068,10 +29080,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ134">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29402,7 +29414,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29895,7 +29907,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -30304,7 +30316,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30716,7 +30728,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ142">
         <v>1.33</v>
@@ -31050,7 +31062,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31256,7 +31268,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31462,7 +31474,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31543,7 +31555,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ146">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31668,7 +31680,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31874,7 +31886,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32286,7 +32298,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32364,7 +32376,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ150">
         <v>1.43</v>
@@ -32492,7 +32504,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32573,7 +32585,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ151">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -32776,7 +32788,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ152">
         <v>0.46</v>
@@ -32904,7 +32916,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33110,7 +33122,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33191,7 +33203,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ154">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33316,7 +33328,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34012,7 +34024,7 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ158">
         <v>1.33</v>
@@ -34218,10 +34230,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ159">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34346,7 +34358,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34427,7 +34439,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ160">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34633,7 +34645,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ161">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34758,7 +34770,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34839,7 +34851,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ162">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35376,7 +35388,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35454,7 +35466,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ165">
         <v>1.69</v>
@@ -35582,7 +35594,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35660,7 +35672,7 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ166">
         <v>2.15</v>
@@ -36072,7 +36084,7 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168">
         <v>0.42</v>
@@ -36200,7 +36212,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36278,7 +36290,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ169">
         <v>1.33</v>
@@ -36406,7 +36418,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36612,7 +36624,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37024,7 +37036,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37105,7 +37117,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37517,7 +37529,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ175">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -37720,10 +37732,10 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ176">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -37848,7 +37860,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38054,7 +38066,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38135,7 +38147,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ178">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38466,7 +38478,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38672,7 +38684,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38956,7 +38968,7 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ182">
         <v>1.38</v>
@@ -39162,7 +39174,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ183">
         <v>1.69</v>
@@ -39290,7 +39302,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39371,7 +39383,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ184">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39496,7 +39508,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39702,7 +39714,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39780,7 +39792,7 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ186">
         <v>2.15</v>
@@ -40320,7 +40332,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40398,7 +40410,7 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ189">
         <v>0.6899999999999999</v>
@@ -40938,7 +40950,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41144,7 +41156,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41225,7 +41237,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ193">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41350,7 +41362,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41431,7 +41443,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ194">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41556,7 +41568,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41762,7 +41774,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41843,7 +41855,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ196">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -42049,7 +42061,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ197">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42380,7 +42392,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42792,7 +42804,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43282,7 +43294,7 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ203">
         <v>0.62</v>
@@ -43410,7 +43422,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43694,7 +43706,7 @@
         <v>1.3</v>
       </c>
       <c r="AP205">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ205">
         <v>1</v>
@@ -43822,7 +43834,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44028,7 +44040,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44234,7 +44246,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44315,7 +44327,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ208">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR208">
         <v>1.87</v>
@@ -44440,7 +44452,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44646,7 +44658,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44724,7 +44736,7 @@
         <v>1.18</v>
       </c>
       <c r="AP210">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ210">
         <v>1.14</v>
@@ -45139,7 +45151,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ212">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR212">
         <v>1.95</v>
@@ -45345,7 +45357,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ213">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR213">
         <v>1.76</v>
@@ -45551,7 +45563,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ214">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR214">
         <v>1.73</v>
@@ -45676,7 +45688,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46088,7 +46100,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46372,7 +46384,7 @@
         <v>2.2</v>
       </c>
       <c r="AP218">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ218">
         <v>2.15</v>
@@ -46784,10 +46796,10 @@
         <v>2.11</v>
       </c>
       <c r="AP220">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ220">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR220">
         <v>1.66</v>
@@ -46912,7 +46924,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47402,7 +47414,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP223">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ223">
         <v>0.42</v>
@@ -47530,7 +47542,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47814,7 +47826,7 @@
         <v>0.82</v>
       </c>
       <c r="AP225">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ225">
         <v>0.6899999999999999</v>
@@ -48148,7 +48160,7 @@
         <v>244</v>
       </c>
       <c r="P227" t="s">
-        <v>376</v>
+        <v>267</v>
       </c>
       <c r="Q227">
         <v>2.55</v>
@@ -48226,10 +48238,10 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ227">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR227">
         <v>1.46</v>
@@ -48354,7 +48366,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -49384,7 +49396,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49796,7 +49808,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49877,7 +49889,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ235">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR235">
         <v>1.73</v>
@@ -50002,7 +50014,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50286,7 +50298,7 @@
         <v>1.45</v>
       </c>
       <c r="AP237">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ237">
         <v>1.38</v>
@@ -50414,7 +50426,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50492,7 +50504,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ238">
         <v>1.33</v>
@@ -50826,7 +50838,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -50904,10 +50916,10 @@
         <v>1.17</v>
       </c>
       <c r="AP240">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ240">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR240">
         <v>1.93</v>
@@ -51110,10 +51122,10 @@
         <v>1.55</v>
       </c>
       <c r="AP241">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AQ241">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR241">
         <v>1.82</v>
@@ -51444,7 +51456,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51650,7 +51662,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51728,7 +51740,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ244">
         <v>1.69</v>
@@ -52140,7 +52152,7 @@
         <v>0.45</v>
       </c>
       <c r="AP246">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ246">
         <v>0.42</v>
@@ -52268,7 +52280,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52349,7 +52361,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ247">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR247">
         <v>1.71</v>
@@ -52474,7 +52486,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52761,7 +52773,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ249">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR249">
         <v>1.74</v>
@@ -52886,7 +52898,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53916,7 +53928,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54328,7 +54340,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -54485,6 +54497,1036 @@
       </c>
       <c r="BP257">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7465685</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F258">
+        <v>27</v>
+      </c>
+      <c r="G258" t="s">
+        <v>81</v>
+      </c>
+      <c r="H258" t="s">
+        <v>83</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258">
+        <v>1</v>
+      </c>
+      <c r="M258">
+        <v>3</v>
+      </c>
+      <c r="N258">
+        <v>4</v>
+      </c>
+      <c r="O258" t="s">
+        <v>267</v>
+      </c>
+      <c r="P258" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q258">
+        <v>3.1</v>
+      </c>
+      <c r="R258">
+        <v>2.2</v>
+      </c>
+      <c r="S258">
+        <v>2.9</v>
+      </c>
+      <c r="T258">
+        <v>1.3</v>
+      </c>
+      <c r="U258">
+        <v>3.2</v>
+      </c>
+      <c r="V258">
+        <v>2.4</v>
+      </c>
+      <c r="W258">
+        <v>1.5</v>
+      </c>
+      <c r="X258">
+        <v>6.1</v>
+      </c>
+      <c r="Y258">
+        <v>1.07</v>
+      </c>
+      <c r="Z258">
+        <v>2.65</v>
+      </c>
+      <c r="AA258">
+        <v>3.6</v>
+      </c>
+      <c r="AB258">
+        <v>2.45</v>
+      </c>
+      <c r="AC258">
+        <v>1.04</v>
+      </c>
+      <c r="AD258">
+        <v>10</v>
+      </c>
+      <c r="AE258">
+        <v>1.2</v>
+      </c>
+      <c r="AF258">
+        <v>4.33</v>
+      </c>
+      <c r="AG258">
+        <v>1.67</v>
+      </c>
+      <c r="AH258">
+        <v>2.15</v>
+      </c>
+      <c r="AI258">
+        <v>1.53</v>
+      </c>
+      <c r="AJ258">
+        <v>2.3</v>
+      </c>
+      <c r="AK258">
+        <v>1.55</v>
+      </c>
+      <c r="AL258">
+        <v>1.22</v>
+      </c>
+      <c r="AM258">
+        <v>1.45</v>
+      </c>
+      <c r="AN258">
+        <v>1.92</v>
+      </c>
+      <c r="AO258">
+        <v>1.31</v>
+      </c>
+      <c r="AP258">
+        <v>1.77</v>
+      </c>
+      <c r="AQ258">
+        <v>1.43</v>
+      </c>
+      <c r="AR258">
+        <v>1.76</v>
+      </c>
+      <c r="AS258">
+        <v>1.7</v>
+      </c>
+      <c r="AT258">
+        <v>3.46</v>
+      </c>
+      <c r="AU258">
+        <v>10</v>
+      </c>
+      <c r="AV258">
+        <v>6</v>
+      </c>
+      <c r="AW258">
+        <v>5</v>
+      </c>
+      <c r="AX258">
+        <v>5</v>
+      </c>
+      <c r="AY258">
+        <v>20</v>
+      </c>
+      <c r="AZ258">
+        <v>11</v>
+      </c>
+      <c r="BA258">
+        <v>4</v>
+      </c>
+      <c r="BB258">
+        <v>5</v>
+      </c>
+      <c r="BC258">
+        <v>9</v>
+      </c>
+      <c r="BD258">
+        <v>2.02</v>
+      </c>
+      <c r="BE258">
+        <v>6.5</v>
+      </c>
+      <c r="BF258">
+        <v>1.95</v>
+      </c>
+      <c r="BG258">
+        <v>1.3</v>
+      </c>
+      <c r="BH258">
+        <v>3.15</v>
+      </c>
+      <c r="BI258">
+        <v>1.5</v>
+      </c>
+      <c r="BJ258">
+        <v>2.35</v>
+      </c>
+      <c r="BK258">
+        <v>1.81</v>
+      </c>
+      <c r="BL258">
+        <v>1.88</v>
+      </c>
+      <c r="BM258">
+        <v>2.25</v>
+      </c>
+      <c r="BN258">
+        <v>1.55</v>
+      </c>
+      <c r="BO258">
+        <v>2.9</v>
+      </c>
+      <c r="BP258">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7465686</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F259">
+        <v>27</v>
+      </c>
+      <c r="G259" t="s">
+        <v>74</v>
+      </c>
+      <c r="H259" t="s">
+        <v>71</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>3</v>
+      </c>
+      <c r="K259">
+        <v>3</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>4</v>
+      </c>
+      <c r="N259">
+        <v>4</v>
+      </c>
+      <c r="O259" t="s">
+        <v>93</v>
+      </c>
+      <c r="P259" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q259">
+        <v>3.55</v>
+      </c>
+      <c r="R259">
+        <v>2.15</v>
+      </c>
+      <c r="S259">
+        <v>2.7</v>
+      </c>
+      <c r="T259">
+        <v>1.36</v>
+      </c>
+      <c r="U259">
+        <v>2.88</v>
+      </c>
+      <c r="V259">
+        <v>2.75</v>
+      </c>
+      <c r="W259">
+        <v>1.4</v>
+      </c>
+      <c r="X259">
+        <v>7.4</v>
+      </c>
+      <c r="Y259">
+        <v>1.04</v>
+      </c>
+      <c r="Z259">
+        <v>3.1</v>
+      </c>
+      <c r="AA259">
+        <v>3.6</v>
+      </c>
+      <c r="AB259">
+        <v>2.15</v>
+      </c>
+      <c r="AC259">
+        <v>1.05</v>
+      </c>
+      <c r="AD259">
+        <v>9.5</v>
+      </c>
+      <c r="AE259">
+        <v>1.28</v>
+      </c>
+      <c r="AF259">
+        <v>3.55</v>
+      </c>
+      <c r="AG259">
+        <v>1.9</v>
+      </c>
+      <c r="AH259">
+        <v>1.85</v>
+      </c>
+      <c r="AI259">
+        <v>1.73</v>
+      </c>
+      <c r="AJ259">
+        <v>1.95</v>
+      </c>
+      <c r="AK259">
+        <v>1.67</v>
+      </c>
+      <c r="AL259">
+        <v>1.22</v>
+      </c>
+      <c r="AM259">
+        <v>1.35</v>
+      </c>
+      <c r="AN259">
+        <v>1.62</v>
+      </c>
+      <c r="AO259">
+        <v>1.73</v>
+      </c>
+      <c r="AP259">
+        <v>1.5</v>
+      </c>
+      <c r="AQ259">
+        <v>1.83</v>
+      </c>
+      <c r="AR259">
+        <v>1.47</v>
+      </c>
+      <c r="AS259">
+        <v>1.58</v>
+      </c>
+      <c r="AT259">
+        <v>3.05</v>
+      </c>
+      <c r="AU259">
+        <v>3</v>
+      </c>
+      <c r="AV259">
+        <v>9</v>
+      </c>
+      <c r="AW259">
+        <v>4</v>
+      </c>
+      <c r="AX259">
+        <v>7</v>
+      </c>
+      <c r="AY259">
+        <v>7</v>
+      </c>
+      <c r="AZ259">
+        <v>16</v>
+      </c>
+      <c r="BA259">
+        <v>2</v>
+      </c>
+      <c r="BB259">
+        <v>6</v>
+      </c>
+      <c r="BC259">
+        <v>8</v>
+      </c>
+      <c r="BD259">
+        <v>2.43</v>
+      </c>
+      <c r="BE259">
+        <v>6.75</v>
+      </c>
+      <c r="BF259">
+        <v>1.67</v>
+      </c>
+      <c r="BG259">
+        <v>1.29</v>
+      </c>
+      <c r="BH259">
+        <v>3.15</v>
+      </c>
+      <c r="BI259">
+        <v>1.5</v>
+      </c>
+      <c r="BJ259">
+        <v>2.38</v>
+      </c>
+      <c r="BK259">
+        <v>1.81</v>
+      </c>
+      <c r="BL259">
+        <v>1.88</v>
+      </c>
+      <c r="BM259">
+        <v>2.28</v>
+      </c>
+      <c r="BN259">
+        <v>1.54</v>
+      </c>
+      <c r="BO259">
+        <v>2.95</v>
+      </c>
+      <c r="BP259">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7465684</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F260">
+        <v>27</v>
+      </c>
+      <c r="G260" t="s">
+        <v>82</v>
+      </c>
+      <c r="H260" t="s">
+        <v>85</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260" t="s">
+        <v>93</v>
+      </c>
+      <c r="P260" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q260">
+        <v>2.5</v>
+      </c>
+      <c r="R260">
+        <v>2.35</v>
+      </c>
+      <c r="S260">
+        <v>4</v>
+      </c>
+      <c r="T260">
+        <v>1.29</v>
+      </c>
+      <c r="U260">
+        <v>3.3</v>
+      </c>
+      <c r="V260">
+        <v>2.4</v>
+      </c>
+      <c r="W260">
+        <v>1.51</v>
+      </c>
+      <c r="X260">
+        <v>5.45</v>
+      </c>
+      <c r="Y260">
+        <v>1.12</v>
+      </c>
+      <c r="Z260">
+        <v>1.95</v>
+      </c>
+      <c r="AA260">
+        <v>3.75</v>
+      </c>
+      <c r="AB260">
+        <v>3.6</v>
+      </c>
+      <c r="AC260">
+        <v>1.02</v>
+      </c>
+      <c r="AD260">
+        <v>15</v>
+      </c>
+      <c r="AE260">
+        <v>1.2</v>
+      </c>
+      <c r="AF260">
+        <v>4.33</v>
+      </c>
+      <c r="AG260">
+        <v>1.66</v>
+      </c>
+      <c r="AH260">
+        <v>2.2</v>
+      </c>
+      <c r="AI260">
+        <v>1.6</v>
+      </c>
+      <c r="AJ260">
+        <v>2.3</v>
+      </c>
+      <c r="AK260">
+        <v>1.3</v>
+      </c>
+      <c r="AL260">
+        <v>1.22</v>
+      </c>
+      <c r="AM260">
+        <v>1.9</v>
+      </c>
+      <c r="AN260">
+        <v>1.75</v>
+      </c>
+      <c r="AO260">
+        <v>1.42</v>
+      </c>
+      <c r="AP260">
+        <v>1.69</v>
+      </c>
+      <c r="AQ260">
+        <v>1.38</v>
+      </c>
+      <c r="AR260">
+        <v>1.97</v>
+      </c>
+      <c r="AS260">
+        <v>1.21</v>
+      </c>
+      <c r="AT260">
+        <v>3.18</v>
+      </c>
+      <c r="AU260">
+        <v>5</v>
+      </c>
+      <c r="AV260">
+        <v>4</v>
+      </c>
+      <c r="AW260">
+        <v>11</v>
+      </c>
+      <c r="AX260">
+        <v>9</v>
+      </c>
+      <c r="AY260">
+        <v>16</v>
+      </c>
+      <c r="AZ260">
+        <v>13</v>
+      </c>
+      <c r="BA260">
+        <v>5</v>
+      </c>
+      <c r="BB260">
+        <v>2</v>
+      </c>
+      <c r="BC260">
+        <v>7</v>
+      </c>
+      <c r="BD260">
+        <v>1.56</v>
+      </c>
+      <c r="BE260">
+        <v>7</v>
+      </c>
+      <c r="BF260">
+        <v>2.65</v>
+      </c>
+      <c r="BG260">
+        <v>1.26</v>
+      </c>
+      <c r="BH260">
+        <v>3.4</v>
+      </c>
+      <c r="BI260">
+        <v>1.45</v>
+      </c>
+      <c r="BJ260">
+        <v>2.55</v>
+      </c>
+      <c r="BK260">
+        <v>1.74</v>
+      </c>
+      <c r="BL260">
+        <v>1.98</v>
+      </c>
+      <c r="BM260">
+        <v>2.15</v>
+      </c>
+      <c r="BN260">
+        <v>1.63</v>
+      </c>
+      <c r="BO260">
+        <v>2.7</v>
+      </c>
+      <c r="BP260">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7465681</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F261">
+        <v>27</v>
+      </c>
+      <c r="G261" t="s">
+        <v>77</v>
+      </c>
+      <c r="H261" t="s">
+        <v>78</v>
+      </c>
+      <c r="I261">
+        <v>3</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>3</v>
+      </c>
+      <c r="L261">
+        <v>5</v>
+      </c>
+      <c r="M261">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>6</v>
+      </c>
+      <c r="O261" t="s">
+        <v>268</v>
+      </c>
+      <c r="P261" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q261">
+        <v>2.2</v>
+      </c>
+      <c r="R261">
+        <v>2.6</v>
+      </c>
+      <c r="S261">
+        <v>4.33</v>
+      </c>
+      <c r="T261">
+        <v>1.25</v>
+      </c>
+      <c r="U261">
+        <v>3.75</v>
+      </c>
+      <c r="V261">
+        <v>2.1</v>
+      </c>
+      <c r="W261">
+        <v>1.67</v>
+      </c>
+      <c r="X261">
+        <v>4.5</v>
+      </c>
+      <c r="Y261">
+        <v>1.18</v>
+      </c>
+      <c r="Z261">
+        <v>1.7</v>
+      </c>
+      <c r="AA261">
+        <v>4.1</v>
+      </c>
+      <c r="AB261">
+        <v>4.2</v>
+      </c>
+      <c r="AC261">
+        <v>1.01</v>
+      </c>
+      <c r="AD261">
+        <v>17</v>
+      </c>
+      <c r="AE261">
+        <v>1.12</v>
+      </c>
+      <c r="AF261">
+        <v>6</v>
+      </c>
+      <c r="AG261">
+        <v>1.44</v>
+      </c>
+      <c r="AH261">
+        <v>2.7</v>
+      </c>
+      <c r="AI261">
+        <v>1.44</v>
+      </c>
+      <c r="AJ261">
+        <v>2.63</v>
+      </c>
+      <c r="AK261">
+        <v>1.19</v>
+      </c>
+      <c r="AL261">
+        <v>1.21</v>
+      </c>
+      <c r="AM261">
+        <v>2.2</v>
+      </c>
+      <c r="AN261">
+        <v>2.15</v>
+      </c>
+      <c r="AO261">
+        <v>1.15</v>
+      </c>
+      <c r="AP261">
+        <v>2.21</v>
+      </c>
+      <c r="AQ261">
+        <v>1.07</v>
+      </c>
+      <c r="AR261">
+        <v>1.81</v>
+      </c>
+      <c r="AS261">
+        <v>1.31</v>
+      </c>
+      <c r="AT261">
+        <v>3.12</v>
+      </c>
+      <c r="AU261">
+        <v>9</v>
+      </c>
+      <c r="AV261">
+        <v>3</v>
+      </c>
+      <c r="AW261">
+        <v>7</v>
+      </c>
+      <c r="AX261">
+        <v>7</v>
+      </c>
+      <c r="AY261">
+        <v>16</v>
+      </c>
+      <c r="AZ261">
+        <v>10</v>
+      </c>
+      <c r="BA261">
+        <v>2</v>
+      </c>
+      <c r="BB261">
+        <v>5</v>
+      </c>
+      <c r="BC261">
+        <v>7</v>
+      </c>
+      <c r="BD261">
+        <v>1.48</v>
+      </c>
+      <c r="BE261">
+        <v>7</v>
+      </c>
+      <c r="BF261">
+        <v>2.95</v>
+      </c>
+      <c r="BG261">
+        <v>1.21</v>
+      </c>
+      <c r="BH261">
+        <v>3.9</v>
+      </c>
+      <c r="BI261">
+        <v>1.38</v>
+      </c>
+      <c r="BJ261">
+        <v>2.8</v>
+      </c>
+      <c r="BK261">
+        <v>1.6</v>
+      </c>
+      <c r="BL261">
+        <v>2.17</v>
+      </c>
+      <c r="BM261">
+        <v>1.95</v>
+      </c>
+      <c r="BN261">
+        <v>1.75</v>
+      </c>
+      <c r="BO261">
+        <v>2.43</v>
+      </c>
+      <c r="BP261">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7465683</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45709.66666666666</v>
+      </c>
+      <c r="F262">
+        <v>27</v>
+      </c>
+      <c r="G262" t="s">
+        <v>72</v>
+      </c>
+      <c r="H262" t="s">
+        <v>75</v>
+      </c>
+      <c r="I262">
+        <v>2</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>3</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
+      </c>
+      <c r="N262">
+        <v>3</v>
+      </c>
+      <c r="O262" t="s">
+        <v>269</v>
+      </c>
+      <c r="P262" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q262">
+        <v>2.55</v>
+      </c>
+      <c r="R262">
+        <v>2.2</v>
+      </c>
+      <c r="S262">
+        <v>3.6</v>
+      </c>
+      <c r="T262">
+        <v>1.3</v>
+      </c>
+      <c r="U262">
+        <v>3.2</v>
+      </c>
+      <c r="V262">
+        <v>2.3</v>
+      </c>
+      <c r="W262">
+        <v>1.55</v>
+      </c>
+      <c r="X262">
+        <v>5.95</v>
+      </c>
+      <c r="Y262">
+        <v>1.08</v>
+      </c>
+      <c r="Z262">
+        <v>2.1</v>
+      </c>
+      <c r="AA262">
+        <v>3.55</v>
+      </c>
+      <c r="AB262">
+        <v>3.2</v>
+      </c>
+      <c r="AC262">
+        <v>1.04</v>
+      </c>
+      <c r="AD262">
+        <v>10</v>
+      </c>
+      <c r="AE262">
+        <v>1.2</v>
+      </c>
+      <c r="AF262">
+        <v>4.33</v>
+      </c>
+      <c r="AG262">
+        <v>1.62</v>
+      </c>
+      <c r="AH262">
+        <v>2.25</v>
+      </c>
+      <c r="AI262">
+        <v>1.5</v>
+      </c>
+      <c r="AJ262">
+        <v>2.38</v>
+      </c>
+      <c r="AK262">
+        <v>1.33</v>
+      </c>
+      <c r="AL262">
+        <v>1.22</v>
+      </c>
+      <c r="AM262">
+        <v>1.67</v>
+      </c>
+      <c r="AN262">
+        <v>1.5</v>
+      </c>
+      <c r="AO262">
+        <v>1</v>
+      </c>
+      <c r="AP262">
+        <v>1.62</v>
+      </c>
+      <c r="AQ262">
+        <v>0.92</v>
+      </c>
+      <c r="AR262">
+        <v>1.5</v>
+      </c>
+      <c r="AS262">
+        <v>1.42</v>
+      </c>
+      <c r="AT262">
+        <v>2.92</v>
+      </c>
+      <c r="AU262">
+        <v>10</v>
+      </c>
+      <c r="AV262">
+        <v>5</v>
+      </c>
+      <c r="AW262">
+        <v>1</v>
+      </c>
+      <c r="AX262">
+        <v>6</v>
+      </c>
+      <c r="AY262">
+        <v>11</v>
+      </c>
+      <c r="AZ262">
+        <v>11</v>
+      </c>
+      <c r="BA262">
+        <v>2</v>
+      </c>
+      <c r="BB262">
+        <v>6</v>
+      </c>
+      <c r="BC262">
+        <v>8</v>
+      </c>
+      <c r="BD262">
+        <v>1.84</v>
+      </c>
+      <c r="BE262">
+        <v>6.75</v>
+      </c>
+      <c r="BF262">
+        <v>2.12</v>
+      </c>
+      <c r="BG262">
+        <v>1.2</v>
+      </c>
+      <c r="BH262">
+        <v>3.95</v>
+      </c>
+      <c r="BI262">
+        <v>1.35</v>
+      </c>
+      <c r="BJ262">
+        <v>2.9</v>
+      </c>
+      <c r="BK262">
+        <v>1.58</v>
+      </c>
+      <c r="BL262">
+        <v>2.2</v>
+      </c>
+      <c r="BM262">
+        <v>1.92</v>
+      </c>
+      <c r="BN262">
+        <v>1.77</v>
+      </c>
+      <c r="BO262">
+        <v>2.4</v>
+      </c>
+      <c r="BP262">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="395">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -826,6 +826,9 @@
     <t>['8', '33', '62']</t>
   </si>
   <si>
+    <t>['77']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1194,6 +1197,9 @@
   <si>
     <t>['26', '34', '38', '61']</t>
   </si>
+  <si>
+    <t>['80', '85', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1554,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP262"/>
+  <dimension ref="A1:BP263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2016,7 +2022,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2222,7 +2228,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2428,7 +2434,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2634,7 +2640,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2840,7 +2846,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3046,7 +3052,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3252,7 +3258,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3333,7 +3339,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ9">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3664,7 +3670,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3948,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ12">
         <v>0.92</v>
@@ -4076,7 +4082,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4694,7 +4700,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5518,7 +5524,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6548,7 +6554,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6754,7 +6760,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6835,7 +6841,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR26">
         <v>1.18</v>
@@ -6960,7 +6966,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7372,7 +7378,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7450,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ29">
         <v>1.14</v>
@@ -7784,7 +7790,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8402,7 +8408,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8608,7 +8614,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9226,7 +9232,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9432,7 +9438,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9844,7 +9850,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10668,7 +10674,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10746,7 +10752,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ45">
         <v>0.42</v>
@@ -10874,7 +10880,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11286,7 +11292,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11367,7 +11373,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -11698,7 +11704,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11904,7 +11910,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12110,7 +12116,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12934,7 +12940,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13346,7 +13352,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13552,7 +13558,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13964,7 +13970,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14170,7 +14176,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14248,7 +14254,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14376,7 +14382,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14457,7 +14463,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ63">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14994,7 +15000,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15406,7 +15412,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15612,7 +15618,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15818,7 +15824,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16024,7 +16030,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16230,7 +16236,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16436,7 +16442,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16642,7 +16648,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16848,7 +16854,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17466,7 +17472,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17672,7 +17678,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18084,7 +18090,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18368,7 +18374,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ82">
         <v>2.15</v>
@@ -18496,7 +18502,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18577,7 +18583,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ83">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18702,7 +18708,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19320,7 +19326,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19938,7 +19944,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20350,7 +20356,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20762,7 +20768,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20968,7 +20974,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21046,7 +21052,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ95">
         <v>1.69</v>
@@ -21174,7 +21180,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21380,7 +21386,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21461,7 +21467,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ97">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -21792,7 +21798,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22204,7 +22210,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22410,7 +22416,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22822,7 +22828,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23234,7 +23240,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24058,7 +24064,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24264,7 +24270,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24470,7 +24476,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25088,7 +25094,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25294,7 +25300,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25500,7 +25506,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25706,7 +25712,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25784,7 +25790,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ118">
         <v>1.38</v>
@@ -25912,7 +25918,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26118,7 +26124,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26324,7 +26330,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26530,7 +26536,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26736,7 +26742,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26942,7 +26948,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27148,7 +27154,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27560,7 +27566,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27766,7 +27772,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27847,7 +27853,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ128">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -28178,7 +28184,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28384,7 +28390,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28796,7 +28802,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28874,7 +28880,7 @@
         <v>1.17</v>
       </c>
       <c r="AP133">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ133">
         <v>1.07</v>
@@ -29414,7 +29420,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -31062,7 +31068,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31268,7 +31274,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31349,7 +31355,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ145">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR145">
         <v>1.6</v>
@@ -31474,7 +31480,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31552,7 +31558,7 @@
         <v>2.5</v>
       </c>
       <c r="AP146">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ146">
         <v>1.83</v>
@@ -31680,7 +31686,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31886,7 +31892,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32298,7 +32304,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32504,7 +32510,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32916,7 +32922,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33122,7 +33128,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33328,7 +33334,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34358,7 +34364,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34770,7 +34776,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35388,7 +35394,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -35469,7 +35475,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ165">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR165">
         <v>1.91</v>
@@ -35594,7 +35600,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36212,7 +36218,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36418,7 +36424,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36624,7 +36630,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36908,7 +36914,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ172">
         <v>0.46</v>
@@ -37036,7 +37042,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37860,7 +37866,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38066,7 +38072,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38478,7 +38484,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38684,7 +38690,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39302,7 +39308,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39508,7 +39514,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39714,7 +39720,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40001,7 +40007,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ187">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR187">
         <v>1.79</v>
@@ -40332,7 +40338,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40950,7 +40956,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41156,7 +41162,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41362,7 +41368,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41568,7 +41574,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41774,7 +41780,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42058,7 +42064,7 @@
         <v>1.6</v>
       </c>
       <c r="AP197">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ197">
         <v>1.43</v>
@@ -42392,7 +42398,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42804,7 +42810,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43422,7 +43428,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43503,7 +43509,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ204">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR204">
         <v>1.4</v>
@@ -43834,7 +43840,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44040,7 +44046,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44246,7 +44252,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44452,7 +44458,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -44658,7 +44664,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -44942,7 +44948,7 @@
         <v>1.09</v>
       </c>
       <c r="AP211">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ211">
         <v>1.07</v>
@@ -45688,7 +45694,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46100,7 +46106,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46924,7 +46930,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47542,7 +47548,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -48366,7 +48372,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -49065,7 +49071,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ231">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR231">
         <v>1.77</v>
@@ -49396,7 +49402,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49808,7 +49814,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50014,7 +50020,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50426,7 +50432,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50838,7 +50844,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51456,7 +51462,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51662,7 +51668,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51946,7 +51952,7 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AQ245">
         <v>0.62</v>
@@ -52280,7 +52286,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52486,7 +52492,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52898,7 +52904,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53928,7 +53934,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54009,7 +54015,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ255">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR255">
         <v>1.7</v>
@@ -54340,7 +54346,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -54546,7 +54552,7 @@
         <v>267</v>
       </c>
       <c r="P258" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q258">
         <v>3.1</v>
@@ -54752,7 +54758,7 @@
         <v>93</v>
       </c>
       <c r="P259" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q259">
         <v>3.55</v>
@@ -55527,6 +55533,212 @@
       </c>
       <c r="BP262">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7465688</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45710.52083333334</v>
+      </c>
+      <c r="F263">
+        <v>27</v>
+      </c>
+      <c r="G263" t="s">
+        <v>80</v>
+      </c>
+      <c r="H263" t="s">
+        <v>88</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>0</v>
+      </c>
+      <c r="L263">
+        <v>1</v>
+      </c>
+      <c r="M263">
+        <v>3</v>
+      </c>
+      <c r="N263">
+        <v>4</v>
+      </c>
+      <c r="O263" t="s">
+        <v>270</v>
+      </c>
+      <c r="P263" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q263">
+        <v>4</v>
+      </c>
+      <c r="R263">
+        <v>2.5</v>
+      </c>
+      <c r="S263">
+        <v>2.3</v>
+      </c>
+      <c r="T263">
+        <v>1.25</v>
+      </c>
+      <c r="U263">
+        <v>3.75</v>
+      </c>
+      <c r="V263">
+        <v>2.2</v>
+      </c>
+      <c r="W263">
+        <v>1.62</v>
+      </c>
+      <c r="X263">
+        <v>5</v>
+      </c>
+      <c r="Y263">
+        <v>1.17</v>
+      </c>
+      <c r="Z263">
+        <v>3.9</v>
+      </c>
+      <c r="AA263">
+        <v>4</v>
+      </c>
+      <c r="AB263">
+        <v>1.75</v>
+      </c>
+      <c r="AC263">
+        <v>1.01</v>
+      </c>
+      <c r="AD263">
+        <v>17</v>
+      </c>
+      <c r="AE263">
+        <v>1.14</v>
+      </c>
+      <c r="AF263">
+        <v>5.5</v>
+      </c>
+      <c r="AG263">
+        <v>1.5</v>
+      </c>
+      <c r="AH263">
+        <v>2.5</v>
+      </c>
+      <c r="AI263">
+        <v>1.5</v>
+      </c>
+      <c r="AJ263">
+        <v>2.5</v>
+      </c>
+      <c r="AK263">
+        <v>1.95</v>
+      </c>
+      <c r="AL263">
+        <v>1.23</v>
+      </c>
+      <c r="AM263">
+        <v>1.25</v>
+      </c>
+      <c r="AN263">
+        <v>0.77</v>
+      </c>
+      <c r="AO263">
+        <v>1.69</v>
+      </c>
+      <c r="AP263">
+        <v>0.71</v>
+      </c>
+      <c r="AQ263">
+        <v>1.79</v>
+      </c>
+      <c r="AR263">
+        <v>1.63</v>
+      </c>
+      <c r="AS263">
+        <v>1.42</v>
+      </c>
+      <c r="AT263">
+        <v>3.05</v>
+      </c>
+      <c r="AU263">
+        <v>4</v>
+      </c>
+      <c r="AV263">
+        <v>6</v>
+      </c>
+      <c r="AW263">
+        <v>7</v>
+      </c>
+      <c r="AX263">
+        <v>6</v>
+      </c>
+      <c r="AY263">
+        <v>11</v>
+      </c>
+      <c r="AZ263">
+        <v>12</v>
+      </c>
+      <c r="BA263">
+        <v>4</v>
+      </c>
+      <c r="BB263">
+        <v>5</v>
+      </c>
+      <c r="BC263">
+        <v>9</v>
+      </c>
+      <c r="BD263">
+        <v>2.48</v>
+      </c>
+      <c r="BE263">
+        <v>6.5</v>
+      </c>
+      <c r="BF263">
+        <v>1.66</v>
+      </c>
+      <c r="BG263">
+        <v>1.3</v>
+      </c>
+      <c r="BH263">
+        <v>3.05</v>
+      </c>
+      <c r="BI263">
+        <v>1.55</v>
+      </c>
+      <c r="BJ263">
+        <v>2.28</v>
+      </c>
+      <c r="BK263">
+        <v>1.9</v>
+      </c>
+      <c r="BL263">
+        <v>1.79</v>
+      </c>
+      <c r="BM263">
+        <v>2.35</v>
+      </c>
+      <c r="BN263">
+        <v>1.5</v>
+      </c>
+      <c r="BO263">
+        <v>3.05</v>
+      </c>
+      <c r="BP263">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="397">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -829,6 +829,9 @@
     <t>['77']</t>
   </si>
   <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1048,9 +1051,6 @@
     <t>['41', '44', '48']</t>
   </si>
   <si>
-    <t>['85']</t>
-  </si>
-  <si>
     <t>['12', '19']</t>
   </si>
   <si>
@@ -1199,6 +1199,12 @@
   </si>
   <si>
     <t>['80', '85', '90+5']</t>
+  </si>
+  <si>
+    <t>['69', '90+3']</t>
+  </si>
+  <si>
+    <t>['1', '2', '5', '28']</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP263"/>
+  <dimension ref="A1:BP265"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1894,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ2">
         <v>1.38</v>
@@ -2022,7 +2028,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2228,7 +2234,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2309,7 +2315,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ4">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2434,7 +2440,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2512,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ5">
         <v>2.15</v>
@@ -2640,7 +2646,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2846,7 +2852,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3052,7 +3058,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3258,7 +3264,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3670,7 +3676,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4082,7 +4088,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4700,7 +4706,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5193,7 +5199,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ18">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5524,7 +5530,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6554,7 +6560,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6635,7 +6641,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ25">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6760,7 +6766,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6966,7 +6972,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7044,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ27">
         <v>0.6899999999999999</v>
@@ -7378,7 +7384,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7790,7 +7796,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8408,7 +8414,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8486,7 +8492,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8614,7 +8620,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9232,7 +9238,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9438,7 +9444,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9850,7 +9856,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10674,7 +10680,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10755,7 +10761,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ45">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -10880,7 +10886,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11292,7 +11298,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11370,7 +11376,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ48">
         <v>1.79</v>
@@ -11576,7 +11582,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ49">
         <v>1.69</v>
@@ -11704,7 +11710,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11910,7 +11916,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12116,7 +12122,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12403,7 +12409,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -12940,7 +12946,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13352,7 +13358,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13558,7 +13564,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13639,7 +13645,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -13970,7 +13976,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14176,7 +14182,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14382,7 +14388,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15000,7 +15006,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15412,7 +15418,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15618,7 +15624,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15824,7 +15830,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16030,7 +16036,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16236,7 +16242,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16442,7 +16448,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16520,7 +16526,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16648,7 +16654,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16854,7 +16860,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16935,7 +16941,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ75">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17138,7 +17144,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ76">
         <v>1.14</v>
@@ -17472,7 +17478,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17678,7 +17684,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18090,7 +18096,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18502,7 +18508,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18708,7 +18714,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18789,7 +18795,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -19326,7 +19332,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19944,7 +19950,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20356,7 +20362,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20640,7 +20646,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20768,7 +20774,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20974,7 +20980,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21180,7 +21186,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21386,7 +21392,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21673,7 +21679,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21798,7 +21804,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21876,7 +21882,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ99">
         <v>1.83</v>
@@ -22210,7 +22216,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22416,7 +22422,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22828,7 +22834,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23115,7 +23121,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ105">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -23240,7 +23246,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24064,7 +24070,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24270,7 +24276,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24476,7 +24482,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24763,7 +24769,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ113">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -25094,7 +25100,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25300,7 +25306,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25506,7 +25512,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25712,7 +25718,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25918,7 +25924,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26124,7 +26130,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26330,7 +26336,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26408,7 +26414,7 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ121">
         <v>1.38</v>
@@ -26536,7 +26542,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26742,7 +26748,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26948,7 +26954,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27154,7 +27160,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27232,10 +27238,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ125">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27566,7 +27572,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27772,7 +27778,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28184,7 +28190,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28390,7 +28396,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28674,7 +28680,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ132">
         <v>0.92</v>
@@ -28802,7 +28808,7 @@
         <v>93</v>
       </c>
       <c r="P133" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -30119,7 +30125,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ139">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30940,7 +30946,7 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ143">
         <v>0.62</v>
@@ -31146,7 +31152,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ144">
         <v>1.69</v>
@@ -33003,7 +33009,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33128,7 +33134,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -34033,7 +34039,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34776,7 +34782,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35266,7 +35272,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ164">
         <v>1</v>
@@ -35394,7 +35400,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="Q165">
         <v>2.8</v>
@@ -36093,7 +36099,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ168">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -37120,7 +37126,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ173">
         <v>0.92</v>
@@ -37947,7 +37953,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ177">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -38072,7 +38078,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -39592,7 +39598,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -40338,7 +40344,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40831,7 +40837,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ191">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -42398,7 +42404,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42476,7 +42482,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ199">
         <v>1.07</v>
@@ -42810,7 +42816,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43506,7 +43512,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ204">
         <v>1.79</v>
@@ -44046,7 +44052,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44458,7 +44464,7 @@
         <v>231</v>
       </c>
       <c r="P209" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="Q209">
         <v>1.93</v>
@@ -45566,7 +45572,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ214">
         <v>1.38</v>
@@ -47008,7 +47014,7 @@
         <v>2.27</v>
       </c>
       <c r="AP221">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ221">
         <v>2.15</v>
@@ -47423,7 +47429,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ223">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR223">
         <v>1.93</v>
@@ -48041,7 +48047,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ226">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48659,7 +48665,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ229">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR229">
         <v>1.74</v>
@@ -50098,7 +50104,7 @@
         <v>1.33</v>
       </c>
       <c r="AP236">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ236">
         <v>1.14</v>
@@ -50513,7 +50519,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ238">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR238">
         <v>1.84</v>
@@ -51334,7 +51340,7 @@
         <v>0.45</v>
       </c>
       <c r="AP242">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ242">
         <v>0.46</v>
@@ -51543,7 +51549,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ243">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR243">
         <v>1.91</v>
@@ -52161,7 +52167,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ246">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR246">
         <v>1.7</v>
@@ -52904,7 +52910,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53394,7 +53400,7 @@
         <v>1.54</v>
       </c>
       <c r="AP252">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AQ252">
         <v>1.43</v>
@@ -55487,13 +55493,13 @@
         <v>11</v>
       </c>
       <c r="BA262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB262">
         <v>6</v>
       </c>
       <c r="BC262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD262">
         <v>1.84</v>
@@ -55739,6 +55745,418 @@
       </c>
       <c r="BP263">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7465682</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45711.34375</v>
+      </c>
+      <c r="F264">
+        <v>27</v>
+      </c>
+      <c r="G264" t="s">
+        <v>70</v>
+      </c>
+      <c r="H264" t="s">
+        <v>84</v>
+      </c>
+      <c r="I264">
+        <v>1</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>1</v>
+      </c>
+      <c r="L264">
+        <v>1</v>
+      </c>
+      <c r="M264">
+        <v>2</v>
+      </c>
+      <c r="N264">
+        <v>3</v>
+      </c>
+      <c r="O264" t="s">
+        <v>235</v>
+      </c>
+      <c r="P264" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q264">
+        <v>2.2</v>
+      </c>
+      <c r="R264">
+        <v>2.38</v>
+      </c>
+      <c r="S264">
+        <v>5</v>
+      </c>
+      <c r="T264">
+        <v>1.33</v>
+      </c>
+      <c r="U264">
+        <v>3.25</v>
+      </c>
+      <c r="V264">
+        <v>2.5</v>
+      </c>
+      <c r="W264">
+        <v>1.5</v>
+      </c>
+      <c r="X264">
+        <v>6.5</v>
+      </c>
+      <c r="Y264">
+        <v>1.11</v>
+      </c>
+      <c r="Z264">
+        <v>1.62</v>
+      </c>
+      <c r="AA264">
+        <v>4</v>
+      </c>
+      <c r="AB264">
+        <v>5</v>
+      </c>
+      <c r="AC264">
+        <v>1.02</v>
+      </c>
+      <c r="AD264">
+        <v>15</v>
+      </c>
+      <c r="AE264">
+        <v>1.22</v>
+      </c>
+      <c r="AF264">
+        <v>4.2</v>
+      </c>
+      <c r="AG264">
+        <v>1.7</v>
+      </c>
+      <c r="AH264">
+        <v>2.1</v>
+      </c>
+      <c r="AI264">
+        <v>1.73</v>
+      </c>
+      <c r="AJ264">
+        <v>2</v>
+      </c>
+      <c r="AK264">
+        <v>1.18</v>
+      </c>
+      <c r="AL264">
+        <v>1.22</v>
+      </c>
+      <c r="AM264">
+        <v>2.2</v>
+      </c>
+      <c r="AN264">
+        <v>1.25</v>
+      </c>
+      <c r="AO264">
+        <v>0.42</v>
+      </c>
+      <c r="AP264">
+        <v>1.15</v>
+      </c>
+      <c r="AQ264">
+        <v>0.62</v>
+      </c>
+      <c r="AR264">
+        <v>1.35</v>
+      </c>
+      <c r="AS264">
+        <v>1.17</v>
+      </c>
+      <c r="AT264">
+        <v>2.52</v>
+      </c>
+      <c r="AU264">
+        <v>6</v>
+      </c>
+      <c r="AV264">
+        <v>9</v>
+      </c>
+      <c r="AW264">
+        <v>12</v>
+      </c>
+      <c r="AX264">
+        <v>3</v>
+      </c>
+      <c r="AY264">
+        <v>18</v>
+      </c>
+      <c r="AZ264">
+        <v>12</v>
+      </c>
+      <c r="BA264">
+        <v>5</v>
+      </c>
+      <c r="BB264">
+        <v>4</v>
+      </c>
+      <c r="BC264">
+        <v>9</v>
+      </c>
+      <c r="BD264">
+        <v>1.47</v>
+      </c>
+      <c r="BE264">
+        <v>6.75</v>
+      </c>
+      <c r="BF264">
+        <v>2.95</v>
+      </c>
+      <c r="BG264">
+        <v>1.29</v>
+      </c>
+      <c r="BH264">
+        <v>3.15</v>
+      </c>
+      <c r="BI264">
+        <v>1.5</v>
+      </c>
+      <c r="BJ264">
+        <v>2.35</v>
+      </c>
+      <c r="BK264">
+        <v>1.82</v>
+      </c>
+      <c r="BL264">
+        <v>1.86</v>
+      </c>
+      <c r="BM264">
+        <v>2.3</v>
+      </c>
+      <c r="BN264">
+        <v>1.54</v>
+      </c>
+      <c r="BO264">
+        <v>2.9</v>
+      </c>
+      <c r="BP264">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7465689</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45711.53125</v>
+      </c>
+      <c r="F265">
+        <v>27</v>
+      </c>
+      <c r="G265" t="s">
+        <v>73</v>
+      </c>
+      <c r="H265" t="s">
+        <v>76</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>4</v>
+      </c>
+      <c r="K265">
+        <v>4</v>
+      </c>
+      <c r="L265">
+        <v>1</v>
+      </c>
+      <c r="M265">
+        <v>4</v>
+      </c>
+      <c r="N265">
+        <v>5</v>
+      </c>
+      <c r="O265" t="s">
+        <v>271</v>
+      </c>
+      <c r="P265" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q265">
+        <v>3.35</v>
+      </c>
+      <c r="R265">
+        <v>2.25</v>
+      </c>
+      <c r="S265">
+        <v>2.65</v>
+      </c>
+      <c r="T265">
+        <v>1.28</v>
+      </c>
+      <c r="U265">
+        <v>3.4</v>
+      </c>
+      <c r="V265">
+        <v>2.25</v>
+      </c>
+      <c r="W265">
+        <v>1.57</v>
+      </c>
+      <c r="X265">
+        <v>5.25</v>
+      </c>
+      <c r="Y265">
+        <v>1.12</v>
+      </c>
+      <c r="Z265">
+        <v>2.95</v>
+      </c>
+      <c r="AA265">
+        <v>3.65</v>
+      </c>
+      <c r="AB265">
+        <v>2.15</v>
+      </c>
+      <c r="AC265">
+        <v>1.03</v>
+      </c>
+      <c r="AD265">
+        <v>11</v>
+      </c>
+      <c r="AE265">
+        <v>1.18</v>
+      </c>
+      <c r="AF265">
+        <v>4.75</v>
+      </c>
+      <c r="AG265">
+        <v>1.57</v>
+      </c>
+      <c r="AH265">
+        <v>2.35</v>
+      </c>
+      <c r="AI265">
+        <v>1.48</v>
+      </c>
+      <c r="AJ265">
+        <v>2.45</v>
+      </c>
+      <c r="AK265">
+        <v>1.65</v>
+      </c>
+      <c r="AL265">
+        <v>1.22</v>
+      </c>
+      <c r="AM265">
+        <v>1.38</v>
+      </c>
+      <c r="AN265">
+        <v>1.92</v>
+      </c>
+      <c r="AO265">
+        <v>1.33</v>
+      </c>
+      <c r="AP265">
+        <v>1.79</v>
+      </c>
+      <c r="AQ265">
+        <v>1.46</v>
+      </c>
+      <c r="AR265">
+        <v>1.71</v>
+      </c>
+      <c r="AS265">
+        <v>1.51</v>
+      </c>
+      <c r="AT265">
+        <v>3.22</v>
+      </c>
+      <c r="AU265">
+        <v>4</v>
+      </c>
+      <c r="AV265">
+        <v>7</v>
+      </c>
+      <c r="AW265">
+        <v>6</v>
+      </c>
+      <c r="AX265">
+        <v>8</v>
+      </c>
+      <c r="AY265">
+        <v>10</v>
+      </c>
+      <c r="AZ265">
+        <v>15</v>
+      </c>
+      <c r="BA265">
+        <v>7</v>
+      </c>
+      <c r="BB265">
+        <v>1</v>
+      </c>
+      <c r="BC265">
+        <v>8</v>
+      </c>
+      <c r="BD265">
+        <v>2.3</v>
+      </c>
+      <c r="BE265">
+        <v>6.4</v>
+      </c>
+      <c r="BF265">
+        <v>1.74</v>
+      </c>
+      <c r="BG265">
+        <v>1.35</v>
+      </c>
+      <c r="BH265">
+        <v>2.9</v>
+      </c>
+      <c r="BI265">
+        <v>1.58</v>
+      </c>
+      <c r="BJ265">
+        <v>2.18</v>
+      </c>
+      <c r="BK265">
+        <v>1.95</v>
+      </c>
+      <c r="BL265">
+        <v>1.75</v>
+      </c>
+      <c r="BM265">
+        <v>2.48</v>
+      </c>
+      <c r="BN265">
+        <v>1.47</v>
+      </c>
+      <c r="BO265">
+        <v>3.2</v>
+      </c>
+      <c r="BP265">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="400">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -832,6 +832,12 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['55']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1087,9 +1093,6 @@
     <t>['45+1', '90+1']</t>
   </si>
   <si>
-    <t>['55']</t>
-  </si>
-  <si>
     <t>['57', '81', '85']</t>
   </si>
   <si>
@@ -1205,6 +1208,12 @@
   </si>
   <si>
     <t>['1', '2', '5', '28']</t>
+  </si>
+  <si>
+    <t>['33', '67']</t>
+  </si>
+  <si>
+    <t>['62', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP265"/>
+  <dimension ref="A1:BP268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2028,7 +2037,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2109,7 +2118,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ3">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2234,7 +2243,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2312,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4">
         <v>0.62</v>
@@ -2440,7 +2449,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2521,7 +2530,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ5">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2646,7 +2655,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2852,7 +2861,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3058,7 +3067,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3264,7 +3273,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3676,7 +3685,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3754,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ11">
         <v>0.6899999999999999</v>
@@ -4088,7 +4097,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4706,7 +4715,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5530,7 +5539,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5611,7 +5620,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ20">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5814,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ21">
         <v>0.62</v>
@@ -6023,7 +6032,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ22">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6560,7 +6569,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6766,7 +6775,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6972,7 +6981,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7384,7 +7393,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7671,7 +7680,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -7796,7 +7805,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7874,7 +7883,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ31">
         <v>1.07</v>
@@ -8414,7 +8423,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8620,7 +8629,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8701,7 +8710,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ35">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -8904,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -9113,7 +9122,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ37">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9238,7 +9247,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9444,7 +9453,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9522,7 +9531,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ39">
         <v>1.38</v>
@@ -9856,7 +9865,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10680,7 +10689,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10886,7 +10895,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11298,7 +11307,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11585,7 +11594,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ49">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11710,7 +11719,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11916,7 +11925,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12122,7 +12131,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12946,7 +12955,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13230,7 +13239,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57">
         <v>0.46</v>
@@ -13358,7 +13367,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13564,7 +13573,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13642,7 +13651,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ59">
         <v>1.46</v>
@@ -13851,7 +13860,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ60">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -13976,7 +13985,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14054,7 +14063,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ61">
         <v>1.07</v>
@@ -14182,7 +14191,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14388,7 +14397,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14466,7 +14475,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.79</v>
@@ -14675,7 +14684,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ64">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -15006,7 +15015,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15418,7 +15427,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15624,7 +15633,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15830,7 +15839,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16036,7 +16045,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16117,7 +16126,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16242,7 +16251,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16448,7 +16457,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16654,7 +16663,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16860,7 +16869,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17478,7 +17487,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17684,7 +17693,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17765,7 +17774,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ79">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -17968,10 +17977,10 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ80">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -18096,7 +18105,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18174,7 +18183,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ81">
         <v>1.38</v>
@@ -18383,7 +18392,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ82">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18508,7 +18517,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18714,7 +18723,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19332,7 +19341,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19950,7 +19959,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20234,7 +20243,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>0.6899999999999999</v>
@@ -20362,7 +20371,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20774,7 +20783,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20980,7 +20989,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21061,7 +21070,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ95">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21186,7 +21195,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21392,7 +21401,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21676,7 +21685,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ98">
         <v>0.62</v>
@@ -21804,7 +21813,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21885,7 +21894,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ99">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22216,7 +22225,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22422,7 +22431,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22834,7 +22843,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22912,7 +22921,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ104">
         <v>1.43</v>
@@ -23118,7 +23127,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ105">
         <v>1.46</v>
@@ -23246,7 +23255,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23324,7 +23333,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106">
         <v>1.14</v>
@@ -24070,7 +24079,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24276,7 +24285,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24482,7 +24491,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25100,7 +25109,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25306,7 +25315,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25512,7 +25521,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25718,7 +25727,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25924,7 +25933,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26005,7 +26014,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ119">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -26130,7 +26139,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26336,7 +26345,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26542,7 +26551,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26623,7 +26632,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ122">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26748,7 +26757,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26826,7 +26835,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -26954,7 +26963,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27035,7 +27044,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ124">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -27160,7 +27169,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27572,7 +27581,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27778,7 +27787,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28062,7 +28071,7 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129">
         <v>1.43</v>
@@ -28190,7 +28199,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28396,7 +28405,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28474,10 +28483,10 @@
         <v>2.4</v>
       </c>
       <c r="AP131">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ131">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -29426,7 +29435,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -31074,7 +31083,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31155,7 +31164,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ144">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -31280,7 +31289,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31358,7 +31367,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ145">
         <v>1.79</v>
@@ -31486,7 +31495,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31567,7 +31576,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ146">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31692,7 +31701,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31773,7 +31782,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ147">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -31898,7 +31907,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32182,7 +32191,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ149">
         <v>1.07</v>
@@ -32310,7 +32319,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32388,7 +32397,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ150">
         <v>1.43</v>
@@ -32516,7 +32525,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32928,7 +32937,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33134,7 +33143,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33212,7 +33221,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ154">
         <v>1.07</v>
@@ -33340,7 +33349,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34036,7 +34045,7 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
         <v>1.46</v>
@@ -34370,7 +34379,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34782,7 +34791,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34863,7 +34872,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ162">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35606,7 +35615,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35687,7 +35696,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ166">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -36224,7 +36233,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>357</v>
+        <v>273</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -36430,7 +36439,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36511,7 +36520,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ170">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -36636,7 +36645,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37048,7 +37057,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37744,7 +37753,7 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176">
         <v>1.38</v>
@@ -37872,7 +37881,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38078,7 +38087,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38362,7 +38371,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ179">
         <v>0.92</v>
@@ -38490,7 +38499,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38696,7 +38705,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38774,7 +38783,7 @@
         <v>1.11</v>
       </c>
       <c r="AP181">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ181">
         <v>1.14</v>
@@ -39189,7 +39198,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ183">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -39314,7 +39323,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39395,7 +39404,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ184">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39520,7 +39529,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39726,7 +39735,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39807,7 +39816,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ186">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40344,7 +40353,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40962,7 +40971,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41168,7 +41177,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41246,7 +41255,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ193">
         <v>0.92</v>
@@ -41374,7 +41383,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41580,7 +41589,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41786,7 +41795,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42404,7 +42413,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42816,7 +42825,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42894,7 +42903,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ201">
         <v>1.14</v>
@@ -43103,7 +43112,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ202">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -43434,7 +43443,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43846,7 +43855,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44052,7 +44061,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44258,7 +44267,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44670,7 +44679,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -45700,7 +45709,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45984,7 +45993,7 @@
         <v>1.18</v>
       </c>
       <c r="AP216">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ216">
         <v>1</v>
@@ -46112,7 +46121,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46399,7 +46408,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ218">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR218">
         <v>1.9</v>
@@ -46811,7 +46820,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ220">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR220">
         <v>1.66</v>
@@ -46936,7 +46945,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47017,7 +47026,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ221">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR221">
         <v>1.34</v>
@@ -47554,7 +47563,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47635,7 +47644,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ224">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR224">
         <v>1.73</v>
@@ -48250,7 +48259,7 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ227">
         <v>1.07</v>
@@ -48378,7 +48387,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48456,7 +48465,7 @@
         <v>1.3</v>
       </c>
       <c r="AP228">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ228">
         <v>1.33</v>
@@ -49408,7 +49417,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49820,7 +49829,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50026,7 +50035,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50438,7 +50447,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50850,7 +50859,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51468,7 +51477,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51674,7 +51683,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51752,10 +51761,10 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ244">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AR244">
         <v>1.44</v>
@@ -52292,7 +52301,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52370,7 +52379,7 @@
         <v>1.42</v>
       </c>
       <c r="AP247">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ247">
         <v>1.43</v>
@@ -52498,7 +52507,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52576,10 +52585,10 @@
         <v>2.08</v>
       </c>
       <c r="AP248">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AQ248">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AR248">
         <v>1.53</v>
@@ -52785,7 +52794,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ249">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR249">
         <v>1.74</v>
@@ -52910,7 +52919,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -53940,7 +53949,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54352,7 +54361,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -54558,7 +54567,7 @@
         <v>267</v>
       </c>
       <c r="P258" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q258">
         <v>3.1</v>
@@ -54764,7 +54773,7 @@
         <v>93</v>
       </c>
       <c r="P259" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q259">
         <v>3.55</v>
@@ -54845,7 +54854,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ259">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR259">
         <v>1.47</v>
@@ -55460,7 +55469,7 @@
         <v>1</v>
       </c>
       <c r="AP262">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ262">
         <v>0.92</v>
@@ -55588,7 +55597,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55794,7 +55803,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56000,7 +56009,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56157,6 +56166,624 @@
       </c>
       <c r="BP265">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7465616</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45712.66666666666</v>
+      </c>
+      <c r="F266">
+        <v>21</v>
+      </c>
+      <c r="G266" t="s">
+        <v>72</v>
+      </c>
+      <c r="H266" t="s">
+        <v>71</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>1</v>
+      </c>
+      <c r="K266">
+        <v>2</v>
+      </c>
+      <c r="L266">
+        <v>1</v>
+      </c>
+      <c r="M266">
+        <v>2</v>
+      </c>
+      <c r="N266">
+        <v>3</v>
+      </c>
+      <c r="O266" t="s">
+        <v>272</v>
+      </c>
+      <c r="P266" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q266">
+        <v>3.75</v>
+      </c>
+      <c r="R266">
+        <v>2.38</v>
+      </c>
+      <c r="S266">
+        <v>2.5</v>
+      </c>
+      <c r="T266">
+        <v>1.3</v>
+      </c>
+      <c r="U266">
+        <v>3.4</v>
+      </c>
+      <c r="V266">
+        <v>2.38</v>
+      </c>
+      <c r="W266">
+        <v>1.53</v>
+      </c>
+      <c r="X266">
+        <v>6</v>
+      </c>
+      <c r="Y266">
+        <v>1.13</v>
+      </c>
+      <c r="Z266">
+        <v>3.25</v>
+      </c>
+      <c r="AA266">
+        <v>3.8</v>
+      </c>
+      <c r="AB266">
+        <v>2</v>
+      </c>
+      <c r="AC266">
+        <v>1.02</v>
+      </c>
+      <c r="AD266">
+        <v>17</v>
+      </c>
+      <c r="AE266">
+        <v>1.18</v>
+      </c>
+      <c r="AF266">
+        <v>4.75</v>
+      </c>
+      <c r="AG266">
+        <v>1.6</v>
+      </c>
+      <c r="AH266">
+        <v>2.3</v>
+      </c>
+      <c r="AI266">
+        <v>1.53</v>
+      </c>
+      <c r="AJ266">
+        <v>2.38</v>
+      </c>
+      <c r="AK266">
+        <v>1.83</v>
+      </c>
+      <c r="AL266">
+        <v>1.22</v>
+      </c>
+      <c r="AM266">
+        <v>1.33</v>
+      </c>
+      <c r="AN266">
+        <v>1.62</v>
+      </c>
+      <c r="AO266">
+        <v>1.83</v>
+      </c>
+      <c r="AP266">
+        <v>1.5</v>
+      </c>
+      <c r="AQ266">
+        <v>1.92</v>
+      </c>
+      <c r="AR266">
+        <v>1.52</v>
+      </c>
+      <c r="AS266">
+        <v>1.63</v>
+      </c>
+      <c r="AT266">
+        <v>3.15</v>
+      </c>
+      <c r="AU266">
+        <v>3</v>
+      </c>
+      <c r="AV266">
+        <v>5</v>
+      </c>
+      <c r="AW266">
+        <v>9</v>
+      </c>
+      <c r="AX266">
+        <v>6</v>
+      </c>
+      <c r="AY266">
+        <v>12</v>
+      </c>
+      <c r="AZ266">
+        <v>11</v>
+      </c>
+      <c r="BA266">
+        <v>3</v>
+      </c>
+      <c r="BB266">
+        <v>8</v>
+      </c>
+      <c r="BC266">
+        <v>11</v>
+      </c>
+      <c r="BD266">
+        <v>2.55</v>
+      </c>
+      <c r="BE266">
+        <v>6.5</v>
+      </c>
+      <c r="BF266">
+        <v>1.64</v>
+      </c>
+      <c r="BG266">
+        <v>1.32</v>
+      </c>
+      <c r="BH266">
+        <v>3.05</v>
+      </c>
+      <c r="BI266">
+        <v>1.54</v>
+      </c>
+      <c r="BJ266">
+        <v>2.3</v>
+      </c>
+      <c r="BK266">
+        <v>1.86</v>
+      </c>
+      <c r="BL266">
+        <v>1.82</v>
+      </c>
+      <c r="BM266">
+        <v>2.33</v>
+      </c>
+      <c r="BN266">
+        <v>1.52</v>
+      </c>
+      <c r="BO266">
+        <v>2.95</v>
+      </c>
+      <c r="BP266">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7465690</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45712.66666666666</v>
+      </c>
+      <c r="F267">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>89</v>
+      </c>
+      <c r="H267" t="s">
+        <v>87</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>0</v>
+      </c>
+      <c r="L267">
+        <v>1</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>2</v>
+      </c>
+      <c r="O267" t="s">
+        <v>273</v>
+      </c>
+      <c r="P267" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q267">
+        <v>4</v>
+      </c>
+      <c r="R267">
+        <v>2.5</v>
+      </c>
+      <c r="S267">
+        <v>2.4</v>
+      </c>
+      <c r="T267">
+        <v>1.25</v>
+      </c>
+      <c r="U267">
+        <v>3.75</v>
+      </c>
+      <c r="V267">
+        <v>2.2</v>
+      </c>
+      <c r="W267">
+        <v>1.62</v>
+      </c>
+      <c r="X267">
+        <v>5</v>
+      </c>
+      <c r="Y267">
+        <v>1.17</v>
+      </c>
+      <c r="Z267">
+        <v>3.5</v>
+      </c>
+      <c r="AA267">
+        <v>4.2</v>
+      </c>
+      <c r="AB267">
+        <v>1.85</v>
+      </c>
+      <c r="AC267">
+        <v>1.03</v>
+      </c>
+      <c r="AD267">
+        <v>11</v>
+      </c>
+      <c r="AE267">
+        <v>1.16</v>
+      </c>
+      <c r="AF267">
+        <v>5</v>
+      </c>
+      <c r="AG267">
+        <v>1.5</v>
+      </c>
+      <c r="AH267">
+        <v>2.5</v>
+      </c>
+      <c r="AI267">
+        <v>1.5</v>
+      </c>
+      <c r="AJ267">
+        <v>2.5</v>
+      </c>
+      <c r="AK267">
+        <v>1.8</v>
+      </c>
+      <c r="AL267">
+        <v>1.2</v>
+      </c>
+      <c r="AM267">
+        <v>1.35</v>
+      </c>
+      <c r="AN267">
+        <v>1.5</v>
+      </c>
+      <c r="AO267">
+        <v>2.15</v>
+      </c>
+      <c r="AP267">
+        <v>1.46</v>
+      </c>
+      <c r="AQ267">
+        <v>2.07</v>
+      </c>
+      <c r="AR267">
+        <v>1.73</v>
+      </c>
+      <c r="AS267">
+        <v>1.92</v>
+      </c>
+      <c r="AT267">
+        <v>3.65</v>
+      </c>
+      <c r="AU267">
+        <v>4</v>
+      </c>
+      <c r="AV267">
+        <v>7</v>
+      </c>
+      <c r="AW267">
+        <v>5</v>
+      </c>
+      <c r="AX267">
+        <v>9</v>
+      </c>
+      <c r="AY267">
+        <v>9</v>
+      </c>
+      <c r="AZ267">
+        <v>16</v>
+      </c>
+      <c r="BA267">
+        <v>1</v>
+      </c>
+      <c r="BB267">
+        <v>3</v>
+      </c>
+      <c r="BC267">
+        <v>4</v>
+      </c>
+      <c r="BD267">
+        <v>2.7</v>
+      </c>
+      <c r="BE267">
+        <v>7.4</v>
+      </c>
+      <c r="BF267">
+        <v>1.6</v>
+      </c>
+      <c r="BG267">
+        <v>1.2</v>
+      </c>
+      <c r="BH267">
+        <v>4</v>
+      </c>
+      <c r="BI267">
+        <v>1.27</v>
+      </c>
+      <c r="BJ267">
+        <v>3.35</v>
+      </c>
+      <c r="BK267">
+        <v>1.52</v>
+      </c>
+      <c r="BL267">
+        <v>2.32</v>
+      </c>
+      <c r="BM267">
+        <v>1.9</v>
+      </c>
+      <c r="BN267">
+        <v>1.78</v>
+      </c>
+      <c r="BO267">
+        <v>2.48</v>
+      </c>
+      <c r="BP267">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7465691</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45712.66666666666</v>
+      </c>
+      <c r="F268">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>79</v>
+      </c>
+      <c r="H268" t="s">
+        <v>86</v>
+      </c>
+      <c r="I268">
+        <v>1</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268">
+        <v>1</v>
+      </c>
+      <c r="M268">
+        <v>2</v>
+      </c>
+      <c r="N268">
+        <v>3</v>
+      </c>
+      <c r="O268" t="s">
+        <v>112</v>
+      </c>
+      <c r="P268" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q268">
+        <v>4</v>
+      </c>
+      <c r="R268">
+        <v>2.6</v>
+      </c>
+      <c r="S268">
+        <v>2.25</v>
+      </c>
+      <c r="T268">
+        <v>1.22</v>
+      </c>
+      <c r="U268">
+        <v>4</v>
+      </c>
+      <c r="V268">
+        <v>2</v>
+      </c>
+      <c r="W268">
+        <v>1.73</v>
+      </c>
+      <c r="X268">
+        <v>4.33</v>
+      </c>
+      <c r="Y268">
+        <v>1.2</v>
+      </c>
+      <c r="Z268">
+        <v>3.3</v>
+      </c>
+      <c r="AA268">
+        <v>5</v>
+      </c>
+      <c r="AB268">
+        <v>1.75</v>
+      </c>
+      <c r="AC268">
+        <v>1.01</v>
+      </c>
+      <c r="AD268">
+        <v>17</v>
+      </c>
+      <c r="AE268">
+        <v>1.12</v>
+      </c>
+      <c r="AF268">
+        <v>6</v>
+      </c>
+      <c r="AG268">
+        <v>1.36</v>
+      </c>
+      <c r="AH268">
+        <v>3.1</v>
+      </c>
+      <c r="AI268">
+        <v>1.4</v>
+      </c>
+      <c r="AJ268">
+        <v>2.75</v>
+      </c>
+      <c r="AK268">
+        <v>2.05</v>
+      </c>
+      <c r="AL268">
+        <v>1.16</v>
+      </c>
+      <c r="AM268">
+        <v>1.28</v>
+      </c>
+      <c r="AN268">
+        <v>0.67</v>
+      </c>
+      <c r="AO268">
+        <v>1.69</v>
+      </c>
+      <c r="AP268">
+        <v>0.62</v>
+      </c>
+      <c r="AQ268">
+        <v>1.79</v>
+      </c>
+      <c r="AR268">
+        <v>1.52</v>
+      </c>
+      <c r="AS268">
+        <v>1.26</v>
+      </c>
+      <c r="AT268">
+        <v>2.78</v>
+      </c>
+      <c r="AU268">
+        <v>4</v>
+      </c>
+      <c r="AV268">
+        <v>7</v>
+      </c>
+      <c r="AW268">
+        <v>9</v>
+      </c>
+      <c r="AX268">
+        <v>12</v>
+      </c>
+      <c r="AY268">
+        <v>13</v>
+      </c>
+      <c r="AZ268">
+        <v>19</v>
+      </c>
+      <c r="BA268">
+        <v>6</v>
+      </c>
+      <c r="BB268">
+        <v>9</v>
+      </c>
+      <c r="BC268">
+        <v>15</v>
+      </c>
+      <c r="BD268">
+        <v>2.72</v>
+      </c>
+      <c r="BE268">
+        <v>7.4</v>
+      </c>
+      <c r="BF268">
+        <v>1.6</v>
+      </c>
+      <c r="BG268">
+        <v>1.25</v>
+      </c>
+      <c r="BH268">
+        <v>3.45</v>
+      </c>
+      <c r="BI268">
+        <v>1.28</v>
+      </c>
+      <c r="BJ268">
+        <v>3.3</v>
+      </c>
+      <c r="BK268">
+        <v>1.52</v>
+      </c>
+      <c r="BL268">
+        <v>2.32</v>
+      </c>
+      <c r="BM268">
+        <v>1.92</v>
+      </c>
+      <c r="BN268">
+        <v>1.78</v>
+      </c>
+      <c r="BO268">
+        <v>2.55</v>
+      </c>
+      <c r="BP268">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="406">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -838,6 +838,15 @@
     <t>['55']</t>
   </si>
   <si>
+    <t>['19', '39', '67', '81', '87']</t>
+  </si>
+  <si>
+    <t>['29', '75', '89']</t>
+  </si>
+  <si>
+    <t>['9', '64', '74']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1215,6 +1224,15 @@
   <si>
     <t>['62', '90+3']</t>
   </si>
+  <si>
+    <t>['19', '42']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['30', '53']</t>
+  </si>
 </sst>
 </file>
 
@@ -1575,7 +1593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP268"/>
+  <dimension ref="A1:BP273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2037,7 +2055,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2243,7 +2261,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2449,7 +2467,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2655,7 +2673,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2861,7 +2879,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3067,7 +3085,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3148,7 +3166,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3273,7 +3291,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3685,7 +3703,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3763,10 +3781,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ11">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4097,7 +4115,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4590,7 +4608,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ15">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4715,7 +4733,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4793,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5205,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>1.46</v>
@@ -5411,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5539,7 +5557,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5617,10 +5635,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ20">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6238,7 +6256,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ23">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6569,7 +6587,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6775,7 +6793,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6981,7 +6999,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7062,7 +7080,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ27">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7393,7 +7411,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7805,7 +7823,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7883,7 +7901,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ31">
         <v>1.07</v>
@@ -8423,7 +8441,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8629,7 +8647,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8707,10 +8725,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ35">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -8916,7 +8934,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -9119,7 +9137,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>2.07</v>
@@ -9247,7 +9265,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9453,7 +9471,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9737,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ40">
         <v>0.46</v>
@@ -9865,7 +9883,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9946,7 +9964,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ41">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.77</v>
@@ -10561,10 +10579,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ44">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10689,7 +10707,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10895,7 +10913,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11307,7 +11325,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11719,7 +11737,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11800,7 +11818,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ50">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -11925,7 +11943,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12131,7 +12149,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12621,7 +12639,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54">
         <v>1.14</v>
@@ -12830,7 +12848,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -12955,7 +12973,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13367,7 +13385,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13445,7 +13463,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ58">
         <v>1.38</v>
@@ -13573,7 +13591,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13651,7 +13669,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ59">
         <v>1.46</v>
@@ -13857,7 +13875,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ60">
         <v>1.79</v>
@@ -13985,7 +14003,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14191,7 +14209,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14397,7 +14415,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14684,7 +14702,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ64">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -15015,7 +15033,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15093,7 +15111,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>1.43</v>
@@ -15427,7 +15445,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15508,7 +15526,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ68">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15633,7 +15651,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15839,7 +15857,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15920,7 +15938,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ70">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -16045,7 +16063,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16123,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
         <v>2.07</v>
@@ -16251,7 +16269,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16329,10 +16347,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16457,7 +16475,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16663,7 +16681,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16869,7 +16887,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17487,7 +17505,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17693,7 +17711,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17771,10 +17789,10 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ79">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18105,7 +18123,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18183,10 +18201,10 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ81">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18517,7 +18535,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18723,7 +18741,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19213,7 +19231,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ86">
         <v>1.07</v>
@@ -19341,7 +19359,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19831,7 +19849,7 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -19959,7 +19977,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20040,7 +20058,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ90">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR90">
         <v>1.95</v>
@@ -20246,7 +20264,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20371,7 +20389,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20452,7 +20470,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR92">
         <v>1.75</v>
@@ -20658,7 +20676,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -20783,7 +20801,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20864,7 +20882,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ94">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -20989,7 +21007,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21195,7 +21213,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21401,7 +21419,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21479,7 +21497,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ97">
         <v>1.79</v>
@@ -21813,7 +21831,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21894,7 +21912,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ99">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22225,7 +22243,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22431,7 +22449,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22843,7 +22861,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22921,7 +22939,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ104">
         <v>1.43</v>
@@ -23255,7 +23273,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23539,7 +23557,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ107">
         <v>1.43</v>
@@ -23951,7 +23969,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -24079,7 +24097,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24157,7 +24175,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>0.92</v>
@@ -24285,7 +24303,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24363,7 +24381,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ111">
         <v>1.38</v>
@@ -24491,7 +24509,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24572,7 +24590,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ112">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR112">
         <v>1.74</v>
@@ -24775,7 +24793,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ113">
         <v>0.62</v>
@@ -24981,7 +24999,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ114">
         <v>1.43</v>
@@ -25109,7 +25127,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25190,7 +25208,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ115">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25315,7 +25333,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25521,7 +25539,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25727,7 +25745,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25933,7 +25951,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26139,7 +26157,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26345,7 +26363,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26426,7 +26444,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ121">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26551,7 +26569,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26757,7 +26775,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26838,7 +26856,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ123">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -26963,7 +26981,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27169,7 +27187,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27581,7 +27599,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27787,7 +27805,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28199,7 +28217,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28277,7 +28295,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ130">
         <v>0.62</v>
@@ -28405,7 +28423,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28483,10 +28501,10 @@
         <v>2.4</v>
       </c>
       <c r="AP131">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ131">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28692,7 +28710,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ132">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR132">
         <v>1.8</v>
@@ -29307,7 +29325,7 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29435,7 +29453,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29516,7 +29534,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ136">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -30131,7 +30149,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ139">
         <v>0.62</v>
@@ -30543,10 +30561,10 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -30752,7 +30770,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ142">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -31083,7 +31101,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31289,7 +31307,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31367,7 +31385,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ145">
         <v>1.79</v>
@@ -31495,7 +31513,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31576,7 +31594,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ146">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31701,7 +31719,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31907,7 +31925,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -31985,7 +32003,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
         <v>1.14</v>
@@ -32319,7 +32337,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32525,7 +32543,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32937,7 +32955,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33143,7 +33161,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33221,7 +33239,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ154">
         <v>1.07</v>
@@ -33349,7 +33367,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33427,7 +33445,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
         <v>0.46</v>
@@ -33636,7 +33654,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ156">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR156">
         <v>1.76</v>
@@ -33839,10 +33857,10 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ157">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34379,7 +34397,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34457,7 +34475,7 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ160">
         <v>1.38</v>
@@ -34663,7 +34681,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ161">
         <v>1.43</v>
@@ -34791,7 +34809,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34872,7 +34890,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ162">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35078,7 +35096,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ163">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35615,7 +35633,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35902,7 +35920,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ167">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -36314,7 +36332,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ169">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -36439,7 +36457,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36645,7 +36663,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37057,7 +37075,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37341,7 +37359,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ174">
         <v>1.07</v>
@@ -37547,7 +37565,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ175">
         <v>1.07</v>
@@ -37881,7 +37899,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37959,7 +37977,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ177">
         <v>1.46</v>
@@ -38087,7 +38105,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38374,7 +38392,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ179">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR179">
         <v>1.58</v>
@@ -38499,7 +38517,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38577,7 +38595,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ180">
         <v>1.43</v>
@@ -38705,7 +38723,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38783,7 +38801,7 @@
         <v>1.11</v>
       </c>
       <c r="AP181">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ181">
         <v>1.14</v>
@@ -38992,7 +39010,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ182">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39323,7 +39341,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39404,7 +39422,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ184">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39529,7 +39547,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39610,7 +39628,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ185">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39735,7 +39753,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40353,7 +40371,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40434,7 +40452,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ189">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40971,7 +40989,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41049,10 +41067,10 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ192">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41177,7 +41195,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41255,7 +41273,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ193">
         <v>0.92</v>
@@ -41383,7 +41401,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41461,7 +41479,7 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ194">
         <v>1.07</v>
@@ -41589,7 +41607,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41667,7 +41685,7 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ195">
         <v>1.43</v>
@@ -41795,7 +41813,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42285,10 +42303,10 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ198">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR198">
         <v>1.99</v>
@@ -42413,7 +42431,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42825,7 +42843,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43443,7 +43461,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43855,7 +43873,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -43936,7 +43954,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ206">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -44061,7 +44079,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44142,7 +44160,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ207">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44267,7 +44285,7 @@
         <v>230</v>
       </c>
       <c r="P208" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q208">
         <v>2.2</v>
@@ -44345,7 +44363,7 @@
         <v>1.3</v>
       </c>
       <c r="AP208">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ208">
         <v>1.07</v>
@@ -44554,7 +44572,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ209">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR209">
         <v>1.86</v>
@@ -44679,7 +44697,7 @@
         <v>93</v>
       </c>
       <c r="P210" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q210">
         <v>4.2</v>
@@ -45169,7 +45187,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ212">
         <v>0.92</v>
@@ -45375,7 +45393,7 @@
         <v>1.55</v>
       </c>
       <c r="AP213">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ213">
         <v>1.43</v>
@@ -45709,7 +45727,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46121,7 +46139,7 @@
         <v>104</v>
       </c>
       <c r="P217" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q217">
         <v>4.5</v>
@@ -46199,10 +46217,10 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ217">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR217">
         <v>1.39</v>
@@ -46820,7 +46838,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ220">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR220">
         <v>1.66</v>
@@ -46945,7 +46963,7 @@
         <v>239</v>
       </c>
       <c r="P221" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q221">
         <v>3.6</v>
@@ -47229,7 +47247,7 @@
         <v>0.64</v>
       </c>
       <c r="AP222">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ222">
         <v>0.62</v>
@@ -47563,7 +47581,7 @@
         <v>93</v>
       </c>
       <c r="P224" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q224">
         <v>3.2</v>
@@ -47850,7 +47868,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ225">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR225">
         <v>1.68</v>
@@ -48387,7 +48405,7 @@
         <v>245</v>
       </c>
       <c r="P228" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q228">
         <v>2.88</v>
@@ -48465,10 +48483,10 @@
         <v>1.3</v>
       </c>
       <c r="AP228">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ228">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR228">
         <v>1.56</v>
@@ -49289,10 +49307,10 @@
         <v>1</v>
       </c>
       <c r="AP232">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ232">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR232">
         <v>1.8</v>
@@ -49417,7 +49435,7 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q233">
         <v>1.91</v>
@@ -49701,7 +49719,7 @@
         <v>1</v>
       </c>
       <c r="AP234">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ234">
         <v>1.07</v>
@@ -49829,7 +49847,7 @@
         <v>237</v>
       </c>
       <c r="P235" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50035,7 +50053,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50322,7 +50340,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ237">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR237">
         <v>1.48</v>
@@ -50447,7 +50465,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50734,7 +50752,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ239">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR239">
         <v>1.78</v>
@@ -50859,7 +50877,7 @@
         <v>255</v>
       </c>
       <c r="P240" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q240">
         <v>2.2</v>
@@ -51477,7 +51495,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51555,7 +51573,7 @@
         <v>1.18</v>
       </c>
       <c r="AP243">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ243">
         <v>1.46</v>
@@ -51683,7 +51701,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52301,7 +52319,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52507,7 +52525,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52585,7 +52603,7 @@
         <v>2.08</v>
       </c>
       <c r="AP248">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ248">
         <v>2.07</v>
@@ -52794,7 +52812,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ249">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR249">
         <v>1.74</v>
@@ -52919,7 +52937,7 @@
         <v>263</v>
       </c>
       <c r="P250" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q250">
         <v>2.75</v>
@@ -52997,7 +53015,7 @@
         <v>1.23</v>
       </c>
       <c r="AP250">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ250">
         <v>1.14</v>
@@ -53203,7 +53221,7 @@
         <v>0.42</v>
       </c>
       <c r="AP251">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ251">
         <v>0.46</v>
@@ -53824,7 +53842,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ254">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR254">
         <v>1.85</v>
@@ -53949,7 +53967,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54236,7 +54254,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ256">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR256">
         <v>1.77</v>
@@ -54361,7 +54379,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -54442,7 +54460,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ257">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR257">
         <v>1.84</v>
@@ -54567,7 +54585,7 @@
         <v>267</v>
       </c>
       <c r="P258" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q258">
         <v>3.1</v>
@@ -54773,7 +54791,7 @@
         <v>93</v>
       </c>
       <c r="P259" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q259">
         <v>3.55</v>
@@ -54854,7 +54872,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ259">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR259">
         <v>1.47</v>
@@ -55597,7 +55615,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55803,7 +55821,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56009,7 +56027,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56215,7 +56233,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56296,7 +56314,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ266">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR266">
         <v>1.52</v>
@@ -56421,7 +56439,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56627,7 +56645,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56705,7 +56723,7 @@
         <v>1.69</v>
       </c>
       <c r="AP268">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AQ268">
         <v>1.79</v>
@@ -56784,6 +56802,1036 @@
       </c>
       <c r="BP268">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7465656</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F269">
+        <v>24</v>
+      </c>
+      <c r="G269" t="s">
+        <v>84</v>
+      </c>
+      <c r="H269" t="s">
+        <v>89</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>2</v>
+      </c>
+      <c r="K269">
+        <v>2</v>
+      </c>
+      <c r="L269">
+        <v>1</v>
+      </c>
+      <c r="M269">
+        <v>2</v>
+      </c>
+      <c r="N269">
+        <v>3</v>
+      </c>
+      <c r="O269" t="s">
+        <v>187</v>
+      </c>
+      <c r="P269" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q269">
+        <v>3.25</v>
+      </c>
+      <c r="R269">
+        <v>2.4</v>
+      </c>
+      <c r="S269">
+        <v>2.75</v>
+      </c>
+      <c r="T269">
+        <v>1.29</v>
+      </c>
+      <c r="U269">
+        <v>3.5</v>
+      </c>
+      <c r="V269">
+        <v>2.25</v>
+      </c>
+      <c r="W269">
+        <v>1.57</v>
+      </c>
+      <c r="X269">
+        <v>5.5</v>
+      </c>
+      <c r="Y269">
+        <v>1.14</v>
+      </c>
+      <c r="Z269">
+        <v>3</v>
+      </c>
+      <c r="AA269">
+        <v>3.6</v>
+      </c>
+      <c r="AB269">
+        <v>2.25</v>
+      </c>
+      <c r="AC269">
+        <v>1.04</v>
+      </c>
+      <c r="AD269">
+        <v>10</v>
+      </c>
+      <c r="AE269">
+        <v>1.16</v>
+      </c>
+      <c r="AF269">
+        <v>5</v>
+      </c>
+      <c r="AG269">
+        <v>1.53</v>
+      </c>
+      <c r="AH269">
+        <v>2.4</v>
+      </c>
+      <c r="AI269">
+        <v>1.44</v>
+      </c>
+      <c r="AJ269">
+        <v>2.63</v>
+      </c>
+      <c r="AK269">
+        <v>1.68</v>
+      </c>
+      <c r="AL269">
+        <v>1.22</v>
+      </c>
+      <c r="AM269">
+        <v>1.38</v>
+      </c>
+      <c r="AN269">
+        <v>0.75</v>
+      </c>
+      <c r="AO269">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP269">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ269">
+        <v>0.86</v>
+      </c>
+      <c r="AR269">
+        <v>1.38</v>
+      </c>
+      <c r="AS269">
+        <v>1.54</v>
+      </c>
+      <c r="AT269">
+        <v>2.92</v>
+      </c>
+      <c r="AU269">
+        <v>8</v>
+      </c>
+      <c r="AV269">
+        <v>7</v>
+      </c>
+      <c r="AW269">
+        <v>3</v>
+      </c>
+      <c r="AX269">
+        <v>4</v>
+      </c>
+      <c r="AY269">
+        <v>11</v>
+      </c>
+      <c r="AZ269">
+        <v>11</v>
+      </c>
+      <c r="BA269">
+        <v>5</v>
+      </c>
+      <c r="BB269">
+        <v>10</v>
+      </c>
+      <c r="BC269">
+        <v>15</v>
+      </c>
+      <c r="BD269">
+        <v>2.05</v>
+      </c>
+      <c r="BE269">
+        <v>6.5</v>
+      </c>
+      <c r="BF269">
+        <v>1.95</v>
+      </c>
+      <c r="BG269">
+        <v>1.27</v>
+      </c>
+      <c r="BH269">
+        <v>3.3</v>
+      </c>
+      <c r="BI269">
+        <v>1.48</v>
+      </c>
+      <c r="BJ269">
+        <v>2.45</v>
+      </c>
+      <c r="BK269">
+        <v>1.77</v>
+      </c>
+      <c r="BL269">
+        <v>1.93</v>
+      </c>
+      <c r="BM269">
+        <v>2.2</v>
+      </c>
+      <c r="BN269">
+        <v>1.58</v>
+      </c>
+      <c r="BO269">
+        <v>2.8</v>
+      </c>
+      <c r="BP269">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7465696</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F270">
+        <v>28</v>
+      </c>
+      <c r="G270" t="s">
+        <v>87</v>
+      </c>
+      <c r="H270" t="s">
+        <v>80</v>
+      </c>
+      <c r="I270">
+        <v>2</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>2</v>
+      </c>
+      <c r="L270">
+        <v>5</v>
+      </c>
+      <c r="M270">
+        <v>0</v>
+      </c>
+      <c r="N270">
+        <v>5</v>
+      </c>
+      <c r="O270" t="s">
+        <v>274</v>
+      </c>
+      <c r="P270" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q270">
+        <v>1.91</v>
+      </c>
+      <c r="R270">
+        <v>2.5</v>
+      </c>
+      <c r="S270">
+        <v>6.5</v>
+      </c>
+      <c r="T270">
+        <v>1.3</v>
+      </c>
+      <c r="U270">
+        <v>3.4</v>
+      </c>
+      <c r="V270">
+        <v>2.5</v>
+      </c>
+      <c r="W270">
+        <v>1.5</v>
+      </c>
+      <c r="X270">
+        <v>6</v>
+      </c>
+      <c r="Y270">
+        <v>1.13</v>
+      </c>
+      <c r="Z270">
+        <v>1.38</v>
+      </c>
+      <c r="AA270">
+        <v>4.5</v>
+      </c>
+      <c r="AB270">
+        <v>8</v>
+      </c>
+      <c r="AC270">
+        <v>1.04</v>
+      </c>
+      <c r="AD270">
+        <v>10</v>
+      </c>
+      <c r="AE270">
+        <v>1.2</v>
+      </c>
+      <c r="AF270">
+        <v>4.33</v>
+      </c>
+      <c r="AG270">
+        <v>1.67</v>
+      </c>
+      <c r="AH270">
+        <v>2.15</v>
+      </c>
+      <c r="AI270">
+        <v>1.83</v>
+      </c>
+      <c r="AJ270">
+        <v>1.83</v>
+      </c>
+      <c r="AK270">
+        <v>1.1</v>
+      </c>
+      <c r="AL270">
+        <v>1.18</v>
+      </c>
+      <c r="AM270">
+        <v>2.8</v>
+      </c>
+      <c r="AN270">
+        <v>1.31</v>
+      </c>
+      <c r="AO270">
+        <v>1.33</v>
+      </c>
+      <c r="AP270">
+        <v>1.43</v>
+      </c>
+      <c r="AQ270">
+        <v>1.23</v>
+      </c>
+      <c r="AR270">
+        <v>1.77</v>
+      </c>
+      <c r="AS270">
+        <v>1.42</v>
+      </c>
+      <c r="AT270">
+        <v>3.19</v>
+      </c>
+      <c r="AU270">
+        <v>9</v>
+      </c>
+      <c r="AV270">
+        <v>0</v>
+      </c>
+      <c r="AW270">
+        <v>10</v>
+      </c>
+      <c r="AX270">
+        <v>8</v>
+      </c>
+      <c r="AY270">
+        <v>19</v>
+      </c>
+      <c r="AZ270">
+        <v>8</v>
+      </c>
+      <c r="BA270">
+        <v>9</v>
+      </c>
+      <c r="BB270">
+        <v>4</v>
+      </c>
+      <c r="BC270">
+        <v>13</v>
+      </c>
+      <c r="BD270">
+        <v>1.3</v>
+      </c>
+      <c r="BE270">
+        <v>7.5</v>
+      </c>
+      <c r="BF270">
+        <v>3.8</v>
+      </c>
+      <c r="BG270">
+        <v>1.3</v>
+      </c>
+      <c r="BH270">
+        <v>3.15</v>
+      </c>
+      <c r="BI270">
+        <v>1.5</v>
+      </c>
+      <c r="BJ270">
+        <v>2.33</v>
+      </c>
+      <c r="BK270">
+        <v>1.83</v>
+      </c>
+      <c r="BL270">
+        <v>1.85</v>
+      </c>
+      <c r="BM270">
+        <v>2.28</v>
+      </c>
+      <c r="BN270">
+        <v>1.55</v>
+      </c>
+      <c r="BO270">
+        <v>2.9</v>
+      </c>
+      <c r="BP270">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7465694</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F271">
+        <v>28</v>
+      </c>
+      <c r="G271" t="s">
+        <v>88</v>
+      </c>
+      <c r="H271" t="s">
+        <v>72</v>
+      </c>
+      <c r="I271">
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271">
+        <v>2</v>
+      </c>
+      <c r="L271">
+        <v>3</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>4</v>
+      </c>
+      <c r="O271" t="s">
+        <v>275</v>
+      </c>
+      <c r="P271" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q271">
+        <v>2.05</v>
+      </c>
+      <c r="R271">
+        <v>2.5</v>
+      </c>
+      <c r="S271">
+        <v>5</v>
+      </c>
+      <c r="T271">
+        <v>1.25</v>
+      </c>
+      <c r="U271">
+        <v>3.75</v>
+      </c>
+      <c r="V271">
+        <v>2.2</v>
+      </c>
+      <c r="W271">
+        <v>1.62</v>
+      </c>
+      <c r="X271">
+        <v>5</v>
+      </c>
+      <c r="Y271">
+        <v>1.17</v>
+      </c>
+      <c r="Z271">
+        <v>1.5</v>
+      </c>
+      <c r="AA271">
+        <v>4.2</v>
+      </c>
+      <c r="AB271">
+        <v>5.75</v>
+      </c>
+      <c r="AC271">
+        <v>1.04</v>
+      </c>
+      <c r="AD271">
+        <v>10</v>
+      </c>
+      <c r="AE271">
+        <v>1.15</v>
+      </c>
+      <c r="AF271">
+        <v>5.25</v>
+      </c>
+      <c r="AG271">
+        <v>1.5</v>
+      </c>
+      <c r="AH271">
+        <v>2.5</v>
+      </c>
+      <c r="AI271">
+        <v>1.57</v>
+      </c>
+      <c r="AJ271">
+        <v>2.25</v>
+      </c>
+      <c r="AK271">
+        <v>1.16</v>
+      </c>
+      <c r="AL271">
+        <v>1.19</v>
+      </c>
+      <c r="AM271">
+        <v>2.4</v>
+      </c>
+      <c r="AN271">
+        <v>2.31</v>
+      </c>
+      <c r="AO271">
+        <v>1.38</v>
+      </c>
+      <c r="AP271">
+        <v>2.36</v>
+      </c>
+      <c r="AQ271">
+        <v>1.29</v>
+      </c>
+      <c r="AR271">
+        <v>1.87</v>
+      </c>
+      <c r="AS271">
+        <v>1.36</v>
+      </c>
+      <c r="AT271">
+        <v>3.23</v>
+      </c>
+      <c r="AU271">
+        <v>9</v>
+      </c>
+      <c r="AV271">
+        <v>5</v>
+      </c>
+      <c r="AW271">
+        <v>4</v>
+      </c>
+      <c r="AX271">
+        <v>13</v>
+      </c>
+      <c r="AY271">
+        <v>13</v>
+      </c>
+      <c r="AZ271">
+        <v>18</v>
+      </c>
+      <c r="BA271">
+        <v>3</v>
+      </c>
+      <c r="BB271">
+        <v>7</v>
+      </c>
+      <c r="BC271">
+        <v>10</v>
+      </c>
+      <c r="BD271">
+        <v>1.4</v>
+      </c>
+      <c r="BE271">
+        <v>7.5</v>
+      </c>
+      <c r="BF271">
+        <v>3.3</v>
+      </c>
+      <c r="BG271">
+        <v>1.29</v>
+      </c>
+      <c r="BH271">
+        <v>3.2</v>
+      </c>
+      <c r="BI271">
+        <v>1.5</v>
+      </c>
+      <c r="BJ271">
+        <v>2.38</v>
+      </c>
+      <c r="BK271">
+        <v>1.81</v>
+      </c>
+      <c r="BL271">
+        <v>1.88</v>
+      </c>
+      <c r="BM271">
+        <v>2.23</v>
+      </c>
+      <c r="BN271">
+        <v>1.56</v>
+      </c>
+      <c r="BO271">
+        <v>2.85</v>
+      </c>
+      <c r="BP271">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7465693</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F272">
+        <v>28</v>
+      </c>
+      <c r="G272" t="s">
+        <v>86</v>
+      </c>
+      <c r="H272" t="s">
+        <v>71</v>
+      </c>
+      <c r="I272">
+        <v>1</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>1</v>
+      </c>
+      <c r="L272">
+        <v>3</v>
+      </c>
+      <c r="M272">
+        <v>0</v>
+      </c>
+      <c r="N272">
+        <v>3</v>
+      </c>
+      <c r="O272" t="s">
+        <v>276</v>
+      </c>
+      <c r="P272" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q272">
+        <v>2.88</v>
+      </c>
+      <c r="R272">
+        <v>2.38</v>
+      </c>
+      <c r="S272">
+        <v>3.25</v>
+      </c>
+      <c r="T272">
+        <v>1.29</v>
+      </c>
+      <c r="U272">
+        <v>3.5</v>
+      </c>
+      <c r="V272">
+        <v>2.38</v>
+      </c>
+      <c r="W272">
+        <v>1.53</v>
+      </c>
+      <c r="X272">
+        <v>5.5</v>
+      </c>
+      <c r="Y272">
+        <v>1.14</v>
+      </c>
+      <c r="Z272">
+        <v>2.35</v>
+      </c>
+      <c r="AA272">
+        <v>3.4</v>
+      </c>
+      <c r="AB272">
+        <v>2.9</v>
+      </c>
+      <c r="AC272">
+        <v>1.04</v>
+      </c>
+      <c r="AD272">
+        <v>10</v>
+      </c>
+      <c r="AE272">
+        <v>1.18</v>
+      </c>
+      <c r="AF272">
+        <v>4.75</v>
+      </c>
+      <c r="AG272">
+        <v>1.57</v>
+      </c>
+      <c r="AH272">
+        <v>2.35</v>
+      </c>
+      <c r="AI272">
+        <v>1.5</v>
+      </c>
+      <c r="AJ272">
+        <v>2.5</v>
+      </c>
+      <c r="AK272">
+        <v>1.43</v>
+      </c>
+      <c r="AL272">
+        <v>1.27</v>
+      </c>
+      <c r="AM272">
+        <v>1.57</v>
+      </c>
+      <c r="AN272">
+        <v>1.92</v>
+      </c>
+      <c r="AO272">
+        <v>1.92</v>
+      </c>
+      <c r="AP272">
+        <v>2</v>
+      </c>
+      <c r="AQ272">
+        <v>1.79</v>
+      </c>
+      <c r="AR272">
+        <v>1.69</v>
+      </c>
+      <c r="AS272">
+        <v>1.61</v>
+      </c>
+      <c r="AT272">
+        <v>3.3</v>
+      </c>
+      <c r="AU272">
+        <v>4</v>
+      </c>
+      <c r="AV272">
+        <v>0</v>
+      </c>
+      <c r="AW272">
+        <v>6</v>
+      </c>
+      <c r="AX272">
+        <v>8</v>
+      </c>
+      <c r="AY272">
+        <v>10</v>
+      </c>
+      <c r="AZ272">
+        <v>8</v>
+      </c>
+      <c r="BA272">
+        <v>3</v>
+      </c>
+      <c r="BB272">
+        <v>3</v>
+      </c>
+      <c r="BC272">
+        <v>6</v>
+      </c>
+      <c r="BD272">
+        <v>1.85</v>
+      </c>
+      <c r="BE272">
+        <v>6.75</v>
+      </c>
+      <c r="BF272">
+        <v>2.15</v>
+      </c>
+      <c r="BG272">
+        <v>1.27</v>
+      </c>
+      <c r="BH272">
+        <v>3.3</v>
+      </c>
+      <c r="BI272">
+        <v>1.48</v>
+      </c>
+      <c r="BJ272">
+        <v>2.45</v>
+      </c>
+      <c r="BK272">
+        <v>1.77</v>
+      </c>
+      <c r="BL272">
+        <v>1.93</v>
+      </c>
+      <c r="BM272">
+        <v>2.18</v>
+      </c>
+      <c r="BN272">
+        <v>1.58</v>
+      </c>
+      <c r="BO272">
+        <v>2.8</v>
+      </c>
+      <c r="BP272">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7465695</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45716.66666666666</v>
+      </c>
+      <c r="F273">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>79</v>
+      </c>
+      <c r="H273" t="s">
+        <v>77</v>
+      </c>
+      <c r="I273">
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273">
+        <v>2</v>
+      </c>
+      <c r="L273">
+        <v>1</v>
+      </c>
+      <c r="M273">
+        <v>2</v>
+      </c>
+      <c r="N273">
+        <v>3</v>
+      </c>
+      <c r="O273" t="s">
+        <v>142</v>
+      </c>
+      <c r="P273" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q273">
+        <v>4.5</v>
+      </c>
+      <c r="R273">
+        <v>2.75</v>
+      </c>
+      <c r="S273">
+        <v>2</v>
+      </c>
+      <c r="T273">
+        <v>1.2</v>
+      </c>
+      <c r="U273">
+        <v>4.33</v>
+      </c>
+      <c r="V273">
+        <v>1.91</v>
+      </c>
+      <c r="W273">
+        <v>1.8</v>
+      </c>
+      <c r="X273">
+        <v>4</v>
+      </c>
+      <c r="Y273">
+        <v>1.22</v>
+      </c>
+      <c r="Z273">
+        <v>5.75</v>
+      </c>
+      <c r="AA273">
+        <v>4.5</v>
+      </c>
+      <c r="AB273">
+        <v>1.5</v>
+      </c>
+      <c r="AC273">
+        <v>1.01</v>
+      </c>
+      <c r="AD273">
+        <v>17</v>
+      </c>
+      <c r="AE273">
+        <v>1.11</v>
+      </c>
+      <c r="AF273">
+        <v>6.25</v>
+      </c>
+      <c r="AG273">
+        <v>1.33</v>
+      </c>
+      <c r="AH273">
+        <v>3.4</v>
+      </c>
+      <c r="AI273">
+        <v>1.4</v>
+      </c>
+      <c r="AJ273">
+        <v>2.75</v>
+      </c>
+      <c r="AK273">
+        <v>2.35</v>
+      </c>
+      <c r="AL273">
+        <v>1.19</v>
+      </c>
+      <c r="AM273">
+        <v>1.17</v>
+      </c>
+      <c r="AN273">
+        <v>0.62</v>
+      </c>
+      <c r="AO273">
+        <v>0.92</v>
+      </c>
+      <c r="AP273">
+        <v>0.57</v>
+      </c>
+      <c r="AQ273">
+        <v>1.07</v>
+      </c>
+      <c r="AR273">
+        <v>1.51</v>
+      </c>
+      <c r="AS273">
+        <v>1.77</v>
+      </c>
+      <c r="AT273">
+        <v>3.28</v>
+      </c>
+      <c r="AU273">
+        <v>7</v>
+      </c>
+      <c r="AV273">
+        <v>8</v>
+      </c>
+      <c r="AW273">
+        <v>17</v>
+      </c>
+      <c r="AX273">
+        <v>12</v>
+      </c>
+      <c r="AY273">
+        <v>24</v>
+      </c>
+      <c r="AZ273">
+        <v>20</v>
+      </c>
+      <c r="BA273">
+        <v>5</v>
+      </c>
+      <c r="BB273">
+        <v>5</v>
+      </c>
+      <c r="BC273">
+        <v>10</v>
+      </c>
+      <c r="BD273">
+        <v>3.15</v>
+      </c>
+      <c r="BE273">
+        <v>7</v>
+      </c>
+      <c r="BF273">
+        <v>1.42</v>
+      </c>
+      <c r="BG273">
+        <v>1.26</v>
+      </c>
+      <c r="BH273">
+        <v>3.4</v>
+      </c>
+      <c r="BI273">
+        <v>1.46</v>
+      </c>
+      <c r="BJ273">
+        <v>2.5</v>
+      </c>
+      <c r="BK273">
+        <v>1.74</v>
+      </c>
+      <c r="BL273">
+        <v>1.97</v>
+      </c>
+      <c r="BM273">
+        <v>2.15</v>
+      </c>
+      <c r="BN273">
+        <v>1.61</v>
+      </c>
+      <c r="BO273">
+        <v>2.7</v>
+      </c>
+      <c r="BP273">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,9 @@
     <t>['29', '75', '89']</t>
   </si>
   <si>
+    <t>['32', '51']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1233,6 +1236,9 @@
   <si>
     <t>['45+1']</t>
   </si>
+  <si>
+    <t>['46']</t>
+  </si>
 </sst>
 </file>
 
@@ -1593,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP274"/>
+  <dimension ref="A1:BP275"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1930,7 +1936,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ2">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2055,7 +2061,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2261,7 +2267,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2467,7 +2473,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2673,7 +2679,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2879,7 +2885,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3085,7 +3091,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3163,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ8">
         <v>1.23</v>
@@ -3291,7 +3297,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3703,7 +3709,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4115,7 +4121,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4733,7 +4739,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5557,7 +5563,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6587,7 +6593,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6793,7 +6799,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6871,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ26">
         <v>1.79</v>
@@ -6999,7 +7005,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7411,7 +7417,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7823,7 +7829,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8441,7 +8447,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8647,7 +8653,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9265,7 +9271,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9343,7 +9349,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ38">
         <v>1.43</v>
@@ -9471,7 +9477,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9552,7 +9558,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9883,7 +9889,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10707,7 +10713,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10913,7 +10919,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11325,7 +11331,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11737,7 +11743,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11943,7 +11949,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12149,7 +12155,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12973,7 +12979,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13385,7 +13391,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13466,7 +13472,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ58">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13591,7 +13597,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -14003,7 +14009,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14209,7 +14215,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14415,7 +14421,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14905,7 +14911,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -15033,7 +15039,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15445,7 +15451,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15651,7 +15657,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15857,7 +15863,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16063,7 +16069,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16269,7 +16275,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16475,7 +16481,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16681,7 +16687,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16887,7 +16893,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16965,7 +16971,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ75">
         <v>0.62</v>
@@ -17380,7 +17386,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ77">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17505,7 +17511,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17711,7 +17717,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18123,7 +18129,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18535,7 +18541,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18741,7 +18747,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19359,7 +19365,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19977,7 +19983,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20389,7 +20395,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20801,7 +20807,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21007,7 +21013,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21213,7 +21219,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21419,7 +21425,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21831,7 +21837,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22243,7 +22249,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22449,7 +22455,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22733,7 +22739,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ103">
         <v>1.14</v>
@@ -22861,7 +22867,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23273,7 +23279,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24097,7 +24103,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24303,7 +24309,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24384,7 +24390,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ111">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24509,7 +24515,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24587,7 +24593,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -25127,7 +25133,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25333,7 +25339,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25539,7 +25545,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25745,7 +25751,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25826,7 +25832,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ118">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25951,7 +25957,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26157,7 +26163,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26363,7 +26369,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26569,7 +26575,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26775,7 +26781,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26981,7 +26987,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27187,7 +27193,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27599,7 +27605,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27805,7 +27811,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28217,7 +28223,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28423,7 +28429,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29122,7 +29128,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ134">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29453,7 +29459,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29943,7 +29949,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ138">
         <v>0.92</v>
@@ -31101,7 +31107,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31307,7 +31313,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31513,7 +31519,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31719,7 +31725,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31925,7 +31931,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32337,7 +32343,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32543,7 +32549,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32955,7 +32961,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33161,7 +33167,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33367,7 +33373,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34397,7 +34403,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34478,7 +34484,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ160">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34809,7 +34815,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34887,7 +34893,7 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ162">
         <v>1.79</v>
@@ -35633,7 +35639,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36457,7 +36463,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36663,7 +36669,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37075,7 +37081,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37774,7 +37780,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ176">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -37899,7 +37905,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38105,7 +38111,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38517,7 +38523,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38723,7 +38729,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39341,7 +39347,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39547,7 +39553,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39753,7 +39759,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40243,7 +40249,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ188">
         <v>0.57</v>
@@ -40371,7 +40377,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40989,7 +40995,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41195,7 +41201,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41401,7 +41407,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41607,7 +41613,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41813,7 +41819,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41894,7 +41900,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ196">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -42431,7 +42437,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42715,7 +42721,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ200">
         <v>0.46</v>
@@ -42843,7 +42849,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43461,7 +43467,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43873,7 +43879,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44079,7 +44085,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44491,7 +44497,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44903,7 +44909,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45393,7 +45399,7 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ213">
         <v>1.29</v>
@@ -45602,7 +45608,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ214">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR214">
         <v>1.73</v>
@@ -45727,7 +45733,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46345,7 +46351,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46551,7 +46557,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46757,7 +46763,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -48611,7 +48617,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49229,7 +49235,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49719,7 +49725,7 @@
         <v>1.67</v>
       </c>
       <c r="AP234">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ234">
         <v>1.43</v>
@@ -49847,7 +49853,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50053,7 +50059,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50465,7 +50471,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50958,7 +50964,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ240">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR240">
         <v>1.82</v>
@@ -51289,7 +51295,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51495,7 +51501,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51701,7 +51707,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52319,7 +52325,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52525,7 +52531,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -53633,7 +53639,7 @@
         <v>0.75</v>
       </c>
       <c r="AP253">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ253">
         <v>0.86</v>
@@ -53761,7 +53767,7 @@
         <v>264</v>
       </c>
       <c r="P254" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q254">
         <v>2.75</v>
@@ -53967,7 +53973,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54379,7 +54385,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -55078,7 +55084,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ260">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR260">
         <v>1.97</v>
@@ -55203,7 +55209,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55409,7 +55415,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55615,7 +55621,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55821,7 +55827,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56027,7 +56033,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56233,7 +56239,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56439,7 +56445,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56645,7 +56651,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -57057,7 +57063,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57263,7 +57269,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57675,7 +57681,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58038,6 +58044,212 @@
       </c>
       <c r="BP274">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7465697</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45718.34375</v>
+      </c>
+      <c r="F275">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>76</v>
+      </c>
+      <c r="H275" t="s">
+        <v>85</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>3</v>
+      </c>
+      <c r="O275" t="s">
+        <v>277</v>
+      </c>
+      <c r="P275" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q275">
+        <v>2.2</v>
+      </c>
+      <c r="R275">
+        <v>2.38</v>
+      </c>
+      <c r="S275">
+        <v>5</v>
+      </c>
+      <c r="T275">
+        <v>1.33</v>
+      </c>
+      <c r="U275">
+        <v>3.25</v>
+      </c>
+      <c r="V275">
+        <v>2.63</v>
+      </c>
+      <c r="W275">
+        <v>1.44</v>
+      </c>
+      <c r="X275">
+        <v>6.5</v>
+      </c>
+      <c r="Y275">
+        <v>1.11</v>
+      </c>
+      <c r="Z275">
+        <v>1.6</v>
+      </c>
+      <c r="AA275">
+        <v>3.75</v>
+      </c>
+      <c r="AB275">
+        <v>5.5</v>
+      </c>
+      <c r="AC275">
+        <v>1.02</v>
+      </c>
+      <c r="AD275">
+        <v>15</v>
+      </c>
+      <c r="AE275">
+        <v>1.22</v>
+      </c>
+      <c r="AF275">
+        <v>4.2</v>
+      </c>
+      <c r="AG275">
+        <v>1.7</v>
+      </c>
+      <c r="AH275">
+        <v>2.1</v>
+      </c>
+      <c r="AI275">
+        <v>1.73</v>
+      </c>
+      <c r="AJ275">
+        <v>2</v>
+      </c>
+      <c r="AK275">
+        <v>1.16</v>
+      </c>
+      <c r="AL275">
+        <v>1.18</v>
+      </c>
+      <c r="AM275">
+        <v>2.35</v>
+      </c>
+      <c r="AN275">
+        <v>2.14</v>
+      </c>
+      <c r="AO275">
+        <v>1.38</v>
+      </c>
+      <c r="AP275">
+        <v>2.2</v>
+      </c>
+      <c r="AQ275">
+        <v>1.29</v>
+      </c>
+      <c r="AR275">
+        <v>1.86</v>
+      </c>
+      <c r="AS275">
+        <v>1.22</v>
+      </c>
+      <c r="AT275">
+        <v>3.08</v>
+      </c>
+      <c r="AU275">
+        <v>7</v>
+      </c>
+      <c r="AV275">
+        <v>6</v>
+      </c>
+      <c r="AW275">
+        <v>5</v>
+      </c>
+      <c r="AX275">
+        <v>4</v>
+      </c>
+      <c r="AY275">
+        <v>12</v>
+      </c>
+      <c r="AZ275">
+        <v>10</v>
+      </c>
+      <c r="BA275">
+        <v>2</v>
+      </c>
+      <c r="BB275">
+        <v>6</v>
+      </c>
+      <c r="BC275">
+        <v>8</v>
+      </c>
+      <c r="BD275">
+        <v>1.47</v>
+      </c>
+      <c r="BE275">
+        <v>6.75</v>
+      </c>
+      <c r="BF275">
+        <v>3.05</v>
+      </c>
+      <c r="BG275">
+        <v>1.33</v>
+      </c>
+      <c r="BH275">
+        <v>2.95</v>
+      </c>
+      <c r="BI275">
+        <v>1.55</v>
+      </c>
+      <c r="BJ275">
+        <v>2.25</v>
+      </c>
+      <c r="BK275">
+        <v>1.91</v>
+      </c>
+      <c r="BL275">
+        <v>1.79</v>
+      </c>
+      <c r="BM275">
+        <v>2.4</v>
+      </c>
+      <c r="BN275">
+        <v>1.49</v>
+      </c>
+      <c r="BO275">
+        <v>3.1</v>
+      </c>
+      <c r="BP275">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="408">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -850,6 +850,9 @@
     <t>['32', '51']</t>
   </si>
   <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1202,9 +1205,6 @@
   </si>
   <si>
     <t>['8', '13']</t>
-  </si>
-  <si>
-    <t>['59']</t>
   </si>
   <si>
     <t>['24', '54', '62']</t>
@@ -1599,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP275"/>
+  <dimension ref="A1:BP276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2061,7 +2061,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2267,7 +2267,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2473,7 +2473,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -2679,7 +2679,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2885,7 +2885,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3091,7 +3091,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3297,7 +3297,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3584,7 +3584,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4121,7 +4121,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15">
         <v>1.07</v>
@@ -4739,7 +4739,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5563,7 +5563,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6593,7 +6593,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6799,7 +6799,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7005,7 +7005,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7417,7 +7417,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7498,7 +7498,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7829,7 +7829,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8447,7 +8447,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8653,7 +8653,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9271,7 +9271,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9477,7 +9477,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9889,7 +9889,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10713,7 +10713,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10919,7 +10919,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11331,7 +11331,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11743,7 +11743,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11949,7 +11949,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12027,7 +12027,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ51">
         <v>1.07</v>
@@ -12155,7 +12155,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12236,7 +12236,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12648,7 +12648,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -12851,7 +12851,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ55">
         <v>1.23</v>
@@ -12979,7 +12979,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13391,7 +13391,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13597,7 +13597,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -14009,7 +14009,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14215,7 +14215,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14421,7 +14421,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15039,7 +15039,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15451,7 +15451,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15657,7 +15657,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15863,7 +15863,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16069,7 +16069,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16275,7 +16275,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16481,7 +16481,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16687,7 +16687,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16765,7 +16765,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ74">
         <v>1.07</v>
@@ -16893,7 +16893,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17180,7 +17180,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ76">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17511,7 +17511,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17717,7 +17717,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18129,7 +18129,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18541,7 +18541,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18747,7 +18747,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19365,7 +19365,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19983,7 +19983,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20395,7 +20395,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20807,7 +20807,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21013,7 +21013,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21219,7 +21219,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21425,7 +21425,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21837,7 +21837,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22249,7 +22249,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22327,7 +22327,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ101">
         <v>0.57</v>
@@ -22455,7 +22455,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22742,7 +22742,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22867,7 +22867,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23279,7 +23279,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23360,7 +23360,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -24103,7 +24103,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24309,7 +24309,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24515,7 +24515,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25133,7 +25133,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25339,7 +25339,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25545,7 +25545,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25751,7 +25751,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25957,7 +25957,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26035,7 +26035,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ119">
         <v>2.07</v>
@@ -26163,7 +26163,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26369,7 +26369,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26575,7 +26575,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26781,7 +26781,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26987,7 +26987,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27193,7 +27193,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27605,7 +27605,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -27686,7 +27686,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ127">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27811,7 +27811,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28223,7 +28223,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28429,7 +28429,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29459,7 +29459,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29743,7 +29743,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ137">
         <v>1.43</v>
@@ -31107,7 +31107,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31313,7 +31313,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31519,7 +31519,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31725,7 +31725,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31931,7 +31931,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32012,7 +32012,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32343,7 +32343,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32549,7 +32549,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32961,7 +32961,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33167,7 +33167,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33373,7 +33373,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34403,7 +34403,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34815,7 +34815,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35099,7 +35099,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ163">
         <v>0.86</v>
@@ -35639,7 +35639,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36463,7 +36463,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36669,7 +36669,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37081,7 +37081,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37905,7 +37905,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38111,7 +38111,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38523,7 +38523,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38729,7 +38729,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38810,7 +38810,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ181">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -39347,7 +39347,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39553,7 +39553,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39759,7 +39759,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40043,7 +40043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP187">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ187">
         <v>1.79</v>
@@ -40377,7 +40377,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40995,7 +40995,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41201,7 +41201,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41407,7 +41407,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41613,7 +41613,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41819,7 +41819,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42437,7 +42437,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42849,7 +42849,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42930,7 +42930,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ201">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -43133,7 +43133,7 @@
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ202">
         <v>1.79</v>
@@ -43467,7 +43467,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43879,7 +43879,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44085,7 +44085,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44497,7 +44497,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44578,7 +44578,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ209">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR209">
         <v>1.37</v>
@@ -44909,7 +44909,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45733,7 +45733,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46351,7 +46351,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46557,7 +46557,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46763,7 +46763,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -48077,7 +48077,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ226">
         <v>1.46</v>
@@ -48617,7 +48617,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49235,7 +49235,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49853,7 +49853,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49931,7 +49931,7 @@
         <v>0.82</v>
       </c>
       <c r="AP235">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ235">
         <v>0.92</v>
@@ -50059,7 +50059,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50140,7 +50140,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ236">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR236">
         <v>1.7</v>
@@ -50471,7 +50471,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51295,7 +51295,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51501,7 +51501,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51707,7 +51707,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52325,7 +52325,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52531,7 +52531,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -53767,7 +53767,7 @@
         <v>264</v>
       </c>
       <c r="P254" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q254">
         <v>2.75</v>
@@ -53848,7 +53848,7 @@
         <v>2</v>
       </c>
       <c r="AQ254">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR254">
         <v>1.74</v>
@@ -53973,7 +53973,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54385,7 +54385,7 @@
         <v>173</v>
       </c>
       <c r="P257" t="s">
-        <v>396</v>
+        <v>278</v>
       </c>
       <c r="Q257">
         <v>1.8</v>
@@ -54463,7 +54463,7 @@
         <v>1.42</v>
       </c>
       <c r="AP257">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ257">
         <v>1.29</v>
@@ -56445,7 +56445,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -58250,6 +58250,212 @@
       </c>
       <c r="BP275">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7465698</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45718.53125</v>
+      </c>
+      <c r="F276">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>83</v>
+      </c>
+      <c r="H276" t="s">
+        <v>82</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276">
+        <v>1</v>
+      </c>
+      <c r="L276">
+        <v>1</v>
+      </c>
+      <c r="M276">
+        <v>1</v>
+      </c>
+      <c r="N276">
+        <v>2</v>
+      </c>
+      <c r="O276" t="s">
+        <v>278</v>
+      </c>
+      <c r="P276" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q276">
+        <v>2.1</v>
+      </c>
+      <c r="R276">
+        <v>2.4</v>
+      </c>
+      <c r="S276">
+        <v>4.75</v>
+      </c>
+      <c r="T276">
+        <v>1.29</v>
+      </c>
+      <c r="U276">
+        <v>3.5</v>
+      </c>
+      <c r="V276">
+        <v>2.38</v>
+      </c>
+      <c r="W276">
+        <v>1.53</v>
+      </c>
+      <c r="X276">
+        <v>5.5</v>
+      </c>
+      <c r="Y276">
+        <v>1.14</v>
+      </c>
+      <c r="Z276">
+        <v>1.6</v>
+      </c>
+      <c r="AA276">
+        <v>4.1</v>
+      </c>
+      <c r="AB276">
+        <v>5</v>
+      </c>
+      <c r="AC276">
+        <v>1.02</v>
+      </c>
+      <c r="AD276">
+        <v>19</v>
+      </c>
+      <c r="AE276">
+        <v>1.18</v>
+      </c>
+      <c r="AF276">
+        <v>4.75</v>
+      </c>
+      <c r="AG276">
+        <v>1.57</v>
+      </c>
+      <c r="AH276">
+        <v>2.35</v>
+      </c>
+      <c r="AI276">
+        <v>1.62</v>
+      </c>
+      <c r="AJ276">
+        <v>2.2</v>
+      </c>
+      <c r="AK276">
+        <v>1.18</v>
+      </c>
+      <c r="AL276">
+        <v>1.18</v>
+      </c>
+      <c r="AM276">
+        <v>2.3</v>
+      </c>
+      <c r="AN276">
+        <v>2.23</v>
+      </c>
+      <c r="AO276">
+        <v>1.14</v>
+      </c>
+      <c r="AP276">
+        <v>2.14</v>
+      </c>
+      <c r="AQ276">
+        <v>1.13</v>
+      </c>
+      <c r="AR276">
+        <v>1.89</v>
+      </c>
+      <c r="AS276">
+        <v>1.82</v>
+      </c>
+      <c r="AT276">
+        <v>3.71</v>
+      </c>
+      <c r="AU276">
+        <v>8</v>
+      </c>
+      <c r="AV276">
+        <v>5</v>
+      </c>
+      <c r="AW276">
+        <v>13</v>
+      </c>
+      <c r="AX276">
+        <v>6</v>
+      </c>
+      <c r="AY276">
+        <v>21</v>
+      </c>
+      <c r="AZ276">
+        <v>11</v>
+      </c>
+      <c r="BA276">
+        <v>14</v>
+      </c>
+      <c r="BB276">
+        <v>2</v>
+      </c>
+      <c r="BC276">
+        <v>16</v>
+      </c>
+      <c r="BD276">
+        <v>1.55</v>
+      </c>
+      <c r="BE276">
+        <v>6.75</v>
+      </c>
+      <c r="BF276">
+        <v>2.7</v>
+      </c>
+      <c r="BG276">
+        <v>1.32</v>
+      </c>
+      <c r="BH276">
+        <v>3.05</v>
+      </c>
+      <c r="BI276">
+        <v>1.54</v>
+      </c>
+      <c r="BJ276">
+        <v>2.28</v>
+      </c>
+      <c r="BK276">
+        <v>1.89</v>
+      </c>
+      <c r="BL276">
+        <v>1.8</v>
+      </c>
+      <c r="BM276">
+        <v>2.33</v>
+      </c>
+      <c r="BN276">
+        <v>1.5</v>
+      </c>
+      <c r="BO276">
+        <v>3.05</v>
+      </c>
+      <c r="BP276">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="410">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1239,6 +1239,12 @@
   <si>
     <t>['46']</t>
   </si>
+  <si>
+    <t>['68', '88']</t>
+  </si>
+  <si>
+    <t>['21', '40']</t>
+  </si>
 </sst>
 </file>
 
@@ -1599,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP276"/>
+  <dimension ref="A1:BP279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2966,7 +2972,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3581,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ10">
         <v>1.13</v>
@@ -4202,7 +4208,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4408,7 +4414,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ14">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4817,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -5847,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ21">
         <v>0.57</v>
@@ -7701,7 +7707,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ30">
         <v>1.79</v>
@@ -7910,7 +7916,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ31">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -8116,7 +8122,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ32">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8731,7 +8737,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ35">
         <v>1.79</v>
@@ -9555,7 +9561,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ39">
         <v>1.29</v>
@@ -9764,7 +9770,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ40">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -10176,7 +10182,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ42">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -11203,7 +11209,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ47">
         <v>0.92</v>
@@ -12030,7 +12036,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ51">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -13266,7 +13272,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13469,7 +13475,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58">
         <v>1.29</v>
@@ -14087,7 +14093,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61">
         <v>1.07</v>
@@ -14914,7 +14920,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ65">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15738,7 +15744,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15941,7 +15947,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ70">
         <v>1.07</v>
@@ -16147,7 +16153,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ71">
         <v>2.07</v>
@@ -16562,7 +16568,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ73">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -18001,7 +18007,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ80">
         <v>1.79</v>
@@ -19237,10 +19243,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ86">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19443,10 +19449,10 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ87">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -20885,7 +20891,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ94">
         <v>1.29</v>
@@ -21300,7 +21306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ96">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21709,7 +21715,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ98">
         <v>0.62</v>
@@ -23151,7 +23157,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105">
         <v>1.46</v>
@@ -23566,7 +23572,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -23772,7 +23778,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ108">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -23975,7 +23981,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -25008,7 +25014,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ114">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -26244,7 +26250,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ120">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26653,7 +26659,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ122">
         <v>2.07</v>
@@ -26859,7 +26865,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>1.23</v>
@@ -27480,7 +27486,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ126">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -28301,7 +28307,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ130">
         <v>0.57</v>
@@ -29746,7 +29752,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ137">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -30364,7 +30370,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ140">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -32009,7 +32015,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ148">
         <v>1.13</v>
@@ -32215,10 +32221,10 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32424,7 +32430,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ150">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32836,7 +32842,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ152">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -33039,7 +33045,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ153">
         <v>1.46</v>
@@ -33454,7 +33460,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -34687,7 +34693,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ161">
         <v>1.43</v>
@@ -36747,7 +36753,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ171">
         <v>0.57</v>
@@ -36956,7 +36962,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ172">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -37368,7 +37374,7 @@
         <v>2</v>
       </c>
       <c r="AQ174">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -38395,7 +38401,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ179">
         <v>1.07</v>
@@ -38601,10 +38607,10 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ180">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -39425,7 +39431,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ184">
         <v>1.79</v>
@@ -41073,7 +41079,7 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ192">
         <v>1.29</v>
@@ -41694,7 +41700,7 @@
         <v>2</v>
       </c>
       <c r="AQ195">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -42518,7 +42524,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ199">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42724,7 +42730,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ200">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42927,7 +42933,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ201">
         <v>1.13</v>
@@ -44163,7 +44169,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ207">
         <v>0.86</v>
@@ -44372,7 +44378,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ208">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR208">
         <v>1.58</v>
@@ -45814,7 +45820,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ215">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -46223,7 +46229,7 @@
         <v>1.18</v>
       </c>
       <c r="AP217">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ217">
         <v>1</v>
@@ -46429,7 +46435,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ218">
         <v>1.07</v>
@@ -47668,7 +47674,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ224">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR224">
         <v>1.74</v>
@@ -48904,7 +48910,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ230">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR230">
         <v>1.75</v>
@@ -49728,7 +49734,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ234">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR234">
         <v>1.81</v>
@@ -50755,7 +50761,7 @@
         <v>1.45</v>
       </c>
       <c r="AP239">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ239">
         <v>1.23</v>
@@ -51170,7 +51176,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ241">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR241">
         <v>1.34</v>
@@ -52403,7 +52409,7 @@
         <v>1.42</v>
       </c>
       <c r="AP247">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ247">
         <v>1.43</v>
@@ -53024,7 +53030,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ250">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AR250">
         <v>1.71</v>
@@ -53230,7 +53236,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ251">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR251">
         <v>1.74</v>
@@ -53436,7 +53442,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ252">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR252">
         <v>1.77</v>
@@ -56523,7 +56529,7 @@
         <v>2.15</v>
       </c>
       <c r="AP267">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ267">
         <v>2.07</v>
@@ -57347,7 +57353,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP271">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ271">
         <v>0.86</v>
@@ -58456,6 +58462,624 @@
       </c>
       <c r="BP276">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7465699</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F277">
+        <v>28</v>
+      </c>
+      <c r="G277" t="s">
+        <v>89</v>
+      </c>
+      <c r="H277" t="s">
+        <v>70</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>0</v>
+      </c>
+      <c r="L277">
+        <v>0</v>
+      </c>
+      <c r="M277">
+        <v>2</v>
+      </c>
+      <c r="N277">
+        <v>2</v>
+      </c>
+      <c r="O277" t="s">
+        <v>93</v>
+      </c>
+      <c r="P277" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q277">
+        <v>2.75</v>
+      </c>
+      <c r="R277">
+        <v>2.3</v>
+      </c>
+      <c r="S277">
+        <v>3.6</v>
+      </c>
+      <c r="T277">
+        <v>1.3</v>
+      </c>
+      <c r="U277">
+        <v>3.4</v>
+      </c>
+      <c r="V277">
+        <v>2.5</v>
+      </c>
+      <c r="W277">
+        <v>1.5</v>
+      </c>
+      <c r="X277">
+        <v>6</v>
+      </c>
+      <c r="Y277">
+        <v>1.13</v>
+      </c>
+      <c r="Z277">
+        <v>2.1</v>
+      </c>
+      <c r="AA277">
+        <v>3.6</v>
+      </c>
+      <c r="AB277">
+        <v>3.2</v>
+      </c>
+      <c r="AC277">
+        <v>1.04</v>
+      </c>
+      <c r="AD277">
+        <v>10</v>
+      </c>
+      <c r="AE277">
+        <v>1.2</v>
+      </c>
+      <c r="AF277">
+        <v>4.33</v>
+      </c>
+      <c r="AG277">
+        <v>1.65</v>
+      </c>
+      <c r="AH277">
+        <v>2.2</v>
+      </c>
+      <c r="AI277">
+        <v>1.53</v>
+      </c>
+      <c r="AJ277">
+        <v>2.38</v>
+      </c>
+      <c r="AK277">
+        <v>1.35</v>
+      </c>
+      <c r="AL277">
+        <v>1.22</v>
+      </c>
+      <c r="AM277">
+        <v>1.7</v>
+      </c>
+      <c r="AN277">
+        <v>1.46</v>
+      </c>
+      <c r="AO277">
+        <v>1.43</v>
+      </c>
+      <c r="AP277">
+        <v>1.36</v>
+      </c>
+      <c r="AQ277">
+        <v>1.53</v>
+      </c>
+      <c r="AR277">
+        <v>1.69</v>
+      </c>
+      <c r="AS277">
+        <v>1.24</v>
+      </c>
+      <c r="AT277">
+        <v>2.93</v>
+      </c>
+      <c r="AU277">
+        <v>5</v>
+      </c>
+      <c r="AV277">
+        <v>7</v>
+      </c>
+      <c r="AW277">
+        <v>4</v>
+      </c>
+      <c r="AX277">
+        <v>10</v>
+      </c>
+      <c r="AY277">
+        <v>9</v>
+      </c>
+      <c r="AZ277">
+        <v>17</v>
+      </c>
+      <c r="BA277">
+        <v>1</v>
+      </c>
+      <c r="BB277">
+        <v>13</v>
+      </c>
+      <c r="BC277">
+        <v>14</v>
+      </c>
+      <c r="BD277">
+        <v>1.73</v>
+      </c>
+      <c r="BE277">
+        <v>6.75</v>
+      </c>
+      <c r="BF277">
+        <v>2.32</v>
+      </c>
+      <c r="BG277">
+        <v>1.22</v>
+      </c>
+      <c r="BH277">
+        <v>3.7</v>
+      </c>
+      <c r="BI277">
+        <v>1.38</v>
+      </c>
+      <c r="BJ277">
+        <v>2.7</v>
+      </c>
+      <c r="BK277">
+        <v>1.64</v>
+      </c>
+      <c r="BL277">
+        <v>2.12</v>
+      </c>
+      <c r="BM277">
+        <v>1.98</v>
+      </c>
+      <c r="BN277">
+        <v>1.72</v>
+      </c>
+      <c r="BO277">
+        <v>2.48</v>
+      </c>
+      <c r="BP277">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7465700</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F278">
+        <v>28</v>
+      </c>
+      <c r="G278" t="s">
+        <v>78</v>
+      </c>
+      <c r="H278" t="s">
+        <v>81</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>2</v>
+      </c>
+      <c r="K278">
+        <v>2</v>
+      </c>
+      <c r="L278">
+        <v>1</v>
+      </c>
+      <c r="M278">
+        <v>2</v>
+      </c>
+      <c r="N278">
+        <v>3</v>
+      </c>
+      <c r="O278" t="s">
+        <v>156</v>
+      </c>
+      <c r="P278" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q278">
+        <v>3.5</v>
+      </c>
+      <c r="R278">
+        <v>2.38</v>
+      </c>
+      <c r="S278">
+        <v>2.75</v>
+      </c>
+      <c r="T278">
+        <v>1.3</v>
+      </c>
+      <c r="U278">
+        <v>3.4</v>
+      </c>
+      <c r="V278">
+        <v>2.38</v>
+      </c>
+      <c r="W278">
+        <v>1.53</v>
+      </c>
+      <c r="X278">
+        <v>5.5</v>
+      </c>
+      <c r="Y278">
+        <v>1.14</v>
+      </c>
+      <c r="Z278">
+        <v>3</v>
+      </c>
+      <c r="AA278">
+        <v>3.9</v>
+      </c>
+      <c r="AB278">
+        <v>2.1</v>
+      </c>
+      <c r="AC278">
+        <v>1.03</v>
+      </c>
+      <c r="AD278">
+        <v>11</v>
+      </c>
+      <c r="AE278">
+        <v>1.18</v>
+      </c>
+      <c r="AF278">
+        <v>4.75</v>
+      </c>
+      <c r="AG278">
+        <v>1.57</v>
+      </c>
+      <c r="AH278">
+        <v>2.35</v>
+      </c>
+      <c r="AI278">
+        <v>1.53</v>
+      </c>
+      <c r="AJ278">
+        <v>2.38</v>
+      </c>
+      <c r="AK278">
+        <v>1.7</v>
+      </c>
+      <c r="AL278">
+        <v>1.22</v>
+      </c>
+      <c r="AM278">
+        <v>1.36</v>
+      </c>
+      <c r="AN278">
+        <v>1.25</v>
+      </c>
+      <c r="AO278">
+        <v>1.07</v>
+      </c>
+      <c r="AP278">
+        <v>1.15</v>
+      </c>
+      <c r="AQ278">
+        <v>1.2</v>
+      </c>
+      <c r="AR278">
+        <v>1.75</v>
+      </c>
+      <c r="AS278">
+        <v>1.54</v>
+      </c>
+      <c r="AT278">
+        <v>3.29</v>
+      </c>
+      <c r="AU278">
+        <v>5</v>
+      </c>
+      <c r="AV278">
+        <v>6</v>
+      </c>
+      <c r="AW278">
+        <v>6</v>
+      </c>
+      <c r="AX278">
+        <v>8</v>
+      </c>
+      <c r="AY278">
+        <v>11</v>
+      </c>
+      <c r="AZ278">
+        <v>14</v>
+      </c>
+      <c r="BA278">
+        <v>4</v>
+      </c>
+      <c r="BB278">
+        <v>6</v>
+      </c>
+      <c r="BC278">
+        <v>10</v>
+      </c>
+      <c r="BD278">
+        <v>2.33</v>
+      </c>
+      <c r="BE278">
+        <v>6.5</v>
+      </c>
+      <c r="BF278">
+        <v>1.73</v>
+      </c>
+      <c r="BG278">
+        <v>1.22</v>
+      </c>
+      <c r="BH278">
+        <v>3.8</v>
+      </c>
+      <c r="BI278">
+        <v>1.38</v>
+      </c>
+      <c r="BJ278">
+        <v>2.8</v>
+      </c>
+      <c r="BK278">
+        <v>1.63</v>
+      </c>
+      <c r="BL278">
+        <v>2.12</v>
+      </c>
+      <c r="BM278">
+        <v>1.98</v>
+      </c>
+      <c r="BN278">
+        <v>1.73</v>
+      </c>
+      <c r="BO278">
+        <v>2.48</v>
+      </c>
+      <c r="BP278">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7465701</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45719.66666666666</v>
+      </c>
+      <c r="F279">
+        <v>28</v>
+      </c>
+      <c r="G279" t="s">
+        <v>84</v>
+      </c>
+      <c r="H279" t="s">
+        <v>74</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>2</v>
+      </c>
+      <c r="O279" t="s">
+        <v>103</v>
+      </c>
+      <c r="P279" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q279">
+        <v>3.1</v>
+      </c>
+      <c r="R279">
+        <v>2.2</v>
+      </c>
+      <c r="S279">
+        <v>3.4</v>
+      </c>
+      <c r="T279">
+        <v>1.4</v>
+      </c>
+      <c r="U279">
+        <v>2.75</v>
+      </c>
+      <c r="V279">
+        <v>2.75</v>
+      </c>
+      <c r="W279">
+        <v>1.4</v>
+      </c>
+      <c r="X279">
+        <v>8</v>
+      </c>
+      <c r="Y279">
+        <v>1.08</v>
+      </c>
+      <c r="Z279">
+        <v>2.5</v>
+      </c>
+      <c r="AA279">
+        <v>3.4</v>
+      </c>
+      <c r="AB279">
+        <v>2.7</v>
+      </c>
+      <c r="AC279">
+        <v>1.05</v>
+      </c>
+      <c r="AD279">
+        <v>9</v>
+      </c>
+      <c r="AE279">
+        <v>1.28</v>
+      </c>
+      <c r="AF279">
+        <v>3.5</v>
+      </c>
+      <c r="AG279">
+        <v>1.9</v>
+      </c>
+      <c r="AH279">
+        <v>1.9</v>
+      </c>
+      <c r="AI279">
+        <v>1.73</v>
+      </c>
+      <c r="AJ279">
+        <v>2</v>
+      </c>
+      <c r="AK279">
+        <v>1.42</v>
+      </c>
+      <c r="AL279">
+        <v>1.25</v>
+      </c>
+      <c r="AM279">
+        <v>1.53</v>
+      </c>
+      <c r="AN279">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO279">
+        <v>0.46</v>
+      </c>
+      <c r="AP279">
+        <v>0.71</v>
+      </c>
+      <c r="AQ279">
+        <v>0.5</v>
+      </c>
+      <c r="AR279">
+        <v>1.4</v>
+      </c>
+      <c r="AS279">
+        <v>1.04</v>
+      </c>
+      <c r="AT279">
+        <v>2.44</v>
+      </c>
+      <c r="AU279">
+        <v>7</v>
+      </c>
+      <c r="AV279">
+        <v>4</v>
+      </c>
+      <c r="AW279">
+        <v>12</v>
+      </c>
+      <c r="AX279">
+        <v>3</v>
+      </c>
+      <c r="AY279">
+        <v>19</v>
+      </c>
+      <c r="AZ279">
+        <v>7</v>
+      </c>
+      <c r="BA279">
+        <v>6</v>
+      </c>
+      <c r="BB279">
+        <v>3</v>
+      </c>
+      <c r="BC279">
+        <v>9</v>
+      </c>
+      <c r="BD279">
+        <v>1.89</v>
+      </c>
+      <c r="BE279">
+        <v>6.4</v>
+      </c>
+      <c r="BF279">
+        <v>2.12</v>
+      </c>
+      <c r="BG279">
+        <v>1.36</v>
+      </c>
+      <c r="BH279">
+        <v>2.85</v>
+      </c>
+      <c r="BI279">
+        <v>1.6</v>
+      </c>
+      <c r="BJ279">
+        <v>2.17</v>
+      </c>
+      <c r="BK279">
+        <v>1.98</v>
+      </c>
+      <c r="BL279">
+        <v>1.74</v>
+      </c>
+      <c r="BM279">
+        <v>2.48</v>
+      </c>
+      <c r="BN279">
+        <v>1.47</v>
+      </c>
+      <c r="BO279">
+        <v>3.25</v>
+      </c>
+      <c r="BP279">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="419">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -853,13 +853,31 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['7', '39', '44', '45+2', '54']</t>
+  </si>
+  <si>
+    <t>['48', '60']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['10', '14', '23', '78']</t>
+  </si>
+  <si>
+    <t>['37', '69', '73']</t>
+  </si>
+  <si>
+    <t>['41', '83']</t>
+  </si>
+  <si>
+    <t>['27', '68', '77', '80', '85']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
     <t>['8']</t>
-  </si>
-  <si>
-    <t>['70']</t>
   </si>
   <si>
     <t>['7']</t>
@@ -938,9 +956,6 @@
   </si>
   <si>
     <t>['12', '29', '51']</t>
-  </si>
-  <si>
-    <t>['48', '60']</t>
   </si>
   <si>
     <t>['55', '58']</t>
@@ -1244,6 +1259,18 @@
   </si>
   <si>
     <t>['21', '40']</t>
+  </si>
+  <si>
+    <t>['3', '82']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['8', '32', '80']</t>
+  </si>
+  <si>
+    <t>['6', '32']</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP279"/>
+  <dimension ref="A1:BP289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1939,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
         <v>1.29</v>
@@ -2067,7 +2094,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2145,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ3">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2273,7 +2300,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2351,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2560,7 +2587,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ5">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2685,7 +2712,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2763,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2891,7 +2918,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3097,7 +3124,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3303,7 +3330,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3381,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3587,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
         <v>1.13</v>
@@ -3715,7 +3742,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3796,7 +3823,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ11">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3999,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ12">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4127,7 +4154,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4205,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ13">
         <v>1.53</v>
@@ -4411,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ14">
         <v>0.5</v>
@@ -4745,7 +4772,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4826,7 +4853,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5029,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
         <v>1.07</v>
@@ -5238,7 +5265,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5569,7 +5596,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5856,7 +5883,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ21">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6059,10 +6086,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6265,7 +6292,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23">
         <v>1.29</v>
@@ -6471,10 +6498,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR24">
         <v>2.49</v>
@@ -6599,7 +6626,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6677,10 +6704,10 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ25">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6805,7 +6832,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6886,7 +6913,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ26">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR26">
         <v>1.18</v>
@@ -7011,7 +7038,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7089,10 +7116,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ27">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7298,7 +7325,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ28">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7423,7 +7450,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7501,7 +7528,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ29">
         <v>1.13</v>
@@ -7707,10 +7734,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -7835,7 +7862,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8325,7 +8352,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ33">
         <v>1.07</v>
@@ -8453,7 +8480,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8534,7 +8561,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR34">
         <v>1.12</v>
@@ -8659,7 +8686,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8943,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ36">
         <v>1.23</v>
@@ -9152,7 +9179,7 @@
         <v>2</v>
       </c>
       <c r="AQ37">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9277,7 +9304,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9358,7 +9385,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ38">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9483,7 +9510,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9895,7 +9922,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -9973,7 +10000,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -10179,7 +10206,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ42">
         <v>1.53</v>
@@ -10385,10 +10412,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ43">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR43">
         <v>1.9</v>
@@ -10594,7 +10621,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ44">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10719,7 +10746,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10797,10 +10824,10 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ45">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -10925,7 +10952,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11003,10 +11030,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR46">
         <v>1.3</v>
@@ -11209,10 +11236,10 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11337,7 +11364,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11418,7 +11445,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ48">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -11621,10 +11648,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11749,7 +11776,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11827,7 +11854,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ50">
         <v>1.29</v>
@@ -11955,7 +11982,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12161,7 +12188,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12239,7 +12266,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ52">
         <v>1.13</v>
@@ -12445,10 +12472,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -12985,7 +13012,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13063,10 +13090,10 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ56">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13269,7 +13296,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>0.5</v>
@@ -13397,7 +13424,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13603,7 +13630,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -13684,7 +13711,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ59">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -13890,7 +13917,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ60">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -14015,7 +14042,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14221,7 +14248,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14299,10 +14326,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ62">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR62">
         <v>1.68</v>
@@ -14427,7 +14454,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14505,10 +14532,10 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -14711,7 +14738,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ64">
         <v>1.79</v>
@@ -15045,7 +15072,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15126,7 +15153,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15329,10 +15356,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ67">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR67">
         <v>1.6</v>
@@ -15457,7 +15484,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15538,7 +15565,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ68">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15663,7 +15690,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15741,7 +15768,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69">
         <v>1.53</v>
@@ -15869,7 +15896,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -15947,7 +15974,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ70">
         <v>1.07</v>
@@ -16075,7 +16102,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16156,7 +16183,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ71">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16281,7 +16308,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16487,7 +16514,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16693,7 +16720,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16899,7 +16926,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -16980,7 +17007,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ75">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17183,7 +17210,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ76">
         <v>1.13</v>
@@ -17389,7 +17416,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ77">
         <v>1.29</v>
@@ -17517,7 +17544,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17595,10 +17622,10 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ78">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17723,7 +17750,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18010,7 +18037,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ80">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -18135,7 +18162,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18419,10 +18446,10 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ82">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18547,7 +18574,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18628,7 +18655,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ83">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18753,7 +18780,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18831,10 +18858,10 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -19037,10 +19064,10 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19371,7 +19398,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19449,7 +19476,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ87">
         <v>1.53</v>
@@ -19655,10 +19682,10 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ88">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR88">
         <v>1.89</v>
@@ -19864,7 +19891,7 @@
         <v>2</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR89">
         <v>1.66</v>
@@ -19989,7 +20016,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20067,7 +20094,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90">
         <v>1.07</v>
@@ -20273,10 +20300,10 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ91">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20401,7 +20428,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20479,7 +20506,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ92">
         <v>1.07</v>
@@ -20813,7 +20840,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20891,7 +20918,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ94">
         <v>1.29</v>
@@ -21019,7 +21046,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21097,10 +21124,10 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ95">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21225,7 +21252,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21303,7 +21330,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ96">
         <v>1.2</v>
@@ -21431,7 +21458,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21512,7 +21539,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ97">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -21718,7 +21745,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ98">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21843,7 +21870,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21921,7 +21948,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ99">
         <v>1.79</v>
@@ -22127,10 +22154,10 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22255,7 +22282,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22336,7 +22363,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ101">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR101">
         <v>1.83</v>
@@ -22461,7 +22488,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22539,10 +22566,10 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR102">
         <v>1.75</v>
@@ -22873,7 +22900,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22954,7 +22981,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ104">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23160,7 +23187,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -23285,7 +23312,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23363,7 +23390,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106">
         <v>1.13</v>
@@ -23775,7 +23802,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ108">
         <v>0.5</v>
@@ -24109,7 +24136,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24190,7 +24217,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24315,7 +24342,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24521,7 +24548,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24808,7 +24835,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -25139,7 +25166,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25217,10 +25244,10 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ115">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25345,7 +25372,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25423,7 +25450,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ116">
         <v>1.07</v>
@@ -25551,7 +25578,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25632,7 +25659,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ117">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25757,7 +25784,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25835,7 +25862,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ118">
         <v>1.29</v>
@@ -25963,7 +25990,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26044,7 +26071,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ119">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -26169,7 +26196,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26247,7 +26274,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ120">
         <v>1.2</v>
@@ -26375,7 +26402,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26581,7 +26608,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26659,10 +26686,10 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26787,7 +26814,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26993,7 +27020,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27071,10 +27098,10 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ124">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -27199,7 +27226,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27277,10 +27304,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ125">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27689,7 +27716,7 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ127">
         <v>1.13</v>
@@ -27817,7 +27844,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27895,10 +27922,10 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -28101,10 +28128,10 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ129">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28229,7 +28256,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28310,7 +28337,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ130">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28435,7 +28462,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28925,7 +28952,7 @@
         <v>1.17</v>
       </c>
       <c r="AP133">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ133">
         <v>1.07</v>
@@ -29131,7 +29158,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ134">
         <v>1.29</v>
@@ -29340,7 +29367,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.75</v>
@@ -29465,7 +29492,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29543,10 +29570,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ136">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -29958,7 +29985,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ138">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -30164,7 +30191,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ139">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30367,7 +30394,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ140">
         <v>1.2</v>
@@ -30779,7 +30806,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ142">
         <v>1.23</v>
@@ -30985,10 +31012,10 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ143">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR143">
         <v>1.29</v>
@@ -31113,7 +31140,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31194,7 +31221,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ144">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -31319,7 +31346,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31400,7 +31427,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ145">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR145">
         <v>1.6</v>
@@ -31525,7 +31552,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31603,7 +31630,7 @@
         <v>2.5</v>
       </c>
       <c r="AP146">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ146">
         <v>1.79</v>
@@ -31731,7 +31758,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31812,7 +31839,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ147">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -31937,7 +31964,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32349,7 +32376,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32427,7 +32454,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ150">
         <v>1.53</v>
@@ -32555,7 +32582,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32633,10 +32660,10 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ151">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -32839,7 +32866,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
         <v>0.5</v>
@@ -32967,7 +32994,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33045,10 +33072,10 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ153">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33173,7 +33200,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33379,7 +33406,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33663,7 +33690,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ156">
         <v>1.07</v>
@@ -33872,7 +33899,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ157">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34075,10 +34102,10 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ158">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34281,10 +34308,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ159">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34409,7 +34436,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34696,7 +34723,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ161">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34821,7 +34848,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35108,7 +35135,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ163">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35311,10 +35338,10 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ164">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35517,10 +35544,10 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ165">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR165">
         <v>1.91</v>
@@ -35645,7 +35672,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35723,10 +35750,10 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ166">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -36135,10 +36162,10 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ168">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -36341,7 +36368,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ169">
         <v>1.23</v>
@@ -36469,7 +36496,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36547,10 +36574,10 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ170">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -36675,7 +36702,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36753,10 +36780,10 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ171">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -36959,7 +36986,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ172">
         <v>0.5</v>
@@ -37087,7 +37114,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37168,7 +37195,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ173">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37783,7 +37810,7 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ176">
         <v>1.29</v>
@@ -37911,7 +37938,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -37992,7 +38019,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ177">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -38117,7 +38144,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38195,10 +38222,10 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ178">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38529,7 +38556,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38735,7 +38762,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39019,7 +39046,7 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ182">
         <v>1.29</v>
@@ -39225,10 +39252,10 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ183">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -39353,7 +39380,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39431,7 +39458,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ184">
         <v>1.79</v>
@@ -39559,7 +39586,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39637,7 +39664,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ185">
         <v>1.23</v>
@@ -39765,7 +39792,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39843,10 +39870,10 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ186">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40052,7 +40079,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ187">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR187">
         <v>1.79</v>
@@ -40258,7 +40285,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ188">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -40383,7 +40410,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40461,10 +40488,10 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ189">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40667,10 +40694,10 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR190">
         <v>1.73</v>
@@ -40876,7 +40903,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ191">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -41001,7 +41028,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41207,7 +41234,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41288,7 +41315,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ193">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41413,7 +41440,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41619,7 +41646,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41825,7 +41852,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41903,7 +41930,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ196">
         <v>1.29</v>
@@ -42109,10 +42136,10 @@
         <v>1.6</v>
       </c>
       <c r="AP197">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ197">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42443,7 +42470,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42855,7 +42882,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43142,7 +43169,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ202">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -43345,10 +43372,10 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ203">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -43473,7 +43500,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43551,10 +43578,10 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ204">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR204">
         <v>1.4</v>
@@ -43757,10 +43784,10 @@
         <v>1.3</v>
       </c>
       <c r="AP205">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR205">
         <v>1.65</v>
@@ -43885,7 +43912,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44091,7 +44118,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44169,10 +44196,10 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ207">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44375,7 +44402,7 @@
         <v>1.09</v>
       </c>
       <c r="AP208">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ208">
         <v>1.2</v>
@@ -44503,7 +44530,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44581,7 +44608,7 @@
         <v>1.18</v>
       </c>
       <c r="AP209">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ209">
         <v>1.13</v>
@@ -44790,7 +44817,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ210">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR210">
         <v>1.76</v>
@@ -44915,7 +44942,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45202,7 +45229,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ212">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR212">
         <v>1.95</v>
@@ -45739,7 +45766,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45817,7 +45844,7 @@
         <v>1.55</v>
       </c>
       <c r="AP215">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ215">
         <v>1.53</v>
@@ -46023,10 +46050,10 @@
         <v>2.2</v>
       </c>
       <c r="AP216">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ216">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR216">
         <v>1.9</v>
@@ -46232,7 +46259,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ217">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46357,7 +46384,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46563,7 +46590,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46641,10 +46668,10 @@
         <v>2.27</v>
       </c>
       <c r="AP219">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ219">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR219">
         <v>1.34</v>
@@ -46769,7 +46796,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46850,7 +46877,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ220">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -47053,10 +47080,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP221">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ221">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR221">
         <v>1.93</v>
@@ -47262,7 +47289,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ222">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR222">
         <v>1.91</v>
@@ -47465,7 +47492,7 @@
         <v>2.11</v>
       </c>
       <c r="AP223">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ223">
         <v>1.79</v>
@@ -47671,7 +47698,7 @@
         <v>0.5</v>
       </c>
       <c r="AP224">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224">
         <v>0.5</v>
@@ -47877,10 +47904,10 @@
         <v>0.82</v>
       </c>
       <c r="AP225">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ225">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR225">
         <v>1.68</v>
@@ -48086,7 +48113,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ226">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48289,7 +48316,7 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ227">
         <v>1.07</v>
@@ -48495,10 +48522,10 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ228">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR228">
         <v>1.74</v>
@@ -48623,7 +48650,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49241,7 +49268,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49319,10 +49346,10 @@
         <v>1.08</v>
       </c>
       <c r="AP232">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ232">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR232">
         <v>1.63</v>
@@ -49525,10 +49552,10 @@
         <v>1.73</v>
       </c>
       <c r="AP233">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ233">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR233">
         <v>1.77</v>
@@ -49859,7 +49886,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49940,7 +49967,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ235">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR235">
         <v>1.73</v>
@@ -50065,7 +50092,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50349,7 +50376,7 @@
         <v>1.45</v>
       </c>
       <c r="AP237">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ237">
         <v>1.29</v>
@@ -50477,7 +50504,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50555,10 +50582,10 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ238">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR238">
         <v>1.84</v>
@@ -50761,7 +50788,7 @@
         <v>1.45</v>
       </c>
       <c r="AP239">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ239">
         <v>1.23</v>
@@ -50967,7 +50994,7 @@
         <v>1.55</v>
       </c>
       <c r="AP240">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ240">
         <v>1.29</v>
@@ -51173,7 +51200,7 @@
         <v>0.45</v>
       </c>
       <c r="AP241">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ241">
         <v>0.5</v>
@@ -51301,7 +51328,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51379,7 +51406,7 @@
         <v>1.17</v>
       </c>
       <c r="AP242">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ242">
         <v>1.07</v>
@@ -51507,7 +51534,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51588,7 +51615,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ243">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR243">
         <v>1.91</v>
@@ -51713,7 +51740,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51791,10 +51818,10 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ244">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR244">
         <v>1.44</v>
@@ -51997,10 +52024,10 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ245">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR245">
         <v>1.55</v>
@@ -52203,10 +52230,10 @@
         <v>0.45</v>
       </c>
       <c r="AP246">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ246">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR246">
         <v>1.7</v>
@@ -52331,7 +52358,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52412,7 +52439,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ247">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR247">
         <v>1.71</v>
@@ -52537,7 +52564,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52618,7 +52645,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ248">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR248">
         <v>1.53</v>
@@ -53439,7 +53466,7 @@
         <v>0.92</v>
       </c>
       <c r="AP252">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ252">
         <v>1.2</v>
@@ -53648,7 +53675,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ253">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR253">
         <v>1.85</v>
@@ -53979,7 +54006,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54057,10 +54084,10 @@
         <v>1.58</v>
       </c>
       <c r="AP255">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ255">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR255">
         <v>1.7</v>
@@ -54675,7 +54702,7 @@
         <v>1.15</v>
       </c>
       <c r="AP258">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AQ258">
         <v>1.07</v>
@@ -54881,10 +54908,10 @@
         <v>1</v>
       </c>
       <c r="AP259">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ259">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR259">
         <v>1.5</v>
@@ -55087,7 +55114,7 @@
         <v>1.42</v>
       </c>
       <c r="AP260">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ260">
         <v>1.29</v>
@@ -55215,7 +55242,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55293,10 +55320,10 @@
         <v>1.31</v>
       </c>
       <c r="AP261">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ261">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR261">
         <v>1.76</v>
@@ -55421,7 +55448,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55499,7 +55526,7 @@
         <v>1.73</v>
       </c>
       <c r="AP262">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ262">
         <v>1.79</v>
@@ -55627,7 +55654,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55705,10 +55732,10 @@
         <v>1.69</v>
       </c>
       <c r="AP263">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AQ263">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR263">
         <v>1.63</v>
@@ -55833,7 +55860,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -55911,10 +55938,10 @@
         <v>0.42</v>
       </c>
       <c r="AP264">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ264">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR264">
         <v>1.35</v>
@@ -56039,7 +56066,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56120,7 +56147,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ265">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR265">
         <v>1.71</v>
@@ -56245,7 +56272,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56323,7 +56350,7 @@
         <v>1.83</v>
       </c>
       <c r="AP266">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ266">
         <v>1.79</v>
@@ -56451,7 +56478,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56532,7 +56559,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ267">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AR267">
         <v>1.73</v>
@@ -56657,7 +56684,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56738,7 +56765,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ268">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR268">
         <v>1.52</v>
@@ -57069,7 +57096,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57275,7 +57302,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57356,7 +57383,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ271">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR271">
         <v>1.38</v>
@@ -57687,7 +57714,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -57974,7 +58001,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ274">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR274">
         <v>1.73</v>
@@ -58099,7 +58126,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58305,7 +58332,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58511,7 +58538,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58717,7 +58744,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58795,7 +58822,7 @@
         <v>1.07</v>
       </c>
       <c r="AP278">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AQ278">
         <v>1.2</v>
@@ -58923,7 +58950,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59080,6 +59107,2066 @@
       </c>
       <c r="BP279">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7465711</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F280">
+        <v>29</v>
+      </c>
+      <c r="G280" t="s">
+        <v>81</v>
+      </c>
+      <c r="H280" t="s">
+        <v>86</v>
+      </c>
+      <c r="I280">
+        <v>4</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>4</v>
+      </c>
+      <c r="L280">
+        <v>5</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>5</v>
+      </c>
+      <c r="O280" t="s">
+        <v>279</v>
+      </c>
+      <c r="P280" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q280">
+        <v>2.42</v>
+      </c>
+      <c r="R280">
+        <v>2.53</v>
+      </c>
+      <c r="S280">
+        <v>3.95</v>
+      </c>
+      <c r="T280">
+        <v>1.29</v>
+      </c>
+      <c r="U280">
+        <v>3.5</v>
+      </c>
+      <c r="V280">
+        <v>2.25</v>
+      </c>
+      <c r="W280">
+        <v>1.61</v>
+      </c>
+      <c r="X280">
+        <v>5.5</v>
+      </c>
+      <c r="Y280">
+        <v>1.14</v>
+      </c>
+      <c r="Z280">
+        <v>1.94</v>
+      </c>
+      <c r="AA280">
+        <v>3.85</v>
+      </c>
+      <c r="AB280">
+        <v>3.54</v>
+      </c>
+      <c r="AC280">
+        <v>1.01</v>
+      </c>
+      <c r="AD280">
+        <v>15</v>
+      </c>
+      <c r="AE280">
+        <v>1.18</v>
+      </c>
+      <c r="AF280">
+        <v>4.75</v>
+      </c>
+      <c r="AG280">
+        <v>1.53</v>
+      </c>
+      <c r="AH280">
+        <v>2.4</v>
+      </c>
+      <c r="AI280">
+        <v>1.5</v>
+      </c>
+      <c r="AJ280">
+        <v>2.5</v>
+      </c>
+      <c r="AK280">
+        <v>1.29</v>
+      </c>
+      <c r="AL280">
+        <v>1.25</v>
+      </c>
+      <c r="AM280">
+        <v>1.83</v>
+      </c>
+      <c r="AN280">
+        <v>1.77</v>
+      </c>
+      <c r="AO280">
+        <v>1.79</v>
+      </c>
+      <c r="AP280">
+        <v>1.86</v>
+      </c>
+      <c r="AQ280">
+        <v>1.67</v>
+      </c>
+      <c r="AR280">
+        <v>1.78</v>
+      </c>
+      <c r="AS280">
+        <v>1.32</v>
+      </c>
+      <c r="AT280">
+        <v>3.1</v>
+      </c>
+      <c r="AU280">
+        <v>7</v>
+      </c>
+      <c r="AV280">
+        <v>4</v>
+      </c>
+      <c r="AW280">
+        <v>8</v>
+      </c>
+      <c r="AX280">
+        <v>7</v>
+      </c>
+      <c r="AY280">
+        <v>15</v>
+      </c>
+      <c r="AZ280">
+        <v>11</v>
+      </c>
+      <c r="BA280">
+        <v>4</v>
+      </c>
+      <c r="BB280">
+        <v>4</v>
+      </c>
+      <c r="BC280">
+        <v>8</v>
+      </c>
+      <c r="BD280">
+        <v>1.66</v>
+      </c>
+      <c r="BE280">
+        <v>6.75</v>
+      </c>
+      <c r="BF280">
+        <v>2.43</v>
+      </c>
+      <c r="BG280">
+        <v>1.25</v>
+      </c>
+      <c r="BH280">
+        <v>3.45</v>
+      </c>
+      <c r="BI280">
+        <v>1.44</v>
+      </c>
+      <c r="BJ280">
+        <v>2.55</v>
+      </c>
+      <c r="BK280">
+        <v>1.72</v>
+      </c>
+      <c r="BL280">
+        <v>1.98</v>
+      </c>
+      <c r="BM280">
+        <v>2.08</v>
+      </c>
+      <c r="BN280">
+        <v>1.65</v>
+      </c>
+      <c r="BO280">
+        <v>2.65</v>
+      </c>
+      <c r="BP280">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7465712</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F281">
+        <v>29</v>
+      </c>
+      <c r="G281" t="s">
+        <v>74</v>
+      </c>
+      <c r="H281" t="s">
+        <v>88</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281">
+        <v>1</v>
+      </c>
+      <c r="L281">
+        <v>0</v>
+      </c>
+      <c r="M281">
+        <v>2</v>
+      </c>
+      <c r="N281">
+        <v>2</v>
+      </c>
+      <c r="O281" t="s">
+        <v>93</v>
+      </c>
+      <c r="P281" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q281">
+        <v>4.53</v>
+      </c>
+      <c r="R281">
+        <v>2.5</v>
+      </c>
+      <c r="S281">
+        <v>2.27</v>
+      </c>
+      <c r="T281">
+        <v>1.3</v>
+      </c>
+      <c r="U281">
+        <v>3.4</v>
+      </c>
+      <c r="V281">
+        <v>2.38</v>
+      </c>
+      <c r="W281">
+        <v>1.57</v>
+      </c>
+      <c r="X281">
+        <v>6</v>
+      </c>
+      <c r="Y281">
+        <v>1.13</v>
+      </c>
+      <c r="Z281">
+        <v>4.22</v>
+      </c>
+      <c r="AA281">
+        <v>3.99</v>
+      </c>
+      <c r="AB281">
+        <v>1.75</v>
+      </c>
+      <c r="AC281">
+        <v>1.04</v>
+      </c>
+      <c r="AD281">
+        <v>10</v>
+      </c>
+      <c r="AE281">
+        <v>1.2</v>
+      </c>
+      <c r="AF281">
+        <v>4.33</v>
+      </c>
+      <c r="AG281">
+        <v>1.57</v>
+      </c>
+      <c r="AH281">
+        <v>2.25</v>
+      </c>
+      <c r="AI281">
+        <v>1.57</v>
+      </c>
+      <c r="AJ281">
+        <v>2.25</v>
+      </c>
+      <c r="AK281">
+        <v>1.98</v>
+      </c>
+      <c r="AL281">
+        <v>1.25</v>
+      </c>
+      <c r="AM281">
+        <v>1.23</v>
+      </c>
+      <c r="AN281">
+        <v>1.5</v>
+      </c>
+      <c r="AO281">
+        <v>1.79</v>
+      </c>
+      <c r="AP281">
+        <v>1.4</v>
+      </c>
+      <c r="AQ281">
+        <v>1.87</v>
+      </c>
+      <c r="AR281">
+        <v>1.45</v>
+      </c>
+      <c r="AS281">
+        <v>1.41</v>
+      </c>
+      <c r="AT281">
+        <v>2.86</v>
+      </c>
+      <c r="AU281">
+        <v>3</v>
+      </c>
+      <c r="AV281">
+        <v>8</v>
+      </c>
+      <c r="AW281">
+        <v>4</v>
+      </c>
+      <c r="AX281">
+        <v>8</v>
+      </c>
+      <c r="AY281">
+        <v>7</v>
+      </c>
+      <c r="AZ281">
+        <v>16</v>
+      </c>
+      <c r="BA281">
+        <v>6</v>
+      </c>
+      <c r="BB281">
+        <v>9</v>
+      </c>
+      <c r="BC281">
+        <v>15</v>
+      </c>
+      <c r="BD281">
+        <v>2.7</v>
+      </c>
+      <c r="BE281">
+        <v>7</v>
+      </c>
+      <c r="BF281">
+        <v>1.52</v>
+      </c>
+      <c r="BG281">
+        <v>1.26</v>
+      </c>
+      <c r="BH281">
+        <v>3.4</v>
+      </c>
+      <c r="BI281">
+        <v>1.47</v>
+      </c>
+      <c r="BJ281">
+        <v>2.48</v>
+      </c>
+      <c r="BK281">
+        <v>1.74</v>
+      </c>
+      <c r="BL281">
+        <v>1.96</v>
+      </c>
+      <c r="BM281">
+        <v>2.17</v>
+      </c>
+      <c r="BN281">
+        <v>1.6</v>
+      </c>
+      <c r="BO281">
+        <v>2.8</v>
+      </c>
+      <c r="BP281">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7465710</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F282">
+        <v>29</v>
+      </c>
+      <c r="G282" t="s">
+        <v>82</v>
+      </c>
+      <c r="H282" t="s">
+        <v>79</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282">
+        <v>1</v>
+      </c>
+      <c r="L282">
+        <v>2</v>
+      </c>
+      <c r="M282">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>3</v>
+      </c>
+      <c r="O282" t="s">
+        <v>280</v>
+      </c>
+      <c r="P282" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q282">
+        <v>1.73</v>
+      </c>
+      <c r="R282">
+        <v>2.7</v>
+      </c>
+      <c r="S282">
+        <v>5.75</v>
+      </c>
+      <c r="T282">
+        <v>1.2</v>
+      </c>
+      <c r="U282">
+        <v>4</v>
+      </c>
+      <c r="V282">
+        <v>1.95</v>
+      </c>
+      <c r="W282">
+        <v>1.77</v>
+      </c>
+      <c r="X282">
+        <v>4.15</v>
+      </c>
+      <c r="Y282">
+        <v>1.18</v>
+      </c>
+      <c r="Z282">
+        <v>1.33</v>
+      </c>
+      <c r="AA282">
+        <v>5.25</v>
+      </c>
+      <c r="AB282">
+        <v>7.5</v>
+      </c>
+      <c r="AC282">
+        <v>1.01</v>
+      </c>
+      <c r="AD282">
+        <v>23</v>
+      </c>
+      <c r="AE282">
+        <v>1.11</v>
+      </c>
+      <c r="AF282">
+        <v>6.25</v>
+      </c>
+      <c r="AG282">
+        <v>1.38</v>
+      </c>
+      <c r="AH282">
+        <v>3</v>
+      </c>
+      <c r="AI282">
+        <v>1.57</v>
+      </c>
+      <c r="AJ282">
+        <v>2.2</v>
+      </c>
+      <c r="AK282">
+        <v>1.07</v>
+      </c>
+      <c r="AL282">
+        <v>1.11</v>
+      </c>
+      <c r="AM282">
+        <v>3.2</v>
+      </c>
+      <c r="AN282">
+        <v>1.69</v>
+      </c>
+      <c r="AO282">
+        <v>1</v>
+      </c>
+      <c r="AP282">
+        <v>1.79</v>
+      </c>
+      <c r="AQ282">
+        <v>0.93</v>
+      </c>
+      <c r="AR282">
+        <v>1.96</v>
+      </c>
+      <c r="AS282">
+        <v>1.29</v>
+      </c>
+      <c r="AT282">
+        <v>3.25</v>
+      </c>
+      <c r="AU282">
+        <v>6</v>
+      </c>
+      <c r="AV282">
+        <v>5</v>
+      </c>
+      <c r="AW282">
+        <v>21</v>
+      </c>
+      <c r="AX282">
+        <v>14</v>
+      </c>
+      <c r="AY282">
+        <v>27</v>
+      </c>
+      <c r="AZ282">
+        <v>19</v>
+      </c>
+      <c r="BA282">
+        <v>10</v>
+      </c>
+      <c r="BB282">
+        <v>4</v>
+      </c>
+      <c r="BC282">
+        <v>14</v>
+      </c>
+      <c r="BD282">
+        <v>1.26</v>
+      </c>
+      <c r="BE282">
+        <v>7.5</v>
+      </c>
+      <c r="BF282">
+        <v>4.1</v>
+      </c>
+      <c r="BG282">
+        <v>1.26</v>
+      </c>
+      <c r="BH282">
+        <v>3.4</v>
+      </c>
+      <c r="BI282">
+        <v>1.46</v>
+      </c>
+      <c r="BJ282">
+        <v>2.5</v>
+      </c>
+      <c r="BK282">
+        <v>1.74</v>
+      </c>
+      <c r="BL282">
+        <v>1.98</v>
+      </c>
+      <c r="BM282">
+        <v>2.12</v>
+      </c>
+      <c r="BN282">
+        <v>1.63</v>
+      </c>
+      <c r="BO282">
+        <v>2.65</v>
+      </c>
+      <c r="BP282">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7465714</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F283">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>80</v>
+      </c>
+      <c r="H283" t="s">
+        <v>89</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>0</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>1</v>
+      </c>
+      <c r="O283" t="s">
+        <v>281</v>
+      </c>
+      <c r="P283" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q283">
+        <v>2.66</v>
+      </c>
+      <c r="R283">
+        <v>2.42</v>
+      </c>
+      <c r="S283">
+        <v>3.68</v>
+      </c>
+      <c r="T283">
+        <v>1.3</v>
+      </c>
+      <c r="U283">
+        <v>3.4</v>
+      </c>
+      <c r="V283">
+        <v>2.42</v>
+      </c>
+      <c r="W283">
+        <v>1.53</v>
+      </c>
+      <c r="X283">
+        <v>6</v>
+      </c>
+      <c r="Y283">
+        <v>1.13</v>
+      </c>
+      <c r="Z283">
+        <v>2.16</v>
+      </c>
+      <c r="AA283">
+        <v>3.56</v>
+      </c>
+      <c r="AB283">
+        <v>3.2</v>
+      </c>
+      <c r="AC283">
+        <v>1.04</v>
+      </c>
+      <c r="AD283">
+        <v>10</v>
+      </c>
+      <c r="AE283">
+        <v>1.22</v>
+      </c>
+      <c r="AF283">
+        <v>4.2</v>
+      </c>
+      <c r="AG283">
+        <v>1.6</v>
+      </c>
+      <c r="AH283">
+        <v>2.2</v>
+      </c>
+      <c r="AI283">
+        <v>1.53</v>
+      </c>
+      <c r="AJ283">
+        <v>2.38</v>
+      </c>
+      <c r="AK283">
+        <v>1.33</v>
+      </c>
+      <c r="AL283">
+        <v>1.27</v>
+      </c>
+      <c r="AM283">
+        <v>1.72</v>
+      </c>
+      <c r="AN283">
+        <v>0.71</v>
+      </c>
+      <c r="AO283">
+        <v>0.86</v>
+      </c>
+      <c r="AP283">
+        <v>0.87</v>
+      </c>
+      <c r="AQ283">
+        <v>0.8</v>
+      </c>
+      <c r="AR283">
+        <v>1.6</v>
+      </c>
+      <c r="AS283">
+        <v>1.54</v>
+      </c>
+      <c r="AT283">
+        <v>3.14</v>
+      </c>
+      <c r="AU283">
+        <v>5</v>
+      </c>
+      <c r="AV283">
+        <v>5</v>
+      </c>
+      <c r="AW283">
+        <v>4</v>
+      </c>
+      <c r="AX283">
+        <v>2</v>
+      </c>
+      <c r="AY283">
+        <v>11</v>
+      </c>
+      <c r="AZ283">
+        <v>7</v>
+      </c>
+      <c r="BA283">
+        <v>5</v>
+      </c>
+      <c r="BB283">
+        <v>5</v>
+      </c>
+      <c r="BC283">
+        <v>10</v>
+      </c>
+      <c r="BD283">
+        <v>1.75</v>
+      </c>
+      <c r="BE283">
+        <v>6.75</v>
+      </c>
+      <c r="BF283">
+        <v>2.28</v>
+      </c>
+      <c r="BG283">
+        <v>1.25</v>
+      </c>
+      <c r="BH283">
+        <v>3.4</v>
+      </c>
+      <c r="BI283">
+        <v>1.44</v>
+      </c>
+      <c r="BJ283">
+        <v>2.55</v>
+      </c>
+      <c r="BK283">
+        <v>1.73</v>
+      </c>
+      <c r="BL283">
+        <v>1.98</v>
+      </c>
+      <c r="BM283">
+        <v>2.15</v>
+      </c>
+      <c r="BN283">
+        <v>1.63</v>
+      </c>
+      <c r="BO283">
+        <v>2.7</v>
+      </c>
+      <c r="BP283">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7465707</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F284">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>72</v>
+      </c>
+      <c r="H284" t="s">
+        <v>73</v>
+      </c>
+      <c r="I284">
+        <v>3</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>3</v>
+      </c>
+      <c r="L284">
+        <v>4</v>
+      </c>
+      <c r="M284">
+        <v>0</v>
+      </c>
+      <c r="N284">
+        <v>4</v>
+      </c>
+      <c r="O284" t="s">
+        <v>282</v>
+      </c>
+      <c r="P284" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q284">
+        <v>2.55</v>
+      </c>
+      <c r="R284">
+        <v>2.2</v>
+      </c>
+      <c r="S284">
+        <v>3.65</v>
+      </c>
+      <c r="T284">
+        <v>1.3</v>
+      </c>
+      <c r="U284">
+        <v>3.2</v>
+      </c>
+      <c r="V284">
+        <v>2.4</v>
+      </c>
+      <c r="W284">
+        <v>1.5</v>
+      </c>
+      <c r="X284">
+        <v>5.9</v>
+      </c>
+      <c r="Y284">
+        <v>1.08</v>
+      </c>
+      <c r="Z284">
+        <v>2.1</v>
+      </c>
+      <c r="AA284">
+        <v>3.55</v>
+      </c>
+      <c r="AB284">
+        <v>3.2</v>
+      </c>
+      <c r="AC284">
+        <v>1.04</v>
+      </c>
+      <c r="AD284">
+        <v>10</v>
+      </c>
+      <c r="AE284">
+        <v>1.22</v>
+      </c>
+      <c r="AF284">
+        <v>4.2</v>
+      </c>
+      <c r="AG284">
+        <v>1.65</v>
+      </c>
+      <c r="AH284">
+        <v>2.2</v>
+      </c>
+      <c r="AI284">
+        <v>1.53</v>
+      </c>
+      <c r="AJ284">
+        <v>2.3</v>
+      </c>
+      <c r="AK284">
+        <v>1.33</v>
+      </c>
+      <c r="AL284">
+        <v>1.22</v>
+      </c>
+      <c r="AM284">
+        <v>1.7</v>
+      </c>
+      <c r="AN284">
+        <v>1.5</v>
+      </c>
+      <c r="AO284">
+        <v>0.57</v>
+      </c>
+      <c r="AP284">
+        <v>1.6</v>
+      </c>
+      <c r="AQ284">
+        <v>0.53</v>
+      </c>
+      <c r="AR284">
+        <v>1.5</v>
+      </c>
+      <c r="AS284">
+        <v>1.32</v>
+      </c>
+      <c r="AT284">
+        <v>2.82</v>
+      </c>
+      <c r="AU284">
+        <v>13</v>
+      </c>
+      <c r="AV284">
+        <v>4</v>
+      </c>
+      <c r="AW284">
+        <v>12</v>
+      </c>
+      <c r="AX284">
+        <v>11</v>
+      </c>
+      <c r="AY284">
+        <v>25</v>
+      </c>
+      <c r="AZ284">
+        <v>15</v>
+      </c>
+      <c r="BA284">
+        <v>4</v>
+      </c>
+      <c r="BB284">
+        <v>2</v>
+      </c>
+      <c r="BC284">
+        <v>6</v>
+      </c>
+      <c r="BD284">
+        <v>1.76</v>
+      </c>
+      <c r="BE284">
+        <v>6.4</v>
+      </c>
+      <c r="BF284">
+        <v>2.3</v>
+      </c>
+      <c r="BG284">
+        <v>1.33</v>
+      </c>
+      <c r="BH284">
+        <v>2.95</v>
+      </c>
+      <c r="BI284">
+        <v>1.56</v>
+      </c>
+      <c r="BJ284">
+        <v>2.23</v>
+      </c>
+      <c r="BK284">
+        <v>1.92</v>
+      </c>
+      <c r="BL284">
+        <v>1.77</v>
+      </c>
+      <c r="BM284">
+        <v>2.4</v>
+      </c>
+      <c r="BN284">
+        <v>1.49</v>
+      </c>
+      <c r="BO284">
+        <v>3.15</v>
+      </c>
+      <c r="BP284">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7465706</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F285">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>71</v>
+      </c>
+      <c r="H285" t="s">
+        <v>76</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+      <c r="M285">
+        <v>1</v>
+      </c>
+      <c r="N285">
+        <v>1</v>
+      </c>
+      <c r="O285" t="s">
+        <v>93</v>
+      </c>
+      <c r="P285" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q285">
+        <v>2.95</v>
+      </c>
+      <c r="R285">
+        <v>2.2</v>
+      </c>
+      <c r="S285">
+        <v>3.1</v>
+      </c>
+      <c r="T285">
+        <v>1.3</v>
+      </c>
+      <c r="U285">
+        <v>3.2</v>
+      </c>
+      <c r="V285">
+        <v>2.4</v>
+      </c>
+      <c r="W285">
+        <v>1.5</v>
+      </c>
+      <c r="X285">
+        <v>6.05</v>
+      </c>
+      <c r="Y285">
+        <v>1.07</v>
+      </c>
+      <c r="Z285">
+        <v>2.5</v>
+      </c>
+      <c r="AA285">
+        <v>3.5</v>
+      </c>
+      <c r="AB285">
+        <v>2.62</v>
+      </c>
+      <c r="AC285">
+        <v>1.04</v>
+      </c>
+      <c r="AD285">
+        <v>10</v>
+      </c>
+      <c r="AE285">
+        <v>1.2</v>
+      </c>
+      <c r="AF285">
+        <v>4.33</v>
+      </c>
+      <c r="AG285">
+        <v>1.65</v>
+      </c>
+      <c r="AH285">
+        <v>2.2</v>
+      </c>
+      <c r="AI285">
+        <v>1.5</v>
+      </c>
+      <c r="AJ285">
+        <v>2.38</v>
+      </c>
+      <c r="AK285">
+        <v>1.48</v>
+      </c>
+      <c r="AL285">
+        <v>1.25</v>
+      </c>
+      <c r="AM285">
+        <v>1.5</v>
+      </c>
+      <c r="AN285">
+        <v>1.14</v>
+      </c>
+      <c r="AO285">
+        <v>1.46</v>
+      </c>
+      <c r="AP285">
+        <v>1.07</v>
+      </c>
+      <c r="AQ285">
+        <v>1.57</v>
+      </c>
+      <c r="AR285">
+        <v>1.71</v>
+      </c>
+      <c r="AS285">
+        <v>1.53</v>
+      </c>
+      <c r="AT285">
+        <v>3.24</v>
+      </c>
+      <c r="AU285">
+        <v>4</v>
+      </c>
+      <c r="AV285">
+        <v>5</v>
+      </c>
+      <c r="AW285">
+        <v>4</v>
+      </c>
+      <c r="AX285">
+        <v>11</v>
+      </c>
+      <c r="AY285">
+        <v>8</v>
+      </c>
+      <c r="AZ285">
+        <v>16</v>
+      </c>
+      <c r="BA285">
+        <v>5</v>
+      </c>
+      <c r="BB285">
+        <v>12</v>
+      </c>
+      <c r="BC285">
+        <v>17</v>
+      </c>
+      <c r="BD285">
+        <v>1.95</v>
+      </c>
+      <c r="BE285">
+        <v>6.5</v>
+      </c>
+      <c r="BF285">
+        <v>2.02</v>
+      </c>
+      <c r="BG285">
+        <v>1.33</v>
+      </c>
+      <c r="BH285">
+        <v>2.95</v>
+      </c>
+      <c r="BI285">
+        <v>1.56</v>
+      </c>
+      <c r="BJ285">
+        <v>2.23</v>
+      </c>
+      <c r="BK285">
+        <v>1.92</v>
+      </c>
+      <c r="BL285">
+        <v>1.78</v>
+      </c>
+      <c r="BM285">
+        <v>2.43</v>
+      </c>
+      <c r="BN285">
+        <v>1.49</v>
+      </c>
+      <c r="BO285">
+        <v>3.15</v>
+      </c>
+      <c r="BP285">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7465705</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F286">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>70</v>
+      </c>
+      <c r="H286" t="s">
+        <v>75</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>2</v>
+      </c>
+      <c r="K286">
+        <v>3</v>
+      </c>
+      <c r="L286">
+        <v>3</v>
+      </c>
+      <c r="M286">
+        <v>3</v>
+      </c>
+      <c r="N286">
+        <v>6</v>
+      </c>
+      <c r="O286" t="s">
+        <v>283</v>
+      </c>
+      <c r="P286" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q286">
+        <v>2.57</v>
+      </c>
+      <c r="R286">
+        <v>2.42</v>
+      </c>
+      <c r="S286">
+        <v>3.86</v>
+      </c>
+      <c r="T286">
+        <v>1.33</v>
+      </c>
+      <c r="U286">
+        <v>3.25</v>
+      </c>
+      <c r="V286">
+        <v>2.49</v>
+      </c>
+      <c r="W286">
+        <v>1.56</v>
+      </c>
+      <c r="X286">
+        <v>6</v>
+      </c>
+      <c r="Y286">
+        <v>1.13</v>
+      </c>
+      <c r="Z286">
+        <v>2.05</v>
+      </c>
+      <c r="AA286">
+        <v>3.66</v>
+      </c>
+      <c r="AB286">
+        <v>3.38</v>
+      </c>
+      <c r="AC286">
+        <v>1.04</v>
+      </c>
+      <c r="AD286">
+        <v>10</v>
+      </c>
+      <c r="AE286">
+        <v>1.22</v>
+      </c>
+      <c r="AF286">
+        <v>4.2</v>
+      </c>
+      <c r="AG286">
+        <v>1.6</v>
+      </c>
+      <c r="AH286">
+        <v>2.2</v>
+      </c>
+      <c r="AI286">
+        <v>1.57</v>
+      </c>
+      <c r="AJ286">
+        <v>2.25</v>
+      </c>
+      <c r="AK286">
+        <v>1.32</v>
+      </c>
+      <c r="AL286">
+        <v>1.26</v>
+      </c>
+      <c r="AM286">
+        <v>1.73</v>
+      </c>
+      <c r="AN286">
+        <v>1.15</v>
+      </c>
+      <c r="AO286">
+        <v>0.92</v>
+      </c>
+      <c r="AP286">
+        <v>1.14</v>
+      </c>
+      <c r="AQ286">
+        <v>0.93</v>
+      </c>
+      <c r="AR286">
+        <v>1.39</v>
+      </c>
+      <c r="AS286">
+        <v>1.43</v>
+      </c>
+      <c r="AT286">
+        <v>2.82</v>
+      </c>
+      <c r="AU286">
+        <v>7</v>
+      </c>
+      <c r="AV286">
+        <v>9</v>
+      </c>
+      <c r="AW286">
+        <v>11</v>
+      </c>
+      <c r="AX286">
+        <v>13</v>
+      </c>
+      <c r="AY286">
+        <v>18</v>
+      </c>
+      <c r="AZ286">
+        <v>22</v>
+      </c>
+      <c r="BA286">
+        <v>3</v>
+      </c>
+      <c r="BB286">
+        <v>6</v>
+      </c>
+      <c r="BC286">
+        <v>9</v>
+      </c>
+      <c r="BD286">
+        <v>1.78</v>
+      </c>
+      <c r="BE286">
+        <v>6.75</v>
+      </c>
+      <c r="BF286">
+        <v>2.2</v>
+      </c>
+      <c r="BG286">
+        <v>1.18</v>
+      </c>
+      <c r="BH286">
+        <v>4.2</v>
+      </c>
+      <c r="BI286">
+        <v>1.3</v>
+      </c>
+      <c r="BJ286">
+        <v>3.05</v>
+      </c>
+      <c r="BK286">
+        <v>1.52</v>
+      </c>
+      <c r="BL286">
+        <v>2.33</v>
+      </c>
+      <c r="BM286">
+        <v>1.82</v>
+      </c>
+      <c r="BN286">
+        <v>1.86</v>
+      </c>
+      <c r="BO286">
+        <v>2.25</v>
+      </c>
+      <c r="BP286">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7465703</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F287">
+        <v>29</v>
+      </c>
+      <c r="G287" t="s">
+        <v>85</v>
+      </c>
+      <c r="H287" t="s">
+        <v>87</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>2</v>
+      </c>
+      <c r="K287">
+        <v>2</v>
+      </c>
+      <c r="L287">
+        <v>0</v>
+      </c>
+      <c r="M287">
+        <v>2</v>
+      </c>
+      <c r="N287">
+        <v>2</v>
+      </c>
+      <c r="O287" t="s">
+        <v>93</v>
+      </c>
+      <c r="P287" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q287">
+        <v>3.7</v>
+      </c>
+      <c r="R287">
+        <v>2.15</v>
+      </c>
+      <c r="S287">
+        <v>2.62</v>
+      </c>
+      <c r="T287">
+        <v>1.36</v>
+      </c>
+      <c r="U287">
+        <v>2.85</v>
+      </c>
+      <c r="V287">
+        <v>2.75</v>
+      </c>
+      <c r="W287">
+        <v>1.4</v>
+      </c>
+      <c r="X287">
+        <v>6.6</v>
+      </c>
+      <c r="Y287">
+        <v>1.06</v>
+      </c>
+      <c r="Z287">
+        <v>3.3</v>
+      </c>
+      <c r="AA287">
+        <v>3.55</v>
+      </c>
+      <c r="AB287">
+        <v>2.05</v>
+      </c>
+      <c r="AC287">
+        <v>1.05</v>
+      </c>
+      <c r="AD287">
+        <v>9.5</v>
+      </c>
+      <c r="AE287">
+        <v>1.28</v>
+      </c>
+      <c r="AF287">
+        <v>3.55</v>
+      </c>
+      <c r="AG287">
+        <v>1.85</v>
+      </c>
+      <c r="AH287">
+        <v>1.9</v>
+      </c>
+      <c r="AI287">
+        <v>1.7</v>
+      </c>
+      <c r="AJ287">
+        <v>2</v>
+      </c>
+      <c r="AK287">
+        <v>1.73</v>
+      </c>
+      <c r="AL287">
+        <v>1.22</v>
+      </c>
+      <c r="AM287">
+        <v>1.3</v>
+      </c>
+      <c r="AN287">
+        <v>1.79</v>
+      </c>
+      <c r="AO287">
+        <v>2.07</v>
+      </c>
+      <c r="AP287">
+        <v>1.67</v>
+      </c>
+      <c r="AQ287">
+        <v>2.13</v>
+      </c>
+      <c r="AR287">
+        <v>1.76</v>
+      </c>
+      <c r="AS287">
+        <v>1.93</v>
+      </c>
+      <c r="AT287">
+        <v>3.69</v>
+      </c>
+      <c r="AU287">
+        <v>2</v>
+      </c>
+      <c r="AV287">
+        <v>5</v>
+      </c>
+      <c r="AW287">
+        <v>7</v>
+      </c>
+      <c r="AX287">
+        <v>8</v>
+      </c>
+      <c r="AY287">
+        <v>9</v>
+      </c>
+      <c r="AZ287">
+        <v>13</v>
+      </c>
+      <c r="BA287">
+        <v>2</v>
+      </c>
+      <c r="BB287">
+        <v>4</v>
+      </c>
+      <c r="BC287">
+        <v>6</v>
+      </c>
+      <c r="BD287">
+        <v>2.43</v>
+      </c>
+      <c r="BE287">
+        <v>6.75</v>
+      </c>
+      <c r="BF287">
+        <v>1.67</v>
+      </c>
+      <c r="BG287">
+        <v>1.3</v>
+      </c>
+      <c r="BH287">
+        <v>3.15</v>
+      </c>
+      <c r="BI287">
+        <v>1.5</v>
+      </c>
+      <c r="BJ287">
+        <v>2.33</v>
+      </c>
+      <c r="BK287">
+        <v>1.83</v>
+      </c>
+      <c r="BL287">
+        <v>1.85</v>
+      </c>
+      <c r="BM287">
+        <v>2.3</v>
+      </c>
+      <c r="BN287">
+        <v>1.54</v>
+      </c>
+      <c r="BO287">
+        <v>2.9</v>
+      </c>
+      <c r="BP287">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7465702</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F288">
+        <v>29</v>
+      </c>
+      <c r="G288" t="s">
+        <v>77</v>
+      </c>
+      <c r="H288" t="s">
+        <v>83</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>2</v>
+      </c>
+      <c r="L288">
+        <v>2</v>
+      </c>
+      <c r="M288">
+        <v>1</v>
+      </c>
+      <c r="N288">
+        <v>3</v>
+      </c>
+      <c r="O288" t="s">
+        <v>284</v>
+      </c>
+      <c r="P288" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q288">
+        <v>2.7</v>
+      </c>
+      <c r="R288">
+        <v>2.25</v>
+      </c>
+      <c r="S288">
+        <v>3.25</v>
+      </c>
+      <c r="T288">
+        <v>1.28</v>
+      </c>
+      <c r="U288">
+        <v>3.4</v>
+      </c>
+      <c r="V288">
+        <v>2.2</v>
+      </c>
+      <c r="W288">
+        <v>1.6</v>
+      </c>
+      <c r="X288">
+        <v>5.2</v>
+      </c>
+      <c r="Y288">
+        <v>1.12</v>
+      </c>
+      <c r="Z288">
+        <v>2.2</v>
+      </c>
+      <c r="AA288">
+        <v>3.65</v>
+      </c>
+      <c r="AB288">
+        <v>2.88</v>
+      </c>
+      <c r="AC288">
+        <v>1.01</v>
+      </c>
+      <c r="AD288">
+        <v>13</v>
+      </c>
+      <c r="AE288">
+        <v>1.18</v>
+      </c>
+      <c r="AF288">
+        <v>4.75</v>
+      </c>
+      <c r="AG288">
+        <v>1.55</v>
+      </c>
+      <c r="AH288">
+        <v>2.4</v>
+      </c>
+      <c r="AI288">
+        <v>1.45</v>
+      </c>
+      <c r="AJ288">
+        <v>2.5</v>
+      </c>
+      <c r="AK288">
+        <v>1.4</v>
+      </c>
+      <c r="AL288">
+        <v>1.22</v>
+      </c>
+      <c r="AM288">
+        <v>1.62</v>
+      </c>
+      <c r="AN288">
+        <v>2.21</v>
+      </c>
+      <c r="AO288">
+        <v>1.43</v>
+      </c>
+      <c r="AP288">
+        <v>2.27</v>
+      </c>
+      <c r="AQ288">
+        <v>1.33</v>
+      </c>
+      <c r="AR288">
+        <v>1.81</v>
+      </c>
+      <c r="AS288">
+        <v>1.68</v>
+      </c>
+      <c r="AT288">
+        <v>3.49</v>
+      </c>
+      <c r="AU288">
+        <v>3</v>
+      </c>
+      <c r="AV288">
+        <v>4</v>
+      </c>
+      <c r="AW288">
+        <v>6</v>
+      </c>
+      <c r="AX288">
+        <v>12</v>
+      </c>
+      <c r="AY288">
+        <v>10</v>
+      </c>
+      <c r="AZ288">
+        <v>16</v>
+      </c>
+      <c r="BA288">
+        <v>1</v>
+      </c>
+      <c r="BB288">
+        <v>8</v>
+      </c>
+      <c r="BC288">
+        <v>9</v>
+      </c>
+      <c r="BD288">
+        <v>1.81</v>
+      </c>
+      <c r="BE288">
+        <v>6.4</v>
+      </c>
+      <c r="BF288">
+        <v>2.2</v>
+      </c>
+      <c r="BG288">
+        <v>1.28</v>
+      </c>
+      <c r="BH288">
+        <v>3.2</v>
+      </c>
+      <c r="BI288">
+        <v>1.49</v>
+      </c>
+      <c r="BJ288">
+        <v>2.4</v>
+      </c>
+      <c r="BK288">
+        <v>1.8</v>
+      </c>
+      <c r="BL288">
+        <v>1.9</v>
+      </c>
+      <c r="BM288">
+        <v>2.25</v>
+      </c>
+      <c r="BN288">
+        <v>1.55</v>
+      </c>
+      <c r="BO288">
+        <v>2.9</v>
+      </c>
+      <c r="BP288">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7465709</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45723.66666666666</v>
+      </c>
+      <c r="F289">
+        <v>29</v>
+      </c>
+      <c r="G289" t="s">
+        <v>78</v>
+      </c>
+      <c r="H289" t="s">
+        <v>84</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289">
+        <v>1</v>
+      </c>
+      <c r="K289">
+        <v>2</v>
+      </c>
+      <c r="L289">
+        <v>5</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>6</v>
+      </c>
+      <c r="O289" t="s">
+        <v>285</v>
+      </c>
+      <c r="P289" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q289">
+        <v>2.03</v>
+      </c>
+      <c r="R289">
+        <v>2.63</v>
+      </c>
+      <c r="S289">
+        <v>5.27</v>
+      </c>
+      <c r="T289">
+        <v>1.29</v>
+      </c>
+      <c r="U289">
+        <v>3.5</v>
+      </c>
+      <c r="V289">
+        <v>2.24</v>
+      </c>
+      <c r="W289">
+        <v>1.61</v>
+      </c>
+      <c r="X289">
+        <v>5.5</v>
+      </c>
+      <c r="Y289">
+        <v>1.14</v>
+      </c>
+      <c r="Z289">
+        <v>1.56</v>
+      </c>
+      <c r="AA289">
+        <v>4.37</v>
+      </c>
+      <c r="AB289">
+        <v>5.13</v>
+      </c>
+      <c r="AC289">
+        <v>1.01</v>
+      </c>
+      <c r="AD289">
+        <v>15</v>
+      </c>
+      <c r="AE289">
+        <v>1.18</v>
+      </c>
+      <c r="AF289">
+        <v>4.75</v>
+      </c>
+      <c r="AG289">
+        <v>1.53</v>
+      </c>
+      <c r="AH289">
+        <v>2.4</v>
+      </c>
+      <c r="AI289">
+        <v>1.62</v>
+      </c>
+      <c r="AJ289">
+        <v>2.2</v>
+      </c>
+      <c r="AK289">
+        <v>1.2</v>
+      </c>
+      <c r="AL289">
+        <v>1.21</v>
+      </c>
+      <c r="AM289">
+        <v>2.2</v>
+      </c>
+      <c r="AN289">
+        <v>1.15</v>
+      </c>
+      <c r="AO289">
+        <v>0.62</v>
+      </c>
+      <c r="AP289">
+        <v>1.29</v>
+      </c>
+      <c r="AQ289">
+        <v>0.57</v>
+      </c>
+      <c r="AR289">
+        <v>1.73</v>
+      </c>
+      <c r="AS289">
+        <v>1.21</v>
+      </c>
+      <c r="AT289">
+        <v>2.94</v>
+      </c>
+      <c r="AU289">
+        <v>8</v>
+      </c>
+      <c r="AV289">
+        <v>6</v>
+      </c>
+      <c r="AW289">
+        <v>9</v>
+      </c>
+      <c r="AX289">
+        <v>7</v>
+      </c>
+      <c r="AY289">
+        <v>17</v>
+      </c>
+      <c r="AZ289">
+        <v>13</v>
+      </c>
+      <c r="BA289">
+        <v>10</v>
+      </c>
+      <c r="BB289">
+        <v>9</v>
+      </c>
+      <c r="BC289">
+        <v>19</v>
+      </c>
+      <c r="BD289">
+        <v>1.5</v>
+      </c>
+      <c r="BE289">
+        <v>6.75</v>
+      </c>
+      <c r="BF289">
+        <v>2.8</v>
+      </c>
+      <c r="BG289">
+        <v>1.29</v>
+      </c>
+      <c r="BH289">
+        <v>3.2</v>
+      </c>
+      <c r="BI289">
+        <v>1.49</v>
+      </c>
+      <c r="BJ289">
+        <v>2.4</v>
+      </c>
+      <c r="BK289">
+        <v>1.81</v>
+      </c>
+      <c r="BL289">
+        <v>1.88</v>
+      </c>
+      <c r="BM289">
+        <v>2.3</v>
+      </c>
+      <c r="BN289">
+        <v>1.54</v>
+      </c>
+      <c r="BO289">
+        <v>2.95</v>
+      </c>
+      <c r="BP289">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -60091,13 +60091,13 @@
         <v>15</v>
       </c>
       <c r="BA284">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB284">
         <v>2</v>
       </c>
       <c r="BC284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD284">
         <v>1.76</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="423">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -874,6 +874,12 @@
     <t>['27', '68', '77', '80', '85']</t>
   </si>
   <si>
+    <t>['34', '56']</t>
+  </si>
+  <si>
+    <t>['32', '77', '90+3']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1272,6 +1278,12 @@
   <si>
     <t>['6', '32']</t>
   </si>
+  <si>
+    <t>['55', '65']</t>
+  </si>
+  <si>
+    <t>['3', '13']</t>
+  </si>
 </sst>
 </file>
 
@@ -1632,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP289"/>
+  <dimension ref="A1:BP293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1969,7 +1981,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ2">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2094,7 +2106,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2175,7 +2187,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2300,7 +2312,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2712,7 +2724,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2918,7 +2930,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3124,7 +3136,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3330,7 +3342,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3742,7 +3754,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3820,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ11">
         <v>0.8</v>
@@ -4029,7 +4041,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ12">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4154,7 +4166,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4441,7 +4453,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4644,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ15">
         <v>1.07</v>
@@ -4772,7 +4784,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4850,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ16">
         <v>0.93</v>
@@ -5468,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ19">
         <v>1.29</v>
@@ -5596,7 +5608,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6626,7 +6638,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6832,7 +6844,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7038,7 +7050,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7450,7 +7462,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7737,7 +7749,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -7862,7 +7874,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7940,7 +7952,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ31">
         <v>1.2</v>
@@ -8480,7 +8492,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8686,7 +8698,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8764,7 +8776,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ35">
         <v>1.79</v>
@@ -9304,7 +9316,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9510,7 +9522,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9591,7 +9603,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ39">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9797,7 +9809,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ40">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -9922,7 +9934,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10618,7 +10630,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ44">
         <v>0.8</v>
@@ -10746,7 +10758,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10952,7 +10964,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11239,7 +11251,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11364,7 +11376,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11651,7 +11663,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11776,7 +11788,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11982,7 +11994,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12060,7 +12072,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ51">
         <v>1.2</v>
@@ -12188,7 +12200,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12678,7 +12690,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ54">
         <v>1.13</v>
@@ -12884,7 +12896,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ55">
         <v>1.23</v>
@@ -13012,7 +13024,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13093,7 +13105,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ56">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13299,7 +13311,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13424,7 +13436,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13502,10 +13514,10 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ58">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13708,7 +13720,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ59">
         <v>1.57</v>
@@ -13917,7 +13929,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ60">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -14042,7 +14054,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14248,7 +14260,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14454,7 +14466,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15072,7 +15084,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15484,7 +15496,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15690,7 +15702,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15896,7 +15908,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16102,7 +16114,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16180,7 +16192,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ71">
         <v>2.13</v>
@@ -16308,7 +16320,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16514,7 +16526,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16595,7 +16607,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16720,7 +16732,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16798,7 +16810,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ74">
         <v>1.07</v>
@@ -16926,7 +16938,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17419,7 +17431,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ77">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17544,7 +17556,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17625,7 +17637,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ78">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17750,7 +17762,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17828,7 +17840,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ79">
         <v>1.79</v>
@@ -18037,7 +18049,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ80">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -18162,7 +18174,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18240,7 +18252,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ81">
         <v>1.29</v>
@@ -18574,7 +18586,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18780,7 +18792,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19270,7 +19282,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ86">
         <v>1.2</v>
@@ -19398,7 +19410,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20016,7 +20028,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20428,7 +20440,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20840,7 +20852,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21046,7 +21058,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21127,7 +21139,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ95">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21252,7 +21264,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21458,7 +21470,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21536,7 +21548,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ97">
         <v>1.87</v>
@@ -21870,7 +21882,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22157,7 +22169,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22282,7 +22294,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22360,7 +22372,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ101">
         <v>0.53</v>
@@ -22488,7 +22500,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22900,7 +22912,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -22978,7 +22990,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ104">
         <v>1.33</v>
@@ -23312,7 +23324,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23596,7 +23608,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ107">
         <v>1.53</v>
@@ -23805,7 +23817,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ108">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -24008,7 +24020,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ109">
         <v>1.07</v>
@@ -24136,7 +24148,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24217,7 +24229,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24342,7 +24354,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24423,7 +24435,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ111">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24548,7 +24560,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25166,7 +25178,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25372,7 +25384,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25578,7 +25590,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25784,7 +25796,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25865,7 +25877,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ118">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -25990,7 +26002,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26068,7 +26080,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ119">
         <v>2.13</v>
@@ -26196,7 +26208,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26402,7 +26414,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26608,7 +26620,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26814,7 +26826,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27020,7 +27032,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27101,7 +27113,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ124">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -27226,7 +27238,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27513,7 +27525,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ126">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -27844,7 +27856,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28256,7 +28268,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28334,7 +28346,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ130">
         <v>0.53</v>
@@ -28462,7 +28474,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28540,7 +28552,7 @@
         <v>2.4</v>
       </c>
       <c r="AP131">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ131">
         <v>1.79</v>
@@ -29161,7 +29173,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ134">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29364,7 +29376,7 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29492,7 +29504,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29776,7 +29788,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ137">
         <v>1.53</v>
@@ -29985,7 +29997,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ138">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -31140,7 +31152,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31221,7 +31233,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -31346,7 +31358,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31424,7 +31436,7 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ145">
         <v>1.87</v>
@@ -31552,7 +31564,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31758,7 +31770,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31964,7 +31976,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32042,7 +32054,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ148">
         <v>1.13</v>
@@ -32376,7 +32388,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32582,7 +32594,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32869,7 +32881,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -32994,7 +33006,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33200,7 +33212,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33278,7 +33290,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ154">
         <v>1.07</v>
@@ -33406,7 +33418,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33487,7 +33499,7 @@
         <v>2</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -34311,7 +34323,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ159">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34436,7 +34448,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34514,10 +34526,10 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ160">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34720,7 +34732,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ161">
         <v>1.33</v>
@@ -34848,7 +34860,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35132,7 +35144,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ163">
         <v>0.8</v>
@@ -35672,7 +35684,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36496,7 +36508,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36577,7 +36589,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ170">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -36702,7 +36714,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36989,7 +37001,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ172">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -37114,7 +37126,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37195,7 +37207,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ173">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37813,7 +37825,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ176">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -37938,7 +37950,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38016,7 +38028,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ177">
         <v>1.57</v>
@@ -38144,7 +38156,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38556,7 +38568,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38634,7 +38646,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ180">
         <v>1.53</v>
@@ -38762,7 +38774,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38840,7 +38852,7 @@
         <v>1.11</v>
       </c>
       <c r="AP181">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ181">
         <v>1.13</v>
@@ -39255,7 +39267,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ183">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -39380,7 +39392,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39586,7 +39598,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39792,7 +39804,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40076,7 +40088,7 @@
         <v>1.67</v>
       </c>
       <c r="AP187">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ187">
         <v>1.87</v>
@@ -40410,7 +40422,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41028,7 +41040,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41106,7 +41118,7 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ192">
         <v>1.29</v>
@@ -41234,7 +41246,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41312,10 +41324,10 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ193">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41440,7 +41452,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41518,7 +41530,7 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ194">
         <v>1.07</v>
@@ -41646,7 +41658,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41852,7 +41864,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41933,7 +41945,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ196">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -42470,7 +42482,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42757,7 +42769,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ200">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42882,7 +42894,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43166,10 +43178,10 @@
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ202">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -43500,7 +43512,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43912,7 +43924,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44118,7 +44130,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44530,7 +44542,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44814,7 +44826,7 @@
         <v>1.55</v>
       </c>
       <c r="AP210">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ210">
         <v>1.33</v>
@@ -44942,7 +44954,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45229,7 +45241,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ212">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR212">
         <v>1.95</v>
@@ -45641,7 +45653,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ214">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR214">
         <v>1.73</v>
@@ -45766,7 +45778,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46384,7 +46396,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46462,7 +46474,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ218">
         <v>1.07</v>
@@ -46590,7 +46602,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46796,7 +46808,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46877,7 +46889,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ220">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -47701,7 +47713,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ224">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR224">
         <v>1.74</v>
@@ -48110,7 +48122,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ226">
         <v>1.57</v>
@@ -48650,7 +48662,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48728,7 +48740,7 @@
         <v>1.3</v>
       </c>
       <c r="AP229">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ229">
         <v>1.23</v>
@@ -48934,7 +48946,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ230">
         <v>1.2</v>
@@ -49268,7 +49280,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49886,7 +49898,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -49964,10 +49976,10 @@
         <v>0.82</v>
       </c>
       <c r="AP235">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ235">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR235">
         <v>1.73</v>
@@ -50092,7 +50104,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50504,7 +50516,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50997,7 +51009,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ240">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR240">
         <v>1.82</v>
@@ -51203,7 +51215,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ241">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR241">
         <v>1.34</v>
@@ -51328,7 +51340,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51534,7 +51546,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51740,7 +51752,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51821,7 +51833,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ244">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR244">
         <v>1.44</v>
@@ -52358,7 +52370,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52564,7 +52576,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52642,7 +52654,7 @@
         <v>2.08</v>
       </c>
       <c r="AP248">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ248">
         <v>2.13</v>
@@ -53054,10 +53066,10 @@
         <v>0.42</v>
       </c>
       <c r="AP250">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ250">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR250">
         <v>1.71</v>
@@ -54006,7 +54018,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54496,7 +54508,7 @@
         <v>1.42</v>
       </c>
       <c r="AP257">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ257">
         <v>1.29</v>
@@ -54911,7 +54923,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ259">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR259">
         <v>1.5</v>
@@ -55117,7 +55129,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ260">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR260">
         <v>1.97</v>
@@ -55242,7 +55254,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55448,7 +55460,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55654,7 +55666,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55860,7 +55872,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56066,7 +56078,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56272,7 +56284,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56478,7 +56490,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56684,7 +56696,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56762,10 +56774,10 @@
         <v>1.69</v>
       </c>
       <c r="AP268">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ268">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR268">
         <v>1.52</v>
@@ -56968,7 +56980,7 @@
         <v>1.33</v>
       </c>
       <c r="AP269">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ269">
         <v>1.23</v>
@@ -57096,7 +57108,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57174,7 +57186,7 @@
         <v>0.92</v>
       </c>
       <c r="AP270">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="AQ270">
         <v>1.07</v>
@@ -57302,7 +57314,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57380,7 +57392,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP271">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ271">
         <v>0.8</v>
@@ -57714,7 +57726,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58126,7 +58138,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58207,7 +58219,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ275">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR275">
         <v>1.86</v>
@@ -58332,7 +58344,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58410,7 +58422,7 @@
         <v>1.14</v>
       </c>
       <c r="AP276">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ276">
         <v>1.13</v>
@@ -58538,7 +58550,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58744,7 +58756,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58950,7 +58962,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59028,10 +59040,10 @@
         <v>0.46</v>
       </c>
       <c r="AP279">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AQ279">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AR279">
         <v>1.4</v>
@@ -59237,7 +59249,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ280">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AR280">
         <v>1.78</v>
@@ -59362,7 +59374,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59568,7 +59580,7 @@
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q282">
         <v>1.73</v>
@@ -60392,7 +60404,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60473,7 +60485,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ286">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR286">
         <v>1.39</v>
@@ -60598,7 +60610,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61167,6 +61179,830 @@
       </c>
       <c r="BP289">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7465723</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45726.66666666666</v>
+      </c>
+      <c r="F290">
+        <v>31</v>
+      </c>
+      <c r="G290" t="s">
+        <v>79</v>
+      </c>
+      <c r="H290" t="s">
+        <v>74</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>2</v>
+      </c>
+      <c r="M290">
+        <v>2</v>
+      </c>
+      <c r="N290">
+        <v>4</v>
+      </c>
+      <c r="O290" t="s">
+        <v>286</v>
+      </c>
+      <c r="P290" t="s">
+        <v>421</v>
+      </c>
+      <c r="Q290">
+        <v>2.5</v>
+      </c>
+      <c r="R290">
+        <v>2.5</v>
+      </c>
+      <c r="S290">
+        <v>3.6</v>
+      </c>
+      <c r="T290">
+        <v>1.25</v>
+      </c>
+      <c r="U290">
+        <v>3.75</v>
+      </c>
+      <c r="V290">
+        <v>2.2</v>
+      </c>
+      <c r="W290">
+        <v>1.62</v>
+      </c>
+      <c r="X290">
+        <v>5</v>
+      </c>
+      <c r="Y290">
+        <v>1.17</v>
+      </c>
+      <c r="Z290">
+        <v>1.99</v>
+      </c>
+      <c r="AA290">
+        <v>3.93</v>
+      </c>
+      <c r="AB290">
+        <v>3.34</v>
+      </c>
+      <c r="AC290">
+        <v>1.01</v>
+      </c>
+      <c r="AD290">
+        <v>15</v>
+      </c>
+      <c r="AE290">
+        <v>1.18</v>
+      </c>
+      <c r="AF290">
+        <v>4.75</v>
+      </c>
+      <c r="AG290">
+        <v>1.5</v>
+      </c>
+      <c r="AH290">
+        <v>2.5</v>
+      </c>
+      <c r="AI290">
+        <v>1.44</v>
+      </c>
+      <c r="AJ290">
+        <v>2.63</v>
+      </c>
+      <c r="AK290">
+        <v>1.31</v>
+      </c>
+      <c r="AL290">
+        <v>1.26</v>
+      </c>
+      <c r="AM290">
+        <v>1.77</v>
+      </c>
+      <c r="AN290">
+        <v>0.57</v>
+      </c>
+      <c r="AO290">
+        <v>0.5</v>
+      </c>
+      <c r="AP290">
+        <v>0.6</v>
+      </c>
+      <c r="AQ290">
+        <v>0.53</v>
+      </c>
+      <c r="AR290">
+        <v>1.6</v>
+      </c>
+      <c r="AS290">
+        <v>1.06</v>
+      </c>
+      <c r="AT290">
+        <v>2.66</v>
+      </c>
+      <c r="AU290">
+        <v>10</v>
+      </c>
+      <c r="AV290">
+        <v>8</v>
+      </c>
+      <c r="AW290">
+        <v>7</v>
+      </c>
+      <c r="AX290">
+        <v>5</v>
+      </c>
+      <c r="AY290">
+        <v>17</v>
+      </c>
+      <c r="AZ290">
+        <v>13</v>
+      </c>
+      <c r="BA290">
+        <v>3</v>
+      </c>
+      <c r="BB290">
+        <v>6</v>
+      </c>
+      <c r="BC290">
+        <v>9</v>
+      </c>
+      <c r="BD290">
+        <v>1.78</v>
+      </c>
+      <c r="BE290">
+        <v>8.6</v>
+      </c>
+      <c r="BF290">
+        <v>2.34</v>
+      </c>
+      <c r="BG290">
+        <v>1.27</v>
+      </c>
+      <c r="BH290">
+        <v>3.3</v>
+      </c>
+      <c r="BI290">
+        <v>1.31</v>
+      </c>
+      <c r="BJ290">
+        <v>2.92</v>
+      </c>
+      <c r="BK290">
+        <v>1.57</v>
+      </c>
+      <c r="BL290">
+        <v>2.19</v>
+      </c>
+      <c r="BM290">
+        <v>1.98</v>
+      </c>
+      <c r="BN290">
+        <v>1.74</v>
+      </c>
+      <c r="BO290">
+        <v>2.54</v>
+      </c>
+      <c r="BP290">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7465722</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45726.66666666666</v>
+      </c>
+      <c r="F291">
+        <v>31</v>
+      </c>
+      <c r="G291" t="s">
+        <v>84</v>
+      </c>
+      <c r="H291" t="s">
+        <v>75</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>2</v>
+      </c>
+      <c r="L291">
+        <v>0</v>
+      </c>
+      <c r="M291">
+        <v>2</v>
+      </c>
+      <c r="N291">
+        <v>2</v>
+      </c>
+      <c r="O291" t="s">
+        <v>93</v>
+      </c>
+      <c r="P291" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q291">
+        <v>3.25</v>
+      </c>
+      <c r="R291">
+        <v>2.3</v>
+      </c>
+      <c r="S291">
+        <v>2.88</v>
+      </c>
+      <c r="T291">
+        <v>1.33</v>
+      </c>
+      <c r="U291">
+        <v>3.25</v>
+      </c>
+      <c r="V291">
+        <v>2.5</v>
+      </c>
+      <c r="W291">
+        <v>1.5</v>
+      </c>
+      <c r="X291">
+        <v>6</v>
+      </c>
+      <c r="Y291">
+        <v>1.13</v>
+      </c>
+      <c r="Z291">
+        <v>2.83</v>
+      </c>
+      <c r="AA291">
+        <v>3.71</v>
+      </c>
+      <c r="AB291">
+        <v>2.32</v>
+      </c>
+      <c r="AC291">
+        <v>1.04</v>
+      </c>
+      <c r="AD291">
+        <v>10</v>
+      </c>
+      <c r="AE291">
+        <v>1.2</v>
+      </c>
+      <c r="AF291">
+        <v>4.33</v>
+      </c>
+      <c r="AG291">
+        <v>1.65</v>
+      </c>
+      <c r="AH291">
+        <v>2.2</v>
+      </c>
+      <c r="AI291">
+        <v>1.57</v>
+      </c>
+      <c r="AJ291">
+        <v>2.25</v>
+      </c>
+      <c r="AK291">
+        <v>1.57</v>
+      </c>
+      <c r="AL291">
+        <v>1.27</v>
+      </c>
+      <c r="AM291">
+        <v>1.42</v>
+      </c>
+      <c r="AN291">
+        <v>0.71</v>
+      </c>
+      <c r="AO291">
+        <v>0.93</v>
+      </c>
+      <c r="AP291">
+        <v>0.67</v>
+      </c>
+      <c r="AQ291">
+        <v>1.07</v>
+      </c>
+      <c r="AR291">
+        <v>1.47</v>
+      </c>
+      <c r="AS291">
+        <v>1.5</v>
+      </c>
+      <c r="AT291">
+        <v>2.97</v>
+      </c>
+      <c r="AU291">
+        <v>4</v>
+      </c>
+      <c r="AV291">
+        <v>7</v>
+      </c>
+      <c r="AW291">
+        <v>2</v>
+      </c>
+      <c r="AX291">
+        <v>9</v>
+      </c>
+      <c r="AY291">
+        <v>6</v>
+      </c>
+      <c r="AZ291">
+        <v>19</v>
+      </c>
+      <c r="BA291">
+        <v>2</v>
+      </c>
+      <c r="BB291">
+        <v>9</v>
+      </c>
+      <c r="BC291">
+        <v>11</v>
+      </c>
+      <c r="BD291">
+        <v>2.57</v>
+      </c>
+      <c r="BE291">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF291">
+        <v>1.66</v>
+      </c>
+      <c r="BG291">
+        <v>1.24</v>
+      </c>
+      <c r="BH291">
+        <v>3.55</v>
+      </c>
+      <c r="BI291">
+        <v>1.29</v>
+      </c>
+      <c r="BJ291">
+        <v>3.04</v>
+      </c>
+      <c r="BK291">
+        <v>1.55</v>
+      </c>
+      <c r="BL291">
+        <v>2.23</v>
+      </c>
+      <c r="BM291">
+        <v>1.94</v>
+      </c>
+      <c r="BN291">
+        <v>1.77</v>
+      </c>
+      <c r="BO291">
+        <v>2.48</v>
+      </c>
+      <c r="BP291">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7465726</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45726.66666666666</v>
+      </c>
+      <c r="F292">
+        <v>31</v>
+      </c>
+      <c r="G292" t="s">
+        <v>87</v>
+      </c>
+      <c r="H292" t="s">
+        <v>86</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>1</v>
+      </c>
+      <c r="L292">
+        <v>1</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
+      </c>
+      <c r="N292">
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
+        <v>168</v>
+      </c>
+      <c r="P292" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q292">
+        <v>2</v>
+      </c>
+      <c r="R292">
+        <v>2.63</v>
+      </c>
+      <c r="S292">
+        <v>5</v>
+      </c>
+      <c r="T292">
+        <v>1.25</v>
+      </c>
+      <c r="U292">
+        <v>3.75</v>
+      </c>
+      <c r="V292">
+        <v>2.1</v>
+      </c>
+      <c r="W292">
+        <v>1.67</v>
+      </c>
+      <c r="X292">
+        <v>4.5</v>
+      </c>
+      <c r="Y292">
+        <v>1.18</v>
+      </c>
+      <c r="Z292">
+        <v>1.58</v>
+      </c>
+      <c r="AA292">
+        <v>4.49</v>
+      </c>
+      <c r="AB292">
+        <v>4.84</v>
+      </c>
+      <c r="AC292">
+        <v>1.01</v>
+      </c>
+      <c r="AD292">
+        <v>17</v>
+      </c>
+      <c r="AE292">
+        <v>1.14</v>
+      </c>
+      <c r="AF292">
+        <v>5.5</v>
+      </c>
+      <c r="AG292">
+        <v>1.44</v>
+      </c>
+      <c r="AH292">
+        <v>2.7</v>
+      </c>
+      <c r="AI292">
+        <v>1.57</v>
+      </c>
+      <c r="AJ292">
+        <v>2.25</v>
+      </c>
+      <c r="AK292">
+        <v>1.14</v>
+      </c>
+      <c r="AL292">
+        <v>1.19</v>
+      </c>
+      <c r="AM292">
+        <v>2.5</v>
+      </c>
+      <c r="AN292">
+        <v>1.43</v>
+      </c>
+      <c r="AO292">
+        <v>1.67</v>
+      </c>
+      <c r="AP292">
+        <v>1.53</v>
+      </c>
+      <c r="AQ292">
+        <v>1.56</v>
+      </c>
+      <c r="AR292">
+        <v>1.8</v>
+      </c>
+      <c r="AS292">
+        <v>1.32</v>
+      </c>
+      <c r="AT292">
+        <v>3.12</v>
+      </c>
+      <c r="AU292">
+        <v>5</v>
+      </c>
+      <c r="AV292">
+        <v>2</v>
+      </c>
+      <c r="AW292">
+        <v>14</v>
+      </c>
+      <c r="AX292">
+        <v>4</v>
+      </c>
+      <c r="AY292">
+        <v>19</v>
+      </c>
+      <c r="AZ292">
+        <v>6</v>
+      </c>
+      <c r="BA292">
+        <v>5</v>
+      </c>
+      <c r="BB292">
+        <v>2</v>
+      </c>
+      <c r="BC292">
+        <v>7</v>
+      </c>
+      <c r="BD292">
+        <v>1.36</v>
+      </c>
+      <c r="BE292">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF292">
+        <v>3.72</v>
+      </c>
+      <c r="BG292">
+        <v>1.24</v>
+      </c>
+      <c r="BH292">
+        <v>3.55</v>
+      </c>
+      <c r="BI292">
+        <v>1.26</v>
+      </c>
+      <c r="BJ292">
+        <v>3.22</v>
+      </c>
+      <c r="BK292">
+        <v>1.49</v>
+      </c>
+      <c r="BL292">
+        <v>2.38</v>
+      </c>
+      <c r="BM292">
+        <v>1.84</v>
+      </c>
+      <c r="BN292">
+        <v>1.86</v>
+      </c>
+      <c r="BO292">
+        <v>2.32</v>
+      </c>
+      <c r="BP292">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7465719</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45726.66666666666</v>
+      </c>
+      <c r="F293">
+        <v>31</v>
+      </c>
+      <c r="G293" t="s">
+        <v>83</v>
+      </c>
+      <c r="H293" t="s">
+        <v>85</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293">
+        <v>2</v>
+      </c>
+      <c r="L293">
+        <v>3</v>
+      </c>
+      <c r="M293">
+        <v>1</v>
+      </c>
+      <c r="N293">
+        <v>4</v>
+      </c>
+      <c r="O293" t="s">
+        <v>287</v>
+      </c>
+      <c r="P293" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q293">
+        <v>2.05</v>
+      </c>
+      <c r="R293">
+        <v>2.4</v>
+      </c>
+      <c r="S293">
+        <v>5.5</v>
+      </c>
+      <c r="T293">
+        <v>1.3</v>
+      </c>
+      <c r="U293">
+        <v>3.4</v>
+      </c>
+      <c r="V293">
+        <v>2.5</v>
+      </c>
+      <c r="W293">
+        <v>1.5</v>
+      </c>
+      <c r="X293">
+        <v>6</v>
+      </c>
+      <c r="Y293">
+        <v>1.13</v>
+      </c>
+      <c r="Z293">
+        <v>1.52</v>
+      </c>
+      <c r="AA293">
+        <v>4.37</v>
+      </c>
+      <c r="AB293">
+        <v>5.72</v>
+      </c>
+      <c r="AC293">
+        <v>1.03</v>
+      </c>
+      <c r="AD293">
+        <v>11</v>
+      </c>
+      <c r="AE293">
+        <v>1.2</v>
+      </c>
+      <c r="AF293">
+        <v>4.33</v>
+      </c>
+      <c r="AG293">
+        <v>1.61</v>
+      </c>
+      <c r="AH293">
+        <v>2.15</v>
+      </c>
+      <c r="AI293">
+        <v>1.73</v>
+      </c>
+      <c r="AJ293">
+        <v>2</v>
+      </c>
+      <c r="AK293">
+        <v>1.14</v>
+      </c>
+      <c r="AL293">
+        <v>1.21</v>
+      </c>
+      <c r="AM293">
+        <v>2.45</v>
+      </c>
+      <c r="AN293">
+        <v>2.14</v>
+      </c>
+      <c r="AO293">
+        <v>1.29</v>
+      </c>
+      <c r="AP293">
+        <v>2.2</v>
+      </c>
+      <c r="AQ293">
+        <v>1.2</v>
+      </c>
+      <c r="AR293">
+        <v>1.94</v>
+      </c>
+      <c r="AS293">
+        <v>1.22</v>
+      </c>
+      <c r="AT293">
+        <v>3.16</v>
+      </c>
+      <c r="AU293">
+        <v>6</v>
+      </c>
+      <c r="AV293">
+        <v>5</v>
+      </c>
+      <c r="AW293">
+        <v>10</v>
+      </c>
+      <c r="AX293">
+        <v>3</v>
+      </c>
+      <c r="AY293">
+        <v>16</v>
+      </c>
+      <c r="AZ293">
+        <v>8</v>
+      </c>
+      <c r="BA293">
+        <v>6</v>
+      </c>
+      <c r="BB293">
+        <v>2</v>
+      </c>
+      <c r="BC293">
+        <v>8</v>
+      </c>
+      <c r="BD293">
+        <v>1.26</v>
+      </c>
+      <c r="BE293">
+        <v>10.75</v>
+      </c>
+      <c r="BF293">
+        <v>4.6</v>
+      </c>
+      <c r="BG293">
+        <v>1.2</v>
+      </c>
+      <c r="BH293">
+        <v>3.95</v>
+      </c>
+      <c r="BI293">
+        <v>1.3</v>
+      </c>
+      <c r="BJ293">
+        <v>2.97</v>
+      </c>
+      <c r="BK293">
+        <v>1.55</v>
+      </c>
+      <c r="BL293">
+        <v>2.23</v>
+      </c>
+      <c r="BM293">
+        <v>1.94</v>
+      </c>
+      <c r="BN293">
+        <v>1.77</v>
+      </c>
+      <c r="BO293">
+        <v>2.48</v>
+      </c>
+      <c r="BP293">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="428">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -880,6 +880,12 @@
     <t>['32', '77', '90+3']</t>
   </si>
   <si>
+    <t>['17', '73', '87']</t>
+  </si>
+  <si>
+    <t>['56', '59', '76']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1284,6 +1290,15 @@
   <si>
     <t>['3', '13']</t>
   </si>
+  <si>
+    <t>['38', '66']</t>
+  </si>
+  <si>
+    <t>['24', '30', '35']</t>
+  </si>
+  <si>
+    <t>['11', '39']</t>
+  </si>
 </sst>
 </file>
 
@@ -1644,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP293"/>
+  <dimension ref="A1:BP297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2106,7 +2121,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2312,7 +2327,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2724,7 +2739,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2930,7 +2945,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3011,7 +3026,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ7">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3136,7 +3151,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3214,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ8">
         <v>1.23</v>
@@ -3342,7 +3357,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3754,7 +3769,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4166,7 +4181,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4450,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ14">
         <v>0.53</v>
@@ -4784,7 +4799,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5071,7 +5086,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5483,7 +5498,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ19">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5608,7 +5623,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5686,10 +5701,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ20">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5892,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21">
         <v>0.53</v>
@@ -6307,7 +6322,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ23">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6638,7 +6653,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6844,7 +6859,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6922,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ26">
         <v>1.87</v>
@@ -7050,7 +7065,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7462,7 +7477,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7874,7 +7889,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -7955,7 +7970,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ31">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -8367,7 +8382,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ33">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8492,7 +8507,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8698,7 +8713,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8779,7 +8794,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ35">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -9316,7 +9331,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9394,7 +9409,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ38">
         <v>1.33</v>
@@ -9522,7 +9537,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9600,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39">
         <v>1.2</v>
@@ -9806,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ40">
         <v>0.53</v>
@@ -9934,7 +9949,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10012,7 +10027,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ41">
         <v>1.07</v>
@@ -10758,7 +10773,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10964,7 +10979,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11376,7 +11391,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11788,7 +11803,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11869,7 +11884,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ50">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -11994,7 +12009,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12075,7 +12090,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ51">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -12200,7 +12215,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -13024,7 +13039,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13436,7 +13451,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13926,7 +13941,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ60">
         <v>1.56</v>
@@ -14054,7 +14069,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14132,10 +14147,10 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14260,7 +14275,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14466,7 +14481,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14753,7 +14768,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ64">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -14956,10 +14971,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ65">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15084,7 +15099,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15368,7 +15383,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ67">
         <v>0.53</v>
@@ -15496,7 +15511,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15702,7 +15717,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15908,7 +15923,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16114,7 +16129,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16320,7 +16335,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16398,7 +16413,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ72">
         <v>1.23</v>
@@ -16526,7 +16541,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16732,7 +16747,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16813,7 +16828,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ74">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -16938,7 +16953,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17016,7 +17031,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ75">
         <v>0.57</v>
@@ -17556,7 +17571,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17762,7 +17777,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17843,7 +17858,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ79">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18046,7 +18061,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ80">
         <v>1.56</v>
@@ -18174,7 +18189,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18255,7 +18270,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ81">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18586,7 +18601,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18792,7 +18807,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19076,7 +19091,7 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -19285,7 +19300,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19410,7 +19425,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20028,7 +20043,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20440,7 +20455,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20852,7 +20867,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20933,7 +20948,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ94">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -21058,7 +21073,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21264,7 +21279,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21345,7 +21360,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ96">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21470,7 +21485,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21754,7 +21769,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ98">
         <v>0.57</v>
@@ -21882,7 +21897,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21963,7 +21978,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ99">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22294,7 +22309,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22500,7 +22515,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22784,7 +22799,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ103">
         <v>1.13</v>
@@ -22912,7 +22927,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23196,7 +23211,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
         <v>1.57</v>
@@ -23324,7 +23339,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -24023,7 +24038,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ109">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -24148,7 +24163,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24354,7 +24369,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24432,7 +24447,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ111">
         <v>1.2</v>
@@ -24560,7 +24575,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24638,7 +24653,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ112">
         <v>1.07</v>
@@ -25050,7 +25065,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ114">
         <v>1.53</v>
@@ -25178,7 +25193,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25256,7 +25271,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ115">
         <v>0.8</v>
@@ -25384,7 +25399,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25465,7 +25480,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25590,7 +25605,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25796,7 +25811,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26002,7 +26017,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26208,7 +26223,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26289,7 +26304,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ120">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26414,7 +26429,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26495,7 +26510,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ121">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26620,7 +26635,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26826,7 +26841,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26904,7 +26919,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ123">
         <v>1.23</v>
@@ -27032,7 +27047,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27238,7 +27253,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27856,7 +27871,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28268,7 +28283,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28474,7 +28489,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28555,7 +28570,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ131">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28967,7 +28982,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ133">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -29504,7 +29519,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29994,7 +30009,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ138">
         <v>1.07</v>
@@ -30200,7 +30215,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ139">
         <v>0.57</v>
@@ -30406,10 +30421,10 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ140">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -30615,7 +30630,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -31152,7 +31167,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31358,7 +31373,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31564,7 +31579,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31645,7 +31660,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ146">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31770,7 +31785,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31976,7 +31991,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32260,10 +32275,10 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ149">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32388,7 +32403,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32594,7 +32609,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33006,7 +33021,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33212,7 +33227,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33293,7 +33308,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ154">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33418,7 +33433,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33908,7 +33923,7 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ157">
         <v>0.8</v>
@@ -34320,7 +34335,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ159">
         <v>1.07</v>
@@ -34448,7 +34463,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34860,7 +34875,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34938,10 +34953,10 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ162">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35556,7 +35571,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ165">
         <v>1.87</v>
@@ -35684,7 +35699,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35971,7 +35986,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ167">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -36508,7 +36523,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36714,7 +36729,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37126,7 +37141,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37413,7 +37428,7 @@
         <v>2</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -37616,10 +37631,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ175">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -37950,7 +37965,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38156,7 +38171,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38440,7 +38455,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ179">
         <v>1.07</v>
@@ -38568,7 +38583,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38774,7 +38789,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39061,7 +39076,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ182">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39264,7 +39279,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ183">
         <v>1.56</v>
@@ -39392,7 +39407,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39473,7 +39488,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ184">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39598,7 +39613,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39804,7 +39819,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40294,7 +40309,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ188">
         <v>0.53</v>
@@ -40422,7 +40437,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41040,7 +41055,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41121,7 +41136,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ192">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41246,7 +41261,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41452,7 +41467,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41533,7 +41548,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ194">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41658,7 +41673,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41864,7 +41879,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42354,7 +42369,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ198">
         <v>1.07</v>
@@ -42482,7 +42497,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42563,7 +42578,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ199">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42766,7 +42781,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ200">
         <v>0.53</v>
@@ -42894,7 +42909,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42972,7 +42987,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ201">
         <v>1.13</v>
@@ -43512,7 +43527,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43924,7 +43939,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44130,7 +44145,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44417,7 +44432,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ208">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR208">
         <v>1.58</v>
@@ -44542,7 +44557,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44954,7 +44969,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45035,7 +45050,7 @@
         <v>2</v>
       </c>
       <c r="AQ211">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR211">
         <v>1.87</v>
@@ -45238,7 +45253,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ212">
         <v>1.07</v>
@@ -45444,10 +45459,10 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ213">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR213">
         <v>1.86</v>
@@ -45778,7 +45793,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46062,7 +46077,7 @@
         <v>2.2</v>
       </c>
       <c r="AP216">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ216">
         <v>2.13</v>
@@ -46268,7 +46283,7 @@
         <v>1.18</v>
       </c>
       <c r="AP217">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ217">
         <v>0.93</v>
@@ -46396,7 +46411,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46602,7 +46617,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46808,7 +46823,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47092,7 +47107,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP221">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ221">
         <v>0.57</v>
@@ -47298,7 +47313,7 @@
         <v>0.64</v>
       </c>
       <c r="AP222">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ222">
         <v>0.53</v>
@@ -47507,7 +47522,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ223">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR223">
         <v>1.66</v>
@@ -48331,7 +48346,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ227">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR227">
         <v>1.46</v>
@@ -48662,7 +48677,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48949,7 +48964,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ230">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR230">
         <v>1.75</v>
@@ -49280,7 +49295,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49770,7 +49785,7 @@
         <v>1.67</v>
       </c>
       <c r="AP234">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ234">
         <v>1.53</v>
@@ -49898,7 +49913,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50104,7 +50119,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50391,7 +50406,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ237">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR237">
         <v>1.48</v>
@@ -50516,7 +50531,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51340,7 +51355,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51418,10 +51433,10 @@
         <v>1.17</v>
       </c>
       <c r="AP242">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ242">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR242">
         <v>1.93</v>
@@ -51546,7 +51561,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51624,7 +51639,7 @@
         <v>1.18</v>
       </c>
       <c r="AP243">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ243">
         <v>1.57</v>
@@ -51752,7 +51767,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52370,7 +52385,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52448,7 +52463,7 @@
         <v>1.42</v>
       </c>
       <c r="AP247">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ247">
         <v>1.33</v>
@@ -52576,7 +52591,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52863,7 +52878,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ249">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR249">
         <v>1.74</v>
@@ -53481,7 +53496,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ252">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR252">
         <v>1.77</v>
@@ -53684,7 +53699,7 @@
         <v>0.75</v>
       </c>
       <c r="AP253">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ253">
         <v>0.8</v>
@@ -54018,7 +54033,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54511,7 +54526,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ257">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR257">
         <v>1.84</v>
@@ -54717,7 +54732,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ258">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR258">
         <v>1.81</v>
@@ -55126,7 +55141,7 @@
         <v>1.42</v>
       </c>
       <c r="AP260">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ260">
         <v>1.2</v>
@@ -55254,7 +55269,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55460,7 +55475,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55541,7 +55556,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ262">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR262">
         <v>1.47</v>
@@ -55666,7 +55681,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55872,7 +55887,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56078,7 +56093,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56284,7 +56299,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56365,7 +56380,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ266">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR266">
         <v>1.52</v>
@@ -56490,7 +56505,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56568,7 +56583,7 @@
         <v>2.15</v>
       </c>
       <c r="AP267">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ267">
         <v>2.13</v>
@@ -56696,7 +56711,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -57108,7 +57123,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57314,7 +57329,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57601,7 +57616,7 @@
         <v>2</v>
       </c>
       <c r="AQ272">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AR272">
         <v>1.69</v>
@@ -57726,7 +57741,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -57804,10 +57819,10 @@
         <v>1.38</v>
       </c>
       <c r="AP273">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AQ273">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR273">
         <v>1.87</v>
@@ -58138,7 +58153,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58216,7 +58231,7 @@
         <v>1.38</v>
       </c>
       <c r="AP275">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ275">
         <v>1.2</v>
@@ -58344,7 +58359,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58550,7 +58565,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58628,7 +58643,7 @@
         <v>1.43</v>
       </c>
       <c r="AP277">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ277">
         <v>1.53</v>
@@ -58756,7 +58771,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58837,7 +58852,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ278">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR278">
         <v>1.75</v>
@@ -58962,7 +58977,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59374,7 +59389,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59580,7 +59595,7 @@
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q282">
         <v>1.73</v>
@@ -59658,7 +59673,7 @@
         <v>1</v>
       </c>
       <c r="AP282">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ282">
         <v>0.93</v>
@@ -60404,7 +60419,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60610,7 +60625,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61228,7 +61243,7 @@
         <v>286</v>
       </c>
       <c r="P290" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q290">
         <v>2.5</v>
@@ -61434,7 +61449,7 @@
         <v>93</v>
       </c>
       <c r="P291" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q291">
         <v>3.25</v>
@@ -62003,6 +62018,830 @@
       </c>
       <c r="BP293">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7465721</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45727.66666666666</v>
+      </c>
+      <c r="F294">
+        <v>31</v>
+      </c>
+      <c r="G294" t="s">
+        <v>89</v>
+      </c>
+      <c r="H294" t="s">
+        <v>71</v>
+      </c>
+      <c r="I294">
+        <v>0</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>0</v>
+      </c>
+      <c r="M294">
+        <v>2</v>
+      </c>
+      <c r="N294">
+        <v>2</v>
+      </c>
+      <c r="O294" t="s">
+        <v>93</v>
+      </c>
+      <c r="P294" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q294">
+        <v>3.6</v>
+      </c>
+      <c r="R294">
+        <v>2.38</v>
+      </c>
+      <c r="S294">
+        <v>2.63</v>
+      </c>
+      <c r="T294">
+        <v>1.29</v>
+      </c>
+      <c r="U294">
+        <v>3.5</v>
+      </c>
+      <c r="V294">
+        <v>2.38</v>
+      </c>
+      <c r="W294">
+        <v>1.53</v>
+      </c>
+      <c r="X294">
+        <v>5.5</v>
+      </c>
+      <c r="Y294">
+        <v>1.14</v>
+      </c>
+      <c r="Z294">
+        <v>3.35</v>
+      </c>
+      <c r="AA294">
+        <v>3.73</v>
+      </c>
+      <c r="AB294">
+        <v>2.04</v>
+      </c>
+      <c r="AC294">
+        <v>1.04</v>
+      </c>
+      <c r="AD294">
+        <v>10</v>
+      </c>
+      <c r="AE294">
+        <v>1.2</v>
+      </c>
+      <c r="AF294">
+        <v>4.5</v>
+      </c>
+      <c r="AG294">
+        <v>1.57</v>
+      </c>
+      <c r="AH294">
+        <v>2.35</v>
+      </c>
+      <c r="AI294">
+        <v>1.5</v>
+      </c>
+      <c r="AJ294">
+        <v>2.5</v>
+      </c>
+      <c r="AK294">
+        <v>1.66</v>
+      </c>
+      <c r="AL294">
+        <v>1.26</v>
+      </c>
+      <c r="AM294">
+        <v>1.37</v>
+      </c>
+      <c r="AN294">
+        <v>1.36</v>
+      </c>
+      <c r="AO294">
+        <v>1.79</v>
+      </c>
+      <c r="AP294">
+        <v>1.27</v>
+      </c>
+      <c r="AQ294">
+        <v>1.87</v>
+      </c>
+      <c r="AR294">
+        <v>1.66</v>
+      </c>
+      <c r="AS294">
+        <v>1.56</v>
+      </c>
+      <c r="AT294">
+        <v>3.22</v>
+      </c>
+      <c r="AU294">
+        <v>7</v>
+      </c>
+      <c r="AV294">
+        <v>8</v>
+      </c>
+      <c r="AW294">
+        <v>4</v>
+      </c>
+      <c r="AX294">
+        <v>6</v>
+      </c>
+      <c r="AY294">
+        <v>11</v>
+      </c>
+      <c r="AZ294">
+        <v>14</v>
+      </c>
+      <c r="BA294">
+        <v>4</v>
+      </c>
+      <c r="BB294">
+        <v>7</v>
+      </c>
+      <c r="BC294">
+        <v>11</v>
+      </c>
+      <c r="BD294">
+        <v>2.11</v>
+      </c>
+      <c r="BE294">
+        <v>8.6</v>
+      </c>
+      <c r="BF294">
+        <v>1.94</v>
+      </c>
+      <c r="BG294">
+        <v>1.24</v>
+      </c>
+      <c r="BH294">
+        <v>3.55</v>
+      </c>
+      <c r="BI294">
+        <v>1.28</v>
+      </c>
+      <c r="BJ294">
+        <v>3.05</v>
+      </c>
+      <c r="BK294">
+        <v>1.53</v>
+      </c>
+      <c r="BL294">
+        <v>2.28</v>
+      </c>
+      <c r="BM294">
+        <v>1.92</v>
+      </c>
+      <c r="BN294">
+        <v>1.79</v>
+      </c>
+      <c r="BO294">
+        <v>2.45</v>
+      </c>
+      <c r="BP294">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7465717</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45727.66666666666</v>
+      </c>
+      <c r="F295">
+        <v>31</v>
+      </c>
+      <c r="G295" t="s">
+        <v>76</v>
+      </c>
+      <c r="H295" t="s">
+        <v>78</v>
+      </c>
+      <c r="I295">
+        <v>0</v>
+      </c>
+      <c r="J295">
+        <v>3</v>
+      </c>
+      <c r="K295">
+        <v>3</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295">
+        <v>3</v>
+      </c>
+      <c r="N295">
+        <v>3</v>
+      </c>
+      <c r="O295" t="s">
+        <v>93</v>
+      </c>
+      <c r="P295" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q295">
+        <v>2</v>
+      </c>
+      <c r="R295">
+        <v>2.63</v>
+      </c>
+      <c r="S295">
+        <v>5</v>
+      </c>
+      <c r="T295">
+        <v>1.22</v>
+      </c>
+      <c r="U295">
+        <v>4</v>
+      </c>
+      <c r="V295">
+        <v>2.1</v>
+      </c>
+      <c r="W295">
+        <v>1.67</v>
+      </c>
+      <c r="X295">
+        <v>4.5</v>
+      </c>
+      <c r="Y295">
+        <v>1.18</v>
+      </c>
+      <c r="Z295">
+        <v>1.52</v>
+      </c>
+      <c r="AA295">
+        <v>4.65</v>
+      </c>
+      <c r="AB295">
+        <v>5.29</v>
+      </c>
+      <c r="AC295">
+        <v>1.01</v>
+      </c>
+      <c r="AD295">
+        <v>17</v>
+      </c>
+      <c r="AE295">
+        <v>1.12</v>
+      </c>
+      <c r="AF295">
+        <v>5.75</v>
+      </c>
+      <c r="AG295">
+        <v>1.44</v>
+      </c>
+      <c r="AH295">
+        <v>2.7</v>
+      </c>
+      <c r="AI295">
+        <v>1.53</v>
+      </c>
+      <c r="AJ295">
+        <v>2.38</v>
+      </c>
+      <c r="AK295">
+        <v>1.15</v>
+      </c>
+      <c r="AL295">
+        <v>1.19</v>
+      </c>
+      <c r="AM295">
+        <v>2.4</v>
+      </c>
+      <c r="AN295">
+        <v>2.2</v>
+      </c>
+      <c r="AO295">
+        <v>1.07</v>
+      </c>
+      <c r="AP295">
+        <v>2.06</v>
+      </c>
+      <c r="AQ295">
+        <v>1.2</v>
+      </c>
+      <c r="AR295">
+        <v>1.84</v>
+      </c>
+      <c r="AS295">
+        <v>1.3</v>
+      </c>
+      <c r="AT295">
+        <v>3.14</v>
+      </c>
+      <c r="AU295">
+        <v>4</v>
+      </c>
+      <c r="AV295">
+        <v>7</v>
+      </c>
+      <c r="AW295">
+        <v>10</v>
+      </c>
+      <c r="AX295">
+        <v>3</v>
+      </c>
+      <c r="AY295">
+        <v>20</v>
+      </c>
+      <c r="AZ295">
+        <v>10</v>
+      </c>
+      <c r="BA295">
+        <v>7</v>
+      </c>
+      <c r="BB295">
+        <v>6</v>
+      </c>
+      <c r="BC295">
+        <v>13</v>
+      </c>
+      <c r="BD295">
+        <v>1.31</v>
+      </c>
+      <c r="BE295">
+        <v>9.9</v>
+      </c>
+      <c r="BF295">
+        <v>4.15</v>
+      </c>
+      <c r="BG295">
+        <v>1.19</v>
+      </c>
+      <c r="BH295">
+        <v>3.75</v>
+      </c>
+      <c r="BI295">
+        <v>1.4</v>
+      </c>
+      <c r="BJ295">
+        <v>2.64</v>
+      </c>
+      <c r="BK295">
+        <v>1.72</v>
+      </c>
+      <c r="BL295">
+        <v>2</v>
+      </c>
+      <c r="BM295">
+        <v>2.15</v>
+      </c>
+      <c r="BN295">
+        <v>1.59</v>
+      </c>
+      <c r="BO295">
+        <v>2.83</v>
+      </c>
+      <c r="BP295">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7465725</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45727.66666666666</v>
+      </c>
+      <c r="F296">
+        <v>31</v>
+      </c>
+      <c r="G296" t="s">
+        <v>82</v>
+      </c>
+      <c r="H296" t="s">
+        <v>72</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>2</v>
+      </c>
+      <c r="K296">
+        <v>3</v>
+      </c>
+      <c r="L296">
+        <v>3</v>
+      </c>
+      <c r="M296">
+        <v>2</v>
+      </c>
+      <c r="N296">
+        <v>5</v>
+      </c>
+      <c r="O296" t="s">
+        <v>288</v>
+      </c>
+      <c r="P296" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q296">
+        <v>2.5</v>
+      </c>
+      <c r="R296">
+        <v>2.3</v>
+      </c>
+      <c r="S296">
+        <v>4</v>
+      </c>
+      <c r="T296">
+        <v>1.33</v>
+      </c>
+      <c r="U296">
+        <v>3.25</v>
+      </c>
+      <c r="V296">
+        <v>2.63</v>
+      </c>
+      <c r="W296">
+        <v>1.44</v>
+      </c>
+      <c r="X296">
+        <v>6.5</v>
+      </c>
+      <c r="Y296">
+        <v>1.11</v>
+      </c>
+      <c r="Z296">
+        <v>1.93</v>
+      </c>
+      <c r="AA296">
+        <v>3.71</v>
+      </c>
+      <c r="AB296">
+        <v>3.73</v>
+      </c>
+      <c r="AC296">
+        <v>1.04</v>
+      </c>
+      <c r="AD296">
+        <v>10</v>
+      </c>
+      <c r="AE296">
+        <v>1.22</v>
+      </c>
+      <c r="AF296">
+        <v>4</v>
+      </c>
+      <c r="AG296">
+        <v>1.67</v>
+      </c>
+      <c r="AH296">
+        <v>2.1</v>
+      </c>
+      <c r="AI296">
+        <v>1.62</v>
+      </c>
+      <c r="AJ296">
+        <v>2.2</v>
+      </c>
+      <c r="AK296">
+        <v>1.28</v>
+      </c>
+      <c r="AL296">
+        <v>1.28</v>
+      </c>
+      <c r="AM296">
+        <v>1.8</v>
+      </c>
+      <c r="AN296">
+        <v>1.79</v>
+      </c>
+      <c r="AO296">
+        <v>1.29</v>
+      </c>
+      <c r="AP296">
+        <v>1.87</v>
+      </c>
+      <c r="AQ296">
+        <v>1.2</v>
+      </c>
+      <c r="AR296">
+        <v>1.99</v>
+      </c>
+      <c r="AS296">
+        <v>1.4</v>
+      </c>
+      <c r="AT296">
+        <v>3.39</v>
+      </c>
+      <c r="AU296">
+        <v>6</v>
+      </c>
+      <c r="AV296">
+        <v>4</v>
+      </c>
+      <c r="AW296">
+        <v>6</v>
+      </c>
+      <c r="AX296">
+        <v>8</v>
+      </c>
+      <c r="AY296">
+        <v>12</v>
+      </c>
+      <c r="AZ296">
+        <v>12</v>
+      </c>
+      <c r="BA296">
+        <v>4</v>
+      </c>
+      <c r="BB296">
+        <v>4</v>
+      </c>
+      <c r="BC296">
+        <v>8</v>
+      </c>
+      <c r="BD296">
+        <v>1.46</v>
+      </c>
+      <c r="BE296">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF296">
+        <v>3.2</v>
+      </c>
+      <c r="BG296">
+        <v>1.29</v>
+      </c>
+      <c r="BH296">
+        <v>3.15</v>
+      </c>
+      <c r="BI296">
+        <v>1.33</v>
+      </c>
+      <c r="BJ296">
+        <v>2.83</v>
+      </c>
+      <c r="BK296">
+        <v>1.6</v>
+      </c>
+      <c r="BL296">
+        <v>2.14</v>
+      </c>
+      <c r="BM296">
+        <v>2.02</v>
+      </c>
+      <c r="BN296">
+        <v>1.71</v>
+      </c>
+      <c r="BO296">
+        <v>2.6</v>
+      </c>
+      <c r="BP296">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7465720</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45727.66666666666</v>
+      </c>
+      <c r="F297">
+        <v>31</v>
+      </c>
+      <c r="G297" t="s">
+        <v>88</v>
+      </c>
+      <c r="H297" t="s">
+        <v>81</v>
+      </c>
+      <c r="I297">
+        <v>0</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>0</v>
+      </c>
+      <c r="L297">
+        <v>3</v>
+      </c>
+      <c r="M297">
+        <v>0</v>
+      </c>
+      <c r="N297">
+        <v>3</v>
+      </c>
+      <c r="O297" t="s">
+        <v>289</v>
+      </c>
+      <c r="P297" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q297">
+        <v>2.3</v>
+      </c>
+      <c r="R297">
+        <v>2.5</v>
+      </c>
+      <c r="S297">
+        <v>4.33</v>
+      </c>
+      <c r="T297">
+        <v>1.29</v>
+      </c>
+      <c r="U297">
+        <v>3.5</v>
+      </c>
+      <c r="V297">
+        <v>2.25</v>
+      </c>
+      <c r="W297">
+        <v>1.57</v>
+      </c>
+      <c r="X297">
+        <v>5.5</v>
+      </c>
+      <c r="Y297">
+        <v>1.14</v>
+      </c>
+      <c r="Z297">
+        <v>1.78</v>
+      </c>
+      <c r="AA297">
+        <v>4.05</v>
+      </c>
+      <c r="AB297">
+        <v>4.02</v>
+      </c>
+      <c r="AC297">
+        <v>1.01</v>
+      </c>
+      <c r="AD297">
+        <v>15</v>
+      </c>
+      <c r="AE297">
+        <v>1.18</v>
+      </c>
+      <c r="AF297">
+        <v>4.75</v>
+      </c>
+      <c r="AG297">
+        <v>1.53</v>
+      </c>
+      <c r="AH297">
+        <v>2.4</v>
+      </c>
+      <c r="AI297">
+        <v>1.5</v>
+      </c>
+      <c r="AJ297">
+        <v>2.5</v>
+      </c>
+      <c r="AK297">
+        <v>1.23</v>
+      </c>
+      <c r="AL297">
+        <v>1.25</v>
+      </c>
+      <c r="AM297">
+        <v>1.95</v>
+      </c>
+      <c r="AN297">
+        <v>2.36</v>
+      </c>
+      <c r="AO297">
+        <v>1.2</v>
+      </c>
+      <c r="AP297">
+        <v>2.4</v>
+      </c>
+      <c r="AQ297">
+        <v>1.13</v>
+      </c>
+      <c r="AR297">
+        <v>1.86</v>
+      </c>
+      <c r="AS297">
+        <v>1.54</v>
+      </c>
+      <c r="AT297">
+        <v>3.4</v>
+      </c>
+      <c r="AU297">
+        <v>7</v>
+      </c>
+      <c r="AV297">
+        <v>5</v>
+      </c>
+      <c r="AW297">
+        <v>5</v>
+      </c>
+      <c r="AX297">
+        <v>9</v>
+      </c>
+      <c r="AY297">
+        <v>12</v>
+      </c>
+      <c r="AZ297">
+        <v>18</v>
+      </c>
+      <c r="BA297">
+        <v>7</v>
+      </c>
+      <c r="BB297">
+        <v>4</v>
+      </c>
+      <c r="BC297">
+        <v>11</v>
+      </c>
+      <c r="BD297">
+        <v>1.91</v>
+      </c>
+      <c r="BE297">
+        <v>8.4</v>
+      </c>
+      <c r="BF297">
+        <v>2.16</v>
+      </c>
+      <c r="BG297">
+        <v>1.21</v>
+      </c>
+      <c r="BH297">
+        <v>3.8</v>
+      </c>
+      <c r="BI297">
+        <v>1.33</v>
+      </c>
+      <c r="BJ297">
+        <v>2.81</v>
+      </c>
+      <c r="BK297">
+        <v>1.62</v>
+      </c>
+      <c r="BL297">
+        <v>2.11</v>
+      </c>
+      <c r="BM297">
+        <v>2.04</v>
+      </c>
+      <c r="BN297">
+        <v>1.69</v>
+      </c>
+      <c r="BO297">
+        <v>2.64</v>
+      </c>
+      <c r="BP297">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="432">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -886,6 +886,21 @@
     <t>['56', '59', '76']</t>
   </si>
   <si>
+    <t>['10', '69', '80']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['28', '40', '58', '89']</t>
+  </si>
+  <si>
+    <t>['7', '90+2']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1054,9 +1069,6 @@
     <t>['9', '13', '23']</t>
   </si>
   <si>
-    <t>['54']</t>
-  </si>
-  <si>
     <t>['48', '88']</t>
   </si>
   <si>
@@ -1100,9 +1112,6 @@
   </si>
   <si>
     <t>['12', '19']</t>
-  </si>
-  <si>
-    <t>['6']</t>
   </si>
   <si>
     <t>['4', '20', '27', '42']</t>
@@ -1298,6 +1307,9 @@
   </si>
   <si>
     <t>['11', '39']</t>
+  </si>
+  <si>
+    <t>['47', '84']</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP297"/>
+  <dimension ref="A1:BP304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1993,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ2">
         <v>1.2</v>
@@ -2121,7 +2133,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2199,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
         <v>1.56</v>
@@ -2327,7 +2339,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2405,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2611,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5">
         <v>2.13</v>
@@ -2739,7 +2751,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2820,7 +2832,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2945,7 +2957,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3023,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ7">
         <v>1.13</v>
@@ -3151,7 +3163,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3232,7 +3244,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3357,7 +3369,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3644,7 +3656,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3769,7 +3781,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4181,7 +4193,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4259,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ13">
         <v>1.53</v>
@@ -4799,7 +4811,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5086,7 +5098,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5289,10 +5301,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ18">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5623,7 +5635,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6319,7 +6331,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ23">
         <v>1.2</v>
@@ -6653,7 +6665,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6734,7 +6746,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ25">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6859,7 +6871,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7065,7 +7077,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7143,7 +7155,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
         <v>0.8</v>
@@ -7349,10 +7361,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7477,7 +7489,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7558,7 +7570,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ29">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7889,7 +7901,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8173,7 +8185,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ32">
         <v>1.53</v>
@@ -8379,10 +8391,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ33">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8507,7 +8519,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8585,7 +8597,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
         <v>0.93</v>
@@ -8713,7 +8725,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8997,10 +9009,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -9203,7 +9215,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ37">
         <v>2.13</v>
@@ -9331,7 +9343,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9412,7 +9424,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9537,7 +9549,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9949,7 +9961,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10439,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ43">
         <v>0.53</v>
@@ -10773,7 +10785,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10854,7 +10866,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ45">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -10979,7 +10991,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11391,7 +11403,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11469,7 +11481,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48">
         <v>1.87</v>
@@ -11675,7 +11687,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ49">
         <v>1.56</v>
@@ -11803,7 +11815,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12009,7 +12021,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12215,7 +12227,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12293,10 +12305,10 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ52">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12502,7 +12514,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ53">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -12708,7 +12720,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ54">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -12914,7 +12926,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ55">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -13039,7 +13051,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13117,7 +13129,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ56">
         <v>1.07</v>
@@ -13323,7 +13335,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ57">
         <v>0.53</v>
@@ -13451,7 +13463,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13738,7 +13750,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ59">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -14069,7 +14081,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14150,7 +14162,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ61">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14275,7 +14287,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14481,7 +14493,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14559,7 +14571,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ63">
         <v>1.87</v>
@@ -15099,7 +15111,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15177,10 +15189,10 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15511,7 +15523,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15589,7 +15601,7 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ68">
         <v>0.8</v>
@@ -15717,7 +15729,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15923,7 +15935,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16129,7 +16141,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16335,7 +16347,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16416,7 +16428,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ72">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16541,7 +16553,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16619,7 +16631,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ73">
         <v>0.53</v>
@@ -16747,7 +16759,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16828,7 +16840,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ74">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -16953,7 +16965,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17034,7 +17046,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ75">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17237,10 +17249,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ76">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17443,7 +17455,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17571,7 +17583,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17777,7 +17789,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18189,7 +18201,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18601,7 +18613,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18679,7 +18691,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ83">
         <v>1.87</v>
@@ -18807,7 +18819,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18888,7 +18900,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -19094,7 +19106,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19425,7 +19437,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19709,7 +19721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ88">
         <v>0.53</v>
@@ -19915,7 +19927,7 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ89">
         <v>0.93</v>
@@ -20043,7 +20055,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20327,7 +20339,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91">
         <v>0.8</v>
@@ -20455,7 +20467,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20533,7 +20545,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ92">
         <v>1.07</v>
@@ -20739,10 +20751,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ93">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -20867,7 +20879,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21073,7 +21085,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21279,7 +21291,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21485,7 +21497,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21772,7 +21784,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ98">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21897,7 +21909,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21975,7 +21987,7 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ99">
         <v>1.87</v>
@@ -22309,7 +22321,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22515,7 +22527,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22802,7 +22814,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ103">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22927,7 +22939,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23008,7 +23020,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23214,7 +23226,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -23339,7 +23351,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>346</v>
+        <v>292</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23417,10 +23429,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ106">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23829,7 +23841,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ108">
         <v>0.53</v>
@@ -24038,7 +24050,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ109">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -24163,7 +24175,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24241,7 +24253,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ110">
         <v>1.07</v>
@@ -24369,7 +24381,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24575,7 +24587,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24859,10 +24871,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ113">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -25193,7 +25205,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25399,7 +25411,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25480,7 +25492,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ116">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25605,7 +25617,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25683,7 +25695,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ117">
         <v>0.93</v>
@@ -25811,7 +25823,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26017,7 +26029,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26223,7 +26235,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26301,7 +26313,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -26429,7 +26441,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26507,7 +26519,7 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ121">
         <v>1.2</v>
@@ -26635,7 +26647,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26841,7 +26853,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26922,7 +26934,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ123">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27047,7 +27059,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27253,7 +27265,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27331,10 +27343,10 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ125">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27537,7 +27549,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ126">
         <v>0.53</v>
@@ -27746,7 +27758,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ127">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27871,7 +27883,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27949,7 +27961,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ128">
         <v>1.87</v>
@@ -28155,10 +28167,10 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ129">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28283,7 +28295,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28489,7 +28501,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28773,7 +28785,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ132">
         <v>1.07</v>
@@ -28982,7 +28994,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ133">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -29519,7 +29531,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29597,7 +29609,7 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ136">
         <v>0.8</v>
@@ -30218,7 +30230,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ139">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30627,7 +30639,7 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ141">
         <v>1.2</v>
@@ -30833,10 +30845,10 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -31039,7 +31051,7 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ143">
         <v>0.53</v>
@@ -31167,7 +31179,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>362</v>
+        <v>291</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31245,7 +31257,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ144">
         <v>1.56</v>
@@ -31373,7 +31385,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31579,7 +31591,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31785,7 +31797,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31863,7 +31875,7 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ147">
         <v>2.13</v>
@@ -31991,7 +32003,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32072,7 +32084,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ148">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32403,7 +32415,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32481,7 +32493,7 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ150">
         <v>1.53</v>
@@ -32609,7 +32621,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32690,7 +32702,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -33021,7 +33033,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33102,7 +33114,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ153">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33227,7 +33239,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33308,7 +33320,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ154">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33433,7 +33445,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33511,7 +33523,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ155">
         <v>0.53</v>
@@ -33717,7 +33729,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ156">
         <v>1.07</v>
@@ -34129,10 +34141,10 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ158">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34463,7 +34475,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34750,7 +34762,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ161">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34875,7 +34887,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35365,7 +35377,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ164">
         <v>0.93</v>
@@ -35699,7 +35711,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35777,7 +35789,7 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ166">
         <v>2.13</v>
@@ -35983,7 +35995,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ167">
         <v>1.2</v>
@@ -36192,7 +36204,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ168">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -36398,7 +36410,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ169">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -36523,7 +36535,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36729,7 +36741,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37141,7 +37153,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37219,7 +37231,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ173">
         <v>1.07</v>
@@ -37425,7 +37437,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ174">
         <v>1.13</v>
@@ -37634,7 +37646,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ175">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -37837,7 +37849,7 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ176">
         <v>1.2</v>
@@ -37965,7 +37977,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38046,7 +38058,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ177">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -38171,7 +38183,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38249,10 +38261,10 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ178">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38583,7 +38595,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38789,7 +38801,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38870,7 +38882,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ181">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -39073,7 +39085,7 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ182">
         <v>1.2</v>
@@ -39407,7 +39419,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39613,7 +39625,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39691,10 +39703,10 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
+        <v>1.07</v>
+      </c>
+      <c r="AQ185">
         <v>1.14</v>
-      </c>
-      <c r="AQ185">
-        <v>1.23</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39819,7 +39831,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40437,7 +40449,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40927,10 +40939,10 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ191">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -41055,7 +41067,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41261,7 +41273,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41467,7 +41479,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41548,7 +41560,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ194">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41673,7 +41685,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41751,7 +41763,7 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195">
         <v>1.53</v>
@@ -41879,7 +41891,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -41957,7 +41969,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ196">
         <v>1.2</v>
@@ -42166,7 +42178,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ197">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42497,7 +42509,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42575,7 +42587,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ199">
         <v>1.13</v>
@@ -42909,7 +42921,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -42990,7 +43002,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ201">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -43527,7 +43539,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43605,7 +43617,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ204">
         <v>1.87</v>
@@ -43811,7 +43823,7 @@
         <v>1.3</v>
       </c>
       <c r="AP205">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ205">
         <v>0.93</v>
@@ -43939,7 +43951,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44017,10 +44029,10 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ206">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -44145,7 +44157,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44557,7 +44569,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44638,7 +44650,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ209">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR209">
         <v>1.37</v>
@@ -44844,7 +44856,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ210">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR210">
         <v>1.76</v>
@@ -44969,7 +44981,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45047,10 +45059,10 @@
         <v>1.3</v>
       </c>
       <c r="AP211">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ211">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR211">
         <v>1.87</v>
@@ -45665,7 +45677,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ214">
         <v>1.2</v>
@@ -45793,7 +45805,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45871,7 +45883,7 @@
         <v>1.55</v>
       </c>
       <c r="AP215">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ215">
         <v>1.53</v>
@@ -46411,7 +46423,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46617,7 +46629,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46695,7 +46707,7 @@
         <v>2.27</v>
       </c>
       <c r="AP219">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ219">
         <v>2.13</v>
@@ -46823,7 +46835,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46901,7 +46913,7 @@
         <v>1.45</v>
       </c>
       <c r="AP220">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ220">
         <v>1.56</v>
@@ -47110,7 +47122,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ221">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR221">
         <v>1.93</v>
@@ -47931,7 +47943,7 @@
         <v>0.82</v>
       </c>
       <c r="AP225">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ225">
         <v>0.8</v>
@@ -48140,7 +48152,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ226">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48343,10 +48355,10 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ227">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR227">
         <v>1.46</v>
@@ -48552,7 +48564,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ228">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR228">
         <v>1.74</v>
@@ -48677,7 +48689,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48758,7 +48770,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ229">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR229">
         <v>1.56</v>
@@ -49167,7 +49179,7 @@
         <v>1</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ231">
         <v>1.07</v>
@@ -49295,7 +49307,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49373,7 +49385,7 @@
         <v>1.08</v>
       </c>
       <c r="AP232">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ232">
         <v>0.93</v>
@@ -49913,7 +49925,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50119,7 +50131,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50197,10 +50209,10 @@
         <v>1.33</v>
       </c>
       <c r="AP236">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ236">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR236">
         <v>1.7</v>
@@ -50531,7 +50543,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50612,7 +50624,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ238">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR238">
         <v>1.84</v>
@@ -50818,7 +50830,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ239">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR239">
         <v>1.78</v>
@@ -51227,7 +51239,7 @@
         <v>0.45</v>
       </c>
       <c r="AP241">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ241">
         <v>0.53</v>
@@ -51355,7 +51367,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51436,7 +51448,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ242">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR242">
         <v>1.93</v>
@@ -51561,7 +51573,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51642,7 +51654,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ243">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR243">
         <v>1.91</v>
@@ -51767,7 +51779,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51845,7 +51857,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ244">
         <v>1.56</v>
@@ -52257,10 +52269,10 @@
         <v>0.45</v>
       </c>
       <c r="AP246">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ246">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR246">
         <v>1.7</v>
@@ -52385,7 +52397,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52466,7 +52478,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ247">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR247">
         <v>1.71</v>
@@ -52591,7 +52603,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52875,7 +52887,7 @@
         <v>1.9</v>
       </c>
       <c r="AP249">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ249">
         <v>1.87</v>
@@ -53287,7 +53299,7 @@
         <v>1.54</v>
       </c>
       <c r="AP251">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ251">
         <v>1.53</v>
@@ -53905,10 +53917,10 @@
         <v>1.23</v>
       </c>
       <c r="AP254">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ254">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR254">
         <v>1.74</v>
@@ -54033,7 +54045,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54111,7 +54123,7 @@
         <v>1.58</v>
       </c>
       <c r="AP255">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ255">
         <v>1.87</v>
@@ -54317,7 +54329,7 @@
         <v>1</v>
       </c>
       <c r="AP256">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ256">
         <v>1.07</v>
@@ -54732,7 +54744,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ258">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR258">
         <v>1.81</v>
@@ -54935,7 +54947,7 @@
         <v>1</v>
       </c>
       <c r="AP259">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ259">
         <v>1.07</v>
@@ -55269,7 +55281,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55347,10 +55359,10 @@
         <v>1.31</v>
       </c>
       <c r="AP261">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ261">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR261">
         <v>1.76</v>
@@ -55475,7 +55487,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55681,7 +55693,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55887,7 +55899,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -55965,10 +55977,10 @@
         <v>0.42</v>
       </c>
       <c r="AP264">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ264">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR264">
         <v>1.35</v>
@@ -56093,7 +56105,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56171,10 +56183,10 @@
         <v>1.33</v>
       </c>
       <c r="AP265">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ265">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR265">
         <v>1.71</v>
@@ -56299,7 +56311,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56377,7 +56389,7 @@
         <v>1.83</v>
       </c>
       <c r="AP266">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ266">
         <v>1.87</v>
@@ -56505,7 +56517,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56711,7 +56723,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -56998,7 +57010,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ269">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR269">
         <v>1.77</v>
@@ -57123,7 +57135,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57329,7 +57341,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57613,7 +57625,7 @@
         <v>1.92</v>
       </c>
       <c r="AP272">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ272">
         <v>1.87</v>
@@ -57741,7 +57753,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58025,7 +58037,7 @@
         <v>0.62</v>
       </c>
       <c r="AP274">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ274">
         <v>0.53</v>
@@ -58153,7 +58165,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58359,7 +58371,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58440,7 +58452,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ276">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AR276">
         <v>1.89</v>
@@ -58565,7 +58577,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58771,7 +58783,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58977,7 +58989,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59261,7 +59273,7 @@
         <v>1.79</v>
       </c>
       <c r="AP280">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ280">
         <v>1.56</v>
@@ -59389,7 +59401,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59595,7 +59607,7 @@
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q282">
         <v>1.73</v>
@@ -60085,7 +60097,7 @@
         <v>0.57</v>
       </c>
       <c r="AP284">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ284">
         <v>0.53</v>
@@ -60291,10 +60303,10 @@
         <v>1.46</v>
       </c>
       <c r="AP285">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ285">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR285">
         <v>1.71</v>
@@ -60419,7 +60431,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60497,7 +60509,7 @@
         <v>0.92</v>
       </c>
       <c r="AP286">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ286">
         <v>1.07</v>
@@ -60625,7 +60637,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -60912,7 +60924,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ288">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AR288">
         <v>1.81</v>
@@ -61118,7 +61130,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ289">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR289">
         <v>1.73</v>
@@ -61243,7 +61255,7 @@
         <v>286</v>
       </c>
       <c r="P290" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q290">
         <v>2.5</v>
@@ -61449,7 +61461,7 @@
         <v>93</v>
       </c>
       <c r="P291" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q291">
         <v>3.25</v>
@@ -62067,7 +62079,7 @@
         <v>93</v>
       </c>
       <c r="P294" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q294">
         <v>3.6</v>
@@ -62273,7 +62285,7 @@
         <v>93</v>
       </c>
       <c r="P295" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62354,7 +62366,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ295">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR295">
         <v>1.84</v>
@@ -62479,7 +62491,7 @@
         <v>288</v>
       </c>
       <c r="P296" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q296">
         <v>2.5</v>
@@ -62842,6 +62854,1448 @@
       </c>
       <c r="BP297">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7465736</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F298">
+        <v>30</v>
+      </c>
+      <c r="G298" t="s">
+        <v>75</v>
+      </c>
+      <c r="H298" t="s">
+        <v>76</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+      <c r="M298">
+        <v>1</v>
+      </c>
+      <c r="N298">
+        <v>1</v>
+      </c>
+      <c r="O298" t="s">
+        <v>93</v>
+      </c>
+      <c r="P298" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q298">
+        <v>3.1</v>
+      </c>
+      <c r="R298">
+        <v>2.3</v>
+      </c>
+      <c r="S298">
+        <v>3.1</v>
+      </c>
+      <c r="T298">
+        <v>1.33</v>
+      </c>
+      <c r="U298">
+        <v>3.25</v>
+      </c>
+      <c r="V298">
+        <v>2.5</v>
+      </c>
+      <c r="W298">
+        <v>1.5</v>
+      </c>
+      <c r="X298">
+        <v>6</v>
+      </c>
+      <c r="Y298">
+        <v>1.13</v>
+      </c>
+      <c r="Z298">
+        <v>2.4</v>
+      </c>
+      <c r="AA298">
+        <v>3.6</v>
+      </c>
+      <c r="AB298">
+        <v>2.4</v>
+      </c>
+      <c r="AC298">
+        <v>1.03</v>
+      </c>
+      <c r="AD298">
+        <v>11</v>
+      </c>
+      <c r="AE298">
+        <v>1.2</v>
+      </c>
+      <c r="AF298">
+        <v>4.33</v>
+      </c>
+      <c r="AG298">
+        <v>1.65</v>
+      </c>
+      <c r="AH298">
+        <v>2.2</v>
+      </c>
+      <c r="AI298">
+        <v>1.57</v>
+      </c>
+      <c r="AJ298">
+        <v>2.25</v>
+      </c>
+      <c r="AK298">
+        <v>1.5</v>
+      </c>
+      <c r="AL298">
+        <v>1.26</v>
+      </c>
+      <c r="AM298">
+        <v>1.5</v>
+      </c>
+      <c r="AN298">
+        <v>1.27</v>
+      </c>
+      <c r="AO298">
+        <v>1.57</v>
+      </c>
+      <c r="AP298">
+        <v>1.19</v>
+      </c>
+      <c r="AQ298">
+        <v>1.67</v>
+      </c>
+      <c r="AR298">
+        <v>1.72</v>
+      </c>
+      <c r="AS298">
+        <v>1.54</v>
+      </c>
+      <c r="AT298">
+        <v>3.26</v>
+      </c>
+      <c r="AU298">
+        <v>3</v>
+      </c>
+      <c r="AV298">
+        <v>4</v>
+      </c>
+      <c r="AW298">
+        <v>5</v>
+      </c>
+      <c r="AX298">
+        <v>2</v>
+      </c>
+      <c r="AY298">
+        <v>8</v>
+      </c>
+      <c r="AZ298">
+        <v>6</v>
+      </c>
+      <c r="BA298">
+        <v>2</v>
+      </c>
+      <c r="BB298">
+        <v>2</v>
+      </c>
+      <c r="BC298">
+        <v>4</v>
+      </c>
+      <c r="BD298">
+        <v>1.89</v>
+      </c>
+      <c r="BE298">
+        <v>6.4</v>
+      </c>
+      <c r="BF298">
+        <v>2.1</v>
+      </c>
+      <c r="BG298">
+        <v>1.27</v>
+      </c>
+      <c r="BH298">
+        <v>3.3</v>
+      </c>
+      <c r="BI298">
+        <v>1.48</v>
+      </c>
+      <c r="BJ298">
+        <v>2.45</v>
+      </c>
+      <c r="BK298">
+        <v>1.76</v>
+      </c>
+      <c r="BL298">
+        <v>1.94</v>
+      </c>
+      <c r="BM298">
+        <v>2.18</v>
+      </c>
+      <c r="BN298">
+        <v>1.58</v>
+      </c>
+      <c r="BO298">
+        <v>2.8</v>
+      </c>
+      <c r="BP298">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7465733</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F299">
+        <v>30</v>
+      </c>
+      <c r="G299" t="s">
+        <v>81</v>
+      </c>
+      <c r="H299" t="s">
+        <v>82</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>1</v>
+      </c>
+      <c r="L299">
+        <v>3</v>
+      </c>
+      <c r="M299">
+        <v>1</v>
+      </c>
+      <c r="N299">
+        <v>4</v>
+      </c>
+      <c r="O299" t="s">
+        <v>290</v>
+      </c>
+      <c r="P299" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q299">
+        <v>2.4</v>
+      </c>
+      <c r="R299">
+        <v>2.4</v>
+      </c>
+      <c r="S299">
+        <v>4</v>
+      </c>
+      <c r="T299">
+        <v>1.29</v>
+      </c>
+      <c r="U299">
+        <v>3.5</v>
+      </c>
+      <c r="V299">
+        <v>2.38</v>
+      </c>
+      <c r="W299">
+        <v>1.53</v>
+      </c>
+      <c r="X299">
+        <v>5.5</v>
+      </c>
+      <c r="Y299">
+        <v>1.14</v>
+      </c>
+      <c r="Z299">
+        <v>1.8</v>
+      </c>
+      <c r="AA299">
+        <v>3.6</v>
+      </c>
+      <c r="AB299">
+        <v>3.7</v>
+      </c>
+      <c r="AC299">
+        <v>1.04</v>
+      </c>
+      <c r="AD299">
+        <v>10</v>
+      </c>
+      <c r="AE299">
+        <v>1.18</v>
+      </c>
+      <c r="AF299">
+        <v>4.75</v>
+      </c>
+      <c r="AG299">
+        <v>1.57</v>
+      </c>
+      <c r="AH299">
+        <v>2.35</v>
+      </c>
+      <c r="AI299">
+        <v>1.53</v>
+      </c>
+      <c r="AJ299">
+        <v>2.38</v>
+      </c>
+      <c r="AK299">
+        <v>1.25</v>
+      </c>
+      <c r="AL299">
+        <v>1.26</v>
+      </c>
+      <c r="AM299">
+        <v>1.9</v>
+      </c>
+      <c r="AN299">
+        <v>1.86</v>
+      </c>
+      <c r="AO299">
+        <v>1.13</v>
+      </c>
+      <c r="AP299">
+        <v>1.93</v>
+      </c>
+      <c r="AQ299">
+        <v>1.06</v>
+      </c>
+      <c r="AR299">
+        <v>1.78</v>
+      </c>
+      <c r="AS299">
+        <v>1.77</v>
+      </c>
+      <c r="AT299">
+        <v>3.55</v>
+      </c>
+      <c r="AU299">
+        <v>12</v>
+      </c>
+      <c r="AV299">
+        <v>8</v>
+      </c>
+      <c r="AW299">
+        <v>10</v>
+      </c>
+      <c r="AX299">
+        <v>5</v>
+      </c>
+      <c r="AY299">
+        <v>22</v>
+      </c>
+      <c r="AZ299">
+        <v>13</v>
+      </c>
+      <c r="BA299">
+        <v>7</v>
+      </c>
+      <c r="BB299">
+        <v>4</v>
+      </c>
+      <c r="BC299">
+        <v>11</v>
+      </c>
+      <c r="BD299">
+        <v>1.67</v>
+      </c>
+      <c r="BE299">
+        <v>6.5</v>
+      </c>
+      <c r="BF299">
+        <v>2.43</v>
+      </c>
+      <c r="BG299">
+        <v>1.26</v>
+      </c>
+      <c r="BH299">
+        <v>3.4</v>
+      </c>
+      <c r="BI299">
+        <v>1.47</v>
+      </c>
+      <c r="BJ299">
+        <v>2.48</v>
+      </c>
+      <c r="BK299">
+        <v>1.75</v>
+      </c>
+      <c r="BL299">
+        <v>1.95</v>
+      </c>
+      <c r="BM299">
+        <v>2.18</v>
+      </c>
+      <c r="BN299">
+        <v>1.58</v>
+      </c>
+      <c r="BO299">
+        <v>2.75</v>
+      </c>
+      <c r="BP299">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7465732</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F300">
+        <v>30</v>
+      </c>
+      <c r="G300" t="s">
+        <v>73</v>
+      </c>
+      <c r="H300" t="s">
+        <v>78</v>
+      </c>
+      <c r="I300">
+        <v>0</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>0</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+      <c r="M300">
+        <v>1</v>
+      </c>
+      <c r="N300">
+        <v>1</v>
+      </c>
+      <c r="O300" t="s">
+        <v>93</v>
+      </c>
+      <c r="P300" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q300">
+        <v>2.88</v>
+      </c>
+      <c r="R300">
+        <v>2.4</v>
+      </c>
+      <c r="S300">
+        <v>3.1</v>
+      </c>
+      <c r="T300">
+        <v>1.25</v>
+      </c>
+      <c r="U300">
+        <v>3.75</v>
+      </c>
+      <c r="V300">
+        <v>2.25</v>
+      </c>
+      <c r="W300">
+        <v>1.57</v>
+      </c>
+      <c r="X300">
+        <v>5.5</v>
+      </c>
+      <c r="Y300">
+        <v>1.14</v>
+      </c>
+      <c r="Z300">
+        <v>2.25</v>
+      </c>
+      <c r="AA300">
+        <v>3.5</v>
+      </c>
+      <c r="AB300">
+        <v>2.6</v>
+      </c>
+      <c r="AC300">
+        <v>1.01</v>
+      </c>
+      <c r="AD300">
+        <v>18.5</v>
+      </c>
+      <c r="AE300">
+        <v>1.17</v>
+      </c>
+      <c r="AF300">
+        <v>5</v>
+      </c>
+      <c r="AG300">
+        <v>1.5</v>
+      </c>
+      <c r="AH300">
+        <v>2.5</v>
+      </c>
+      <c r="AI300">
+        <v>1.44</v>
+      </c>
+      <c r="AJ300">
+        <v>2.63</v>
+      </c>
+      <c r="AK300">
+        <v>1.44</v>
+      </c>
+      <c r="AL300">
+        <v>1.22</v>
+      </c>
+      <c r="AM300">
+        <v>1.57</v>
+      </c>
+      <c r="AN300">
+        <v>1.79</v>
+      </c>
+      <c r="AO300">
+        <v>1.2</v>
+      </c>
+      <c r="AP300">
+        <v>1.67</v>
+      </c>
+      <c r="AQ300">
+        <v>1.31</v>
+      </c>
+      <c r="AR300">
+        <v>1.68</v>
+      </c>
+      <c r="AS300">
+        <v>1.31</v>
+      </c>
+      <c r="AT300">
+        <v>2.99</v>
+      </c>
+      <c r="AU300">
+        <v>0</v>
+      </c>
+      <c r="AV300">
+        <v>8</v>
+      </c>
+      <c r="AW300">
+        <v>7</v>
+      </c>
+      <c r="AX300">
+        <v>13</v>
+      </c>
+      <c r="AY300">
+        <v>7</v>
+      </c>
+      <c r="AZ300">
+        <v>21</v>
+      </c>
+      <c r="BA300">
+        <v>1</v>
+      </c>
+      <c r="BB300">
+        <v>7</v>
+      </c>
+      <c r="BC300">
+        <v>8</v>
+      </c>
+      <c r="BD300">
+        <v>1.86</v>
+      </c>
+      <c r="BE300">
+        <v>6.5</v>
+      </c>
+      <c r="BF300">
+        <v>2.15</v>
+      </c>
+      <c r="BG300">
+        <v>1.25</v>
+      </c>
+      <c r="BH300">
+        <v>3.45</v>
+      </c>
+      <c r="BI300">
+        <v>1.45</v>
+      </c>
+      <c r="BJ300">
+        <v>2.55</v>
+      </c>
+      <c r="BK300">
+        <v>1.72</v>
+      </c>
+      <c r="BL300">
+        <v>1.98</v>
+      </c>
+      <c r="BM300">
+        <v>2.12</v>
+      </c>
+      <c r="BN300">
+        <v>1.64</v>
+      </c>
+      <c r="BO300">
+        <v>2.65</v>
+      </c>
+      <c r="BP300">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7465731</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F301">
+        <v>30</v>
+      </c>
+      <c r="G301" t="s">
+        <v>72</v>
+      </c>
+      <c r="H301" t="s">
+        <v>79</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>1</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="M301">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>2</v>
+      </c>
+      <c r="O301" t="s">
+        <v>291</v>
+      </c>
+      <c r="P301" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q301">
+        <v>2</v>
+      </c>
+      <c r="R301">
+        <v>2.63</v>
+      </c>
+      <c r="S301">
+        <v>5</v>
+      </c>
+      <c r="T301">
+        <v>1.25</v>
+      </c>
+      <c r="U301">
+        <v>3.75</v>
+      </c>
+      <c r="V301">
+        <v>2.1</v>
+      </c>
+      <c r="W301">
+        <v>1.67</v>
+      </c>
+      <c r="X301">
+        <v>4.5</v>
+      </c>
+      <c r="Y301">
+        <v>1.18</v>
+      </c>
+      <c r="Z301">
+        <v>1.48</v>
+      </c>
+      <c r="AA301">
+        <v>4</v>
+      </c>
+      <c r="AB301">
+        <v>5.25</v>
+      </c>
+      <c r="AC301">
+        <v>1.01</v>
+      </c>
+      <c r="AD301">
+        <v>13</v>
+      </c>
+      <c r="AE301">
+        <v>1.14</v>
+      </c>
+      <c r="AF301">
+        <v>5.5</v>
+      </c>
+      <c r="AG301">
+        <v>1.44</v>
+      </c>
+      <c r="AH301">
+        <v>2.7</v>
+      </c>
+      <c r="AI301">
+        <v>1.53</v>
+      </c>
+      <c r="AJ301">
+        <v>2.38</v>
+      </c>
+      <c r="AK301">
+        <v>1.14</v>
+      </c>
+      <c r="AL301">
+        <v>1.15</v>
+      </c>
+      <c r="AM301">
+        <v>2.5</v>
+      </c>
+      <c r="AN301">
+        <v>1.6</v>
+      </c>
+      <c r="AO301">
+        <v>0.93</v>
+      </c>
+      <c r="AP301">
+        <v>1.56</v>
+      </c>
+      <c r="AQ301">
+        <v>0.93</v>
+      </c>
+      <c r="AR301">
+        <v>1.59</v>
+      </c>
+      <c r="AS301">
+        <v>1.33</v>
+      </c>
+      <c r="AT301">
+        <v>2.92</v>
+      </c>
+      <c r="AU301">
+        <v>3</v>
+      </c>
+      <c r="AV301">
+        <v>4</v>
+      </c>
+      <c r="AW301">
+        <v>11</v>
+      </c>
+      <c r="AX301">
+        <v>6</v>
+      </c>
+      <c r="AY301">
+        <v>14</v>
+      </c>
+      <c r="AZ301">
+        <v>10</v>
+      </c>
+      <c r="BA301">
+        <v>7</v>
+      </c>
+      <c r="BB301">
+        <v>6</v>
+      </c>
+      <c r="BC301">
+        <v>13</v>
+      </c>
+      <c r="BD301">
+        <v>1.46</v>
+      </c>
+      <c r="BE301">
+        <v>6.75</v>
+      </c>
+      <c r="BF301">
+        <v>3.05</v>
+      </c>
+      <c r="BG301">
+        <v>1.3</v>
+      </c>
+      <c r="BH301">
+        <v>3.15</v>
+      </c>
+      <c r="BI301">
+        <v>1.52</v>
+      </c>
+      <c r="BJ301">
+        <v>2.33</v>
+      </c>
+      <c r="BK301">
+        <v>1.84</v>
+      </c>
+      <c r="BL301">
+        <v>1.84</v>
+      </c>
+      <c r="BM301">
+        <v>2.28</v>
+      </c>
+      <c r="BN301">
+        <v>1.55</v>
+      </c>
+      <c r="BO301">
+        <v>2.9</v>
+      </c>
+      <c r="BP301">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7465728</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F302">
+        <v>30</v>
+      </c>
+      <c r="G302" t="s">
+        <v>70</v>
+      </c>
+      <c r="H302" t="s">
+        <v>83</v>
+      </c>
+      <c r="I302">
+        <v>0</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>0</v>
+      </c>
+      <c r="L302">
+        <v>1</v>
+      </c>
+      <c r="M302">
+        <v>2</v>
+      </c>
+      <c r="N302">
+        <v>3</v>
+      </c>
+      <c r="O302" t="s">
+        <v>292</v>
+      </c>
+      <c r="P302" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q302">
+        <v>4</v>
+      </c>
+      <c r="R302">
+        <v>2.3</v>
+      </c>
+      <c r="S302">
+        <v>2.3</v>
+      </c>
+      <c r="T302">
+        <v>1.28</v>
+      </c>
+      <c r="U302">
+        <v>3.3</v>
+      </c>
+      <c r="V302">
+        <v>2.3</v>
+      </c>
+      <c r="W302">
+        <v>1.55</v>
+      </c>
+      <c r="X302">
+        <v>5.25</v>
+      </c>
+      <c r="Y302">
+        <v>1.13</v>
+      </c>
+      <c r="Z302">
+        <v>3.94</v>
+      </c>
+      <c r="AA302">
+        <v>3.97</v>
+      </c>
+      <c r="AB302">
+        <v>1.81</v>
+      </c>
+      <c r="AC302">
+        <v>1.04</v>
+      </c>
+      <c r="AD302">
+        <v>10</v>
+      </c>
+      <c r="AE302">
+        <v>1.2</v>
+      </c>
+      <c r="AF302">
+        <v>4.33</v>
+      </c>
+      <c r="AG302">
+        <v>1.6</v>
+      </c>
+      <c r="AH302">
+        <v>2.2</v>
+      </c>
+      <c r="AI302">
+        <v>1.58</v>
+      </c>
+      <c r="AJ302">
+        <v>2.2</v>
+      </c>
+      <c r="AK302">
+        <v>1.95</v>
+      </c>
+      <c r="AL302">
+        <v>1.24</v>
+      </c>
+      <c r="AM302">
+        <v>1.24</v>
+      </c>
+      <c r="AN302">
+        <v>1.14</v>
+      </c>
+      <c r="AO302">
+        <v>1.33</v>
+      </c>
+      <c r="AP302">
+        <v>1.07</v>
+      </c>
+      <c r="AQ302">
+        <v>1.44</v>
+      </c>
+      <c r="AR302">
+        <v>1.43</v>
+      </c>
+      <c r="AS302">
+        <v>1.67</v>
+      </c>
+      <c r="AT302">
+        <v>3.1</v>
+      </c>
+      <c r="AU302">
+        <v>3</v>
+      </c>
+      <c r="AV302">
+        <v>9</v>
+      </c>
+      <c r="AW302">
+        <v>6</v>
+      </c>
+      <c r="AX302">
+        <v>13</v>
+      </c>
+      <c r="AY302">
+        <v>9</v>
+      </c>
+      <c r="AZ302">
+        <v>22</v>
+      </c>
+      <c r="BA302">
+        <v>1</v>
+      </c>
+      <c r="BB302">
+        <v>5</v>
+      </c>
+      <c r="BC302">
+        <v>6</v>
+      </c>
+      <c r="BD302">
+        <v>2.75</v>
+      </c>
+      <c r="BE302">
+        <v>6.75</v>
+      </c>
+      <c r="BF302">
+        <v>1.52</v>
+      </c>
+      <c r="BG302">
+        <v>1.26</v>
+      </c>
+      <c r="BH302">
+        <v>3.4</v>
+      </c>
+      <c r="BI302">
+        <v>1.46</v>
+      </c>
+      <c r="BJ302">
+        <v>2.5</v>
+      </c>
+      <c r="BK302">
+        <v>1.74</v>
+      </c>
+      <c r="BL302">
+        <v>1.97</v>
+      </c>
+      <c r="BM302">
+        <v>2.12</v>
+      </c>
+      <c r="BN302">
+        <v>1.63</v>
+      </c>
+      <c r="BO302">
+        <v>2.65</v>
+      </c>
+      <c r="BP302">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7465727</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F303">
+        <v>30</v>
+      </c>
+      <c r="G303" t="s">
+        <v>86</v>
+      </c>
+      <c r="H303" t="s">
+        <v>80</v>
+      </c>
+      <c r="I303">
+        <v>2</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>2</v>
+      </c>
+      <c r="L303">
+        <v>4</v>
+      </c>
+      <c r="M303">
+        <v>0</v>
+      </c>
+      <c r="N303">
+        <v>4</v>
+      </c>
+      <c r="O303" t="s">
+        <v>293</v>
+      </c>
+      <c r="P303" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q303">
+        <v>2.2</v>
+      </c>
+      <c r="R303">
+        <v>2.37</v>
+      </c>
+      <c r="S303">
+        <v>4</v>
+      </c>
+      <c r="T303">
+        <v>1.27</v>
+      </c>
+      <c r="U303">
+        <v>3.4</v>
+      </c>
+      <c r="V303">
+        <v>2.25</v>
+      </c>
+      <c r="W303">
+        <v>1.55</v>
+      </c>
+      <c r="X303">
+        <v>5.25</v>
+      </c>
+      <c r="Y303">
+        <v>1.14</v>
+      </c>
+      <c r="Z303">
+        <v>1.76</v>
+      </c>
+      <c r="AA303">
+        <v>4.18</v>
+      </c>
+      <c r="AB303">
+        <v>4</v>
+      </c>
+      <c r="AC303">
+        <v>1.03</v>
+      </c>
+      <c r="AD303">
+        <v>11</v>
+      </c>
+      <c r="AE303">
+        <v>1.18</v>
+      </c>
+      <c r="AF303">
+        <v>4.75</v>
+      </c>
+      <c r="AG303">
+        <v>1.57</v>
+      </c>
+      <c r="AH303">
+        <v>2.25</v>
+      </c>
+      <c r="AI303">
+        <v>1.6</v>
+      </c>
+      <c r="AJ303">
+        <v>2.2</v>
+      </c>
+      <c r="AK303">
+        <v>1.23</v>
+      </c>
+      <c r="AL303">
+        <v>1.23</v>
+      </c>
+      <c r="AM303">
+        <v>2.05</v>
+      </c>
+      <c r="AN303">
+        <v>2</v>
+      </c>
+      <c r="AO303">
+        <v>1.23</v>
+      </c>
+      <c r="AP303">
+        <v>2.07</v>
+      </c>
+      <c r="AQ303">
+        <v>1.14</v>
+      </c>
+      <c r="AR303">
+        <v>1.65</v>
+      </c>
+      <c r="AS303">
+        <v>1.36</v>
+      </c>
+      <c r="AT303">
+        <v>3.01</v>
+      </c>
+      <c r="AU303">
+        <v>8</v>
+      </c>
+      <c r="AV303">
+        <v>3</v>
+      </c>
+      <c r="AW303">
+        <v>5</v>
+      </c>
+      <c r="AX303">
+        <v>4</v>
+      </c>
+      <c r="AY303">
+        <v>13</v>
+      </c>
+      <c r="AZ303">
+        <v>7</v>
+      </c>
+      <c r="BA303">
+        <v>9</v>
+      </c>
+      <c r="BB303">
+        <v>2</v>
+      </c>
+      <c r="BC303">
+        <v>11</v>
+      </c>
+      <c r="BD303">
+        <v>1.53</v>
+      </c>
+      <c r="BE303">
+        <v>7</v>
+      </c>
+      <c r="BF303">
+        <v>2.7</v>
+      </c>
+      <c r="BG303">
+        <v>1.3</v>
+      </c>
+      <c r="BH303">
+        <v>3.15</v>
+      </c>
+      <c r="BI303">
+        <v>1.5</v>
+      </c>
+      <c r="BJ303">
+        <v>2.35</v>
+      </c>
+      <c r="BK303">
+        <v>1.83</v>
+      </c>
+      <c r="BL303">
+        <v>1.85</v>
+      </c>
+      <c r="BM303">
+        <v>2.3</v>
+      </c>
+      <c r="BN303">
+        <v>1.54</v>
+      </c>
+      <c r="BO303">
+        <v>2.9</v>
+      </c>
+      <c r="BP303">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7465730</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45730.66666666666</v>
+      </c>
+      <c r="F304">
+        <v>30</v>
+      </c>
+      <c r="G304" t="s">
+        <v>71</v>
+      </c>
+      <c r="H304" t="s">
+        <v>84</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>1</v>
+      </c>
+      <c r="L304">
+        <v>2</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
+      </c>
+      <c r="N304">
+        <v>2</v>
+      </c>
+      <c r="O304" t="s">
+        <v>294</v>
+      </c>
+      <c r="P304" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q304">
+        <v>1.73</v>
+      </c>
+      <c r="R304">
+        <v>2.63</v>
+      </c>
+      <c r="S304">
+        <v>7.5</v>
+      </c>
+      <c r="T304">
+        <v>1.25</v>
+      </c>
+      <c r="U304">
+        <v>3.75</v>
+      </c>
+      <c r="V304">
+        <v>2.2</v>
+      </c>
+      <c r="W304">
+        <v>1.62</v>
+      </c>
+      <c r="X304">
+        <v>5</v>
+      </c>
+      <c r="Y304">
+        <v>1.17</v>
+      </c>
+      <c r="Z304">
+        <v>1.3</v>
+      </c>
+      <c r="AA304">
+        <v>5</v>
+      </c>
+      <c r="AB304">
+        <v>7</v>
+      </c>
+      <c r="AC304">
+        <v>1.01</v>
+      </c>
+      <c r="AD304">
+        <v>16.5</v>
+      </c>
+      <c r="AE304">
+        <v>1.14</v>
+      </c>
+      <c r="AF304">
+        <v>5.5</v>
+      </c>
+      <c r="AG304">
+        <v>1.5</v>
+      </c>
+      <c r="AH304">
+        <v>2.5</v>
+      </c>
+      <c r="AI304">
+        <v>1.83</v>
+      </c>
+      <c r="AJ304">
+        <v>1.83</v>
+      </c>
+      <c r="AK304">
+        <v>1.07</v>
+      </c>
+      <c r="AL304">
+        <v>1.15</v>
+      </c>
+      <c r="AM304">
+        <v>3.25</v>
+      </c>
+      <c r="AN304">
+        <v>1.07</v>
+      </c>
+      <c r="AO304">
+        <v>0.57</v>
+      </c>
+      <c r="AP304">
+        <v>1.19</v>
+      </c>
+      <c r="AQ304">
+        <v>0.53</v>
+      </c>
+      <c r="AR304">
+        <v>1.67</v>
+      </c>
+      <c r="AS304">
+        <v>1.23</v>
+      </c>
+      <c r="AT304">
+        <v>2.9</v>
+      </c>
+      <c r="AU304">
+        <v>8</v>
+      </c>
+      <c r="AV304">
+        <v>4</v>
+      </c>
+      <c r="AW304">
+        <v>9</v>
+      </c>
+      <c r="AX304">
+        <v>3</v>
+      </c>
+      <c r="AY304">
+        <v>17</v>
+      </c>
+      <c r="AZ304">
+        <v>7</v>
+      </c>
+      <c r="BA304">
+        <v>8</v>
+      </c>
+      <c r="BB304">
+        <v>3</v>
+      </c>
+      <c r="BC304">
+        <v>11</v>
+      </c>
+      <c r="BD304">
+        <v>1.24</v>
+      </c>
+      <c r="BE304">
+        <v>8</v>
+      </c>
+      <c r="BF304">
+        <v>4.3</v>
+      </c>
+      <c r="BG304">
+        <v>1.28</v>
+      </c>
+      <c r="BH304">
+        <v>3.3</v>
+      </c>
+      <c r="BI304">
+        <v>1.49</v>
+      </c>
+      <c r="BJ304">
+        <v>2.4</v>
+      </c>
+      <c r="BK304">
+        <v>1.78</v>
+      </c>
+      <c r="BL304">
+        <v>1.92</v>
+      </c>
+      <c r="BM304">
+        <v>2.18</v>
+      </c>
+      <c r="BN304">
+        <v>1.58</v>
+      </c>
+      <c r="BO304">
+        <v>2.8</v>
+      </c>
+      <c r="BP304">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="433">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -901,6 +901,9 @@
     <t>['7', '90+2']</t>
   </si>
   <si>
+    <t>['6', '32', '48', '58']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1309,7 +1312,7 @@
     <t>['11', '39']</t>
   </si>
   <si>
-    <t>['47', '84']</t>
+    <t>['47', '83']</t>
   </si>
 </sst>
 </file>
@@ -1671,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP304"/>
+  <dimension ref="A1:BP305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2133,7 +2136,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2339,7 +2342,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2626,7 +2629,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2751,7 +2754,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2957,7 +2960,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3163,7 +3166,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3369,7 +3372,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3781,7 +3784,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4193,7 +4196,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4811,7 +4814,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5635,7 +5638,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5713,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ20">
         <v>1.87</v>
@@ -6128,7 +6131,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ22">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6665,7 +6668,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6871,7 +6874,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7077,7 +7080,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7489,7 +7492,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7901,7 +7904,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8519,7 +8522,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8725,7 +8728,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9218,7 +9221,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ37">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9343,7 +9346,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9549,7 +9552,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9833,7 +9836,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ40">
         <v>0.53</v>
@@ -9961,7 +9964,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10785,7 +10788,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10991,7 +10994,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11403,7 +11406,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11815,7 +11818,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12021,7 +12024,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12227,7 +12230,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -13051,7 +13054,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13463,7 +13466,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13953,7 +13956,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ60">
         <v>1.56</v>
@@ -14081,7 +14084,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14287,7 +14290,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14493,7 +14496,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15111,7 +15114,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15523,7 +15526,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15729,7 +15732,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15935,7 +15938,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16141,7 +16144,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16222,7 +16225,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ71">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16347,7 +16350,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16425,7 +16428,7 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ72">
         <v>1.14</v>
@@ -16553,7 +16556,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16759,7 +16762,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16965,7 +16968,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17583,7 +17586,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17789,7 +17792,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18201,7 +18204,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18488,7 +18491,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ82">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18613,7 +18616,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18819,7 +18822,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19437,7 +19440,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20055,7 +20058,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20467,7 +20470,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20879,7 +20882,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21085,7 +21088,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21291,7 +21294,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21497,7 +21500,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21909,7 +21912,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22321,7 +22324,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22527,7 +22530,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22939,7 +22942,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -24175,7 +24178,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24381,7 +24384,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24459,7 +24462,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ111">
         <v>1.2</v>
@@ -24587,7 +24590,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25077,7 +25080,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ114">
         <v>1.53</v>
@@ -25205,7 +25208,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25411,7 +25414,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25617,7 +25620,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25823,7 +25826,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26029,7 +26032,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26110,7 +26113,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ119">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -26235,7 +26238,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26441,7 +26444,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26647,7 +26650,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26728,7 +26731,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ122">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26853,7 +26856,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27059,7 +27062,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27265,7 +27268,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27883,7 +27886,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28295,7 +28298,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28501,7 +28504,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29531,7 +29534,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30227,7 +30230,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ139">
         <v>0.53</v>
@@ -31385,7 +31388,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31591,7 +31594,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31797,7 +31800,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31878,7 +31881,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ147">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -32003,7 +32006,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32415,7 +32418,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32621,7 +32624,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33033,7 +33036,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33239,7 +33242,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33445,7 +33448,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33935,7 +33938,7 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ157">
         <v>0.8</v>
@@ -34475,7 +34478,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34887,7 +34890,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35711,7 +35714,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35792,7 +35795,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ166">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -36535,7 +36538,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36741,7 +36744,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37153,7 +37156,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37643,7 +37646,7 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ175">
         <v>1.31</v>
@@ -37977,7 +37980,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38183,7 +38186,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38595,7 +38598,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38801,7 +38804,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39419,7 +39422,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39625,7 +39628,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39831,7 +39834,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39912,7 +39915,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ186">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40449,7 +40452,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41067,7 +41070,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41273,7 +41276,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41479,7 +41482,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41685,7 +41688,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41891,7 +41894,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42381,7 +42384,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ198">
         <v>1.07</v>
@@ -42509,7 +42512,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42921,7 +42924,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43539,7 +43542,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43951,7 +43954,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44157,7 +44160,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44569,7 +44572,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44981,7 +44984,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45265,7 +45268,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ212">
         <v>1.07</v>
@@ -45805,7 +45808,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46092,7 +46095,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ216">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR216">
         <v>1.9</v>
@@ -46423,7 +46426,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46629,7 +46632,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46710,7 +46713,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ219">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR219">
         <v>1.34</v>
@@ -46835,7 +46838,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47325,7 +47328,7 @@
         <v>0.64</v>
       </c>
       <c r="AP222">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ222">
         <v>0.53</v>
@@ -48689,7 +48692,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49307,7 +49310,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49925,7 +49928,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50131,7 +50134,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50543,7 +50546,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51367,7 +51370,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51573,7 +51576,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51651,7 +51654,7 @@
         <v>1.18</v>
       </c>
       <c r="AP243">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ243">
         <v>1.67</v>
@@ -51779,7 +51782,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52397,7 +52400,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52603,7 +52606,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -52684,7 +52687,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ248">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR248">
         <v>1.53</v>
@@ -54045,7 +54048,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -55281,7 +55284,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55487,7 +55490,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55693,7 +55696,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55899,7 +55902,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56105,7 +56108,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56311,7 +56314,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56517,7 +56520,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56598,7 +56601,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ267">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR267">
         <v>1.73</v>
@@ -56723,7 +56726,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -57135,7 +57138,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57341,7 +57344,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57753,7 +57756,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -57831,7 +57834,7 @@
         <v>1.38</v>
       </c>
       <c r="AP273">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ273">
         <v>1.2</v>
@@ -58165,7 +58168,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58371,7 +58374,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58577,7 +58580,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58783,7 +58786,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58989,7 +58992,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59401,7 +59404,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59607,7 +59610,7 @@
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q282">
         <v>1.73</v>
@@ -60431,7 +60434,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60637,7 +60640,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -60718,7 +60721,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ287">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AR287">
         <v>1.76</v>
@@ -61255,7 +61258,7 @@
         <v>286</v>
       </c>
       <c r="P290" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q290">
         <v>2.5</v>
@@ -61461,7 +61464,7 @@
         <v>93</v>
       </c>
       <c r="P291" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q291">
         <v>3.25</v>
@@ -62079,7 +62082,7 @@
         <v>93</v>
       </c>
       <c r="P294" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q294">
         <v>3.6</v>
@@ -62285,7 +62288,7 @@
         <v>93</v>
       </c>
       <c r="P295" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62491,7 +62494,7 @@
         <v>288</v>
       </c>
       <c r="P296" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q296">
         <v>2.5</v>
@@ -62775,7 +62778,7 @@
         <v>1.2</v>
       </c>
       <c r="AP297">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AQ297">
         <v>1.13</v>
@@ -63727,7 +63730,7 @@
         <v>292</v>
       </c>
       <c r="P302" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q302">
         <v>4</v>
@@ -64296,6 +64299,212 @@
       </c>
       <c r="BP304">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7465737</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45731.52083333334</v>
+      </c>
+      <c r="F305">
+        <v>30</v>
+      </c>
+      <c r="G305" t="s">
+        <v>88</v>
+      </c>
+      <c r="H305" t="s">
+        <v>87</v>
+      </c>
+      <c r="I305">
+        <v>2</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>2</v>
+      </c>
+      <c r="L305">
+        <v>4</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>5</v>
+      </c>
+      <c r="O305" t="s">
+        <v>295</v>
+      </c>
+      <c r="P305" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q305">
+        <v>2.63</v>
+      </c>
+      <c r="R305">
+        <v>2.38</v>
+      </c>
+      <c r="S305">
+        <v>3.75</v>
+      </c>
+      <c r="T305">
+        <v>1.3</v>
+      </c>
+      <c r="U305">
+        <v>3.4</v>
+      </c>
+      <c r="V305">
+        <v>2.5</v>
+      </c>
+      <c r="W305">
+        <v>1.5</v>
+      </c>
+      <c r="X305">
+        <v>6</v>
+      </c>
+      <c r="Y305">
+        <v>1.13</v>
+      </c>
+      <c r="Z305">
+        <v>1.95</v>
+      </c>
+      <c r="AA305">
+        <v>3.4</v>
+      </c>
+      <c r="AB305">
+        <v>3.2</v>
+      </c>
+      <c r="AC305">
+        <v>1.03</v>
+      </c>
+      <c r="AD305">
+        <v>12.4</v>
+      </c>
+      <c r="AE305">
+        <v>1.18</v>
+      </c>
+      <c r="AF305">
+        <v>4.5</v>
+      </c>
+      <c r="AG305">
+        <v>1.62</v>
+      </c>
+      <c r="AH305">
+        <v>2.25</v>
+      </c>
+      <c r="AI305">
+        <v>1.53</v>
+      </c>
+      <c r="AJ305">
+        <v>2.38</v>
+      </c>
+      <c r="AK305">
+        <v>1.44</v>
+      </c>
+      <c r="AL305">
+        <v>1.27</v>
+      </c>
+      <c r="AM305">
+        <v>1.55</v>
+      </c>
+      <c r="AN305">
+        <v>2.4</v>
+      </c>
+      <c r="AO305">
+        <v>2.13</v>
+      </c>
+      <c r="AP305">
+        <v>2.44</v>
+      </c>
+      <c r="AQ305">
+        <v>2</v>
+      </c>
+      <c r="AR305">
+        <v>1.84</v>
+      </c>
+      <c r="AS305">
+        <v>1.89</v>
+      </c>
+      <c r="AT305">
+        <v>3.73</v>
+      </c>
+      <c r="AU305">
+        <v>9</v>
+      </c>
+      <c r="AV305">
+        <v>4</v>
+      </c>
+      <c r="AW305">
+        <v>5</v>
+      </c>
+      <c r="AX305">
+        <v>7</v>
+      </c>
+      <c r="AY305">
+        <v>17</v>
+      </c>
+      <c r="AZ305">
+        <v>14</v>
+      </c>
+      <c r="BA305">
+        <v>3</v>
+      </c>
+      <c r="BB305">
+        <v>5</v>
+      </c>
+      <c r="BC305">
+        <v>8</v>
+      </c>
+      <c r="BD305">
+        <v>1.95</v>
+      </c>
+      <c r="BE305">
+        <v>8</v>
+      </c>
+      <c r="BF305">
+        <v>2.05</v>
+      </c>
+      <c r="BG305">
+        <v>1.28</v>
+      </c>
+      <c r="BH305">
+        <v>3.3</v>
+      </c>
+      <c r="BI305">
+        <v>1.33</v>
+      </c>
+      <c r="BJ305">
+        <v>2.83</v>
+      </c>
+      <c r="BK305">
+        <v>1.61</v>
+      </c>
+      <c r="BL305">
+        <v>2.12</v>
+      </c>
+      <c r="BM305">
+        <v>2.04</v>
+      </c>
+      <c r="BN305">
+        <v>1.69</v>
+      </c>
+      <c r="BO305">
+        <v>2.64</v>
+      </c>
+      <c r="BP305">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="435">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -904,6 +904,9 @@
     <t>['6', '32', '48', '58']</t>
   </si>
   <si>
+    <t>['45', '56', '78']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1314,6 +1317,9 @@
   <si>
     <t>['47', '83']</t>
   </si>
+  <si>
+    <t>['5', '69']</t>
+  </si>
 </sst>
 </file>
 
@@ -1674,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP305"/>
+  <dimension ref="A1:BP307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2136,7 +2142,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2342,7 +2348,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2754,7 +2760,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2832,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ6">
         <v>1.44</v>
@@ -2960,7 +2966,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3166,7 +3172,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3372,7 +3378,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3784,7 +3790,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3865,7 +3871,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ11">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4196,7 +4202,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4689,7 +4695,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ15">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4814,7 +4820,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5098,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
         <v>1.31</v>
@@ -5638,7 +5644,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6128,7 +6134,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ22">
         <v>2</v>
@@ -6540,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>0.53</v>
@@ -6668,7 +6674,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6874,7 +6880,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7080,7 +7086,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7161,7 +7167,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7492,7 +7498,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7904,7 +7910,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8522,7 +8528,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8728,7 +8734,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9346,7 +9352,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9552,7 +9558,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9964,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10045,7 +10051,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR41">
         <v>1.77</v>
@@ -10663,7 +10669,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ44">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10788,7 +10794,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10994,7 +11000,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11072,7 +11078,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ46">
         <v>0.93</v>
@@ -11406,7 +11412,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11818,7 +11824,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12024,7 +12030,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12230,7 +12236,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12514,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ53">
         <v>1.67</v>
@@ -13054,7 +13060,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13466,7 +13472,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -14084,7 +14090,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14290,7 +14296,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14496,7 +14502,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14780,7 +14786,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
         <v>1.87</v>
@@ -15114,7 +15120,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15526,7 +15532,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15607,7 +15613,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ68">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15732,7 +15738,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15810,7 +15816,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ69">
         <v>1.53</v>
@@ -15938,7 +15944,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16019,7 +16025,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ70">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -16144,7 +16150,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16350,7 +16356,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16556,7 +16562,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16762,7 +16768,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16968,7 +16974,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17586,7 +17592,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17792,7 +17798,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18204,7 +18210,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18616,7 +18622,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18822,7 +18828,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18900,7 +18906,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ84">
         <v>1.67</v>
@@ -19440,7 +19446,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20058,7 +20064,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20136,10 +20142,10 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR90">
         <v>1.95</v>
@@ -20345,7 +20351,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20470,7 +20476,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20551,7 +20557,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ92">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR92">
         <v>1.75</v>
@@ -20882,7 +20888,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21088,7 +21094,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21294,7 +21300,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21372,7 +21378,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ96">
         <v>1.13</v>
@@ -21500,7 +21506,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21912,7 +21918,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22196,7 +22202,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100">
         <v>1.07</v>
@@ -22324,7 +22330,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22530,7 +22536,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22942,7 +22948,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -24178,7 +24184,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24384,7 +24390,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24590,7 +24596,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24671,7 +24677,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ112">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR112">
         <v>1.74</v>
@@ -25208,7 +25214,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25289,7 +25295,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ115">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25414,7 +25420,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25492,7 +25498,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ116">
         <v>1.31</v>
@@ -25620,7 +25626,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25826,7 +25832,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26032,7 +26038,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26238,7 +26244,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26444,7 +26450,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26650,7 +26656,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26856,7 +26862,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27062,7 +27068,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27268,7 +27274,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27758,7 +27764,7 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ127">
         <v>1.06</v>
@@ -27886,7 +27892,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28298,7 +28304,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28504,7 +28510,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28791,7 +28797,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ132">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR132">
         <v>1.8</v>
@@ -29200,7 +29206,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ134">
         <v>1.2</v>
@@ -29534,7 +29540,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29615,7 +29621,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ136">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -31388,7 +31394,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31594,7 +31600,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31800,7 +31806,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32006,7 +32012,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32418,7 +32424,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32624,7 +32630,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32702,7 +32708,7 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ151">
         <v>1.44</v>
@@ -33036,7 +33042,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33242,7 +33248,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33448,7 +33454,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33735,7 +33741,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ156">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR156">
         <v>1.76</v>
@@ -33941,7 +33947,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ157">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34478,7 +34484,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34890,7 +34896,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35177,7 +35183,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ163">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35714,7 +35720,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36204,7 +36210,7 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ168">
         <v>0.53</v>
@@ -36538,7 +36544,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36616,7 +36622,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ170">
         <v>1.56</v>
@@ -36744,7 +36750,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37156,7 +37162,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37980,7 +37986,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38186,7 +38192,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38473,7 +38479,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ179">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR179">
         <v>1.58</v>
@@ -38598,7 +38604,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38804,7 +38810,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39422,7 +39428,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39628,7 +39634,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39834,7 +39840,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40452,7 +40458,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40530,10 +40536,10 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ189">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40736,7 +40742,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ190">
         <v>0.93</v>
@@ -41070,7 +41076,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41276,7 +41282,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41482,7 +41488,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41688,7 +41694,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41894,7 +41900,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42387,7 +42393,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ198">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR198">
         <v>1.99</v>
@@ -42512,7 +42518,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42924,7 +42930,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43414,7 +43420,7 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ203">
         <v>0.53</v>
@@ -43542,7 +43548,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43954,7 +43960,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44160,7 +44166,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44241,7 +44247,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ207">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44572,7 +44578,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44650,7 +44656,7 @@
         <v>1.18</v>
       </c>
       <c r="AP209">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ209">
         <v>1.06</v>
@@ -44984,7 +44990,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45808,7 +45814,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46426,7 +46432,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46507,7 +46513,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ218">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR218">
         <v>1.39</v>
@@ -46632,7 +46638,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46838,7 +46844,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47740,7 +47746,7 @@
         <v>0.5</v>
       </c>
       <c r="AP224">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ224">
         <v>0.53</v>
@@ -47949,7 +47955,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ225">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR225">
         <v>1.68</v>
@@ -48564,7 +48570,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ228">
         <v>0.53</v>
@@ -48692,7 +48698,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49185,7 +49191,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ231">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR231">
         <v>1.8</v>
@@ -49310,7 +49316,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49594,7 +49600,7 @@
         <v>1.73</v>
       </c>
       <c r="AP233">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ233">
         <v>1.87</v>
@@ -49928,7 +49934,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50134,7 +50140,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50418,7 +50424,7 @@
         <v>1.45</v>
       </c>
       <c r="AP237">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ237">
         <v>1.2</v>
@@ -50546,7 +50552,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51370,7 +51376,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51576,7 +51582,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51782,7 +51788,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52400,7 +52406,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52606,7 +52612,7 @@
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q248">
         <v>4.5</v>
@@ -53508,7 +53514,7 @@
         <v>0.92</v>
       </c>
       <c r="AP252">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ252">
         <v>1.13</v>
@@ -53717,7 +53723,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ253">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR253">
         <v>1.85</v>
@@ -54048,7 +54054,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54335,7 +54341,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ256">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR256">
         <v>1.77</v>
@@ -55284,7 +55290,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55490,7 +55496,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55568,7 +55574,7 @@
         <v>1.73</v>
       </c>
       <c r="AP262">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ262">
         <v>1.87</v>
@@ -55696,7 +55702,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55902,7 +55908,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56108,7 +56114,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56314,7 +56320,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56520,7 +56526,7 @@
         <v>273</v>
       </c>
       <c r="P267" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56726,7 +56732,7 @@
         <v>112</v>
       </c>
       <c r="P268" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q268">
         <v>4</v>
@@ -57138,7 +57144,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57219,7 +57225,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ270">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AR270">
         <v>1.51</v>
@@ -57344,7 +57350,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57425,7 +57431,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ271">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR271">
         <v>1.38</v>
@@ -57756,7 +57762,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58168,7 +58174,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58374,7 +58380,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58580,7 +58586,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58786,7 +58792,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58992,7 +58998,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59404,7 +59410,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59482,7 +59488,7 @@
         <v>1.79</v>
       </c>
       <c r="AP281">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AQ281">
         <v>1.87</v>
@@ -59610,7 +59616,7 @@
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q282">
         <v>1.73</v>
@@ -59897,7 +59903,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ283">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR283">
         <v>1.6</v>
@@ -60434,7 +60440,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60640,7 +60646,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -60718,7 +60724,7 @@
         <v>2.07</v>
       </c>
       <c r="AP287">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ287">
         <v>2</v>
@@ -61258,7 +61264,7 @@
         <v>286</v>
       </c>
       <c r="P290" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q290">
         <v>2.5</v>
@@ -61464,7 +61470,7 @@
         <v>93</v>
       </c>
       <c r="P291" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q291">
         <v>3.25</v>
@@ -62082,7 +62088,7 @@
         <v>93</v>
       </c>
       <c r="P294" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q294">
         <v>3.6</v>
@@ -62288,7 +62294,7 @@
         <v>93</v>
       </c>
       <c r="P295" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q295">
         <v>2</v>
@@ -62494,7 +62500,7 @@
         <v>288</v>
       </c>
       <c r="P296" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q296">
         <v>2.5</v>
@@ -63730,7 +63736,7 @@
         <v>292</v>
       </c>
       <c r="P302" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q302">
         <v>4</v>
@@ -64505,6 +64511,418 @@
       </c>
       <c r="BP305">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7465735</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45732.34375</v>
+      </c>
+      <c r="F306">
+        <v>30</v>
+      </c>
+      <c r="G306" t="s">
+        <v>74</v>
+      </c>
+      <c r="H306" t="s">
+        <v>77</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>1</v>
+      </c>
+      <c r="K306">
+        <v>1</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306">
+        <v>2</v>
+      </c>
+      <c r="N306">
+        <v>2</v>
+      </c>
+      <c r="O306" t="s">
+        <v>93</v>
+      </c>
+      <c r="P306" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q306">
+        <v>4.75</v>
+      </c>
+      <c r="R306">
+        <v>2.3</v>
+      </c>
+      <c r="S306">
+        <v>2.3</v>
+      </c>
+      <c r="T306">
+        <v>1.33</v>
+      </c>
+      <c r="U306">
+        <v>3.25</v>
+      </c>
+      <c r="V306">
+        <v>2.63</v>
+      </c>
+      <c r="W306">
+        <v>1.44</v>
+      </c>
+      <c r="X306">
+        <v>6.5</v>
+      </c>
+      <c r="Y306">
+        <v>1.11</v>
+      </c>
+      <c r="Z306">
+        <v>4.47</v>
+      </c>
+      <c r="AA306">
+        <v>3.89</v>
+      </c>
+      <c r="AB306">
+        <v>1.73</v>
+      </c>
+      <c r="AC306">
+        <v>1.04</v>
+      </c>
+      <c r="AD306">
+        <v>10</v>
+      </c>
+      <c r="AE306">
+        <v>1.22</v>
+      </c>
+      <c r="AF306">
+        <v>4.2</v>
+      </c>
+      <c r="AG306">
+        <v>1.7</v>
+      </c>
+      <c r="AH306">
+        <v>2.1</v>
+      </c>
+      <c r="AI306">
+        <v>1.73</v>
+      </c>
+      <c r="AJ306">
+        <v>2</v>
+      </c>
+      <c r="AK306">
+        <v>2.15</v>
+      </c>
+      <c r="AL306">
+        <v>1.24</v>
+      </c>
+      <c r="AM306">
+        <v>1.18</v>
+      </c>
+      <c r="AN306">
+        <v>1.4</v>
+      </c>
+      <c r="AO306">
+        <v>1.07</v>
+      </c>
+      <c r="AP306">
+        <v>1.31</v>
+      </c>
+      <c r="AQ306">
+        <v>1.2</v>
+      </c>
+      <c r="AR306">
+        <v>1.42</v>
+      </c>
+      <c r="AS306">
+        <v>1.8</v>
+      </c>
+      <c r="AT306">
+        <v>3.22</v>
+      </c>
+      <c r="AU306">
+        <v>3</v>
+      </c>
+      <c r="AV306">
+        <v>5</v>
+      </c>
+      <c r="AW306">
+        <v>3</v>
+      </c>
+      <c r="AX306">
+        <v>6</v>
+      </c>
+      <c r="AY306">
+        <v>6</v>
+      </c>
+      <c r="AZ306">
+        <v>11</v>
+      </c>
+      <c r="BA306">
+        <v>5</v>
+      </c>
+      <c r="BB306">
+        <v>5</v>
+      </c>
+      <c r="BC306">
+        <v>10</v>
+      </c>
+      <c r="BD306">
+        <v>2.7</v>
+      </c>
+      <c r="BE306">
+        <v>8.5</v>
+      </c>
+      <c r="BF306">
+        <v>1.57</v>
+      </c>
+      <c r="BG306">
+        <v>1.27</v>
+      </c>
+      <c r="BH306">
+        <v>3.3</v>
+      </c>
+      <c r="BI306">
+        <v>1.34</v>
+      </c>
+      <c r="BJ306">
+        <v>2.78</v>
+      </c>
+      <c r="BK306">
+        <v>1.63</v>
+      </c>
+      <c r="BL306">
+        <v>2.09</v>
+      </c>
+      <c r="BM306">
+        <v>2.06</v>
+      </c>
+      <c r="BN306">
+        <v>1.68</v>
+      </c>
+      <c r="BO306">
+        <v>2.67</v>
+      </c>
+      <c r="BP306">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7465738</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45732.53125</v>
+      </c>
+      <c r="F307">
+        <v>30</v>
+      </c>
+      <c r="G307" t="s">
+        <v>85</v>
+      </c>
+      <c r="H307" t="s">
+        <v>89</v>
+      </c>
+      <c r="I307">
+        <v>1</v>
+      </c>
+      <c r="J307">
+        <v>1</v>
+      </c>
+      <c r="K307">
+        <v>2</v>
+      </c>
+      <c r="L307">
+        <v>3</v>
+      </c>
+      <c r="M307">
+        <v>1</v>
+      </c>
+      <c r="N307">
+        <v>4</v>
+      </c>
+      <c r="O307" t="s">
+        <v>296</v>
+      </c>
+      <c r="P307" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q307">
+        <v>2.6</v>
+      </c>
+      <c r="R307">
+        <v>2.3</v>
+      </c>
+      <c r="S307">
+        <v>3.75</v>
+      </c>
+      <c r="T307">
+        <v>1.3</v>
+      </c>
+      <c r="U307">
+        <v>3.4</v>
+      </c>
+      <c r="V307">
+        <v>2.5</v>
+      </c>
+      <c r="W307">
+        <v>1.5</v>
+      </c>
+      <c r="X307">
+        <v>6</v>
+      </c>
+      <c r="Y307">
+        <v>1.13</v>
+      </c>
+      <c r="Z307">
+        <v>2</v>
+      </c>
+      <c r="AA307">
+        <v>3.4</v>
+      </c>
+      <c r="AB307">
+        <v>3.3</v>
+      </c>
+      <c r="AC307">
+        <v>1.04</v>
+      </c>
+      <c r="AD307">
+        <v>10</v>
+      </c>
+      <c r="AE307">
+        <v>1.22</v>
+      </c>
+      <c r="AF307">
+        <v>4.2</v>
+      </c>
+      <c r="AG307">
+        <v>1.65</v>
+      </c>
+      <c r="AH307">
+        <v>2.2</v>
+      </c>
+      <c r="AI307">
+        <v>1.57</v>
+      </c>
+      <c r="AJ307">
+        <v>2.25</v>
+      </c>
+      <c r="AK307">
+        <v>1.28</v>
+      </c>
+      <c r="AL307">
+        <v>1.27</v>
+      </c>
+      <c r="AM307">
+        <v>1.82</v>
+      </c>
+      <c r="AN307">
+        <v>1.67</v>
+      </c>
+      <c r="AO307">
+        <v>0.8</v>
+      </c>
+      <c r="AP307">
+        <v>1.75</v>
+      </c>
+      <c r="AQ307">
+        <v>0.75</v>
+      </c>
+      <c r="AR307">
+        <v>1.71</v>
+      </c>
+      <c r="AS307">
+        <v>1.52</v>
+      </c>
+      <c r="AT307">
+        <v>3.23</v>
+      </c>
+      <c r="AU307">
+        <v>11</v>
+      </c>
+      <c r="AV307">
+        <v>3</v>
+      </c>
+      <c r="AW307">
+        <v>6</v>
+      </c>
+      <c r="AX307">
+        <v>2</v>
+      </c>
+      <c r="AY307">
+        <v>17</v>
+      </c>
+      <c r="AZ307">
+        <v>5</v>
+      </c>
+      <c r="BA307">
+        <v>6</v>
+      </c>
+      <c r="BB307">
+        <v>6</v>
+      </c>
+      <c r="BC307">
+        <v>12</v>
+      </c>
+      <c r="BD307">
+        <v>1.6</v>
+      </c>
+      <c r="BE307">
+        <v>8.5</v>
+      </c>
+      <c r="BF307">
+        <v>2.6</v>
+      </c>
+      <c r="BG307">
+        <v>1.19</v>
+      </c>
+      <c r="BH307">
+        <v>3.82</v>
+      </c>
+      <c r="BI307">
+        <v>1.39</v>
+      </c>
+      <c r="BJ307">
+        <v>2.67</v>
+      </c>
+      <c r="BK307">
+        <v>1.7</v>
+      </c>
+      <c r="BL307">
+        <v>2.03</v>
+      </c>
+      <c r="BM307">
+        <v>2.14</v>
+      </c>
+      <c r="BN307">
+        <v>1.6</v>
+      </c>
+      <c r="BO307">
+        <v>2.78</v>
+      </c>
+      <c r="BP307">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -766,10 +766,10 @@
     <t>['48', '56', '60', '69']</t>
   </si>
   <si>
-    <t>['43', '48', '72']</t>
+    <t>['47', '90+4']</t>
   </si>
   <si>
-    <t>['47', '90+4']</t>
+    <t>['43', '48', '72']</t>
   </si>
   <si>
     <t>['23', '47', '58']</t>
@@ -796,19 +796,19 @@
     <t>['4', '21', '71', '79', '88', '90+3']</t>
   </si>
   <si>
-    <t>['53', '57', '81']</t>
-  </si>
-  <si>
     <t>['51']</t>
   </si>
   <si>
     <t>['36', '59']</t>
   </si>
   <si>
-    <t>['41', '45+2']</t>
+    <t>['53', '57', '81']</t>
   </si>
   <si>
     <t>['9', '71']</t>
+  </si>
+  <si>
+    <t>['41', '45+2']</t>
   </si>
   <si>
     <t>['56']</t>
@@ -832,10 +832,10 @@
     <t>['85']</t>
   </si>
   <si>
-    <t>['19']</t>
+    <t>['55']</t>
   </si>
   <si>
-    <t>['55']</t>
+    <t>['19']</t>
   </si>
   <si>
     <t>['19', '39', '67', '81', '87']</t>
@@ -853,16 +853,16 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['48', '60']</t>
+  </si>
+  <si>
     <t>['7', '39', '44', '45+2', '54']</t>
   </si>
   <si>
-    <t>['48', '60']</t>
+    <t>['27', '68', '77', '80', '85']</t>
   </si>
   <si>
     <t>['70']</t>
-  </si>
-  <si>
-    <t>['10', '14', '23', '78']</t>
   </si>
   <si>
     <t>['37', '69', '73']</t>
@@ -871,7 +871,7 @@
     <t>['41', '83']</t>
   </si>
   <si>
-    <t>['27', '68', '77', '80', '85']</t>
+    <t>['10', '14', '23', '78']</t>
   </si>
   <si>
     <t>['34', '56']</t>
@@ -886,19 +886,19 @@
     <t>['56', '59', '76']</t>
   </si>
   <si>
-    <t>['10', '69', '80']</t>
+    <t>['28', '40', '58', '89']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['7', '90+2']</t>
   </si>
   <si>
     <t>['6']</t>
   </si>
   <si>
-    <t>['54']</t>
-  </si>
-  <si>
-    <t>['28', '40', '58', '89']</t>
-  </si>
-  <si>
-    <t>['7', '90+2']</t>
+    <t>['10', '69', '80']</t>
   </si>
   <si>
     <t>['6', '32', '48', '58']</t>
@@ -1240,10 +1240,10 @@
     <t>['2']</t>
   </si>
   <si>
-    <t>['22', '60']</t>
+    <t>['13', '18', '76', '90+4']</t>
   </si>
   <si>
-    <t>['13', '18', '76', '90+4']</t>
+    <t>['22', '60']</t>
   </si>
   <si>
     <t>['8', '13']</t>
@@ -1264,10 +1264,10 @@
     <t>['1', '2', '5', '28']</t>
   </si>
   <si>
-    <t>['33', '67']</t>
+    <t>['62', '90+3']</t>
   </si>
   <si>
-    <t>['62', '90+3']</t>
+    <t>['33', '67']</t>
   </si>
   <si>
     <t>['30', '53']</t>
@@ -1288,10 +1288,10 @@
     <t>['21', '40']</t>
   </si>
   <si>
-    <t>['3', '82']</t>
+    <t>['34']</t>
   </si>
   <si>
-    <t>['34']</t>
+    <t>['3', '82']</t>
   </si>
   <si>
     <t>['8', '32', '80']</t>
@@ -1306,13 +1306,13 @@
     <t>['3', '13']</t>
   </si>
   <si>
-    <t>['38', '66']</t>
+    <t>['11', '39']</t>
   </si>
   <si>
     <t>['24', '30', '35']</t>
   </si>
   <si>
-    <t>['11', '39']</t>
+    <t>['38', '66']</t>
   </si>
   <si>
     <t>['47', '83']</t>
@@ -2554,7 +2554,7 @@
         <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q5">
         <v>3</v>
@@ -10588,7 +10588,7 @@
         <v>93</v>
       </c>
       <c r="P44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q44">
         <v>2</v>
@@ -13678,7 +13678,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>3.63</v>
@@ -23360,7 +23360,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -27686,7 +27686,7 @@
         <v>145</v>
       </c>
       <c r="P127" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q127">
         <v>2.85</v>
@@ -31188,7 +31188,7 @@
         <v>188</v>
       </c>
       <c r="P144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -36338,7 +36338,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q169">
         <v>1.78</v>
@@ -49480,7 +49480,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>7465646</v>
+        <v>7465645</v>
       </c>
       <c r="C233" t="s">
         <v>68</v>
@@ -49495,25 +49495,25 @@
         <v>24</v>
       </c>
       <c r="G233" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H233" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233">
         <v>1</v>
       </c>
       <c r="L233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N233">
         <v>3</v>
@@ -49522,160 +49522,160 @@
         <v>250</v>
       </c>
       <c r="P233" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="Q233">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="R233">
         <v>2.5</v>
       </c>
       <c r="S233">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="T233">
         <v>1.25</v>
       </c>
       <c r="U233">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="V233">
+        <v>2.2</v>
+      </c>
+      <c r="W233">
+        <v>1.6</v>
+      </c>
+      <c r="X233">
+        <v>5.5</v>
+      </c>
+      <c r="Y233">
+        <v>1.13</v>
+      </c>
+      <c r="Z233">
+        <v>1.53</v>
+      </c>
+      <c r="AA233">
+        <v>4.5</v>
+      </c>
+      <c r="AB233">
+        <v>5.25</v>
+      </c>
+      <c r="AC233">
+        <v>1.03</v>
+      </c>
+      <c r="AD233">
+        <v>11</v>
+      </c>
+      <c r="AE233">
+        <v>1.18</v>
+      </c>
+      <c r="AF233">
+        <v>4.75</v>
+      </c>
+      <c r="AG233">
+        <v>1.57</v>
+      </c>
+      <c r="AH233">
+        <v>2.38</v>
+      </c>
+      <c r="AI233">
+        <v>1.62</v>
+      </c>
+      <c r="AJ233">
         <v>2.1</v>
       </c>
-      <c r="W233">
+      <c r="AK233">
+        <v>1.15</v>
+      </c>
+      <c r="AL233">
+        <v>1.15</v>
+      </c>
+      <c r="AM233">
+        <v>2.4</v>
+      </c>
+      <c r="AN233">
+        <v>2</v>
+      </c>
+      <c r="AO233">
         <v>1.67</v>
       </c>
-      <c r="X233">
-        <v>5</v>
-      </c>
-      <c r="Y233">
-        <v>1.17</v>
-      </c>
-      <c r="Z233">
-        <v>3.6</v>
-      </c>
-      <c r="AA233">
-        <v>4</v>
-      </c>
-      <c r="AB233">
-        <v>1.91</v>
-      </c>
-      <c r="AC233">
-        <v>1.01</v>
-      </c>
-      <c r="AD233">
-        <v>17</v>
-      </c>
-      <c r="AE233">
-        <v>1.15</v>
-      </c>
-      <c r="AF233">
-        <v>5.5</v>
-      </c>
-      <c r="AG233">
-        <v>1.44</v>
-      </c>
-      <c r="AH233">
-        <v>2.7</v>
-      </c>
-      <c r="AI233">
-        <v>1.44</v>
-      </c>
-      <c r="AJ233">
-        <v>2.63</v>
-      </c>
-      <c r="AK233">
-        <v>1.9</v>
-      </c>
-      <c r="AL233">
-        <v>1.25</v>
-      </c>
-      <c r="AM233">
-        <v>1.25</v>
-      </c>
-      <c r="AN233">
-        <v>1.83</v>
-      </c>
-      <c r="AO233">
-        <v>1.73</v>
-      </c>
       <c r="AP233">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AQ233">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AR233">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AS233">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AT233">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AU233">
         <v>6</v>
       </c>
       <c r="AV233">
+        <v>5</v>
+      </c>
+      <c r="AW233">
+        <v>13</v>
+      </c>
+      <c r="AX233">
         <v>2</v>
       </c>
-      <c r="AW233">
+      <c r="AY233">
+        <v>19</v>
+      </c>
+      <c r="AZ233">
+        <v>7</v>
+      </c>
+      <c r="BA233">
         <v>11</v>
       </c>
-      <c r="AX233">
-        <v>7</v>
-      </c>
-      <c r="AY233">
-        <v>17</v>
-      </c>
-      <c r="AZ233">
-        <v>9</v>
-      </c>
-      <c r="BA233">
-        <v>4</v>
-      </c>
       <c r="BB233">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC233">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD233">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="BE233">
         <v>6.75</v>
       </c>
       <c r="BF233">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="BG233">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BH233">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI233">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BJ233">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="BK233">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BL233">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="BM233">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="BN233">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BO233">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BP233">
         <v>1.38</v>
@@ -49686,7 +49686,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>7465645</v>
+        <v>7465646</v>
       </c>
       <c r="C234" t="s">
         <v>68</v>
@@ -49701,25 +49701,25 @@
         <v>24</v>
       </c>
       <c r="G234" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H234" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K234">
         <v>1</v>
       </c>
       <c r="L234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N234">
         <v>3</v>
@@ -49728,160 +49728,160 @@
         <v>251</v>
       </c>
       <c r="P234" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="Q234">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="R234">
         <v>2.5</v>
       </c>
       <c r="S234">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="T234">
         <v>1.25</v>
       </c>
       <c r="U234">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="V234">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W234">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X234">
+        <v>5</v>
+      </c>
+      <c r="Y234">
+        <v>1.17</v>
+      </c>
+      <c r="Z234">
+        <v>3.6</v>
+      </c>
+      <c r="AA234">
+        <v>4</v>
+      </c>
+      <c r="AB234">
+        <v>1.91</v>
+      </c>
+      <c r="AC234">
+        <v>1.01</v>
+      </c>
+      <c r="AD234">
+        <v>17</v>
+      </c>
+      <c r="AE234">
+        <v>1.15</v>
+      </c>
+      <c r="AF234">
         <v>5.5</v>
       </c>
-      <c r="Y234">
-        <v>1.13</v>
-      </c>
-      <c r="Z234">
-        <v>1.53</v>
-      </c>
-      <c r="AA234">
-        <v>4.5</v>
-      </c>
-      <c r="AB234">
-        <v>5.25</v>
-      </c>
-      <c r="AC234">
-        <v>1.03</v>
-      </c>
-      <c r="AD234">
-        <v>11</v>
-      </c>
-      <c r="AE234">
-        <v>1.18</v>
-      </c>
-      <c r="AF234">
-        <v>4.75</v>
-      </c>
       <c r="AG234">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH234">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AI234">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ234">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK234">
-        <v>1.15</v>
+        <v>1.9</v>
       </c>
       <c r="AL234">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AM234">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AN234">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AO234">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AP234">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AQ234">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AR234">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AS234">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AT234">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="AU234">
         <v>6</v>
       </c>
       <c r="AV234">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW234">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX234">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY234">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ234">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA234">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BB234">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC234">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD234">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="BE234">
         <v>6.75</v>
       </c>
       <c r="BF234">
-        <v>2.75</v>
+        <v>1.58</v>
       </c>
       <c r="BG234">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BH234">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BI234">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BJ234">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="BK234">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BL234">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BM234">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="BN234">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="BO234">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BP234">
         <v>1.38</v>
@@ -52364,7 +52364,7 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>7465666</v>
+        <v>7465667</v>
       </c>
       <c r="C247" t="s">
         <v>68</v>
@@ -52379,25 +52379,25 @@
         <v>25</v>
       </c>
       <c r="G247" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H247" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I247">
         <v>0</v>
       </c>
       <c r="J247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L247">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M247">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N247">
         <v>5</v>
@@ -52412,7 +52412,7 @@
         <v>4.5</v>
       </c>
       <c r="R247">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S247">
         <v>2.2</v>
@@ -52424,16 +52424,16 @@
         <v>3.75</v>
       </c>
       <c r="V247">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W247">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X247">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y247">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z247">
         <v>4.33</v>
@@ -52457,10 +52457,10 @@
         <v>5.5</v>
       </c>
       <c r="AG247">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AH247">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AI247">
         <v>1.5</v>
@@ -52469,100 +52469,100 @@
         <v>2.5</v>
       </c>
       <c r="AK247">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL247">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AM247">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AN247">
-        <v>1.36</v>
+        <v>0.73</v>
       </c>
       <c r="AO247">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="AP247">
-        <v>1.27</v>
+        <v>0.6</v>
       </c>
       <c r="AQ247">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AR247">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AS247">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AT247">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="AU247">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV247">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AW247">
         <v>6</v>
       </c>
       <c r="AX247">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY247">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ247">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BA247">
+        <v>3</v>
+      </c>
+      <c r="BB247">
+        <v>6</v>
+      </c>
+      <c r="BC247">
         <v>9</v>
       </c>
-      <c r="BB247">
-        <v>7</v>
-      </c>
-      <c r="BC247">
-        <v>16</v>
-      </c>
       <c r="BD247">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE247">
         <v>7</v>
       </c>
       <c r="BF247">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BG247">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BH247">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BI247">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BJ247">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="BK247">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BL247">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="BM247">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="BN247">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BO247">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BP247">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="248" spans="1:68">
@@ -52570,7 +52570,7 @@
         <v>247</v>
       </c>
       <c r="B248">
-        <v>7465667</v>
+        <v>7465668</v>
       </c>
       <c r="C248" t="s">
         <v>68</v>
@@ -52585,88 +52585,88 @@
         <v>25</v>
       </c>
       <c r="G248" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H248" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="I248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
         <v>2</v>
       </c>
-      <c r="K248">
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
         <v>2</v>
-      </c>
-      <c r="L248">
-        <v>1</v>
-      </c>
-      <c r="M248">
-        <v>4</v>
-      </c>
-      <c r="N248">
-        <v>5</v>
       </c>
       <c r="O248" t="s">
         <v>261</v>
       </c>
       <c r="P248" t="s">
-        <v>409</v>
+        <v>93</v>
       </c>
       <c r="Q248">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R248">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S248">
+        <v>2.75</v>
+      </c>
+      <c r="T248">
+        <v>1.29</v>
+      </c>
+      <c r="U248">
+        <v>3.5</v>
+      </c>
+      <c r="V248">
+        <v>2.38</v>
+      </c>
+      <c r="W248">
+        <v>1.53</v>
+      </c>
+      <c r="X248">
+        <v>5.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.14</v>
+      </c>
+      <c r="Z248">
+        <v>3</v>
+      </c>
+      <c r="AA248">
+        <v>3.6</v>
+      </c>
+      <c r="AB248">
         <v>2.2</v>
-      </c>
-      <c r="T248">
-        <v>1.25</v>
-      </c>
-      <c r="U248">
-        <v>3.75</v>
-      </c>
-      <c r="V248">
-        <v>2.1</v>
-      </c>
-      <c r="W248">
-        <v>1.67</v>
-      </c>
-      <c r="X248">
-        <v>4.5</v>
-      </c>
-      <c r="Y248">
-        <v>1.18</v>
-      </c>
-      <c r="Z248">
-        <v>4.33</v>
-      </c>
-      <c r="AA248">
-        <v>4.33</v>
-      </c>
-      <c r="AB248">
-        <v>1.67</v>
       </c>
       <c r="AC248">
         <v>1.01</v>
       </c>
       <c r="AD248">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE248">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF248">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AG248">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH248">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AI248">
         <v>1.5</v>
@@ -52675,100 +52675,100 @@
         <v>2.5</v>
       </c>
       <c r="AK248">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AL248">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AM248">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AN248">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AO248">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AP248">
-        <v>0.6</v>
+        <v>1.19</v>
       </c>
       <c r="AQ248">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR248">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AS248">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AT248">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="AU248">
         <v>6</v>
       </c>
       <c r="AV248">
+        <v>5</v>
+      </c>
+      <c r="AW248">
+        <v>15</v>
+      </c>
+      <c r="AX248">
+        <v>5</v>
+      </c>
+      <c r="AY248">
+        <v>21</v>
+      </c>
+      <c r="AZ248">
         <v>10</v>
-      </c>
-      <c r="AW248">
-        <v>6</v>
-      </c>
-      <c r="AX248">
-        <v>14</v>
-      </c>
-      <c r="AY248">
-        <v>14</v>
-      </c>
-      <c r="AZ248">
-        <v>32</v>
       </c>
       <c r="BA248">
         <v>3</v>
       </c>
       <c r="BB248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC248">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD248">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="BE248">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF248">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="BG248">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BH248">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BI248">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BJ248">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="BK248">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="BL248">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="BM248">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="BN248">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="BO248">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="BP248">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="249" spans="1:68">
@@ -52776,7 +52776,7 @@
         <v>248</v>
       </c>
       <c r="B249">
-        <v>7465668</v>
+        <v>7465666</v>
       </c>
       <c r="C249" t="s">
         <v>68</v>
@@ -52791,88 +52791,88 @@
         <v>25</v>
       </c>
       <c r="G249" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H249" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K249">
         <v>1</v>
       </c>
       <c r="L249">
+        <v>3</v>
+      </c>
+      <c r="M249">
         <v>2</v>
       </c>
-      <c r="M249">
-        <v>0</v>
-      </c>
       <c r="N249">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O249" t="s">
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>93</v>
+        <v>409</v>
       </c>
       <c r="Q249">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R249">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S249">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="T249">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U249">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V249">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="W249">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X249">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y249">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z249">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AA249">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AB249">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AC249">
         <v>1.01</v>
       </c>
       <c r="AD249">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE249">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF249">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AG249">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH249">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AI249">
         <v>1.5</v>
@@ -52881,100 +52881,100 @@
         <v>2.5</v>
       </c>
       <c r="AK249">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AL249">
+        <v>1.16</v>
+      </c>
+      <c r="AM249">
+        <v>1.2</v>
+      </c>
+      <c r="AN249">
+        <v>1.36</v>
+      </c>
+      <c r="AO249">
+        <v>1.42</v>
+      </c>
+      <c r="AP249">
+        <v>1.27</v>
+      </c>
+      <c r="AQ249">
+        <v>1.44</v>
+      </c>
+      <c r="AR249">
+        <v>1.71</v>
+      </c>
+      <c r="AS249">
+        <v>1.73</v>
+      </c>
+      <c r="AT249">
+        <v>3.44</v>
+      </c>
+      <c r="AU249">
+        <v>9</v>
+      </c>
+      <c r="AV249">
+        <v>4</v>
+      </c>
+      <c r="AW249">
+        <v>6</v>
+      </c>
+      <c r="AX249">
+        <v>8</v>
+      </c>
+      <c r="AY249">
+        <v>15</v>
+      </c>
+      <c r="AZ249">
+        <v>12</v>
+      </c>
+      <c r="BA249">
+        <v>9</v>
+      </c>
+      <c r="BB249">
+        <v>7</v>
+      </c>
+      <c r="BC249">
+        <v>16</v>
+      </c>
+      <c r="BD249">
+        <v>2.9</v>
+      </c>
+      <c r="BE249">
+        <v>7</v>
+      </c>
+      <c r="BF249">
+        <v>1.5</v>
+      </c>
+      <c r="BG249">
         <v>1.22</v>
       </c>
-      <c r="AM249">
+      <c r="BH249">
+        <v>3.8</v>
+      </c>
+      <c r="BI249">
         <v>1.38</v>
       </c>
-      <c r="AN249">
-        <v>0.83</v>
-      </c>
-      <c r="AO249">
-        <v>1.9</v>
-      </c>
-      <c r="AP249">
-        <v>1.19</v>
-      </c>
-      <c r="AQ249">
-        <v>1.87</v>
-      </c>
-      <c r="AR249">
-        <v>1.74</v>
-      </c>
-      <c r="AS249">
-        <v>1.61</v>
-      </c>
-      <c r="AT249">
-        <v>3.35</v>
-      </c>
-      <c r="AU249">
-        <v>6</v>
-      </c>
-      <c r="AV249">
-        <v>5</v>
-      </c>
-      <c r="AW249">
-        <v>15</v>
-      </c>
-      <c r="AX249">
-        <v>5</v>
-      </c>
-      <c r="AY249">
-        <v>21</v>
-      </c>
-      <c r="AZ249">
-        <v>10</v>
-      </c>
-      <c r="BA249">
-        <v>3</v>
-      </c>
-      <c r="BB249">
-        <v>5</v>
-      </c>
-      <c r="BC249">
-        <v>8</v>
-      </c>
-      <c r="BD249">
-        <v>2.17</v>
-      </c>
-      <c r="BE249">
-        <v>6.75</v>
-      </c>
-      <c r="BF249">
-        <v>1.81</v>
-      </c>
-      <c r="BG249">
-        <v>1.19</v>
-      </c>
-      <c r="BH249">
-        <v>4.1</v>
-      </c>
-      <c r="BI249">
-        <v>1.33</v>
-      </c>
       <c r="BJ249">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="BK249">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BL249">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="BM249">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="BN249">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="BO249">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="BP249">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="250" spans="1:68">
@@ -52982,7 +52982,7 @@
         <v>249</v>
       </c>
       <c r="B250">
-        <v>7465674</v>
+        <v>7465677</v>
       </c>
       <c r="C250" t="s">
         <v>68</v>
@@ -52997,190 +52997,190 @@
         <v>26</v>
       </c>
       <c r="G250" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H250" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250">
         <v>0</v>
       </c>
       <c r="K250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M250">
         <v>1</v>
       </c>
       <c r="N250">
+        <v>3</v>
+      </c>
+      <c r="O250" t="s">
+        <v>263</v>
+      </c>
+      <c r="P250" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q250">
+        <v>2.75</v>
+      </c>
+      <c r="R250">
+        <v>2.3</v>
+      </c>
+      <c r="S250">
+        <v>3.1</v>
+      </c>
+      <c r="T250">
+        <v>1.25</v>
+      </c>
+      <c r="U250">
+        <v>3.55</v>
+      </c>
+      <c r="V250">
+        <v>2.1</v>
+      </c>
+      <c r="W250">
+        <v>1.65</v>
+      </c>
+      <c r="X250">
+        <v>4.8</v>
+      </c>
+      <c r="Y250">
+        <v>1.16</v>
+      </c>
+      <c r="Z250">
+        <v>2.35</v>
+      </c>
+      <c r="AA250">
+        <v>3.7</v>
+      </c>
+      <c r="AB250">
+        <v>2.7</v>
+      </c>
+      <c r="AC250">
+        <v>1.01</v>
+      </c>
+      <c r="AD250">
+        <v>13</v>
+      </c>
+      <c r="AE250">
+        <v>1.17</v>
+      </c>
+      <c r="AF250">
+        <v>5</v>
+      </c>
+      <c r="AG250">
+        <v>1.5</v>
+      </c>
+      <c r="AH250">
+        <v>2.55</v>
+      </c>
+      <c r="AI250">
+        <v>1.4</v>
+      </c>
+      <c r="AJ250">
+        <v>2.65</v>
+      </c>
+      <c r="AK250">
+        <v>1.45</v>
+      </c>
+      <c r="AL250">
+        <v>1.22</v>
+      </c>
+      <c r="AM250">
+        <v>1.57</v>
+      </c>
+      <c r="AN250">
+        <v>1.83</v>
+      </c>
+      <c r="AO250">
+        <v>1.23</v>
+      </c>
+      <c r="AP250">
+        <v>2.07</v>
+      </c>
+      <c r="AQ250">
+        <v>1.06</v>
+      </c>
+      <c r="AR250">
+        <v>1.74</v>
+      </c>
+      <c r="AS250">
+        <v>1.76</v>
+      </c>
+      <c r="AT250">
+        <v>3.5</v>
+      </c>
+      <c r="AU250">
+        <v>4</v>
+      </c>
+      <c r="AV250">
+        <v>8</v>
+      </c>
+      <c r="AW250">
+        <v>5</v>
+      </c>
+      <c r="AX250">
+        <v>13</v>
+      </c>
+      <c r="AY250">
+        <v>9</v>
+      </c>
+      <c r="AZ250">
+        <v>21</v>
+      </c>
+      <c r="BA250">
+        <v>0</v>
+      </c>
+      <c r="BB250">
+        <v>8</v>
+      </c>
+      <c r="BC250">
+        <v>8</v>
+      </c>
+      <c r="BD250">
         <v>2</v>
       </c>
-      <c r="O250" t="s">
-        <v>127</v>
-      </c>
-      <c r="P250" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q250">
-        <v>1.91</v>
-      </c>
-      <c r="R250">
-        <v>2.5</v>
-      </c>
-      <c r="S250">
-        <v>6</v>
-      </c>
-      <c r="T250">
-        <v>1.29</v>
-      </c>
-      <c r="U250">
-        <v>3.5</v>
-      </c>
-      <c r="V250">
-        <v>2.38</v>
-      </c>
-      <c r="W250">
-        <v>1.53</v>
-      </c>
-      <c r="X250">
-        <v>5.5</v>
-      </c>
-      <c r="Y250">
-        <v>1.14</v>
-      </c>
-      <c r="Z250">
-        <v>1.42</v>
-      </c>
-      <c r="AA250">
-        <v>4.5</v>
-      </c>
-      <c r="AB250">
-        <v>6</v>
-      </c>
-      <c r="AC250">
-        <v>1.02</v>
-      </c>
-      <c r="AD250">
-        <v>17</v>
-      </c>
-      <c r="AE250">
-        <v>1.18</v>
-      </c>
-      <c r="AF250">
-        <v>4.75</v>
-      </c>
-      <c r="AG250">
-        <v>1.6</v>
-      </c>
-      <c r="AH250">
-        <v>2.3</v>
-      </c>
-      <c r="AI250">
-        <v>1.8</v>
-      </c>
-      <c r="AJ250">
-        <v>1.91</v>
-      </c>
-      <c r="AK250">
-        <v>1.1</v>
-      </c>
-      <c r="AL250">
-        <v>1.18</v>
-      </c>
-      <c r="AM250">
-        <v>2.85</v>
-      </c>
-      <c r="AN250">
-        <v>1.33</v>
-      </c>
-      <c r="AO250">
-        <v>0.42</v>
-      </c>
-      <c r="AP250">
-        <v>1.53</v>
-      </c>
-      <c r="AQ250">
-        <v>0.53</v>
-      </c>
-      <c r="AR250">
-        <v>1.71</v>
-      </c>
-      <c r="AS250">
-        <v>1.1</v>
-      </c>
-      <c r="AT250">
-        <v>2.81</v>
-      </c>
-      <c r="AU250">
-        <v>6</v>
-      </c>
-      <c r="AV250">
-        <v>0</v>
-      </c>
-      <c r="AW250">
-        <v>11</v>
-      </c>
-      <c r="AX250">
-        <v>0</v>
-      </c>
-      <c r="AY250">
-        <v>23</v>
-      </c>
-      <c r="AZ250">
-        <v>0</v>
-      </c>
-      <c r="BA250">
-        <v>5</v>
-      </c>
-      <c r="BB250">
-        <v>5</v>
-      </c>
-      <c r="BC250">
-        <v>10</v>
-      </c>
-      <c r="BD250">
-        <v>1.3</v>
-      </c>
       <c r="BE250">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF250">
-        <v>3.9</v>
+        <v>1.98</v>
       </c>
       <c r="BG250">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BH250">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI250">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BJ250">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BK250">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BL250">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BM250">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BN250">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BO250">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BP250">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="251" spans="1:68">
@@ -53188,7 +53188,7 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>7465673</v>
+        <v>7465669</v>
       </c>
       <c r="C251" t="s">
         <v>68</v>
@@ -53203,190 +53203,190 @@
         <v>26</v>
       </c>
       <c r="G251" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H251" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="I251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J251">
         <v>0</v>
       </c>
       <c r="K251">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M251">
         <v>0</v>
       </c>
       <c r="N251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O251" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="P251" t="s">
         <v>93</v>
       </c>
       <c r="Q251">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="R251">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S251">
+        <v>6.5</v>
+      </c>
+      <c r="T251">
+        <v>1.29</v>
+      </c>
+      <c r="U251">
         <v>3.5</v>
       </c>
-      <c r="T251">
-        <v>1.28</v>
-      </c>
-      <c r="U251">
-        <v>3.4</v>
-      </c>
       <c r="V251">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="W251">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X251">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y251">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z251">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AA251">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB251">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="AC251">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AD251">
         <v>17</v>
       </c>
       <c r="AE251">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF251">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AG251">
+        <v>1.53</v>
+      </c>
+      <c r="AH251">
+        <v>2.4</v>
+      </c>
+      <c r="AI251">
+        <v>1.8</v>
+      </c>
+      <c r="AJ251">
+        <v>1.91</v>
+      </c>
+      <c r="AK251">
+        <v>1.12</v>
+      </c>
+      <c r="AL251">
+        <v>1.17</v>
+      </c>
+      <c r="AM251">
+        <v>2.75</v>
+      </c>
+      <c r="AN251">
+        <v>2.08</v>
+      </c>
+      <c r="AO251">
+        <v>0.75</v>
+      </c>
+      <c r="AP251">
+        <v>2.06</v>
+      </c>
+      <c r="AQ251">
+        <v>0.75</v>
+      </c>
+      <c r="AR251">
+        <v>1.85</v>
+      </c>
+      <c r="AS251">
+        <v>1.59</v>
+      </c>
+      <c r="AT251">
+        <v>3.44</v>
+      </c>
+      <c r="AU251">
+        <v>8</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>9</v>
+      </c>
+      <c r="AX251">
+        <v>3</v>
+      </c>
+      <c r="AY251">
+        <v>17</v>
+      </c>
+      <c r="AZ251">
+        <v>7</v>
+      </c>
+      <c r="BA251">
+        <v>6</v>
+      </c>
+      <c r="BB251">
+        <v>5</v>
+      </c>
+      <c r="BC251">
+        <v>11</v>
+      </c>
+      <c r="BD251">
+        <v>1.38</v>
+      </c>
+      <c r="BE251">
+        <v>7</v>
+      </c>
+      <c r="BF251">
+        <v>3.4</v>
+      </c>
+      <c r="BG251">
+        <v>1.27</v>
+      </c>
+      <c r="BH251">
+        <v>3.4</v>
+      </c>
+      <c r="BI251">
+        <v>1.46</v>
+      </c>
+      <c r="BJ251">
+        <v>2.5</v>
+      </c>
+      <c r="BK251">
+        <v>1.74</v>
+      </c>
+      <c r="BL251">
+        <v>1.97</v>
+      </c>
+      <c r="BM251">
+        <v>2.17</v>
+      </c>
+      <c r="BN251">
         <v>1.6</v>
       </c>
-      <c r="AH251">
-        <v>2.3</v>
-      </c>
-      <c r="AI251">
-        <v>1.52</v>
-      </c>
-      <c r="AJ251">
-        <v>2.5</v>
-      </c>
-      <c r="AK251">
-        <v>1.4</v>
-      </c>
-      <c r="AL251">
-        <v>1.22</v>
-      </c>
-      <c r="AM251">
-        <v>1.66</v>
-      </c>
-      <c r="AN251">
-        <v>1.83</v>
-      </c>
-      <c r="AO251">
-        <v>1.54</v>
-      </c>
-      <c r="AP251">
-        <v>1.67</v>
-      </c>
-      <c r="AQ251">
-        <v>1.53</v>
-      </c>
-      <c r="AR251">
-        <v>1.74</v>
-      </c>
-      <c r="AS251">
-        <v>1.24</v>
-      </c>
-      <c r="AT251">
-        <v>2.98</v>
-      </c>
-      <c r="AU251">
-        <v>7</v>
-      </c>
-      <c r="AV251">
-        <v>3</v>
-      </c>
-      <c r="AW251">
-        <v>2</v>
-      </c>
-      <c r="AX251">
-        <v>9</v>
-      </c>
-      <c r="AY251">
-        <v>9</v>
-      </c>
-      <c r="AZ251">
-        <v>12</v>
-      </c>
-      <c r="BA251">
-        <v>2</v>
-      </c>
-      <c r="BB251">
-        <v>4</v>
-      </c>
-      <c r="BC251">
-        <v>6</v>
-      </c>
-      <c r="BD251">
-        <v>1.81</v>
-      </c>
-      <c r="BE251">
-        <v>6.5</v>
-      </c>
-      <c r="BF251">
-        <v>2.18</v>
-      </c>
-      <c r="BG251">
-        <v>1.3</v>
-      </c>
-      <c r="BH251">
-        <v>3.15</v>
-      </c>
-      <c r="BI251">
-        <v>1.5</v>
-      </c>
-      <c r="BJ251">
-        <v>2.33</v>
-      </c>
-      <c r="BK251">
-        <v>1.84</v>
-      </c>
-      <c r="BL251">
-        <v>1.84</v>
-      </c>
-      <c r="BM251">
-        <v>2.32</v>
-      </c>
-      <c r="BN251">
-        <v>1.52</v>
-      </c>
       <c r="BO251">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="BP251">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="252" spans="1:68">
@@ -53600,7 +53600,7 @@
         <v>252</v>
       </c>
       <c r="B253">
-        <v>7465669</v>
+        <v>7465673</v>
       </c>
       <c r="C253" t="s">
         <v>68</v>
@@ -53615,190 +53615,190 @@
         <v>26</v>
       </c>
       <c r="G253" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H253" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="I253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J253">
         <v>0</v>
       </c>
       <c r="K253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M253">
         <v>0</v>
       </c>
       <c r="N253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O253" t="s">
-        <v>145</v>
+        <v>264</v>
       </c>
       <c r="P253" t="s">
         <v>93</v>
       </c>
       <c r="Q253">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R253">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S253">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="T253">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="U253">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V253">
+        <v>2.34</v>
+      </c>
+      <c r="W253">
+        <v>1.54</v>
+      </c>
+      <c r="X253">
+        <v>5.4</v>
+      </c>
+      <c r="Y253">
+        <v>1.12</v>
+      </c>
+      <c r="Z253">
         <v>2.25</v>
       </c>
-      <c r="W253">
-        <v>1.57</v>
-      </c>
-      <c r="X253">
-        <v>5.5</v>
-      </c>
-      <c r="Y253">
-        <v>1.14</v>
-      </c>
-      <c r="Z253">
-        <v>1.36</v>
-      </c>
       <c r="AA253">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB253">
-        <v>7</v>
+        <v>2.95</v>
       </c>
       <c r="AC253">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD253">
         <v>17</v>
       </c>
       <c r="AE253">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF253">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AG253">
+        <v>1.6</v>
+      </c>
+      <c r="AH253">
+        <v>2.3</v>
+      </c>
+      <c r="AI253">
+        <v>1.52</v>
+      </c>
+      <c r="AJ253">
+        <v>2.5</v>
+      </c>
+      <c r="AK253">
+        <v>1.4</v>
+      </c>
+      <c r="AL253">
+        <v>1.22</v>
+      </c>
+      <c r="AM253">
+        <v>1.66</v>
+      </c>
+      <c r="AN253">
+        <v>1.83</v>
+      </c>
+      <c r="AO253">
+        <v>1.54</v>
+      </c>
+      <c r="AP253">
+        <v>1.67</v>
+      </c>
+      <c r="AQ253">
         <v>1.53</v>
       </c>
-      <c r="AH253">
-        <v>2.4</v>
-      </c>
-      <c r="AI253">
-        <v>1.8</v>
-      </c>
-      <c r="AJ253">
-        <v>1.91</v>
-      </c>
-      <c r="AK253">
-        <v>1.12</v>
-      </c>
-      <c r="AL253">
-        <v>1.17</v>
-      </c>
-      <c r="AM253">
-        <v>2.75</v>
-      </c>
-      <c r="AN253">
-        <v>2.08</v>
-      </c>
-      <c r="AO253">
-        <v>0.75</v>
-      </c>
-      <c r="AP253">
-        <v>2.06</v>
-      </c>
-      <c r="AQ253">
-        <v>0.75</v>
-      </c>
       <c r="AR253">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AS253">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="AT253">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="AU253">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV253">
+        <v>3</v>
+      </c>
+      <c r="AW253">
+        <v>2</v>
+      </c>
+      <c r="AX253">
+        <v>9</v>
+      </c>
+      <c r="AY253">
+        <v>9</v>
+      </c>
+      <c r="AZ253">
+        <v>12</v>
+      </c>
+      <c r="BA253">
+        <v>2</v>
+      </c>
+      <c r="BB253">
         <v>4</v>
       </c>
-      <c r="AW253">
-        <v>9</v>
-      </c>
-      <c r="AX253">
-        <v>3</v>
-      </c>
-      <c r="AY253">
-        <v>17</v>
-      </c>
-      <c r="AZ253">
-        <v>7</v>
-      </c>
-      <c r="BA253">
+      <c r="BC253">
         <v>6</v>
       </c>
-      <c r="BB253">
-        <v>5</v>
-      </c>
-      <c r="BC253">
-        <v>11</v>
-      </c>
       <c r="BD253">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="BE253">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BF253">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="BG253">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BH253">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BI253">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BJ253">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BK253">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="BL253">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="BM253">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="BN253">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BO253">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="BP253">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="254" spans="1:68">
@@ -53806,7 +53806,7 @@
         <v>253</v>
       </c>
       <c r="B254">
-        <v>7465677</v>
+        <v>7465674</v>
       </c>
       <c r="C254" t="s">
         <v>68</v>
@@ -53821,190 +53821,190 @@
         <v>26</v>
       </c>
       <c r="G254" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H254" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J254">
         <v>0</v>
       </c>
       <c r="K254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L254">
+        <v>1</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
         <v>2</v>
       </c>
-      <c r="M254">
-        <v>1</v>
-      </c>
-      <c r="N254">
-        <v>3</v>
-      </c>
       <c r="O254" t="s">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="P254" t="s">
-        <v>281</v>
+        <v>147</v>
       </c>
       <c r="Q254">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="R254">
+        <v>2.5</v>
+      </c>
+      <c r="S254">
+        <v>6</v>
+      </c>
+      <c r="T254">
+        <v>1.29</v>
+      </c>
+      <c r="U254">
+        <v>3.5</v>
+      </c>
+      <c r="V254">
+        <v>2.38</v>
+      </c>
+      <c r="W254">
+        <v>1.53</v>
+      </c>
+      <c r="X254">
+        <v>5.5</v>
+      </c>
+      <c r="Y254">
+        <v>1.14</v>
+      </c>
+      <c r="Z254">
+        <v>1.42</v>
+      </c>
+      <c r="AA254">
+        <v>4.5</v>
+      </c>
+      <c r="AB254">
+        <v>6</v>
+      </c>
+      <c r="AC254">
+        <v>1.02</v>
+      </c>
+      <c r="AD254">
+        <v>17</v>
+      </c>
+      <c r="AE254">
+        <v>1.18</v>
+      </c>
+      <c r="AF254">
+        <v>4.75</v>
+      </c>
+      <c r="AG254">
+        <v>1.6</v>
+      </c>
+      <c r="AH254">
         <v>2.3</v>
       </c>
-      <c r="S254">
-        <v>3.1</v>
-      </c>
-      <c r="T254">
+      <c r="AI254">
+        <v>1.8</v>
+      </c>
+      <c r="AJ254">
+        <v>1.91</v>
+      </c>
+      <c r="AK254">
+        <v>1.1</v>
+      </c>
+      <c r="AL254">
+        <v>1.18</v>
+      </c>
+      <c r="AM254">
+        <v>2.85</v>
+      </c>
+      <c r="AN254">
+        <v>1.33</v>
+      </c>
+      <c r="AO254">
+        <v>0.42</v>
+      </c>
+      <c r="AP254">
+        <v>1.53</v>
+      </c>
+      <c r="AQ254">
+        <v>0.53</v>
+      </c>
+      <c r="AR254">
+        <v>1.71</v>
+      </c>
+      <c r="AS254">
+        <v>1.1</v>
+      </c>
+      <c r="AT254">
+        <v>2.81</v>
+      </c>
+      <c r="AU254">
+        <v>6</v>
+      </c>
+      <c r="AV254">
+        <v>0</v>
+      </c>
+      <c r="AW254">
+        <v>11</v>
+      </c>
+      <c r="AX254">
+        <v>0</v>
+      </c>
+      <c r="AY254">
+        <v>23</v>
+      </c>
+      <c r="AZ254">
+        <v>0</v>
+      </c>
+      <c r="BA254">
+        <v>5</v>
+      </c>
+      <c r="BB254">
+        <v>5</v>
+      </c>
+      <c r="BC254">
+        <v>10</v>
+      </c>
+      <c r="BD254">
+        <v>1.3</v>
+      </c>
+      <c r="BE254">
+        <v>8</v>
+      </c>
+      <c r="BF254">
+        <v>3.9</v>
+      </c>
+      <c r="BG254">
         <v>1.25</v>
       </c>
-      <c r="U254">
-        <v>3.55</v>
-      </c>
-      <c r="V254">
-        <v>2.1</v>
-      </c>
-      <c r="W254">
-        <v>1.65</v>
-      </c>
-      <c r="X254">
-        <v>4.8</v>
-      </c>
-      <c r="Y254">
-        <v>1.16</v>
-      </c>
-      <c r="Z254">
-        <v>2.35</v>
-      </c>
-      <c r="AA254">
-        <v>3.7</v>
-      </c>
-      <c r="AB254">
-        <v>2.7</v>
-      </c>
-      <c r="AC254">
-        <v>1.01</v>
-      </c>
-      <c r="AD254">
-        <v>13</v>
-      </c>
-      <c r="AE254">
-        <v>1.17</v>
-      </c>
-      <c r="AF254">
-        <v>5</v>
-      </c>
-      <c r="AG254">
-        <v>1.5</v>
-      </c>
-      <c r="AH254">
+      <c r="BH254">
+        <v>3.4</v>
+      </c>
+      <c r="BI254">
+        <v>1.44</v>
+      </c>
+      <c r="BJ254">
         <v>2.55</v>
       </c>
-      <c r="AI254">
+      <c r="BK254">
+        <v>1.74</v>
+      </c>
+      <c r="BL254">
+        <v>1.98</v>
+      </c>
+      <c r="BM254">
+        <v>2.12</v>
+      </c>
+      <c r="BN254">
+        <v>1.63</v>
+      </c>
+      <c r="BO254">
+        <v>2.65</v>
+      </c>
+      <c r="BP254">
         <v>1.4</v>
-      </c>
-      <c r="AJ254">
-        <v>2.65</v>
-      </c>
-      <c r="AK254">
-        <v>1.45</v>
-      </c>
-      <c r="AL254">
-        <v>1.22</v>
-      </c>
-      <c r="AM254">
-        <v>1.57</v>
-      </c>
-      <c r="AN254">
-        <v>1.83</v>
-      </c>
-      <c r="AO254">
-        <v>1.23</v>
-      </c>
-      <c r="AP254">
-        <v>2.07</v>
-      </c>
-      <c r="AQ254">
-        <v>1.06</v>
-      </c>
-      <c r="AR254">
-        <v>1.74</v>
-      </c>
-      <c r="AS254">
-        <v>1.76</v>
-      </c>
-      <c r="AT254">
-        <v>3.5</v>
-      </c>
-      <c r="AU254">
-        <v>4</v>
-      </c>
-      <c r="AV254">
-        <v>8</v>
-      </c>
-      <c r="AW254">
-        <v>5</v>
-      </c>
-      <c r="AX254">
-        <v>13</v>
-      </c>
-      <c r="AY254">
-        <v>9</v>
-      </c>
-      <c r="AZ254">
-        <v>21</v>
-      </c>
-      <c r="BA254">
-        <v>0</v>
-      </c>
-      <c r="BB254">
-        <v>8</v>
-      </c>
-      <c r="BC254">
-        <v>8</v>
-      </c>
-      <c r="BD254">
-        <v>2</v>
-      </c>
-      <c r="BE254">
-        <v>6.4</v>
-      </c>
-      <c r="BF254">
-        <v>1.98</v>
-      </c>
-      <c r="BG254">
-        <v>1.27</v>
-      </c>
-      <c r="BH254">
-        <v>3.3</v>
-      </c>
-      <c r="BI254">
-        <v>1.47</v>
-      </c>
-      <c r="BJ254">
-        <v>2.48</v>
-      </c>
-      <c r="BK254">
-        <v>1.76</v>
-      </c>
-      <c r="BL254">
-        <v>1.93</v>
-      </c>
-      <c r="BM254">
-        <v>2.18</v>
-      </c>
-      <c r="BN254">
-        <v>1.58</v>
-      </c>
-      <c r="BO254">
-        <v>2.8</v>
-      </c>
-      <c r="BP254">
-        <v>1.38</v>
       </c>
     </row>
     <row r="255" spans="1:68">
@@ -56278,7 +56278,7 @@
         <v>265</v>
       </c>
       <c r="B266">
-        <v>7465616</v>
+        <v>7465690</v>
       </c>
       <c r="C266" t="s">
         <v>68</v>
@@ -56290,193 +56290,193 @@
         <v>45712.66666666666</v>
       </c>
       <c r="F266">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G266" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H266" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="I266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K266">
+        <v>0</v>
+      </c>
+      <c r="L266">
+        <v>1</v>
+      </c>
+      <c r="M266">
+        <v>1</v>
+      </c>
+      <c r="N266">
         <v>2</v>
-      </c>
-      <c r="L266">
-        <v>1</v>
-      </c>
-      <c r="M266">
-        <v>2</v>
-      </c>
-      <c r="N266">
-        <v>3</v>
       </c>
       <c r="O266" t="s">
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>416</v>
+        <v>337</v>
       </c>
       <c r="Q266">
+        <v>4</v>
+      </c>
+      <c r="R266">
+        <v>2.5</v>
+      </c>
+      <c r="S266">
+        <v>2.4</v>
+      </c>
+      <c r="T266">
+        <v>1.25</v>
+      </c>
+      <c r="U266">
         <v>3.75</v>
       </c>
-      <c r="R266">
-        <v>2.38</v>
-      </c>
-      <c r="S266">
+      <c r="V266">
+        <v>2.2</v>
+      </c>
+      <c r="W266">
+        <v>1.62</v>
+      </c>
+      <c r="X266">
+        <v>5</v>
+      </c>
+      <c r="Y266">
+        <v>1.17</v>
+      </c>
+      <c r="Z266">
+        <v>3.5</v>
+      </c>
+      <c r="AA266">
+        <v>4.2</v>
+      </c>
+      <c r="AB266">
+        <v>1.85</v>
+      </c>
+      <c r="AC266">
+        <v>1.03</v>
+      </c>
+      <c r="AD266">
+        <v>11</v>
+      </c>
+      <c r="AE266">
+        <v>1.16</v>
+      </c>
+      <c r="AF266">
+        <v>5</v>
+      </c>
+      <c r="AG266">
+        <v>1.5</v>
+      </c>
+      <c r="AH266">
         <v>2.5</v>
       </c>
-      <c r="T266">
-        <v>1.3</v>
-      </c>
-      <c r="U266">
-        <v>3.4</v>
-      </c>
-      <c r="V266">
-        <v>2.38</v>
-      </c>
-      <c r="W266">
-        <v>1.53</v>
-      </c>
-      <c r="X266">
-        <v>6</v>
-      </c>
-      <c r="Y266">
-        <v>1.13</v>
-      </c>
-      <c r="Z266">
-        <v>3.25</v>
-      </c>
-      <c r="AA266">
-        <v>3.8</v>
-      </c>
-      <c r="AB266">
+      <c r="AI266">
+        <v>1.5</v>
+      </c>
+      <c r="AJ266">
+        <v>2.5</v>
+      </c>
+      <c r="AK266">
+        <v>1.8</v>
+      </c>
+      <c r="AL266">
+        <v>1.2</v>
+      </c>
+      <c r="AM266">
+        <v>1.35</v>
+      </c>
+      <c r="AN266">
+        <v>1.5</v>
+      </c>
+      <c r="AO266">
+        <v>2.15</v>
+      </c>
+      <c r="AP266">
+        <v>1.27</v>
+      </c>
+      <c r="AQ266">
         <v>2</v>
       </c>
-      <c r="AC266">
-        <v>1.02</v>
-      </c>
-      <c r="AD266">
-        <v>17</v>
-      </c>
-      <c r="AE266">
-        <v>1.18</v>
-      </c>
-      <c r="AF266">
-        <v>4.75</v>
-      </c>
-      <c r="AG266">
+      <c r="AR266">
+        <v>1.73</v>
+      </c>
+      <c r="AS266">
+        <v>1.92</v>
+      </c>
+      <c r="AT266">
+        <v>3.65</v>
+      </c>
+      <c r="AU266">
+        <v>4</v>
+      </c>
+      <c r="AV266">
+        <v>7</v>
+      </c>
+      <c r="AW266">
+        <v>5</v>
+      </c>
+      <c r="AX266">
+        <v>9</v>
+      </c>
+      <c r="AY266">
+        <v>9</v>
+      </c>
+      <c r="AZ266">
+        <v>16</v>
+      </c>
+      <c r="BA266">
+        <v>1</v>
+      </c>
+      <c r="BB266">
+        <v>3</v>
+      </c>
+      <c r="BC266">
+        <v>4</v>
+      </c>
+      <c r="BD266">
+        <v>2.7</v>
+      </c>
+      <c r="BE266">
+        <v>7.4</v>
+      </c>
+      <c r="BF266">
         <v>1.6</v>
       </c>
-      <c r="AH266">
-        <v>2.3</v>
-      </c>
-      <c r="AI266">
-        <v>1.53</v>
-      </c>
-      <c r="AJ266">
-        <v>2.38</v>
-      </c>
-      <c r="AK266">
-        <v>1.83</v>
-      </c>
-      <c r="AL266">
-        <v>1.22</v>
-      </c>
-      <c r="AM266">
-        <v>1.33</v>
-      </c>
-      <c r="AN266">
-        <v>1.62</v>
-      </c>
-      <c r="AO266">
-        <v>1.83</v>
-      </c>
-      <c r="AP266">
-        <v>1.56</v>
-      </c>
-      <c r="AQ266">
-        <v>1.87</v>
-      </c>
-      <c r="AR266">
+      <c r="BG266">
+        <v>1.2</v>
+      </c>
+      <c r="BH266">
+        <v>4</v>
+      </c>
+      <c r="BI266">
+        <v>1.27</v>
+      </c>
+      <c r="BJ266">
+        <v>3.35</v>
+      </c>
+      <c r="BK266">
         <v>1.52</v>
       </c>
-      <c r="AS266">
-        <v>1.63</v>
-      </c>
-      <c r="AT266">
-        <v>3.15</v>
-      </c>
-      <c r="AU266">
-        <v>3</v>
-      </c>
-      <c r="AV266">
-        <v>5</v>
-      </c>
-      <c r="AW266">
-        <v>9</v>
-      </c>
-      <c r="AX266">
-        <v>6</v>
-      </c>
-      <c r="AY266">
-        <v>12</v>
-      </c>
-      <c r="AZ266">
-        <v>11</v>
-      </c>
-      <c r="BA266">
-        <v>3</v>
-      </c>
-      <c r="BB266">
-        <v>8</v>
-      </c>
-      <c r="BC266">
-        <v>11</v>
-      </c>
-      <c r="BD266">
-        <v>2.55</v>
-      </c>
-      <c r="BE266">
-        <v>6.5</v>
-      </c>
-      <c r="BF266">
-        <v>1.64</v>
-      </c>
-      <c r="BG266">
-        <v>1.32</v>
-      </c>
-      <c r="BH266">
-        <v>3.05</v>
-      </c>
-      <c r="BI266">
-        <v>1.54</v>
-      </c>
-      <c r="BJ266">
-        <v>2.3</v>
-      </c>
-      <c r="BK266">
-        <v>1.86</v>
-      </c>
       <c r="BL266">
-        <v>1.82</v>
+        <v>2.32</v>
       </c>
       <c r="BM266">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="BN266">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="BO266">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="BP266">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="267" spans="1:68">
@@ -56484,7 +56484,7 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>7465690</v>
+        <v>7465691</v>
       </c>
       <c r="C267" t="s">
         <v>68</v>
@@ -56499,124 +56499,124 @@
         <v>27</v>
       </c>
       <c r="G267" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H267" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267">
         <v>0</v>
       </c>
       <c r="K267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267">
         <v>1</v>
       </c>
       <c r="M267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O267" t="s">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>337</v>
+        <v>416</v>
       </c>
       <c r="Q267">
         <v>4</v>
       </c>
       <c r="R267">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S267">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T267">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U267">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V267">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="W267">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="X267">
+        <v>4.33</v>
+      </c>
+      <c r="Y267">
+        <v>1.2</v>
+      </c>
+      <c r="Z267">
+        <v>3.3</v>
+      </c>
+      <c r="AA267">
         <v>5</v>
       </c>
-      <c r="Y267">
-        <v>1.17</v>
-      </c>
-      <c r="Z267">
-        <v>3.5</v>
-      </c>
-      <c r="AA267">
-        <v>4.2</v>
-      </c>
       <c r="AB267">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC267">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AD267">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE267">
+        <v>1.12</v>
+      </c>
+      <c r="AF267">
+        <v>6</v>
+      </c>
+      <c r="AG267">
+        <v>1.36</v>
+      </c>
+      <c r="AH267">
+        <v>3.1</v>
+      </c>
+      <c r="AI267">
+        <v>1.4</v>
+      </c>
+      <c r="AJ267">
+        <v>2.75</v>
+      </c>
+      <c r="AK267">
+        <v>2.05</v>
+      </c>
+      <c r="AL267">
         <v>1.16</v>
       </c>
-      <c r="AF267">
-        <v>5</v>
-      </c>
-      <c r="AG267">
-        <v>1.5</v>
-      </c>
-      <c r="AH267">
-        <v>2.5</v>
-      </c>
-      <c r="AI267">
-        <v>1.5</v>
-      </c>
-      <c r="AJ267">
-        <v>2.5</v>
-      </c>
-      <c r="AK267">
-        <v>1.8</v>
-      </c>
-      <c r="AL267">
-        <v>1.2</v>
-      </c>
       <c r="AM267">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AN267">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO267">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AP267">
-        <v>1.27</v>
+        <v>0.6</v>
       </c>
       <c r="AQ267">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AR267">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AS267">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="AT267">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
       <c r="AU267">
         <v>4</v>
@@ -56625,28 +56625,28 @@
         <v>7</v>
       </c>
       <c r="AW267">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX267">
+        <v>12</v>
+      </c>
+      <c r="AY267">
+        <v>13</v>
+      </c>
+      <c r="AZ267">
+        <v>19</v>
+      </c>
+      <c r="BA267">
+        <v>6</v>
+      </c>
+      <c r="BB267">
         <v>9</v>
       </c>
-      <c r="AY267">
-        <v>9</v>
-      </c>
-      <c r="AZ267">
-        <v>16</v>
-      </c>
-      <c r="BA267">
-        <v>1</v>
-      </c>
-      <c r="BB267">
-        <v>3</v>
-      </c>
       <c r="BC267">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BD267">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BE267">
         <v>7.4</v>
@@ -56655,16 +56655,16 @@
         <v>1.6</v>
       </c>
       <c r="BG267">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BH267">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BI267">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BJ267">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BK267">
         <v>1.52</v>
@@ -56673,16 +56673,16 @@
         <v>2.32</v>
       </c>
       <c r="BM267">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BN267">
         <v>1.78</v>
       </c>
       <c r="BO267">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BP267">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="268" spans="1:68">
@@ -56690,7 +56690,7 @@
         <v>267</v>
       </c>
       <c r="B268">
-        <v>7465691</v>
+        <v>7465616</v>
       </c>
       <c r="C268" t="s">
         <v>68</v>
@@ -56702,22 +56702,22 @@
         <v>45712.66666666666</v>
       </c>
       <c r="F268">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G268" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H268" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="I268">
         <v>1</v>
       </c>
       <c r="J268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L268">
         <v>1</v>
@@ -56729,166 +56729,166 @@
         <v>3</v>
       </c>
       <c r="O268" t="s">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="P268" t="s">
         <v>417</v>
       </c>
       <c r="Q268">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R268">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S268">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T268">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U268">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V268">
+        <v>2.38</v>
+      </c>
+      <c r="W268">
+        <v>1.53</v>
+      </c>
+      <c r="X268">
+        <v>6</v>
+      </c>
+      <c r="Y268">
+        <v>1.13</v>
+      </c>
+      <c r="Z268">
+        <v>3.25</v>
+      </c>
+      <c r="AA268">
+        <v>3.8</v>
+      </c>
+      <c r="AB268">
         <v>2</v>
       </c>
-      <c r="W268">
-        <v>1.73</v>
-      </c>
-      <c r="X268">
-        <v>4.33</v>
-      </c>
-      <c r="Y268">
-        <v>1.2</v>
-      </c>
-      <c r="Z268">
-        <v>3.3</v>
-      </c>
-      <c r="AA268">
-        <v>5</v>
-      </c>
-      <c r="AB268">
-        <v>1.75</v>
-      </c>
       <c r="AC268">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AD268">
         <v>17</v>
       </c>
       <c r="AE268">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF268">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AG268">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AH268">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AI268">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ268">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK268">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AL268">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AM268">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AN268">
-        <v>0.67</v>
+        <v>1.62</v>
       </c>
       <c r="AO268">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AP268">
-        <v>0.6</v>
+        <v>1.56</v>
       </c>
       <c r="AQ268">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AR268">
         <v>1.52</v>
       </c>
       <c r="AS268">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AT268">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="AU268">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV268">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW268">
         <v>9</v>
       </c>
       <c r="AX268">
+        <v>6</v>
+      </c>
+      <c r="AY268">
         <v>12</v>
       </c>
-      <c r="AY268">
-        <v>13</v>
-      </c>
       <c r="AZ268">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA268">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC268">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BD268">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="BE268">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF268">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BG268">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="BH268">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BI268">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="BJ268">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="BK268">
+        <v>1.86</v>
+      </c>
+      <c r="BL268">
+        <v>1.82</v>
+      </c>
+      <c r="BM268">
+        <v>2.33</v>
+      </c>
+      <c r="BN268">
         <v>1.52</v>
       </c>
-      <c r="BL268">
-        <v>2.32</v>
-      </c>
-      <c r="BM268">
-        <v>1.92</v>
-      </c>
-      <c r="BN268">
-        <v>1.78</v>
-      </c>
       <c r="BO268">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="BP268">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="269" spans="1:68">
@@ -59162,7 +59162,7 @@
         <v>279</v>
       </c>
       <c r="B280">
-        <v>7465711</v>
+        <v>7465710</v>
       </c>
       <c r="C280" t="s">
         <v>68</v>
@@ -59177,190 +59177,190 @@
         <v>29</v>
       </c>
       <c r="G280" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H280" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I280">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L280">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N280">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O280" t="s">
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>93</v>
+        <v>424</v>
       </c>
       <c r="Q280">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="R280">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="S280">
-        <v>3.95</v>
+        <v>5.75</v>
       </c>
       <c r="T280">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="U280">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="V280">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="W280">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="X280">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="Y280">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z280">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AA280">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="AB280">
-        <v>3.54</v>
+        <v>7.5</v>
       </c>
       <c r="AC280">
         <v>1.01</v>
       </c>
       <c r="AD280">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AE280">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF280">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="AG280">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AH280">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AI280">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ280">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK280">
+        <v>1.07</v>
+      </c>
+      <c r="AL280">
+        <v>1.11</v>
+      </c>
+      <c r="AM280">
+        <v>3.2</v>
+      </c>
+      <c r="AN280">
+        <v>1.69</v>
+      </c>
+      <c r="AO280">
+        <v>1</v>
+      </c>
+      <c r="AP280">
+        <v>1.87</v>
+      </c>
+      <c r="AQ280">
+        <v>0.93</v>
+      </c>
+      <c r="AR280">
+        <v>1.96</v>
+      </c>
+      <c r="AS280">
         <v>1.29</v>
       </c>
-      <c r="AL280">
-        <v>1.25</v>
-      </c>
-      <c r="AM280">
-        <v>1.83</v>
-      </c>
-      <c r="AN280">
-        <v>1.77</v>
-      </c>
-      <c r="AO280">
-        <v>1.79</v>
-      </c>
-      <c r="AP280">
-        <v>1.93</v>
-      </c>
-      <c r="AQ280">
-        <v>1.56</v>
-      </c>
-      <c r="AR280">
-        <v>1.78</v>
-      </c>
-      <c r="AS280">
-        <v>1.32</v>
-      </c>
       <c r="AT280">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AU280">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW280">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AX280">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AY280">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AZ280">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BA280">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BB280">
         <v>4</v>
       </c>
       <c r="BC280">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD280">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="BE280">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF280">
-        <v>2.43</v>
+        <v>4.1</v>
       </c>
       <c r="BG280">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BH280">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI280">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BJ280">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BK280">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BL280">
         <v>1.98</v>
       </c>
       <c r="BM280">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BN280">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BO280">
         <v>2.65</v>
       </c>
       <c r="BP280">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="281" spans="1:68">
@@ -59410,7 +59410,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59574,7 +59574,7 @@
         <v>281</v>
       </c>
       <c r="B282">
-        <v>7465710</v>
+        <v>7465711</v>
       </c>
       <c r="C282" t="s">
         <v>68</v>
@@ -59589,190 +59589,190 @@
         <v>29</v>
       </c>
       <c r="G282" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H282" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I282">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K282">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L282">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N282">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O282" t="s">
         <v>280</v>
       </c>
       <c r="P282" t="s">
-        <v>425</v>
+        <v>93</v>
       </c>
       <c r="Q282">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="R282">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S282">
-        <v>5.75</v>
+        <v>3.95</v>
       </c>
       <c r="T282">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="U282">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V282">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="W282">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="X282">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="Y282">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z282">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AA282">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="AB282">
-        <v>7.5</v>
+        <v>3.54</v>
       </c>
       <c r="AC282">
         <v>1.01</v>
       </c>
       <c r="AD282">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE282">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF282">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="AG282">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AH282">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AI282">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ282">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK282">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AL282">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AM282">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AN282">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AO282">
-        <v>1</v>
+        <v>1.79</v>
       </c>
       <c r="AP282">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AQ282">
-        <v>0.93</v>
+        <v>1.56</v>
       </c>
       <c r="AR282">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AS282">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AT282">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AU282">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV282">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW282">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AX282">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AY282">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AZ282">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA282">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BB282">
         <v>4</v>
       </c>
       <c r="BC282">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BD282">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="BE282">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF282">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="BG282">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BH282">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI282">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BJ282">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BK282">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="BL282">
         <v>1.98</v>
       </c>
       <c r="BM282">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BN282">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO282">
         <v>2.65</v>
       </c>
       <c r="BP282">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="283" spans="1:68">
@@ -59780,7 +59780,7 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>7465714</v>
+        <v>7465709</v>
       </c>
       <c r="C283" t="s">
         <v>68</v>
@@ -59795,190 +59795,190 @@
         <v>29</v>
       </c>
       <c r="G283" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H283" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L283">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N283">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O283" t="s">
         <v>281</v>
       </c>
       <c r="P283" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="Q283">
-        <v>2.66</v>
+        <v>2.03</v>
       </c>
       <c r="R283">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="S283">
-        <v>3.68</v>
+        <v>5.27</v>
       </c>
       <c r="T283">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="U283">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V283">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="W283">
+        <v>1.61</v>
+      </c>
+      <c r="X283">
+        <v>5.5</v>
+      </c>
+      <c r="Y283">
+        <v>1.14</v>
+      </c>
+      <c r="Z283">
+        <v>1.56</v>
+      </c>
+      <c r="AA283">
+        <v>4.37</v>
+      </c>
+      <c r="AB283">
+        <v>5.13</v>
+      </c>
+      <c r="AC283">
+        <v>1.01</v>
+      </c>
+      <c r="AD283">
+        <v>15</v>
+      </c>
+      <c r="AE283">
+        <v>1.18</v>
+      </c>
+      <c r="AF283">
+        <v>4.75</v>
+      </c>
+      <c r="AG283">
         <v>1.53</v>
       </c>
-      <c r="X283">
+      <c r="AH283">
+        <v>2.4</v>
+      </c>
+      <c r="AI283">
+        <v>1.62</v>
+      </c>
+      <c r="AJ283">
+        <v>2.2</v>
+      </c>
+      <c r="AK283">
+        <v>1.2</v>
+      </c>
+      <c r="AL283">
+        <v>1.21</v>
+      </c>
+      <c r="AM283">
+        <v>2.2</v>
+      </c>
+      <c r="AN283">
+        <v>1.15</v>
+      </c>
+      <c r="AO283">
+        <v>0.62</v>
+      </c>
+      <c r="AP283">
+        <v>1.29</v>
+      </c>
+      <c r="AQ283">
+        <v>0.53</v>
+      </c>
+      <c r="AR283">
+        <v>1.73</v>
+      </c>
+      <c r="AS283">
+        <v>1.21</v>
+      </c>
+      <c r="AT283">
+        <v>2.94</v>
+      </c>
+      <c r="AU283">
+        <v>8</v>
+      </c>
+      <c r="AV283">
         <v>6</v>
       </c>
-      <c r="Y283">
-        <v>1.13</v>
-      </c>
-      <c r="Z283">
-        <v>2.16</v>
-      </c>
-      <c r="AA283">
-        <v>3.56</v>
-      </c>
-      <c r="AB283">
-        <v>3.2</v>
-      </c>
-      <c r="AC283">
-        <v>1.04</v>
-      </c>
-      <c r="AD283">
+      <c r="AW283">
+        <v>9</v>
+      </c>
+      <c r="AX283">
+        <v>7</v>
+      </c>
+      <c r="AY283">
+        <v>17</v>
+      </c>
+      <c r="AZ283">
+        <v>13</v>
+      </c>
+      <c r="BA283">
         <v>10</v>
       </c>
-      <c r="AE283">
-        <v>1.22</v>
-      </c>
-      <c r="AF283">
-        <v>4.2</v>
-      </c>
-      <c r="AG283">
-        <v>1.6</v>
-      </c>
-      <c r="AH283">
-        <v>2.2</v>
-      </c>
-      <c r="AI283">
-        <v>1.53</v>
-      </c>
-      <c r="AJ283">
-        <v>2.38</v>
-      </c>
-      <c r="AK283">
-        <v>1.33</v>
-      </c>
-      <c r="AL283">
-        <v>1.27</v>
-      </c>
-      <c r="AM283">
-        <v>1.72</v>
-      </c>
-      <c r="AN283">
-        <v>0.71</v>
-      </c>
-      <c r="AO283">
-        <v>0.86</v>
-      </c>
-      <c r="AP283">
-        <v>0.87</v>
-      </c>
-      <c r="AQ283">
-        <v>0.75</v>
-      </c>
-      <c r="AR283">
-        <v>1.6</v>
-      </c>
-      <c r="AS283">
-        <v>1.54</v>
-      </c>
-      <c r="AT283">
-        <v>3.14</v>
-      </c>
-      <c r="AU283">
-        <v>5</v>
-      </c>
-      <c r="AV283">
-        <v>5</v>
-      </c>
-      <c r="AW283">
-        <v>4</v>
-      </c>
-      <c r="AX283">
-        <v>2</v>
-      </c>
-      <c r="AY283">
-        <v>11</v>
-      </c>
-      <c r="AZ283">
-        <v>7</v>
-      </c>
-      <c r="BA283">
-        <v>5</v>
-      </c>
       <c r="BB283">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC283">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BD283">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="BE283">
         <v>6.75</v>
       </c>
       <c r="BF283">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="BG283">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BH283">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BI283">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BJ283">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BK283">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BL283">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="BM283">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="BN283">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="BO283">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="BP283">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="284" spans="1:68">
@@ -59986,7 +59986,7 @@
         <v>283</v>
       </c>
       <c r="B284">
-        <v>7465707</v>
+        <v>7465714</v>
       </c>
       <c r="C284" t="s">
         <v>68</v>
@@ -60001,28 +60001,28 @@
         <v>29</v>
       </c>
       <c r="G284" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H284" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I284">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J284">
         <v>0</v>
       </c>
       <c r="K284">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L284">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M284">
         <v>0</v>
       </c>
       <c r="N284">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O284" t="s">
         <v>282</v>
@@ -60031,37 +60031,37 @@
         <v>93</v>
       </c>
       <c r="Q284">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="R284">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="S284">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="T284">
         <v>1.3</v>
       </c>
       <c r="U284">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V284">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W284">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X284">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y284">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z284">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AA284">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="AB284">
         <v>3.2</v>
@@ -60079,7 +60079,7 @@
         <v>4.2</v>
       </c>
       <c r="AG284">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH284">
         <v>2.2</v>
@@ -60088,103 +60088,103 @@
         <v>1.53</v>
       </c>
       <c r="AJ284">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK284">
         <v>1.33</v>
       </c>
       <c r="AL284">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AM284">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AN284">
-        <v>1.5</v>
+        <v>0.71</v>
       </c>
       <c r="AO284">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="AP284">
-        <v>1.56</v>
+        <v>0.87</v>
       </c>
       <c r="AQ284">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="AR284">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AS284">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AT284">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="AU284">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AV284">
+        <v>5</v>
+      </c>
+      <c r="AW284">
         <v>4</v>
       </c>
-      <c r="AW284">
-        <v>12</v>
-      </c>
       <c r="AX284">
+        <v>2</v>
+      </c>
+      <c r="AY284">
         <v>11</v>
       </c>
-      <c r="AY284">
-        <v>25</v>
-      </c>
       <c r="AZ284">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BA284">
         <v>5</v>
       </c>
       <c r="BB284">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC284">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD284">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BE284">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF284">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BG284">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BH284">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="BI284">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="BJ284">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="BK284">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="BL284">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="BM284">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="BN284">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="BO284">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="BP284">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="285" spans="1:68">
@@ -61016,7 +61016,7 @@
         <v>288</v>
       </c>
       <c r="B289">
-        <v>7465709</v>
+        <v>7465707</v>
       </c>
       <c r="C289" t="s">
         <v>68</v>
@@ -61031,190 +61031,190 @@
         <v>29</v>
       </c>
       <c r="G289" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H289" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I289">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L289">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N289">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O289" t="s">
         <v>285</v>
       </c>
       <c r="P289" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="Q289">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="R289">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S289">
-        <v>5.27</v>
+        <v>3.65</v>
       </c>
       <c r="T289">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U289">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V289">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="W289">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X289">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y289">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z289">
+        <v>2.1</v>
+      </c>
+      <c r="AA289">
+        <v>3.55</v>
+      </c>
+      <c r="AB289">
+        <v>3.2</v>
+      </c>
+      <c r="AC289">
+        <v>1.04</v>
+      </c>
+      <c r="AD289">
+        <v>10</v>
+      </c>
+      <c r="AE289">
+        <v>1.22</v>
+      </c>
+      <c r="AF289">
+        <v>4.2</v>
+      </c>
+      <c r="AG289">
+        <v>1.65</v>
+      </c>
+      <c r="AH289">
+        <v>2.2</v>
+      </c>
+      <c r="AI289">
+        <v>1.53</v>
+      </c>
+      <c r="AJ289">
+        <v>2.3</v>
+      </c>
+      <c r="AK289">
+        <v>1.33</v>
+      </c>
+      <c r="AL289">
+        <v>1.22</v>
+      </c>
+      <c r="AM289">
+        <v>1.7</v>
+      </c>
+      <c r="AN289">
+        <v>1.5</v>
+      </c>
+      <c r="AO289">
+        <v>0.57</v>
+      </c>
+      <c r="AP289">
         <v>1.56</v>
-      </c>
-      <c r="AA289">
-        <v>4.37</v>
-      </c>
-      <c r="AB289">
-        <v>5.13</v>
-      </c>
-      <c r="AC289">
-        <v>1.01</v>
-      </c>
-      <c r="AD289">
-        <v>15</v>
-      </c>
-      <c r="AE289">
-        <v>1.18</v>
-      </c>
-      <c r="AF289">
-        <v>4.75</v>
-      </c>
-      <c r="AG289">
-        <v>1.53</v>
-      </c>
-      <c r="AH289">
-        <v>2.4</v>
-      </c>
-      <c r="AI289">
-        <v>1.62</v>
-      </c>
-      <c r="AJ289">
-        <v>2.2</v>
-      </c>
-      <c r="AK289">
-        <v>1.2</v>
-      </c>
-      <c r="AL289">
-        <v>1.21</v>
-      </c>
-      <c r="AM289">
-        <v>2.2</v>
-      </c>
-      <c r="AN289">
-        <v>1.15</v>
-      </c>
-      <c r="AO289">
-        <v>0.62</v>
-      </c>
-      <c r="AP289">
-        <v>1.29</v>
       </c>
       <c r="AQ289">
         <v>0.53</v>
       </c>
       <c r="AR289">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AS289">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT289">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="AU289">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AV289">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW289">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX289">
+        <v>11</v>
+      </c>
+      <c r="AY289">
+        <v>25</v>
+      </c>
+      <c r="AZ289">
+        <v>15</v>
+      </c>
+      <c r="BA289">
+        <v>5</v>
+      </c>
+      <c r="BB289">
+        <v>2</v>
+      </c>
+      <c r="BC289">
         <v>7</v>
       </c>
-      <c r="AY289">
-        <v>17</v>
-      </c>
-      <c r="AZ289">
-        <v>13</v>
-      </c>
-      <c r="BA289">
-        <v>10</v>
-      </c>
-      <c r="BB289">
-        <v>9</v>
-      </c>
-      <c r="BC289">
-        <v>19</v>
-      </c>
       <c r="BD289">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="BE289">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF289">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="BG289">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BH289">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="BI289">
+        <v>1.56</v>
+      </c>
+      <c r="BJ289">
+        <v>2.23</v>
+      </c>
+      <c r="BK289">
+        <v>1.92</v>
+      </c>
+      <c r="BL289">
+        <v>1.77</v>
+      </c>
+      <c r="BM289">
+        <v>2.4</v>
+      </c>
+      <c r="BN289">
         <v>1.49</v>
       </c>
-      <c r="BJ289">
-        <v>2.4</v>
-      </c>
-      <c r="BK289">
-        <v>1.81</v>
-      </c>
-      <c r="BL289">
-        <v>1.88</v>
-      </c>
-      <c r="BM289">
-        <v>2.3</v>
-      </c>
-      <c r="BN289">
-        <v>1.54</v>
-      </c>
       <c r="BO289">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="BP289">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="290" spans="1:68">
@@ -61222,7 +61222,7 @@
         <v>289</v>
       </c>
       <c r="B290">
-        <v>7465723</v>
+        <v>7465726</v>
       </c>
       <c r="C290" t="s">
         <v>68</v>
@@ -61237,10 +61237,10 @@
         <v>31</v>
       </c>
       <c r="G290" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H290" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I290">
         <v>1</v>
@@ -61252,28 +61252,28 @@
         <v>1</v>
       </c>
       <c r="L290">
+        <v>1</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>1</v>
+      </c>
+      <c r="O290" t="s">
+        <v>168</v>
+      </c>
+      <c r="P290" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q290">
         <v>2</v>
       </c>
-      <c r="M290">
-        <v>2</v>
-      </c>
-      <c r="N290">
-        <v>4</v>
-      </c>
-      <c r="O290" t="s">
-        <v>286</v>
-      </c>
-      <c r="P290" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q290">
-        <v>2.5</v>
-      </c>
       <c r="R290">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S290">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="T290">
         <v>1.25</v>
@@ -61282,145 +61282,145 @@
         <v>3.75</v>
       </c>
       <c r="V290">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="W290">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X290">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y290">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z290">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="AA290">
-        <v>3.93</v>
+        <v>4.49</v>
       </c>
       <c r="AB290">
-        <v>3.34</v>
+        <v>4.84</v>
       </c>
       <c r="AC290">
         <v>1.01</v>
       </c>
       <c r="AD290">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE290">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF290">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AG290">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH290">
+        <v>2.7</v>
+      </c>
+      <c r="AI290">
+        <v>1.57</v>
+      </c>
+      <c r="AJ290">
+        <v>2.25</v>
+      </c>
+      <c r="AK290">
+        <v>1.14</v>
+      </c>
+      <c r="AL290">
+        <v>1.19</v>
+      </c>
+      <c r="AM290">
         <v>2.5</v>
       </c>
-      <c r="AI290">
-        <v>1.44</v>
-      </c>
-      <c r="AJ290">
-        <v>2.63</v>
-      </c>
-      <c r="AK290">
-        <v>1.31</v>
-      </c>
-      <c r="AL290">
+      <c r="AN290">
+        <v>1.43</v>
+      </c>
+      <c r="AO290">
+        <v>1.67</v>
+      </c>
+      <c r="AP290">
+        <v>1.53</v>
+      </c>
+      <c r="AQ290">
+        <v>1.56</v>
+      </c>
+      <c r="AR290">
+        <v>1.8</v>
+      </c>
+      <c r="AS290">
+        <v>1.32</v>
+      </c>
+      <c r="AT290">
+        <v>3.12</v>
+      </c>
+      <c r="AU290">
+        <v>5</v>
+      </c>
+      <c r="AV290">
+        <v>2</v>
+      </c>
+      <c r="AW290">
+        <v>14</v>
+      </c>
+      <c r="AX290">
+        <v>4</v>
+      </c>
+      <c r="AY290">
+        <v>19</v>
+      </c>
+      <c r="AZ290">
+        <v>6</v>
+      </c>
+      <c r="BA290">
+        <v>5</v>
+      </c>
+      <c r="BB290">
+        <v>2</v>
+      </c>
+      <c r="BC290">
+        <v>7</v>
+      </c>
+      <c r="BD290">
+        <v>1.36</v>
+      </c>
+      <c r="BE290">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF290">
+        <v>3.72</v>
+      </c>
+      <c r="BG290">
+        <v>1.24</v>
+      </c>
+      <c r="BH290">
+        <v>3.55</v>
+      </c>
+      <c r="BI290">
         <v>1.26</v>
       </c>
-      <c r="AM290">
-        <v>1.77</v>
-      </c>
-      <c r="AN290">
-        <v>0.57</v>
-      </c>
-      <c r="AO290">
-        <v>0.5</v>
-      </c>
-      <c r="AP290">
-        <v>0.6</v>
-      </c>
-      <c r="AQ290">
-        <v>0.53</v>
-      </c>
-      <c r="AR290">
-        <v>1.6</v>
-      </c>
-      <c r="AS290">
-        <v>1.06</v>
-      </c>
-      <c r="AT290">
-        <v>2.66</v>
-      </c>
-      <c r="AU290">
-        <v>10</v>
-      </c>
-      <c r="AV290">
-        <v>8</v>
-      </c>
-      <c r="AW290">
-        <v>7</v>
-      </c>
-      <c r="AX290">
-        <v>5</v>
-      </c>
-      <c r="AY290">
-        <v>17</v>
-      </c>
-      <c r="AZ290">
-        <v>13</v>
-      </c>
-      <c r="BA290">
-        <v>3</v>
-      </c>
-      <c r="BB290">
-        <v>6</v>
-      </c>
-      <c r="BC290">
-        <v>9</v>
-      </c>
-      <c r="BD290">
-        <v>1.78</v>
-      </c>
-      <c r="BE290">
-        <v>8.6</v>
-      </c>
-      <c r="BF290">
-        <v>2.34</v>
-      </c>
-      <c r="BG290">
-        <v>1.27</v>
-      </c>
-      <c r="BH290">
-        <v>3.3</v>
-      </c>
-      <c r="BI290">
-        <v>1.31</v>
-      </c>
       <c r="BJ290">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="BK290">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="BL290">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="BM290">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="BN290">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="BO290">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="BP290">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="291" spans="1:68">
@@ -61428,7 +61428,7 @@
         <v>290</v>
       </c>
       <c r="B291">
-        <v>7465722</v>
+        <v>7465723</v>
       </c>
       <c r="C291" t="s">
         <v>68</v>
@@ -61443,190 +61443,190 @@
         <v>31</v>
       </c>
       <c r="G291" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H291" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>1</v>
+      </c>
+      <c r="L291">
         <v>2</v>
-      </c>
-      <c r="K291">
-        <v>2</v>
-      </c>
-      <c r="L291">
-        <v>0</v>
       </c>
       <c r="M291">
         <v>2</v>
       </c>
       <c r="N291">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O291" t="s">
-        <v>93</v>
+        <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q291">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="R291">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S291">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="T291">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="U291">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="V291">
+        <v>2.2</v>
+      </c>
+      <c r="W291">
+        <v>1.62</v>
+      </c>
+      <c r="X291">
+        <v>5</v>
+      </c>
+      <c r="Y291">
+        <v>1.17</v>
+      </c>
+      <c r="Z291">
+        <v>1.99</v>
+      </c>
+      <c r="AA291">
+        <v>3.93</v>
+      </c>
+      <c r="AB291">
+        <v>3.34</v>
+      </c>
+      <c r="AC291">
+        <v>1.01</v>
+      </c>
+      <c r="AD291">
+        <v>15</v>
+      </c>
+      <c r="AE291">
+        <v>1.18</v>
+      </c>
+      <c r="AF291">
+        <v>4.75</v>
+      </c>
+      <c r="AG291">
+        <v>1.5</v>
+      </c>
+      <c r="AH291">
         <v>2.5</v>
       </c>
-      <c r="W291">
-        <v>1.5</v>
-      </c>
-      <c r="X291">
+      <c r="AI291">
+        <v>1.44</v>
+      </c>
+      <c r="AJ291">
+        <v>2.63</v>
+      </c>
+      <c r="AK291">
+        <v>1.31</v>
+      </c>
+      <c r="AL291">
+        <v>1.26</v>
+      </c>
+      <c r="AM291">
+        <v>1.77</v>
+      </c>
+      <c r="AN291">
+        <v>0.57</v>
+      </c>
+      <c r="AO291">
+        <v>0.5</v>
+      </c>
+      <c r="AP291">
+        <v>0.6</v>
+      </c>
+      <c r="AQ291">
+        <v>0.53</v>
+      </c>
+      <c r="AR291">
+        <v>1.6</v>
+      </c>
+      <c r="AS291">
+        <v>1.06</v>
+      </c>
+      <c r="AT291">
+        <v>2.66</v>
+      </c>
+      <c r="AU291">
+        <v>10</v>
+      </c>
+      <c r="AV291">
+        <v>8</v>
+      </c>
+      <c r="AW291">
+        <v>7</v>
+      </c>
+      <c r="AX291">
+        <v>5</v>
+      </c>
+      <c r="AY291">
+        <v>17</v>
+      </c>
+      <c r="AZ291">
+        <v>13</v>
+      </c>
+      <c r="BA291">
+        <v>3</v>
+      </c>
+      <c r="BB291">
         <v>6</v>
       </c>
-      <c r="Y291">
-        <v>1.13</v>
-      </c>
-      <c r="Z291">
-        <v>2.83</v>
-      </c>
-      <c r="AA291">
-        <v>3.71</v>
-      </c>
-      <c r="AB291">
-        <v>2.32</v>
-      </c>
-      <c r="AC291">
-        <v>1.04</v>
-      </c>
-      <c r="AD291">
-        <v>10</v>
-      </c>
-      <c r="AE291">
-        <v>1.2</v>
-      </c>
-      <c r="AF291">
-        <v>4.33</v>
-      </c>
-      <c r="AG291">
-        <v>1.65</v>
-      </c>
-      <c r="AH291">
-        <v>2.2</v>
-      </c>
-      <c r="AI291">
+      <c r="BC291">
+        <v>9</v>
+      </c>
+      <c r="BD291">
+        <v>1.78</v>
+      </c>
+      <c r="BE291">
+        <v>8.6</v>
+      </c>
+      <c r="BF291">
+        <v>2.34</v>
+      </c>
+      <c r="BG291">
+        <v>1.27</v>
+      </c>
+      <c r="BH291">
+        <v>3.3</v>
+      </c>
+      <c r="BI291">
+        <v>1.31</v>
+      </c>
+      <c r="BJ291">
+        <v>2.92</v>
+      </c>
+      <c r="BK291">
         <v>1.57</v>
       </c>
-      <c r="AJ291">
-        <v>2.25</v>
-      </c>
-      <c r="AK291">
-        <v>1.57</v>
-      </c>
-      <c r="AL291">
-        <v>1.27</v>
-      </c>
-      <c r="AM291">
-        <v>1.42</v>
-      </c>
-      <c r="AN291">
-        <v>0.71</v>
-      </c>
-      <c r="AO291">
-        <v>0.93</v>
-      </c>
-      <c r="AP291">
-        <v>0.67</v>
-      </c>
-      <c r="AQ291">
-        <v>1.07</v>
-      </c>
-      <c r="AR291">
-        <v>1.47</v>
-      </c>
-      <c r="AS291">
-        <v>1.5</v>
-      </c>
-      <c r="AT291">
-        <v>2.97</v>
-      </c>
-      <c r="AU291">
-        <v>4</v>
-      </c>
-      <c r="AV291">
-        <v>7</v>
-      </c>
-      <c r="AW291">
-        <v>2</v>
-      </c>
-      <c r="AX291">
-        <v>9</v>
-      </c>
-      <c r="AY291">
-        <v>6</v>
-      </c>
-      <c r="AZ291">
-        <v>19</v>
-      </c>
-      <c r="BA291">
-        <v>2</v>
-      </c>
-      <c r="BB291">
-        <v>9</v>
-      </c>
-      <c r="BC291">
-        <v>11</v>
-      </c>
-      <c r="BD291">
-        <v>2.57</v>
-      </c>
-      <c r="BE291">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF291">
-        <v>1.66</v>
-      </c>
-      <c r="BG291">
-        <v>1.24</v>
-      </c>
-      <c r="BH291">
-        <v>3.55</v>
-      </c>
-      <c r="BI291">
-        <v>1.29</v>
-      </c>
-      <c r="BJ291">
-        <v>3.04</v>
-      </c>
-      <c r="BK291">
-        <v>1.55</v>
-      </c>
       <c r="BL291">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="BM291">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BN291">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BO291">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BP291">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="292" spans="1:68">
@@ -61634,7 +61634,7 @@
         <v>291</v>
       </c>
       <c r="B292">
-        <v>7465726</v>
+        <v>7465719</v>
       </c>
       <c r="C292" t="s">
         <v>68</v>
@@ -61649,190 +61649,190 @@
         <v>31</v>
       </c>
       <c r="G292" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H292" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I292">
         <v>1</v>
       </c>
       <c r="J292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L292">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N292">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O292" t="s">
-        <v>168</v>
+        <v>287</v>
       </c>
       <c r="P292" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="Q292">
+        <v>2.05</v>
+      </c>
+      <c r="R292">
+        <v>2.4</v>
+      </c>
+      <c r="S292">
+        <v>5.5</v>
+      </c>
+      <c r="T292">
+        <v>1.3</v>
+      </c>
+      <c r="U292">
+        <v>3.4</v>
+      </c>
+      <c r="V292">
+        <v>2.5</v>
+      </c>
+      <c r="W292">
+        <v>1.5</v>
+      </c>
+      <c r="X292">
+        <v>6</v>
+      </c>
+      <c r="Y292">
+        <v>1.13</v>
+      </c>
+      <c r="Z292">
+        <v>1.52</v>
+      </c>
+      <c r="AA292">
+        <v>4.37</v>
+      </c>
+      <c r="AB292">
+        <v>5.72</v>
+      </c>
+      <c r="AC292">
+        <v>1.03</v>
+      </c>
+      <c r="AD292">
+        <v>11</v>
+      </c>
+      <c r="AE292">
+        <v>1.2</v>
+      </c>
+      <c r="AF292">
+        <v>4.33</v>
+      </c>
+      <c r="AG292">
+        <v>1.61</v>
+      </c>
+      <c r="AH292">
+        <v>2.15</v>
+      </c>
+      <c r="AI292">
+        <v>1.73</v>
+      </c>
+      <c r="AJ292">
         <v>2</v>
-      </c>
-      <c r="R292">
-        <v>2.63</v>
-      </c>
-      <c r="S292">
-        <v>5</v>
-      </c>
-      <c r="T292">
-        <v>1.25</v>
-      </c>
-      <c r="U292">
-        <v>3.75</v>
-      </c>
-      <c r="V292">
-        <v>2.1</v>
-      </c>
-      <c r="W292">
-        <v>1.67</v>
-      </c>
-      <c r="X292">
-        <v>4.5</v>
-      </c>
-      <c r="Y292">
-        <v>1.18</v>
-      </c>
-      <c r="Z292">
-        <v>1.58</v>
-      </c>
-      <c r="AA292">
-        <v>4.49</v>
-      </c>
-      <c r="AB292">
-        <v>4.84</v>
-      </c>
-      <c r="AC292">
-        <v>1.01</v>
-      </c>
-      <c r="AD292">
-        <v>17</v>
-      </c>
-      <c r="AE292">
-        <v>1.14</v>
-      </c>
-      <c r="AF292">
-        <v>5.5</v>
-      </c>
-      <c r="AG292">
-        <v>1.44</v>
-      </c>
-      <c r="AH292">
-        <v>2.7</v>
-      </c>
-      <c r="AI292">
-        <v>1.57</v>
-      </c>
-      <c r="AJ292">
-        <v>2.25</v>
       </c>
       <c r="AK292">
         <v>1.14</v>
       </c>
       <c r="AL292">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AM292">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AN292">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AO292">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP292">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AQ292">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AR292">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AS292">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AT292">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="AU292">
+        <v>6</v>
+      </c>
+      <c r="AV292">
         <v>5</v>
       </c>
-      <c r="AV292">
-        <v>2</v>
-      </c>
       <c r="AW292">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AX292">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY292">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ292">
+        <v>8</v>
+      </c>
+      <c r="BA292">
         <v>6</v>
-      </c>
-      <c r="BA292">
-        <v>5</v>
       </c>
       <c r="BB292">
         <v>2</v>
       </c>
       <c r="BC292">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD292">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="BE292">
-        <v>9.800000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="BF292">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="BG292">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="BH292">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BI292">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BJ292">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="BK292">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="BL292">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="BM292">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="BN292">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BO292">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="BP292">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="293" spans="1:68">
@@ -61840,7 +61840,7 @@
         <v>292</v>
       </c>
       <c r="B293">
-        <v>7465719</v>
+        <v>7465722</v>
       </c>
       <c r="C293" t="s">
         <v>68</v>
@@ -61855,49 +61855,49 @@
         <v>31</v>
       </c>
       <c r="G293" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H293" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K293">
         <v>2</v>
       </c>
       <c r="L293">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N293">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O293" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="Q293">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R293">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S293">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="T293">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U293">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V293">
         <v>2.5</v>
@@ -61912,19 +61912,19 @@
         <v>1.13</v>
       </c>
       <c r="Z293">
-        <v>1.52</v>
+        <v>2.83</v>
       </c>
       <c r="AA293">
-        <v>4.37</v>
+        <v>3.71</v>
       </c>
       <c r="AB293">
-        <v>5.72</v>
+        <v>2.32</v>
       </c>
       <c r="AC293">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD293">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE293">
         <v>1.2</v>
@@ -61933,94 +61933,94 @@
         <v>4.33</v>
       </c>
       <c r="AG293">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH293">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI293">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ293">
+        <v>2.25</v>
+      </c>
+      <c r="AK293">
+        <v>1.57</v>
+      </c>
+      <c r="AL293">
+        <v>1.27</v>
+      </c>
+      <c r="AM293">
+        <v>1.42</v>
+      </c>
+      <c r="AN293">
+        <v>0.71</v>
+      </c>
+      <c r="AO293">
+        <v>0.93</v>
+      </c>
+      <c r="AP293">
+        <v>0.67</v>
+      </c>
+      <c r="AQ293">
+        <v>1.07</v>
+      </c>
+      <c r="AR293">
+        <v>1.47</v>
+      </c>
+      <c r="AS293">
+        <v>1.5</v>
+      </c>
+      <c r="AT293">
+        <v>2.97</v>
+      </c>
+      <c r="AU293">
+        <v>4</v>
+      </c>
+      <c r="AV293">
+        <v>7</v>
+      </c>
+      <c r="AW293">
         <v>2</v>
       </c>
-      <c r="AK293">
-        <v>1.14</v>
-      </c>
-      <c r="AL293">
-        <v>1.21</v>
-      </c>
-      <c r="AM293">
-        <v>2.45</v>
-      </c>
-      <c r="AN293">
-        <v>2.14</v>
-      </c>
-      <c r="AO293">
+      <c r="AX293">
+        <v>9</v>
+      </c>
+      <c r="AY293">
+        <v>6</v>
+      </c>
+      <c r="AZ293">
+        <v>19</v>
+      </c>
+      <c r="BA293">
+        <v>2</v>
+      </c>
+      <c r="BB293">
+        <v>9</v>
+      </c>
+      <c r="BC293">
+        <v>11</v>
+      </c>
+      <c r="BD293">
+        <v>2.57</v>
+      </c>
+      <c r="BE293">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF293">
+        <v>1.66</v>
+      </c>
+      <c r="BG293">
+        <v>1.24</v>
+      </c>
+      <c r="BH293">
+        <v>3.55</v>
+      </c>
+      <c r="BI293">
         <v>1.29</v>
       </c>
-      <c r="AP293">
-        <v>2.2</v>
-      </c>
-      <c r="AQ293">
-        <v>1.2</v>
-      </c>
-      <c r="AR293">
-        <v>1.94</v>
-      </c>
-      <c r="AS293">
-        <v>1.22</v>
-      </c>
-      <c r="AT293">
-        <v>3.16</v>
-      </c>
-      <c r="AU293">
-        <v>6</v>
-      </c>
-      <c r="AV293">
-        <v>5</v>
-      </c>
-      <c r="AW293">
-        <v>10</v>
-      </c>
-      <c r="AX293">
-        <v>3</v>
-      </c>
-      <c r="AY293">
-        <v>16</v>
-      </c>
-      <c r="AZ293">
-        <v>8</v>
-      </c>
-      <c r="BA293">
-        <v>6</v>
-      </c>
-      <c r="BB293">
-        <v>2</v>
-      </c>
-      <c r="BC293">
-        <v>8</v>
-      </c>
-      <c r="BD293">
-        <v>1.26</v>
-      </c>
-      <c r="BE293">
-        <v>10.75</v>
-      </c>
-      <c r="BF293">
-        <v>4.6</v>
-      </c>
-      <c r="BG293">
-        <v>1.2</v>
-      </c>
-      <c r="BH293">
-        <v>3.95</v>
-      </c>
-      <c r="BI293">
-        <v>1.3</v>
-      </c>
       <c r="BJ293">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="BK293">
         <v>1.55</v>
@@ -62046,7 +62046,7 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>7465721</v>
+        <v>7465725</v>
       </c>
       <c r="C294" t="s">
         <v>68</v>
@@ -62061,70 +62061,70 @@
         <v>31</v>
       </c>
       <c r="G294" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H294" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K294">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L294">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M294">
         <v>2</v>
       </c>
       <c r="N294">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O294" t="s">
-        <v>93</v>
+        <v>288</v>
       </c>
       <c r="P294" t="s">
         <v>430</v>
       </c>
       <c r="Q294">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="R294">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S294">
+        <v>4</v>
+      </c>
+      <c r="T294">
+        <v>1.33</v>
+      </c>
+      <c r="U294">
+        <v>3.25</v>
+      </c>
+      <c r="V294">
         <v>2.63</v>
       </c>
-      <c r="T294">
-        <v>1.29</v>
-      </c>
-      <c r="U294">
-        <v>3.5</v>
-      </c>
-      <c r="V294">
-        <v>2.38</v>
-      </c>
       <c r="W294">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="X294">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y294">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z294">
-        <v>3.35</v>
+        <v>1.93</v>
       </c>
       <c r="AA294">
+        <v>3.71</v>
+      </c>
+      <c r="AB294">
         <v>3.73</v>
-      </c>
-      <c r="AB294">
-        <v>2.04</v>
       </c>
       <c r="AC294">
         <v>1.04</v>
@@ -62133,118 +62133,118 @@
         <v>10</v>
       </c>
       <c r="AE294">
+        <v>1.22</v>
+      </c>
+      <c r="AF294">
+        <v>4</v>
+      </c>
+      <c r="AG294">
+        <v>1.67</v>
+      </c>
+      <c r="AH294">
+        <v>2.1</v>
+      </c>
+      <c r="AI294">
+        <v>1.62</v>
+      </c>
+      <c r="AJ294">
+        <v>2.2</v>
+      </c>
+      <c r="AK294">
+        <v>1.28</v>
+      </c>
+      <c r="AL294">
+        <v>1.28</v>
+      </c>
+      <c r="AM294">
+        <v>1.8</v>
+      </c>
+      <c r="AN294">
+        <v>1.79</v>
+      </c>
+      <c r="AO294">
+        <v>1.29</v>
+      </c>
+      <c r="AP294">
+        <v>1.87</v>
+      </c>
+      <c r="AQ294">
         <v>1.2</v>
       </c>
-      <c r="AF294">
-        <v>4.5</v>
-      </c>
-      <c r="AG294">
-        <v>1.57</v>
-      </c>
-      <c r="AH294">
-        <v>2.35</v>
-      </c>
-      <c r="AI294">
-        <v>1.5</v>
-      </c>
-      <c r="AJ294">
-        <v>2.5</v>
-      </c>
-      <c r="AK294">
-        <v>1.66</v>
-      </c>
-      <c r="AL294">
-        <v>1.26</v>
-      </c>
-      <c r="AM294">
-        <v>1.37</v>
-      </c>
-      <c r="AN294">
-        <v>1.36</v>
-      </c>
-      <c r="AO294">
-        <v>1.79</v>
-      </c>
-      <c r="AP294">
-        <v>1.27</v>
-      </c>
-      <c r="AQ294">
-        <v>1.87</v>
-      </c>
       <c r="AR294">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="AS294">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT294">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="AU294">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV294">
+        <v>4</v>
+      </c>
+      <c r="AW294">
+        <v>6</v>
+      </c>
+      <c r="AX294">
         <v>8</v>
       </c>
-      <c r="AW294">
-        <v>4</v>
-      </c>
-      <c r="AX294">
-        <v>6</v>
-      </c>
       <c r="AY294">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ294">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA294">
         <v>4</v>
       </c>
       <c r="BB294">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BC294">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD294">
-        <v>2.11</v>
+        <v>1.46</v>
       </c>
       <c r="BE294">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF294">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="BG294">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BH294">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BI294">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BJ294">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="BK294">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BL294">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BM294">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="BN294">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="BO294">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="BP294">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="295" spans="1:68">
@@ -62252,7 +62252,7 @@
         <v>294</v>
       </c>
       <c r="B295">
-        <v>7465717</v>
+        <v>7465720</v>
       </c>
       <c r="C295" t="s">
         <v>68</v>
@@ -62267,190 +62267,190 @@
         <v>31</v>
       </c>
       <c r="G295" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H295" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I295">
         <v>0</v>
       </c>
       <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>0</v>
+      </c>
+      <c r="L295">
         <v>3</v>
       </c>
-      <c r="K295">
-        <v>3</v>
-      </c>
-      <c r="L295">
-        <v>0</v>
-      </c>
       <c r="M295">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N295">
         <v>3</v>
       </c>
       <c r="O295" t="s">
+        <v>289</v>
+      </c>
+      <c r="P295" t="s">
         <v>93</v>
       </c>
-      <c r="P295" t="s">
-        <v>431</v>
-      </c>
       <c r="Q295">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="R295">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S295">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="T295">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="U295">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="V295">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="W295">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="X295">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y295">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z295">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AA295">
-        <v>4.65</v>
+        <v>4.05</v>
       </c>
       <c r="AB295">
-        <v>5.29</v>
+        <v>4.02</v>
       </c>
       <c r="AC295">
         <v>1.01</v>
       </c>
       <c r="AD295">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE295">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF295">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AG295">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH295">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AI295">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ295">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK295">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AL295">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AM295">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AN295">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AO295">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AP295">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AQ295">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AR295">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AS295">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AT295">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AU295">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV295">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW295">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX295">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY295">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ295">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA295">
         <v>7</v>
       </c>
       <c r="BB295">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC295">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD295">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="BE295">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF295">
-        <v>4.15</v>
+        <v>2.16</v>
       </c>
       <c r="BG295">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BH295">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI295">
+        <v>1.33</v>
+      </c>
+      <c r="BJ295">
+        <v>2.81</v>
+      </c>
+      <c r="BK295">
+        <v>1.62</v>
+      </c>
+      <c r="BL295">
+        <v>2.11</v>
+      </c>
+      <c r="BM295">
+        <v>2.04</v>
+      </c>
+      <c r="BN295">
+        <v>1.69</v>
+      </c>
+      <c r="BO295">
+        <v>2.64</v>
+      </c>
+      <c r="BP295">
         <v>1.4</v>
-      </c>
-      <c r="BJ295">
-        <v>2.64</v>
-      </c>
-      <c r="BK295">
-        <v>1.72</v>
-      </c>
-      <c r="BL295">
-        <v>2</v>
-      </c>
-      <c r="BM295">
-        <v>2.15</v>
-      </c>
-      <c r="BN295">
-        <v>1.59</v>
-      </c>
-      <c r="BO295">
-        <v>2.83</v>
-      </c>
-      <c r="BP295">
-        <v>1.33</v>
       </c>
     </row>
     <row r="296" spans="1:68">
@@ -62458,7 +62458,7 @@
         <v>295</v>
       </c>
       <c r="B296">
-        <v>7465725</v>
+        <v>7465717</v>
       </c>
       <c r="C296" t="s">
         <v>68</v>
@@ -62473,190 +62473,190 @@
         <v>31</v>
       </c>
       <c r="G296" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H296" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K296">
         <v>3</v>
       </c>
       <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296">
         <v>3</v>
       </c>
-      <c r="M296">
+      <c r="N296">
+        <v>3</v>
+      </c>
+      <c r="O296" t="s">
+        <v>93</v>
+      </c>
+      <c r="P296" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q296">
         <v>2</v>
       </c>
-      <c r="N296">
+      <c r="R296">
+        <v>2.63</v>
+      </c>
+      <c r="S296">
         <v>5</v>
       </c>
-      <c r="O296" t="s">
-        <v>288</v>
-      </c>
-      <c r="P296" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q296">
-        <v>2.5</v>
-      </c>
-      <c r="R296">
-        <v>2.3</v>
-      </c>
-      <c r="S296">
+      <c r="T296">
+        <v>1.22</v>
+      </c>
+      <c r="U296">
         <v>4</v>
       </c>
-      <c r="T296">
+      <c r="V296">
+        <v>2.1</v>
+      </c>
+      <c r="W296">
+        <v>1.67</v>
+      </c>
+      <c r="X296">
+        <v>4.5</v>
+      </c>
+      <c r="Y296">
+        <v>1.18</v>
+      </c>
+      <c r="Z296">
+        <v>1.52</v>
+      </c>
+      <c r="AA296">
+        <v>4.65</v>
+      </c>
+      <c r="AB296">
+        <v>5.29</v>
+      </c>
+      <c r="AC296">
+        <v>1.01</v>
+      </c>
+      <c r="AD296">
+        <v>17</v>
+      </c>
+      <c r="AE296">
+        <v>1.12</v>
+      </c>
+      <c r="AF296">
+        <v>5.75</v>
+      </c>
+      <c r="AG296">
+        <v>1.44</v>
+      </c>
+      <c r="AH296">
+        <v>2.7</v>
+      </c>
+      <c r="AI296">
+        <v>1.53</v>
+      </c>
+      <c r="AJ296">
+        <v>2.38</v>
+      </c>
+      <c r="AK296">
+        <v>1.15</v>
+      </c>
+      <c r="AL296">
+        <v>1.19</v>
+      </c>
+      <c r="AM296">
+        <v>2.4</v>
+      </c>
+      <c r="AN296">
+        <v>2.2</v>
+      </c>
+      <c r="AO296">
+        <v>1.07</v>
+      </c>
+      <c r="AP296">
+        <v>2.06</v>
+      </c>
+      <c r="AQ296">
+        <v>1.31</v>
+      </c>
+      <c r="AR296">
+        <v>1.84</v>
+      </c>
+      <c r="AS296">
+        <v>1.3</v>
+      </c>
+      <c r="AT296">
+        <v>3.14</v>
+      </c>
+      <c r="AU296">
+        <v>4</v>
+      </c>
+      <c r="AV296">
+        <v>7</v>
+      </c>
+      <c r="AW296">
+        <v>10</v>
+      </c>
+      <c r="AX296">
+        <v>3</v>
+      </c>
+      <c r="AY296">
+        <v>20</v>
+      </c>
+      <c r="AZ296">
+        <v>10</v>
+      </c>
+      <c r="BA296">
+        <v>7</v>
+      </c>
+      <c r="BB296">
+        <v>6</v>
+      </c>
+      <c r="BC296">
+        <v>13</v>
+      </c>
+      <c r="BD296">
+        <v>1.31</v>
+      </c>
+      <c r="BE296">
+        <v>9.9</v>
+      </c>
+      <c r="BF296">
+        <v>4.15</v>
+      </c>
+      <c r="BG296">
+        <v>1.19</v>
+      </c>
+      <c r="BH296">
+        <v>3.75</v>
+      </c>
+      <c r="BI296">
+        <v>1.4</v>
+      </c>
+      <c r="BJ296">
+        <v>2.64</v>
+      </c>
+      <c r="BK296">
+        <v>1.72</v>
+      </c>
+      <c r="BL296">
+        <v>2</v>
+      </c>
+      <c r="BM296">
+        <v>2.15</v>
+      </c>
+      <c r="BN296">
+        <v>1.59</v>
+      </c>
+      <c r="BO296">
+        <v>2.83</v>
+      </c>
+      <c r="BP296">
         <v>1.33</v>
-      </c>
-      <c r="U296">
-        <v>3.25</v>
-      </c>
-      <c r="V296">
-        <v>2.63</v>
-      </c>
-      <c r="W296">
-        <v>1.44</v>
-      </c>
-      <c r="X296">
-        <v>6.5</v>
-      </c>
-      <c r="Y296">
-        <v>1.11</v>
-      </c>
-      <c r="Z296">
-        <v>1.93</v>
-      </c>
-      <c r="AA296">
-        <v>3.71</v>
-      </c>
-      <c r="AB296">
-        <v>3.73</v>
-      </c>
-      <c r="AC296">
-        <v>1.04</v>
-      </c>
-      <c r="AD296">
-        <v>10</v>
-      </c>
-      <c r="AE296">
-        <v>1.22</v>
-      </c>
-      <c r="AF296">
-        <v>4</v>
-      </c>
-      <c r="AG296">
-        <v>1.67</v>
-      </c>
-      <c r="AH296">
-        <v>2.1</v>
-      </c>
-      <c r="AI296">
-        <v>1.62</v>
-      </c>
-      <c r="AJ296">
-        <v>2.2</v>
-      </c>
-      <c r="AK296">
-        <v>1.28</v>
-      </c>
-      <c r="AL296">
-        <v>1.28</v>
-      </c>
-      <c r="AM296">
-        <v>1.8</v>
-      </c>
-      <c r="AN296">
-        <v>1.79</v>
-      </c>
-      <c r="AO296">
-        <v>1.29</v>
-      </c>
-      <c r="AP296">
-        <v>1.87</v>
-      </c>
-      <c r="AQ296">
-        <v>1.2</v>
-      </c>
-      <c r="AR296">
-        <v>1.99</v>
-      </c>
-      <c r="AS296">
-        <v>1.4</v>
-      </c>
-      <c r="AT296">
-        <v>3.39</v>
-      </c>
-      <c r="AU296">
-        <v>6</v>
-      </c>
-      <c r="AV296">
-        <v>4</v>
-      </c>
-      <c r="AW296">
-        <v>6</v>
-      </c>
-      <c r="AX296">
-        <v>8</v>
-      </c>
-      <c r="AY296">
-        <v>12</v>
-      </c>
-      <c r="AZ296">
-        <v>12</v>
-      </c>
-      <c r="BA296">
-        <v>4</v>
-      </c>
-      <c r="BB296">
-        <v>4</v>
-      </c>
-      <c r="BC296">
-        <v>8</v>
-      </c>
-      <c r="BD296">
-        <v>1.46</v>
-      </c>
-      <c r="BE296">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF296">
-        <v>3.2</v>
-      </c>
-      <c r="BG296">
-        <v>1.29</v>
-      </c>
-      <c r="BH296">
-        <v>3.15</v>
-      </c>
-      <c r="BI296">
-        <v>1.33</v>
-      </c>
-      <c r="BJ296">
-        <v>2.83</v>
-      </c>
-      <c r="BK296">
-        <v>1.6</v>
-      </c>
-      <c r="BL296">
-        <v>2.14</v>
-      </c>
-      <c r="BM296">
-        <v>2.02</v>
-      </c>
-      <c r="BN296">
-        <v>1.71</v>
-      </c>
-      <c r="BO296">
-        <v>2.6</v>
-      </c>
-      <c r="BP296">
-        <v>1.41</v>
       </c>
     </row>
     <row r="297" spans="1:68">
@@ -62664,7 +62664,7 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>7465720</v>
+        <v>7465721</v>
       </c>
       <c r="C297" t="s">
         <v>68</v>
@@ -62679,43 +62679,43 @@
         <v>31</v>
       </c>
       <c r="G297" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H297" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I297">
         <v>0</v>
       </c>
       <c r="J297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L297">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M297">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N297">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O297" t="s">
-        <v>289</v>
+        <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="Q297">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R297">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S297">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="T297">
         <v>1.29</v>
@@ -62724,10 +62724,10 @@
         <v>3.5</v>
       </c>
       <c r="V297">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="W297">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X297">
         <v>5.5</v>
@@ -62736,31 +62736,31 @@
         <v>1.14</v>
       </c>
       <c r="Z297">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="AA297">
-        <v>4.05</v>
+        <v>3.73</v>
       </c>
       <c r="AB297">
-        <v>4.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC297">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AD297">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE297">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF297">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AG297">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH297">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AI297">
         <v>1.5</v>
@@ -62769,100 +62769,100 @@
         <v>2.5</v>
       </c>
       <c r="AK297">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="AL297">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AM297">
-        <v>1.95</v>
+        <v>1.37</v>
       </c>
       <c r="AN297">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="AO297">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AP297">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="AQ297">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="AR297">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AS297">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AT297">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AU297">
         <v>7</v>
       </c>
       <c r="AV297">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW297">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX297">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY297">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ297">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA297">
+        <v>4</v>
+      </c>
+      <c r="BB297">
         <v>7</v>
-      </c>
-      <c r="BB297">
-        <v>4</v>
       </c>
       <c r="BC297">
         <v>11</v>
       </c>
       <c r="BD297">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="BE297">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF297">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="BG297">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH297">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI297">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BJ297">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="BK297">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BL297">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="BM297">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="BN297">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO297">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="BP297">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="298" spans="1:68">
@@ -62870,7 +62870,7 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>7465736</v>
+        <v>7465727</v>
       </c>
       <c r="C298" t="s">
         <v>68</v>
@@ -62885,70 +62885,70 @@
         <v>30</v>
       </c>
       <c r="G298" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H298" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L298">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N298">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O298" t="s">
+        <v>290</v>
+      </c>
+      <c r="P298" t="s">
         <v>93</v>
       </c>
-      <c r="P298" t="s">
-        <v>110</v>
-      </c>
       <c r="Q298">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="R298">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S298">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="T298">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="U298">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V298">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="W298">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X298">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Y298">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z298">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AA298">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="AB298">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AC298">
         <v>1.03</v>
@@ -62957,118 +62957,118 @@
         <v>11</v>
       </c>
       <c r="AE298">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF298">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AG298">
+        <v>1.57</v>
+      </c>
+      <c r="AH298">
+        <v>2.25</v>
+      </c>
+      <c r="AI298">
+        <v>1.6</v>
+      </c>
+      <c r="AJ298">
+        <v>2.2</v>
+      </c>
+      <c r="AK298">
+        <v>1.23</v>
+      </c>
+      <c r="AL298">
+        <v>1.23</v>
+      </c>
+      <c r="AM298">
+        <v>2.05</v>
+      </c>
+      <c r="AN298">
+        <v>2</v>
+      </c>
+      <c r="AO298">
+        <v>1.23</v>
+      </c>
+      <c r="AP298">
+        <v>2.07</v>
+      </c>
+      <c r="AQ298">
+        <v>1.14</v>
+      </c>
+      <c r="AR298">
         <v>1.65</v>
       </c>
-      <c r="AH298">
-        <v>2.2</v>
-      </c>
-      <c r="AI298">
-        <v>1.57</v>
-      </c>
-      <c r="AJ298">
-        <v>2.25</v>
-      </c>
-      <c r="AK298">
-        <v>1.5</v>
-      </c>
-      <c r="AL298">
-        <v>1.26</v>
-      </c>
-      <c r="AM298">
-        <v>1.5</v>
-      </c>
-      <c r="AN298">
-        <v>1.27</v>
-      </c>
-      <c r="AO298">
-        <v>1.57</v>
-      </c>
-      <c r="AP298">
-        <v>1.19</v>
-      </c>
-      <c r="AQ298">
-        <v>1.67</v>
-      </c>
-      <c r="AR298">
-        <v>1.72</v>
-      </c>
       <c r="AS298">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AT298">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
       <c r="AU298">
+        <v>8</v>
+      </c>
+      <c r="AV298">
         <v>3</v>
-      </c>
-      <c r="AV298">
-        <v>4</v>
       </c>
       <c r="AW298">
         <v>5</v>
       </c>
       <c r="AX298">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY298">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA298">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BB298">
         <v>2</v>
       </c>
       <c r="BC298">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BD298">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="BE298">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF298">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="BG298">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BH298">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI298">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BJ298">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BK298">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="BL298">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="BM298">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BN298">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO298">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BP298">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="299" spans="1:68">
@@ -63076,7 +63076,7 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>7465733</v>
+        <v>7465728</v>
       </c>
       <c r="C299" t="s">
         <v>68</v>
@@ -63091,70 +63091,70 @@
         <v>30</v>
       </c>
       <c r="G299" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H299" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J299">
         <v>0</v>
       </c>
       <c r="K299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L299">
+        <v>1</v>
+      </c>
+      <c r="M299">
+        <v>2</v>
+      </c>
+      <c r="N299">
         <v>3</v>
       </c>
-      <c r="M299">
-        <v>1</v>
-      </c>
-      <c r="N299">
+      <c r="O299" t="s">
+        <v>291</v>
+      </c>
+      <c r="P299" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q299">
         <v>4</v>
       </c>
-      <c r="O299" t="s">
-        <v>290</v>
-      </c>
-      <c r="P299" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q299">
-        <v>2.4</v>
-      </c>
       <c r="R299">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S299">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="T299">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="U299">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V299">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="W299">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X299">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Y299">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z299">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA299">
-        <v>3.6</v>
+        <v>3.97</v>
       </c>
       <c r="AB299">
-        <v>3.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC299">
         <v>1.04</v>
@@ -63163,88 +63163,88 @@
         <v>10</v>
       </c>
       <c r="AE299">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF299">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AG299">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH299">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AI299">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AJ299">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK299">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AL299">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AM299">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="AN299">
-        <v>1.86</v>
+        <v>1.14</v>
       </c>
       <c r="AO299">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AP299">
-        <v>1.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ299">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="AR299">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="AS299">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AT299">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AU299">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AV299">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW299">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX299">
+        <v>13</v>
+      </c>
+      <c r="AY299">
+        <v>9</v>
+      </c>
+      <c r="AZ299">
+        <v>22</v>
+      </c>
+      <c r="BA299">
+        <v>1</v>
+      </c>
+      <c r="BB299">
         <v>5</v>
       </c>
-      <c r="AY299">
-        <v>22</v>
-      </c>
-      <c r="AZ299">
-        <v>13</v>
-      </c>
-      <c r="BA299">
-        <v>7</v>
-      </c>
-      <c r="BB299">
-        <v>4</v>
-      </c>
       <c r="BC299">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BD299">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="BE299">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF299">
-        <v>2.43</v>
+        <v>1.52</v>
       </c>
       <c r="BG299">
         <v>1.26</v>
@@ -63253,28 +63253,28 @@
         <v>3.4</v>
       </c>
       <c r="BI299">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BJ299">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BK299">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BL299">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BM299">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BN299">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BO299">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="BP299">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="300" spans="1:68">
@@ -63282,7 +63282,7 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>7465732</v>
+        <v>7465730</v>
       </c>
       <c r="C300" t="s">
         <v>68</v>
@@ -63297,43 +63297,43 @@
         <v>30</v>
       </c>
       <c r="G300" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H300" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J300">
         <v>0</v>
       </c>
       <c r="K300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L300">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M300">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O300" t="s">
+        <v>292</v>
+      </c>
+      <c r="P300" t="s">
         <v>93</v>
       </c>
-      <c r="P300" t="s">
-        <v>156</v>
-      </c>
       <c r="Q300">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="R300">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S300">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="T300">
         <v>1.25</v>
@@ -63342,37 +63342,37 @@
         <v>3.75</v>
       </c>
       <c r="V300">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="W300">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="X300">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y300">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z300">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA300">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AB300">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="AC300">
         <v>1.01</v>
       </c>
       <c r="AD300">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE300">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF300">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AG300">
         <v>1.5</v>
@@ -63381,106 +63381,106 @@
         <v>2.5</v>
       </c>
       <c r="AI300">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ300">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AK300">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AL300">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AM300">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="AN300">
-        <v>1.79</v>
+        <v>1.07</v>
       </c>
       <c r="AO300">
-        <v>1.2</v>
+        <v>0.57</v>
       </c>
       <c r="AP300">
+        <v>1.19</v>
+      </c>
+      <c r="AQ300">
+        <v>0.53</v>
+      </c>
+      <c r="AR300">
         <v>1.67</v>
       </c>
-      <c r="AQ300">
-        <v>1.31</v>
-      </c>
-      <c r="AR300">
-        <v>1.68</v>
-      </c>
       <c r="AS300">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT300">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AU300">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV300">
+        <v>4</v>
+      </c>
+      <c r="AW300">
+        <v>9</v>
+      </c>
+      <c r="AX300">
+        <v>3</v>
+      </c>
+      <c r="AY300">
+        <v>17</v>
+      </c>
+      <c r="AZ300">
+        <v>7</v>
+      </c>
+      <c r="BA300">
         <v>8</v>
       </c>
-      <c r="AW300">
-        <v>7</v>
-      </c>
-      <c r="AX300">
-        <v>13</v>
-      </c>
-      <c r="AY300">
-        <v>7</v>
-      </c>
-      <c r="AZ300">
-        <v>21</v>
-      </c>
-      <c r="BA300">
-        <v>1</v>
-      </c>
       <c r="BB300">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BC300">
+        <v>11</v>
+      </c>
+      <c r="BD300">
+        <v>1.24</v>
+      </c>
+      <c r="BE300">
         <v>8</v>
       </c>
-      <c r="BD300">
-        <v>1.86</v>
-      </c>
-      <c r="BE300">
-        <v>6.5</v>
-      </c>
       <c r="BF300">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="BG300">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BH300">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI300">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BJ300">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BK300">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="BL300">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="BM300">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BN300">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BO300">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BP300">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="301" spans="1:68">
@@ -63527,7 +63527,7 @@
         <v>2</v>
       </c>
       <c r="O301" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P301" t="s">
         <v>246</v>
@@ -63694,7 +63694,7 @@
         <v>301</v>
       </c>
       <c r="B302">
-        <v>7465728</v>
+        <v>7465732</v>
       </c>
       <c r="C302" t="s">
         <v>68</v>
@@ -63709,10 +63709,10 @@
         <v>30</v>
       </c>
       <c r="G302" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H302" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I302">
         <v>0</v>
@@ -63724,169 +63724,169 @@
         <v>0</v>
       </c>
       <c r="L302">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N302">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O302" t="s">
-        <v>292</v>
+        <v>93</v>
       </c>
       <c r="P302" t="s">
-        <v>433</v>
+        <v>156</v>
       </c>
       <c r="Q302">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R302">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S302">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T302">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="U302">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="V302">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="W302">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X302">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y302">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z302">
-        <v>3.94</v>
+        <v>2.25</v>
       </c>
       <c r="AA302">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="AB302">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="AC302">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD302">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AE302">
+        <v>1.17</v>
+      </c>
+      <c r="AF302">
+        <v>5</v>
+      </c>
+      <c r="AG302">
+        <v>1.5</v>
+      </c>
+      <c r="AH302">
+        <v>2.5</v>
+      </c>
+      <c r="AI302">
+        <v>1.44</v>
+      </c>
+      <c r="AJ302">
+        <v>2.63</v>
+      </c>
+      <c r="AK302">
+        <v>1.44</v>
+      </c>
+      <c r="AL302">
+        <v>1.22</v>
+      </c>
+      <c r="AM302">
+        <v>1.57</v>
+      </c>
+      <c r="AN302">
+        <v>1.79</v>
+      </c>
+      <c r="AO302">
         <v>1.2</v>
       </c>
-      <c r="AF302">
-        <v>4.33</v>
-      </c>
-      <c r="AG302">
-        <v>1.6</v>
-      </c>
-      <c r="AH302">
-        <v>2.2</v>
-      </c>
-      <c r="AI302">
-        <v>1.58</v>
-      </c>
-      <c r="AJ302">
-        <v>2.2</v>
-      </c>
-      <c r="AK302">
-        <v>1.95</v>
-      </c>
-      <c r="AL302">
-        <v>1.24</v>
-      </c>
-      <c r="AM302">
-        <v>1.24</v>
-      </c>
-      <c r="AN302">
-        <v>1.14</v>
-      </c>
-      <c r="AO302">
-        <v>1.33</v>
-      </c>
       <c r="AP302">
-        <v>1.07</v>
+        <v>1.67</v>
       </c>
       <c r="AQ302">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AR302">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AS302">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AT302">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AU302">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV302">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW302">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX302">
         <v>13</v>
       </c>
       <c r="AY302">
+        <v>7</v>
+      </c>
+      <c r="AZ302">
+        <v>21</v>
+      </c>
+      <c r="BA302">
+        <v>1</v>
+      </c>
+      <c r="BB302">
+        <v>8</v>
+      </c>
+      <c r="BC302">
         <v>9</v>
       </c>
-      <c r="AZ302">
-        <v>22</v>
-      </c>
-      <c r="BA302">
-        <v>1</v>
-      </c>
-      <c r="BB302">
-        <v>5</v>
-      </c>
-      <c r="BC302">
-        <v>6</v>
-      </c>
       <c r="BD302">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="BE302">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF302">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="BG302">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BH302">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI302">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BJ302">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="BK302">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="BL302">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BM302">
         <v>2.12</v>
       </c>
       <c r="BN302">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BO302">
         <v>2.65</v>
@@ -63900,7 +63900,7 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>7465727</v>
+        <v>7465733</v>
       </c>
       <c r="C303" t="s">
         <v>68</v>
@@ -63915,76 +63915,76 @@
         <v>30</v>
       </c>
       <c r="G303" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H303" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J303">
         <v>0</v>
       </c>
       <c r="K303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L303">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N303">
         <v>4</v>
       </c>
       <c r="O303" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P303" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="Q303">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R303">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S303">
         <v>4</v>
       </c>
       <c r="T303">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="U303">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V303">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="W303">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X303">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y303">
         <v>1.14</v>
       </c>
       <c r="Z303">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AA303">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="AB303">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC303">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD303">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE303">
         <v>1.18</v>
@@ -63996,109 +63996,109 @@
         <v>1.57</v>
       </c>
       <c r="AH303">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AI303">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AJ303">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK303">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL303">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AM303">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AN303">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AO303">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AP303">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AQ303">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AR303">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AS303">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AT303">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU303">
+        <v>12</v>
+      </c>
+      <c r="AV303">
         <v>8</v>
       </c>
-      <c r="AV303">
-        <v>3</v>
-      </c>
       <c r="AW303">
+        <v>10</v>
+      </c>
+      <c r="AX303">
         <v>5</v>
       </c>
-      <c r="AX303">
+      <c r="AY303">
+        <v>22</v>
+      </c>
+      <c r="AZ303">
+        <v>13</v>
+      </c>
+      <c r="BA303">
+        <v>7</v>
+      </c>
+      <c r="BB303">
         <v>4</v>
-      </c>
-      <c r="AY303">
-        <v>13</v>
-      </c>
-      <c r="AZ303">
-        <v>7</v>
-      </c>
-      <c r="BA303">
-        <v>9</v>
-      </c>
-      <c r="BB303">
-        <v>2</v>
       </c>
       <c r="BC303">
         <v>11</v>
       </c>
       <c r="BD303">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="BE303">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BF303">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BG303">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BH303">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BI303">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BJ303">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="BK303">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BL303">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM303">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BN303">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="BO303">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="BP303">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="304" spans="1:68">
@@ -64106,7 +64106,7 @@
         <v>303</v>
       </c>
       <c r="B304">
-        <v>7465730</v>
+        <v>7465736</v>
       </c>
       <c r="C304" t="s">
         <v>68</v>
@@ -64121,178 +64121,178 @@
         <v>30</v>
       </c>
       <c r="G304" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H304" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K304">
         <v>1</v>
       </c>
       <c r="L304">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O304" t="s">
-        <v>294</v>
+        <v>93</v>
       </c>
       <c r="P304" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="Q304">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="R304">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S304">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="T304">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="U304">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="V304">
+        <v>2.5</v>
+      </c>
+      <c r="W304">
+        <v>1.5</v>
+      </c>
+      <c r="X304">
+        <v>6</v>
+      </c>
+      <c r="Y304">
+        <v>1.13</v>
+      </c>
+      <c r="Z304">
+        <v>2.4</v>
+      </c>
+      <c r="AA304">
+        <v>3.6</v>
+      </c>
+      <c r="AB304">
+        <v>2.4</v>
+      </c>
+      <c r="AC304">
+        <v>1.03</v>
+      </c>
+      <c r="AD304">
+        <v>11</v>
+      </c>
+      <c r="AE304">
+        <v>1.2</v>
+      </c>
+      <c r="AF304">
+        <v>4.33</v>
+      </c>
+      <c r="AG304">
+        <v>1.65</v>
+      </c>
+      <c r="AH304">
         <v>2.2</v>
       </c>
-      <c r="W304">
-        <v>1.62</v>
-      </c>
-      <c r="X304">
-        <v>5</v>
-      </c>
-      <c r="Y304">
-        <v>1.17</v>
-      </c>
-      <c r="Z304">
-        <v>1.3</v>
-      </c>
-      <c r="AA304">
-        <v>5</v>
-      </c>
-      <c r="AB304">
-        <v>7</v>
-      </c>
-      <c r="AC304">
-        <v>1.01</v>
-      </c>
-      <c r="AD304">
-        <v>16.5</v>
-      </c>
-      <c r="AE304">
-        <v>1.14</v>
-      </c>
-      <c r="AF304">
-        <v>5.5</v>
-      </c>
-      <c r="AG304">
+      <c r="AI304">
+        <v>1.57</v>
+      </c>
+      <c r="AJ304">
+        <v>2.25</v>
+      </c>
+      <c r="AK304">
         <v>1.5</v>
       </c>
-      <c r="AH304">
-        <v>2.5</v>
-      </c>
-      <c r="AI304">
-        <v>1.83</v>
-      </c>
-      <c r="AJ304">
-        <v>1.83</v>
-      </c>
-      <c r="AK304">
-        <v>1.07</v>
-      </c>
       <c r="AL304">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AM304">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AN304">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AO304">
-        <v>0.57</v>
+        <v>1.57</v>
       </c>
       <c r="AP304">
         <v>1.19</v>
       </c>
       <c r="AQ304">
-        <v>0.53</v>
+        <v>1.67</v>
       </c>
       <c r="AR304">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AS304">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AT304">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="AU304">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV304">
         <v>4</v>
       </c>
       <c r="AW304">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AX304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY304">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AZ304">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA304">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BB304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC304">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BD304">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="BE304">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF304">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="BG304">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BH304">
         <v>3.3</v>
       </c>
       <c r="BI304">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BJ304">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BK304">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BL304">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BM304">
         <v>2.18</v>
@@ -64766,7 +64766,7 @@
         <v>296</v>
       </c>
       <c r="P307" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q307">
         <v>2.6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="435">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1680,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP307"/>
+  <dimension ref="A1:BP308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ9">
         <v>1.87</v>
@@ -5931,7 +5931,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ21">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6549,7 +6549,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR24">
         <v>2.49</v>
@@ -6752,7 +6752,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ25">
         <v>0.53</v>
@@ -10254,7 +10254,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ42">
         <v>1.53</v>
@@ -10463,7 +10463,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ43">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR43">
         <v>1.9</v>
@@ -11902,7 +11902,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ50">
         <v>1.2</v>
@@ -15407,7 +15407,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ67">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR67">
         <v>1.6</v>
@@ -17670,7 +17670,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ78">
         <v>1.07</v>
@@ -19733,7 +19733,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ88">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR88">
         <v>1.89</v>
@@ -22411,7 +22411,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ101">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR101">
         <v>1.83</v>
@@ -22614,7 +22614,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ102">
         <v>0.93</v>
@@ -27146,7 +27146,7 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ124">
         <v>1.56</v>
@@ -28385,7 +28385,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ130">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -31063,7 +31063,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ143">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR143">
         <v>1.29</v>
@@ -32914,7 +32914,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ152">
         <v>0.53</v>
@@ -36416,7 +36416,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ169">
         <v>1.14</v>
@@ -36831,7 +36831,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ171">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -39918,7 +39918,7 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ186">
         <v>2</v>
@@ -40333,7 +40333,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ188">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR188">
         <v>1.68</v>
@@ -43423,7 +43423,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ203">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -47337,7 +47337,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ222">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR222">
         <v>1.91</v>
@@ -47540,7 +47540,7 @@
         <v>2.11</v>
       </c>
       <c r="AP223">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ223">
         <v>1.87</v>
@@ -50630,7 +50630,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ238">
         <v>1.67</v>
@@ -51042,7 +51042,7 @@
         <v>1.55</v>
       </c>
       <c r="AP240">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ240">
         <v>1.2</v>
@@ -52075,7 +52075,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ245">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR245">
         <v>1.55</v>
@@ -54750,7 +54750,7 @@
         <v>1.15</v>
       </c>
       <c r="AP258">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ258">
         <v>1.31</v>
@@ -58049,7 +58049,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ274">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR274">
         <v>1.73</v>
@@ -60930,7 +60930,7 @@
         <v>1.43</v>
       </c>
       <c r="AP288">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AQ288">
         <v>1.44</v>
@@ -61139,7 +61139,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ289">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR289">
         <v>1.5</v>
@@ -64923,6 +64923,212 @@
       </c>
       <c r="BP307">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7465715</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45738.61458333334</v>
+      </c>
+      <c r="F308">
+        <v>31</v>
+      </c>
+      <c r="G308" t="s">
+        <v>77</v>
+      </c>
+      <c r="H308" t="s">
+        <v>73</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308" t="s">
+        <v>93</v>
+      </c>
+      <c r="P308" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q308">
+        <v>1.91</v>
+      </c>
+      <c r="R308">
+        <v>2.63</v>
+      </c>
+      <c r="S308">
+        <v>5.5</v>
+      </c>
+      <c r="T308">
+        <v>1.25</v>
+      </c>
+      <c r="U308">
+        <v>3.75</v>
+      </c>
+      <c r="V308">
+        <v>2.1</v>
+      </c>
+      <c r="W308">
+        <v>1.67</v>
+      </c>
+      <c r="X308">
+        <v>4.5</v>
+      </c>
+      <c r="Y308">
+        <v>1.18</v>
+      </c>
+      <c r="Z308">
+        <v>1.42</v>
+      </c>
+      <c r="AA308">
+        <v>5</v>
+      </c>
+      <c r="AB308">
+        <v>6.31</v>
+      </c>
+      <c r="AC308">
+        <v>1.01</v>
+      </c>
+      <c r="AD308">
+        <v>17</v>
+      </c>
+      <c r="AE308">
+        <v>1.14</v>
+      </c>
+      <c r="AF308">
+        <v>5.5</v>
+      </c>
+      <c r="AG308">
+        <v>1.44</v>
+      </c>
+      <c r="AH308">
+        <v>2.7</v>
+      </c>
+      <c r="AI308">
+        <v>1.62</v>
+      </c>
+      <c r="AJ308">
+        <v>2.2</v>
+      </c>
+      <c r="AK308">
+        <v>1.1</v>
+      </c>
+      <c r="AL308">
+        <v>1.13</v>
+      </c>
+      <c r="AM308">
+        <v>2.8</v>
+      </c>
+      <c r="AN308">
+        <v>2.27</v>
+      </c>
+      <c r="AO308">
+        <v>0.53</v>
+      </c>
+      <c r="AP308">
+        <v>2.19</v>
+      </c>
+      <c r="AQ308">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR308">
+        <v>1.75</v>
+      </c>
+      <c r="AS308">
+        <v>1.33</v>
+      </c>
+      <c r="AT308">
+        <v>3.08</v>
+      </c>
+      <c r="AU308">
+        <v>4</v>
+      </c>
+      <c r="AV308">
+        <v>2</v>
+      </c>
+      <c r="AW308">
+        <v>15</v>
+      </c>
+      <c r="AX308">
+        <v>6</v>
+      </c>
+      <c r="AY308">
+        <v>19</v>
+      </c>
+      <c r="AZ308">
+        <v>8</v>
+      </c>
+      <c r="BA308">
+        <v>10</v>
+      </c>
+      <c r="BB308">
+        <v>3</v>
+      </c>
+      <c r="BC308">
+        <v>13</v>
+      </c>
+      <c r="BD308">
+        <v>1.33</v>
+      </c>
+      <c r="BE308">
+        <v>7.5</v>
+      </c>
+      <c r="BF308">
+        <v>3.65</v>
+      </c>
+      <c r="BG308">
+        <v>1.26</v>
+      </c>
+      <c r="BH308">
+        <v>3.4</v>
+      </c>
+      <c r="BI308">
+        <v>1.46</v>
+      </c>
+      <c r="BJ308">
+        <v>2.5</v>
+      </c>
+      <c r="BK308">
+        <v>1.74</v>
+      </c>
+      <c r="BL308">
+        <v>1.98</v>
+      </c>
+      <c r="BM308">
+        <v>2.17</v>
+      </c>
+      <c r="BN308">
+        <v>1.6</v>
+      </c>
+      <c r="BO308">
+        <v>2.7</v>
+      </c>
+      <c r="BP308">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="437">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -907,6 +907,9 @@
     <t>['45', '56', '78']</t>
   </si>
   <si>
+    <t>['7', '44']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1320,6 +1323,9 @@
   <si>
     <t>['5', '69']</t>
   </si>
+  <si>
+    <t>['21', '84']</t>
+  </si>
 </sst>
 </file>
 
@@ -1680,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP308"/>
+  <dimension ref="A1:BP309"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2142,7 +2148,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2348,7 +2354,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2760,7 +2766,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2966,7 +2972,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3172,7 +3178,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3378,7 +3384,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3790,7 +3796,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4074,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ12">
         <v>1.07</v>
@@ -4202,7 +4208,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4283,7 +4289,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4820,7 +4826,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5644,7 +5650,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6674,7 +6680,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6880,7 +6886,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7086,7 +7092,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7498,7 +7504,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7576,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ29">
         <v>1.06</v>
@@ -7910,7 +7916,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8197,7 +8203,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8528,7 +8534,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8734,7 +8740,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9352,7 +9358,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9558,7 +9564,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9970,7 +9976,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10257,7 +10263,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ42">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -10794,7 +10800,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10872,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ45">
         <v>0.53</v>
@@ -11000,7 +11006,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11412,7 +11418,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11824,7 +11830,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12030,7 +12036,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12236,7 +12242,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -13060,7 +13066,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13472,7 +13478,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -14090,7 +14096,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14296,7 +14302,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14374,7 +14380,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ62">
         <v>0.93</v>
@@ -14502,7 +14508,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15120,7 +15126,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15532,7 +15538,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15738,7 +15744,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15819,7 +15825,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ69">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15944,7 +15950,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16150,7 +16156,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16356,7 +16362,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16562,7 +16568,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16768,7 +16774,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16974,7 +16980,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17592,7 +17598,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17798,7 +17804,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18210,7 +18216,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18494,7 +18500,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ82">
         <v>2</v>
@@ -18622,7 +18628,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18828,7 +18834,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19446,7 +19452,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19527,7 +19533,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ87">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -20064,7 +20070,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20476,7 +20482,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20888,7 +20894,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21094,7 +21100,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21172,7 +21178,7 @@
         <v>1.4</v>
       </c>
       <c r="AP95">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ95">
         <v>1.56</v>
@@ -21300,7 +21306,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21506,7 +21512,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21918,7 +21924,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22330,7 +22336,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22536,7 +22542,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22948,7 +22954,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23647,7 +23653,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -24184,7 +24190,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24390,7 +24396,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24596,7 +24602,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25089,7 +25095,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ114">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -25214,7 +25220,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25420,7 +25426,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25626,7 +25632,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25832,7 +25838,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25910,7 +25916,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ118">
         <v>1.2</v>
@@ -26038,7 +26044,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26244,7 +26250,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26450,7 +26456,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26656,7 +26662,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26862,7 +26868,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27068,7 +27074,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27274,7 +27280,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27892,7 +27898,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28304,7 +28310,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28510,7 +28516,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29000,7 +29006,7 @@
         <v>1.17</v>
       </c>
       <c r="AP133">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ133">
         <v>1.31</v>
@@ -29540,7 +29546,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29827,7 +29833,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ137">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -31394,7 +31400,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31600,7 +31606,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31678,7 +31684,7 @@
         <v>2.5</v>
       </c>
       <c r="AP146">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ146">
         <v>1.87</v>
@@ -31806,7 +31812,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32012,7 +32018,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32424,7 +32430,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32505,7 +32511,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ150">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32630,7 +32636,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33042,7 +33048,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33248,7 +33254,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33454,7 +33460,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34484,7 +34490,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34896,7 +34902,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35720,7 +35726,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36544,7 +36550,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36750,7 +36756,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37034,7 +37040,7 @@
         <v>0.5</v>
       </c>
       <c r="AP172">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ172">
         <v>0.53</v>
@@ -37162,7 +37168,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37986,7 +37992,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38192,7 +38198,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38604,7 +38610,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38685,7 +38691,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ180">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -38810,7 +38816,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39428,7 +39434,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39634,7 +39640,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39840,7 +39846,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40458,7 +40464,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41076,7 +41082,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41282,7 +41288,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41488,7 +41494,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41694,7 +41700,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41775,7 +41781,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ195">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -41900,7 +41906,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42184,7 +42190,7 @@
         <v>1.6</v>
       </c>
       <c r="AP197">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ197">
         <v>1.44</v>
@@ -42518,7 +42524,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42930,7 +42936,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43548,7 +43554,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43960,7 +43966,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44166,7 +44172,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44450,7 +44456,7 @@
         <v>1.09</v>
       </c>
       <c r="AP208">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ208">
         <v>1.13</v>
@@ -44578,7 +44584,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44990,7 +44996,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45814,7 +45820,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45895,7 +45901,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ215">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -46432,7 +46438,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46638,7 +46644,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46844,7 +46850,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -48698,7 +48704,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49316,7 +49322,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49603,7 +49609,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ233">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR233">
         <v>1.81</v>
@@ -49934,7 +49940,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50140,7 +50146,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50552,7 +50558,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51376,7 +51382,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51582,7 +51588,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51788,7 +51794,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52072,7 +52078,7 @@
         <v>0.58</v>
       </c>
       <c r="AP245">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ245">
         <v>0.5600000000000001</v>
@@ -52406,7 +52412,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52818,7 +52824,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -53723,7 +53729,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ253">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR253">
         <v>1.74</v>
@@ -54054,7 +54060,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -55290,7 +55296,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55496,7 +55502,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55702,7 +55708,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55780,7 +55786,7 @@
         <v>1.69</v>
       </c>
       <c r="AP263">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ263">
         <v>1.87</v>
@@ -55908,7 +55914,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56114,7 +56120,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56320,7 +56326,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56526,7 +56532,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56732,7 +56738,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -57144,7 +57150,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57350,7 +57356,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57762,7 +57768,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58174,7 +58180,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58380,7 +58386,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58586,7 +58592,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58667,7 +58673,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ277">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR277">
         <v>1.69</v>
@@ -58792,7 +58798,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58998,7 +59004,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59204,7 +59210,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59410,7 +59416,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -60106,7 +60112,7 @@
         <v>0.86</v>
       </c>
       <c r="AP284">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="AQ284">
         <v>0.75</v>
@@ -60440,7 +60446,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60646,7 +60652,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61470,7 +61476,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61882,7 +61888,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62088,7 +62094,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62500,7 +62506,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62706,7 +62712,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -63118,7 +63124,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -64560,7 +64566,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -65128,6 +65134,212 @@
         <v>2.7</v>
       </c>
       <c r="BP308">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7465716</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45738.70833333334</v>
+      </c>
+      <c r="F309">
+        <v>31</v>
+      </c>
+      <c r="G309" t="s">
+        <v>80</v>
+      </c>
+      <c r="H309" t="s">
+        <v>70</v>
+      </c>
+      <c r="I309">
+        <v>2</v>
+      </c>
+      <c r="J309">
+        <v>1</v>
+      </c>
+      <c r="K309">
+        <v>3</v>
+      </c>
+      <c r="L309">
+        <v>2</v>
+      </c>
+      <c r="M309">
+        <v>2</v>
+      </c>
+      <c r="N309">
+        <v>4</v>
+      </c>
+      <c r="O309" t="s">
+        <v>297</v>
+      </c>
+      <c r="P309" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q309">
+        <v>3</v>
+      </c>
+      <c r="R309">
+        <v>2.25</v>
+      </c>
+      <c r="S309">
+        <v>3.4</v>
+      </c>
+      <c r="T309">
+        <v>1.33</v>
+      </c>
+      <c r="U309">
+        <v>3.25</v>
+      </c>
+      <c r="V309">
+        <v>2.63</v>
+      </c>
+      <c r="W309">
+        <v>1.44</v>
+      </c>
+      <c r="X309">
+        <v>6.5</v>
+      </c>
+      <c r="Y309">
+        <v>1.11</v>
+      </c>
+      <c r="Z309">
+        <v>2.38</v>
+      </c>
+      <c r="AA309">
+        <v>3.44</v>
+      </c>
+      <c r="AB309">
+        <v>2.9</v>
+      </c>
+      <c r="AC309">
+        <v>1.05</v>
+      </c>
+      <c r="AD309">
+        <v>9.5</v>
+      </c>
+      <c r="AE309">
+        <v>1.22</v>
+      </c>
+      <c r="AF309">
+        <v>4</v>
+      </c>
+      <c r="AG309">
+        <v>1.57</v>
+      </c>
+      <c r="AH309">
+        <v>2.28</v>
+      </c>
+      <c r="AI309">
+        <v>1.57</v>
+      </c>
+      <c r="AJ309">
+        <v>2.25</v>
+      </c>
+      <c r="AK309">
+        <v>1.4</v>
+      </c>
+      <c r="AL309">
+        <v>1.25</v>
+      </c>
+      <c r="AM309">
+        <v>1.57</v>
+      </c>
+      <c r="AN309">
+        <v>0.87</v>
+      </c>
+      <c r="AO309">
+        <v>1.53</v>
+      </c>
+      <c r="AP309">
+        <v>0.88</v>
+      </c>
+      <c r="AQ309">
+        <v>1.5</v>
+      </c>
+      <c r="AR309">
+        <v>1.59</v>
+      </c>
+      <c r="AS309">
+        <v>1.3</v>
+      </c>
+      <c r="AT309">
+        <v>2.89</v>
+      </c>
+      <c r="AU309">
+        <v>4</v>
+      </c>
+      <c r="AV309">
+        <v>3</v>
+      </c>
+      <c r="AW309">
+        <v>8</v>
+      </c>
+      <c r="AX309">
+        <v>7</v>
+      </c>
+      <c r="AY309">
+        <v>12</v>
+      </c>
+      <c r="AZ309">
+        <v>10</v>
+      </c>
+      <c r="BA309">
+        <v>7</v>
+      </c>
+      <c r="BB309">
+        <v>2</v>
+      </c>
+      <c r="BC309">
+        <v>9</v>
+      </c>
+      <c r="BD309">
+        <v>1.8</v>
+      </c>
+      <c r="BE309">
+        <v>6.5</v>
+      </c>
+      <c r="BF309">
+        <v>2.2</v>
+      </c>
+      <c r="BG309">
+        <v>1.26</v>
+      </c>
+      <c r="BH309">
+        <v>3.4</v>
+      </c>
+      <c r="BI309">
+        <v>1.46</v>
+      </c>
+      <c r="BJ309">
+        <v>2.5</v>
+      </c>
+      <c r="BK309">
+        <v>1.74</v>
+      </c>
+      <c r="BL309">
+        <v>1.98</v>
+      </c>
+      <c r="BM309">
+        <v>2.12</v>
+      </c>
+      <c r="BN309">
+        <v>1.63</v>
+      </c>
+      <c r="BO309">
+        <v>2.7</v>
+      </c>
+      <c r="BP309">
         <v>1.4</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="444">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -910,6 +910,18 @@
     <t>['7', '44']</t>
   </si>
   <si>
+    <t>['19', '52', '84']</t>
+  </si>
+  <si>
+    <t>['42', '84']</t>
+  </si>
+  <si>
+    <t>['41', '47', '74']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1326,6 +1338,15 @@
   <si>
     <t>['21', '84']</t>
   </si>
+  <si>
+    <t>['11', '78']</t>
+  </si>
+  <si>
+    <t>['5', '68']</t>
+  </si>
+  <si>
+    <t>['50', '64']</t>
+  </si>
 </sst>
 </file>
 
@@ -1686,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP309"/>
+  <dimension ref="A1:BP314"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2020,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ2">
         <v>1.2</v>
@@ -2148,7 +2169,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2354,7 +2375,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2435,7 +2456,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ4">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2638,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5">
         <v>2</v>
@@ -2766,7 +2787,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2972,7 +2993,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3178,7 +3199,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3384,7 +3405,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3796,7 +3817,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4083,7 +4104,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ12">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4208,7 +4229,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4286,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.5</v>
@@ -4698,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4826,7 +4847,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5522,10 +5543,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5650,7 +5671,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5731,7 +5752,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ20">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6349,7 +6370,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR23">
         <v>2.16</v>
@@ -6680,7 +6701,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6761,7 +6782,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ25">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>1.58</v>
@@ -6886,7 +6907,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7092,7 +7113,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7170,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ27">
         <v>0.75</v>
@@ -7504,7 +7525,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7916,7 +7937,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8406,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1.31</v>
@@ -8534,7 +8555,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8612,7 +8633,7 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ34">
         <v>0.93</v>
@@ -8740,7 +8761,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8821,7 +8842,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ35">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR35">
         <v>0.8</v>
@@ -9358,7 +9379,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9564,7 +9585,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9976,7 +9997,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10057,7 +10078,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ41">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR41">
         <v>1.77</v>
@@ -10466,7 +10487,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>0.5600000000000001</v>
@@ -10672,7 +10693,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ44">
         <v>0.75</v>
@@ -10800,7 +10821,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -10881,7 +10902,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ45">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR45">
         <v>1.68</v>
@@ -11006,7 +11027,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11293,7 +11314,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>2.09</v>
@@ -11418,7 +11439,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11496,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ48">
         <v>1.87</v>
@@ -11702,7 +11723,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ49">
         <v>1.56</v>
@@ -11830,7 +11851,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11911,7 +11932,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ50">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR50">
         <v>1.58</v>
@@ -12036,7 +12057,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12114,7 +12135,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51">
         <v>1.13</v>
@@ -12242,7 +12263,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12732,7 +12753,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ54">
         <v>1.06</v>
@@ -12938,7 +12959,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ55">
         <v>1.14</v>
@@ -13066,7 +13087,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13147,7 +13168,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ56">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.88</v>
@@ -13478,7 +13499,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -14096,7 +14117,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14302,7 +14323,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14508,7 +14529,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14795,7 +14816,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR64">
         <v>2.12</v>
@@ -15126,7 +15147,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15538,7 +15559,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15744,7 +15765,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15950,7 +15971,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16031,7 +16052,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ70">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR70">
         <v>1.9</v>
@@ -16156,7 +16177,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16362,7 +16383,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16568,7 +16589,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16646,7 +16667,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ73">
         <v>0.53</v>
@@ -16774,7 +16795,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16852,7 +16873,7 @@
         <v>1.33</v>
       </c>
       <c r="AP74">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
         <v>1.31</v>
@@ -16980,7 +17001,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17061,7 +17082,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ75">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.48</v>
@@ -17264,7 +17285,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ76">
         <v>1.06</v>
@@ -17470,7 +17491,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.2</v>
@@ -17598,7 +17619,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17679,7 +17700,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ78">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17804,7 +17825,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -17882,10 +17903,10 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ79">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR79">
         <v>1.92</v>
@@ -18216,7 +18237,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18297,7 +18318,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ81">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR81">
         <v>1.73</v>
@@ -18628,7 +18649,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18834,7 +18855,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19452,7 +19473,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20070,7 +20091,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20151,7 +20172,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ90">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR90">
         <v>1.95</v>
@@ -20482,7 +20503,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20560,10 +20581,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
         <v>1.75</v>
@@ -20766,7 +20787,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ93">
         <v>1.14</v>
@@ -20894,7 +20915,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20975,7 +20996,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ94">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR94">
         <v>1.92</v>
@@ -21100,7 +21121,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21306,7 +21327,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21512,7 +21533,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21590,7 +21611,7 @@
         <v>1.4</v>
       </c>
       <c r="AP97">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ97">
         <v>1.87</v>
@@ -21799,7 +21820,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ98">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR98">
         <v>1.49</v>
@@ -21924,7 +21945,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22002,10 +22023,10 @@
         <v>2.25</v>
       </c>
       <c r="AP99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ99">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR99">
         <v>1.31</v>
@@ -22211,7 +22232,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ100">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -22336,7 +22357,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22414,7 +22435,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ101">
         <v>0.5600000000000001</v>
@@ -22542,7 +22563,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22954,7 +22975,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23650,7 +23671,7 @@
         <v>2</v>
       </c>
       <c r="AP107">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ107">
         <v>1.5</v>
@@ -24190,7 +24211,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24271,7 +24292,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ110">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>2.02</v>
@@ -24396,7 +24417,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24602,7 +24623,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24683,7 +24704,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ112">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR112">
         <v>1.74</v>
@@ -24889,7 +24910,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ113">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR113">
         <v>2.08</v>
@@ -25220,7 +25241,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25426,7 +25447,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25632,7 +25653,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25838,7 +25859,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26044,7 +26065,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26122,7 +26143,7 @@
         <v>1.8</v>
       </c>
       <c r="AP119">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ119">
         <v>2</v>
@@ -26250,7 +26271,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26456,7 +26477,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26534,10 +26555,10 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ121">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR121">
         <v>1.74</v>
@@ -26662,7 +26683,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26868,7 +26889,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27074,7 +27095,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27280,7 +27301,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27358,7 +27379,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ125">
         <v>1.67</v>
@@ -27898,7 +27919,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -27976,7 +27997,7 @@
         <v>1.67</v>
       </c>
       <c r="AP128">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
         <v>1.87</v>
@@ -28310,7 +28331,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28516,7 +28537,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28597,7 +28618,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ131">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR131">
         <v>1.6</v>
@@ -28800,10 +28821,10 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ132">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR132">
         <v>1.8</v>
@@ -29418,7 +29439,7 @@
         <v>1.71</v>
       </c>
       <c r="AP135">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29546,7 +29567,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29830,7 +29851,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ137">
         <v>1.5</v>
@@ -30039,7 +30060,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ138">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -30245,7 +30266,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ139">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR139">
         <v>1.86</v>
@@ -30657,7 +30678,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ141">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR141">
         <v>2.06</v>
@@ -30860,7 +30881,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
         <v>1.14</v>
@@ -31066,7 +31087,7 @@
         <v>0.43</v>
       </c>
       <c r="AP143">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ143">
         <v>0.5600000000000001</v>
@@ -31272,7 +31293,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ144">
         <v>1.56</v>
@@ -31400,7 +31421,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31606,7 +31627,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31687,7 +31708,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ146">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR146">
         <v>1.65</v>
@@ -31812,7 +31833,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32018,7 +32039,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32430,7 +32451,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32636,7 +32657,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33048,7 +33069,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33254,7 +33275,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33460,7 +33481,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33747,7 +33768,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ156">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR156">
         <v>1.76</v>
@@ -34365,7 +34386,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ159">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR159">
         <v>1.83</v>
@@ -34490,7 +34511,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34568,7 +34589,7 @@
         <v>1.43</v>
       </c>
       <c r="AP160">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ160">
         <v>1.2</v>
@@ -34902,7 +34923,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -34983,7 +35004,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ162">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR162">
         <v>1.64</v>
@@ -35186,7 +35207,7 @@
         <v>1.13</v>
       </c>
       <c r="AP163">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ163">
         <v>0.75</v>
@@ -35392,7 +35413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ164">
         <v>0.93</v>
@@ -35726,7 +35747,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35804,7 +35825,7 @@
         <v>2.25</v>
       </c>
       <c r="AP166">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ166">
         <v>2</v>
@@ -36013,7 +36034,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ167">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR167">
         <v>1.58</v>
@@ -36219,7 +36240,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ168">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR168">
         <v>1.16</v>
@@ -36550,7 +36571,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36756,7 +36777,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37168,7 +37189,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37246,10 +37267,10 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ173">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR173">
         <v>1.68</v>
@@ -37992,7 +38013,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38070,7 +38091,7 @@
         <v>1.25</v>
       </c>
       <c r="AP177">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ177">
         <v>1.67</v>
@@ -38198,7 +38219,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38485,7 +38506,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ179">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR179">
         <v>1.58</v>
@@ -38610,7 +38631,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38816,7 +38837,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39100,10 +39121,10 @@
         <v>2</v>
       </c>
       <c r="AP182">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ182">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR182">
         <v>1.69</v>
@@ -39434,7 +39455,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39515,7 +39536,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ184">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR184">
         <v>1.84</v>
@@ -39640,7 +39661,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39718,7 +39739,7 @@
         <v>0.88</v>
       </c>
       <c r="AP185">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ185">
         <v>1.14</v>
@@ -39846,7 +39867,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40130,7 +40151,7 @@
         <v>1.67</v>
       </c>
       <c r="AP187">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ187">
         <v>1.87</v>
@@ -40464,7 +40485,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40957,7 +40978,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ191">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR191">
         <v>1.68</v>
@@ -41082,7 +41103,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41163,7 +41184,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ192">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41288,7 +41309,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41369,7 +41390,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ193">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR193">
         <v>1.56</v>
@@ -41494,7 +41515,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41572,7 +41593,7 @@
         <v>1.11</v>
       </c>
       <c r="AP194">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ194">
         <v>1.31</v>
@@ -41700,7 +41721,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41906,7 +41927,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42399,7 +42420,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ198">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR198">
         <v>1.99</v>
@@ -42524,7 +42545,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42602,7 +42623,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ199">
         <v>1.13</v>
@@ -42936,7 +42957,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43220,7 +43241,7 @@
         <v>1.6</v>
       </c>
       <c r="AP202">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ202">
         <v>1.56</v>
@@ -43554,7 +43575,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43632,7 +43653,7 @@
         <v>1.6</v>
       </c>
       <c r="AP204">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ204">
         <v>1.87</v>
@@ -43838,7 +43859,7 @@
         <v>1.3</v>
       </c>
       <c r="AP205">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>0.93</v>
@@ -43966,7 +43987,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44172,7 +44193,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44584,7 +44605,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44868,7 +44889,7 @@
         <v>1.55</v>
       </c>
       <c r="AP210">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ210">
         <v>1.44</v>
@@ -44996,7 +45017,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45283,7 +45304,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ212">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.95</v>
@@ -45489,7 +45510,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ213">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR213">
         <v>1.86</v>
@@ -45692,7 +45713,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ214">
         <v>1.2</v>
@@ -45820,7 +45841,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46438,7 +46459,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46519,7 +46540,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ218">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR218">
         <v>1.39</v>
@@ -46644,7 +46665,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46722,7 +46743,7 @@
         <v>2.27</v>
       </c>
       <c r="AP219">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ219">
         <v>2</v>
@@ -46850,7 +46871,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47137,7 +47158,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ221">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR221">
         <v>1.93</v>
@@ -47549,7 +47570,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ223">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR223">
         <v>1.66</v>
@@ -47958,7 +47979,7 @@
         <v>0.82</v>
       </c>
       <c r="AP225">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ225">
         <v>0.75</v>
@@ -48164,7 +48185,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ226">
         <v>1.67</v>
@@ -48579,7 +48600,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ228">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR228">
         <v>1.74</v>
@@ -48704,7 +48725,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48988,7 +49009,7 @@
         <v>1</v>
       </c>
       <c r="AP230">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ230">
         <v>1.13</v>
@@ -49197,7 +49218,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ231">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR231">
         <v>1.8</v>
@@ -49322,7 +49343,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49940,7 +49961,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50018,10 +50039,10 @@
         <v>0.82</v>
       </c>
       <c r="AP235">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ235">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR235">
         <v>1.73</v>
@@ -50146,7 +50167,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50224,7 +50245,7 @@
         <v>1.33</v>
       </c>
       <c r="AP236">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ236">
         <v>1.06</v>
@@ -50433,7 +50454,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ237">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR237">
         <v>1.48</v>
@@ -50558,7 +50579,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51254,7 +51275,7 @@
         <v>0.45</v>
       </c>
       <c r="AP241">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ241">
         <v>0.53</v>
@@ -51382,7 +51403,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51588,7 +51609,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51794,7 +51815,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52284,10 +52305,10 @@
         <v>0.45</v>
       </c>
       <c r="AP246">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ246">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR246">
         <v>1.7</v>
@@ -52412,7 +52433,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52699,7 +52720,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ248">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR248">
         <v>1.74</v>
@@ -52824,7 +52845,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -53726,7 +53747,7 @@
         <v>1.54</v>
       </c>
       <c r="AP253">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ253">
         <v>1.5</v>
@@ -53932,7 +53953,7 @@
         <v>0.42</v>
       </c>
       <c r="AP254">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ254">
         <v>0.53</v>
@@ -54060,7 +54081,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54347,7 +54368,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ256">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR256">
         <v>1.77</v>
@@ -54550,10 +54571,10 @@
         <v>1.42</v>
       </c>
       <c r="AP257">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ257">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR257">
         <v>1.84</v>
@@ -54965,7 +54986,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ259">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR259">
         <v>1.5</v>
@@ -55296,7 +55317,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55374,7 +55395,7 @@
         <v>1.31</v>
       </c>
       <c r="AP261">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ261">
         <v>1.44</v>
@@ -55502,7 +55523,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55583,7 +55604,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ262">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR262">
         <v>1.47</v>
@@ -55708,7 +55729,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55914,7 +55935,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -55992,10 +56013,10 @@
         <v>0.42</v>
       </c>
       <c r="AP264">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ264">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR264">
         <v>1.35</v>
@@ -56120,7 +56141,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56198,7 +56219,7 @@
         <v>1.33</v>
       </c>
       <c r="AP265">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ265">
         <v>1.67</v>
@@ -56326,7 +56347,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56532,7 +56553,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56738,7 +56759,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -56819,7 +56840,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ268">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR268">
         <v>1.52</v>
@@ -57022,7 +57043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP269">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ269">
         <v>1.14</v>
@@ -57150,7 +57171,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57231,7 +57252,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ270">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR270">
         <v>1.51</v>
@@ -57356,7 +57377,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57643,7 +57664,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ272">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR272">
         <v>1.69</v>
@@ -57768,7 +57789,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -57849,7 +57870,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ273">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR273">
         <v>1.87</v>
@@ -58180,7 +58201,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58386,7 +58407,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58464,7 +58485,7 @@
         <v>1.14</v>
       </c>
       <c r="AP276">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ276">
         <v>1.06</v>
@@ -58592,7 +58613,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58798,7 +58819,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -59004,7 +59025,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59210,7 +59231,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59416,7 +59437,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59700,7 +59721,7 @@
         <v>1.79</v>
       </c>
       <c r="AP282">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ282">
         <v>1.56</v>
@@ -59909,7 +59930,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ283">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR283">
         <v>1.73</v>
@@ -60446,7 +60467,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60524,10 +60545,10 @@
         <v>0.92</v>
       </c>
       <c r="AP286">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ286">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR286">
         <v>1.39</v>
@@ -60652,7 +60673,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61348,7 +61369,7 @@
         <v>1.67</v>
       </c>
       <c r="AP290">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ290">
         <v>1.56</v>
@@ -61476,7 +61497,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61760,7 +61781,7 @@
         <v>1.29</v>
       </c>
       <c r="AP292">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ292">
         <v>1.2</v>
@@ -61888,7 +61909,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -61969,7 +61990,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ293">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR293">
         <v>1.47</v>
@@ -62094,7 +62115,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62175,7 +62196,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ294">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AR294">
         <v>1.99</v>
@@ -62506,7 +62527,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62712,7 +62733,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -62793,7 +62814,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ297">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR297">
         <v>1.66</v>
@@ -63124,7 +63145,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -63202,7 +63223,7 @@
         <v>1.33</v>
       </c>
       <c r="AP299">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AQ299">
         <v>1.44</v>
@@ -63411,7 +63432,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ300">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="AR300">
         <v>1.67</v>
@@ -63820,7 +63841,7 @@
         <v>1.2</v>
       </c>
       <c r="AP302">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ302">
         <v>1.31</v>
@@ -64026,7 +64047,7 @@
         <v>1.13</v>
       </c>
       <c r="AP303">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ303">
         <v>1.06</v>
@@ -64566,7 +64587,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -64647,7 +64668,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ306">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR306">
         <v>1.42</v>
@@ -65184,7 +65205,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65341,6 +65362,1036 @@
       </c>
       <c r="BP309">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7465743</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F310">
+        <v>32</v>
+      </c>
+      <c r="G310" t="s">
+        <v>81</v>
+      </c>
+      <c r="H310" t="s">
+        <v>75</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>1</v>
+      </c>
+      <c r="M310">
+        <v>0</v>
+      </c>
+      <c r="N310">
+        <v>1</v>
+      </c>
+      <c r="O310" t="s">
+        <v>226</v>
+      </c>
+      <c r="P310" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q310">
+        <v>2.2</v>
+      </c>
+      <c r="R310">
+        <v>2.4</v>
+      </c>
+      <c r="S310">
+        <v>4.75</v>
+      </c>
+      <c r="T310">
+        <v>1.3</v>
+      </c>
+      <c r="U310">
+        <v>3.4</v>
+      </c>
+      <c r="V310">
+        <v>2.38</v>
+      </c>
+      <c r="W310">
+        <v>1.53</v>
+      </c>
+      <c r="X310">
+        <v>6</v>
+      </c>
+      <c r="Y310">
+        <v>1.13</v>
+      </c>
+      <c r="Z310">
+        <v>1.65</v>
+      </c>
+      <c r="AA310">
+        <v>3.75</v>
+      </c>
+      <c r="AB310">
+        <v>4.5</v>
+      </c>
+      <c r="AC310">
+        <v>2.35</v>
+      </c>
+      <c r="AD310">
+        <v>1.61</v>
+      </c>
+      <c r="AE310">
+        <v>0</v>
+      </c>
+      <c r="AF310">
+        <v>0</v>
+      </c>
+      <c r="AG310">
+        <v>1.6</v>
+      </c>
+      <c r="AH310">
+        <v>2.3</v>
+      </c>
+      <c r="AI310">
+        <v>1.62</v>
+      </c>
+      <c r="AJ310">
+        <v>2.2</v>
+      </c>
+      <c r="AK310">
+        <v>0</v>
+      </c>
+      <c r="AL310">
+        <v>0</v>
+      </c>
+      <c r="AM310">
+        <v>0</v>
+      </c>
+      <c r="AN310">
+        <v>1.93</v>
+      </c>
+      <c r="AO310">
+        <v>1.07</v>
+      </c>
+      <c r="AP310">
+        <v>2</v>
+      </c>
+      <c r="AQ310">
+        <v>1</v>
+      </c>
+      <c r="AR310">
+        <v>1.83</v>
+      </c>
+      <c r="AS310">
+        <v>1.53</v>
+      </c>
+      <c r="AT310">
+        <v>3.36</v>
+      </c>
+      <c r="AU310">
+        <v>7</v>
+      </c>
+      <c r="AV310">
+        <v>5</v>
+      </c>
+      <c r="AW310">
+        <v>13</v>
+      </c>
+      <c r="AX310">
+        <v>9</v>
+      </c>
+      <c r="AY310">
+        <v>20</v>
+      </c>
+      <c r="AZ310">
+        <v>14</v>
+      </c>
+      <c r="BA310">
+        <v>5</v>
+      </c>
+      <c r="BB310">
+        <v>8</v>
+      </c>
+      <c r="BC310">
+        <v>13</v>
+      </c>
+      <c r="BD310">
+        <v>0</v>
+      </c>
+      <c r="BE310">
+        <v>0</v>
+      </c>
+      <c r="BF310">
+        <v>0</v>
+      </c>
+      <c r="BG310">
+        <v>0</v>
+      </c>
+      <c r="BH310">
+        <v>0</v>
+      </c>
+      <c r="BI310">
+        <v>0</v>
+      </c>
+      <c r="BJ310">
+        <v>0</v>
+      </c>
+      <c r="BK310">
+        <v>0</v>
+      </c>
+      <c r="BL310">
+        <v>0</v>
+      </c>
+      <c r="BM310">
+        <v>0</v>
+      </c>
+      <c r="BN310">
+        <v>0</v>
+      </c>
+      <c r="BO310">
+        <v>0</v>
+      </c>
+      <c r="BP310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7467162</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F311">
+        <v>32</v>
+      </c>
+      <c r="G311" t="s">
+        <v>87</v>
+      </c>
+      <c r="H311" t="s">
+        <v>77</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <v>1</v>
+      </c>
+      <c r="K311">
+        <v>2</v>
+      </c>
+      <c r="L311">
+        <v>3</v>
+      </c>
+      <c r="M311">
+        <v>2</v>
+      </c>
+      <c r="N311">
+        <v>5</v>
+      </c>
+      <c r="O311" t="s">
+        <v>298</v>
+      </c>
+      <c r="P311" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q311">
+        <v>2.4</v>
+      </c>
+      <c r="R311">
+        <v>2.4</v>
+      </c>
+      <c r="S311">
+        <v>4</v>
+      </c>
+      <c r="T311">
+        <v>1.29</v>
+      </c>
+      <c r="U311">
+        <v>3.5</v>
+      </c>
+      <c r="V311">
+        <v>2.25</v>
+      </c>
+      <c r="W311">
+        <v>1.57</v>
+      </c>
+      <c r="X311">
+        <v>5.5</v>
+      </c>
+      <c r="Y311">
+        <v>1.14</v>
+      </c>
+      <c r="Z311">
+        <v>1.85</v>
+      </c>
+      <c r="AA311">
+        <v>3.7</v>
+      </c>
+      <c r="AB311">
+        <v>3.6</v>
+      </c>
+      <c r="AC311">
+        <v>0</v>
+      </c>
+      <c r="AD311">
+        <v>0</v>
+      </c>
+      <c r="AE311">
+        <v>0</v>
+      </c>
+      <c r="AF311">
+        <v>0</v>
+      </c>
+      <c r="AG311">
+        <v>1.57</v>
+      </c>
+      <c r="AH311">
+        <v>2.35</v>
+      </c>
+      <c r="AI311">
+        <v>1.5</v>
+      </c>
+      <c r="AJ311">
+        <v>2.5</v>
+      </c>
+      <c r="AK311">
+        <v>0</v>
+      </c>
+      <c r="AL311">
+        <v>0</v>
+      </c>
+      <c r="AM311">
+        <v>0</v>
+      </c>
+      <c r="AN311">
+        <v>1.53</v>
+      </c>
+      <c r="AO311">
+        <v>1.2</v>
+      </c>
+      <c r="AP311">
+        <v>1.63</v>
+      </c>
+      <c r="AQ311">
+        <v>1.13</v>
+      </c>
+      <c r="AR311">
+        <v>1.82</v>
+      </c>
+      <c r="AS311">
+        <v>1.77</v>
+      </c>
+      <c r="AT311">
+        <v>3.59</v>
+      </c>
+      <c r="AU311">
+        <v>6</v>
+      </c>
+      <c r="AV311">
+        <v>5</v>
+      </c>
+      <c r="AW311">
+        <v>7</v>
+      </c>
+      <c r="AX311">
+        <v>7</v>
+      </c>
+      <c r="AY311">
+        <v>13</v>
+      </c>
+      <c r="AZ311">
+        <v>12</v>
+      </c>
+      <c r="BA311">
+        <v>5</v>
+      </c>
+      <c r="BB311">
+        <v>0</v>
+      </c>
+      <c r="BC311">
+        <v>5</v>
+      </c>
+      <c r="BD311">
+        <v>0</v>
+      </c>
+      <c r="BE311">
+        <v>0</v>
+      </c>
+      <c r="BF311">
+        <v>0</v>
+      </c>
+      <c r="BG311">
+        <v>0</v>
+      </c>
+      <c r="BH311">
+        <v>0</v>
+      </c>
+      <c r="BI311">
+        <v>0</v>
+      </c>
+      <c r="BJ311">
+        <v>0</v>
+      </c>
+      <c r="BK311">
+        <v>0</v>
+      </c>
+      <c r="BL311">
+        <v>0</v>
+      </c>
+      <c r="BM311">
+        <v>0</v>
+      </c>
+      <c r="BN311">
+        <v>0</v>
+      </c>
+      <c r="BO311">
+        <v>0</v>
+      </c>
+      <c r="BP311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:68">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>7465741</v>
+      </c>
+      <c r="C312" t="s">
+        <v>68</v>
+      </c>
+      <c r="D312" t="s">
+        <v>69</v>
+      </c>
+      <c r="E312" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F312">
+        <v>32</v>
+      </c>
+      <c r="G312" t="s">
+        <v>70</v>
+      </c>
+      <c r="H312" t="s">
+        <v>72</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+      <c r="J312">
+        <v>1</v>
+      </c>
+      <c r="K312">
+        <v>2</v>
+      </c>
+      <c r="L312">
+        <v>2</v>
+      </c>
+      <c r="M312">
+        <v>2</v>
+      </c>
+      <c r="N312">
+        <v>4</v>
+      </c>
+      <c r="O312" t="s">
+        <v>299</v>
+      </c>
+      <c r="P312" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q312">
+        <v>2.88</v>
+      </c>
+      <c r="R312">
+        <v>2.3</v>
+      </c>
+      <c r="S312">
+        <v>3.4</v>
+      </c>
+      <c r="T312">
+        <v>1.33</v>
+      </c>
+      <c r="U312">
+        <v>3.25</v>
+      </c>
+      <c r="V312">
+        <v>2.63</v>
+      </c>
+      <c r="W312">
+        <v>1.44</v>
+      </c>
+      <c r="X312">
+        <v>6.5</v>
+      </c>
+      <c r="Y312">
+        <v>1.11</v>
+      </c>
+      <c r="Z312">
+        <v>2.2</v>
+      </c>
+      <c r="AA312">
+        <v>3.5</v>
+      </c>
+      <c r="AB312">
+        <v>2.88</v>
+      </c>
+      <c r="AC312">
+        <v>0</v>
+      </c>
+      <c r="AD312">
+        <v>0</v>
+      </c>
+      <c r="AE312">
+        <v>0</v>
+      </c>
+      <c r="AF312">
+        <v>0</v>
+      </c>
+      <c r="AG312">
+        <v>1.7</v>
+      </c>
+      <c r="AH312">
+        <v>2.1</v>
+      </c>
+      <c r="AI312">
+        <v>1.57</v>
+      </c>
+      <c r="AJ312">
+        <v>2.25</v>
+      </c>
+      <c r="AK312">
+        <v>0</v>
+      </c>
+      <c r="AL312">
+        <v>0</v>
+      </c>
+      <c r="AM312">
+        <v>0</v>
+      </c>
+      <c r="AN312">
+        <v>1.07</v>
+      </c>
+      <c r="AO312">
+        <v>1.2</v>
+      </c>
+      <c r="AP312">
+        <v>1.06</v>
+      </c>
+      <c r="AQ312">
+        <v>1.19</v>
+      </c>
+      <c r="AR312">
+        <v>1.39</v>
+      </c>
+      <c r="AS312">
+        <v>1.39</v>
+      </c>
+      <c r="AT312">
+        <v>2.78</v>
+      </c>
+      <c r="AU312">
+        <v>5</v>
+      </c>
+      <c r="AV312">
+        <v>7</v>
+      </c>
+      <c r="AW312">
+        <v>6</v>
+      </c>
+      <c r="AX312">
+        <v>8</v>
+      </c>
+      <c r="AY312">
+        <v>11</v>
+      </c>
+      <c r="AZ312">
+        <v>15</v>
+      </c>
+      <c r="BA312">
+        <v>3</v>
+      </c>
+      <c r="BB312">
+        <v>4</v>
+      </c>
+      <c r="BC312">
+        <v>7</v>
+      </c>
+      <c r="BD312">
+        <v>0</v>
+      </c>
+      <c r="BE312">
+        <v>0</v>
+      </c>
+      <c r="BF312">
+        <v>0</v>
+      </c>
+      <c r="BG312">
+        <v>0</v>
+      </c>
+      <c r="BH312">
+        <v>0</v>
+      </c>
+      <c r="BI312">
+        <v>0</v>
+      </c>
+      <c r="BJ312">
+        <v>0</v>
+      </c>
+      <c r="BK312">
+        <v>0</v>
+      </c>
+      <c r="BL312">
+        <v>0</v>
+      </c>
+      <c r="BM312">
+        <v>0</v>
+      </c>
+      <c r="BN312">
+        <v>0</v>
+      </c>
+      <c r="BO312">
+        <v>0</v>
+      </c>
+      <c r="BP312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:68">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>7465740</v>
+      </c>
+      <c r="C313" t="s">
+        <v>68</v>
+      </c>
+      <c r="D313" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F313">
+        <v>32</v>
+      </c>
+      <c r="G313" t="s">
+        <v>83</v>
+      </c>
+      <c r="H313" t="s">
+        <v>84</v>
+      </c>
+      <c r="I313">
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>1</v>
+      </c>
+      <c r="L313">
+        <v>3</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
+      </c>
+      <c r="N313">
+        <v>3</v>
+      </c>
+      <c r="O313" t="s">
+        <v>300</v>
+      </c>
+      <c r="P313" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q313">
+        <v>1.57</v>
+      </c>
+      <c r="R313">
+        <v>3</v>
+      </c>
+      <c r="S313">
+        <v>9</v>
+      </c>
+      <c r="T313">
+        <v>1.22</v>
+      </c>
+      <c r="U313">
+        <v>4</v>
+      </c>
+      <c r="V313">
+        <v>2</v>
+      </c>
+      <c r="W313">
+        <v>1.73</v>
+      </c>
+      <c r="X313">
+        <v>4.33</v>
+      </c>
+      <c r="Y313">
+        <v>1.2</v>
+      </c>
+      <c r="Z313">
+        <v>1.2</v>
+      </c>
+      <c r="AA313">
+        <v>7</v>
+      </c>
+      <c r="AB313">
+        <v>9</v>
+      </c>
+      <c r="AC313">
+        <v>0</v>
+      </c>
+      <c r="AD313">
+        <v>0</v>
+      </c>
+      <c r="AE313">
+        <v>0</v>
+      </c>
+      <c r="AF313">
+        <v>0</v>
+      </c>
+      <c r="AG313">
+        <v>1.36</v>
+      </c>
+      <c r="AH313">
+        <v>3.1</v>
+      </c>
+      <c r="AI313">
+        <v>1.83</v>
+      </c>
+      <c r="AJ313">
+        <v>1.83</v>
+      </c>
+      <c r="AK313">
+        <v>0</v>
+      </c>
+      <c r="AL313">
+        <v>0</v>
+      </c>
+      <c r="AM313">
+        <v>0</v>
+      </c>
+      <c r="AN313">
+        <v>2.2</v>
+      </c>
+      <c r="AO313">
+        <v>0.53</v>
+      </c>
+      <c r="AP313">
+        <v>2.25</v>
+      </c>
+      <c r="AQ313">
+        <v>0.5</v>
+      </c>
+      <c r="AR313">
+        <v>1.93</v>
+      </c>
+      <c r="AS313">
+        <v>1.21</v>
+      </c>
+      <c r="AT313">
+        <v>3.14</v>
+      </c>
+      <c r="AU313">
+        <v>6</v>
+      </c>
+      <c r="AV313">
+        <v>0</v>
+      </c>
+      <c r="AW313">
+        <v>22</v>
+      </c>
+      <c r="AX313">
+        <v>6</v>
+      </c>
+      <c r="AY313">
+        <v>29</v>
+      </c>
+      <c r="AZ313">
+        <v>6</v>
+      </c>
+      <c r="BA313">
+        <v>7</v>
+      </c>
+      <c r="BB313">
+        <v>1</v>
+      </c>
+      <c r="BC313">
+        <v>8</v>
+      </c>
+      <c r="BD313">
+        <v>0</v>
+      </c>
+      <c r="BE313">
+        <v>0</v>
+      </c>
+      <c r="BF313">
+        <v>0</v>
+      </c>
+      <c r="BG313">
+        <v>0</v>
+      </c>
+      <c r="BH313">
+        <v>0</v>
+      </c>
+      <c r="BI313">
+        <v>0</v>
+      </c>
+      <c r="BJ313">
+        <v>0</v>
+      </c>
+      <c r="BK313">
+        <v>0</v>
+      </c>
+      <c r="BL313">
+        <v>0</v>
+      </c>
+      <c r="BM313">
+        <v>0</v>
+      </c>
+      <c r="BN313">
+        <v>0</v>
+      </c>
+      <c r="BO313">
+        <v>0</v>
+      </c>
+      <c r="BP313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:68">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>7465742</v>
+      </c>
+      <c r="C314" t="s">
+        <v>68</v>
+      </c>
+      <c r="D314" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="2">
+        <v>45744.66666666666</v>
+      </c>
+      <c r="F314">
+        <v>32</v>
+      </c>
+      <c r="G314" t="s">
+        <v>73</v>
+      </c>
+      <c r="H314" t="s">
+        <v>71</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>0</v>
+      </c>
+      <c r="L314">
+        <v>1</v>
+      </c>
+      <c r="M314">
+        <v>2</v>
+      </c>
+      <c r="N314">
+        <v>3</v>
+      </c>
+      <c r="O314" t="s">
+        <v>301</v>
+      </c>
+      <c r="P314" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q314">
+        <v>3.5</v>
+      </c>
+      <c r="R314">
+        <v>2.3</v>
+      </c>
+      <c r="S314">
+        <v>2.88</v>
+      </c>
+      <c r="T314">
+        <v>1.33</v>
+      </c>
+      <c r="U314">
+        <v>3.25</v>
+      </c>
+      <c r="V314">
+        <v>2.63</v>
+      </c>
+      <c r="W314">
+        <v>1.44</v>
+      </c>
+      <c r="X314">
+        <v>6.5</v>
+      </c>
+      <c r="Y314">
+        <v>1.11</v>
+      </c>
+      <c r="Z314">
+        <v>3</v>
+      </c>
+      <c r="AA314">
+        <v>3.4</v>
+      </c>
+      <c r="AB314">
+        <v>2.15</v>
+      </c>
+      <c r="AC314">
+        <v>0</v>
+      </c>
+      <c r="AD314">
+        <v>0</v>
+      </c>
+      <c r="AE314">
+        <v>0</v>
+      </c>
+      <c r="AF314">
+        <v>0</v>
+      </c>
+      <c r="AG314">
+        <v>1.7</v>
+      </c>
+      <c r="AH314">
+        <v>2.1</v>
+      </c>
+      <c r="AI314">
+        <v>1.57</v>
+      </c>
+      <c r="AJ314">
+        <v>2.25</v>
+      </c>
+      <c r="AK314">
+        <v>0</v>
+      </c>
+      <c r="AL314">
+        <v>0</v>
+      </c>
+      <c r="AM314">
+        <v>0</v>
+      </c>
+      <c r="AN314">
+        <v>1.67</v>
+      </c>
+      <c r="AO314">
+        <v>1.87</v>
+      </c>
+      <c r="AP314">
+        <v>1.56</v>
+      </c>
+      <c r="AQ314">
+        <v>1.94</v>
+      </c>
+      <c r="AR314">
+        <v>1.6</v>
+      </c>
+      <c r="AS314">
+        <v>1.58</v>
+      </c>
+      <c r="AT314">
+        <v>3.18</v>
+      </c>
+      <c r="AU314">
+        <v>5</v>
+      </c>
+      <c r="AV314">
+        <v>6</v>
+      </c>
+      <c r="AW314">
+        <v>13</v>
+      </c>
+      <c r="AX314">
+        <v>5</v>
+      </c>
+      <c r="AY314">
+        <v>18</v>
+      </c>
+      <c r="AZ314">
+        <v>11</v>
+      </c>
+      <c r="BA314">
+        <v>8</v>
+      </c>
+      <c r="BB314">
+        <v>2</v>
+      </c>
+      <c r="BC314">
+        <v>10</v>
+      </c>
+      <c r="BD314">
+        <v>0</v>
+      </c>
+      <c r="BE314">
+        <v>0</v>
+      </c>
+      <c r="BF314">
+        <v>0</v>
+      </c>
+      <c r="BG314">
+        <v>0</v>
+      </c>
+      <c r="BH314">
+        <v>0</v>
+      </c>
+      <c r="BI314">
+        <v>0</v>
+      </c>
+      <c r="BJ314">
+        <v>0</v>
+      </c>
+      <c r="BK314">
+        <v>0</v>
+      </c>
+      <c r="BL314">
+        <v>0</v>
+      </c>
+      <c r="BM314">
+        <v>0</v>
+      </c>
+      <c r="BN314">
+        <v>0</v>
+      </c>
+      <c r="BO314">
+        <v>0</v>
+      </c>
+      <c r="BP314">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="445">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1347,6 +1347,9 @@
   <si>
     <t>['50', '64']</t>
   </si>
+  <si>
+    <t>['3', '45+1', '71', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1707,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP314"/>
+  <dimension ref="A1:BP315"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3280,7 +3283,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ8">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4513,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ14">
         <v>0.53</v>
@@ -9048,7 +9051,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ36">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -10075,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
         <v>1.13</v>
@@ -12962,7 +12965,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -15431,7 +15434,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ67">
         <v>0.5600000000000001</v>
@@ -16464,7 +16467,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ72">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -19139,7 +19142,7 @@
         <v>1.25</v>
       </c>
       <c r="AP85">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ85">
         <v>1.44</v>
@@ -20790,7 +20793,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ93">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -25319,7 +25322,7 @@
         <v>1.8</v>
       </c>
       <c r="AP115">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ115">
         <v>0.75</v>
@@ -26970,7 +26973,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ123">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -30469,7 +30472,7 @@
         <v>1.71</v>
       </c>
       <c r="AP140">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ140">
         <v>1.13</v>
@@ -30884,7 +30887,7 @@
         <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -34383,7 +34386,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -35619,7 +35622,7 @@
         <v>1.75</v>
       </c>
       <c r="AP165">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165">
         <v>1.87</v>
@@ -36446,7 +36449,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ169">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -39327,7 +39330,7 @@
         <v>1.44</v>
       </c>
       <c r="AP183">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ183">
         <v>1.56</v>
@@ -39742,7 +39745,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ185">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -44068,7 +44071,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ206">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -46125,7 +46128,7 @@
         <v>2.2</v>
       </c>
       <c r="AP216">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ216">
         <v>2</v>
@@ -47155,7 +47158,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP221">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ221">
         <v>0.5</v>
@@ -48806,7 +48809,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ229">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR229">
         <v>1.56</v>
@@ -50866,7 +50869,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ239">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR239">
         <v>1.78</v>
@@ -51481,7 +51484,7 @@
         <v>1.17</v>
       </c>
       <c r="AP242">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ242">
         <v>1.31</v>
@@ -55189,7 +55192,7 @@
         <v>1.42</v>
       </c>
       <c r="AP260">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ260">
         <v>1.2</v>
@@ -57046,7 +57049,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ269">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR269">
         <v>1.77</v>
@@ -59309,7 +59312,7 @@
         <v>1</v>
       </c>
       <c r="AP280">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ280">
         <v>0.93</v>
@@ -62193,7 +62196,7 @@
         <v>1.29</v>
       </c>
       <c r="AP294">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AQ294">
         <v>1.19</v>
@@ -63020,7 +63023,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ298">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AR298">
         <v>1.65</v>
@@ -66391,6 +66394,212 @@
         <v>0</v>
       </c>
       <c r="BP314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:68">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>7465744</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="2">
+        <v>45745.52083333334</v>
+      </c>
+      <c r="F315">
+        <v>32</v>
+      </c>
+      <c r="G315" t="s">
+        <v>82</v>
+      </c>
+      <c r="H315" t="s">
+        <v>80</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>2</v>
+      </c>
+      <c r="K315">
+        <v>2</v>
+      </c>
+      <c r="L315">
+        <v>1</v>
+      </c>
+      <c r="M315">
+        <v>4</v>
+      </c>
+      <c r="N315">
+        <v>5</v>
+      </c>
+      <c r="O315" t="s">
+        <v>102</v>
+      </c>
+      <c r="P315" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q315">
+        <v>2.38</v>
+      </c>
+      <c r="R315">
+        <v>2.4</v>
+      </c>
+      <c r="S315">
+        <v>4.33</v>
+      </c>
+      <c r="T315">
+        <v>1.29</v>
+      </c>
+      <c r="U315">
+        <v>3.5</v>
+      </c>
+      <c r="V315">
+        <v>2.38</v>
+      </c>
+      <c r="W315">
+        <v>1.53</v>
+      </c>
+      <c r="X315">
+        <v>5.5</v>
+      </c>
+      <c r="Y315">
+        <v>1.14</v>
+      </c>
+      <c r="Z315">
+        <v>1.75</v>
+      </c>
+      <c r="AA315">
+        <v>3.6</v>
+      </c>
+      <c r="AB315">
+        <v>4</v>
+      </c>
+      <c r="AC315">
+        <v>0</v>
+      </c>
+      <c r="AD315">
+        <v>0</v>
+      </c>
+      <c r="AE315">
+        <v>0</v>
+      </c>
+      <c r="AF315">
+        <v>0</v>
+      </c>
+      <c r="AG315">
+        <v>1.6</v>
+      </c>
+      <c r="AH315">
+        <v>2.3</v>
+      </c>
+      <c r="AI315">
+        <v>1.57</v>
+      </c>
+      <c r="AJ315">
+        <v>2.25</v>
+      </c>
+      <c r="AK315">
+        <v>0</v>
+      </c>
+      <c r="AL315">
+        <v>0</v>
+      </c>
+      <c r="AM315">
+        <v>0</v>
+      </c>
+      <c r="AN315">
+        <v>1.87</v>
+      </c>
+      <c r="AO315">
+        <v>1.14</v>
+      </c>
+      <c r="AP315">
+        <v>1.75</v>
+      </c>
+      <c r="AQ315">
+        <v>1.27</v>
+      </c>
+      <c r="AR315">
+        <v>1.96</v>
+      </c>
+      <c r="AS315">
+        <v>1.32</v>
+      </c>
+      <c r="AT315">
+        <v>3.28</v>
+      </c>
+      <c r="AU315">
+        <v>8</v>
+      </c>
+      <c r="AV315">
+        <v>7</v>
+      </c>
+      <c r="AW315">
+        <v>7</v>
+      </c>
+      <c r="AX315">
+        <v>9</v>
+      </c>
+      <c r="AY315">
+        <v>16</v>
+      </c>
+      <c r="AZ315">
+        <v>16</v>
+      </c>
+      <c r="BA315">
+        <v>6</v>
+      </c>
+      <c r="BB315">
+        <v>4</v>
+      </c>
+      <c r="BC315">
+        <v>10</v>
+      </c>
+      <c r="BD315">
+        <v>0</v>
+      </c>
+      <c r="BE315">
+        <v>0</v>
+      </c>
+      <c r="BF315">
+        <v>0</v>
+      </c>
+      <c r="BG315">
+        <v>0</v>
+      </c>
+      <c r="BH315">
+        <v>0</v>
+      </c>
+      <c r="BI315">
+        <v>0</v>
+      </c>
+      <c r="BJ315">
+        <v>0</v>
+      </c>
+      <c r="BK315">
+        <v>0</v>
+      </c>
+      <c r="BL315">
+        <v>0</v>
+      </c>
+      <c r="BM315">
+        <v>0</v>
+      </c>
+      <c r="BN315">
+        <v>0</v>
+      </c>
+      <c r="BO315">
+        <v>0</v>
+      </c>
+      <c r="BP315">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="446">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -922,6 +922,9 @@
     <t>['82']</t>
   </si>
   <si>
+    <t>['9', '90+2']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1710,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP315"/>
+  <dimension ref="A1:BP316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2172,7 +2175,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2253,7 +2256,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2378,7 +2381,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2790,7 +2793,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2996,7 +2999,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3202,7 +3205,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3280,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8">
         <v>1.27</v>
@@ -3408,7 +3411,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3820,7 +3823,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4232,7 +4235,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4850,7 +4853,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5674,7 +5677,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6704,7 +6707,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6910,7 +6913,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6988,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ26">
         <v>1.87</v>
@@ -7116,7 +7119,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7528,7 +7531,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7815,7 +7818,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ30">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR30">
         <v>2.2</v>
@@ -7940,7 +7943,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8558,7 +8561,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8764,7 +8767,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9382,7 +9385,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9460,7 +9463,7 @@
         <v>0.5</v>
       </c>
       <c r="AP38">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ38">
         <v>1.44</v>
@@ -9588,7 +9591,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -10000,7 +10003,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10824,7 +10827,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11030,7 +11033,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11442,7 +11445,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11729,7 +11732,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ49">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR49">
         <v>1.39</v>
@@ -11854,7 +11857,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12060,7 +12063,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12266,7 +12269,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -13090,7 +13093,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13502,7 +13505,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13995,7 +13998,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ60">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR60">
         <v>1.64</v>
@@ -14120,7 +14123,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14326,7 +14329,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14532,7 +14535,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15022,7 +15025,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ65">
         <v>1.13</v>
@@ -15150,7 +15153,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15562,7 +15565,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15768,7 +15771,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15974,7 +15977,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16180,7 +16183,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16386,7 +16389,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16592,7 +16595,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16798,7 +16801,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -17004,7 +17007,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17082,7 +17085,7 @@
         <v>0.67</v>
       </c>
       <c r="AP75">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -17622,7 +17625,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17828,7 +17831,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18115,7 +18118,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ80">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR80">
         <v>1.68</v>
@@ -18240,7 +18243,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18652,7 +18655,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18858,7 +18861,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19476,7 +19479,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -20094,7 +20097,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20506,7 +20509,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20918,7 +20921,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21124,7 +21127,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21205,7 +21208,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ95">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR95">
         <v>1.66</v>
@@ -21330,7 +21333,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21536,7 +21539,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21948,7 +21951,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22360,7 +22363,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22566,7 +22569,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22850,7 +22853,7 @@
         <v>1.2</v>
       </c>
       <c r="AP103">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ103">
         <v>1.06</v>
@@ -22978,7 +22981,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -24214,7 +24217,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24420,7 +24423,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24626,7 +24629,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24704,7 +24707,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ112">
         <v>1.13</v>
@@ -25244,7 +25247,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25450,7 +25453,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25656,7 +25659,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25862,7 +25865,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26068,7 +26071,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26274,7 +26277,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26480,7 +26483,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26686,7 +26689,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26892,7 +26895,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27098,7 +27101,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27179,7 +27182,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ124">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR124">
         <v>1.75</v>
@@ -27304,7 +27307,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27922,7 +27925,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28334,7 +28337,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28540,7 +28543,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29570,7 +29573,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -30060,7 +30063,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -31299,7 +31302,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ144">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR144">
         <v>1.68</v>
@@ -31424,7 +31427,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31630,7 +31633,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31836,7 +31839,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32042,7 +32045,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32454,7 +32457,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32660,7 +32663,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33072,7 +33075,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33278,7 +33281,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33484,7 +33487,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34514,7 +34517,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34926,7 +34929,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35004,7 +35007,7 @@
         <v>2.57</v>
       </c>
       <c r="AP162">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ162">
         <v>1.94</v>
@@ -35750,7 +35753,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36574,7 +36577,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36655,7 +36658,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ170">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR170">
         <v>1.8</v>
@@ -36780,7 +36783,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37192,7 +37195,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -38016,7 +38019,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38222,7 +38225,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38634,7 +38637,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38840,7 +38843,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39333,7 +39336,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ183">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR183">
         <v>1.89</v>
@@ -39458,7 +39461,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39664,7 +39667,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39870,7 +39873,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40360,7 +40363,7 @@
         <v>0.78</v>
       </c>
       <c r="AP188">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ188">
         <v>0.5600000000000001</v>
@@ -40488,7 +40491,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41106,7 +41109,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41312,7 +41315,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41518,7 +41521,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41724,7 +41727,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41930,7 +41933,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42548,7 +42551,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42832,7 +42835,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP200">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ200">
         <v>0.53</v>
@@ -42960,7 +42963,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43247,7 +43250,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ202">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR202">
         <v>1.76</v>
@@ -43578,7 +43581,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43990,7 +43993,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44196,7 +44199,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44608,7 +44611,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -45020,7 +45023,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45510,7 +45513,7 @@
         <v>1.6</v>
       </c>
       <c r="AP213">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ213">
         <v>1.19</v>
@@ -45844,7 +45847,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46462,7 +46465,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46668,7 +46671,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46874,7 +46877,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46955,7 +46958,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ220">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR220">
         <v>1.73</v>
@@ -48728,7 +48731,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49346,7 +49349,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49630,7 +49633,7 @@
         <v>1.67</v>
       </c>
       <c r="AP233">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ233">
         <v>1.5</v>
@@ -49964,7 +49967,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50170,7 +50173,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50582,7 +50585,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -51406,7 +51409,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51612,7 +51615,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51818,7 +51821,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51899,7 +51902,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ244">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR244">
         <v>1.44</v>
@@ -52436,7 +52439,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52848,7 +52851,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -53338,7 +53341,7 @@
         <v>0.75</v>
       </c>
       <c r="AP251">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ251">
         <v>0.75</v>
@@ -54084,7 +54087,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -55320,7 +55323,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55526,7 +55529,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55732,7 +55735,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55938,7 +55941,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56144,7 +56147,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56350,7 +56353,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56556,7 +56559,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56637,7 +56640,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ267">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR267">
         <v>1.52</v>
@@ -56762,7 +56765,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -57174,7 +57177,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57380,7 +57383,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57792,7 +57795,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58204,7 +58207,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58282,7 +58285,7 @@
         <v>1.38</v>
       </c>
       <c r="AP275">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ275">
         <v>1.2</v>
@@ -58410,7 +58413,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58616,7 +58619,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58822,7 +58825,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -59028,7 +59031,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59234,7 +59237,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59440,7 +59443,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59727,7 +59730,7 @@
         <v>2</v>
       </c>
       <c r="AQ282">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR282">
         <v>1.78</v>
@@ -60470,7 +60473,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60676,7 +60679,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61375,7 +61378,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ290">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR290">
         <v>1.8</v>
@@ -61500,7 +61503,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61912,7 +61915,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62118,7 +62121,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62530,7 +62533,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62608,7 +62611,7 @@
         <v>1.07</v>
       </c>
       <c r="AP296">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AQ296">
         <v>1.31</v>
@@ -62736,7 +62739,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -63148,7 +63151,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -64590,7 +64593,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -65208,7 +65211,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65620,7 +65623,7 @@
         <v>298</v>
       </c>
       <c r="P311" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q311">
         <v>2.4</v>
@@ -65826,7 +65829,7 @@
         <v>299</v>
       </c>
       <c r="P312" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q312">
         <v>2.88</v>
@@ -66238,7 +66241,7 @@
         <v>301</v>
       </c>
       <c r="P314" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q314">
         <v>3.5</v>
@@ -66444,7 +66447,7 @@
         <v>102</v>
       </c>
       <c r="P315" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q315">
         <v>2.38</v>
@@ -66600,6 +66603,212 @@
         <v>0</v>
       </c>
       <c r="BP315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:68">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>7465746</v>
+      </c>
+      <c r="C316" t="s">
+        <v>68</v>
+      </c>
+      <c r="D316" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="2">
+        <v>45746.48958333334</v>
+      </c>
+      <c r="F316">
+        <v>32</v>
+      </c>
+      <c r="G316" t="s">
+        <v>76</v>
+      </c>
+      <c r="H316" t="s">
+        <v>86</v>
+      </c>
+      <c r="I316">
+        <v>1</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>1</v>
+      </c>
+      <c r="L316">
+        <v>2</v>
+      </c>
+      <c r="M316">
+        <v>1</v>
+      </c>
+      <c r="N316">
+        <v>3</v>
+      </c>
+      <c r="O316" t="s">
+        <v>302</v>
+      </c>
+      <c r="P316" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q316">
+        <v>2.2</v>
+      </c>
+      <c r="R316">
+        <v>2.5</v>
+      </c>
+      <c r="S316">
+        <v>4.5</v>
+      </c>
+      <c r="T316">
+        <v>1.29</v>
+      </c>
+      <c r="U316">
+        <v>3.5</v>
+      </c>
+      <c r="V316">
+        <v>2.25</v>
+      </c>
+      <c r="W316">
+        <v>1.57</v>
+      </c>
+      <c r="X316">
+        <v>5.5</v>
+      </c>
+      <c r="Y316">
+        <v>1.14</v>
+      </c>
+      <c r="Z316">
+        <v>1.65</v>
+      </c>
+      <c r="AA316">
+        <v>3.9</v>
+      </c>
+      <c r="AB316">
+        <v>4.33</v>
+      </c>
+      <c r="AC316">
+        <v>0</v>
+      </c>
+      <c r="AD316">
+        <v>0</v>
+      </c>
+      <c r="AE316">
+        <v>0</v>
+      </c>
+      <c r="AF316">
+        <v>0</v>
+      </c>
+      <c r="AG316">
+        <v>1.53</v>
+      </c>
+      <c r="AH316">
+        <v>2.4</v>
+      </c>
+      <c r="AI316">
+        <v>1.57</v>
+      </c>
+      <c r="AJ316">
+        <v>2.25</v>
+      </c>
+      <c r="AK316">
+        <v>0</v>
+      </c>
+      <c r="AL316">
+        <v>0</v>
+      </c>
+      <c r="AM316">
+        <v>0</v>
+      </c>
+      <c r="AN316">
+        <v>2.06</v>
+      </c>
+      <c r="AO316">
+        <v>1.56</v>
+      </c>
+      <c r="AP316">
+        <v>2.12</v>
+      </c>
+      <c r="AQ316">
+        <v>1.47</v>
+      </c>
+      <c r="AR316">
+        <v>1.83</v>
+      </c>
+      <c r="AS316">
+        <v>1.28</v>
+      </c>
+      <c r="AT316">
+        <v>3.11</v>
+      </c>
+      <c r="AU316">
+        <v>4</v>
+      </c>
+      <c r="AV316">
+        <v>6</v>
+      </c>
+      <c r="AW316">
+        <v>9</v>
+      </c>
+      <c r="AX316">
+        <v>7</v>
+      </c>
+      <c r="AY316">
+        <v>13</v>
+      </c>
+      <c r="AZ316">
+        <v>13</v>
+      </c>
+      <c r="BA316">
+        <v>4</v>
+      </c>
+      <c r="BB316">
+        <v>4</v>
+      </c>
+      <c r="BC316">
+        <v>8</v>
+      </c>
+      <c r="BD316">
+        <v>0</v>
+      </c>
+      <c r="BE316">
+        <v>0</v>
+      </c>
+      <c r="BF316">
+        <v>0</v>
+      </c>
+      <c r="BG316">
+        <v>0</v>
+      </c>
+      <c r="BH316">
+        <v>0</v>
+      </c>
+      <c r="BI316">
+        <v>0</v>
+      </c>
+      <c r="BJ316">
+        <v>0</v>
+      </c>
+      <c r="BK316">
+        <v>0</v>
+      </c>
+      <c r="BL316">
+        <v>0</v>
+      </c>
+      <c r="BM316">
+        <v>0</v>
+      </c>
+      <c r="BN316">
+        <v>0</v>
+      </c>
+      <c r="BO316">
+        <v>0</v>
+      </c>
+      <c r="BP316">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="449">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -925,6 +925,9 @@
     <t>['9', '90+2']</t>
   </si>
   <si>
+    <t>['26', '87']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1353,6 +1356,12 @@
   <si>
     <t>['3', '45+1', '71', '90']</t>
   </si>
+  <si>
+    <t>['37', '63']</t>
+  </si>
+  <si>
+    <t>['2', '15', '42', '56']</t>
+  </si>
 </sst>
 </file>
 
@@ -1713,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP316"/>
+  <dimension ref="A1:BP319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2050,7 +2059,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ2">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2175,7 +2184,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2381,7 +2390,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2793,7 +2802,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2999,7 +3008,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3205,7 +3214,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3411,7 +3420,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3492,7 +3501,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ9">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3695,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ10">
         <v>1.06</v>
@@ -3823,7 +3832,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3901,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ11">
         <v>0.75</v>
@@ -4235,7 +4244,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4522,7 +4531,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ14">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4853,7 +4862,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5677,7 +5686,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5961,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ21">
         <v>0.5600000000000001</v>
@@ -6707,7 +6716,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6913,7 +6922,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -6994,7 +7003,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ26">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR26">
         <v>1.18</v>
@@ -7119,7 +7128,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7531,7 +7540,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7815,7 +7824,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30">
         <v>1.47</v>
@@ -7943,7 +7952,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8021,7 +8030,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ31">
         <v>1.13</v>
@@ -8561,7 +8570,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8767,7 +8776,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9385,7 +9394,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9591,7 +9600,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9669,10 +9678,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ39">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR39">
         <v>2.22</v>
@@ -9878,7 +9887,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ40">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR40">
         <v>1.64</v>
@@ -10003,7 +10012,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10827,7 +10836,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11033,7 +11042,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11317,7 +11326,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11445,7 +11454,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11526,7 +11535,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ48">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR48">
         <v>1.9</v>
@@ -11857,7 +11866,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12063,7 +12072,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12269,7 +12278,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -13093,7 +13102,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13380,7 +13389,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ57">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR57">
         <v>1.47</v>
@@ -13505,7 +13514,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13586,7 +13595,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ58">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR58">
         <v>1.06</v>
@@ -13789,7 +13798,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ59">
         <v>1.67</v>
@@ -14123,7 +14132,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14201,7 +14210,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ61">
         <v>1.31</v>
@@ -14329,7 +14338,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14535,7 +14544,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14616,7 +14625,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ63">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR63">
         <v>1.46</v>
@@ -15153,7 +15162,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15565,7 +15574,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15771,7 +15780,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15977,7 +15986,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16055,7 +16064,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70">
         <v>1.13</v>
@@ -16183,7 +16192,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16389,7 +16398,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16595,7 +16604,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16676,7 +16685,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ73">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR73">
         <v>1.77</v>
@@ -16801,7 +16810,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -17007,7 +17016,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17500,7 +17509,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR77">
         <v>1.86</v>
@@ -17625,7 +17634,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17831,7 +17840,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18115,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ80">
         <v>1.47</v>
@@ -18243,7 +18252,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18321,7 +18330,7 @@
         <v>2.33</v>
       </c>
       <c r="AP81">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ81">
         <v>1.19</v>
@@ -18655,7 +18664,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18736,7 +18745,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ83">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR83">
         <v>1.68</v>
@@ -18861,7 +18870,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19479,7 +19488,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19557,7 +19566,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87">
         <v>1.5</v>
@@ -20097,7 +20106,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20509,7 +20518,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20921,7 +20930,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -20999,7 +21008,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ94">
         <v>1.19</v>
@@ -21127,7 +21136,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21333,7 +21342,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21539,7 +21548,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21620,7 +21629,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ97">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -21823,7 +21832,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ98">
         <v>0.5</v>
@@ -21951,7 +21960,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22363,7 +22372,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22569,7 +22578,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22981,7 +22990,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23059,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ104">
         <v>1.44</v>
@@ -23265,7 +23274,7 @@
         <v>1.25</v>
       </c>
       <c r="AP105">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ105">
         <v>1.67</v>
@@ -23886,7 +23895,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ108">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR108">
         <v>1.82</v>
@@ -24217,7 +24226,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24423,7 +24432,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24504,7 +24513,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ111">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR111">
         <v>1.8</v>
@@ -24629,7 +24638,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25247,7 +25256,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25453,7 +25462,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25659,7 +25668,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25865,7 +25874,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -25946,7 +25955,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ118">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR118">
         <v>1.66</v>
@@ -26071,7 +26080,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26277,7 +26286,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26483,7 +26492,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26689,7 +26698,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26767,7 +26776,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ122">
         <v>2</v>
@@ -26895,7 +26904,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26973,7 +26982,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ123">
         <v>1.27</v>
@@ -27101,7 +27110,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27307,7 +27316,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27594,7 +27603,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ126">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR126">
         <v>1.62</v>
@@ -27925,7 +27934,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28006,7 +28015,7 @@
         <v>2</v>
       </c>
       <c r="AQ128">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -28337,7 +28346,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28543,7 +28552,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28621,7 +28630,7 @@
         <v>2.4</v>
       </c>
       <c r="AP131">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ131">
         <v>1.94</v>
@@ -29242,7 +29251,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ134">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR134">
         <v>1.22</v>
@@ -29573,7 +29582,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -31427,7 +31436,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31505,10 +31514,10 @@
         <v>1.57</v>
       </c>
       <c r="AP145">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ145">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR145">
         <v>1.6</v>
@@ -31633,7 +31642,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31839,7 +31848,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32045,7 +32054,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32329,7 +32338,7 @@
         <v>1.5</v>
       </c>
       <c r="AP149">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ149">
         <v>1.13</v>
@@ -32457,7 +32466,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32663,7 +32672,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32950,7 +32959,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ152">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR152">
         <v>1.79</v>
@@ -33075,7 +33084,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33153,7 +33162,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ153">
         <v>1.67</v>
@@ -33281,7 +33290,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33359,7 +33368,7 @@
         <v>1.43</v>
       </c>
       <c r="AP154">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ154">
         <v>1.31</v>
@@ -33487,7 +33496,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33568,7 +33577,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ155">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR155">
         <v>2.01</v>
@@ -34517,7 +34526,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34598,7 +34607,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ160">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR160">
         <v>1.85</v>
@@ -34929,7 +34938,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35628,7 +35637,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR165">
         <v>1.91</v>
@@ -35753,7 +35762,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36577,7 +36586,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36783,7 +36792,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36861,7 +36870,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ171">
         <v>0.5600000000000001</v>
@@ -37070,7 +37079,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ172">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR172">
         <v>1.65</v>
@@ -37195,7 +37204,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37894,7 +37903,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ176">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR176">
         <v>1.56</v>
@@ -38019,7 +38028,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38225,7 +38234,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38509,7 +38518,7 @@
         <v>1.25</v>
       </c>
       <c r="AP179">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ179">
         <v>1.13</v>
@@ -38637,7 +38646,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38843,7 +38852,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38921,7 +38930,7 @@
         <v>1.11</v>
       </c>
       <c r="AP181">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ181">
         <v>1.06</v>
@@ -39461,7 +39470,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39539,7 +39548,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ184">
         <v>1.94</v>
@@ -39667,7 +39676,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39873,7 +39882,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40160,7 +40169,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ187">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR187">
         <v>1.79</v>
@@ -40491,7 +40500,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41109,7 +41118,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41315,7 +41324,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41393,7 +41402,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41521,7 +41530,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41727,7 +41736,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41933,7 +41942,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42014,7 +42023,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ196">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR196">
         <v>1.66</v>
@@ -42551,7 +42560,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42838,7 +42847,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ200">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR200">
         <v>1.75</v>
@@ -42963,7 +42972,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43041,7 +43050,7 @@
         <v>1.3</v>
       </c>
       <c r="AP201">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ201">
         <v>1.06</v>
@@ -43581,7 +43590,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43662,7 +43671,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ204">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR204">
         <v>1.4</v>
@@ -43993,7 +44002,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44199,7 +44208,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44277,7 +44286,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ207">
         <v>0.75</v>
@@ -44611,7 +44620,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -45023,7 +45032,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45722,7 +45731,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ214">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR214">
         <v>1.73</v>
@@ -45847,7 +45856,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46337,7 +46346,7 @@
         <v>1.18</v>
       </c>
       <c r="AP217">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ217">
         <v>0.93</v>
@@ -46465,7 +46474,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46671,7 +46680,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46877,7 +46886,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47782,7 +47791,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ224">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR224">
         <v>1.74</v>
@@ -48731,7 +48740,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48809,7 +48818,7 @@
         <v>1.3</v>
       </c>
       <c r="AP229">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ229">
         <v>1.27</v>
@@ -49349,7 +49358,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49842,7 +49851,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ234">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR234">
         <v>1.77</v>
@@ -49967,7 +49976,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50173,7 +50182,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50585,7 +50594,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50869,7 +50878,7 @@
         <v>1.45</v>
       </c>
       <c r="AP239">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ239">
         <v>1.27</v>
@@ -51078,7 +51087,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ240">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR240">
         <v>1.82</v>
@@ -51284,7 +51293,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ241">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR241">
         <v>1.34</v>
@@ -51409,7 +51418,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51615,7 +51624,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51821,7 +51830,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52439,7 +52448,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52517,7 +52526,7 @@
         <v>2.08</v>
       </c>
       <c r="AP247">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ247">
         <v>2</v>
@@ -52851,7 +52860,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -52929,7 +52938,7 @@
         <v>1.42</v>
       </c>
       <c r="AP249">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ249">
         <v>1.44</v>
@@ -53962,7 +53971,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ254">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR254">
         <v>1.71</v>
@@ -54087,7 +54096,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54168,7 +54177,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ255">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR255">
         <v>1.7</v>
@@ -55198,7 +55207,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ260">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR260">
         <v>1.97</v>
@@ -55323,7 +55332,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55529,7 +55538,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55735,7 +55744,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55816,7 +55825,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ263">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR263">
         <v>1.63</v>
@@ -55941,7 +55950,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56147,7 +56156,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56353,7 +56362,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56431,7 +56440,7 @@
         <v>2.15</v>
       </c>
       <c r="AP266">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ266">
         <v>2</v>
@@ -56559,7 +56568,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56637,7 +56646,7 @@
         <v>1.69</v>
       </c>
       <c r="AP267">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ267">
         <v>1.47</v>
@@ -56765,7 +56774,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -57177,7 +57186,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57255,7 +57264,7 @@
         <v>0.92</v>
       </c>
       <c r="AP270">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ270">
         <v>1.13</v>
@@ -57383,7 +57392,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57795,7 +57804,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58207,7 +58216,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58288,7 +58297,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ275">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR275">
         <v>1.86</v>
@@ -58413,7 +58422,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58619,7 +58628,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58697,7 +58706,7 @@
         <v>1.43</v>
       </c>
       <c r="AP277">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ277">
         <v>1.5</v>
@@ -58825,7 +58834,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58903,7 +58912,7 @@
         <v>1.07</v>
       </c>
       <c r="AP278">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ278">
         <v>1.13</v>
@@ -59031,7 +59040,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59112,7 +59121,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ279">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR279">
         <v>1.4</v>
@@ -59237,7 +59246,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59443,7 +59452,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59524,7 +59533,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ281">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AR281">
         <v>1.45</v>
@@ -59933,7 +59942,7 @@
         <v>0.62</v>
       </c>
       <c r="AP283">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ283">
         <v>0.5</v>
@@ -60473,7 +60482,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60679,7 +60688,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61503,7 +61512,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61581,10 +61590,10 @@
         <v>0.5</v>
       </c>
       <c r="AP291">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ291">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR291">
         <v>1.6</v>
@@ -61790,7 +61799,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ292">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AR292">
         <v>1.94</v>
@@ -61915,7 +61924,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62121,7 +62130,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62533,7 +62542,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62739,7 +62748,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -62817,7 +62826,7 @@
         <v>1.79</v>
       </c>
       <c r="AP297">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AQ297">
         <v>1.94</v>
@@ -63151,7 +63160,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -64593,7 +64602,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -65211,7 +65220,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65623,7 +65632,7 @@
         <v>298</v>
       </c>
       <c r="P311" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q311">
         <v>2.4</v>
@@ -65829,7 +65838,7 @@
         <v>299</v>
       </c>
       <c r="P312" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q312">
         <v>2.88</v>
@@ -66241,7 +66250,7 @@
         <v>301</v>
       </c>
       <c r="P314" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q314">
         <v>3.5</v>
@@ -66447,7 +66456,7 @@
         <v>102</v>
       </c>
       <c r="P315" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q315">
         <v>2.38</v>
@@ -66653,7 +66662,7 @@
         <v>302</v>
       </c>
       <c r="P316" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q316">
         <v>2.2</v>
@@ -66810,6 +66819,624 @@
       </c>
       <c r="BP316">
         <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7465747</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45747.625</v>
+      </c>
+      <c r="F317">
+        <v>32</v>
+      </c>
+      <c r="G317" t="s">
+        <v>89</v>
+      </c>
+      <c r="H317" t="s">
+        <v>88</v>
+      </c>
+      <c r="I317">
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <v>1</v>
+      </c>
+      <c r="K317">
+        <v>1</v>
+      </c>
+      <c r="L317">
+        <v>0</v>
+      </c>
+      <c r="M317">
+        <v>2</v>
+      </c>
+      <c r="N317">
+        <v>2</v>
+      </c>
+      <c r="O317" t="s">
+        <v>93</v>
+      </c>
+      <c r="P317" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q317">
+        <v>4</v>
+      </c>
+      <c r="R317">
+        <v>2.5</v>
+      </c>
+      <c r="S317">
+        <v>2.38</v>
+      </c>
+      <c r="T317">
+        <v>1.25</v>
+      </c>
+      <c r="U317">
+        <v>3.75</v>
+      </c>
+      <c r="V317">
+        <v>2.2</v>
+      </c>
+      <c r="W317">
+        <v>1.62</v>
+      </c>
+      <c r="X317">
+        <v>5</v>
+      </c>
+      <c r="Y317">
+        <v>1.17</v>
+      </c>
+      <c r="Z317">
+        <v>3.7</v>
+      </c>
+      <c r="AA317">
+        <v>3.8</v>
+      </c>
+      <c r="AB317">
+        <v>1.8</v>
+      </c>
+      <c r="AC317">
+        <v>1.01</v>
+      </c>
+      <c r="AD317">
+        <v>17</v>
+      </c>
+      <c r="AE317">
+        <v>1.15</v>
+      </c>
+      <c r="AF317">
+        <v>5.25</v>
+      </c>
+      <c r="AG317">
+        <v>1.48</v>
+      </c>
+      <c r="AH317">
+        <v>2.6</v>
+      </c>
+      <c r="AI317">
+        <v>1.5</v>
+      </c>
+      <c r="AJ317">
+        <v>2.5</v>
+      </c>
+      <c r="AK317">
+        <v>1.93</v>
+      </c>
+      <c r="AL317">
+        <v>1.24</v>
+      </c>
+      <c r="AM317">
+        <v>1.26</v>
+      </c>
+      <c r="AN317">
+        <v>1.27</v>
+      </c>
+      <c r="AO317">
+        <v>1.87</v>
+      </c>
+      <c r="AP317">
+        <v>1.19</v>
+      </c>
+      <c r="AQ317">
+        <v>1.94</v>
+      </c>
+      <c r="AR317">
+        <v>1.65</v>
+      </c>
+      <c r="AS317">
+        <v>1.47</v>
+      </c>
+      <c r="AT317">
+        <v>3.12</v>
+      </c>
+      <c r="AU317">
+        <v>4</v>
+      </c>
+      <c r="AV317">
+        <v>6</v>
+      </c>
+      <c r="AW317">
+        <v>4</v>
+      </c>
+      <c r="AX317">
+        <v>11</v>
+      </c>
+      <c r="AY317">
+        <v>8</v>
+      </c>
+      <c r="AZ317">
+        <v>17</v>
+      </c>
+      <c r="BA317">
+        <v>2</v>
+      </c>
+      <c r="BB317">
+        <v>4</v>
+      </c>
+      <c r="BC317">
+        <v>6</v>
+      </c>
+      <c r="BD317">
+        <v>2.3</v>
+      </c>
+      <c r="BE317">
+        <v>8.5</v>
+      </c>
+      <c r="BF317">
+        <v>1.75</v>
+      </c>
+      <c r="BG317">
+        <v>1.22</v>
+      </c>
+      <c r="BH317">
+        <v>3.8</v>
+      </c>
+      <c r="BI317">
+        <v>1.28</v>
+      </c>
+      <c r="BJ317">
+        <v>3.08</v>
+      </c>
+      <c r="BK317">
+        <v>1.53</v>
+      </c>
+      <c r="BL317">
+        <v>2.28</v>
+      </c>
+      <c r="BM317">
+        <v>1.9</v>
+      </c>
+      <c r="BN317">
+        <v>1.8</v>
+      </c>
+      <c r="BO317">
+        <v>2.42</v>
+      </c>
+      <c r="BP317">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7465748</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45747.625</v>
+      </c>
+      <c r="F318">
+        <v>32</v>
+      </c>
+      <c r="G318" t="s">
+        <v>78</v>
+      </c>
+      <c r="H318" t="s">
+        <v>74</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>1</v>
+      </c>
+      <c r="L318">
+        <v>1</v>
+      </c>
+      <c r="M318">
+        <v>1</v>
+      </c>
+      <c r="N318">
+        <v>2</v>
+      </c>
+      <c r="O318" t="s">
+        <v>104</v>
+      </c>
+      <c r="P318" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q318">
+        <v>2.2</v>
+      </c>
+      <c r="R318">
+        <v>2.4</v>
+      </c>
+      <c r="S318">
+        <v>4.75</v>
+      </c>
+      <c r="T318">
+        <v>1.3</v>
+      </c>
+      <c r="U318">
+        <v>3.4</v>
+      </c>
+      <c r="V318">
+        <v>2.38</v>
+      </c>
+      <c r="W318">
+        <v>1.53</v>
+      </c>
+      <c r="X318">
+        <v>6</v>
+      </c>
+      <c r="Y318">
+        <v>1.13</v>
+      </c>
+      <c r="Z318">
+        <v>1.65</v>
+      </c>
+      <c r="AA318">
+        <v>3.9</v>
+      </c>
+      <c r="AB318">
+        <v>4.5</v>
+      </c>
+      <c r="AC318">
+        <v>1.04</v>
+      </c>
+      <c r="AD318">
+        <v>10</v>
+      </c>
+      <c r="AE318">
+        <v>1.2</v>
+      </c>
+      <c r="AF318">
+        <v>4.33</v>
+      </c>
+      <c r="AG318">
+        <v>1.62</v>
+      </c>
+      <c r="AH318">
+        <v>2.25</v>
+      </c>
+      <c r="AI318">
+        <v>1.62</v>
+      </c>
+      <c r="AJ318">
+        <v>2.2</v>
+      </c>
+      <c r="AK318">
+        <v>1.19</v>
+      </c>
+      <c r="AL318">
+        <v>1.24</v>
+      </c>
+      <c r="AM318">
+        <v>2.1</v>
+      </c>
+      <c r="AN318">
+        <v>1.29</v>
+      </c>
+      <c r="AO318">
+        <v>0.53</v>
+      </c>
+      <c r="AP318">
+        <v>1.27</v>
+      </c>
+      <c r="AQ318">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR318">
+        <v>1.75</v>
+      </c>
+      <c r="AS318">
+        <v>1.11</v>
+      </c>
+      <c r="AT318">
+        <v>2.86</v>
+      </c>
+      <c r="AU318">
+        <v>9</v>
+      </c>
+      <c r="AV318">
+        <v>7</v>
+      </c>
+      <c r="AW318">
+        <v>8</v>
+      </c>
+      <c r="AX318">
+        <v>4</v>
+      </c>
+      <c r="AY318">
+        <v>17</v>
+      </c>
+      <c r="AZ318">
+        <v>11</v>
+      </c>
+      <c r="BA318">
+        <v>5</v>
+      </c>
+      <c r="BB318">
+        <v>4</v>
+      </c>
+      <c r="BC318">
+        <v>9</v>
+      </c>
+      <c r="BD318">
+        <v>1.5</v>
+      </c>
+      <c r="BE318">
+        <v>9</v>
+      </c>
+      <c r="BF318">
+        <v>2.88</v>
+      </c>
+      <c r="BG318">
+        <v>1.21</v>
+      </c>
+      <c r="BH318">
+        <v>3.9</v>
+      </c>
+      <c r="BI318">
+        <v>1.3</v>
+      </c>
+      <c r="BJ318">
+        <v>2.97</v>
+      </c>
+      <c r="BK318">
+        <v>1.55</v>
+      </c>
+      <c r="BL318">
+        <v>2.23</v>
+      </c>
+      <c r="BM318">
+        <v>1.94</v>
+      </c>
+      <c r="BN318">
+        <v>1.77</v>
+      </c>
+      <c r="BO318">
+        <v>2.48</v>
+      </c>
+      <c r="BP318">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7465749</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45747.625</v>
+      </c>
+      <c r="F319">
+        <v>32</v>
+      </c>
+      <c r="G319" t="s">
+        <v>79</v>
+      </c>
+      <c r="H319" t="s">
+        <v>85</v>
+      </c>
+      <c r="I319">
+        <v>1</v>
+      </c>
+      <c r="J319">
+        <v>3</v>
+      </c>
+      <c r="K319">
+        <v>4</v>
+      </c>
+      <c r="L319">
+        <v>2</v>
+      </c>
+      <c r="M319">
+        <v>4</v>
+      </c>
+      <c r="N319">
+        <v>6</v>
+      </c>
+      <c r="O319" t="s">
+        <v>303</v>
+      </c>
+      <c r="P319" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q319">
+        <v>3.4</v>
+      </c>
+      <c r="R319">
+        <v>2.4</v>
+      </c>
+      <c r="S319">
+        <v>2.63</v>
+      </c>
+      <c r="T319">
+        <v>1.25</v>
+      </c>
+      <c r="U319">
+        <v>3.75</v>
+      </c>
+      <c r="V319">
+        <v>2.2</v>
+      </c>
+      <c r="W319">
+        <v>1.62</v>
+      </c>
+      <c r="X319">
+        <v>5</v>
+      </c>
+      <c r="Y319">
+        <v>1.17</v>
+      </c>
+      <c r="Z319">
+        <v>3</v>
+      </c>
+      <c r="AA319">
+        <v>3.6</v>
+      </c>
+      <c r="AB319">
+        <v>2.1</v>
+      </c>
+      <c r="AC319">
+        <v>1.01</v>
+      </c>
+      <c r="AD319">
+        <v>15</v>
+      </c>
+      <c r="AE319">
+        <v>1.17</v>
+      </c>
+      <c r="AF319">
+        <v>5</v>
+      </c>
+      <c r="AG319">
+        <v>1.5</v>
+      </c>
+      <c r="AH319">
+        <v>2.5</v>
+      </c>
+      <c r="AI319">
+        <v>1.44</v>
+      </c>
+      <c r="AJ319">
+        <v>2.63</v>
+      </c>
+      <c r="AK319">
+        <v>1.66</v>
+      </c>
+      <c r="AL319">
+        <v>1.26</v>
+      </c>
+      <c r="AM319">
+        <v>1.37</v>
+      </c>
+      <c r="AN319">
+        <v>0.6</v>
+      </c>
+      <c r="AO319">
+        <v>1.2</v>
+      </c>
+      <c r="AP319">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ319">
+        <v>1.31</v>
+      </c>
+      <c r="AR319">
+        <v>1.64</v>
+      </c>
+      <c r="AS319">
+        <v>1.21</v>
+      </c>
+      <c r="AT319">
+        <v>2.85</v>
+      </c>
+      <c r="AU319">
+        <v>9</v>
+      </c>
+      <c r="AV319">
+        <v>7</v>
+      </c>
+      <c r="AW319">
+        <v>6</v>
+      </c>
+      <c r="AX319">
+        <v>9</v>
+      </c>
+      <c r="AY319">
+        <v>15</v>
+      </c>
+      <c r="AZ319">
+        <v>16</v>
+      </c>
+      <c r="BA319">
+        <v>8</v>
+      </c>
+      <c r="BB319">
+        <v>2</v>
+      </c>
+      <c r="BC319">
+        <v>10</v>
+      </c>
+      <c r="BD319">
+        <v>2.2</v>
+      </c>
+      <c r="BE319">
+        <v>8.5</v>
+      </c>
+      <c r="BF319">
+        <v>1.8</v>
+      </c>
+      <c r="BG319">
+        <v>1.25</v>
+      </c>
+      <c r="BH319">
+        <v>3.4</v>
+      </c>
+      <c r="BI319">
+        <v>1.31</v>
+      </c>
+      <c r="BJ319">
+        <v>2.92</v>
+      </c>
+      <c r="BK319">
+        <v>1.57</v>
+      </c>
+      <c r="BL319">
+        <v>2.19</v>
+      </c>
+      <c r="BM319">
+        <v>1.96</v>
+      </c>
+      <c r="BN319">
+        <v>1.75</v>
+      </c>
+      <c r="BO319">
+        <v>2.54</v>
+      </c>
+      <c r="BP319">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="449">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1722,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP319"/>
+  <dimension ref="A1:BP320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3295,7 +3295,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
         <v>0.93</v>
@@ -8854,7 +8854,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ35">
         <v>1.94</v>
@@ -9063,7 +9063,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ36">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -12977,7 +12977,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -13592,7 +13592,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ58">
         <v>1.31</v>
@@ -16270,7 +16270,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
         <v>2</v>
@@ -16479,7 +16479,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -19360,7 +19360,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ86">
         <v>1.13</v>
@@ -20805,7 +20805,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ93">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -24098,7 +24098,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ109">
         <v>1.31</v>
@@ -26985,7 +26985,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ123">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -28424,7 +28424,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -30899,7 +30899,7 @@
         <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -32132,7 +32132,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
         <v>1.06</v>
@@ -34810,7 +34810,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ161">
         <v>1.44</v>
@@ -36461,7 +36461,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ169">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -38724,7 +38724,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ180">
         <v>1.5</v>
@@ -39757,7 +39757,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ185">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -41196,7 +41196,7 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ192">
         <v>1.19</v>
@@ -44083,7 +44083,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ206">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -46552,7 +46552,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ218">
         <v>1.13</v>
@@ -48821,7 +48821,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ229">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR229">
         <v>1.56</v>
@@ -50881,7 +50881,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ239">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR239">
         <v>1.78</v>
@@ -57061,7 +57061,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ269">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR269">
         <v>1.77</v>
@@ -57470,7 +57470,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP271">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ271">
         <v>0.75</v>
@@ -59118,7 +59118,7 @@
         <v>0.46</v>
       </c>
       <c r="AP279">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ279">
         <v>0.5600000000000001</v>
@@ -62002,7 +62002,7 @@
         <v>0.93</v>
       </c>
       <c r="AP293">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ293">
         <v>1</v>
@@ -63035,7 +63035,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ298">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR298">
         <v>1.65</v>
@@ -66537,7 +66537,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ315">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR315">
         <v>1.96</v>
@@ -67437,6 +67437,212 @@
       </c>
       <c r="BP319">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7465680</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45748.625</v>
+      </c>
+      <c r="F320">
+        <v>26</v>
+      </c>
+      <c r="G320" t="s">
+        <v>84</v>
+      </c>
+      <c r="H320" t="s">
+        <v>80</v>
+      </c>
+      <c r="I320">
+        <v>0</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>0</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+      <c r="M320">
+        <v>0</v>
+      </c>
+      <c r="N320">
+        <v>0</v>
+      </c>
+      <c r="O320" t="s">
+        <v>93</v>
+      </c>
+      <c r="P320" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q320">
+        <v>3.6</v>
+      </c>
+      <c r="R320">
+        <v>2.25</v>
+      </c>
+      <c r="S320">
+        <v>2.75</v>
+      </c>
+      <c r="T320">
+        <v>1.33</v>
+      </c>
+      <c r="U320">
+        <v>3.25</v>
+      </c>
+      <c r="V320">
+        <v>2.63</v>
+      </c>
+      <c r="W320">
+        <v>1.44</v>
+      </c>
+      <c r="X320">
+        <v>6.5</v>
+      </c>
+      <c r="Y320">
+        <v>1.11</v>
+      </c>
+      <c r="Z320">
+        <v>3.1</v>
+      </c>
+      <c r="AA320">
+        <v>3.7</v>
+      </c>
+      <c r="AB320">
+        <v>2.15</v>
+      </c>
+      <c r="AC320">
+        <v>1.03</v>
+      </c>
+      <c r="AD320">
+        <v>13</v>
+      </c>
+      <c r="AE320">
+        <v>1.22</v>
+      </c>
+      <c r="AF320">
+        <v>4.2</v>
+      </c>
+      <c r="AG320">
+        <v>1.7</v>
+      </c>
+      <c r="AH320">
+        <v>2.1</v>
+      </c>
+      <c r="AI320">
+        <v>1.62</v>
+      </c>
+      <c r="AJ320">
+        <v>2.2</v>
+      </c>
+      <c r="AK320">
+        <v>1.63</v>
+      </c>
+      <c r="AL320">
+        <v>1.25</v>
+      </c>
+      <c r="AM320">
+        <v>1.4</v>
+      </c>
+      <c r="AN320">
+        <v>0.67</v>
+      </c>
+      <c r="AO320">
+        <v>1.27</v>
+      </c>
+      <c r="AP320">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ320">
+        <v>1.25</v>
+      </c>
+      <c r="AR320">
+        <v>1.42</v>
+      </c>
+      <c r="AS320">
+        <v>1.36</v>
+      </c>
+      <c r="AT320">
+        <v>2.78</v>
+      </c>
+      <c r="AU320">
+        <v>6</v>
+      </c>
+      <c r="AV320">
+        <v>6</v>
+      </c>
+      <c r="AW320">
+        <v>7</v>
+      </c>
+      <c r="AX320">
+        <v>11</v>
+      </c>
+      <c r="AY320">
+        <v>13</v>
+      </c>
+      <c r="AZ320">
+        <v>17</v>
+      </c>
+      <c r="BA320">
+        <v>7</v>
+      </c>
+      <c r="BB320">
+        <v>7</v>
+      </c>
+      <c r="BC320">
+        <v>14</v>
+      </c>
+      <c r="BD320">
+        <v>2.12</v>
+      </c>
+      <c r="BE320">
+        <v>6.5</v>
+      </c>
+      <c r="BF320">
+        <v>1.88</v>
+      </c>
+      <c r="BG320">
+        <v>1.38</v>
+      </c>
+      <c r="BH320">
+        <v>2.8</v>
+      </c>
+      <c r="BI320">
+        <v>1.65</v>
+      </c>
+      <c r="BJ320">
+        <v>2.08</v>
+      </c>
+      <c r="BK320">
+        <v>2.02</v>
+      </c>
+      <c r="BL320">
+        <v>1.7</v>
+      </c>
+      <c r="BM320">
+        <v>2.55</v>
+      </c>
+      <c r="BN320">
+        <v>1.44</v>
+      </c>
+      <c r="BO320">
+        <v>3.4</v>
+      </c>
+      <c r="BP320">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="456">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -928,6 +928,24 @@
     <t>['26', '87']</t>
   </si>
   <si>
+    <t>['22', '28']</t>
+  </si>
+  <si>
+    <t>['26', '84']</t>
+  </si>
+  <si>
+    <t>['68', '80', '86', '90']</t>
+  </si>
+  <si>
+    <t>['40', '48', '63']</t>
+  </si>
+  <si>
+    <t>['19', '70', '90+3']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1112,9 +1130,6 @@
   </si>
   <si>
     <t>['41', '63']</t>
-  </si>
-  <si>
-    <t>['35']</t>
   </si>
   <si>
     <t>['25', '78']</t>
@@ -1361,6 +1376,12 @@
   </si>
   <si>
     <t>['2', '15', '42', '56']</t>
+  </si>
+  <si>
+    <t>['68', '90']</t>
+  </si>
+  <si>
+    <t>['86', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP320"/>
+  <dimension ref="A1:BP326"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2184,7 +2205,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2262,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
         <v>1.47</v>
@@ -2390,7 +2411,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2674,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ5">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2802,7 +2823,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -2880,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ6">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3008,7 +3029,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3086,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ7">
         <v>1.13</v>
@@ -3214,7 +3235,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3295,7 +3316,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ8">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3420,7 +3441,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3832,7 +3853,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3913,7 +3934,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ11">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4244,7 +4265,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4862,7 +4883,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4943,7 +4964,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ16">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5149,7 +5170,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5352,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -5686,7 +5707,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -5764,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ20">
         <v>1.94</v>
@@ -6176,10 +6197,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR22">
         <v>1.14</v>
@@ -6382,7 +6403,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ23">
         <v>1.19</v>
@@ -6716,7 +6737,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6922,7 +6943,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7128,7 +7149,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7209,7 +7230,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ27">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7412,10 +7433,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR28">
         <v>1.82</v>
@@ -7540,7 +7561,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7952,7 +7973,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8236,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ32">
         <v>1.5</v>
@@ -8445,7 +8466,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR33">
         <v>1.26</v>
@@ -8570,7 +8591,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8648,10 +8669,10 @@
         <v>3</v>
       </c>
       <c r="AP34">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ34">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR34">
         <v>1.12</v>
@@ -8776,7 +8797,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9063,7 +9084,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR36">
         <v>1.09</v>
@@ -9266,10 +9287,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ37">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR37">
         <v>1.18</v>
@@ -9394,7 +9415,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9475,7 +9496,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ38">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR38">
         <v>1.6</v>
@@ -9600,7 +9621,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9884,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ40">
         <v>0.5600000000000001</v>
@@ -10012,7 +10033,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10711,7 +10732,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ44">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR44">
         <v>2.05</v>
@@ -10836,7 +10857,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11042,7 +11063,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11120,10 +11141,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ46">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR46">
         <v>1.3</v>
@@ -11454,7 +11475,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11532,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ48">
         <v>1.94</v>
@@ -11866,7 +11887,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12072,7 +12093,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12278,7 +12299,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12356,7 +12377,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ52">
         <v>1.06</v>
@@ -12977,7 +12998,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ55">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR55">
         <v>1.7</v>
@@ -13102,7 +13123,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13180,7 +13201,7 @@
         <v>3</v>
       </c>
       <c r="AP56">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -13514,7 +13535,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -14004,7 +14025,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ60">
         <v>1.47</v>
@@ -14132,7 +14153,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14213,7 +14234,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ61">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR61">
         <v>1.96</v>
@@ -14338,7 +14359,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14419,7 +14440,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ62">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR62">
         <v>1.68</v>
@@ -14544,7 +14565,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15162,7 +15183,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15240,10 +15261,10 @@
         <v>1.33</v>
       </c>
       <c r="AP66">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ66">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR66">
         <v>1.48</v>
@@ -15574,7 +15595,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15652,10 +15673,10 @@
         <v>2.33</v>
       </c>
       <c r="AP68">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15780,7 +15801,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15858,7 +15879,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -15986,7 +16007,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16192,7 +16213,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16273,7 +16294,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR71">
         <v>1.34</v>
@@ -16398,7 +16419,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16476,10 +16497,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ72">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16604,7 +16625,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16682,7 +16703,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ73">
         <v>0.5600000000000001</v>
@@ -16810,7 +16831,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -16891,7 +16912,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR74">
         <v>1.75</v>
@@ -17016,7 +17037,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17634,7 +17655,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17840,7 +17861,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18252,7 +18273,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18539,7 +18560,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ82">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR82">
         <v>1.76</v>
@@ -18664,7 +18685,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18742,7 +18763,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
         <v>1.94</v>
@@ -18870,7 +18891,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18948,7 +18969,7 @@
         <v>0.67</v>
       </c>
       <c r="AP84">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ84">
         <v>1.67</v>
@@ -19157,7 +19178,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ85">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR85">
         <v>1.66</v>
@@ -19488,7 +19509,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19772,7 +19793,7 @@
         <v>0.5</v>
       </c>
       <c r="AP88">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ88">
         <v>0.5600000000000001</v>
@@ -19978,10 +19999,10 @@
         <v>2.25</v>
       </c>
       <c r="AP89">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ89">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR89">
         <v>1.66</v>
@@ -20106,7 +20127,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20393,7 +20414,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR91">
         <v>1.69</v>
@@ -20518,7 +20539,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20802,10 +20823,10 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ93">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR93">
         <v>1.74</v>
@@ -20930,7 +20951,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21136,7 +21157,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21342,7 +21363,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21420,7 +21441,7 @@
         <v>1.6</v>
       </c>
       <c r="AP96">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ96">
         <v>1.13</v>
@@ -21548,7 +21569,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21960,7 +21981,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22372,7 +22393,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22578,7 +22599,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22659,7 +22680,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ102">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR102">
         <v>1.75</v>
@@ -22990,7 +23011,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23071,7 +23092,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ104">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23892,7 +23913,7 @@
         <v>0.5</v>
       </c>
       <c r="AP108">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ108">
         <v>0.5600000000000001</v>
@@ -24101,7 +24122,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ109">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR109">
         <v>1.34</v>
@@ -24226,7 +24247,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24304,7 +24325,7 @@
         <v>1.4</v>
       </c>
       <c r="AP110">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ110">
         <v>1</v>
@@ -24432,7 +24453,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24510,7 +24531,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ111">
         <v>1.31</v>
@@ -24638,7 +24659,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -24922,7 +24943,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ113">
         <v>0.5</v>
@@ -25128,7 +25149,7 @@
         <v>1.67</v>
       </c>
       <c r="AP114">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ114">
         <v>1.5</v>
@@ -25256,7 +25277,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25337,7 +25358,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25462,7 +25483,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25540,10 +25561,10 @@
         <v>1.4</v>
       </c>
       <c r="AP116">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ116">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR116">
         <v>1.22</v>
@@ -25668,7 +25689,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25746,10 +25767,10 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ117">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25874,7 +25895,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26080,7 +26101,7 @@
         <v>93</v>
       </c>
       <c r="P119" t="s">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -26161,7 +26182,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR119">
         <v>1.83</v>
@@ -26286,7 +26307,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26364,7 +26385,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ120">
         <v>1.13</v>
@@ -26492,7 +26513,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26570,7 +26591,7 @@
         <v>2.6</v>
       </c>
       <c r="AP121">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ121">
         <v>1.19</v>
@@ -26698,7 +26719,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26779,7 +26800,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR122">
         <v>1.92</v>
@@ -26904,7 +26925,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -26985,7 +27006,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR123">
         <v>1.47</v>
@@ -27110,7 +27131,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27316,7 +27337,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27600,7 +27621,7 @@
         <v>0.4</v>
       </c>
       <c r="AP126">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ126">
         <v>0.5600000000000001</v>
@@ -27934,7 +27955,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28221,7 +28242,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ129">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR129">
         <v>1.74</v>
@@ -28346,7 +28367,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28552,7 +28573,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -28836,7 +28857,7 @@
         <v>1.5</v>
       </c>
       <c r="AP132">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ132">
         <v>1.13</v>
@@ -29045,7 +29066,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ133">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR133">
         <v>1.73</v>
@@ -29248,7 +29269,7 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ134">
         <v>1.31</v>
@@ -29457,7 +29478,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ135">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR135">
         <v>1.75</v>
@@ -29582,7 +29603,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29660,10 +29681,10 @@
         <v>1.5</v>
       </c>
       <c r="AP136">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR136">
         <v>1.7</v>
@@ -30278,7 +30299,7 @@
         <v>0.67</v>
       </c>
       <c r="AP139">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ139">
         <v>0.5</v>
@@ -30690,7 +30711,7 @@
         <v>2.67</v>
       </c>
       <c r="AP141">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ141">
         <v>1.19</v>
@@ -30899,7 +30920,7 @@
         <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR142">
         <v>1.74</v>
@@ -31308,7 +31329,7 @@
         <v>1.43</v>
       </c>
       <c r="AP144">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ144">
         <v>1.47</v>
@@ -31436,7 +31457,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31642,7 +31663,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31848,7 +31869,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -31926,10 +31947,10 @@
         <v>2.14</v>
       </c>
       <c r="AP147">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ147">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR147">
         <v>1.58</v>
@@ -32054,7 +32075,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32466,7 +32487,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32672,7 +32693,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32753,7 +32774,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ151">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR151">
         <v>1.8</v>
@@ -33084,7 +33105,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33290,7 +33311,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33371,7 +33392,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ154">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR154">
         <v>1.6</v>
@@ -33496,7 +33517,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -33574,7 +33595,7 @@
         <v>0.43</v>
       </c>
       <c r="AP155">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ155">
         <v>0.5600000000000001</v>
@@ -33780,7 +33801,7 @@
         <v>1.43</v>
       </c>
       <c r="AP156">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ156">
         <v>1.13</v>
@@ -33986,10 +34007,10 @@
         <v>1.29</v>
       </c>
       <c r="AP157">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ157">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR157">
         <v>2.01</v>
@@ -34526,7 +34547,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34813,7 +34834,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ161">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR161">
         <v>1.46</v>
@@ -34938,7 +34959,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35225,7 +35246,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ163">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR163">
         <v>1.78</v>
@@ -35431,7 +35452,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ164">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR164">
         <v>1.3</v>
@@ -35762,7 +35783,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -35843,7 +35864,7 @@
         <v>2</v>
       </c>
       <c r="AQ166">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR166">
         <v>1.74</v>
@@ -36046,7 +36067,7 @@
         <v>2.29</v>
       </c>
       <c r="AP167">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ167">
         <v>1.19</v>
@@ -36252,7 +36273,7 @@
         <v>0.57</v>
       </c>
       <c r="AP168">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ168">
         <v>0.5</v>
@@ -36461,7 +36482,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ169">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR169">
         <v>1.79</v>
@@ -36586,7 +36607,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36792,7 +36813,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37204,7 +37225,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37282,7 +37303,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ173">
         <v>1</v>
@@ -37488,7 +37509,7 @@
         <v>1.33</v>
       </c>
       <c r="AP174">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ174">
         <v>1.13</v>
@@ -37694,10 +37715,10 @@
         <v>1.25</v>
       </c>
       <c r="AP175">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ175">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR175">
         <v>2.04</v>
@@ -38028,7 +38049,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38234,7 +38255,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38312,10 +38333,10 @@
         <v>1.67</v>
       </c>
       <c r="AP178">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ178">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR178">
         <v>1.72</v>
@@ -38646,7 +38667,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38852,7 +38873,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39470,7 +39491,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39676,7 +39697,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39757,7 +39778,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR185">
         <v>1.43</v>
@@ -39882,7 +39903,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39963,7 +39984,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ186">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR186">
         <v>1.72</v>
@@ -40500,7 +40521,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40578,10 +40599,10 @@
         <v>1</v>
       </c>
       <c r="AP189">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ189">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR189">
         <v>1.28</v>
@@ -40787,7 +40808,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ190">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR190">
         <v>1.73</v>
@@ -40990,7 +41011,7 @@
         <v>0.63</v>
       </c>
       <c r="AP191">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ191">
         <v>0.5</v>
@@ -41118,7 +41139,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41324,7 +41345,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41530,7 +41551,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41611,7 +41632,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ194">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR194">
         <v>1.8</v>
@@ -41736,7 +41757,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41814,7 +41835,7 @@
         <v>1.6</v>
       </c>
       <c r="AP195">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ195">
         <v>1.5</v>
@@ -41942,7 +41963,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42020,7 +42041,7 @@
         <v>1.56</v>
       </c>
       <c r="AP196">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ196">
         <v>1.31</v>
@@ -42229,7 +42250,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ197">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR197">
         <v>1.58</v>
@@ -42432,7 +42453,7 @@
         <v>1.11</v>
       </c>
       <c r="AP198">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ198">
         <v>1.13</v>
@@ -42560,7 +42581,7 @@
         <v>225</v>
       </c>
       <c r="P199" t="s">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="Q199">
         <v>3.5</v>
@@ -42638,7 +42659,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ199">
         <v>1.13</v>
@@ -42972,7 +42993,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43462,7 +43483,7 @@
         <v>0.7</v>
       </c>
       <c r="AP203">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ203">
         <v>0.5600000000000001</v>
@@ -43590,7 +43611,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -43877,7 +43898,7 @@
         <v>2</v>
       </c>
       <c r="AQ205">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR205">
         <v>1.65</v>
@@ -44002,7 +44023,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44080,10 +44101,10 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ206">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR206">
         <v>1.66</v>
@@ -44208,7 +44229,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44289,7 +44310,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ207">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44620,7 +44641,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44698,7 +44719,7 @@
         <v>1.18</v>
       </c>
       <c r="AP209">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ209">
         <v>1.06</v>
@@ -44907,7 +44928,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ210">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR210">
         <v>1.76</v>
@@ -45032,7 +45053,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45110,10 +45131,10 @@
         <v>1.3</v>
       </c>
       <c r="AP211">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ211">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR211">
         <v>1.87</v>
@@ -45316,7 +45337,7 @@
         <v>0.9</v>
       </c>
       <c r="AP212">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45728,7 +45749,7 @@
         <v>1.7</v>
       </c>
       <c r="AP214">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ214">
         <v>1.31</v>
@@ -45856,7 +45877,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45934,7 +45955,7 @@
         <v>1.55</v>
       </c>
       <c r="AP215">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ215">
         <v>1.5</v>
@@ -46143,7 +46164,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ216">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR216">
         <v>1.9</v>
@@ -46349,7 +46370,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ217">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46474,7 +46495,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46680,7 +46701,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46761,7 +46782,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ219">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR219">
         <v>1.34</v>
@@ -46886,7 +46907,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -46964,7 +46985,7 @@
         <v>1.45</v>
       </c>
       <c r="AP220">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ220">
         <v>1.47</v>
@@ -47376,7 +47397,7 @@
         <v>0.64</v>
       </c>
       <c r="AP222">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ222">
         <v>0.5600000000000001</v>
@@ -47997,7 +48018,7 @@
         <v>2</v>
       </c>
       <c r="AQ225">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR225">
         <v>1.68</v>
@@ -48409,7 +48430,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ227">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR227">
         <v>1.46</v>
@@ -48740,7 +48761,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -48821,7 +48842,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ229">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR229">
         <v>1.56</v>
@@ -49230,7 +49251,7 @@
         <v>1</v>
       </c>
       <c r="AP231">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ231">
         <v>1.13</v>
@@ -49358,7 +49379,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49436,10 +49457,10 @@
         <v>1.08</v>
       </c>
       <c r="AP232">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ232">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR232">
         <v>1.63</v>
@@ -49976,7 +49997,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50182,7 +50203,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50260,7 +50281,7 @@
         <v>1.33</v>
       </c>
       <c r="AP236">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ236">
         <v>1.06</v>
@@ -50466,7 +50487,7 @@
         <v>1.45</v>
       </c>
       <c r="AP237">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ237">
         <v>1.19</v>
@@ -50594,7 +50615,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50881,7 +50902,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ239">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR239">
         <v>1.78</v>
@@ -51418,7 +51439,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51499,7 +51520,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ242">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR242">
         <v>1.93</v>
@@ -51624,7 +51645,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51702,7 +51723,7 @@
         <v>1.18</v>
       </c>
       <c r="AP243">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ243">
         <v>1.67</v>
@@ -51830,7 +51851,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52448,7 +52469,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52529,7 +52550,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ247">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR247">
         <v>1.53</v>
@@ -52732,7 +52753,7 @@
         <v>1.9</v>
       </c>
       <c r="AP248">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ248">
         <v>1.94</v>
@@ -52860,7 +52881,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -52941,7 +52962,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ249">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR249">
         <v>1.71</v>
@@ -53144,7 +53165,7 @@
         <v>1.23</v>
       </c>
       <c r="AP250">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ250">
         <v>1.06</v>
@@ -53353,7 +53374,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ251">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR251">
         <v>1.85</v>
@@ -53762,7 +53783,7 @@
         <v>1.54</v>
       </c>
       <c r="AP253">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ253">
         <v>1.5</v>
@@ -54096,7 +54117,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54174,7 +54195,7 @@
         <v>1.58</v>
       </c>
       <c r="AP255">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ255">
         <v>1.94</v>
@@ -54380,7 +54401,7 @@
         <v>1</v>
       </c>
       <c r="AP256">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ256">
         <v>1.13</v>
@@ -54795,7 +54816,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ258">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR258">
         <v>1.81</v>
@@ -55332,7 +55353,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55413,7 +55434,7 @@
         <v>2</v>
       </c>
       <c r="AQ261">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR261">
         <v>1.76</v>
@@ -55538,7 +55559,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55616,7 +55637,7 @@
         <v>1.73</v>
       </c>
       <c r="AP262">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ262">
         <v>1.94</v>
@@ -55744,7 +55765,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55950,7 +55971,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56156,7 +56177,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56234,7 +56255,7 @@
         <v>1.33</v>
       </c>
       <c r="AP265">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ265">
         <v>1.67</v>
@@ -56362,7 +56383,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56443,7 +56464,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ266">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR266">
         <v>1.73</v>
@@ -56568,7 +56589,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56774,7 +56795,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -57061,7 +57082,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ269">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR269">
         <v>1.77</v>
@@ -57186,7 +57207,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57392,7 +57413,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57473,7 +57494,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ271">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR271">
         <v>1.38</v>
@@ -57676,7 +57697,7 @@
         <v>1.92</v>
       </c>
       <c r="AP272">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ272">
         <v>1.94</v>
@@ -57804,7 +57825,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -57882,7 +57903,7 @@
         <v>1.38</v>
       </c>
       <c r="AP273">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ273">
         <v>1.19</v>
@@ -58088,7 +58109,7 @@
         <v>0.62</v>
       </c>
       <c r="AP274">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ274">
         <v>0.5600000000000001</v>
@@ -58216,7 +58237,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58422,7 +58443,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58628,7 +58649,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58834,7 +58855,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -59040,7 +59061,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59246,7 +59267,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59327,7 +59348,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ280">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR280">
         <v>1.96</v>
@@ -59452,7 +59473,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59530,7 +59551,7 @@
         <v>1.79</v>
       </c>
       <c r="AP281">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ281">
         <v>1.94</v>
@@ -60151,7 +60172,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ284">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR284">
         <v>1.6</v>
@@ -60354,7 +60375,7 @@
         <v>1.46</v>
       </c>
       <c r="AP285">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ285">
         <v>1.67</v>
@@ -60482,7 +60503,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60688,7 +60709,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -60769,7 +60790,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ287">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR287">
         <v>1.76</v>
@@ -60975,7 +60996,7 @@
         <v>2.19</v>
       </c>
       <c r="AQ288">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR288">
         <v>1.81</v>
@@ -61512,7 +61533,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61924,7 +61945,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62130,7 +62151,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62414,7 +62435,7 @@
         <v>1.2</v>
       </c>
       <c r="AP295">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ295">
         <v>1.13</v>
@@ -62542,7 +62563,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62623,7 +62644,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ296">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR296">
         <v>1.84</v>
@@ -62748,7 +62769,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -63032,10 +63053,10 @@
         <v>1.23</v>
       </c>
       <c r="AP298">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ298">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR298">
         <v>1.65</v>
@@ -63160,7 +63181,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -63241,7 +63262,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ299">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AR299">
         <v>1.43</v>
@@ -63444,7 +63465,7 @@
         <v>0.57</v>
       </c>
       <c r="AP300">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AQ300">
         <v>0.5</v>
@@ -63653,7 +63674,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ301">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR301">
         <v>1.59</v>
@@ -63856,10 +63877,10 @@
         <v>1.2</v>
       </c>
       <c r="AP302">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ302">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR302">
         <v>1.68</v>
@@ -64268,7 +64289,7 @@
         <v>1.57</v>
       </c>
       <c r="AP304">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ304">
         <v>1.67</v>
@@ -64474,10 +64495,10 @@
         <v>2.13</v>
       </c>
       <c r="AP305">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AQ305">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AR305">
         <v>1.84</v>
@@ -64602,7 +64623,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -64680,7 +64701,7 @@
         <v>1.07</v>
       </c>
       <c r="AP306">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ306">
         <v>1.13</v>
@@ -64889,7 +64910,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ307">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="AR307">
         <v>1.71</v>
@@ -65220,7 +65241,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65632,7 +65653,7 @@
         <v>298</v>
       </c>
       <c r="P311" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="Q311">
         <v>2.4</v>
@@ -65838,7 +65859,7 @@
         <v>299</v>
       </c>
       <c r="P312" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="Q312">
         <v>2.88</v>
@@ -66250,7 +66271,7 @@
         <v>301</v>
       </c>
       <c r="P314" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="Q314">
         <v>3.5</v>
@@ -66328,7 +66349,7 @@
         <v>1.87</v>
       </c>
       <c r="AP314">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AQ314">
         <v>1.94</v>
@@ -66456,7 +66477,7 @@
         <v>102</v>
       </c>
       <c r="P315" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="Q315">
         <v>2.38</v>
@@ -66537,7 +66558,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ315">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR315">
         <v>1.96</v>
@@ -66662,7 +66683,7 @@
         <v>302</v>
       </c>
       <c r="P316" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q316">
         <v>2.2</v>
@@ -66868,7 +66889,7 @@
         <v>93</v>
       </c>
       <c r="P317" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="Q317">
         <v>4</v>
@@ -67280,7 +67301,7 @@
         <v>303</v>
       </c>
       <c r="P319" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="Q319">
         <v>3.4</v>
@@ -67567,7 +67588,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ320">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR320">
         <v>1.42</v>
@@ -67643,6 +67664,1242 @@
       </c>
       <c r="BP320">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7465758</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F321">
+        <v>33</v>
+      </c>
+      <c r="G321" t="s">
+        <v>75</v>
+      </c>
+      <c r="H321" t="s">
+        <v>78</v>
+      </c>
+      <c r="I321">
+        <v>2</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>2</v>
+      </c>
+      <c r="L321">
+        <v>2</v>
+      </c>
+      <c r="M321">
+        <v>2</v>
+      </c>
+      <c r="N321">
+        <v>4</v>
+      </c>
+      <c r="O321" t="s">
+        <v>304</v>
+      </c>
+      <c r="P321" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q321">
+        <v>2.3</v>
+      </c>
+      <c r="R321">
+        <v>2.5</v>
+      </c>
+      <c r="S321">
+        <v>4</v>
+      </c>
+      <c r="T321">
+        <v>1.25</v>
+      </c>
+      <c r="U321">
+        <v>3.75</v>
+      </c>
+      <c r="V321">
+        <v>2.1</v>
+      </c>
+      <c r="W321">
+        <v>1.67</v>
+      </c>
+      <c r="X321">
+        <v>4.5</v>
+      </c>
+      <c r="Y321">
+        <v>1.18</v>
+      </c>
+      <c r="Z321">
+        <v>1.8</v>
+      </c>
+      <c r="AA321">
+        <v>4.2</v>
+      </c>
+      <c r="AB321">
+        <v>3.4</v>
+      </c>
+      <c r="AC321">
+        <v>1.01</v>
+      </c>
+      <c r="AD321">
+        <v>16.5</v>
+      </c>
+      <c r="AE321">
+        <v>1.1</v>
+      </c>
+      <c r="AF321">
+        <v>6</v>
+      </c>
+      <c r="AG321">
+        <v>1.4</v>
+      </c>
+      <c r="AH321">
+        <v>2.88</v>
+      </c>
+      <c r="AI321">
+        <v>1.44</v>
+      </c>
+      <c r="AJ321">
+        <v>2.63</v>
+      </c>
+      <c r="AK321">
+        <v>1.29</v>
+      </c>
+      <c r="AL321">
+        <v>1.22</v>
+      </c>
+      <c r="AM321">
+        <v>1.88</v>
+      </c>
+      <c r="AN321">
+        <v>1.19</v>
+      </c>
+      <c r="AO321">
+        <v>1.31</v>
+      </c>
+      <c r="AP321">
+        <v>1.18</v>
+      </c>
+      <c r="AQ321">
+        <v>1.29</v>
+      </c>
+      <c r="AR321">
+        <v>1.67</v>
+      </c>
+      <c r="AS321">
+        <v>1.37</v>
+      </c>
+      <c r="AT321">
+        <v>3.04</v>
+      </c>
+      <c r="AU321">
+        <v>6</v>
+      </c>
+      <c r="AV321">
+        <v>10</v>
+      </c>
+      <c r="AW321">
+        <v>9</v>
+      </c>
+      <c r="AX321">
+        <v>6</v>
+      </c>
+      <c r="AY321">
+        <v>15</v>
+      </c>
+      <c r="AZ321">
+        <v>16</v>
+      </c>
+      <c r="BA321">
+        <v>6</v>
+      </c>
+      <c r="BB321">
+        <v>7</v>
+      </c>
+      <c r="BC321">
+        <v>13</v>
+      </c>
+      <c r="BD321">
+        <v>1.64</v>
+      </c>
+      <c r="BE321">
+        <v>7</v>
+      </c>
+      <c r="BF321">
+        <v>2.45</v>
+      </c>
+      <c r="BG321">
+        <v>1.16</v>
+      </c>
+      <c r="BH321">
+        <v>4.4</v>
+      </c>
+      <c r="BI321">
+        <v>1.29</v>
+      </c>
+      <c r="BJ321">
+        <v>3.15</v>
+      </c>
+      <c r="BK321">
+        <v>1.48</v>
+      </c>
+      <c r="BL321">
+        <v>2.43</v>
+      </c>
+      <c r="BM321">
+        <v>1.75</v>
+      </c>
+      <c r="BN321">
+        <v>1.95</v>
+      </c>
+      <c r="BO321">
+        <v>2.15</v>
+      </c>
+      <c r="BP321">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="322" spans="1:68">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>7465757</v>
+      </c>
+      <c r="C322" t="s">
+        <v>68</v>
+      </c>
+      <c r="D322" t="s">
+        <v>69</v>
+      </c>
+      <c r="E322" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F322">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>74</v>
+      </c>
+      <c r="H322" t="s">
+        <v>80</v>
+      </c>
+      <c r="I322">
+        <v>1</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>1</v>
+      </c>
+      <c r="L322">
+        <v>2</v>
+      </c>
+      <c r="M322">
+        <v>1</v>
+      </c>
+      <c r="N322">
+        <v>3</v>
+      </c>
+      <c r="O322" t="s">
+        <v>305</v>
+      </c>
+      <c r="P322" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q322">
+        <v>3</v>
+      </c>
+      <c r="R322">
+        <v>2.25</v>
+      </c>
+      <c r="S322">
+        <v>3.25</v>
+      </c>
+      <c r="T322">
+        <v>1.36</v>
+      </c>
+      <c r="U322">
+        <v>3</v>
+      </c>
+      <c r="V322">
+        <v>2.63</v>
+      </c>
+      <c r="W322">
+        <v>1.44</v>
+      </c>
+      <c r="X322">
+        <v>7</v>
+      </c>
+      <c r="Y322">
+        <v>1.1</v>
+      </c>
+      <c r="Z322">
+        <v>2.35</v>
+      </c>
+      <c r="AA322">
+        <v>3.4</v>
+      </c>
+      <c r="AB322">
+        <v>2.7</v>
+      </c>
+      <c r="AC322">
+        <v>1.01</v>
+      </c>
+      <c r="AD322">
+        <v>11</v>
+      </c>
+      <c r="AE322">
+        <v>1.2</v>
+      </c>
+      <c r="AF322">
+        <v>4.2</v>
+      </c>
+      <c r="AG322">
+        <v>1.75</v>
+      </c>
+      <c r="AH322">
+        <v>2.05</v>
+      </c>
+      <c r="AI322">
+        <v>1.62</v>
+      </c>
+      <c r="AJ322">
+        <v>2.2</v>
+      </c>
+      <c r="AK322">
+        <v>1.43</v>
+      </c>
+      <c r="AL322">
+        <v>1.29</v>
+      </c>
+      <c r="AM322">
+        <v>1.53</v>
+      </c>
+      <c r="AN322">
+        <v>1.31</v>
+      </c>
+      <c r="AO322">
+        <v>1.25</v>
+      </c>
+      <c r="AP322">
+        <v>1.41</v>
+      </c>
+      <c r="AQ322">
+        <v>1.18</v>
+      </c>
+      <c r="AR322">
+        <v>1.39</v>
+      </c>
+      <c r="AS322">
+        <v>1.39</v>
+      </c>
+      <c r="AT322">
+        <v>2.78</v>
+      </c>
+      <c r="AU322">
+        <v>4</v>
+      </c>
+      <c r="AV322">
+        <v>10</v>
+      </c>
+      <c r="AW322">
+        <v>7</v>
+      </c>
+      <c r="AX322">
+        <v>19</v>
+      </c>
+      <c r="AY322">
+        <v>11</v>
+      </c>
+      <c r="AZ322">
+        <v>29</v>
+      </c>
+      <c r="BA322">
+        <v>6</v>
+      </c>
+      <c r="BB322">
+        <v>10</v>
+      </c>
+      <c r="BC322">
+        <v>16</v>
+      </c>
+      <c r="BD322">
+        <v>1.98</v>
+      </c>
+      <c r="BE322">
+        <v>6.5</v>
+      </c>
+      <c r="BF322">
+        <v>1.98</v>
+      </c>
+      <c r="BG322">
+        <v>1.27</v>
+      </c>
+      <c r="BH322">
+        <v>3.3</v>
+      </c>
+      <c r="BI322">
+        <v>1.48</v>
+      </c>
+      <c r="BJ322">
+        <v>2.48</v>
+      </c>
+      <c r="BK322">
+        <v>1.76</v>
+      </c>
+      <c r="BL322">
+        <v>1.94</v>
+      </c>
+      <c r="BM322">
+        <v>2.17</v>
+      </c>
+      <c r="BN322">
+        <v>1.58</v>
+      </c>
+      <c r="BO322">
+        <v>2.75</v>
+      </c>
+      <c r="BP322">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="323" spans="1:68">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>7465754</v>
+      </c>
+      <c r="C323" t="s">
+        <v>68</v>
+      </c>
+      <c r="D323" t="s">
+        <v>69</v>
+      </c>
+      <c r="E323" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F323">
+        <v>33</v>
+      </c>
+      <c r="G323" t="s">
+        <v>88</v>
+      </c>
+      <c r="H323" t="s">
+        <v>79</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>0</v>
+      </c>
+      <c r="K323">
+        <v>0</v>
+      </c>
+      <c r="L323">
+        <v>4</v>
+      </c>
+      <c r="M323">
+        <v>0</v>
+      </c>
+      <c r="N323">
+        <v>4</v>
+      </c>
+      <c r="O323" t="s">
+        <v>306</v>
+      </c>
+      <c r="P323" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q323">
+        <v>1.57</v>
+      </c>
+      <c r="R323">
+        <v>3.2</v>
+      </c>
+      <c r="S323">
+        <v>8</v>
+      </c>
+      <c r="T323">
+        <v>1.17</v>
+      </c>
+      <c r="U323">
+        <v>5</v>
+      </c>
+      <c r="V323">
+        <v>1.8</v>
+      </c>
+      <c r="W323">
+        <v>1.91</v>
+      </c>
+      <c r="X323">
+        <v>3.5</v>
+      </c>
+      <c r="Y323">
+        <v>1.29</v>
+      </c>
+      <c r="Z323">
+        <v>1.2</v>
+      </c>
+      <c r="AA323">
+        <v>7</v>
+      </c>
+      <c r="AB323">
+        <v>9.5</v>
+      </c>
+      <c r="AC323">
+        <v>1</v>
+      </c>
+      <c r="AD323">
+        <v>23</v>
+      </c>
+      <c r="AE323">
+        <v>1.02</v>
+      </c>
+      <c r="AF323">
+        <v>10</v>
+      </c>
+      <c r="AG323">
+        <v>1.25</v>
+      </c>
+      <c r="AH323">
+        <v>4</v>
+      </c>
+      <c r="AI323">
+        <v>1.62</v>
+      </c>
+      <c r="AJ323">
+        <v>2.2</v>
+      </c>
+      <c r="AK323">
+        <v>1.04</v>
+      </c>
+      <c r="AL323">
+        <v>1.09</v>
+      </c>
+      <c r="AM323">
+        <v>4.4</v>
+      </c>
+      <c r="AN323">
+        <v>2.44</v>
+      </c>
+      <c r="AO323">
+        <v>0.93</v>
+      </c>
+      <c r="AP323">
+        <v>2.47</v>
+      </c>
+      <c r="AQ323">
+        <v>0.88</v>
+      </c>
+      <c r="AR323">
+        <v>1.84</v>
+      </c>
+      <c r="AS323">
+        <v>1.31</v>
+      </c>
+      <c r="AT323">
+        <v>3.15</v>
+      </c>
+      <c r="AU323">
+        <v>8</v>
+      </c>
+      <c r="AV323">
+        <v>5</v>
+      </c>
+      <c r="AW323">
+        <v>9</v>
+      </c>
+      <c r="AX323">
+        <v>10</v>
+      </c>
+      <c r="AY323">
+        <v>17</v>
+      </c>
+      <c r="AZ323">
+        <v>15</v>
+      </c>
+      <c r="BA323">
+        <v>3</v>
+      </c>
+      <c r="BB323">
+        <v>5</v>
+      </c>
+      <c r="BC323">
+        <v>8</v>
+      </c>
+      <c r="BD323">
+        <v>1.2</v>
+      </c>
+      <c r="BE323">
+        <v>9</v>
+      </c>
+      <c r="BF323">
+        <v>4.8</v>
+      </c>
+      <c r="BG323">
+        <v>1.21</v>
+      </c>
+      <c r="BH323">
+        <v>3.8</v>
+      </c>
+      <c r="BI323">
+        <v>1.38</v>
+      </c>
+      <c r="BJ323">
+        <v>2.8</v>
+      </c>
+      <c r="BK323">
+        <v>1.61</v>
+      </c>
+      <c r="BL323">
+        <v>2.15</v>
+      </c>
+      <c r="BM323">
+        <v>1.95</v>
+      </c>
+      <c r="BN323">
+        <v>1.75</v>
+      </c>
+      <c r="BO323">
+        <v>2.4</v>
+      </c>
+      <c r="BP323">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="324" spans="1:68">
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>7465753</v>
+      </c>
+      <c r="C324" t="s">
+        <v>68</v>
+      </c>
+      <c r="D324" t="s">
+        <v>69</v>
+      </c>
+      <c r="E324" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F324">
+        <v>33</v>
+      </c>
+      <c r="G324" t="s">
+        <v>71</v>
+      </c>
+      <c r="H324" t="s">
+        <v>87</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+      <c r="J324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>1</v>
+      </c>
+      <c r="L324">
+        <v>3</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
+      </c>
+      <c r="N324">
+        <v>3</v>
+      </c>
+      <c r="O324" t="s">
+        <v>307</v>
+      </c>
+      <c r="P324" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q324">
+        <v>3.35</v>
+      </c>
+      <c r="R324">
+        <v>2.15</v>
+      </c>
+      <c r="S324">
+        <v>2.8</v>
+      </c>
+      <c r="T324">
+        <v>1.33</v>
+      </c>
+      <c r="U324">
+        <v>3</v>
+      </c>
+      <c r="V324">
+        <v>2.45</v>
+      </c>
+      <c r="W324">
+        <v>1.48</v>
+      </c>
+      <c r="X324">
+        <v>5.5</v>
+      </c>
+      <c r="Y324">
+        <v>1.08</v>
+      </c>
+      <c r="Z324">
+        <v>2.95</v>
+      </c>
+      <c r="AA324">
+        <v>3.4</v>
+      </c>
+      <c r="AB324">
+        <v>2.25</v>
+      </c>
+      <c r="AC324">
+        <v>1.05</v>
+      </c>
+      <c r="AD324">
+        <v>9.5</v>
+      </c>
+      <c r="AE324">
+        <v>1.22</v>
+      </c>
+      <c r="AF324">
+        <v>4</v>
+      </c>
+      <c r="AG324">
+        <v>1.7</v>
+      </c>
+      <c r="AH324">
+        <v>2.1</v>
+      </c>
+      <c r="AI324">
+        <v>1.55</v>
+      </c>
+      <c r="AJ324">
+        <v>2.25</v>
+      </c>
+      <c r="AK324">
+        <v>1.6</v>
+      </c>
+      <c r="AL324">
+        <v>1.25</v>
+      </c>
+      <c r="AM324">
+        <v>1.38</v>
+      </c>
+      <c r="AN324">
+        <v>1.19</v>
+      </c>
+      <c r="AO324">
+        <v>2</v>
+      </c>
+      <c r="AP324">
+        <v>1.29</v>
+      </c>
+      <c r="AQ324">
+        <v>1.88</v>
+      </c>
+      <c r="AR324">
+        <v>1.7</v>
+      </c>
+      <c r="AS324">
+        <v>1.86</v>
+      </c>
+      <c r="AT324">
+        <v>3.56</v>
+      </c>
+      <c r="AU324">
+        <v>6</v>
+      </c>
+      <c r="AV324">
+        <v>6</v>
+      </c>
+      <c r="AW324">
+        <v>6</v>
+      </c>
+      <c r="AX324">
+        <v>13</v>
+      </c>
+      <c r="AY324">
+        <v>12</v>
+      </c>
+      <c r="AZ324">
+        <v>19</v>
+      </c>
+      <c r="BA324">
+        <v>4</v>
+      </c>
+      <c r="BB324">
+        <v>8</v>
+      </c>
+      <c r="BC324">
+        <v>12</v>
+      </c>
+      <c r="BD324">
+        <v>2.18</v>
+      </c>
+      <c r="BE324">
+        <v>6.5</v>
+      </c>
+      <c r="BF324">
+        <v>1.82</v>
+      </c>
+      <c r="BG324">
+        <v>1.28</v>
+      </c>
+      <c r="BH324">
+        <v>3.3</v>
+      </c>
+      <c r="BI324">
+        <v>1.49</v>
+      </c>
+      <c r="BJ324">
+        <v>2.4</v>
+      </c>
+      <c r="BK324">
+        <v>1.79</v>
+      </c>
+      <c r="BL324">
+        <v>1.9</v>
+      </c>
+      <c r="BM324">
+        <v>2.23</v>
+      </c>
+      <c r="BN324">
+        <v>1.56</v>
+      </c>
+      <c r="BO324">
+        <v>2.9</v>
+      </c>
+      <c r="BP324">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="325" spans="1:68">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>7465752</v>
+      </c>
+      <c r="C325" t="s">
+        <v>68</v>
+      </c>
+      <c r="D325" t="s">
+        <v>69</v>
+      </c>
+      <c r="E325" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F325">
+        <v>33</v>
+      </c>
+      <c r="G325" t="s">
+        <v>86</v>
+      </c>
+      <c r="H325" t="s">
+        <v>89</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
+      </c>
+      <c r="L325">
+        <v>3</v>
+      </c>
+      <c r="M325">
+        <v>0</v>
+      </c>
+      <c r="N325">
+        <v>3</v>
+      </c>
+      <c r="O325" t="s">
+        <v>308</v>
+      </c>
+      <c r="P325" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q325">
+        <v>2.25</v>
+      </c>
+      <c r="R325">
+        <v>2.4</v>
+      </c>
+      <c r="S325">
+        <v>4.5</v>
+      </c>
+      <c r="T325">
+        <v>1.29</v>
+      </c>
+      <c r="U325">
+        <v>3.5</v>
+      </c>
+      <c r="V325">
+        <v>2.38</v>
+      </c>
+      <c r="W325">
+        <v>1.53</v>
+      </c>
+      <c r="X325">
+        <v>5.5</v>
+      </c>
+      <c r="Y325">
+        <v>1.14</v>
+      </c>
+      <c r="Z325">
+        <v>1.7</v>
+      </c>
+      <c r="AA325">
+        <v>4.1</v>
+      </c>
+      <c r="AB325">
+        <v>4</v>
+      </c>
+      <c r="AC325">
+        <v>1.02</v>
+      </c>
+      <c r="AD325">
+        <v>13.4</v>
+      </c>
+      <c r="AE325">
+        <v>1.16</v>
+      </c>
+      <c r="AF325">
+        <v>4.7</v>
+      </c>
+      <c r="AG325">
+        <v>1.57</v>
+      </c>
+      <c r="AH325">
+        <v>2.35</v>
+      </c>
+      <c r="AI325">
+        <v>1.57</v>
+      </c>
+      <c r="AJ325">
+        <v>2.25</v>
+      </c>
+      <c r="AK325">
+        <v>1.23</v>
+      </c>
+      <c r="AL325">
+        <v>1.23</v>
+      </c>
+      <c r="AM325">
+        <v>2</v>
+      </c>
+      <c r="AN325">
+        <v>2.07</v>
+      </c>
+      <c r="AO325">
+        <v>0.75</v>
+      </c>
+      <c r="AP325">
+        <v>2.13</v>
+      </c>
+      <c r="AQ325">
+        <v>0.71</v>
+      </c>
+      <c r="AR325">
+        <v>1.66</v>
+      </c>
+      <c r="AS325">
+        <v>1.48</v>
+      </c>
+      <c r="AT325">
+        <v>3.14</v>
+      </c>
+      <c r="AU325">
+        <v>7</v>
+      </c>
+      <c r="AV325">
+        <v>0</v>
+      </c>
+      <c r="AW325">
+        <v>10</v>
+      </c>
+      <c r="AX325">
+        <v>5</v>
+      </c>
+      <c r="AY325">
+        <v>17</v>
+      </c>
+      <c r="AZ325">
+        <v>5</v>
+      </c>
+      <c r="BA325">
+        <v>5</v>
+      </c>
+      <c r="BB325">
+        <v>7</v>
+      </c>
+      <c r="BC325">
+        <v>12</v>
+      </c>
+      <c r="BD325">
+        <v>1.5</v>
+      </c>
+      <c r="BE325">
+        <v>6.75</v>
+      </c>
+      <c r="BF325">
+        <v>2.8</v>
+      </c>
+      <c r="BG325">
+        <v>1.27</v>
+      </c>
+      <c r="BH325">
+        <v>3.3</v>
+      </c>
+      <c r="BI325">
+        <v>1.48</v>
+      </c>
+      <c r="BJ325">
+        <v>2.48</v>
+      </c>
+      <c r="BK325">
+        <v>1.76</v>
+      </c>
+      <c r="BL325">
+        <v>1.93</v>
+      </c>
+      <c r="BM325">
+        <v>2.18</v>
+      </c>
+      <c r="BN325">
+        <v>1.58</v>
+      </c>
+      <c r="BO325">
+        <v>2.75</v>
+      </c>
+      <c r="BP325">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="326" spans="1:68">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>7465756</v>
+      </c>
+      <c r="C326" t="s">
+        <v>68</v>
+      </c>
+      <c r="D326" t="s">
+        <v>69</v>
+      </c>
+      <c r="E326" s="2">
+        <v>45751.625</v>
+      </c>
+      <c r="F326">
+        <v>33</v>
+      </c>
+      <c r="G326" t="s">
+        <v>73</v>
+      </c>
+      <c r="H326" t="s">
+        <v>83</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>1</v>
+      </c>
+      <c r="L326">
+        <v>1</v>
+      </c>
+      <c r="M326">
+        <v>2</v>
+      </c>
+      <c r="N326">
+        <v>3</v>
+      </c>
+      <c r="O326" t="s">
+        <v>309</v>
+      </c>
+      <c r="P326" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q326">
+        <v>4.2</v>
+      </c>
+      <c r="R326">
+        <v>2.4</v>
+      </c>
+      <c r="S326">
+        <v>2.15</v>
+      </c>
+      <c r="T326">
+        <v>1.25</v>
+      </c>
+      <c r="U326">
+        <v>3.5</v>
+      </c>
+      <c r="V326">
+        <v>2.2</v>
+      </c>
+      <c r="W326">
+        <v>1.6</v>
+      </c>
+      <c r="X326">
+        <v>4.8</v>
+      </c>
+      <c r="Y326">
+        <v>1.13</v>
+      </c>
+      <c r="Z326">
+        <v>4.2</v>
+      </c>
+      <c r="AA326">
+        <v>4</v>
+      </c>
+      <c r="AB326">
+        <v>1.73</v>
+      </c>
+      <c r="AC326">
+        <v>1.01</v>
+      </c>
+      <c r="AD326">
+        <v>13</v>
+      </c>
+      <c r="AE326">
+        <v>1.18</v>
+      </c>
+      <c r="AF326">
+        <v>4.75</v>
+      </c>
+      <c r="AG326">
+        <v>1.53</v>
+      </c>
+      <c r="AH326">
+        <v>2.45</v>
+      </c>
+      <c r="AI326">
+        <v>1.5</v>
+      </c>
+      <c r="AJ326">
+        <v>2.35</v>
+      </c>
+      <c r="AK326">
+        <v>2.05</v>
+      </c>
+      <c r="AL326">
+        <v>1.18</v>
+      </c>
+      <c r="AM326">
+        <v>1.22</v>
+      </c>
+      <c r="AN326">
+        <v>1.56</v>
+      </c>
+      <c r="AO326">
+        <v>1.44</v>
+      </c>
+      <c r="AP326">
+        <v>1.47</v>
+      </c>
+      <c r="AQ326">
+        <v>1.53</v>
+      </c>
+      <c r="AR326">
+        <v>1.62</v>
+      </c>
+      <c r="AS326">
+        <v>1.73</v>
+      </c>
+      <c r="AT326">
+        <v>3.35</v>
+      </c>
+      <c r="AU326">
+        <v>4</v>
+      </c>
+      <c r="AV326">
+        <v>7</v>
+      </c>
+      <c r="AW326">
+        <v>5</v>
+      </c>
+      <c r="AX326">
+        <v>6</v>
+      </c>
+      <c r="AY326">
+        <v>9</v>
+      </c>
+      <c r="AZ326">
+        <v>13</v>
+      </c>
+      <c r="BA326">
+        <v>2</v>
+      </c>
+      <c r="BB326">
+        <v>5</v>
+      </c>
+      <c r="BC326">
+        <v>7</v>
+      </c>
+      <c r="BD326">
+        <v>2.7</v>
+      </c>
+      <c r="BE326">
+        <v>6.75</v>
+      </c>
+      <c r="BF326">
+        <v>1.54</v>
+      </c>
+      <c r="BG326">
+        <v>1.29</v>
+      </c>
+      <c r="BH326">
+        <v>3.15</v>
+      </c>
+      <c r="BI326">
+        <v>1.52</v>
+      </c>
+      <c r="BJ326">
+        <v>2.33</v>
+      </c>
+      <c r="BK326">
+        <v>1.83</v>
+      </c>
+      <c r="BL326">
+        <v>1.85</v>
+      </c>
+      <c r="BM326">
+        <v>2.3</v>
+      </c>
+      <c r="BN326">
+        <v>1.54</v>
+      </c>
+      <c r="BO326">
+        <v>2.95</v>
+      </c>
+      <c r="BP326">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="460">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -946,6 +946,15 @@
     <t>['35']</t>
   </si>
   <si>
+    <t>['1', '18']</t>
+  </si>
+  <si>
+    <t>['40', '67']</t>
+  </si>
+  <si>
+    <t>['25', '64']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1383,6 +1392,9 @@
   <si>
     <t>['86', '90+2']</t>
   </si>
+  <si>
+    <t>['38', '90+7']</t>
+  </si>
 </sst>
 </file>
 
@@ -1743,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP326"/>
+  <dimension ref="A1:BP329"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2205,7 +2217,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2411,7 +2423,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2489,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -2823,7 +2835,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -3029,7 +3041,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3110,7 +3122,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3235,7 +3247,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3441,7 +3453,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3519,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ9">
         <v>1.94</v>
@@ -3728,7 +3740,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ10">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3853,7 +3865,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4265,7 +4277,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4346,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4883,7 +4895,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -5167,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ17">
         <v>1.29</v>
@@ -5707,7 +5719,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6609,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ24">
         <v>0.5600000000000001</v>
@@ -6737,7 +6749,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6815,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ25">
         <v>0.5</v>
@@ -6943,7 +6955,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7149,7 +7161,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7561,7 +7573,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7642,7 +7654,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ29">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>2.13</v>
@@ -7973,7 +7985,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8054,7 +8066,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR31">
         <v>2.38</v>
@@ -8260,7 +8272,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR32">
         <v>1.27</v>
@@ -8591,7 +8603,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8797,7 +8809,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -9081,7 +9093,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ36">
         <v>1.18</v>
@@ -9415,7 +9427,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9621,7 +9633,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -10033,7 +10045,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10317,10 +10329,10 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR42">
         <v>1.53</v>
@@ -10857,7 +10869,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11063,7 +11075,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11475,7 +11487,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11887,7 +11899,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -11965,7 +11977,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ50">
         <v>1.19</v>
@@ -12093,7 +12105,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12174,7 +12186,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ51">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -12299,7 +12311,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12380,7 +12392,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ52">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.79</v>
@@ -12583,7 +12595,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
         <v>1.67</v>
@@ -12792,7 +12804,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ54">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.99</v>
@@ -13123,7 +13135,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13407,7 +13419,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ57">
         <v>0.5600000000000001</v>
@@ -13535,7 +13547,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -14153,7 +14165,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14359,7 +14371,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14565,7 +14577,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -14643,7 +14655,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ63">
         <v>1.94</v>
@@ -14849,7 +14861,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ64">
         <v>1.94</v>
@@ -15058,7 +15070,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ65">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR65">
         <v>1.41</v>
@@ -15183,7 +15195,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15595,7 +15607,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15801,7 +15813,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -15882,7 +15894,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -16007,7 +16019,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16213,7 +16225,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16419,7 +16431,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16625,7 +16637,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16831,7 +16843,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -17037,7 +17049,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17324,7 +17336,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ76">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR76">
         <v>1.42</v>
@@ -17655,7 +17667,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17733,7 +17745,7 @@
         <v>2.33</v>
       </c>
       <c r="AP78">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ78">
         <v>1</v>
@@ -17861,7 +17873,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18273,7 +18285,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18685,7 +18697,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18891,7 +18903,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -19384,7 +19396,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19509,7 +19521,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19590,7 +19602,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ87">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR87">
         <v>1.95</v>
@@ -20127,7 +20139,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20205,7 +20217,7 @@
         <v>1.33</v>
       </c>
       <c r="AP90">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ90">
         <v>1.13</v>
@@ -20411,7 +20423,7 @@
         <v>2</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ91">
         <v>0.71</v>
@@ -20539,7 +20551,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20951,7 +20963,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21157,7 +21169,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21363,7 +21375,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21444,7 +21456,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ96">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR96">
         <v>1.22</v>
@@ -21569,7 +21581,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21981,7 +21993,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22265,7 +22277,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ100">
         <v>1</v>
@@ -22393,7 +22405,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22599,7 +22611,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -22677,7 +22689,7 @@
         <v>1.8</v>
       </c>
       <c r="AP102">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ102">
         <v>0.88</v>
@@ -22886,7 +22898,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ103">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -23011,7 +23023,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23501,10 +23513,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ106">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23710,7 +23722,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ107">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR107">
         <v>1.77</v>
@@ -24247,7 +24259,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24453,7 +24465,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24659,7 +24671,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25152,7 +25164,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ114">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR114">
         <v>1.84</v>
@@ -25277,7 +25289,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25483,7 +25495,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25689,7 +25701,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25895,7 +25907,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26307,7 +26319,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26388,7 +26400,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ120">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -26513,7 +26525,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26719,7 +26731,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26925,7 +26937,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27131,7 +27143,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27209,7 +27221,7 @@
         <v>1.67</v>
       </c>
       <c r="AP124">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ124">
         <v>1.47</v>
@@ -27337,7 +27349,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27827,10 +27839,10 @@
         <v>0.86</v>
       </c>
       <c r="AP127">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ127">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.8</v>
@@ -27955,7 +27967,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28239,7 +28251,7 @@
         <v>1.33</v>
       </c>
       <c r="AP129">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ129">
         <v>1.53</v>
@@ -28367,7 +28379,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28573,7 +28585,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29603,7 +29615,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -29890,7 +29902,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR137">
         <v>1.83</v>
@@ -30508,7 +30520,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR140">
         <v>1.77</v>
@@ -31457,7 +31469,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31663,7 +31675,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31869,7 +31881,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32075,7 +32087,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32156,7 +32168,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ148">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.46</v>
@@ -32362,7 +32374,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ149">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR149">
         <v>1.58</v>
@@ -32487,7 +32499,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32565,10 +32577,10 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ150">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR150">
         <v>1.63</v>
@@ -32693,7 +32705,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -32771,7 +32783,7 @@
         <v>1.57</v>
       </c>
       <c r="AP151">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ151">
         <v>1.53</v>
@@ -32977,7 +32989,7 @@
         <v>0.5</v>
       </c>
       <c r="AP152">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ152">
         <v>0.5600000000000001</v>
@@ -33105,7 +33117,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33311,7 +33323,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33517,7 +33529,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34213,7 +34225,7 @@
         <v>1.43</v>
       </c>
       <c r="AP158">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ158">
         <v>1.67</v>
@@ -34547,7 +34559,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34959,7 +34971,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35783,7 +35795,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36479,7 +36491,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ169">
         <v>1.18</v>
@@ -36607,7 +36619,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36685,7 +36697,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ170">
         <v>1.47</v>
@@ -36813,7 +36825,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -37225,7 +37237,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -37512,7 +37524,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ174">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR174">
         <v>2</v>
@@ -37921,7 +37933,7 @@
         <v>1.63</v>
       </c>
       <c r="AP176">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ176">
         <v>1.31</v>
@@ -38049,7 +38061,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38255,7 +38267,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38667,7 +38679,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38748,7 +38760,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ180">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR180">
         <v>1.44</v>
@@ -38873,7 +38885,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -38954,7 +38966,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ181">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR181">
         <v>1.56</v>
@@ -39491,7 +39503,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39697,7 +39709,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39903,7 +39915,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -39981,7 +39993,7 @@
         <v>2.11</v>
       </c>
       <c r="AP186">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ186">
         <v>1.88</v>
@@ -40521,7 +40533,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40805,7 +40817,7 @@
         <v>1.33</v>
       </c>
       <c r="AP190">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ190">
         <v>0.88</v>
@@ -41139,7 +41151,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41345,7 +41357,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41551,7 +41563,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41757,7 +41769,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41838,7 +41850,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ195">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR195">
         <v>1.91</v>
@@ -41963,7 +41975,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -42662,7 +42674,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ199">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR199">
         <v>1.72</v>
@@ -42993,7 +43005,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43074,7 +43086,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ201">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.61</v>
@@ -43611,7 +43623,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -44023,7 +44035,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44229,7 +44241,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44516,7 +44528,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ208">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR208">
         <v>1.58</v>
@@ -44641,7 +44653,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -44722,7 +44734,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ209">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR209">
         <v>1.37</v>
@@ -45053,7 +45065,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45877,7 +45889,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -45958,7 +45970,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ215">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR215">
         <v>1.65</v>
@@ -46495,7 +46507,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46701,7 +46713,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46907,7 +46919,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -47603,7 +47615,7 @@
         <v>2.11</v>
       </c>
       <c r="AP223">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ223">
         <v>1.94</v>
@@ -47809,7 +47821,7 @@
         <v>0.5</v>
       </c>
       <c r="AP224">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ224">
         <v>0.5600000000000001</v>
@@ -48427,7 +48439,7 @@
         <v>1.27</v>
       </c>
       <c r="AP227">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ227">
         <v>1.29</v>
@@ -48633,7 +48645,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ228">
         <v>0.5</v>
@@ -48761,7 +48773,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49048,7 +49060,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ230">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR230">
         <v>1.75</v>
@@ -49379,7 +49391,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -49666,7 +49678,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ233">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR233">
         <v>1.81</v>
@@ -49869,7 +49881,7 @@
         <v>1.73</v>
       </c>
       <c r="AP234">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ234">
         <v>1.94</v>
@@ -49997,7 +50009,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50203,7 +50215,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50284,7 +50296,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ236">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR236">
         <v>1.7</v>
@@ -50615,7 +50627,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50693,7 +50705,7 @@
         <v>1</v>
       </c>
       <c r="AP238">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ238">
         <v>1.67</v>
@@ -51105,7 +51117,7 @@
         <v>1.55</v>
       </c>
       <c r="AP240">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ240">
         <v>1.31</v>
@@ -51439,7 +51451,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51645,7 +51657,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51851,7 +51863,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -51929,7 +51941,7 @@
         <v>1.58</v>
       </c>
       <c r="AP244">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ244">
         <v>1.47</v>
@@ -52469,7 +52481,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52881,7 +52893,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -53168,7 +53180,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ250">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR250">
         <v>1.74</v>
@@ -53577,10 +53589,10 @@
         <v>0.92</v>
       </c>
       <c r="AP252">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ252">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR252">
         <v>1.77</v>
@@ -53786,7 +53798,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ253">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR253">
         <v>1.74</v>
@@ -54117,7 +54129,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -54813,7 +54825,7 @@
         <v>1.15</v>
       </c>
       <c r="AP258">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ258">
         <v>1.29</v>
@@ -55019,7 +55031,7 @@
         <v>1</v>
       </c>
       <c r="AP259">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ259">
         <v>1</v>
@@ -55353,7 +55365,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55559,7 +55571,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55765,7 +55777,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55971,7 +55983,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56177,7 +56189,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56383,7 +56395,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56589,7 +56601,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56795,7 +56807,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -56873,7 +56885,7 @@
         <v>1.83</v>
       </c>
       <c r="AP268">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ268">
         <v>1.94</v>
@@ -57207,7 +57219,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57413,7 +57425,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57825,7 +57837,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58237,7 +58249,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58443,7 +58455,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58524,7 +58536,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ276">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR276">
         <v>1.89</v>
@@ -58649,7 +58661,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58730,7 +58742,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ277">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR277">
         <v>1.69</v>
@@ -58855,7 +58867,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58936,7 +58948,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ278">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR278">
         <v>1.75</v>
@@ -59061,7 +59073,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59267,7 +59279,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59473,7 +59485,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -60503,7 +60515,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60709,7 +60721,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -60787,7 +60799,7 @@
         <v>2.07</v>
       </c>
       <c r="AP287">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ287">
         <v>1.88</v>
@@ -60993,7 +61005,7 @@
         <v>1.43</v>
       </c>
       <c r="AP288">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ288">
         <v>1.53</v>
@@ -61199,7 +61211,7 @@
         <v>0.57</v>
       </c>
       <c r="AP289">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ289">
         <v>0.5600000000000001</v>
@@ -61533,7 +61545,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61945,7 +61957,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62151,7 +62163,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62438,7 +62450,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ295">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AR295">
         <v>1.86</v>
@@ -62563,7 +62575,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62769,7 +62781,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -63181,7 +63193,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -63671,7 +63683,7 @@
         <v>0.93</v>
       </c>
       <c r="AP301">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ301">
         <v>0.88</v>
@@ -64086,7 +64098,7 @@
         <v>2</v>
       </c>
       <c r="AQ303">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR303">
         <v>1.78</v>
@@ -64623,7 +64635,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -64907,7 +64919,7 @@
         <v>0.8</v>
       </c>
       <c r="AP307">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AQ307">
         <v>0.71</v>
@@ -65113,7 +65125,7 @@
         <v>0.53</v>
       </c>
       <c r="AP308">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AQ308">
         <v>0.5600000000000001</v>
@@ -65241,7 +65253,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65322,7 +65334,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ309">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR309">
         <v>1.59</v>
@@ -65653,7 +65665,7 @@
         <v>298</v>
       </c>
       <c r="P311" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="Q311">
         <v>2.4</v>
@@ -65859,7 +65871,7 @@
         <v>299</v>
       </c>
       <c r="P312" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Q312">
         <v>2.88</v>
@@ -66271,7 +66283,7 @@
         <v>301</v>
       </c>
       <c r="P314" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="Q314">
         <v>3.5</v>
@@ -66477,7 +66489,7 @@
         <v>102</v>
       </c>
       <c r="P315" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="Q315">
         <v>2.38</v>
@@ -66683,7 +66695,7 @@
         <v>302</v>
       </c>
       <c r="P316" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q316">
         <v>2.2</v>
@@ -66889,7 +66901,7 @@
         <v>93</v>
       </c>
       <c r="P317" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="Q317">
         <v>4</v>
@@ -67301,7 +67313,7 @@
         <v>303</v>
       </c>
       <c r="P319" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="Q319">
         <v>3.4</v>
@@ -67713,7 +67725,7 @@
         <v>304</v>
       </c>
       <c r="P321" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="Q321">
         <v>2.3</v>
@@ -68743,7 +68755,7 @@
         <v>309</v>
       </c>
       <c r="P326" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Q326">
         <v>4.2</v>
@@ -68900,6 +68912,624 @@
       </c>
       <c r="BP326">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="327" spans="1:68">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>7465759</v>
+      </c>
+      <c r="C327" t="s">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>69</v>
+      </c>
+      <c r="E327" s="2">
+        <v>45752.47916666666</v>
+      </c>
+      <c r="F327">
+        <v>33</v>
+      </c>
+      <c r="G327" t="s">
+        <v>72</v>
+      </c>
+      <c r="H327" t="s">
+        <v>81</v>
+      </c>
+      <c r="I327">
+        <v>2</v>
+      </c>
+      <c r="J327">
+        <v>1</v>
+      </c>
+      <c r="K327">
+        <v>3</v>
+      </c>
+      <c r="L327">
+        <v>2</v>
+      </c>
+      <c r="M327">
+        <v>2</v>
+      </c>
+      <c r="N327">
+        <v>4</v>
+      </c>
+      <c r="O327" t="s">
+        <v>310</v>
+      </c>
+      <c r="P327" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q327">
+        <v>3.25</v>
+      </c>
+      <c r="R327">
+        <v>2.25</v>
+      </c>
+      <c r="S327">
+        <v>3.1</v>
+      </c>
+      <c r="T327">
+        <v>1.36</v>
+      </c>
+      <c r="U327">
+        <v>3</v>
+      </c>
+      <c r="V327">
+        <v>2.63</v>
+      </c>
+      <c r="W327">
+        <v>1.44</v>
+      </c>
+      <c r="X327">
+        <v>7</v>
+      </c>
+      <c r="Y327">
+        <v>1.1</v>
+      </c>
+      <c r="Z327">
+        <v>2.76</v>
+      </c>
+      <c r="AA327">
+        <v>3.37</v>
+      </c>
+      <c r="AB327">
+        <v>2.53</v>
+      </c>
+      <c r="AC327">
+        <v>0</v>
+      </c>
+      <c r="AD327">
+        <v>0</v>
+      </c>
+      <c r="AE327">
+        <v>1.14</v>
+      </c>
+      <c r="AF327">
+        <v>4.33</v>
+      </c>
+      <c r="AG327">
+        <v>1.71</v>
+      </c>
+      <c r="AH327">
+        <v>2.04</v>
+      </c>
+      <c r="AI327">
+        <v>1.62</v>
+      </c>
+      <c r="AJ327">
+        <v>2.2</v>
+      </c>
+      <c r="AK327">
+        <v>1.66</v>
+      </c>
+      <c r="AL327">
+        <v>1.31</v>
+      </c>
+      <c r="AM327">
+        <v>1.4</v>
+      </c>
+      <c r="AN327">
+        <v>1.56</v>
+      </c>
+      <c r="AO327">
+        <v>1.13</v>
+      </c>
+      <c r="AP327">
+        <v>1.53</v>
+      </c>
+      <c r="AQ327">
+        <v>1.12</v>
+      </c>
+      <c r="AR327">
+        <v>1.58</v>
+      </c>
+      <c r="AS327">
+        <v>1.55</v>
+      </c>
+      <c r="AT327">
+        <v>3.13</v>
+      </c>
+      <c r="AU327">
+        <v>-1</v>
+      </c>
+      <c r="AV327">
+        <v>-1</v>
+      </c>
+      <c r="AW327">
+        <v>-1</v>
+      </c>
+      <c r="AX327">
+        <v>-1</v>
+      </c>
+      <c r="AY327">
+        <v>-1</v>
+      </c>
+      <c r="AZ327">
+        <v>-1</v>
+      </c>
+      <c r="BA327">
+        <v>-1</v>
+      </c>
+      <c r="BB327">
+        <v>-1</v>
+      </c>
+      <c r="BC327">
+        <v>-1</v>
+      </c>
+      <c r="BD327">
+        <v>2.12</v>
+      </c>
+      <c r="BE327">
+        <v>6.45</v>
+      </c>
+      <c r="BF327">
+        <v>2.09</v>
+      </c>
+      <c r="BG327">
+        <v>1.19</v>
+      </c>
+      <c r="BH327">
+        <v>3.82</v>
+      </c>
+      <c r="BI327">
+        <v>1.39</v>
+      </c>
+      <c r="BJ327">
+        <v>2.67</v>
+      </c>
+      <c r="BK327">
+        <v>1.72</v>
+      </c>
+      <c r="BL327">
+        <v>2.1</v>
+      </c>
+      <c r="BM327">
+        <v>2.14</v>
+      </c>
+      <c r="BN327">
+        <v>1.69</v>
+      </c>
+      <c r="BO327">
+        <v>2.78</v>
+      </c>
+      <c r="BP327">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="328" spans="1:68">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>7465751</v>
+      </c>
+      <c r="C328" t="s">
+        <v>68</v>
+      </c>
+      <c r="D328" t="s">
+        <v>69</v>
+      </c>
+      <c r="E328" s="2">
+        <v>45753.30208333334</v>
+      </c>
+      <c r="F328">
+        <v>33</v>
+      </c>
+      <c r="G328" t="s">
+        <v>85</v>
+      </c>
+      <c r="H328" t="s">
+        <v>70</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328">
+        <v>2</v>
+      </c>
+      <c r="L328">
+        <v>2</v>
+      </c>
+      <c r="M328">
+        <v>2</v>
+      </c>
+      <c r="N328">
+        <v>4</v>
+      </c>
+      <c r="O328" t="s">
+        <v>311</v>
+      </c>
+      <c r="P328" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q328">
+        <v>2.75</v>
+      </c>
+      <c r="R328">
+        <v>2.25</v>
+      </c>
+      <c r="S328">
+        <v>3.75</v>
+      </c>
+      <c r="T328">
+        <v>1.36</v>
+      </c>
+      <c r="U328">
+        <v>3</v>
+      </c>
+      <c r="V328">
+        <v>2.63</v>
+      </c>
+      <c r="W328">
+        <v>1.44</v>
+      </c>
+      <c r="X328">
+        <v>7</v>
+      </c>
+      <c r="Y328">
+        <v>1.1</v>
+      </c>
+      <c r="Z328">
+        <v>2.05</v>
+      </c>
+      <c r="AA328">
+        <v>3.7</v>
+      </c>
+      <c r="AB328">
+        <v>3</v>
+      </c>
+      <c r="AC328">
+        <v>1.02</v>
+      </c>
+      <c r="AD328">
+        <v>10</v>
+      </c>
+      <c r="AE328">
+        <v>1.19</v>
+      </c>
+      <c r="AF328">
+        <v>3.8</v>
+      </c>
+      <c r="AG328">
+        <v>1.8</v>
+      </c>
+      <c r="AH328">
+        <v>2</v>
+      </c>
+      <c r="AI328">
+        <v>1.67</v>
+      </c>
+      <c r="AJ328">
+        <v>2.1</v>
+      </c>
+      <c r="AK328">
+        <v>1.29</v>
+      </c>
+      <c r="AL328">
+        <v>1.27</v>
+      </c>
+      <c r="AM328">
+        <v>1.78</v>
+      </c>
+      <c r="AN328">
+        <v>1.75</v>
+      </c>
+      <c r="AO328">
+        <v>1.5</v>
+      </c>
+      <c r="AP328">
+        <v>1.71</v>
+      </c>
+      <c r="AQ328">
+        <v>1.47</v>
+      </c>
+      <c r="AR328">
+        <v>1.74</v>
+      </c>
+      <c r="AS328">
+        <v>1.28</v>
+      </c>
+      <c r="AT328">
+        <v>3.02</v>
+      </c>
+      <c r="AU328">
+        <v>-1</v>
+      </c>
+      <c r="AV328">
+        <v>-1</v>
+      </c>
+      <c r="AW328">
+        <v>-1</v>
+      </c>
+      <c r="AX328">
+        <v>-1</v>
+      </c>
+      <c r="AY328">
+        <v>-1</v>
+      </c>
+      <c r="AZ328">
+        <v>-1</v>
+      </c>
+      <c r="BA328">
+        <v>-1</v>
+      </c>
+      <c r="BB328">
+        <v>-1</v>
+      </c>
+      <c r="BC328">
+        <v>-1</v>
+      </c>
+      <c r="BD328">
+        <v>1.61</v>
+      </c>
+      <c r="BE328">
+        <v>6.75</v>
+      </c>
+      <c r="BF328">
+        <v>2.55</v>
+      </c>
+      <c r="BG328">
+        <v>1.24</v>
+      </c>
+      <c r="BH328">
+        <v>3.65</v>
+      </c>
+      <c r="BI328">
+        <v>1.41</v>
+      </c>
+      <c r="BJ328">
+        <v>2.65</v>
+      </c>
+      <c r="BK328">
+        <v>1.67</v>
+      </c>
+      <c r="BL328">
+        <v>2.07</v>
+      </c>
+      <c r="BM328">
+        <v>2.05</v>
+      </c>
+      <c r="BN328">
+        <v>1.68</v>
+      </c>
+      <c r="BO328">
+        <v>2.55</v>
+      </c>
+      <c r="BP328">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7465760</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45753.48958333334</v>
+      </c>
+      <c r="F329">
+        <v>33</v>
+      </c>
+      <c r="G329" t="s">
+        <v>77</v>
+      </c>
+      <c r="H329" t="s">
+        <v>82</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>2</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
+      </c>
+      <c r="N329">
+        <v>2</v>
+      </c>
+      <c r="O329" t="s">
+        <v>312</v>
+      </c>
+      <c r="P329" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q329">
+        <v>2.25</v>
+      </c>
+      <c r="R329">
+        <v>2.38</v>
+      </c>
+      <c r="S329">
+        <v>4</v>
+      </c>
+      <c r="T329">
+        <v>1.25</v>
+      </c>
+      <c r="U329">
+        <v>3.55</v>
+      </c>
+      <c r="V329">
+        <v>2.15</v>
+      </c>
+      <c r="W329">
+        <v>1.62</v>
+      </c>
+      <c r="X329">
+        <v>5.05</v>
+      </c>
+      <c r="Y329">
+        <v>1.12</v>
+      </c>
+      <c r="Z329">
+        <v>1.77</v>
+      </c>
+      <c r="AA329">
+        <v>3.95</v>
+      </c>
+      <c r="AB329">
+        <v>4</v>
+      </c>
+      <c r="AC329">
+        <v>1.01</v>
+      </c>
+      <c r="AD329">
+        <v>13</v>
+      </c>
+      <c r="AE329">
+        <v>1.17</v>
+      </c>
+      <c r="AF329">
+        <v>5</v>
+      </c>
+      <c r="AG329">
+        <v>1.5</v>
+      </c>
+      <c r="AH329">
+        <v>2.55</v>
+      </c>
+      <c r="AI329">
+        <v>1.48</v>
+      </c>
+      <c r="AJ329">
+        <v>2.45</v>
+      </c>
+      <c r="AK329">
+        <v>1.22</v>
+      </c>
+      <c r="AL329">
+        <v>1.2</v>
+      </c>
+      <c r="AM329">
+        <v>2</v>
+      </c>
+      <c r="AN329">
+        <v>2.19</v>
+      </c>
+      <c r="AO329">
+        <v>1.06</v>
+      </c>
+      <c r="AP329">
+        <v>2.24</v>
+      </c>
+      <c r="AQ329">
+        <v>1</v>
+      </c>
+      <c r="AR329">
+        <v>1.77</v>
+      </c>
+      <c r="AS329">
+        <v>1.76</v>
+      </c>
+      <c r="AT329">
+        <v>3.53</v>
+      </c>
+      <c r="AU329">
+        <v>-1</v>
+      </c>
+      <c r="AV329">
+        <v>-1</v>
+      </c>
+      <c r="AW329">
+        <v>-1</v>
+      </c>
+      <c r="AX329">
+        <v>-1</v>
+      </c>
+      <c r="AY329">
+        <v>-1</v>
+      </c>
+      <c r="AZ329">
+        <v>-1</v>
+      </c>
+      <c r="BA329">
+        <v>-1</v>
+      </c>
+      <c r="BB329">
+        <v>-1</v>
+      </c>
+      <c r="BC329">
+        <v>-1</v>
+      </c>
+      <c r="BD329">
+        <v>1.63</v>
+      </c>
+      <c r="BE329">
+        <v>6.75</v>
+      </c>
+      <c r="BF329">
+        <v>2.55</v>
+      </c>
+      <c r="BG329">
+        <v>1.26</v>
+      </c>
+      <c r="BH329">
+        <v>3.4</v>
+      </c>
+      <c r="BI329">
+        <v>1.46</v>
+      </c>
+      <c r="BJ329">
+        <v>2.5</v>
+      </c>
+      <c r="BK329">
+        <v>1.74</v>
+      </c>
+      <c r="BL329">
+        <v>1.96</v>
+      </c>
+      <c r="BM329">
+        <v>2.15</v>
+      </c>
+      <c r="BN329">
+        <v>1.61</v>
+      </c>
+      <c r="BO329">
+        <v>2.7</v>
+      </c>
+      <c r="BP329">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -69054,31 +69054,31 @@
         <v>3.13</v>
       </c>
       <c r="AU327">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV327">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW327">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AX327">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AY327">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ327">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="BA327">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB327">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC327">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD327">
         <v>2.12</v>
@@ -69260,31 +69260,31 @@
         <v>3.02</v>
       </c>
       <c r="AU328">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AV328">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW328">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AX328">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AY328">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AZ328">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA328">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BB328">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC328">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD328">
         <v>1.61</v>
@@ -69466,31 +69466,31 @@
         <v>3.53</v>
       </c>
       <c r="AU329">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV329">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW329">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AX329">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY329">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AZ329">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BA329">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BB329">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC329">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD329">
         <v>1.63</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="462">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -955,6 +955,12 @@
     <t>['25', '64']</t>
   </si>
   <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['52', '56']</t>
+  </si>
+  <si>
     <t>['5', '18']</t>
   </si>
   <si>
@@ -1145,9 +1151,6 @@
   </si>
   <si>
     <t>['36', '73', '79']</t>
-  </si>
-  <si>
-    <t>['40']</t>
   </si>
   <si>
     <t>['18', '32', '34', '67']</t>
@@ -1394,6 +1397,9 @@
   </si>
   <si>
     <t>['38', '90+7']</t>
+  </si>
+  <si>
+    <t>['14', '72']</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP329"/>
+  <dimension ref="A1:BP331"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2217,7 +2223,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -2423,7 +2429,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q4">
         <v>2.1</v>
@@ -2835,7 +2841,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q6">
         <v>4.33</v>
@@ -3041,7 +3047,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3247,7 +3253,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q8">
         <v>2.2</v>
@@ -3453,7 +3459,7 @@
         <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
@@ -3737,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3865,7 +3871,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4277,7 +4283,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q13">
         <v>2.45</v>
@@ -4895,7 +4901,7 @@
         <v>93</v>
       </c>
       <c r="P16" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -4973,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ16">
         <v>0.88</v>
@@ -5388,7 +5394,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5719,7 +5725,7 @@
         <v>93</v>
       </c>
       <c r="P20" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -6749,7 +6755,7 @@
         <v>105</v>
       </c>
       <c r="P25" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q25">
         <v>1.78</v>
@@ -6955,7 +6961,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q26">
         <v>2.2</v>
@@ -7161,7 +7167,7 @@
         <v>93</v>
       </c>
       <c r="P27" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q27">
         <v>2.39</v>
@@ -7573,7 +7579,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7857,7 +7863,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30">
         <v>1.47</v>
@@ -7985,7 +7991,7 @@
         <v>93</v>
       </c>
       <c r="P31" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q31">
         <v>2.7</v>
@@ -8603,7 +8609,7 @@
         <v>111</v>
       </c>
       <c r="P34" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -8809,7 +8815,7 @@
         <v>112</v>
       </c>
       <c r="P35" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q35">
         <v>3.6</v>
@@ -8887,7 +8893,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ35">
         <v>1.94</v>
@@ -9427,7 +9433,7 @@
         <v>93</v>
       </c>
       <c r="P38" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q38">
         <v>2.88</v>
@@ -9633,7 +9639,7 @@
         <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -10045,7 +10051,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q41">
         <v>2.41</v>
@@ -10869,7 +10875,7 @@
         <v>120</v>
       </c>
       <c r="P45" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11075,7 +11081,7 @@
         <v>93</v>
       </c>
       <c r="P46" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q46">
         <v>2.6</v>
@@ -11359,7 +11365,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11487,7 +11493,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11899,7 +11905,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -12105,7 +12111,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q51">
         <v>2.25</v>
@@ -12311,7 +12317,7 @@
         <v>91</v>
       </c>
       <c r="P52" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q52">
         <v>2.77</v>
@@ -12598,7 +12604,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ53">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR53">
         <v>2.41</v>
@@ -13135,7 +13141,7 @@
         <v>126</v>
       </c>
       <c r="P56" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q56">
         <v>2.3</v>
@@ -13547,7 +13553,7 @@
         <v>93</v>
       </c>
       <c r="P58" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13625,7 +13631,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ58">
         <v>1.31</v>
@@ -13834,7 +13840,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ59">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR59">
         <v>1.91</v>
@@ -14165,7 +14171,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q61">
         <v>2.54</v>
@@ -14371,7 +14377,7 @@
         <v>93</v>
       </c>
       <c r="P62" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14577,7 +14583,7 @@
         <v>131</v>
       </c>
       <c r="P63" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q63">
         <v>2.1</v>
@@ -15195,7 +15201,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -15607,7 +15613,7 @@
         <v>135</v>
       </c>
       <c r="P68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -15813,7 +15819,7 @@
         <v>93</v>
       </c>
       <c r="P69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q69">
         <v>2.88</v>
@@ -16019,7 +16025,7 @@
         <v>136</v>
       </c>
       <c r="P70" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -16097,7 +16103,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70">
         <v>1.13</v>
@@ -16225,7 +16231,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q71">
         <v>3.75</v>
@@ -16303,7 +16309,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ71">
         <v>1.88</v>
@@ -16431,7 +16437,7 @@
         <v>137</v>
       </c>
       <c r="P72" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -16637,7 +16643,7 @@
         <v>138</v>
       </c>
       <c r="P73" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q73">
         <v>2.3</v>
@@ -16843,7 +16849,7 @@
         <v>139</v>
       </c>
       <c r="P74" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q74">
         <v>1.83</v>
@@ -17049,7 +17055,7 @@
         <v>140</v>
       </c>
       <c r="P75" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -17667,7 +17673,7 @@
         <v>141</v>
       </c>
       <c r="P78" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q78">
         <v>2.3</v>
@@ -17873,7 +17879,7 @@
         <v>142</v>
       </c>
       <c r="P79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q79">
         <v>2.5</v>
@@ -18285,7 +18291,7 @@
         <v>143</v>
       </c>
       <c r="P81" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q81">
         <v>2.88</v>
@@ -18697,7 +18703,7 @@
         <v>144</v>
       </c>
       <c r="P83" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q83">
         <v>2.7</v>
@@ -18903,7 +18909,7 @@
         <v>145</v>
       </c>
       <c r="P84" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q84">
         <v>4.1</v>
@@ -18984,7 +18990,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ84">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR84">
         <v>1.34</v>
@@ -19393,7 +19399,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ86">
         <v>1.12</v>
@@ -19521,7 +19527,7 @@
         <v>148</v>
       </c>
       <c r="P87" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q87">
         <v>2.5</v>
@@ -19599,7 +19605,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ87">
         <v>1.47</v>
@@ -20139,7 +20145,7 @@
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q90">
         <v>3.04</v>
@@ -20551,7 +20557,7 @@
         <v>152</v>
       </c>
       <c r="P92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q92">
         <v>2.75</v>
@@ -20963,7 +20969,7 @@
         <v>154</v>
       </c>
       <c r="P94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -21041,7 +21047,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ94">
         <v>1.19</v>
@@ -21169,7 +21175,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21375,7 +21381,7 @@
         <v>156</v>
       </c>
       <c r="P96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -21581,7 +21587,7 @@
         <v>157</v>
       </c>
       <c r="P97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q97">
         <v>2.6</v>
@@ -21993,7 +21999,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -22405,7 +22411,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q101">
         <v>1.91</v>
@@ -22611,7 +22617,7 @@
         <v>160</v>
       </c>
       <c r="P102" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q102">
         <v>2.05</v>
@@ -23023,7 +23029,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q104">
         <v>3.75</v>
@@ -23310,7 +23316,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ105">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR105">
         <v>1.49</v>
@@ -24131,7 +24137,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ109">
         <v>1.29</v>
@@ -24259,7 +24265,7 @@
         <v>166</v>
       </c>
       <c r="P110" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q110">
         <v>2.63</v>
@@ -24465,7 +24471,7 @@
         <v>167</v>
       </c>
       <c r="P111" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -24671,7 +24677,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -25289,7 +25295,7 @@
         <v>171</v>
       </c>
       <c r="P115" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q115">
         <v>1.95</v>
@@ -25495,7 +25501,7 @@
         <v>172</v>
       </c>
       <c r="P116" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -25701,7 +25707,7 @@
         <v>130</v>
       </c>
       <c r="P117" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q117">
         <v>2.3</v>
@@ -25907,7 +25913,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q118">
         <v>3.2</v>
@@ -26319,7 +26325,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q120">
         <v>2.63</v>
@@ -26525,7 +26531,7 @@
         <v>168</v>
       </c>
       <c r="P121" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q121">
         <v>3.1</v>
@@ -26731,7 +26737,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26809,7 +26815,7 @@
         <v>2</v>
       </c>
       <c r="AP122">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122">
         <v>1.88</v>
@@ -26937,7 +26943,7 @@
         <v>93</v>
       </c>
       <c r="P123" t="s">
-        <v>377</v>
+        <v>313</v>
       </c>
       <c r="Q123">
         <v>2.69</v>
@@ -27143,7 +27149,7 @@
         <v>175</v>
       </c>
       <c r="P124" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q124">
         <v>2.26</v>
@@ -27349,7 +27355,7 @@
         <v>93</v>
       </c>
       <c r="P125" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q125">
         <v>4.37</v>
@@ -27430,7 +27436,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR125">
         <v>1.31</v>
@@ -27967,7 +27973,7 @@
         <v>176</v>
       </c>
       <c r="P128" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q128">
         <v>3</v>
@@ -28379,7 +28385,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q130">
         <v>3</v>
@@ -28457,7 +28463,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ130">
         <v>0.5600000000000001</v>
@@ -28585,7 +28591,7 @@
         <v>178</v>
       </c>
       <c r="P131" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q131">
         <v>3.75</v>
@@ -29615,7 +29621,7 @@
         <v>180</v>
       </c>
       <c r="P136" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q136">
         <v>2.25</v>
@@ -31469,7 +31475,7 @@
         <v>143</v>
       </c>
       <c r="P145" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q145">
         <v>4</v>
@@ -31675,7 +31681,7 @@
         <v>93</v>
       </c>
       <c r="P146" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q146">
         <v>4</v>
@@ -31881,7 +31887,7 @@
         <v>93</v>
       </c>
       <c r="P147" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q147">
         <v>3.6</v>
@@ -32087,7 +32093,7 @@
         <v>189</v>
       </c>
       <c r="P148" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q148">
         <v>3.75</v>
@@ -32165,7 +32171,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ148">
         <v>1</v>
@@ -32499,7 +32505,7 @@
         <v>191</v>
       </c>
       <c r="P150" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q150">
         <v>1.91</v>
@@ -32705,7 +32711,7 @@
         <v>93</v>
       </c>
       <c r="P151" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q151">
         <v>3.4</v>
@@ -33117,7 +33123,7 @@
         <v>193</v>
       </c>
       <c r="P153" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q153">
         <v>4</v>
@@ -33195,10 +33201,10 @@
         <v>1.5</v>
       </c>
       <c r="AP153">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ153">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR153">
         <v>1.87</v>
@@ -33323,7 +33329,7 @@
         <v>194</v>
       </c>
       <c r="P154" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q154">
         <v>2.75</v>
@@ -33529,7 +33535,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q155">
         <v>1.91</v>
@@ -34228,7 +34234,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ158">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR158">
         <v>1.63</v>
@@ -34559,7 +34565,7 @@
         <v>144</v>
       </c>
       <c r="P160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q160">
         <v>2.25</v>
@@ -34843,7 +34849,7 @@
         <v>1.75</v>
       </c>
       <c r="AP161">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ161">
         <v>1.53</v>
@@ -34971,7 +34977,7 @@
         <v>200</v>
       </c>
       <c r="P162" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q162">
         <v>2.55</v>
@@ -35795,7 +35801,7 @@
         <v>203</v>
       </c>
       <c r="P166" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q166">
         <v>3.1</v>
@@ -36619,7 +36625,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q170">
         <v>2.95</v>
@@ -36825,7 +36831,7 @@
         <v>207</v>
       </c>
       <c r="P171" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36903,7 +36909,7 @@
         <v>0.5</v>
       </c>
       <c r="AP171">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ171">
         <v>0.5600000000000001</v>
@@ -37237,7 +37243,7 @@
         <v>208</v>
       </c>
       <c r="P173" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q173">
         <v>2.6</v>
@@ -38061,7 +38067,7 @@
         <v>211</v>
       </c>
       <c r="P177" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q177">
         <v>2.75</v>
@@ -38142,7 +38148,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ177">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR177">
         <v>1.93</v>
@@ -38267,7 +38273,7 @@
         <v>212</v>
       </c>
       <c r="P178" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q178">
         <v>3</v>
@@ -38679,7 +38685,7 @@
         <v>93</v>
       </c>
       <c r="P180" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q180">
         <v>3.4</v>
@@ -38757,7 +38763,7 @@
         <v>1.44</v>
       </c>
       <c r="AP180">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ180">
         <v>1.47</v>
@@ -38885,7 +38891,7 @@
         <v>214</v>
       </c>
       <c r="P181" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q181">
         <v>3.75</v>
@@ -39503,7 +39509,7 @@
         <v>216</v>
       </c>
       <c r="P184" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q184">
         <v>3.65</v>
@@ -39581,7 +39587,7 @@
         <v>2.25</v>
       </c>
       <c r="AP184">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ184">
         <v>1.94</v>
@@ -39709,7 +39715,7 @@
         <v>217</v>
       </c>
       <c r="P185" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q185">
         <v>2.4</v>
@@ -39915,7 +39921,7 @@
         <v>93</v>
       </c>
       <c r="P186" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q186">
         <v>2.75</v>
@@ -40533,7 +40539,7 @@
         <v>219</v>
       </c>
       <c r="P189" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41151,7 +41157,7 @@
         <v>221</v>
       </c>
       <c r="P192" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q192">
         <v>3.4</v>
@@ -41229,7 +41235,7 @@
         <v>1.78</v>
       </c>
       <c r="AP192">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ192">
         <v>1.19</v>
@@ -41357,7 +41363,7 @@
         <v>222</v>
       </c>
       <c r="P193" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41563,7 +41569,7 @@
         <v>93</v>
       </c>
       <c r="P194" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q194">
         <v>1.91</v>
@@ -41769,7 +41775,7 @@
         <v>223</v>
       </c>
       <c r="P195" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q195">
         <v>2.25</v>
@@ -41975,7 +41981,7 @@
         <v>93</v>
       </c>
       <c r="P196" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q196">
         <v>2.3</v>
@@ -43005,7 +43011,7 @@
         <v>227</v>
       </c>
       <c r="P201" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q201">
         <v>3.5</v>
@@ -43623,7 +43629,7 @@
         <v>140</v>
       </c>
       <c r="P204" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q204">
         <v>3.75</v>
@@ -44035,7 +44041,7 @@
         <v>156</v>
       </c>
       <c r="P206" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q206">
         <v>2.4</v>
@@ -44241,7 +44247,7 @@
         <v>229</v>
       </c>
       <c r="P207" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q207">
         <v>2.75</v>
@@ -44319,7 +44325,7 @@
         <v>0.9</v>
       </c>
       <c r="AP207">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ207">
         <v>0.71</v>
@@ -44653,7 +44659,7 @@
         <v>93</v>
       </c>
       <c r="P209" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q209">
         <v>4.2</v>
@@ -45065,7 +45071,7 @@
         <v>231</v>
       </c>
       <c r="P211" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q211">
         <v>2.2</v>
@@ -45889,7 +45895,7 @@
         <v>235</v>
       </c>
       <c r="P215" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q215">
         <v>2.15</v>
@@ -46507,7 +46513,7 @@
         <v>104</v>
       </c>
       <c r="P218" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q218">
         <v>4.5</v>
@@ -46585,7 +46591,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ218">
         <v>1.13</v>
@@ -46713,7 +46719,7 @@
         <v>237</v>
       </c>
       <c r="P219" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q219">
         <v>3.6</v>
@@ -46919,7 +46925,7 @@
         <v>93</v>
       </c>
       <c r="P220" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q220">
         <v>3.2</v>
@@ -48236,7 +48242,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ226">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR226">
         <v>1.71</v>
@@ -48773,7 +48779,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q229">
         <v>2.88</v>
@@ -49391,7 +49397,7 @@
         <v>249</v>
       </c>
       <c r="P232" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q232">
         <v>1.91</v>
@@ -50009,7 +50015,7 @@
         <v>241</v>
       </c>
       <c r="P235" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q235">
         <v>1.73</v>
@@ -50215,7 +50221,7 @@
         <v>252</v>
       </c>
       <c r="P236" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q236">
         <v>3.2</v>
@@ -50627,7 +50633,7 @@
         <v>104</v>
       </c>
       <c r="P238" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q238">
         <v>2.88</v>
@@ -50708,7 +50714,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ238">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR238">
         <v>1.84</v>
@@ -50911,7 +50917,7 @@
         <v>1.45</v>
       </c>
       <c r="AP239">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ239">
         <v>1.18</v>
@@ -51451,7 +51457,7 @@
         <v>257</v>
       </c>
       <c r="P242" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q242">
         <v>2.2</v>
@@ -51657,7 +51663,7 @@
         <v>258</v>
       </c>
       <c r="P243" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q243">
         <v>2.5</v>
@@ -51738,7 +51744,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ243">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR243">
         <v>1.91</v>
@@ -51863,7 +51869,7 @@
         <v>93</v>
       </c>
       <c r="P244" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q244">
         <v>3.1</v>
@@ -52481,7 +52487,7 @@
         <v>260</v>
       </c>
       <c r="P247" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q247">
         <v>4.5</v>
@@ -52893,7 +52899,7 @@
         <v>262</v>
       </c>
       <c r="P249" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q249">
         <v>4.5</v>
@@ -54129,7 +54135,7 @@
         <v>265</v>
       </c>
       <c r="P255" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q255">
         <v>3.25</v>
@@ -55365,7 +55371,7 @@
         <v>269</v>
       </c>
       <c r="P261" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q261">
         <v>3.1</v>
@@ -55571,7 +55577,7 @@
         <v>93</v>
       </c>
       <c r="P262" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -55777,7 +55783,7 @@
         <v>270</v>
       </c>
       <c r="P263" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q263">
         <v>4</v>
@@ -55983,7 +55989,7 @@
         <v>235</v>
       </c>
       <c r="P264" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q264">
         <v>2.2</v>
@@ -56189,7 +56195,7 @@
         <v>271</v>
       </c>
       <c r="P265" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q265">
         <v>3.35</v>
@@ -56270,7 +56276,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ265">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR265">
         <v>1.71</v>
@@ -56395,7 +56401,7 @@
         <v>272</v>
       </c>
       <c r="P266" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q266">
         <v>4</v>
@@ -56601,7 +56607,7 @@
         <v>112</v>
       </c>
       <c r="P267" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q267">
         <v>4</v>
@@ -56807,7 +56813,7 @@
         <v>273</v>
       </c>
       <c r="P268" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q268">
         <v>3.75</v>
@@ -57219,7 +57225,7 @@
         <v>142</v>
       </c>
       <c r="P270" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q270">
         <v>4.5</v>
@@ -57425,7 +57431,7 @@
         <v>187</v>
       </c>
       <c r="P271" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q271">
         <v>3.25</v>
@@ -57503,7 +57509,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP271">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ271">
         <v>0.71</v>
@@ -57837,7 +57843,7 @@
         <v>276</v>
       </c>
       <c r="P273" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q273">
         <v>2.05</v>
@@ -58249,7 +58255,7 @@
         <v>277</v>
       </c>
       <c r="P275" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q275">
         <v>2.2</v>
@@ -58455,7 +58461,7 @@
         <v>278</v>
       </c>
       <c r="P276" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q276">
         <v>2.1</v>
@@ -58661,7 +58667,7 @@
         <v>93</v>
       </c>
       <c r="P277" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q277">
         <v>2.75</v>
@@ -58867,7 +58873,7 @@
         <v>156</v>
       </c>
       <c r="P278" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q278">
         <v>3.5</v>
@@ -58945,7 +58951,7 @@
         <v>1.07</v>
       </c>
       <c r="AP278">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ278">
         <v>1.12</v>
@@ -59073,7 +59079,7 @@
         <v>103</v>
       </c>
       <c r="P279" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q279">
         <v>3.1</v>
@@ -59151,7 +59157,7 @@
         <v>0.46</v>
       </c>
       <c r="AP279">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ279">
         <v>0.5600000000000001</v>
@@ -59279,7 +59285,7 @@
         <v>279</v>
       </c>
       <c r="P280" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q280">
         <v>1.73</v>
@@ -59485,7 +59491,7 @@
         <v>93</v>
       </c>
       <c r="P281" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q281">
         <v>4.53</v>
@@ -59975,7 +59981,7 @@
         <v>0.62</v>
       </c>
       <c r="AP283">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ283">
         <v>0.5</v>
@@ -60390,7 +60396,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ285">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR285">
         <v>1.71</v>
@@ -60515,7 +60521,7 @@
         <v>283</v>
       </c>
       <c r="P286" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q286">
         <v>2.57</v>
@@ -60721,7 +60727,7 @@
         <v>93</v>
       </c>
       <c r="P287" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q287">
         <v>3.7</v>
@@ -61545,7 +61551,7 @@
         <v>286</v>
       </c>
       <c r="P291" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q291">
         <v>2.5</v>
@@ -61957,7 +61963,7 @@
         <v>93</v>
       </c>
       <c r="P293" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q293">
         <v>3.25</v>
@@ -62035,7 +62041,7 @@
         <v>0.93</v>
       </c>
       <c r="AP293">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ293">
         <v>1</v>
@@ -62163,7 +62169,7 @@
         <v>288</v>
       </c>
       <c r="P294" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q294">
         <v>2.5</v>
@@ -62575,7 +62581,7 @@
         <v>93</v>
       </c>
       <c r="P296" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62781,7 +62787,7 @@
         <v>93</v>
       </c>
       <c r="P297" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q297">
         <v>3.6</v>
@@ -63193,7 +63199,7 @@
         <v>291</v>
       </c>
       <c r="P299" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q299">
         <v>4</v>
@@ -64304,7 +64310,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ304">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR304">
         <v>1.72</v>
@@ -64635,7 +64641,7 @@
         <v>93</v>
       </c>
       <c r="P306" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q306">
         <v>4.75</v>
@@ -65253,7 +65259,7 @@
         <v>297</v>
       </c>
       <c r="P309" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q309">
         <v>3</v>
@@ -65665,7 +65671,7 @@
         <v>298</v>
       </c>
       <c r="P311" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q311">
         <v>2.4</v>
@@ -65871,7 +65877,7 @@
         <v>299</v>
       </c>
       <c r="P312" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q312">
         <v>2.88</v>
@@ -66283,7 +66289,7 @@
         <v>301</v>
       </c>
       <c r="P314" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q314">
         <v>3.5</v>
@@ -66489,7 +66495,7 @@
         <v>102</v>
       </c>
       <c r="P315" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q315">
         <v>2.38</v>
@@ -66695,7 +66701,7 @@
         <v>302</v>
       </c>
       <c r="P316" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q316">
         <v>2.2</v>
@@ -66901,7 +66907,7 @@
         <v>93</v>
       </c>
       <c r="P317" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q317">
         <v>4</v>
@@ -67185,7 +67191,7 @@
         <v>0.53</v>
       </c>
       <c r="AP318">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ318">
         <v>0.5600000000000001</v>
@@ -67313,7 +67319,7 @@
         <v>303</v>
       </c>
       <c r="P319" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q319">
         <v>3.4</v>
@@ -67597,7 +67603,7 @@
         <v>1.27</v>
       </c>
       <c r="AP320">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AQ320">
         <v>1.18</v>
@@ -67725,7 +67731,7 @@
         <v>304</v>
       </c>
       <c r="P321" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q321">
         <v>2.3</v>
@@ -68755,7 +68761,7 @@
         <v>309</v>
       </c>
       <c r="P326" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q326">
         <v>4.2</v>
@@ -68961,7 +68967,7 @@
         <v>310</v>
       </c>
       <c r="P327" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q327">
         <v>3.25</v>
@@ -69167,7 +69173,7 @@
         <v>311</v>
       </c>
       <c r="P328" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q328">
         <v>2.75</v>
@@ -69530,6 +69536,418 @@
       </c>
       <c r="BP329">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7465762</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45754.625</v>
+      </c>
+      <c r="F330">
+        <v>33</v>
+      </c>
+      <c r="G330" t="s">
+        <v>84</v>
+      </c>
+      <c r="H330" t="s">
+        <v>76</v>
+      </c>
+      <c r="I330">
+        <v>1</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>1</v>
+      </c>
+      <c r="L330">
+        <v>1</v>
+      </c>
+      <c r="M330">
+        <v>1</v>
+      </c>
+      <c r="N330">
+        <v>2</v>
+      </c>
+      <c r="O330" t="s">
+        <v>313</v>
+      </c>
+      <c r="P330" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q330">
+        <v>6</v>
+      </c>
+      <c r="R330">
+        <v>2.4</v>
+      </c>
+      <c r="S330">
+        <v>2</v>
+      </c>
+      <c r="T330">
+        <v>1.3</v>
+      </c>
+      <c r="U330">
+        <v>3.4</v>
+      </c>
+      <c r="V330">
+        <v>2.5</v>
+      </c>
+      <c r="W330">
+        <v>1.5</v>
+      </c>
+      <c r="X330">
+        <v>6</v>
+      </c>
+      <c r="Y330">
+        <v>1.13</v>
+      </c>
+      <c r="Z330">
+        <v>6</v>
+      </c>
+      <c r="AA330">
+        <v>4.5</v>
+      </c>
+      <c r="AB330">
+        <v>1.48</v>
+      </c>
+      <c r="AC330">
+        <v>1.02</v>
+      </c>
+      <c r="AD330">
+        <v>13.2</v>
+      </c>
+      <c r="AE330">
+        <v>1.15</v>
+      </c>
+      <c r="AF330">
+        <v>4.2</v>
+      </c>
+      <c r="AG330">
+        <v>1.62</v>
+      </c>
+      <c r="AH330">
+        <v>2.25</v>
+      </c>
+      <c r="AI330">
+        <v>1.8</v>
+      </c>
+      <c r="AJ330">
+        <v>1.91</v>
+      </c>
+      <c r="AK330">
+        <v>2.58</v>
+      </c>
+      <c r="AL330">
+        <v>1.18</v>
+      </c>
+      <c r="AM330">
+        <v>1.12</v>
+      </c>
+      <c r="AN330">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AO330">
+        <v>1.67</v>
+      </c>
+      <c r="AP330">
+        <v>0.71</v>
+      </c>
+      <c r="AQ330">
+        <v>1.63</v>
+      </c>
+      <c r="AR330">
+        <v>1.43</v>
+      </c>
+      <c r="AS330">
+        <v>1.49</v>
+      </c>
+      <c r="AT330">
+        <v>2.92</v>
+      </c>
+      <c r="AU330">
+        <v>6</v>
+      </c>
+      <c r="AV330">
+        <v>11</v>
+      </c>
+      <c r="AW330">
+        <v>5</v>
+      </c>
+      <c r="AX330">
+        <v>13</v>
+      </c>
+      <c r="AY330">
+        <v>11</v>
+      </c>
+      <c r="AZ330">
+        <v>24</v>
+      </c>
+      <c r="BA330">
+        <v>3</v>
+      </c>
+      <c r="BB330">
+        <v>4</v>
+      </c>
+      <c r="BC330">
+        <v>7</v>
+      </c>
+      <c r="BD330">
+        <v>4.3</v>
+      </c>
+      <c r="BE330">
+        <v>10.25</v>
+      </c>
+      <c r="BF330">
+        <v>1.29</v>
+      </c>
+      <c r="BG330">
+        <v>1.24</v>
+      </c>
+      <c r="BH330">
+        <v>3.55</v>
+      </c>
+      <c r="BI330">
+        <v>1.33</v>
+      </c>
+      <c r="BJ330">
+        <v>2.83</v>
+      </c>
+      <c r="BK330">
+        <v>1.69</v>
+      </c>
+      <c r="BL330">
+        <v>2.13</v>
+      </c>
+      <c r="BM330">
+        <v>2.07</v>
+      </c>
+      <c r="BN330">
+        <v>1.73</v>
+      </c>
+      <c r="BO330">
+        <v>2.6</v>
+      </c>
+      <c r="BP330">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7465678</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45754.625</v>
+      </c>
+      <c r="F331">
+        <v>26</v>
+      </c>
+      <c r="G331" t="s">
+        <v>78</v>
+      </c>
+      <c r="H331" t="s">
+        <v>79</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>2</v>
+      </c>
+      <c r="M331">
+        <v>2</v>
+      </c>
+      <c r="N331">
+        <v>4</v>
+      </c>
+      <c r="O331" t="s">
+        <v>314</v>
+      </c>
+      <c r="P331" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q331">
+        <v>2</v>
+      </c>
+      <c r="R331">
+        <v>2.63</v>
+      </c>
+      <c r="S331">
+        <v>4.75</v>
+      </c>
+      <c r="T331">
+        <v>1.22</v>
+      </c>
+      <c r="U331">
+        <v>4</v>
+      </c>
+      <c r="V331">
+        <v>2</v>
+      </c>
+      <c r="W331">
+        <v>1.73</v>
+      </c>
+      <c r="X331">
+        <v>4.33</v>
+      </c>
+      <c r="Y331">
+        <v>1.2</v>
+      </c>
+      <c r="Z331">
+        <v>1.55</v>
+      </c>
+      <c r="AA331">
+        <v>4.75</v>
+      </c>
+      <c r="AB331">
+        <v>4.75</v>
+      </c>
+      <c r="AC331">
+        <v>1.01</v>
+      </c>
+      <c r="AD331">
+        <v>17</v>
+      </c>
+      <c r="AE331">
+        <v>1.1</v>
+      </c>
+      <c r="AF331">
+        <v>6.5</v>
+      </c>
+      <c r="AG331">
+        <v>1.36</v>
+      </c>
+      <c r="AH331">
+        <v>3.1</v>
+      </c>
+      <c r="AI331">
+        <v>1.44</v>
+      </c>
+      <c r="AJ331">
+        <v>2.63</v>
+      </c>
+      <c r="AK331">
+        <v>1.17</v>
+      </c>
+      <c r="AL331">
+        <v>1.15</v>
+      </c>
+      <c r="AM331">
+        <v>2.45</v>
+      </c>
+      <c r="AN331">
+        <v>1.27</v>
+      </c>
+      <c r="AO331">
+        <v>0.88</v>
+      </c>
+      <c r="AP331">
+        <v>1.25</v>
+      </c>
+      <c r="AQ331">
+        <v>0.88</v>
+      </c>
+      <c r="AR331">
+        <v>1.8</v>
+      </c>
+      <c r="AS331">
+        <v>1.34</v>
+      </c>
+      <c r="AT331">
+        <v>3.14</v>
+      </c>
+      <c r="AU331">
+        <v>7</v>
+      </c>
+      <c r="AV331">
+        <v>9</v>
+      </c>
+      <c r="AW331">
+        <v>3</v>
+      </c>
+      <c r="AX331">
+        <v>8</v>
+      </c>
+      <c r="AY331">
+        <v>10</v>
+      </c>
+      <c r="AZ331">
+        <v>17</v>
+      </c>
+      <c r="BA331">
+        <v>4</v>
+      </c>
+      <c r="BB331">
+        <v>5</v>
+      </c>
+      <c r="BC331">
+        <v>9</v>
+      </c>
+      <c r="BD331">
+        <v>1.49</v>
+      </c>
+      <c r="BE331">
+        <v>6.75</v>
+      </c>
+      <c r="BF331">
+        <v>2.9</v>
+      </c>
+      <c r="BG331">
+        <v>1.22</v>
+      </c>
+      <c r="BH331">
+        <v>3.7</v>
+      </c>
+      <c r="BI331">
+        <v>1.4</v>
+      </c>
+      <c r="BJ331">
+        <v>2.7</v>
+      </c>
+      <c r="BK331">
+        <v>1.66</v>
+      </c>
+      <c r="BL331">
+        <v>2.08</v>
+      </c>
+      <c r="BM331">
+        <v>2.02</v>
+      </c>
+      <c r="BN331">
+        <v>1.7</v>
+      </c>
+      <c r="BO331">
+        <v>2.5</v>
+      </c>
+      <c r="BP331">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Netherlands Eerste Divisie_20242025.xlsx
@@ -21796,46 +21796,46 @@
         <v>93</v>
       </c>
       <c r="Q98">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S98">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T98">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U98">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V98">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W98">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X98">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y98">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z98">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA98">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB98">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD98">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE98">
         <v>0</v>
@@ -21844,16 +21844,16 @@
         <v>0</v>
       </c>
       <c r="AG98">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH98">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI98">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ98">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK98">
         <v>0</v>
@@ -21934,7 +21934,7 @@
         <v>0</v>
       </c>
       <c r="BK98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL98">
         <v>0</v>
@@ -65468,46 +65468,46 @@
         <v>93</v>
       </c>
       <c r="Q310">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R310">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S310">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T310">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U310">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V310">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="W310">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X310">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y310">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z310">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA310">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB310">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AC310">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD310">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE310">
         <v>0</v>
@@ -65516,16 +65516,16 @@
         <v>0</v>
       </c>
       <c r="AG310">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH310">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI310">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ310">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK310">
         <v>0</v>
